--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -828,16 +828,16 @@
         <v>26.16159481048584</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.42356851577759</v>
+        <v>15.42356850624084</v>
       </c>
       <c r="AH2" t="n">
         <v>0.2384566675152635</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.100681271829877</v>
+        <v>1.100681273128776</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.696208940474687</v>
+        <v>0.6962089415234916</v>
       </c>
       <c r="AK2" t="n">
         <v>34.90000152587891</v>
@@ -876,13 +876,13 @@
         <v>2.000651907352315</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.170706992072154</v>
+        <v>4.170707385554227</v>
       </c>
       <c r="AX2" t="n">
         <v>2.438729557726636</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.436553262001023</v>
+        <v>4.436551522069297</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1220,25 +1220,25 @@
         <v>443.562084350586</v>
       </c>
       <c r="AG4" t="n">
-        <v>429.3729141235352</v>
+        <v>429.3729138183594</v>
       </c>
       <c r="AH4" t="n">
         <v>0.1265616017172346</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1637902526456576</v>
+        <v>0.1637902534728188</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.03304626295772439</v>
+        <v>0.03304626369195973</v>
       </c>
       <c r="AK4" t="n">
-        <v>537.6463623046875</v>
+        <v>537.6464233398438</v>
       </c>
       <c r="AL4" t="n">
         <v>352.1670227050781</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.0705786419441109</v>
+        <v>-0.07057874745467574</v>
       </c>
       <c r="AN4" t="n">
         <v>0.4189290308011164</v>
@@ -1268,7 +1268,7 @@
         <v>0.01780069811924512</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.715039337402992</v>
+        <v>0.715039696671345</v>
       </c>
       <c r="AX4" t="n">
         <v>0.06328541001064969</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="X5" t="n">
-        <v>61545304064</v>
+        <v>57480011776</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>61545304064</v>
+        <v>57480011776</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1606,16 +1606,16 @@
         <v>348.3498400878906</v>
       </c>
       <c r="AG6" t="n">
-        <v>335.496290435791</v>
+        <v>335.4962907409668</v>
       </c>
       <c r="AH6" t="n">
         <v>-0.02839056458391731</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.008833781784702843</v>
+        <v>0.008833780867042673</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.03831204701370483</v>
+        <v>0.03831204606923033</v>
       </c>
       <c r="AK6" t="n">
         <v>402.1211853027344</v>
@@ -1651,16 +1651,16 @@
         <v>0.1061492269482283</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.4452923758176119</v>
+        <v>0.4452924699901299</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.363091716724915</v>
+        <v>1.363091968477496</v>
       </c>
       <c r="AX6" t="n">
         <v>0.0760538736323817</v>
       </c>
       <c r="AY6" t="n">
-        <v>135.0729807632123</v>
+        <v>135.0729677202418</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
@@ -2200,13 +2200,13 @@
         <v>-0.042012226659772</v>
       </c>
       <c r="AK9" t="n">
-        <v>777.7011108398438</v>
+        <v>777.7010498046875</v>
       </c>
       <c r="AL9" t="n">
         <v>525.233154296875</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.2069318007464376</v>
+        <v>-0.2069317385052443</v>
       </c>
       <c r="AN9" t="n">
         <v>0.1742785360853973</v>
@@ -2242,7 +2242,7 @@
         <v>-0.05002960325991213</v>
       </c>
       <c r="AY9" t="n">
-        <v>15.27481699173508</v>
+        <v>15.27481862994328</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
@@ -2384,25 +2384,25 @@
         <v>139.7487602233887</v>
       </c>
       <c r="AG10" t="n">
-        <v>167.9171455764771</v>
+        <v>167.9171445083618</v>
       </c>
       <c r="AH10" t="n">
         <v>0.136181806017361</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.05441461481382026</v>
+        <v>-0.05441460879898385</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1677516923979584</v>
+        <v>-0.1677516871040553</v>
       </c>
       <c r="AK10" t="n">
-        <v>324.6299438476562</v>
+        <v>324.6299743652344</v>
       </c>
       <c r="AL10" t="n">
         <v>114.9899978637695</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.5108892393062489</v>
+        <v>-0.5108892852862169</v>
       </c>
       <c r="AN10" t="n">
         <v>0.3808157381427735</v>
@@ -2426,19 +2426,19 @@
         <v>-0.2477934876322756</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.05495424610779409</v>
+        <v>0.0549543530604486</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.3101816723401294</v>
+        <v>-0.3101816266109128</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.8988399087167611</v>
+        <v>0.8988404284641962</v>
       </c>
       <c r="AX10" t="n">
         <v>-0.180872166208434</v>
       </c>
       <c r="AY10" t="n">
-        <v>3159.57997278125</v>
+        <v>3159.580910252624</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2630,7 +2630,7 @@
         <v>-0.2809646650765267</v>
       </c>
       <c r="AY11" t="n">
-        <v>628.6112859901624</v>
+        <v>628.6113927105962</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>15062878208</v>
+        <v>14999209984</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>15062878208</v>
+        <v>14999209984</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="X18" t="n">
-        <v>29658468352</v>
+        <v>29704345600</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>29658468352</v>
+        <v>29704345600</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -4710,16 +4710,16 @@
         <v>383.6615997314453</v>
       </c>
       <c r="AG22" t="n">
-        <v>369.0301217651367</v>
+        <v>369.0301223754883</v>
       </c>
       <c r="AH22" t="n">
         <v>-0.06714668826120085</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.03016048612892341</v>
+        <v>-0.03016048773297431</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.03964846526978261</v>
+        <v>0.03964846355027207</v>
       </c>
       <c r="AK22" t="n">
         <v>480.8090515136719</v>
@@ -4755,16 +4755,16 @@
         <v>0.03895418071335155</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.07653956505391668</v>
+        <v>0.07653966387472577</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.88012106085648</v>
+        <v>6.880120398999536</v>
       </c>
       <c r="AX22" t="n">
         <v>0.03336521571714868</v>
       </c>
       <c r="AY22" t="n">
-        <v>314.1662079586145</v>
+        <v>314.1660756197175</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
@@ -4906,16 +4906,16 @@
         <v>240.2989535522461</v>
       </c>
       <c r="AG23" t="n">
-        <v>258.9958300018311</v>
+        <v>258.9958296966553</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.02250927056751262</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.09307420359629803</v>
+        <v>-0.09307420252766385</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.07218987444490044</v>
+        <v>-0.07218987335165816</v>
       </c>
       <c r="AK23" t="n">
         <v>326.8851013183594</v>
@@ -4954,13 +4954,13 @@
         <v>-0.03031257649624608</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.140739562804514</v>
+        <v>1.140739265101554</v>
       </c>
       <c r="AX23" t="n">
         <v>-0.1777875450691238</v>
       </c>
       <c r="AY23" t="n">
-        <v>162.749263527264</v>
+        <v>162.7492907438941</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5102,16 +5102,16 @@
         <v>210.5663995361328</v>
       </c>
       <c r="AG24" t="n">
-        <v>196.5254197692871</v>
+        <v>196.525419998169</v>
       </c>
       <c r="AH24" t="n">
         <v>0.09400170738457336</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1721638904564351</v>
+        <v>0.1721638890912831</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.07144612530699201</v>
+        <v>0.07144612405914041</v>
       </c>
       <c r="AK24" t="n">
         <v>235.465576171875</v>
@@ -5147,16 +5147,16 @@
         <v>0.2627482859869141</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.3810729481970245</v>
+        <v>0.381072821855476</v>
       </c>
       <c r="AW24" t="n">
-        <v>9.188505643180138</v>
+        <v>9.188503924187904</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2212918167744309</v>
       </c>
       <c r="AY24" t="n">
-        <v>6132.271052672297</v>
+        <v>6132.271660999741</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5298,16 +5298,16 @@
         <v>314.9877679443359</v>
       </c>
       <c r="AG25" t="n">
-        <v>283.4390251922607</v>
+        <v>283.4390239715576</v>
       </c>
       <c r="AH25" t="n">
         <v>0.01581722778913641</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.1288847786703433</v>
+        <v>0.1288847835321763</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.1113069829769393</v>
+        <v>0.1113069877630688</v>
       </c>
       <c r="AK25" t="n">
         <v>339.7869262695312</v>
@@ -5343,16 +5343,16 @@
         <v>0.2334193039579191</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.3398638549246091</v>
+        <v>0.3398637693131061</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.142434353730689</v>
+        <v>1.142434134840745</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.18387125439614</v>
+        <v>0.1838711207212904</v>
       </c>
       <c r="AY25" t="n">
-        <v>3259.927328012307</v>
+        <v>3259.927823226583</v>
       </c>
       <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
@@ -6316,13 +6316,13 @@
         <v>2.9118008961657</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.9282622210991542</v>
+        <v>0.9282620730429174</v>
       </c>
       <c r="AX30" t="n">
         <v>1.432706969358721</v>
       </c>
       <c r="AY30" t="n">
-        <v>526.8243069823308</v>
+        <v>526.8245236547064</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6464,16 +6464,16 @@
         <v>168.4314254760742</v>
       </c>
       <c r="AG31" t="n">
-        <v>166.116236038208</v>
+        <v>166.1162363433838</v>
       </c>
       <c r="AH31" t="n">
         <v>0.001832081015865183</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.01579478031486681</v>
+        <v>0.01579477844872801</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.01393716528307154</v>
+        <v>0.01393716342034534</v>
       </c>
       <c r="AK31" t="n">
         <v>248.7424926757812</v>
@@ -6509,7 +6509,7 @@
         <v>0.2329664348176663</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.07766525554502968</v>
+        <v>0.07766515052558187</v>
       </c>
       <c r="AW31" t="n">
         <v>0.2950304805499708</v>
@@ -6518,7 +6518,7 @@
         <v>-0.009259357974724214</v>
       </c>
       <c r="AY31" t="n">
-        <v>501.8662293552608</v>
+        <v>501.8662740171439</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
@@ -6704,13 +6704,13 @@
         <v>6.631647016669795</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.73459322067393</v>
+        <v>5.734593643176093</v>
       </c>
       <c r="AX32" t="n">
         <v>4.258987527512839</v>
       </c>
       <c r="AY32" t="n">
-        <v>34.83952137391328</v>
+        <v>34.83952436528662</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6842,37 +6842,37 @@
         <v>18.8</v>
       </c>
       <c r="AE33" t="n">
-        <v>148.8000030517578</v>
+        <v>165.3999938964844</v>
       </c>
       <c r="AF33" t="n">
-        <v>161.3980010986328</v>
+        <v>160.8420010375977</v>
       </c>
       <c r="AG33" t="n">
-        <v>95.14900029182434</v>
+        <v>95.84475026130676</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.07805547752215458</v>
+        <v>0.02833832475026998</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.5638630211077837</v>
+        <v>0.7257073908121767</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.6962658630529082</v>
+        <v>0.6781513916942281</v>
       </c>
       <c r="AK33" t="n">
         <v>239</v>
       </c>
       <c r="AL33" t="n">
-        <v>18.39999961853027</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.3774058449717246</v>
+        <v>-0.3079498163327014</v>
       </c>
       <c r="AN33" t="n">
-        <v>7.08695685525473</v>
+        <v>7.844919098842066</v>
       </c>
       <c r="AO33" t="n">
-        <v>35.26570199654282</v>
+        <v>45.85857841679072</v>
       </c>
       <c r="AP33" t="n">
         <v>163526</v>
@@ -6884,25 +6884,25 @@
         <v>1.226390486942855</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.006765899724980429</v>
+        <v>0.1518104934985447</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.08296950263230785</v>
+        <v>0.2090642558970255</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.38566553967463</v>
+        <v>2.348177910679561</v>
       </c>
       <c r="AV33" t="n">
-        <v>7.08695685525473</v>
+        <v>7.668762817497825</v>
       </c>
       <c r="AW33" t="n">
-        <v>3.537794119682881</v>
+        <v>3.948856116888956</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.53658556441762</v>
+        <v>4.042682858041039</v>
       </c>
       <c r="AY33" t="n">
-        <v>11.96743648887802</v>
+        <v>13.41407291921969</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7088,13 +7088,13 @@
         <v>4.701147787526577</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.998340487669816</v>
+        <v>5.998339903678698</v>
       </c>
       <c r="AX34" t="n">
         <v>1.865634237046958</v>
       </c>
       <c r="AY34" t="n">
-        <v>28.58318224083462</v>
+        <v>28.58318745849732</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7284,13 +7284,13 @@
         <v>2.618656336117365</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.208318938274296</v>
+        <v>4.208319283114757</v>
       </c>
       <c r="AX35" t="n">
         <v>1.247172700326574</v>
       </c>
       <c r="AY35" t="n">
-        <v>35.52294030770317</v>
+        <v>35.52293182909789</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7476,13 +7476,13 @@
         <v>5.456049944240522</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.967919919492477</v>
+        <v>6.967919382493537</v>
       </c>
       <c r="AX36" t="n">
         <v>3.12715527518396</v>
       </c>
       <c r="AY36" t="n">
-        <v>122.9099742941469</v>
+        <v>122.9099661775111</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7668,13 +7668,13 @@
         <v>0.3623453615110643</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.034551696203197</v>
+        <v>2.034551917872502</v>
       </c>
       <c r="AX37" t="n">
         <v>0.09541519509543295</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.347321656932146</v>
+        <v>3.347321201986043</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="X38" t="n">
-        <v>11868574720</v>
+        <v>11840870400</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>11868574720</v>
+        <v>11840870400</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>35916</v>
       </c>
       <c r="AD38" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="AE38" t="n">
         <v>47.77000045776367</v>
@@ -7816,16 +7816,16 @@
         <v>58.7477099609375</v>
       </c>
       <c r="AG38" t="n">
-        <v>55.92810264587402</v>
+        <v>55.92810244560242</v>
       </c>
       <c r="AH38" t="n">
         <v>-0.1868619136043451</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.1458676729973459</v>
+        <v>-0.145867669938804</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.05041485731988238</v>
+        <v>0.05041486108128779</v>
       </c>
       <c r="AK38" t="n">
         <v>93.37815856933594</v>
@@ -7858,19 +7858,19 @@
         <v>-0.2991959227553077</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.1106794774902511</v>
+        <v>0.1106795760007153</v>
       </c>
       <c r="AV38" t="n">
         <v>0.9522310097549045</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.8329803047058366</v>
+        <v>0.8329807071556998</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.118442992102425</v>
+        <v>0.1184428922100131</v>
       </c>
       <c r="AY38" t="n">
-        <v>2.869379517017345</v>
+        <v>2.869379218116278</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="X39" t="n">
-        <v>13985423294464</v>
+        <v>14015640109056</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>0.00640118820592761</v>
       </c>
       <c r="AA39" t="n">
-        <v>89523326647.42822</v>
+        <v>89716750164.61523</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -8056,13 +8056,13 @@
         <v>0.1163134729489104</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.75847165582408</v>
+        <v>0.7584715191393565</v>
       </c>
       <c r="AX39" t="n">
         <v>0.1004728578577838</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.8765355131189769</v>
+        <v>0.8765352018091956</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8248,13 +8248,13 @@
         <v>0.1762156630172396</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.995630759369053</v>
+        <v>0.995630596286154</v>
       </c>
       <c r="AX40" t="n">
         <v>0.1068018474350487</v>
       </c>
       <c r="AY40" t="n">
-        <v>3.55573111387979</v>
+        <v>3.555730263986958</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8450,7 +8450,7 @@
         <v>0.2316153655160222</v>
       </c>
       <c r="AY41" t="n">
-        <v>35.95650678066476</v>
+        <v>35.95649640979436</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8592,16 +8592,16 @@
         <v>1042.013900146484</v>
       </c>
       <c r="AG42" t="n">
-        <v>952.6559585571289</v>
+        <v>952.655959777832</v>
       </c>
       <c r="AH42" t="n">
         <v>-0.005790632617171498</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.08746496693079187</v>
+        <v>0.08746496553734873</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.09379875367041723</v>
+        <v>0.09379875226885837</v>
       </c>
       <c r="AK42" t="n">
         <v>1110.633178710938</v>
@@ -8637,16 +8637,16 @@
         <v>0.1070667905125982</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.3676831232125377</v>
+        <v>0.3676830130079589</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.3624081065609115</v>
+        <v>0.3624078878486849</v>
       </c>
       <c r="AX42" t="n">
         <v>0.3764769852523475</v>
       </c>
       <c r="AY42" t="n">
-        <v>2.369820823804102</v>
+        <v>2.369820489291658</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8788,28 +8788,28 @@
         <v>122.4522001647949</v>
       </c>
       <c r="AG43" t="n">
-        <v>108.6837877655029</v>
+        <v>108.6837879180908</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.04566842855348807</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.07522936965069449</v>
+        <v>0.07522936814111336</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.1266832218711298</v>
+        <v>0.1266832202893096</v>
       </c>
       <c r="AK43" t="n">
         <v>133.0599975585938</v>
       </c>
       <c r="AL43" t="n">
-        <v>77.69110870361328</v>
+        <v>77.69111633300781</v>
       </c>
       <c r="AM43" t="n">
         <v>-0.1217495659513177</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.5041618347366512</v>
+        <v>0.5041616870255019</v>
       </c>
       <c r="AO43" t="n">
         <v>27.02609048170021</v>
@@ -8833,16 +8833,16 @@
         <v>0.1071326552031009</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.3109323630808927</v>
+        <v>0.3109322508829941</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.041361884972067</v>
+        <v>2.041360677185458</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.4250142993823633</v>
+        <v>0.4250144319576805</v>
       </c>
       <c r="AY43" t="n">
-        <v>100.4261783081909</v>
+        <v>100.4261678141128</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -8980,16 +8980,16 @@
         <v>2.21364725112915</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.199640626907349</v>
+        <v>2.19964063167572</v>
       </c>
       <c r="AH44" t="n">
         <v>-0.01068245805497203</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.004382793065812796</v>
+        <v>-0.004382795224107561</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.006367687544257983</v>
+        <v>0.006367685362658415</v>
       </c>
       <c r="AK44" t="n">
         <v>2.330364942550659</v>
@@ -9028,10 +9028,10 @@
         <v>-0.01321952293265749</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.09368269801369533</v>
+        <v>0.09368256779342254</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.02642791581024162</v>
+        <v>0.02642780111303766</v>
       </c>
       <c r="AY44" t="n">
         <v>3.022817727194344</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="X48" t="n">
-        <v>1950244274176</v>
+        <v>1949120987136</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>1950244274176</v>
+        <v>1949120987136</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -9970,13 +9970,13 @@
         <v>0.1798126852647073</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.0615457607387071</v>
+        <v>0.06154563015840675</v>
       </c>
       <c r="AX49" t="n">
         <v>0.145964091767107</v>
       </c>
       <c r="AY49" t="n">
-        <v>178.9639864088405</v>
+        <v>178.96408902832</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="X50" t="n">
-        <v>10551757824</v>
+        <v>10547602432</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>1</v>
       </c>
       <c r="AA50" t="n">
-        <v>10551757824</v>
+        <v>10547602432</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
@@ -10118,28 +10118,28 @@
         <v>14.657103099823</v>
       </c>
       <c r="AG50" t="n">
-        <v>14.30421831607819</v>
+        <v>14.30421830654144</v>
       </c>
       <c r="AH50" t="n">
         <v>0.009067061964764145</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.03396072648225834</v>
+        <v>0.0339607271716087</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.02466998027764733</v>
+        <v>0.02466998096080353</v>
       </c>
       <c r="AK50" t="n">
         <v>16.86722755432129</v>
       </c>
       <c r="AL50" t="n">
-        <v>11.91677284240723</v>
+        <v>11.91677379608154</v>
       </c>
       <c r="AM50" t="n">
         <v>-0.1231516908026825</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.2411078198303056</v>
+        <v>0.24110772050706</v>
       </c>
       <c r="AO50" t="n">
         <v>54.83860051743816</v>
@@ -10166,13 +10166,13 @@
         <v>0.2007934086763152</v>
       </c>
       <c r="AW50" t="n">
-        <v>-0.2490321175435813</v>
+        <v>-0.2490322630005551</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.03450408380073022</v>
+        <v>0.03450401479322873</v>
       </c>
       <c r="AY50" t="n">
-        <v>6.500330046530546</v>
+        <v>6.50032596573394</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10314,16 +10314,16 @@
         <v>1015.396804199219</v>
       </c>
       <c r="AG51" t="n">
-        <v>885.5725122070312</v>
+        <v>885.5725106811524</v>
       </c>
       <c r="AH51" t="n">
         <v>-0.07233309351422523</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.06366220633869446</v>
+        <v>0.06366220817142931</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.1465992792263147</v>
+        <v>0.1465992812019536</v>
       </c>
       <c r="AK51" t="n">
         <v>1174.859985351562</v>
@@ -10363,10 +10363,10 @@
       </c>
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="n">
-        <v>0.388706482426141</v>
+        <v>0.3887066073867604</v>
       </c>
       <c r="AY51" t="n">
-        <v>6.207088981781947</v>
+        <v>6.20709066461905</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10508,28 +10508,28 @@
         <v>109.8753311157227</v>
       </c>
       <c r="AG52" t="n">
-        <v>104.4612220001221</v>
+        <v>104.4612226486206</v>
       </c>
       <c r="AH52" t="n">
         <v>-0.02371173261732673</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.0268882039589875</v>
+        <v>0.02688819758403316</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.05182888934225049</v>
+        <v>0.05182888281246378</v>
       </c>
       <c r="AK52" t="n">
         <v>116.6635665893555</v>
       </c>
       <c r="AL52" t="n">
-        <v>84.71997833251953</v>
+        <v>84.71998596191406</v>
       </c>
       <c r="AM52" t="n">
         <v>-0.08051845336902419</v>
       </c>
       <c r="AN52" t="n">
-        <v>0.2661712001629621</v>
+        <v>0.2661710861388684</v>
       </c>
       <c r="AO52" t="n">
         <v>44.35410616099895</v>
@@ -10553,16 +10553,16 @@
         <v>0.03678237676289631</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.2528962340558647</v>
+        <v>0.2528961224101713</v>
       </c>
       <c r="AW52" t="n">
         <v>1.336707132759653</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.1635712097973703</v>
+        <v>0.1635711135037079</v>
       </c>
       <c r="AY52" t="n">
-        <v>199.776009853096</v>
+        <v>199.7761890439543</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10704,16 +10704,16 @@
         <v>266.1299002075195</v>
       </c>
       <c r="AG53" t="n">
-        <v>295.4780754089355</v>
+        <v>295.4780753326416</v>
       </c>
       <c r="AH53" t="n">
         <v>0.1233611526625109</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.01178400814112424</v>
+        <v>0.01178400840237193</v>
       </c>
       <c r="AJ53" t="n">
-        <v>-0.09932437511919867</v>
+        <v>-0.0993243748866397</v>
       </c>
       <c r="AK53" t="n">
         <v>401.7044372558594</v>
@@ -10749,14 +10749,14 @@
         <v>-0.07153539849596691</v>
       </c>
       <c r="AV53" t="n">
-        <v>-0.003146051820460682</v>
+        <v>-0.003145950382594798</v>
       </c>
       <c r="AW53" t="inlineStr"/>
       <c r="AX53" t="n">
         <v>-0.1801048018707326</v>
       </c>
       <c r="AY53" t="n">
-        <v>6.394510853868749</v>
+        <v>6.394512249259964</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10771,12 +10771,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>ENR.DE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Centrus Energy</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -10786,16 +10786,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Nuclear / uranium / SMR</t>
+          <t>Grid + gas/power equipment</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nuclear fuel/enrichment</t>
+          <t>Grid/gas/power equipment</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -10844,131 +10844,131 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp.</t>
+          <t>Siemens Energy AG</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X54" t="n">
-        <v>3469602560</v>
+        <v>124666339328</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>1</v>
+        <v>1.162115097045898</v>
       </c>
       <c r="AA54" t="n">
-        <v>3469602560</v>
+        <v>144876635026.5156</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Mid cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC54" s="2" t="n">
-        <v>35999</v>
+        <v>44103</v>
       </c>
       <c r="AD54" t="n">
-        <v>28.1</v>
+        <v>5.9</v>
       </c>
       <c r="AE54" t="n">
-        <v>173.8899993896484</v>
+        <v>146.5200042724609</v>
       </c>
       <c r="AF54" t="n">
-        <v>174.209599609375</v>
+        <v>152.7915997314453</v>
       </c>
       <c r="AG54" t="n">
-        <v>210.5998001098633</v>
+        <v>150.444681892395</v>
       </c>
       <c r="AH54" t="n">
-        <v>-0.001834572953747671</v>
+        <v>-0.04104672946685328</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.1743107101766692</v>
+        <v>-0.02608718081999861</v>
       </c>
       <c r="AJ54" t="n">
-        <v>-0.1727931388420343</v>
+        <v>0.01559987238850291</v>
       </c>
       <c r="AK54" t="n">
-        <v>436</v>
+        <v>187.6199951171875</v>
       </c>
       <c r="AL54" t="n">
-        <v>146.6100006103516</v>
+        <v>89.11995697021484</v>
       </c>
       <c r="AM54" t="n">
-        <v>-0.6011697261705311</v>
+        <v>-0.2190597586310323</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.1860718823117633</v>
+        <v>0.6440762456991536</v>
       </c>
       <c r="AO54" t="n">
-        <v>45.19582980717624</v>
+        <v>27.9284027992119</v>
       </c>
       <c r="AP54" t="n">
-        <v>1000900</v>
+        <v>1573611</v>
       </c>
       <c r="AQ54" t="n">
-        <v>712500</v>
+        <v>2044957.58</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.404771929824561</v>
+        <v>0.7695078936551828</v>
       </c>
       <c r="AS54" t="n">
-        <v>-0.09134136057658881</v>
+        <v>-0.0457209152053929</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.06198847902755267</v>
+        <v>0.05653311227819846</v>
       </c>
       <c r="AU54" t="n">
-        <v>-0.11212665830738</v>
+        <v>-0.07089405765461476</v>
       </c>
       <c r="AV54" t="n">
-        <v>-0.1533667661210752</v>
+        <v>0.6440762456991536</v>
       </c>
       <c r="AW54" t="n">
-        <v>5.576777453754551</v>
+        <v>5.144740317468241</v>
       </c>
       <c r="AX54" t="n">
-        <v>-0.3618715618728497</v>
+        <v>0.1982477392473279</v>
       </c>
       <c r="AY54" t="n">
-        <v>-0.9200562373175122</v>
+        <v>5.722904204495322</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>Weak momentum</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Centrus Energy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -10978,19 +10978,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Utility / power generation</t>
+          <t>Nuclear / uranium / SMR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Utility/power generation</t>
+          <t>Nuclear fuel/enrichment</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -10998,11 +10998,7 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" s="1" t="n">
         <v>46195</v>
       </c>
@@ -11040,17 +11036,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>The Southern Company</t>
+          <t>Centrus Energy Corp.</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -11059,7 +11055,7 @@
         </is>
       </c>
       <c r="X55" t="n">
-        <v>101358485504</v>
+        <v>3469602560</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -11070,81 +11066,81 @@
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>101358485504</v>
+        <v>3469602560</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC55" s="2" t="n">
-        <v>29951</v>
+        <v>35999</v>
       </c>
       <c r="AD55" t="n">
-        <v>44.7</v>
+        <v>28.1</v>
       </c>
       <c r="AE55" t="n">
-        <v>88.11000061035156</v>
+        <v>173.8899993896484</v>
       </c>
       <c r="AF55" t="n">
-        <v>92.84135726928712</v>
+        <v>174.209599609375</v>
       </c>
       <c r="AG55" t="n">
-        <v>91.04056209564209</v>
+        <v>210.5998001098633</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.05096173513719982</v>
+        <v>-0.001834572953747671</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.03218962424915439</v>
+        <v>-0.1743107101766692</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.01978014120511706</v>
+        <v>-0.1727931388420343</v>
       </c>
       <c r="AK55" t="n">
-        <v>97.49111175537109</v>
+        <v>436</v>
       </c>
       <c r="AL55" t="n">
-        <v>82.06203460693359</v>
+        <v>146.6100006103516</v>
       </c>
       <c r="AM55" t="n">
-        <v>-0.0962252966050795</v>
+        <v>-0.6011697261705311</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.07369992752905685</v>
+        <v>0.1860718823117633</v>
       </c>
       <c r="AO55" t="n">
-        <v>24.75842528391422</v>
+        <v>45.19582980717624</v>
       </c>
       <c r="AP55" t="n">
-        <v>7184000</v>
+        <v>1000900</v>
       </c>
       <c r="AQ55" t="n">
-        <v>5377146</v>
+        <v>712500</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.336024723896283</v>
+        <v>1.404771929824561</v>
       </c>
       <c r="AS55" t="n">
-        <v>-0.04156273831250534</v>
+        <v>-0.09134136057658881</v>
       </c>
       <c r="AT55" t="n">
-        <v>-0.02675777870870788</v>
+        <v>0.06198847902755267</v>
       </c>
       <c r="AU55" t="n">
-        <v>-0.0789397141278696</v>
+        <v>-0.11212665830738</v>
       </c>
       <c r="AV55" t="n">
-        <v>-0.008287574391823593</v>
+        <v>-0.1533667661210752</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.6087811875158762</v>
+        <v>5.576777453754551</v>
       </c>
       <c r="AX55" t="n">
-        <v>0.03552057379947127</v>
+        <v>-0.3618715618728497</v>
       </c>
       <c r="AY55" t="n">
-        <v>326.5828071827355</v>
+        <v>-0.9200562552633821</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11159,12 +11155,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11174,16 +11170,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Grid / power equipment</t>
+          <t>Utility / power generation</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Power generation, data center electricity</t>
+          <t>Utility/power generation</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -11231,10 +11227,12 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Vistra Corp.</t>
+          <t>The Southern Company</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -11244,7 +11242,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Utilities - Independent Power Producers</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -11253,7 +11251,7 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>50110337024</v>
+        <v>101358485504</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -11264,7 +11262,7 @@
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>50110337024</v>
+        <v>101358485504</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
@@ -11272,73 +11270,73 @@
         </is>
       </c>
       <c r="AC56" s="2" t="n">
-        <v>42648</v>
+        <v>29951</v>
       </c>
       <c r="AD56" t="n">
-        <v>9.9</v>
+        <v>44.7</v>
       </c>
       <c r="AE56" t="n">
-        <v>149.3000030517578</v>
+        <v>88.11000061035156</v>
       </c>
       <c r="AF56" t="n">
-        <v>149.6422003173828</v>
+        <v>92.84135726928712</v>
       </c>
       <c r="AG56" t="n">
-        <v>157.4790908813476</v>
+        <v>91.04056209564209</v>
       </c>
       <c r="AH56" t="n">
-        <v>-0.002286769807575806</v>
+        <v>-0.05096173513719982</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.05193761142393405</v>
+        <v>-0.03218962424915439</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-0.04976464189693297</v>
+        <v>0.01978014120511706</v>
       </c>
       <c r="AK56" t="n">
-        <v>217.0162200927734</v>
+        <v>97.49111175537109</v>
       </c>
       <c r="AL56" t="n">
-        <v>134.5216217041016</v>
+        <v>82.06204223632812</v>
       </c>
       <c r="AM56" t="n">
-        <v>-0.3120329762082634</v>
+        <v>-0.0962252966050795</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.1098587807703009</v>
+        <v>0.07369982770604344</v>
       </c>
       <c r="AO56" t="n">
-        <v>54.64608751694557</v>
+        <v>24.75842528391422</v>
       </c>
       <c r="AP56" t="n">
-        <v>4599200</v>
+        <v>7184000</v>
       </c>
       <c r="AQ56" t="n">
-        <v>4336970</v>
+        <v>5377146</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.060463872242603</v>
+        <v>1.336024723896283</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.06195324660891077</v>
+        <v>-0.04156273831250534</v>
       </c>
       <c r="AT56" t="n">
-        <v>0.0177609731869115</v>
+        <v>-0.02675777870870788</v>
       </c>
       <c r="AU56" t="n">
-        <v>-0.08499546964267835</v>
+        <v>-0.0789397141278696</v>
       </c>
       <c r="AV56" t="n">
-        <v>-0.201685231683661</v>
+        <v>-0.008287489231673884</v>
       </c>
       <c r="AW56" t="n">
-        <v>7.688886787233599</v>
+        <v>0.6087812995702628</v>
       </c>
       <c r="AX56" t="n">
-        <v>-0.09391127900469676</v>
+        <v>0.03552066664957043</v>
       </c>
       <c r="AY56" t="n">
-        <v>12.16853694035522</v>
+        <v>326.5828071827355</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11353,12 +11351,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11368,16 +11366,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Utility / power generation</t>
+          <t>Grid / power equipment</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Utility/data center load</t>
+          <t>Power generation, data center electricity</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -11425,12 +11423,10 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
+      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Duke Energy Corporation</t>
+          <t>Vistra Corp.</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -11440,7 +11436,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Utilities - Independent Power Producers</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -11449,7 +11445,7 @@
         </is>
       </c>
       <c r="X57" t="n">
-        <v>93735796736</v>
+        <v>50110337024</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -11460,7 +11456,7 @@
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>93735796736</v>
+        <v>50110337024</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
@@ -11468,77 +11464,77 @@
         </is>
       </c>
       <c r="AC57" s="2" t="n">
-        <v>29297</v>
+        <v>42648</v>
       </c>
       <c r="AD57" t="n">
-        <v>46.5</v>
+        <v>9.9</v>
       </c>
       <c r="AE57" t="n">
-        <v>120.2200012207031</v>
+        <v>149.3000030517578</v>
       </c>
       <c r="AF57" t="n">
-        <v>123.9937292480469</v>
+        <v>149.6422003173828</v>
       </c>
       <c r="AG57" t="n">
-        <v>122.3379981994629</v>
+        <v>157.4790911102295</v>
       </c>
       <c r="AH57" t="n">
-        <v>-0.03043482965009048</v>
+        <v>-0.002286769807575806</v>
       </c>
       <c r="AI57" t="n">
-        <v>-0.01731266662796405</v>
+        <v>-0.05193761280185838</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.01353407014135088</v>
+        <v>-0.04976464327801555</v>
       </c>
       <c r="AK57" t="n">
-        <v>131.1634063720703</v>
+        <v>217.0162200927734</v>
       </c>
       <c r="AL57" t="n">
-        <v>111.0921020507812</v>
+        <v>134.5216217041016</v>
       </c>
       <c r="AM57" t="n">
-        <v>-0.08343337104500093</v>
+        <v>-0.3120329762082634</v>
       </c>
       <c r="AN57" t="n">
-        <v>0.08216514946984654</v>
+        <v>0.1098587807703009</v>
       </c>
       <c r="AO57" t="n">
-        <v>35.99999745686848</v>
+        <v>54.64608751694557</v>
       </c>
       <c r="AP57" t="n">
-        <v>3208500</v>
+        <v>4599200</v>
       </c>
       <c r="AQ57" t="n">
-        <v>4046058</v>
+        <v>4336970</v>
       </c>
       <c r="AR57" t="n">
-        <v>0.7929940697834782</v>
+        <v>1.060463872242603</v>
       </c>
       <c r="AS57" t="n">
-        <v>-0.02861830753519634</v>
+        <v>0.06195324660891077</v>
       </c>
       <c r="AT57" t="n">
-        <v>-0.006333494598784517</v>
+        <v>0.0177609731869115</v>
       </c>
       <c r="AU57" t="n">
-        <v>-0.06679136710076106</v>
+        <v>-0.08499546964267835</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.03174809790081579</v>
+        <v>-0.2016851665495313</v>
       </c>
       <c r="AW57" t="n">
-        <v>0.3909816933907104</v>
+        <v>7.688885822741899</v>
       </c>
       <c r="AX57" t="n">
-        <v>0.05046681596439995</v>
+        <v>-0.09391136291236679</v>
       </c>
       <c r="AY57" t="n">
-        <v>162.8126164560394</v>
+        <v>12.16853472499045</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
@@ -11549,12 +11545,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -11569,11 +11565,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Renewables/grid/utility</t>
+          <t>Utility/data center load</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -11626,7 +11622,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>NextEra Energy, Inc.</t>
+          <t>Duke Energy Corporation</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -11645,7 +11641,7 @@
         </is>
       </c>
       <c r="X58" t="n">
-        <v>174033158144</v>
+        <v>93735796736</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -11656,7 +11652,7 @@
         <v>1</v>
       </c>
       <c r="AA58" t="n">
-        <v>174033158144</v>
+        <v>93735796736</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
@@ -11664,73 +11660,73 @@
         </is>
       </c>
       <c r="AC58" s="2" t="n">
-        <v>26716</v>
+        <v>29297</v>
       </c>
       <c r="AD58" t="n">
-        <v>53.5</v>
+        <v>46.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>83.43000030517578</v>
+        <v>120.2200012207031</v>
       </c>
       <c r="AF58" t="n">
-        <v>85.98187911987304</v>
+        <v>123.9937292480469</v>
       </c>
       <c r="AG58" t="n">
-        <v>86.53848693847657</v>
+        <v>122.3379981994629</v>
       </c>
       <c r="AH58" t="n">
-        <v>-0.02967926312868219</v>
+        <v>-0.03043482965009048</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.03592027944180165</v>
+        <v>-0.01731266662796405</v>
       </c>
       <c r="AJ58" t="n">
-        <v>-0.006431910682691222</v>
+        <v>0.01353407014135088</v>
       </c>
       <c r="AK58" t="n">
-        <v>96.44304656982422</v>
+        <v>131.1634063720703</v>
       </c>
       <c r="AL58" t="n">
-        <v>67.82089996337891</v>
+        <v>111.0920944213867</v>
       </c>
       <c r="AM58" t="n">
-        <v>-0.1349298547431003</v>
+        <v>-0.08343337104500093</v>
       </c>
       <c r="AN58" t="n">
-        <v>0.2301517725395164</v>
+        <v>0.08216522378895008</v>
       </c>
       <c r="AO58" t="n">
-        <v>36.09428148622639</v>
+        <v>35.99999745686848</v>
       </c>
       <c r="AP58" t="n">
-        <v>10765300</v>
+        <v>3208500</v>
       </c>
       <c r="AQ58" t="n">
-        <v>10875956</v>
+        <v>4046058</v>
       </c>
       <c r="AR58" t="n">
-        <v>0.9898256300411661</v>
+        <v>0.7929940697834782</v>
       </c>
       <c r="AS58" t="n">
-        <v>-0.007000814443093528</v>
+        <v>-0.02861830753519634</v>
       </c>
       <c r="AT58" t="n">
-        <v>0.0005639950982567754</v>
+        <v>-0.006333494598784517</v>
       </c>
       <c r="AU58" t="n">
-        <v>-0.07974072294047729</v>
+        <v>-0.06679136710076106</v>
       </c>
       <c r="AV58" t="n">
-        <v>0.2105456475666125</v>
+        <v>0.03174809790081579</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.136737689359486</v>
+        <v>0.3909819389668945</v>
       </c>
       <c r="AX58" t="n">
-        <v>0.05338457880942604</v>
+        <v>0.05046681596439995</v>
       </c>
       <c r="AY58" t="n">
-        <v>240.8891505168681</v>
+        <v>162.8126563695043</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -11745,12 +11741,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NXE</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NexGen Energy</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -11760,19 +11756,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Nuclear / uranium / SMR</t>
+          <t>Utility / power generation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Uranium developer</t>
+          <t>Renewables/grid/utility</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -11780,7 +11776,11 @@
       <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
       <c r="K59" s="1" t="n">
         <v>46195</v>
       </c>
@@ -11818,17 +11818,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>NexGen Energy Ltd.</t>
+          <t>NextEra Energy, Inc.</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="X59" t="n">
-        <v>7194530304</v>
+        <v>174002061312</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -11848,81 +11848,81 @@
         <v>1</v>
       </c>
       <c r="AA59" t="n">
-        <v>7194530304</v>
+        <v>174002061312</v>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Mid cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC59" s="2" t="n">
-        <v>41500</v>
+        <v>26716</v>
       </c>
       <c r="AD59" t="n">
-        <v>13.1</v>
+        <v>53.5</v>
       </c>
       <c r="AE59" t="n">
-        <v>10.72999954223633</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="AF59" t="n">
-        <v>9.87480001449585</v>
+        <v>85.98187911987304</v>
       </c>
       <c r="AG59" t="n">
-        <v>10.81899999856949</v>
+        <v>86.53848690032959</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.08660423770456882</v>
+        <v>-0.02967926312868219</v>
       </c>
       <c r="AI59" t="n">
-        <v>-0.008226310781488833</v>
+        <v>-0.03592027901682626</v>
       </c>
       <c r="AJ59" t="n">
-        <v>-0.08727238970315943</v>
+        <v>-0.006431910244717121</v>
       </c>
       <c r="AK59" t="n">
-        <v>13.92000007629395</v>
+        <v>96.44304656982422</v>
       </c>
       <c r="AL59" t="n">
-        <v>7.559999942779541</v>
+        <v>67.82089996337891</v>
       </c>
       <c r="AM59" t="n">
-        <v>-0.229166703776838</v>
+        <v>-0.1349298547431003</v>
       </c>
       <c r="AN59" t="n">
-        <v>0.4193121195039708</v>
+        <v>0.2301517725395164</v>
       </c>
       <c r="AO59" t="n">
-        <v>49.78165438758908</v>
+        <v>36.09428148622639</v>
       </c>
       <c r="AP59" t="n">
-        <v>3942300</v>
+        <v>10765300</v>
       </c>
       <c r="AQ59" t="n">
-        <v>4905736</v>
+        <v>10875956</v>
       </c>
       <c r="AR59" t="n">
-        <v>0.80361030434577</v>
+        <v>0.9898256300411661</v>
       </c>
       <c r="AS59" t="n">
-        <v>0.02876310913544988</v>
+        <v>-0.007000814443093528</v>
       </c>
       <c r="AT59" t="n">
-        <v>0.03173076305869049</v>
+        <v>0.0005639950982567754</v>
       </c>
       <c r="AU59" t="n">
-        <v>-0.1524486831309324</v>
+        <v>-0.07974072294047729</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.3756409333145696</v>
+        <v>0.2105456475666125</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.347921037021656</v>
+        <v>0.1367375711946375</v>
       </c>
       <c r="AX59" t="n">
-        <v>0.0468292236328125</v>
+        <v>0.05338457880942604</v>
       </c>
       <c r="AY59" t="n">
-        <v>26.30279735361448</v>
+        <v>240.8891505168681</v>
       </c>
       <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
@@ -11937,12 +11937,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>NXE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>NexGen Energy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -11952,31 +11952,27 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Utility / power generation</t>
+          <t>Nuclear / uranium / SMR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Utility/transmission</t>
+          <t>Uranium developer</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" s="1" t="n">
         <v>46195</v>
       </c>
@@ -12014,17 +12010,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Exelon Corporation</t>
+          <t>NexGen Energy Ltd.</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -12033,7 +12029,7 @@
         </is>
       </c>
       <c r="X60" t="n">
-        <v>44960280576</v>
+        <v>7102287872</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -12044,85 +12040,85 @@
         <v>1</v>
       </c>
       <c r="AA60" t="n">
-        <v>44960280576</v>
+        <v>7102287872</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC60" s="2" t="n">
-        <v>26786</v>
+        <v>41500</v>
       </c>
       <c r="AD60" t="n">
-        <v>53.3</v>
+        <v>13.1</v>
       </c>
       <c r="AE60" t="n">
-        <v>43.63999938964844</v>
+        <v>10.72999954223633</v>
       </c>
       <c r="AF60" t="n">
-        <v>45.36317825317383</v>
+        <v>9.87480001449585</v>
       </c>
       <c r="AG60" t="n">
-        <v>45.09055332183838</v>
+        <v>10.81899999856949</v>
       </c>
       <c r="AH60" t="n">
-        <v>-0.03798629042057533</v>
+        <v>0.08660423770456882</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.03216979667196507</v>
+        <v>-0.008226310781488833</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.006046165133294368</v>
+        <v>-0.08727238970315943</v>
       </c>
       <c r="AK60" t="n">
-        <v>49.3515510559082</v>
+        <v>13.92000007629395</v>
       </c>
       <c r="AL60" t="n">
-        <v>41.21672439575195</v>
+        <v>7.559999942779541</v>
       </c>
       <c r="AM60" t="n">
-        <v>-0.1157319586529185</v>
+        <v>-0.229166703776838</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.05879348806636964</v>
+        <v>0.4193121195039708</v>
       </c>
       <c r="AO60" t="n">
-        <v>33.22641898935235</v>
+        <v>49.78165438758908</v>
       </c>
       <c r="AP60" t="n">
-        <v>8368800</v>
+        <v>3942300</v>
       </c>
       <c r="AQ60" t="n">
-        <v>8088446</v>
+        <v>4905736</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.034661046139147</v>
+        <v>0.80361030434577</v>
       </c>
       <c r="AS60" t="n">
-        <v>-0.03408190251339605</v>
+        <v>0.02876310913544988</v>
       </c>
       <c r="AT60" t="n">
-        <v>-0.01661775098224638</v>
+        <v>0.03173076305869049</v>
       </c>
       <c r="AU60" t="n">
-        <v>-0.09503785704290191</v>
+        <v>-0.1524486831309324</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.04172788962020513</v>
+        <v>0.3756409333145696</v>
       </c>
       <c r="AW60" t="n">
-        <v>0.484105908673621</v>
+        <v>1.347921037021656</v>
       </c>
       <c r="AX60" t="n">
-        <v>0.02118893366919594</v>
+        <v>0.0468292236328125</v>
       </c>
       <c r="AY60" t="n">
-        <v>178.6740504280849</v>
+        <v>26.30279735361448</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
@@ -12133,12 +12129,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENR.DE</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12148,27 +12144,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Grid + gas/power equipment</t>
+          <t>Utility / power generation</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Grid/gas/power equipment</t>
+          <t>Utility/transmission</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100</t>
+        </is>
+      </c>
       <c r="K61" s="1" t="n">
         <v>46195</v>
       </c>
@@ -12206,37 +12206,37 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>Siemens Energy AG</t>
+          <t>Exelon Corporation</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X61" t="n">
-        <v>124666339328</v>
+        <v>44960280576</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>1.162115097045898</v>
+        <v>1</v>
       </c>
       <c r="AA61" t="n">
-        <v>144876635026.5156</v>
+        <v>44960280576</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
@@ -12244,81 +12244,81 @@
         </is>
       </c>
       <c r="AC61" s="2" t="n">
-        <v>44103</v>
+        <v>26786</v>
       </c>
       <c r="AD61" t="n">
-        <v>5.9</v>
+        <v>53.3</v>
       </c>
       <c r="AE61" t="n">
-        <v>145.3999938964844</v>
+        <v>43.63999938964844</v>
       </c>
       <c r="AF61" t="n">
-        <v>152.939599609375</v>
+        <v>45.36317825317383</v>
       </c>
       <c r="AG61" t="n">
-        <v>150.2445611572266</v>
+        <v>45.09055334091187</v>
       </c>
       <c r="AH61" t="n">
-        <v>-0.04929793024270779</v>
+        <v>-0.03798629042057533</v>
       </c>
       <c r="AI61" t="n">
-        <v>-0.03224454331942506</v>
+        <v>-0.03216979708136125</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.017937677286888</v>
+        <v>0.006046164707732782</v>
       </c>
       <c r="AK61" t="n">
-        <v>187.6199951171875</v>
+        <v>49.3515510559082</v>
       </c>
       <c r="AL61" t="n">
-        <v>87.20811462402344</v>
+        <v>41.21672439575195</v>
       </c>
       <c r="AM61" t="n">
-        <v>-0.2250293269346505</v>
+        <v>-0.1157319586529185</v>
       </c>
       <c r="AN61" t="n">
-        <v>0.667275969940883</v>
+        <v>0.05879348806636964</v>
       </c>
       <c r="AO61" t="n">
-        <v>29.75684307305193</v>
+        <v>33.22641898935235</v>
       </c>
       <c r="AP61" t="n">
-        <v>1573455</v>
+        <v>8368800</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2044954.46</v>
+        <v>8088446</v>
       </c>
       <c r="AR61" t="n">
-        <v>0.7694327823808849</v>
+        <v>1.034661046139147</v>
       </c>
       <c r="AS61" t="n">
-        <v>-0.05387818306814462</v>
+        <v>-0.03408190251339605</v>
       </c>
       <c r="AT61" t="n">
-        <v>-0.0195550175023349</v>
+        <v>-0.01661775098224638</v>
       </c>
       <c r="AU61" t="n">
-        <v>-0.02252104943539912</v>
+        <v>-0.09503785704290191</v>
       </c>
       <c r="AV61" t="n">
-        <v>0.667275969940883</v>
+        <v>0.04172779476003807</v>
       </c>
       <c r="AW61" t="n">
-        <v>5.299283483767862</v>
+        <v>0.4841056198742086</v>
       </c>
       <c r="AX61" t="n">
-        <v>0.1890882397809488</v>
+        <v>0.02118893366919594</v>
       </c>
       <c r="AY61" t="n">
-        <v>5.671513214907144</v>
+        <v>178.6741827060969</v>
       </c>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>Very weak momentum</t>
+          <t>Weak momentum</t>
         </is>
       </c>
     </row>
@@ -12452,16 +12452,16 @@
         <v>127.2396626281738</v>
       </c>
       <c r="AG62" t="n">
-        <v>145.8210416412354</v>
+        <v>145.8210417175293</v>
       </c>
       <c r="AH62" t="n">
         <v>-0.06459987251873933</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.1837940855209893</v>
+        <v>-0.1837940859480303</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.1274259105813922</v>
+        <v>-0.1274259110379251</v>
       </c>
       <c r="AK62" t="n">
         <v>182.8191833496094</v>
@@ -12497,16 +12497,16 @@
         <v>-0.229132270405264</v>
       </c>
       <c r="AV62" t="n">
-        <v>-0.1839986906476084</v>
+        <v>-0.1839986052822059</v>
       </c>
       <c r="AW62" t="n">
-        <v>2.032391968457286</v>
+        <v>2.032391673736492</v>
       </c>
       <c r="AX62" t="n">
         <v>-0.2767075291052146</v>
       </c>
       <c r="AY62" t="n">
-        <v>15.67231024656018</v>
+        <v>15.67231136019231</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -12644,16 +12644,16 @@
         <v>170.9235604858399</v>
       </c>
       <c r="AG63" t="n">
-        <v>192.2148571014404</v>
+        <v>192.2148574066162</v>
       </c>
       <c r="AH63" t="n">
         <v>-0.07800893048359969</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.1801362354902499</v>
+        <v>-0.1801362367919316</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.1107682149895635</v>
+        <v>-0.1107682164013793</v>
       </c>
       <c r="AK63" t="n">
         <v>237.7264404296875</v>
@@ -12692,13 +12692,13 @@
         <v>-0.03145246615416275</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.920877209070745</v>
+        <v>1.920877828625051</v>
       </c>
       <c r="AX63" t="n">
         <v>-0.1296790162907442</v>
       </c>
       <c r="AY63" t="n">
-        <v>10.13908598672788</v>
+        <v>10.139082232329</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12884,13 +12884,13 @@
         <v>0.3307336837090606</v>
       </c>
       <c r="AW64" t="n">
-        <v>4.700907084646483</v>
+        <v>4.700907699987857</v>
       </c>
       <c r="AX64" t="n">
         <v>0.02211851013774391</v>
       </c>
       <c r="AY64" t="n">
-        <v>15.83632092428827</v>
+        <v>15.83633031634759</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13593,7 +13593,7 @@
         <v>36756</v>
       </c>
       <c r="AD68" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="AE68" t="n">
         <v>496</v>
@@ -13650,13 +13650,13 @@
         <v>9.598384070205395</v>
       </c>
       <c r="AW68" t="n">
-        <v>6.021299216110569</v>
+        <v>6.021299974414672</v>
       </c>
       <c r="AX68" t="n">
         <v>1.403836393753192</v>
       </c>
       <c r="AY68" t="n">
-        <v>-0.4212230228124534</v>
+        <v>-0.4212229403699945</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -14042,7 +14042,7 @@
         <v>0.9263324546816414</v>
       </c>
       <c r="AY70" t="n">
-        <v>3.571041003128463</v>
+        <v>3.57104054504879</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14184,16 +14184,16 @@
         <v>938.2628747558593</v>
       </c>
       <c r="AG71" t="n">
-        <v>606.3405872344971</v>
+        <v>606.3405874633789</v>
       </c>
       <c r="AH71" t="n">
         <v>0.08348103096372705</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.6765990076503177</v>
+        <v>0.6765990070174341</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.5474188838904068</v>
+        <v>0.5474188833062861</v>
       </c>
       <c r="AK71" t="n">
         <v>1213.373413085938</v>
@@ -14238,7 +14238,7 @@
         <v>2.224822079516891</v>
       </c>
       <c r="AY71" t="n">
-        <v>751.613342382347</v>
+        <v>751.6134088037614</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14428,13 +14428,13 @@
         <v>0.5902145558684111</v>
       </c>
       <c r="AW72" t="n">
-        <v>1.35323482999894</v>
+        <v>1.353234147051668</v>
       </c>
       <c r="AX72" t="n">
         <v>0.7573699555803688</v>
       </c>
       <c r="AY72" t="n">
-        <v>196.9175266159076</v>
+        <v>196.9174637139854</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14572,28 +14572,28 @@
         <v>1842943.2175</v>
       </c>
       <c r="AG73" t="n">
-        <v>1305547.82484375</v>
+        <v>1305547.82609375</v>
       </c>
       <c r="AH73" t="n">
         <v>-0.1063208109937331</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.2615393849682339</v>
+        <v>0.2615393837603699</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.4116244402770661</v>
+        <v>0.411624438925503</v>
       </c>
       <c r="AK73" t="n">
         <v>2918367.25</v>
       </c>
       <c r="AL73" t="n">
-        <v>249901.328125</v>
+        <v>249901.34375</v>
       </c>
       <c r="AM73" t="n">
         <v>-0.4356433378972437</v>
       </c>
       <c r="AN73" t="n">
-        <v>5.590601227922146</v>
+        <v>5.590600815846954</v>
       </c>
       <c r="AO73" t="n">
         <v>50.14886876949101</v>
@@ -14617,16 +14617,16 @@
         <v>0.7509379763842638</v>
       </c>
       <c r="AV73" t="n">
-        <v>5.590601227922146</v>
+        <v>5.590600815846954</v>
       </c>
       <c r="AW73" t="n">
-        <v>13.29934782829876</v>
+        <v>13.29934685839451</v>
       </c>
       <c r="AX73" t="n">
         <v>1.438216940981493</v>
       </c>
       <c r="AY73" t="n">
-        <v>-8.197665183609498</v>
+        <v>-8.197665675093898</v>
       </c>
       <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
@@ -14768,16 +14768,16 @@
         <v>266084.62125</v>
       </c>
       <c r="AG74" t="n">
-        <v>211370.9876171875</v>
+        <v>211370.987578125</v>
       </c>
       <c r="AH74" t="n">
         <v>-0.03977915446701163</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.2087751629506234</v>
+        <v>0.2087751631740116</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.2588511992568441</v>
+        <v>0.2588511994894866</v>
       </c>
       <c r="AK74" t="n">
         <v>362100.65625</v>
@@ -14816,7 +14816,7 @@
         <v>2.623337332550552</v>
       </c>
       <c r="AW74" t="n">
-        <v>2.534610356870923</v>
+        <v>2.534609210821542</v>
       </c>
       <c r="AX74" t="n">
         <v>0.9946396499036592</v>
@@ -15154,16 +15154,16 @@
         <v>321.8837994384766</v>
       </c>
       <c r="AG76" t="n">
-        <v>260.6797447967529</v>
+        <v>260.6797444152832</v>
       </c>
       <c r="AH76" t="n">
         <v>-0.04422032288304956</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.1801837313303851</v>
+        <v>0.180183733057425</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.2347863839188706</v>
+        <v>0.2347863857258141</v>
       </c>
       <c r="AK76" t="n">
         <v>433.3299865722656</v>
@@ -15202,13 +15202,13 @@
         <v>2.00488293570199</v>
       </c>
       <c r="AW76" t="n">
-        <v>4.330469745142942</v>
+        <v>4.330468688190853</v>
       </c>
       <c r="AX76" t="n">
         <v>0.6655979668654046</v>
       </c>
       <c r="AY76" t="n">
-        <v>1630.819128476293</v>
+        <v>1630.819257451809</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
@@ -15319,7 +15319,7 @@
         </is>
       </c>
       <c r="X77" t="n">
-        <v>192484655104</v>
+        <v>192786563072</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>1</v>
       </c>
       <c r="AA77" t="n">
-        <v>192484655104</v>
+        <v>192786563072</v>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
@@ -15350,16 +15350,16 @@
         <v>853.5238000488281</v>
       </c>
       <c r="AG77" t="n">
-        <v>592.8090673065185</v>
+        <v>592.8090664672851</v>
       </c>
       <c r="AH77" t="n">
         <v>-0.004972059070538326</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.4326367057029938</v>
+        <v>0.4326367077311621</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.439795453748524</v>
+        <v>0.4397954557868269</v>
       </c>
       <c r="AK77" t="n">
         <v>1093.260498046875</v>
@@ -15398,13 +15398,13 @@
         <v>3.550873484324264</v>
       </c>
       <c r="AW77" t="n">
-        <v>10.35245669585564</v>
+        <v>10.35245901137787</v>
       </c>
       <c r="AX77" t="n">
         <v>1.960868398581041</v>
       </c>
       <c r="AY77" t="n">
-        <v>160.1109503783111</v>
+        <v>160.1109940993699</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15544,16 +15544,16 @@
         <v>506.9789990234375</v>
       </c>
       <c r="AG78" t="n">
-        <v>372.7175621795654</v>
+        <v>372.7175619506836</v>
       </c>
       <c r="AH78" t="n">
         <v>-0.07794998933778796</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.2541936278008501</v>
+        <v>0.2541936285710369</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.360222995822205</v>
+        <v>0.3602229966575032</v>
       </c>
       <c r="AK78" t="n">
         <v>746.22998046875</v>
@@ -15592,10 +15592,10 @@
         <v>4.086720860009092</v>
       </c>
       <c r="AW78" t="n">
-        <v>9.009361643595271</v>
+        <v>9.009362461171825</v>
       </c>
       <c r="AX78" t="n">
-        <v>1.49230520914509</v>
+        <v>1.492305006387072</v>
       </c>
       <c r="AY78" t="n">
         <v>686.9065341881163</v>
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="X79" t="n">
-        <v>9269128192</v>
+        <v>9241384960</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>9269128192</v>
+        <v>9241384960</v>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>41796</v>
       </c>
       <c r="AD81" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="AE81" t="n">
         <v>193.7799987792969</v>
@@ -16246,28 +16246,28 @@
         <v>80.51189971923829</v>
       </c>
       <c r="AG82" t="n">
-        <v>72.71620460510253</v>
+        <v>72.71620405197143</v>
       </c>
       <c r="AH82" t="n">
         <v>0.02817097929582979</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.138398232262636</v>
+        <v>0.1383982409221016</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.1072071233155192</v>
+        <v>0.107207131737723</v>
       </c>
       <c r="AK82" t="n">
         <v>88.16000366210938</v>
       </c>
       <c r="AL82" t="n">
-        <v>54.85111618041992</v>
+        <v>54.85111236572266</v>
       </c>
       <c r="AM82" t="n">
         <v>-0.06102546119930341</v>
       </c>
       <c r="AN82" t="n">
-        <v>0.5091761944645106</v>
+        <v>0.5091762994222782</v>
       </c>
       <c r="AO82" t="n">
         <v>44.30379456759083</v>
@@ -16288,19 +16288,19 @@
         <v>0.1546641497796111</v>
       </c>
       <c r="AU82" t="n">
-        <v>0.2210603979322594</v>
+        <v>0.2210605353487962</v>
       </c>
       <c r="AV82" t="n">
-        <v>0.5091761944645106</v>
+        <v>0.5091762994222782</v>
       </c>
       <c r="AW82" t="n">
-        <v>3.502991805179432</v>
+        <v>3.50299227238394</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.189159650897919</v>
+        <v>0.1891595205677554</v>
       </c>
       <c r="AY82" t="n">
-        <v>1322.062696291342</v>
+        <v>1322.06253873877</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -16680,7 +16680,7 @@
         <v>1.798731676783594</v>
       </c>
       <c r="AW84" t="n">
-        <v>6.093158972973854</v>
+        <v>6.093159545211532</v>
       </c>
       <c r="AX84" t="n">
         <v>1.367640725864218</v>
@@ -16793,7 +16793,7 @@
         </is>
       </c>
       <c r="X85" t="n">
-        <v>952164024320</v>
+        <v>958818418688</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>0.1490135192871094</v>
       </c>
       <c r="AA85" t="n">
-        <v>141885312202.5</v>
+        <v>142876906926</v>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
@@ -16872,13 +16872,13 @@
         <v>1.925062653315979</v>
       </c>
       <c r="AW85" t="n">
-        <v>20.54949547055584</v>
+        <v>20.54949764681158</v>
       </c>
       <c r="AX85" t="n">
         <v>0.3070572850742681</v>
       </c>
       <c r="AY85" t="n">
-        <v>174.8805198931744</v>
+        <v>174.8805017722177</v>
       </c>
       <c r="AZ85" t="inlineStr"/>
       <c r="BA85" t="n">
@@ -17064,13 +17064,13 @@
         <v>0.9772146896470653</v>
       </c>
       <c r="AW86" t="n">
-        <v>33.69297118844349</v>
+        <v>33.6929652410634</v>
       </c>
       <c r="AX86" t="n">
         <v>0.2689711133693431</v>
       </c>
       <c r="AY86" t="n">
-        <v>208.3296619432203</v>
+        <v>208.3296890086166</v>
       </c>
       <c r="AZ86" t="inlineStr"/>
       <c r="BA86" t="n">
@@ -17377,7 +17377,7 @@
         </is>
       </c>
       <c r="X88" t="n">
-        <v>132912226304</v>
+        <v>132642119680</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>1</v>
       </c>
       <c r="AA88" t="n">
-        <v>132912226304</v>
+        <v>132642119680</v>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
@@ -17408,16 +17408,16 @@
         <v>164.9623968505859</v>
       </c>
       <c r="AG88" t="n">
-        <v>143.3228862380981</v>
+        <v>143.3228856277466</v>
       </c>
       <c r="AH88" t="n">
         <v>-0.06463529872499096</v>
       </c>
       <c r="AI88" t="n">
-        <v>0.07659011831106799</v>
+        <v>0.07659012289580991</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.1509843346061195</v>
+        <v>0.1509843395076749</v>
       </c>
       <c r="AK88" t="n">
         <v>255.2094421386719</v>
@@ -17456,13 +17456,13 @@
         <v>1.186340685381857</v>
       </c>
       <c r="AW88" t="n">
-        <v>3.365044009992087</v>
+        <v>3.365043538937378</v>
       </c>
       <c r="AX88" t="n">
         <v>0.7107802857547438</v>
       </c>
       <c r="AY88" t="n">
-        <v>200.6566332657931</v>
+        <v>200.6566175571324</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
@@ -17996,16 +17996,16 @@
         <v>220.6539810180664</v>
       </c>
       <c r="AG91" t="n">
-        <v>151.7107284927368</v>
+        <v>151.7107284545899</v>
       </c>
       <c r="AH91" t="n">
         <v>0.01312472143185262</v>
       </c>
       <c r="AI91" t="n">
-        <v>0.4735279783621915</v>
+        <v>0.4735279787327034</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0.4544388733103359</v>
+        <v>0.4544388736760478</v>
       </c>
       <c r="AK91" t="n">
         <v>316.3519592285156</v>
@@ -18044,7 +18044,7 @@
         <v>2.537443400101073</v>
       </c>
       <c r="AW91" t="n">
-        <v>2.675597894780153</v>
+        <v>2.67559720316809</v>
       </c>
       <c r="AX91" t="n">
         <v>1.504508879888965</v>
@@ -18182,22 +18182,22 @@
         <v>25.2</v>
       </c>
       <c r="AE92" t="n">
-        <v>138.6000061035156</v>
+        <v>136.6000061035156</v>
       </c>
       <c r="AF92" t="n">
-        <v>137.0240010070801</v>
+        <v>136.9340010070801</v>
       </c>
       <c r="AG92" t="n">
-        <v>133.9891653442383</v>
+        <v>134.0662514877319</v>
       </c>
       <c r="AH92" t="n">
-        <v>0.01150167185932727</v>
+        <v>-0.002439094024187405</v>
       </c>
       <c r="AI92" t="n">
-        <v>0.03441204180525648</v>
+        <v>0.01889927246914591</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0.02264985870346203</v>
+        <v>0.02139054003169893</v>
       </c>
       <c r="AK92" t="n">
         <v>164.8832092285156</v>
@@ -18206,13 +18206,13 @@
         <v>110.5768280029297</v>
       </c>
       <c r="AM92" t="n">
-        <v>-0.1594049706333255</v>
+        <v>-0.1715347685027262</v>
       </c>
       <c r="AN92" t="n">
-        <v>0.2534272198497454</v>
+        <v>0.2353402477768349</v>
       </c>
       <c r="AO92" t="n">
-        <v>47.05883484339858</v>
+        <v>41.36548424299842</v>
       </c>
       <c r="AP92" t="n">
         <v>116914</v>
@@ -18224,25 +18224,25 @@
         <v>0.6823959654624083</v>
       </c>
       <c r="AS92" t="n">
-        <v>-0.01352308823120552</v>
+        <v>-0.02148997040713196</v>
       </c>
       <c r="AT92" t="n">
-        <v>-0.06854836518178209</v>
+        <v>-0.0572808015361147</v>
       </c>
       <c r="AU92" t="n">
-        <v>0.1910202848549487</v>
+        <v>0.148631798824965</v>
       </c>
       <c r="AV92" t="n">
-        <v>0.1095590104877036</v>
+        <v>0.06101681857966823</v>
       </c>
       <c r="AW92" t="n">
-        <v>1.032763757670876</v>
+        <v>0.9722692738526797</v>
       </c>
       <c r="AX92" t="n">
-        <v>0.1000460083822694</v>
+        <v>0.08417232930666141</v>
       </c>
       <c r="AY92" t="n">
-        <v>7.582065209047114</v>
+        <v>7.458222892886024</v>
       </c>
       <c r="AZ92" t="inlineStr"/>
       <c r="BA92" t="n">
@@ -18348,7 +18348,9 @@
           <t>DKK</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr"/>
+      <c r="X93" t="n">
+        <v>49976172544</v>
+      </c>
       <c r="Y93" t="inlineStr">
         <is>
           <t>DKK</t>
@@ -18357,10 +18359,12 @@
       <c r="Z93" t="n">
         <v>0.1553856730461121</v>
       </c>
-      <c r="AA93" t="inlineStr"/>
+      <c r="AA93" t="n">
+        <v>7765581207.018066</v>
+      </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC93" s="2" t="n">
@@ -18370,22 +18374,22 @@
         <v>25.4</v>
       </c>
       <c r="AE93" t="n">
-        <v>938.5</v>
+        <v>935</v>
       </c>
       <c r="AF93" t="n">
-        <v>926.87</v>
+        <v>926.79</v>
       </c>
       <c r="AG93" t="n">
-        <v>879.5125</v>
+        <v>880.665</v>
       </c>
       <c r="AH93" t="n">
-        <v>0.01254760646045283</v>
+        <v>0.008858533216802078</v>
       </c>
       <c r="AI93" t="n">
-        <v>0.06706840437174</v>
+        <v>0.06169769435596972</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0.05384516990946686</v>
+        <v>0.05237519374563537</v>
       </c>
       <c r="AK93" t="n">
         <v>1112</v>
@@ -18394,43 +18398,43 @@
         <v>604</v>
       </c>
       <c r="AM93" t="n">
-        <v>-0.1560251798561151</v>
+        <v>-0.1591726618705036</v>
       </c>
       <c r="AN93" t="n">
-        <v>0.5538079470198676</v>
+        <v>0.5480132450331126</v>
       </c>
       <c r="AO93" t="n">
-        <v>38.13559322033898</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="AP93" t="n">
-        <v>116158</v>
+        <v>119853</v>
       </c>
       <c r="AQ93" t="n">
-        <v>142165.92</v>
+        <v>142239.82</v>
       </c>
       <c r="AR93" t="n">
-        <v>0.817059390886367</v>
+        <v>0.8426121461627271</v>
       </c>
       <c r="AS93" t="n">
-        <v>0.005356186395286455</v>
+        <v>0.01300108342361872</v>
       </c>
       <c r="AT93" t="n">
-        <v>-0.0567839195979899</v>
+        <v>-0.03008298755186722</v>
       </c>
       <c r="AU93" t="n">
-        <v>0.1716604244694133</v>
+        <v>0.2158647594278285</v>
       </c>
       <c r="AV93" t="n">
-        <v>0.5448559670781894</v>
+        <v>0.5302782324058919</v>
       </c>
       <c r="AW93" t="n">
-        <v>2.517369322333136</v>
+        <v>2.442649163189437</v>
       </c>
       <c r="AX93" t="n">
-        <v>0.1389563106796117</v>
+        <v>0.1347087378640777</v>
       </c>
       <c r="AY93" t="n">
-        <v>26.78660991178884</v>
+        <v>26.6829868959511</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18616,13 +18620,13 @@
         <v>1.204395453300247</v>
       </c>
       <c r="AW94" t="n">
-        <v>0.8486585110230382</v>
+        <v>0.8486588359701124</v>
       </c>
       <c r="AX94" t="n">
         <v>0.5407065100355539</v>
       </c>
       <c r="AY94" t="n">
-        <v>15.78532874115026</v>
+        <v>15.78533376411662</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18729,7 +18733,7 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>35727474688</v>
+        <v>35726909440</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -18740,7 +18744,7 @@
         <v>1.162115097045898</v>
       </c>
       <c r="AA95" t="n">
-        <v>41519437714.25</v>
+        <v>41518780831.01562</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -18754,37 +18758,37 @@
         <v>19.3</v>
       </c>
       <c r="AE95" t="n">
-        <v>119.8000030517578</v>
+        <v>122.25</v>
       </c>
       <c r="AF95" t="n">
-        <v>128.1320007324219</v>
+        <v>127.7200006103516</v>
       </c>
       <c r="AG95" t="n">
-        <v>114.8407136535644</v>
+        <v>115.049761428833</v>
       </c>
       <c r="AH95" t="n">
-        <v>-0.06502667275182716</v>
+        <v>-0.04282806595843547</v>
       </c>
       <c r="AI95" t="n">
-        <v>0.04318406983392542</v>
+        <v>0.06258368971604411</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.1157367161523635</v>
+        <v>0.1101283394607997</v>
       </c>
       <c r="AK95" t="n">
         <v>156.8999938964844</v>
       </c>
       <c r="AL95" t="n">
-        <v>75.9141845703125</v>
+        <v>76.90678405761719</v>
       </c>
       <c r="AM95" t="n">
-        <v>-0.2364562924661647</v>
+        <v>-0.2208412698814055</v>
       </c>
       <c r="AN95" t="n">
-        <v>0.5780977393071753</v>
+        <v>0.5895866859861476</v>
       </c>
       <c r="AO95" t="n">
-        <v>38.23955015428326</v>
+        <v>37.05881904153264</v>
       </c>
       <c r="AP95" t="n">
         <v>960584</v>
@@ -18796,25 +18800,25 @@
         <v>0.8275728359363715</v>
       </c>
       <c r="AS95" t="n">
-        <v>-0.03775097950395334</v>
+        <v>-0.02976190476190477</v>
       </c>
       <c r="AT95" t="n">
-        <v>-0.1587078076783859</v>
+        <v>-0.1030814580864136</v>
       </c>
       <c r="AU95" t="n">
-        <v>0.244000486748926</v>
+        <v>0.2098347273046584</v>
       </c>
       <c r="AV95" t="n">
-        <v>0.5780977393071753</v>
+        <v>0.5895866859861476</v>
       </c>
       <c r="AW95" t="n">
-        <v>3.19291589469076</v>
+        <v>3.200795732759369</v>
       </c>
       <c r="AX95" t="n">
-        <v>0.3428229165472994</v>
+        <v>0.3702846190828928</v>
       </c>
       <c r="AY95" t="n">
-        <v>10.44212830783314</v>
+        <v>10.67612706668819</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -19117,7 +19121,7 @@
         </is>
       </c>
       <c r="X97" t="n">
-        <v>60406931456</v>
+        <v>60496117760</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
@@ -19128,7 +19132,7 @@
         <v>1</v>
       </c>
       <c r="AA97" t="n">
-        <v>60406931456</v>
+        <v>60496117760</v>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
@@ -19148,16 +19152,16 @@
         <v>204.9561422729492</v>
       </c>
       <c r="AG97" t="n">
-        <v>214.6665753936768</v>
+        <v>214.6665748596191</v>
       </c>
       <c r="AH97" t="n">
         <v>0.01802264417436139</v>
       </c>
       <c r="AI97" t="n">
-        <v>-0.02802756547524266</v>
+        <v>-0.02802756305712384</v>
       </c>
       <c r="AJ97" t="n">
-        <v>-0.04523495613101203</v>
+        <v>-0.04523495375570252</v>
       </c>
       <c r="AK97" t="n">
         <v>246.3216247558594</v>
@@ -19196,13 +19200,13 @@
         <v>0.01043765035190325</v>
       </c>
       <c r="AW97" t="n">
-        <v>0.4768451916538574</v>
+        <v>0.4768448726458816</v>
       </c>
       <c r="AX97" t="n">
-        <v>-0.09562325147653095</v>
+        <v>-0.09562319166285438</v>
       </c>
       <c r="AY97" t="n">
-        <v>6.838324819392996</v>
+        <v>6.83833099744055</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19344,16 +19348,16 @@
         <v>383.6615997314453</v>
       </c>
       <c r="AG98" t="n">
-        <v>369.0301217651367</v>
+        <v>369.0301223754883</v>
       </c>
       <c r="AH98" t="n">
         <v>-0.06714668826120085</v>
       </c>
       <c r="AI98" t="n">
-        <v>-0.03016048612892341</v>
+        <v>-0.03016048773297431</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.03964846526978261</v>
+        <v>0.03964846355027207</v>
       </c>
       <c r="AK98" t="n">
         <v>480.8090515136719</v>
@@ -19389,16 +19393,16 @@
         <v>0.03895418071335155</v>
       </c>
       <c r="AV98" t="n">
-        <v>0.07653956505391668</v>
+        <v>0.07653966387472577</v>
       </c>
       <c r="AW98" t="n">
-        <v>6.88012106085648</v>
+        <v>6.880120398999536</v>
       </c>
       <c r="AX98" t="n">
         <v>0.03336521571714868</v>
       </c>
       <c r="AY98" t="n">
-        <v>314.1662079586145</v>
+        <v>314.1660756197175</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19930,16 +19934,16 @@
         <v>79.47389526367188</v>
       </c>
       <c r="AG101" t="n">
-        <v>76.57119590759277</v>
+        <v>76.57119604110717</v>
       </c>
       <c r="AH101" t="n">
         <v>-0.06673760078236679</v>
       </c>
       <c r="AI101" t="n">
-        <v>-0.03135902097631149</v>
+        <v>-0.03135902266529544</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0.03790850229872511</v>
+        <v>0.03790850048896188</v>
       </c>
       <c r="AK101" t="n">
         <v>102.0957336425781</v>
@@ -19975,16 +19979,16 @@
         <v>0.1537037905116458</v>
       </c>
       <c r="AV101" t="n">
-        <v>0.1546218497375511</v>
+        <v>0.1546219868703691</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.04045089012849479</v>
+        <v>0.04045100148229008</v>
       </c>
       <c r="AX101" t="n">
-        <v>0.159961629764936</v>
+        <v>0.1599614913608218</v>
       </c>
       <c r="AY101" t="n">
-        <v>423.7385477634827</v>
+        <v>423.7385840074089</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20091,7 +20095,7 @@
         </is>
       </c>
       <c r="X102" t="n">
-        <v>46594326528</v>
+        <v>46601060352</v>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
@@ -20102,7 +20106,7 @@
         <v>1</v>
       </c>
       <c r="AA102" t="n">
-        <v>46594326528</v>
+        <v>46601060352</v>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
@@ -20122,16 +20126,16 @@
         <v>57.98179985046387</v>
       </c>
       <c r="AG102" t="n">
-        <v>45.22651369094849</v>
+        <v>45.22651368141175</v>
       </c>
       <c r="AH102" t="n">
         <v>-0.09902759463840849</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.1550746987805511</v>
+        <v>0.1550746990241174</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.282031160895521</v>
+        <v>0.2820311611658581</v>
       </c>
       <c r="AK102" t="n">
         <v>79.81999969482422</v>
@@ -20170,13 +20174,13 @@
         <v>0.965510144239857</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.2150964413380076</v>
+        <v>0.2150963335232143</v>
       </c>
       <c r="AX102" t="n">
         <v>0.9162585781497119</v>
       </c>
       <c r="AY102" t="n">
-        <v>22.857442301442</v>
+        <v>22.85745788749725</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20473,7 +20477,7 @@
         </is>
       </c>
       <c r="X104" t="n">
-        <v>698883899392</v>
+        <v>699089813504</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -20484,7 +20488,7 @@
         <v>0.03162555396556854</v>
       </c>
       <c r="AA104" t="n">
-        <v>22102590475.88867</v>
+        <v>22109102623.75</v>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
@@ -20558,7 +20562,7 @@
         <v>0.8947622560122885</v>
       </c>
       <c r="AY104" t="n">
-        <v>80.45077584829582</v>
+        <v>80.45075530643834</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20690,22 +20694,22 @@
         <v>26.7</v>
       </c>
       <c r="AE105" t="n">
-        <v>287.3500061035156</v>
+        <v>288</v>
       </c>
       <c r="AF105" t="n">
-        <v>284.3249993896484</v>
+        <v>284.5639996337891</v>
       </c>
       <c r="AG105" t="n">
-        <v>258.8802863311768</v>
+        <v>259.1958814239502</v>
       </c>
       <c r="AH105" t="n">
-        <v>0.01063925690797807</v>
+        <v>0.01207461369193852</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.1099725289082789</v>
+        <v>0.1111287664673064</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.09828756534177008</v>
+        <v>0.09787238157671907</v>
       </c>
       <c r="AK105" t="n">
         <v>311</v>
@@ -20714,13 +20718,13 @@
         <v>218.8749847412109</v>
       </c>
       <c r="AM105" t="n">
-        <v>-0.07604499645171825</v>
+        <v>-0.07395498392282962</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.3128499195249144</v>
+        <v>0.3158196234280484</v>
       </c>
       <c r="AO105" t="n">
-        <v>32.27910124556999</v>
+        <v>30.06726173445217</v>
       </c>
       <c r="AP105" t="n">
         <v>462863</v>
@@ -20732,25 +20736,25 @@
         <v>0.6024548960278089</v>
       </c>
       <c r="AS105" t="n">
-        <v>-0.04407850875238239</v>
+        <v>-0.05169579050371786</v>
       </c>
       <c r="AT105" t="n">
-        <v>0.09071927420410453</v>
+        <v>0.1175785268051377</v>
       </c>
       <c r="AU105" t="n">
-        <v>0.1904815187371638</v>
+        <v>0.1468602684283677</v>
       </c>
       <c r="AV105" t="n">
-        <v>0.3060932714013402</v>
+        <v>0.2776008593888024</v>
       </c>
       <c r="AW105" t="n">
-        <v>1.238226407353149</v>
+        <v>1.204109344767292</v>
       </c>
       <c r="AX105" t="n">
-        <v>0.2311602944909676</v>
+        <v>0.233945214136053</v>
       </c>
       <c r="AY105" t="n">
-        <v>14.44130840284293</v>
+        <v>14.47623549592439</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20765,12 +20769,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -20780,19 +20784,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Power distribution + UPS</t>
+          <t>Power distribution / UPS / electrical</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Power distribution, electrical infra, UPS</t>
+          <t>Electrical/data center infrastructure</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -20800,11 +20804,7 @@
       <c r="I106" t="n">
         <v>0</v>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" s="1" t="n">
         <v>46195</v>
       </c>
@@ -20842,7 +20842,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Eaton Corporation plc</t>
+          <t>Legrand SA</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -20852,27 +20852,27 @@
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X106" t="n">
-        <v>159574147072</v>
+        <v>36934975488</v>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>1</v>
+        <v>1.162115097045898</v>
       </c>
       <c r="AA106" t="n">
-        <v>159574147072</v>
+        <v>42922692623.625</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
@@ -20880,77 +20880,77 @@
         </is>
       </c>
       <c r="AC106" s="2" t="n">
-        <v>26451</v>
+        <v>38814</v>
       </c>
       <c r="AD106" t="n">
-        <v>54.3</v>
+        <v>20.4</v>
       </c>
       <c r="AE106" t="n">
-        <v>410.8500061035156</v>
+        <v>140.8999938964844</v>
       </c>
       <c r="AF106" t="n">
-        <v>414.7404779052735</v>
+        <v>137.915998840332</v>
       </c>
       <c r="AG106" t="n">
-        <v>379.2283897399902</v>
+        <v>137.8624683380127</v>
       </c>
       <c r="AH106" t="n">
-        <v>-0.009380496983095066</v>
+        <v>0.02163632269818794</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.08338409575613803</v>
+        <v>0.02203301300992422</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.09364301071876846</v>
+        <v>0.0003882891621243001</v>
       </c>
       <c r="AK106" t="n">
-        <v>459.9599914550781</v>
+        <v>157.5401306152344</v>
       </c>
       <c r="AL106" t="n">
-        <v>313.2000427246094</v>
+        <v>121.6237258911133</v>
       </c>
       <c r="AM106" t="n">
-        <v>-0.1067701240627552</v>
+        <v>-0.1056247487783971</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.3117814497387152</v>
+        <v>0.1584910169799325</v>
       </c>
       <c r="AO106" t="n">
-        <v>30.49304368137287</v>
+        <v>50.1804887104353</v>
       </c>
       <c r="AP106" t="n">
-        <v>1889700</v>
+        <v>615406</v>
       </c>
       <c r="AQ106" t="n">
-        <v>2175164</v>
+        <v>547028.72</v>
       </c>
       <c r="AR106" t="n">
-        <v>0.8687620795489444</v>
+        <v>1.124997605244566</v>
       </c>
       <c r="AS106" t="n">
-        <v>-0.08431395914638384</v>
+        <v>0.004992845673888358</v>
       </c>
       <c r="AT106" t="n">
-        <v>0.02163227641912413</v>
+        <v>0.03299120382230436</v>
       </c>
       <c r="AU106" t="n">
-        <v>0.1707317857940103</v>
+        <v>0.02168740445215223</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.1902434526249752</v>
+        <v>0.04137804414015922</v>
       </c>
       <c r="AW106" t="n">
-        <v>1.608434246749056</v>
+        <v>0.7092154610516277</v>
       </c>
       <c r="AX106" t="n">
-        <v>0.265732345936597</v>
+        <v>0.1204184924182647</v>
       </c>
       <c r="AY106" t="n">
-        <v>1191.448286226923</v>
+        <v>9.405788586438433</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
@@ -20961,12 +20961,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Delta Electronics</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -20976,19 +20976,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power distribution + UPS</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Power supplies, thermal, data center power</t>
+          <t>Power distribution, electrical infra, UPS</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>9</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -20996,7 +20996,11 @@
       <c r="I107" t="n">
         <v>0</v>
       </c>
-      <c r="J107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
       <c r="K107" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21034,37 +21038,37 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>Delta Electronics, Inc.</t>
+          <t>Eaton Corporation plc</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X107" t="n">
-        <v>4740516675584</v>
+        <v>159533056000</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>0.03162555396556854</v>
+        <v>1</v>
       </c>
       <c r="AA107" t="n">
-        <v>149921465948.3594</v>
+        <v>159533056000</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
@@ -21072,93 +21076,93 @@
         </is>
       </c>
       <c r="AC107" s="2" t="n">
-        <v>36529</v>
+        <v>26451</v>
       </c>
       <c r="AD107" t="n">
-        <v>26.7</v>
+        <v>54.3</v>
       </c>
       <c r="AE107" t="n">
-        <v>1825</v>
+        <v>410.8500061035156</v>
       </c>
       <c r="AF107" t="n">
-        <v>1798.5</v>
+        <v>414.7404779052735</v>
       </c>
       <c r="AG107" t="n">
-        <v>1574.711428527832</v>
+        <v>379.2283889770508</v>
       </c>
       <c r="AH107" t="n">
-        <v>0.01473450097303308</v>
+        <v>-0.009380496983095066</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.1589425001545572</v>
+        <v>0.08338409793571255</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.1421140200153266</v>
+        <v>0.09364301291898203</v>
       </c>
       <c r="AK107" t="n">
-        <v>2506.891357421875</v>
+        <v>459.9599914550781</v>
       </c>
       <c r="AL107" t="n">
-        <v>672.4835815429688</v>
+        <v>313.2000427246094</v>
       </c>
       <c r="AM107" t="n">
-        <v>-0.2720067446892244</v>
+        <v>-0.1067701240627552</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.71382090223327</v>
+        <v>0.3117814497387152</v>
       </c>
       <c r="AO107" t="n">
-        <v>44.73684210526316</v>
+        <v>30.49304368137287</v>
       </c>
       <c r="AP107" t="n">
-        <v>8546741</v>
+        <v>1889700</v>
       </c>
       <c r="AQ107" t="n">
-        <v>10881006.94</v>
+        <v>2175164</v>
       </c>
       <c r="AR107" t="n">
-        <v>0.7854733525241185</v>
+        <v>0.8687620795489444</v>
       </c>
       <c r="AS107" t="n">
-        <v>0.106060606060606</v>
+        <v>-0.08431395914638384</v>
       </c>
       <c r="AT107" t="n">
-        <v>-0.2403548479408933</v>
+        <v>0.02163227641912413</v>
       </c>
       <c r="AU107" t="n">
-        <v>0.5037237036438023</v>
+        <v>0.1707317857940103</v>
       </c>
       <c r="AV107" t="n">
-        <v>1.71382090223327</v>
+        <v>0.1902434526249752</v>
       </c>
       <c r="AW107" t="n">
-        <v>5.823234019141283</v>
+        <v>1.608434246749056</v>
       </c>
       <c r="AX107" t="n">
-        <v>0.8437617158981037</v>
+        <v>0.265732345936597</v>
       </c>
       <c r="AY107" t="n">
-        <v>72.88081817110643</v>
+        <v>1191.44921452781</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>Positive momentum</t>
+          <t>Strong momentum</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Delta Electronics</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -21168,31 +21172,27 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Analog/power semiconductors</t>
+          <t>Power supplies, thermal, data center power</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21230,7 +21230,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Delta Electronics, Inc.</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -21240,27 +21240,27 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X108" t="n">
-        <v>175533834240</v>
+        <v>4740516675584</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>1</v>
+        <v>0.03162555396556854</v>
       </c>
       <c r="AA108" t="n">
-        <v>175533834240</v>
+        <v>149921465948.3594</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -21268,73 +21268,73 @@
         </is>
       </c>
       <c r="AC108" s="2" t="n">
-        <v>29297</v>
+        <v>36529</v>
       </c>
       <c r="AD108" t="n">
-        <v>46.5</v>
+        <v>26.7</v>
       </c>
       <c r="AE108" t="n">
-        <v>362.25</v>
+        <v>1825</v>
       </c>
       <c r="AF108" t="n">
-        <v>376.3057611083984</v>
+        <v>1798.5</v>
       </c>
       <c r="AG108" t="n">
-        <v>346.286672744751</v>
+        <v>1574.711428527832</v>
       </c>
       <c r="AH108" t="n">
-        <v>-0.03735196896002224</v>
+        <v>0.01473450097303308</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.04609858972833081</v>
+        <v>0.1589425001545572</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.0866885465897631</v>
+        <v>0.1421140200153266</v>
       </c>
       <c r="AK108" t="n">
-        <v>444.1268615722656</v>
+        <v>2506.891357421875</v>
       </c>
       <c r="AL108" t="n">
-        <v>222.418212890625</v>
+        <v>672.4835815429688</v>
       </c>
       <c r="AM108" t="n">
-        <v>-0.1843546712811089</v>
+        <v>-0.2720067446892244</v>
       </c>
       <c r="AN108" t="n">
-        <v>0.6286885650777969</v>
+        <v>1.71382090223327</v>
       </c>
       <c r="AO108" t="n">
-        <v>27.28635163406187</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="AP108" t="n">
-        <v>3559800</v>
+        <v>8546741</v>
       </c>
       <c r="AQ108" t="n">
-        <v>4096650</v>
+        <v>10881006.94</v>
       </c>
       <c r="AR108" t="n">
-        <v>0.868953901358427</v>
+        <v>0.7854733525241185</v>
       </c>
       <c r="AS108" t="n">
-        <v>-0.06815659562041276</v>
+        <v>0.106060606060606</v>
       </c>
       <c r="AT108" t="n">
-        <v>-0.100364789243492</v>
+        <v>-0.2403548479408933</v>
       </c>
       <c r="AU108" t="n">
-        <v>0.1396232972554954</v>
+        <v>0.5037237036438023</v>
       </c>
       <c r="AV108" t="n">
-        <v>0.4845212296572881</v>
+        <v>1.71382090223327</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.358407012392745</v>
+        <v>5.823234019141283</v>
       </c>
       <c r="AX108" t="n">
-        <v>0.335171270677217</v>
+        <v>0.8437617158981037</v>
       </c>
       <c r="AY108" t="n">
-        <v>818.0759608132261</v>
+        <v>72.8807953524293</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21349,12 +21349,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21369,22 +21369,26 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Power semiconductors</t>
+          <t>Analog/power semiconductors</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+        </is>
+      </c>
       <c r="K109" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21422,7 +21426,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>Infineon Technologies AG</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -21437,22 +21441,22 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X109" t="n">
-        <v>73889554432</v>
+        <v>175533834240</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>1.162115097045898</v>
+        <v>1</v>
       </c>
       <c r="AA109" t="n">
-        <v>85868166719.42188</v>
+        <v>175533834240</v>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
@@ -21460,73 +21464,73 @@
         </is>
       </c>
       <c r="AC109" s="2" t="n">
-        <v>36598</v>
+        <v>29297</v>
       </c>
       <c r="AD109" t="n">
-        <v>26.5</v>
+        <v>46.5</v>
       </c>
       <c r="AE109" t="n">
-        <v>55.52999877929688</v>
+        <v>362.25</v>
       </c>
       <c r="AF109" t="n">
-        <v>64.11040023803712</v>
+        <v>376.3057611083984</v>
       </c>
       <c r="AG109" t="n">
-        <v>53.17253916740417</v>
+        <v>346.2866735076904</v>
       </c>
       <c r="AH109" t="n">
-        <v>-0.133837901914227</v>
+        <v>-0.03735196896002224</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.04433603602172664</v>
+        <v>0.04609858742356443</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.2057050733687373</v>
+        <v>0.08668854419556915</v>
       </c>
       <c r="AK109" t="n">
-        <v>88</v>
+        <v>444.1268615722656</v>
       </c>
       <c r="AL109" t="n">
-        <v>31.33389091491699</v>
+        <v>222.418212890625</v>
       </c>
       <c r="AM109" t="n">
-        <v>-0.3689772865988992</v>
+        <v>-0.1843546712811089</v>
       </c>
       <c r="AN109" t="n">
-        <v>0.7722024669735779</v>
+        <v>0.6286885650777969</v>
       </c>
       <c r="AO109" t="n">
-        <v>29.52444038730508</v>
+        <v>27.28635163406187</v>
       </c>
       <c r="AP109" t="n">
-        <v>3388895</v>
+        <v>3559800</v>
       </c>
       <c r="AQ109" t="n">
-        <v>4175352</v>
+        <v>4096650</v>
       </c>
       <c r="AR109" t="n">
-        <v>0.811642946510857</v>
+        <v>0.868953901358427</v>
       </c>
       <c r="AS109" t="n">
-        <v>-0.07940982990320455</v>
+        <v>-0.06815659562041276</v>
       </c>
       <c r="AT109" t="n">
-        <v>-0.2660587352428802</v>
+        <v>-0.100364789243492</v>
       </c>
       <c r="AU109" t="n">
-        <v>0.4256738816840571</v>
+        <v>0.1396232972554954</v>
       </c>
       <c r="AV109" t="n">
-        <v>0.7722024669735779</v>
+        <v>0.4845211368281166</v>
       </c>
       <c r="AW109" t="n">
-        <v>0.5451704374774571</v>
+        <v>1.358406309530338</v>
       </c>
       <c r="AX109" t="n">
-        <v>0.4623623075877534</v>
+        <v>0.335171270677217</v>
       </c>
       <c r="AY109" t="n">
-        <v>0.09911259201204459</v>
+        <v>818.0763471698114</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21541,12 +21545,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nVent Electric</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -21556,12 +21560,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Enclosures, electrical/thermal infra</t>
+          <t>Power semiconductors</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -21614,37 +21618,37 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>nVent Electric plc</t>
+          <t>Infineon Technologies AG</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X110" t="n">
-        <v>25254692864</v>
+        <v>73889554432</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>1</v>
+        <v>1.162115097045898</v>
       </c>
       <c r="AA110" t="n">
-        <v>25254692864</v>
+        <v>85868166719.42188</v>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
@@ -21652,73 +21656,73 @@
         </is>
       </c>
       <c r="AC110" s="2" t="n">
-        <v>43214</v>
+        <v>36598</v>
       </c>
       <c r="AD110" t="n">
-        <v>8.4</v>
+        <v>26.5</v>
       </c>
       <c r="AE110" t="n">
-        <v>156.0299987792969</v>
+        <v>56.86000061035156</v>
       </c>
       <c r="AF110" t="n">
-        <v>157.2081240844726</v>
+        <v>63.68160018920899</v>
       </c>
       <c r="AG110" t="n">
-        <v>135.1467782974243</v>
+        <v>53.29317355155945</v>
       </c>
       <c r="AH110" t="n">
-        <v>-0.007494048491684335</v>
+        <v>-0.1071204171784201</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.1545225179982745</v>
+        <v>0.0669284041668361</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.1632398941726663</v>
+        <v>0.1949297807832566</v>
       </c>
       <c r="AK110" t="n">
-        <v>184.09619140625</v>
+        <v>88</v>
       </c>
       <c r="AL110" t="n">
-        <v>90.83205413818359</v>
+        <v>31.45297431945801</v>
       </c>
       <c r="AM110" t="n">
-        <v>-0.1524539557965037</v>
+        <v>-0.3538636294278231</v>
       </c>
       <c r="AN110" t="n">
-        <v>0.7177856458241831</v>
+        <v>0.8077781780776072</v>
       </c>
       <c r="AO110" t="n">
-        <v>30.4106631922795</v>
+        <v>34.25754912685052</v>
       </c>
       <c r="AP110" t="n">
-        <v>1610500</v>
+        <v>3389854</v>
       </c>
       <c r="AQ110" t="n">
-        <v>2308326</v>
+        <v>4175371.18</v>
       </c>
       <c r="AR110" t="n">
-        <v>0.6976917471795578</v>
+        <v>0.811868898323909</v>
       </c>
       <c r="AS110" t="n">
-        <v>-0.05258366345091559</v>
+        <v>-0.08408506872968369</v>
       </c>
       <c r="AT110" t="n">
-        <v>-0.0462326515163245</v>
+        <v>-0.2428761416027845</v>
       </c>
       <c r="AU110" t="n">
-        <v>0.4470248527408771</v>
+        <v>0.3762556577599199</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.692611167188022</v>
+        <v>0.7863609131426741</v>
       </c>
       <c r="AW110" t="n">
-        <v>3.838887010492807</v>
+        <v>0.5804970448734528</v>
       </c>
       <c r="AX110" t="n">
-        <v>0.4675328803734569</v>
+        <v>0.4973874217514909</v>
       </c>
       <c r="AY110" t="n">
-        <v>7.170016149344988</v>
+        <v>0.1254375786996094</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21733,12 +21737,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>nVent Electric</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -21748,19 +21752,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Power distribution / UPS / electrical</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Grid/electrical infrastructure construction</t>
+          <t>Enclosures, electrical/thermal infra</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -21768,11 +21772,7 @@
       <c r="I111" t="n">
         <v>0</v>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21810,7 +21810,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>Quanta Services, Inc.</t>
+          <t>nVent Electric plc</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -21820,7 +21820,7 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -21829,7 +21829,7 @@
         </is>
       </c>
       <c r="X111" t="n">
-        <v>93875912704</v>
+        <v>25254692864</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>1</v>
       </c>
       <c r="AA111" t="n">
-        <v>93875912704</v>
+        <v>25254692864</v>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
@@ -21848,73 +21848,73 @@
         </is>
       </c>
       <c r="AC111" s="2" t="n">
-        <v>35838</v>
+        <v>43214</v>
       </c>
       <c r="AD111" t="n">
-        <v>28.6</v>
+        <v>8.4</v>
       </c>
       <c r="AE111" t="n">
-        <v>624.4099731445312</v>
+        <v>156.0299987792969</v>
       </c>
       <c r="AF111" t="n">
-        <v>652.1693212890625</v>
+        <v>157.2081240844726</v>
       </c>
       <c r="AG111" t="n">
-        <v>587.7318704223633</v>
+        <v>135.1467779922485</v>
       </c>
       <c r="AH111" t="n">
-        <v>-0.04256463350600848</v>
+        <v>-0.007494048491684335</v>
       </c>
       <c r="AI111" t="n">
-        <v>0.06240618310490786</v>
+        <v>0.1545225206053089</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.1096374964665305</v>
+        <v>0.1632398967993856</v>
       </c>
       <c r="AK111" t="n">
-        <v>785.1200561523438</v>
+        <v>184.09619140625</v>
       </c>
       <c r="AL111" t="n">
-        <v>372.1830444335938</v>
+        <v>90.83205413818359</v>
       </c>
       <c r="AM111" t="n">
-        <v>-0.2046949148075623</v>
+        <v>-0.1524539557965037</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.6776959146400361</v>
+        <v>0.7177856458241831</v>
       </c>
       <c r="AO111" t="n">
-        <v>22.59849885678597</v>
+        <v>30.4106631922795</v>
       </c>
       <c r="AP111" t="n">
-        <v>653600</v>
+        <v>1610500</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1211894</v>
+        <v>2308326</v>
       </c>
       <c r="AR111" t="n">
-        <v>0.5393210957393964</v>
+        <v>0.6976917471795578</v>
       </c>
       <c r="AS111" t="n">
-        <v>-0.0706248522632319</v>
+        <v>-0.05258366345091559</v>
       </c>
       <c r="AT111" t="n">
-        <v>-0.09988987867473609</v>
+        <v>-0.0462326515163245</v>
       </c>
       <c r="AU111" t="n">
-        <v>0.09961984273045954</v>
+        <v>0.4470248527408771</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.6776959146400361</v>
+        <v>0.6926110271015053</v>
       </c>
       <c r="AW111" t="n">
-        <v>5.086144247483245</v>
+        <v>3.838887010492807</v>
       </c>
       <c r="AX111" t="n">
-        <v>0.4206425136138741</v>
+        <v>0.4675327750663654</v>
       </c>
       <c r="AY111" t="n">
-        <v>83.9061027192683</v>
+        <v>7.170015333387065</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -21929,12 +21929,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -21944,16 +21944,16 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power distribution / UPS / electrical</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>HVAC/cooling</t>
+          <t>Grid/electrical infrastructure construction</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Trane Technologies plc</t>
+          <t>Quanta Services, Inc.</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -22016,7 +22016,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>Building Products &amp; Equipment</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -22025,7 +22025,7 @@
         </is>
       </c>
       <c r="X112" t="n">
-        <v>98548383744</v>
+        <v>93875912704</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>1</v>
       </c>
       <c r="AA112" t="n">
-        <v>98548383744</v>
+        <v>93875912704</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
@@ -22044,73 +22044,73 @@
         </is>
       </c>
       <c r="AC112" s="2" t="n">
-        <v>29297</v>
+        <v>35838</v>
       </c>
       <c r="AD112" t="n">
-        <v>46.5</v>
+        <v>28.6</v>
       </c>
       <c r="AE112" t="n">
-        <v>447.8999938964844</v>
+        <v>624.4099731445312</v>
       </c>
       <c r="AF112" t="n">
-        <v>467.3381292724609</v>
+        <v>652.1693212890625</v>
       </c>
       <c r="AG112" t="n">
-        <v>442.3180722045898</v>
+        <v>587.7318704223633</v>
       </c>
       <c r="AH112" t="n">
-        <v>-0.04159330077825518</v>
+        <v>-0.04256463350600848</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.01261970071463114</v>
+        <v>0.06240618310490786</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.05656575808256448</v>
+        <v>0.1096374964665305</v>
       </c>
       <c r="AK112" t="n">
-        <v>502.2725524902344</v>
+        <v>785.1200561523438</v>
       </c>
       <c r="AL112" t="n">
-        <v>373.7903137207031</v>
+        <v>372.1830444335938</v>
       </c>
       <c r="AM112" t="n">
-        <v>-0.1082530955039738</v>
+        <v>-0.2046949148075623</v>
       </c>
       <c r="AN112" t="n">
-        <v>0.1982653842420223</v>
+        <v>0.6776959146400361</v>
       </c>
       <c r="AO112" t="n">
-        <v>31.6372782658798</v>
+        <v>22.59849885678597</v>
       </c>
       <c r="AP112" t="n">
-        <v>1041800</v>
+        <v>653600</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1142518</v>
+        <v>1211894</v>
       </c>
       <c r="AR112" t="n">
-        <v>0.9118455901788856</v>
+        <v>0.5393210957393964</v>
       </c>
       <c r="AS112" t="n">
-        <v>-0.06914872329709676</v>
+        <v>-0.0706248522632319</v>
       </c>
       <c r="AT112" t="n">
-        <v>-0.02170556049512806</v>
+        <v>-0.09988987867473609</v>
       </c>
       <c r="AU112" t="n">
-        <v>0.05253017166666996</v>
+        <v>0.0996199609244548</v>
       </c>
       <c r="AV112" t="n">
-        <v>0.08997192707857971</v>
+        <v>0.6776959146400361</v>
       </c>
       <c r="AW112" t="n">
-        <v>1.385988741455177</v>
+        <v>5.086142889714263</v>
       </c>
       <c r="AX112" t="n">
-        <v>0.133324247251589</v>
+        <v>0.4206424149746111</v>
       </c>
       <c r="AY112" t="n">
-        <v>502.5952888585201</v>
+        <v>83.9061027192683</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22125,12 +22125,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -22140,29 +22140,29 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Analog/power semiconductors</t>
+          <t>HVAC/cooling</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="K113" s="1" t="n">
@@ -22202,17 +22202,17 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>Trane Technologies plc</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Building Products &amp; Equipment</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="X113" t="n">
-        <v>236019728384</v>
+        <v>98548383744</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
@@ -22232,81 +22232,81 @@
         <v>1</v>
       </c>
       <c r="AA113" t="n">
-        <v>236019728384</v>
+        <v>98548383744</v>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC113" s="2" t="n">
-        <v>26451</v>
+        <v>29297</v>
       </c>
       <c r="AD113" t="n">
-        <v>54.3</v>
+        <v>46.5</v>
       </c>
       <c r="AE113" t="n">
-        <v>258.4400024414062</v>
+        <v>447.8999938964844</v>
       </c>
       <c r="AF113" t="n">
-        <v>279.3170593261719</v>
+        <v>467.3381292724609</v>
       </c>
       <c r="AG113" t="n">
-        <v>237.4760774993896</v>
+        <v>442.318073425293</v>
       </c>
       <c r="AH113" t="n">
-        <v>-0.07474322168194714</v>
+        <v>-0.04159330077825518</v>
       </c>
       <c r="AI113" t="n">
-        <v>0.08827804957352181</v>
+        <v>0.01261969792001771</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.1761903020605928</v>
+        <v>0.05656575516666917</v>
       </c>
       <c r="AK113" t="n">
-        <v>330.5873718261719</v>
+        <v>502.2725524902344</v>
       </c>
       <c r="AL113" t="n">
-        <v>150.7934722900391</v>
+        <v>373.7903137207031</v>
       </c>
       <c r="AM113" t="n">
-        <v>-0.2182399436077125</v>
+        <v>-0.1082530955039738</v>
       </c>
       <c r="AN113" t="n">
-        <v>0.7138673081571978</v>
+        <v>0.1982653842420223</v>
       </c>
       <c r="AO113" t="n">
-        <v>28.28749017724023</v>
+        <v>31.6372782658798</v>
       </c>
       <c r="AP113" t="n">
-        <v>4242600</v>
+        <v>1041800</v>
       </c>
       <c r="AQ113" t="n">
-        <v>7520732</v>
+        <v>1142518</v>
       </c>
       <c r="AR113" t="n">
-        <v>0.5641206201736746</v>
+        <v>0.9118455901788856</v>
       </c>
       <c r="AS113" t="n">
-        <v>-0.09661628016008506</v>
+        <v>-0.06914872329709676</v>
       </c>
       <c r="AT113" t="n">
-        <v>-0.107035958924693</v>
+        <v>-0.02170556049512806</v>
       </c>
       <c r="AU113" t="n">
-        <v>0.3306988250778284</v>
+        <v>0.05253017166666996</v>
       </c>
       <c r="AV113" t="n">
-        <v>0.4108063627675791</v>
+        <v>0.08997192707857971</v>
       </c>
       <c r="AW113" t="n">
-        <v>0.5554848601010631</v>
+        <v>1.385988741455177</v>
       </c>
       <c r="AX113" t="n">
-        <v>0.4803247688325962</v>
+        <v>0.133324247251589</v>
       </c>
       <c r="AY113" t="n">
-        <v>376.7952321810614</v>
+        <v>502.5954913532802</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22321,12 +22321,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -22336,29 +22336,29 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Critical power + liquid/thermal cooling</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Power, cooling, thermal management AI data centers</t>
+          <t>Analog/power semiconductors</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
         </is>
       </c>
       <c r="K114" s="1" t="n">
@@ -22393,20 +22393,22 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr"/>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -22415,7 +22417,7 @@
         </is>
       </c>
       <c r="X114" t="n">
-        <v>108000731136</v>
+        <v>236019728384</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -22426,81 +22428,81 @@
         <v>1</v>
       </c>
       <c r="AA114" t="n">
-        <v>108000731136</v>
+        <v>236019728384</v>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC114" s="2" t="n">
-        <v>43314</v>
+        <v>26451</v>
       </c>
       <c r="AD114" t="n">
-        <v>8.1</v>
+        <v>54.3</v>
       </c>
       <c r="AE114" t="n">
-        <v>280.5299987792969</v>
+        <v>258.4400024414062</v>
       </c>
       <c r="AF114" t="n">
-        <v>282.6975997924804</v>
+        <v>279.3170593261719</v>
       </c>
       <c r="AG114" t="n">
-        <v>257.3463870239258</v>
+        <v>237.4760765075684</v>
       </c>
       <c r="AH114" t="n">
-        <v>-0.007667560724869071</v>
+        <v>-0.07474322168194714</v>
       </c>
       <c r="AI114" t="n">
-        <v>0.09008718569348195</v>
+        <v>0.08827805411872625</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.09851007842669945</v>
+        <v>0.1761903069729638</v>
       </c>
       <c r="AK114" t="n">
-        <v>376.1517333984375</v>
+        <v>330.5873718261719</v>
       </c>
       <c r="AL114" t="n">
-        <v>121.6859512329102</v>
+        <v>150.7934722900391</v>
       </c>
       <c r="AM114" t="n">
-        <v>-0.2542105382719415</v>
+        <v>-0.2182399436077125</v>
       </c>
       <c r="AN114" t="n">
-        <v>1.305360610136128</v>
+        <v>0.7138673081571978</v>
       </c>
       <c r="AO114" t="n">
-        <v>44.06069517796179</v>
+        <v>28.28749017724023</v>
       </c>
       <c r="AP114" t="n">
-        <v>3318600</v>
+        <v>4242600</v>
       </c>
       <c r="AQ114" t="n">
-        <v>5624534</v>
+        <v>7520732</v>
       </c>
       <c r="AR114" t="n">
-        <v>0.590022213395812</v>
+        <v>0.5641206201736746</v>
       </c>
       <c r="AS114" t="n">
-        <v>0.02984583357186854</v>
+        <v>-0.09661628016008506</v>
       </c>
       <c r="AT114" t="n">
-        <v>-0.06647913802224004</v>
+        <v>-0.107035958924693</v>
       </c>
       <c r="AU114" t="n">
-        <v>0.06168004814769179</v>
+        <v>0.3306988250778284</v>
       </c>
       <c r="AV114" t="n">
-        <v>1.26483067955771</v>
+        <v>0.4108064802830889</v>
       </c>
       <c r="AW114" t="n">
-        <v>8.872898371418461</v>
+        <v>0.5554845743934418</v>
       </c>
       <c r="AX114" t="n">
-        <v>0.5981727880012997</v>
+        <v>0.4803247688325962</v>
       </c>
       <c r="AY114" t="n">
-        <v>27.23042269573897</v>
+        <v>376.7953638530685</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22515,12 +22517,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6367.T</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Daikin Industries</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -22530,19 +22532,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Critical power + liquid/thermal cooling</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>HVAC/cooling</t>
+          <t>Power, cooling, thermal management AI data centers</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -22550,7 +22552,11 @@
       <c r="I115" t="n">
         <v>0</v>
       </c>
-      <c r="J115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
       <c r="K115" s="1" t="n">
         <v>46195</v>
       </c>
@@ -22583,12 +22589,10 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
+      <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr">
         <is>
-          <t>Daikin Industries,Ltd.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -22598,27 +22602,27 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>Building Products &amp; Equipment</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X115" t="n">
-        <v>5705890791424</v>
+        <v>108000731136</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>0.00640118820592761</v>
+        <v>1</v>
       </c>
       <c r="AA115" t="n">
-        <v>36524480838.37427</v>
+        <v>108000731136</v>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
@@ -22626,93 +22630,93 @@
         </is>
       </c>
       <c r="AC115" s="2" t="n">
-        <v>36529</v>
+        <v>43314</v>
       </c>
       <c r="AD115" t="n">
-        <v>26.7</v>
+        <v>8.1</v>
       </c>
       <c r="AE115" t="n">
-        <v>20500</v>
+        <v>280.5299987792969</v>
       </c>
       <c r="AF115" t="n">
-        <v>23073.1</v>
+        <v>282.6975997924804</v>
       </c>
       <c r="AG115" t="n">
-        <v>21271.56317382813</v>
+        <v>257.3463871765136</v>
       </c>
       <c r="AH115" t="n">
-        <v>-0.1115194750597015</v>
+        <v>-0.007667560724869071</v>
       </c>
       <c r="AI115" t="n">
-        <v>-0.03627204862769251</v>
+        <v>0.09008718504713897</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0.08469226316138467</v>
+        <v>0.09851007777536203</v>
       </c>
       <c r="AK115" t="n">
-        <v>26150</v>
+        <v>376.1517333984375</v>
       </c>
       <c r="AL115" t="n">
-        <v>16864.458984375</v>
+        <v>121.6859512329102</v>
       </c>
       <c r="AM115" t="n">
-        <v>-0.2160611854684512</v>
+        <v>-0.2542105382719415</v>
       </c>
       <c r="AN115" t="n">
-        <v>0.2155741265695712</v>
+        <v>1.305360610136128</v>
       </c>
       <c r="AO115" t="n">
-        <v>31.80076628352491</v>
+        <v>44.06069517796179</v>
       </c>
       <c r="AP115" t="n">
-        <v>1808300</v>
+        <v>3318600</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1351874</v>
+        <v>5624534</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.337624660286388</v>
+        <v>0.590022213395812</v>
       </c>
       <c r="AS115" t="n">
-        <v>-0.07239819004524883</v>
+        <v>0.02984583357186854</v>
       </c>
       <c r="AT115" t="n">
-        <v>-0.1254266211604096</v>
+        <v>-0.06647913802224004</v>
       </c>
       <c r="AU115" t="n">
-        <v>0.09248836186595266</v>
+        <v>0.06168004814769179</v>
       </c>
       <c r="AV115" t="n">
-        <v>0.05445915869509865</v>
+        <v>1.26483067955771</v>
       </c>
       <c r="AW115" t="n">
-        <v>-0.004904372789216294</v>
+        <v>8.872898371418461</v>
       </c>
       <c r="AX115" t="n">
-        <v>0.02154400887699937</v>
+        <v>0.5981727880012997</v>
       </c>
       <c r="AY115" t="n">
-        <v>18.11730019133693</v>
+        <v>27.23042540502951</v>
       </c>
       <c r="AZ115" t="inlineStr"/>
       <c r="BA115" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive momentum</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>6367.T</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Daikin Industries</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -22722,16 +22726,16 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Power distribution / UPS / electrical</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Electrical/data center infrastructure</t>
+          <t>HVAC/cooling</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -22780,7 +22784,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>Legrand SA</t>
+          <t>Daikin Industries,Ltd.</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -22790,27 +22794,27 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Building Products &amp; Equipment</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="X116" t="n">
-        <v>36933472256</v>
+        <v>5705890791424</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>1.162115097045898</v>
+        <v>0.00640118820592761</v>
       </c>
       <c r="AA116" t="n">
-        <v>42920945695.02344</v>
+        <v>36524480838.37427</v>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
@@ -22818,73 +22822,73 @@
         </is>
       </c>
       <c r="AC116" s="2" t="n">
-        <v>38814</v>
+        <v>36529</v>
       </c>
       <c r="AD116" t="n">
-        <v>20.4</v>
+        <v>26.7</v>
       </c>
       <c r="AE116" t="n">
-        <v>136.4499969482422</v>
+        <v>20500</v>
       </c>
       <c r="AF116" t="n">
-        <v>137.9969989013672</v>
+        <v>23073.1</v>
       </c>
       <c r="AG116" t="n">
-        <v>137.7956073760986</v>
+        <v>21271.56317382813</v>
       </c>
       <c r="AH116" t="n">
-        <v>-0.01121040287427355</v>
+        <v>-0.1115194750597015</v>
       </c>
       <c r="AI116" t="n">
-        <v>-0.009765263592066087</v>
+        <v>-0.03627204862769251</v>
       </c>
       <c r="AJ116" t="n">
-        <v>0.001461523550013277</v>
+        <v>0.08469226316138467</v>
       </c>
       <c r="AK116" t="n">
-        <v>157.5401306152344</v>
+        <v>26150</v>
       </c>
       <c r="AL116" t="n">
-        <v>121.6237258911133</v>
+        <v>16864.458984375</v>
       </c>
       <c r="AM116" t="n">
-        <v>-0.1338715004528043</v>
+        <v>-0.2160611854684512</v>
       </c>
       <c r="AN116" t="n">
-        <v>0.1219027862244781</v>
+        <v>0.2155741265695712</v>
       </c>
       <c r="AO116" t="n">
-        <v>40.89937187473043</v>
+        <v>31.80076628352491</v>
       </c>
       <c r="AP116" t="n">
-        <v>615406</v>
+        <v>1808300</v>
       </c>
       <c r="AQ116" t="n">
-        <v>547028.72</v>
+        <v>1351874</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.124997605244566</v>
+        <v>1.337624660286388</v>
       </c>
       <c r="AS116" t="n">
-        <v>-0.01869835344446447</v>
+        <v>-0.07239819004524883</v>
       </c>
       <c r="AT116" t="n">
-        <v>-0.01266280780494811</v>
+        <v>-0.1254266211604096</v>
       </c>
       <c r="AU116" t="n">
-        <v>0.02375179981675846</v>
+        <v>0.09248836186595266</v>
       </c>
       <c r="AV116" t="n">
-        <v>0.03560259688522005</v>
+        <v>0.05445915869509865</v>
       </c>
       <c r="AW116" t="n">
-        <v>0.6743696131731347</v>
+        <v>-0.004904278447047661</v>
       </c>
       <c r="AX116" t="n">
-        <v>0.08503269335514796</v>
+        <v>0.02154400887699937</v>
       </c>
       <c r="AY116" t="n">
-        <v>9.0771482070859</v>
+        <v>18.11730236758983</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -22995,7 +22999,7 @@
         </is>
       </c>
       <c r="X117" t="n">
-        <v>49220448256</v>
+        <v>49593954304</v>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
@@ -23006,7 +23010,7 @@
         <v>1</v>
       </c>
       <c r="AA117" t="n">
-        <v>49220448256</v>
+        <v>49593954304</v>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
@@ -23026,28 +23030,28 @@
         <v>64.65293197631836</v>
       </c>
       <c r="AG117" t="n">
-        <v>61.04154848098755</v>
+        <v>61.04154865264893</v>
       </c>
       <c r="AH117" t="n">
         <v>-0.07645334466279485</v>
       </c>
       <c r="AI117" t="n">
-        <v>-0.02181382074423666</v>
+        <v>-0.0218138234950972</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0.05916271105828241</v>
+        <v>0.05916270807969926</v>
       </c>
       <c r="AK117" t="n">
         <v>75.72768402099609</v>
       </c>
       <c r="AL117" t="n">
-        <v>49.78789138793945</v>
+        <v>49.78788757324219</v>
       </c>
       <c r="AM117" t="n">
         <v>-0.2115168995803755</v>
       </c>
       <c r="AN117" t="n">
-        <v>0.1992875661116413</v>
+        <v>0.1992876579998339</v>
       </c>
       <c r="AO117" t="n">
         <v>33.89828243690768</v>
@@ -23068,19 +23072,19 @@
         <v>-0.1102491476873531</v>
       </c>
       <c r="AU117" t="n">
-        <v>0.02415120407932658</v>
+        <v>0.02415127108957105</v>
       </c>
       <c r="AV117" t="n">
-        <v>-0.0745176619308423</v>
+        <v>-0.07451755249002423</v>
       </c>
       <c r="AW117" t="n">
-        <v>0.1044755814479419</v>
+        <v>0.1044756593816394</v>
       </c>
       <c r="AX117" t="n">
         <v>0.1284776441270112</v>
       </c>
       <c r="AY117" t="n">
-        <v>4.419210745207267</v>
+        <v>4.419211214263748</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -23222,16 +23226,16 @@
         <v>1328.454790039063</v>
       </c>
       <c r="AG118" t="n">
-        <v>1247.971916809082</v>
+        <v>1247.971918029785</v>
       </c>
       <c r="AH118" t="n">
         <v>-0.07873418461190129</v>
       </c>
       <c r="AI118" t="n">
-        <v>-0.01932089266813874</v>
+        <v>-0.01932089362738953</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0.06449093296567576</v>
+        <v>0.06449093192444444</v>
       </c>
       <c r="AK118" t="n">
         <v>1687.3154296875</v>
@@ -23267,16 +23271,16 @@
         <v>0.1564764559884013</v>
       </c>
       <c r="AV118" t="n">
-        <v>0.4233522155609222</v>
+        <v>0.4233521145256403</v>
       </c>
       <c r="AW118" t="n">
-        <v>1.523578106309782</v>
+        <v>1.523578265110279</v>
       </c>
       <c r="AX118" t="n">
         <v>0.3117215511211182</v>
       </c>
       <c r="AY118" t="n">
-        <v>144.7904805355977</v>
+        <v>144.7904474105446</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23806,16 +23810,16 @@
         <v>63.40241592407227</v>
       </c>
       <c r="AG121" t="n">
-        <v>55.99178832054138</v>
+        <v>55.99178859710693</v>
       </c>
       <c r="AH121" t="n">
         <v>-0.2042889844551667</v>
       </c>
       <c r="AI121" t="n">
-        <v>-0.09897500551110006</v>
+        <v>-0.09897500996161823</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0.1323520435015682</v>
+        <v>0.1323520379084342</v>
       </c>
       <c r="AK121" t="n">
         <v>86.98540496826172</v>
@@ -23848,10 +23852,10 @@
         <v>-0.3393132440439021</v>
       </c>
       <c r="AU121" t="n">
-        <v>0.07713396512458837</v>
+        <v>0.07713387739657263</v>
       </c>
       <c r="AV121" t="n">
-        <v>0.1430147244387932</v>
+        <v>0.1430146256511753</v>
       </c>
       <c r="AW121" t="n">
         <v>-0.5114095980493572</v>
@@ -23860,7 +23864,7 @@
         <v>0.3676460855303298</v>
       </c>
       <c r="AY121" t="n">
-        <v>28.03783324477545</v>
+        <v>28.0378312523719</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -24436,7 +24440,7 @@
         <v>0.3824302751025019</v>
       </c>
       <c r="AY124" t="n">
-        <v>219.5286827821466</v>
+        <v>219.5287274561514</v>
       </c>
       <c r="AZ124" t="inlineStr"/>
       <c r="BA124" t="n">
@@ -24551,10 +24555,10 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>0.1045423597097397</v>
+        <v>0.1045554876327515</v>
       </c>
       <c r="AA125" t="n">
-        <v>3034246654.63385</v>
+        <v>3034627680.627441</v>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
@@ -24568,22 +24572,22 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AE125" t="n">
-        <v>159.75</v>
+        <v>159</v>
       </c>
       <c r="AF125" t="n">
-        <v>172.9619995117187</v>
+        <v>172.848999633789</v>
       </c>
       <c r="AG125" t="n">
-        <v>178.9256217193604</v>
+        <v>178.8914500427246</v>
       </c>
       <c r="AH125" t="n">
-        <v>-0.07638671817518849</v>
+        <v>-0.08012195420934221</v>
       </c>
       <c r="AI125" t="n">
-        <v>-0.1071709100971394</v>
+        <v>-0.111192849283596</v>
       </c>
       <c r="AJ125" t="n">
-        <v>-0.03333017457385379</v>
+        <v>-0.03377718950510178</v>
       </c>
       <c r="AK125" t="n">
         <v>210.6000061035156</v>
@@ -24592,43 +24596,43 @@
         <v>110.4240570068359</v>
       </c>
       <c r="AM125" t="n">
-        <v>-0.2414530134368632</v>
+        <v>-0.245014266894906</v>
       </c>
       <c r="AN125" t="n">
-        <v>0.4466956234918129</v>
+        <v>0.4399036252594568</v>
       </c>
       <c r="AO125" t="n">
-        <v>20.06922242164431</v>
+        <v>20.04609979945602</v>
       </c>
       <c r="AP125" t="n">
-        <v>427899</v>
+        <v>431390</v>
       </c>
       <c r="AQ125" t="n">
-        <v>453195.72</v>
+        <v>453265.54</v>
       </c>
       <c r="AR125" t="n">
-        <v>0.9441814675566663</v>
+        <v>0.9517379150420304</v>
       </c>
       <c r="AS125" t="n">
-        <v>-0.1191067293992051</v>
+        <v>-0.1161756231548866</v>
       </c>
       <c r="AT125" t="n">
-        <v>-0.2410926365795725</v>
+        <v>-0.205</v>
       </c>
       <c r="AU125" t="n">
-        <v>-0.05485422220970382</v>
+        <v>-0.04408244712568554</v>
       </c>
       <c r="AV125" t="n">
-        <v>0.3242555077513409</v>
+        <v>0.3311639999672964</v>
       </c>
       <c r="AW125" t="n">
-        <v>1.102401911432195</v>
+        <v>1.053685172100833</v>
       </c>
       <c r="AX125" t="n">
-        <v>-0.1702470750456787</v>
+        <v>-0.1741426286839619</v>
       </c>
       <c r="AY125" t="n">
-        <v>1.560609221628679</v>
+        <v>1.548587114588752</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24874,22 +24878,22 @@
         <v>29.8</v>
       </c>
       <c r="AE127" t="n">
-        <v>270.6000061035156</v>
+        <v>272.6499938964844</v>
       </c>
       <c r="AF127" t="n">
-        <v>276.8340014648438</v>
+        <v>276.9370013427734</v>
       </c>
       <c r="AG127" t="n">
-        <v>251.5657373046875</v>
+        <v>251.8609435272217</v>
       </c>
       <c r="AH127" t="n">
-        <v>-0.02251889337415736</v>
+        <v>-0.01548008184353422</v>
       </c>
       <c r="AI127" t="n">
-        <v>0.07566320041339525</v>
+        <v>0.08254177911874527</v>
       </c>
       <c r="AJ127" t="n">
-        <v>0.1004439810877433</v>
+        <v>0.09956310599162621</v>
       </c>
       <c r="AK127" t="n">
         <v>289.8500061035156</v>
@@ -24898,43 +24902,43 @@
         <v>203.75</v>
       </c>
       <c r="AM127" t="n">
-        <v>-0.06641366084058364</v>
+        <v>-0.05934107933359334</v>
       </c>
       <c r="AN127" t="n">
-        <v>0.3280981894651074</v>
+        <v>0.338159479246549</v>
       </c>
       <c r="AO127" t="n">
-        <v>35.14413294564962</v>
+        <v>39.38394083146166</v>
       </c>
       <c r="AP127" t="n">
-        <v>805030</v>
+        <v>805152</v>
       </c>
       <c r="AQ127" t="n">
-        <v>930642.52</v>
+        <v>930644.96</v>
       </c>
       <c r="AR127" t="n">
-        <v>0.8650260252454401</v>
+        <v>0.8651548491704076</v>
       </c>
       <c r="AS127" t="n">
-        <v>-0.009154155782231665</v>
+        <v>-0.02555394642037956</v>
       </c>
       <c r="AT127" t="n">
-        <v>0.02383661975603957</v>
+        <v>0.05514706012612591</v>
       </c>
       <c r="AU127" t="n">
-        <v>0.2238805908346508</v>
+        <v>0.1744561751660392</v>
       </c>
       <c r="AV127" t="n">
-        <v>0.222800324709465</v>
+        <v>0.2072250314146635</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.080960849185847</v>
+        <v>1.106406824005582</v>
       </c>
       <c r="AX127" t="n">
-        <v>0.146216747173326</v>
+        <v>0.1549001554763649</v>
       </c>
       <c r="AY127" t="n">
-        <v>27.46550557994578</v>
+        <v>27.68114630588622</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -25066,37 +25070,37 @@
         <v>28.1</v>
       </c>
       <c r="AE128" t="n">
-        <v>191.3999938964844</v>
+        <v>196.6499938964844</v>
       </c>
       <c r="AF128" t="n">
-        <v>227.0400006103516</v>
+        <v>225.3190002441406</v>
       </c>
       <c r="AG128" t="n">
-        <v>206.4884856033325</v>
+        <v>206.8255592727661</v>
       </c>
       <c r="AH128" t="n">
-        <v>-0.1569767733353425</v>
+        <v>-0.1272374114770278</v>
       </c>
       <c r="AI128" t="n">
-        <v>-0.07307183091958636</v>
+        <v>-0.04919878090532304</v>
       </c>
       <c r="AJ128" t="n">
-        <v>0.09952862478975621</v>
+        <v>0.08941564590179585</v>
       </c>
       <c r="AK128" t="n">
         <v>320.2999877929688</v>
       </c>
       <c r="AL128" t="n">
-        <v>110.7517776489258</v>
+        <v>111.1492767333984</v>
       </c>
       <c r="AM128" t="n">
-        <v>-0.4024352132657621</v>
+        <v>-0.3860443290944101</v>
       </c>
       <c r="AN128" t="n">
-        <v>0.7281889100074488</v>
+        <v>0.7692422269932275</v>
       </c>
       <c r="AO128" t="n">
-        <v>20.84487604877739</v>
+        <v>21.87286124057381</v>
       </c>
       <c r="AP128" t="n">
         <v>392446</v>
@@ -25108,25 +25112,25 @@
         <v>0.8613013123648751</v>
       </c>
       <c r="AS128" t="n">
-        <v>-0.1187845461061671</v>
+        <v>-0.1117886209679476</v>
       </c>
       <c r="AT128" t="n">
-        <v>-0.3333333687653286</v>
+        <v>-0.3190789397212291</v>
       </c>
       <c r="AU128" t="n">
-        <v>0.1581878310774369</v>
+        <v>0.1333890896938676</v>
       </c>
       <c r="AV128" t="n">
-        <v>0.7281889100074488</v>
+        <v>0.7613684811950621</v>
       </c>
       <c r="AW128" t="n">
-        <v>2.444083805392196</v>
+        <v>2.454353260659434</v>
       </c>
       <c r="AX128" t="n">
-        <v>0.2917950926041593</v>
+        <v>0.3272283447067676</v>
       </c>
       <c r="AY128" t="n">
-        <v>89.88884948963245</v>
+        <v>92.381892846917</v>
       </c>
       <c r="AZ128" t="inlineStr"/>
       <c r="BA128" t="n">
@@ -25237,7 +25241,7 @@
         </is>
       </c>
       <c r="X129" t="n">
-        <v>80607535104</v>
+        <v>80731348992</v>
       </c>
       <c r="Y129" t="inlineStr">
         <is>
@@ -25248,7 +25252,7 @@
         <v>1</v>
       </c>
       <c r="AA129" t="n">
-        <v>80607535104</v>
+        <v>80731348992</v>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
@@ -25704,13 +25708,13 @@
         <v>2.051615869984702</v>
       </c>
       <c r="AW131" t="n">
-        <v>13.27018421986357</v>
+        <v>13.27018572232209</v>
       </c>
       <c r="AX131" t="n">
         <v>0.5648189138442039</v>
       </c>
       <c r="AY131" t="n">
-        <v>12.95306633800551</v>
+        <v>12.95306059231253</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25852,28 +25856,28 @@
         <v>420.4072003173828</v>
       </c>
       <c r="AG132" t="n">
-        <v>371.8296618652344</v>
+        <v>371.8296598815918</v>
       </c>
       <c r="AH132" t="n">
         <v>0.02022516107789651</v>
       </c>
       <c r="AI132" t="n">
-        <v>0.1535120719270728</v>
+        <v>0.1535120780808468</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.1306446027153016</v>
+        <v>0.1306446087470818</v>
       </c>
       <c r="AK132" t="n">
         <v>477.5700073242188</v>
       </c>
       <c r="AL132" t="n">
-        <v>240.7474517822266</v>
+        <v>240.7474822998047</v>
       </c>
       <c r="AM132" t="n">
         <v>-0.1018908283934055</v>
       </c>
       <c r="AN132" t="n">
-        <v>0.7815765047020702</v>
+        <v>0.7815762788662706</v>
       </c>
       <c r="AO132" t="n">
         <v>48.71185780858202</v>
@@ -25897,16 +25901,16 @@
         <v>0.2363803747094231</v>
       </c>
       <c r="AV132" t="n">
-        <v>0.7815765047020702</v>
+        <v>0.7815762788662706</v>
       </c>
       <c r="AW132" t="n">
-        <v>2.910382836133748</v>
+        <v>2.910383924117892</v>
       </c>
       <c r="AX132" t="n">
         <v>0.3489123683002224</v>
       </c>
       <c r="AY132" t="n">
-        <v>136.3433697723784</v>
+        <v>136.3433278303745</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26092,13 +26096,13 @@
         <v>2.108148947344385</v>
       </c>
       <c r="AW133" t="n">
-        <v>1.401418605033238</v>
+        <v>1.401418869821891</v>
       </c>
       <c r="AX133" t="n">
         <v>1.695843621956961</v>
       </c>
       <c r="AY133" t="n">
-        <v>2.435587711314661</v>
+        <v>2.435587440335663</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26240,28 +26244,28 @@
         <v>205.5908340454102</v>
       </c>
       <c r="AG134" t="n">
-        <v>171.1707736968994</v>
+        <v>171.170774269104</v>
       </c>
       <c r="AH134" t="n">
         <v>-0.09723598833924196</v>
       </c>
       <c r="AI134" t="n">
-        <v>0.08429729033162392</v>
+        <v>0.08429728670694026</v>
       </c>
       <c r="AJ134" t="n">
-        <v>0.201086082659532</v>
+        <v>0.2010860786444366</v>
       </c>
       <c r="AK134" t="n">
         <v>301.3693542480469</v>
       </c>
       <c r="AL134" t="n">
-        <v>90.02336120605469</v>
+        <v>90.02336883544922</v>
       </c>
       <c r="AM134" t="n">
         <v>-0.3841443946196514</v>
       </c>
       <c r="AN134" t="n">
-        <v>1.061687140060182</v>
+        <v>1.061686965334166</v>
       </c>
       <c r="AO134" t="n">
         <v>31.3678449029854</v>
@@ -26285,16 +26289,16 @@
         <v>0.3018468625107043</v>
       </c>
       <c r="AV134" t="n">
-        <v>1.061687140060182</v>
+        <v>1.061686965334166</v>
       </c>
       <c r="AW134" t="n">
-        <v>4.695458621824335</v>
+        <v>4.695459955252399</v>
       </c>
       <c r="AX134" t="n">
-        <v>0.4616952890465102</v>
+        <v>0.4616953768730572</v>
       </c>
       <c r="AY134" t="n">
-        <v>3061.46871764251</v>
+        <v>3061.47097659462</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26490,7 +26494,7 @@
         <v>0.4573138526874467</v>
       </c>
       <c r="AY135" t="n">
-        <v>18.67756002591975</v>
+        <v>18.67756534472116</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26632,16 +26636,16 @@
         <v>533.2680578613281</v>
       </c>
       <c r="AG136" t="n">
-        <v>406.2809387207031</v>
+        <v>406.2809381866455</v>
       </c>
       <c r="AH136" t="n">
         <v>-0.147314404544137</v>
       </c>
       <c r="AI136" t="n">
-        <v>0.1192008979965151</v>
+        <v>0.1192008994677085</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.3125598743088509</v>
+        <v>0.3125598760342152</v>
       </c>
       <c r="AK136" t="n">
         <v>722.2277221679688</v>
@@ -26677,16 +26681,16 @@
         <v>0.3446690011061528</v>
       </c>
       <c r="AV136" t="n">
-        <v>1.809370402346909</v>
+        <v>1.809370137494738</v>
       </c>
       <c r="AW136" t="n">
-        <v>2.483377614107692</v>
+        <v>2.483376799747419</v>
       </c>
       <c r="AX136" t="n">
-        <v>0.6972163483859974</v>
+        <v>0.6972161550601461</v>
       </c>
       <c r="AY136" t="n">
-        <v>6596.354637957629</v>
+        <v>6596.359630176856</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26793,7 +26797,7 @@
         </is>
       </c>
       <c r="X137" t="n">
-        <v>40379961344</v>
+        <v>40394854400</v>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
@@ -26804,7 +26808,7 @@
         <v>1.162115097045898</v>
       </c>
       <c r="AA137" t="n">
-        <v>46926162695.99219</v>
+        <v>46943470141.21094</v>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
@@ -26818,37 +26822,37 @@
         <v>27.7</v>
       </c>
       <c r="AE137" t="n">
-        <v>777</v>
+        <v>825.2000122070312</v>
       </c>
       <c r="AF137" t="n">
-        <v>865.0379992675781</v>
+        <v>862.5819995117188</v>
       </c>
       <c r="AG137" t="n">
-        <v>756.3100914001465</v>
+        <v>757.9552503967285</v>
       </c>
       <c r="AH137" t="n">
-        <v>-0.1017735629441936</v>
+        <v>-0.04333731439544108</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.0273563830961856</v>
+        <v>0.08871864371294413</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.1437610169476189</v>
+        <v>0.1380381613033574</v>
       </c>
       <c r="AK137" t="n">
         <v>1079</v>
       </c>
       <c r="AL137" t="n">
-        <v>420.5625915527344</v>
+        <v>422.4552307128906</v>
       </c>
       <c r="AM137" t="n">
-        <v>-0.2798887859128822</v>
+        <v>-0.2352177829406569</v>
       </c>
       <c r="AN137" t="n">
-        <v>0.8475252331199599</v>
+        <v>0.953343105290734</v>
       </c>
       <c r="AO137" t="n">
-        <v>20.20409402525173</v>
+        <v>33.44681540713944</v>
       </c>
       <c r="AP137" t="n">
         <v>150880</v>
@@ -26860,25 +26864,25 @@
         <v>0.8834181913651961</v>
       </c>
       <c r="AS137" t="n">
-        <v>-0.0672268907563025</v>
+        <v>-0.03372363910183696</v>
       </c>
       <c r="AT137" t="n">
-        <v>-0.1320375453476819</v>
+        <v>-0.08978597570146329</v>
       </c>
       <c r="AU137" t="n">
-        <v>0.1538833442252663</v>
+        <v>0.1690839414783432</v>
       </c>
       <c r="AV137" t="n">
-        <v>0.8475252331199599</v>
+        <v>0.953343105290734</v>
       </c>
       <c r="AW137" t="n">
-        <v>1.536584238364279</v>
+        <v>1.60882234242933</v>
       </c>
       <c r="AX137" t="n">
-        <v>0.4084962507754526</v>
+        <v>0.4958701716003362</v>
       </c>
       <c r="AY137" t="n">
-        <v>263.3537738523577</v>
+        <v>279.7525805725759</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27020,16 +27024,16 @@
         <v>1750.502734375</v>
       </c>
       <c r="AG138" t="n">
-        <v>1476.982750549317</v>
+        <v>1476.982753295898</v>
       </c>
       <c r="AH138" t="n">
         <v>-0.020349999341707</v>
       </c>
       <c r="AI138" t="n">
-        <v>0.1610697580896037</v>
+        <v>0.1610697559304903</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0.1851883400289926</v>
+        <v>0.1851883378250285</v>
       </c>
       <c r="AK138" t="n">
         <v>1986.870361328125</v>
@@ -27068,13 +27072,13 @@
         <v>1.208232313451699</v>
       </c>
       <c r="AW138" t="n">
-        <v>1.140824995675924</v>
+        <v>1.140825158796479</v>
       </c>
       <c r="AX138" t="n">
         <v>0.4806218438116101</v>
       </c>
       <c r="AY138" t="n">
-        <v>973.4977670245831</v>
+        <v>973.4978990532123</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27412,16 +27416,16 @@
         <v>371.7913269042969</v>
       </c>
       <c r="AG140" t="n">
-        <v>316.0734416198731</v>
+        <v>316.0734413909912</v>
       </c>
       <c r="AH140" t="n">
         <v>-0.0397032610951672</v>
       </c>
       <c r="AI140" t="n">
-        <v>0.1295792425631268</v>
+        <v>0.1295792433811018</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0.1762814521804497</v>
+        <v>0.1762814530322436</v>
       </c>
       <c r="AK140" t="n">
         <v>483.6542053222656</v>
@@ -27457,16 +27461,16 @@
         <v>0.2053098229509547</v>
       </c>
       <c r="AV140" t="n">
-        <v>1.976052817796447</v>
+        <v>1.976053007059858</v>
       </c>
       <c r="AW140" t="n">
         <v>1.955925249635726</v>
       </c>
       <c r="AX140" t="n">
-        <v>0.7221596197551501</v>
+        <v>0.722159493001016</v>
       </c>
       <c r="AY140" t="n">
-        <v>319.6856244412734</v>
+        <v>319.6854870926912</v>
       </c>
       <c r="AZ140" t="inlineStr"/>
       <c r="BA140" t="n">
@@ -27765,7 +27769,7 @@
         </is>
       </c>
       <c r="X142" t="n">
-        <v>575309414400</v>
+        <v>575286149120</v>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
@@ -27776,7 +27780,7 @@
         <v>0.1275396347045898</v>
       </c>
       <c r="AA142" t="n">
-        <v>73374752554.6875</v>
+        <v>73371785309.375</v>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
@@ -28036,13 +28040,13 @@
         <v>0.3672204289117476</v>
       </c>
       <c r="AW143" t="n">
-        <v>4.29058192280027</v>
+        <v>4.290582424714299</v>
       </c>
       <c r="AX143" t="n">
         <v>0.07181087340175041</v>
       </c>
       <c r="AY143" t="n">
-        <v>36.2652055095224</v>
+        <v>36.26521484767193</v>
       </c>
       <c r="AZ143" t="inlineStr"/>
       <c r="BA143" t="n">
@@ -28153,7 +28157,7 @@
         </is>
       </c>
       <c r="X144" t="n">
-        <v>24806764544</v>
+        <v>24809037824</v>
       </c>
       <c r="Y144" t="inlineStr">
         <is>
@@ -28164,7 +28168,7 @@
         <v>1</v>
       </c>
       <c r="AA144" t="n">
-        <v>24806764544</v>
+        <v>24809037824</v>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
@@ -28614,13 +28618,13 @@
         <v>0.8084657689976751</v>
       </c>
       <c r="AW146" t="n">
-        <v>7.092142627907686</v>
+        <v>7.092141997107349</v>
       </c>
       <c r="AX146" t="n">
         <v>0.3242636050516647</v>
       </c>
       <c r="AY146" t="n">
-        <v>40.2552811260282</v>
+        <v>40.25528522489727</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28954,16 +28958,16 @@
         <v>439.23205078125</v>
       </c>
       <c r="AG148" t="n">
-        <v>252.8237309646607</v>
+        <v>252.8237310409546</v>
       </c>
       <c r="AH148" t="n">
         <v>0.1933100367246972</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.073144054351848</v>
+        <v>1.073144053726241</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0.7373054701207824</v>
+        <v>0.7373054695965204</v>
       </c>
       <c r="AK148" t="n">
         <v>524.1400146484375</v>
@@ -28999,16 +29003,16 @@
         <v>2.594502499981426</v>
       </c>
       <c r="AV148" t="n">
-        <v>3.25233591929113</v>
+        <v>3.252336445705742</v>
       </c>
       <c r="AW148" t="n">
         <v>10.59849142126263</v>
       </c>
       <c r="AX148" t="n">
-        <v>3.138767719794064</v>
+        <v>3.138767470458151</v>
       </c>
       <c r="AY148" t="n">
-        <v>46.81245152753036</v>
+        <v>46.81245984641048</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29115,7 +29119,7 @@
         </is>
       </c>
       <c r="X149" t="n">
-        <v>1430044934144</v>
+        <v>1421843496960</v>
       </c>
       <c r="Y149" t="inlineStr">
         <is>
@@ -29126,7 +29130,7 @@
         <v>0.03162555396556854</v>
       </c>
       <c r="AA149" t="n">
-        <v>45225963237.95898</v>
+        <v>44966588243.70117</v>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
@@ -29194,13 +29198,13 @@
         <v>1.581131282818862</v>
       </c>
       <c r="AW149" t="n">
-        <v>8.138070892145111</v>
+        <v>8.138071885654073</v>
       </c>
       <c r="AX149" t="n">
         <v>0.7572433619415473</v>
       </c>
       <c r="AY149" t="n">
-        <v>90.22306931053731</v>
+        <v>90.22306312251253</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29390,13 +29394,13 @@
         <v>0.3723908784754635</v>
       </c>
       <c r="AW150" t="n">
-        <v>1.121713437431175</v>
+        <v>1.121713911351523</v>
       </c>
       <c r="AX150" t="n">
         <v>0.1919637837707604</v>
       </c>
       <c r="AY150" t="n">
-        <v>45.9346404239727</v>
+        <v>45.93464404756105</v>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="n">
@@ -29528,22 +29532,22 @@
         <v>38.2</v>
       </c>
       <c r="AE151" t="n">
-        <v>1480.199951171875</v>
+        <v>1489.400024414062</v>
       </c>
       <c r="AF151" t="n">
-        <v>1467.519169921875</v>
+        <v>1468.668264160156</v>
       </c>
       <c r="AG151" t="n">
-        <v>1282.909905395508</v>
+        <v>1284.989844970703</v>
       </c>
       <c r="AH151" t="n">
-        <v>0.008640964636036141</v>
+        <v>0.01411602657987676</v>
       </c>
       <c r="AI151" t="n">
-        <v>0.1537832430372768</v>
+        <v>0.1590753267377143</v>
       </c>
       <c r="AJ151" t="n">
-        <v>0.1438988534970067</v>
+        <v>0.1429415336691946</v>
       </c>
       <c r="AK151" t="n">
         <v>1570.339965820312</v>
@@ -29552,43 +29556,43 @@
         <v>1028.91552734375</v>
       </c>
       <c r="AM151" t="n">
-        <v>-0.05740159240063047</v>
+        <v>-0.0515429417629123</v>
       </c>
       <c r="AN151" t="n">
-        <v>0.4386020152627705</v>
+        <v>0.4475435396131109</v>
       </c>
       <c r="AO151" t="n">
-        <v>41.26363769669801</v>
+        <v>39.66346541805418</v>
       </c>
       <c r="AP151" t="n">
-        <v>9206798</v>
+        <v>9211779</v>
       </c>
       <c r="AQ151" t="n">
-        <v>19562724.5</v>
+        <v>19562824.12</v>
       </c>
       <c r="AR151" t="n">
-        <v>0.4706296405697478</v>
+        <v>0.4708818595666033</v>
       </c>
       <c r="AS151" t="n">
-        <v>-0.05740159240063047</v>
+        <v>-0.02869440413424618</v>
       </c>
       <c r="AT151" t="n">
-        <v>0.1736890272379568</v>
+        <v>0.2156847213483246</v>
       </c>
       <c r="AU151" t="n">
-        <v>0.1475360780526804</v>
+        <v>0.1774880189970516</v>
       </c>
       <c r="AV151" t="n">
-        <v>0.3841249207818986</v>
+        <v>0.3849580897212777</v>
       </c>
       <c r="AW151" t="n">
-        <v>12.21407898788451</v>
+        <v>12.43531174414231</v>
       </c>
       <c r="AX151" t="n">
-        <v>0.2366930891916772</v>
+        <v>0.2443796635559465</v>
       </c>
       <c r="AY151" t="n">
-        <v>10.88812102536262</v>
+        <v>10.96201149468954</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29730,16 +29734,16 @@
         <v>50.0068002319336</v>
       </c>
       <c r="AG152" t="n">
-        <v>33.12728670120239</v>
+        <v>33.12728672981262</v>
       </c>
       <c r="AH152" t="n">
         <v>0.03985857441031748</v>
       </c>
       <c r="AI152" t="n">
-        <v>0.5697029602521779</v>
+        <v>0.569702958896511</v>
       </c>
       <c r="AJ152" t="n">
-        <v>0.5095350453231819</v>
+        <v>0.5095350440194788</v>
       </c>
       <c r="AK152" t="n">
         <v>59.81999969482422</v>
@@ -29775,16 +29779,16 @@
         <v>1.40662170677059</v>
       </c>
       <c r="AV152" t="n">
-        <v>1.256936133858294</v>
+        <v>1.256936320696339</v>
       </c>
       <c r="AW152" t="n">
-        <v>2.912015097065427</v>
+        <v>2.912015658407824</v>
       </c>
       <c r="AX152" t="n">
         <v>1.171635073860988</v>
       </c>
       <c r="AY152" t="n">
-        <v>6.217175956773676</v>
+        <v>6.217174523851832</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -30479,7 +30483,7 @@
         </is>
       </c>
       <c r="X156" t="n">
-        <v>26009260032</v>
+        <v>25609703424</v>
       </c>
       <c r="Y156" t="inlineStr">
         <is>
@@ -30490,7 +30494,7 @@
         <v>1</v>
       </c>
       <c r="AA156" t="n">
-        <v>26009260032</v>
+        <v>25609703424</v>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
@@ -30750,13 +30754,13 @@
         <v>0.6997075054392461</v>
       </c>
       <c r="AW157" t="n">
-        <v>2.275602888462892</v>
+        <v>2.275603191648681</v>
       </c>
       <c r="AX157" t="n">
         <v>0.5642649920088176</v>
       </c>
       <c r="AY157" t="n">
-        <v>7.881863820476596</v>
+        <v>7.881862705913962</v>
       </c>
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="n">
@@ -30898,16 +30902,16 @@
         <v>114.2400685119629</v>
       </c>
       <c r="AG158" t="n">
-        <v>94.24309032440186</v>
+        <v>94.243090133667</v>
       </c>
       <c r="AH158" t="n">
         <v>-0.04411824703337708</v>
       </c>
       <c r="AI158" t="n">
-        <v>0.1587056045419981</v>
+        <v>0.1587056068870565</v>
       </c>
       <c r="AJ158" t="n">
-        <v>0.2121850855986129</v>
+        <v>0.2121850880519065</v>
       </c>
       <c r="AK158" t="n">
         <v>129.5154876708984</v>
@@ -31094,16 +31098,16 @@
         <v>327.0688989257812</v>
       </c>
       <c r="AG159" t="n">
-        <v>292.7086807250977</v>
+        <v>292.708680267334</v>
       </c>
       <c r="AH159" t="n">
         <v>-0.05044469729696444</v>
       </c>
       <c r="AI159" t="n">
-        <v>0.06102082983967194</v>
+        <v>0.06102083149899018</v>
       </c>
       <c r="AJ159" t="n">
-        <v>0.1173870830054184</v>
+        <v>0.1173870847528871</v>
       </c>
       <c r="AK159" t="n">
         <v>385.5466918945312</v>
@@ -31142,13 +31146,13 @@
         <v>0.4799054827315776</v>
       </c>
       <c r="AW159" t="n">
-        <v>4.028704930065206</v>
+        <v>4.028704619457058</v>
       </c>
       <c r="AX159" t="n">
         <v>0.292919480848151</v>
       </c>
       <c r="AY159" t="n">
-        <v>419.3642744991167</v>
+        <v>419.3644101530286</v>
       </c>
       <c r="AZ159" t="inlineStr"/>
       <c r="BA159" t="n">
@@ -32161,7 +32165,7 @@
         <v>41796</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="AE3" t="n">
         <v>193.7799987792969</v>
@@ -32572,16 +32576,16 @@
         <v>383.6615997314453</v>
       </c>
       <c r="AG5" t="n">
-        <v>369.0301217651367</v>
+        <v>369.0301223754883</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.06714668826120085</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.03016048612892341</v>
+        <v>-0.03016048773297431</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.03964846526978261</v>
+        <v>0.03964846355027207</v>
       </c>
       <c r="AK5" t="n">
         <v>480.8090515136719</v>
@@ -32617,16 +32621,16 @@
         <v>0.03895418071335155</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.07653956505391668</v>
+        <v>0.07653966387472577</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.88012106085648</v>
+        <v>6.880120398999536</v>
       </c>
       <c r="AX5" t="n">
         <v>0.03336521571714868</v>
       </c>
       <c r="AY5" t="n">
-        <v>314.1662079586145</v>
+        <v>314.1660756197175</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32974,16 +32978,16 @@
         <v>321.8837994384766</v>
       </c>
       <c r="AG7" t="n">
-        <v>260.6797447967529</v>
+        <v>260.6797444152832</v>
       </c>
       <c r="AH7" t="n">
         <v>-0.04422032288304956</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1801837313303851</v>
+        <v>0.180183733057425</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.2347863839188706</v>
+        <v>0.2347863857258141</v>
       </c>
       <c r="AK7" t="n">
         <v>433.3299865722656</v>
@@ -33022,13 +33026,13 @@
         <v>2.00488293570199</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.330469745142942</v>
+        <v>4.330468688190853</v>
       </c>
       <c r="AX7" t="n">
         <v>0.6655979668654046</v>
       </c>
       <c r="AY7" t="n">
-        <v>1630.819128476293</v>
+        <v>1630.819257451809</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33176,16 +33180,16 @@
         <v>220.6539810180664</v>
       </c>
       <c r="AG8" t="n">
-        <v>151.7107284927368</v>
+        <v>151.7107284545899</v>
       </c>
       <c r="AH8" t="n">
         <v>0.01312472143185262</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.4735279783621915</v>
+        <v>0.4735279787327034</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.4544388733103359</v>
+        <v>0.4544388736760478</v>
       </c>
       <c r="AK8" t="n">
         <v>316.3519592285156</v>
@@ -33224,7 +33228,7 @@
         <v>2.537443400101073</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.675597894780153</v>
+        <v>2.67559720316809</v>
       </c>
       <c r="AX8" t="n">
         <v>1.504508879888965</v>
@@ -33343,7 +33347,7 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>61545304064</v>
+        <v>57480011776</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -33354,7 +33358,7 @@
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>61545304064</v>
+        <v>57480011776</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -33507,7 +33511,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.136562295115675</v>
+        <v>1.136562307468276</v>
       </c>
     </row>
   </sheetData>
@@ -33675,40 +33679,40 @@
         <v>0.375</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5920420687554803</v>
+        <v>0.592042052046124</v>
       </c>
       <c r="L2" t="n">
         <v>0.3221039416194904</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3352683581919266</v>
+        <v>0.3352683068894056</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9102229498529</v>
+        <v>0.9102229102313376</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3604684015608168</v>
+        <v>0.3604682955842911</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5884357882157518</v>
+        <v>0.5884356960451438</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.846262014228706</v>
+        <v>3.846261716237504</v>
       </c>
       <c r="R2" t="n">
         <v>1.259925600111665</v>
       </c>
       <c r="S2" t="n">
-        <v>5.105480767757103</v>
+        <v>5.105479871907336</v>
       </c>
       <c r="T2" t="n">
-        <v>1324.461035375645</v>
+        <v>1324.461205985142</v>
       </c>
       <c r="U2" t="n">
-        <v>326.3382890749966</v>
+        <v>326.3383114059382</v>
       </c>
       <c r="V2" t="n">
-        <v>4093.817173159518</v>
+        <v>4093.817650999466</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33726,10 +33730,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>223.399210678793</v>
+        <v>223.371506358793</v>
       </c>
       <c r="D3" t="n">
-        <v>31.91417295411328</v>
+        <v>31.91021519411328</v>
       </c>
       <c r="E3" t="n">
         <v>13.64767843445557</v>
@@ -33741,7 +33745,7 @@
         <v>85</v>
       </c>
       <c r="H3" t="n">
-        <v>77.87241009805403</v>
+        <v>77.8771073371318</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
@@ -33750,40 +33754,40 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="K3" t="n">
-        <v>2.035627641669401</v>
+        <v>2.107927240773831</v>
       </c>
       <c r="L3" t="n">
         <v>1.865634237046958</v>
       </c>
       <c r="M3" t="n">
-        <v>1.896511466725142</v>
+        <v>1.913651272962642</v>
       </c>
       <c r="N3" t="n">
-        <v>3.972719187296422</v>
+        <v>4.055834324759721</v>
       </c>
       <c r="O3" t="n">
         <v>4.701147787526577</v>
       </c>
       <c r="P3" t="n">
-        <v>3.770333750933438</v>
+        <v>3.790133563750996</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.187785526671776</v>
+        <v>4.246508707768606</v>
       </c>
       <c r="R3" t="n">
-        <v>4.208318938274296</v>
+        <v>4.208319283114757</v>
       </c>
       <c r="S3" t="n">
-        <v>4.884357666330646</v>
+        <v>4.898602315733307</v>
       </c>
       <c r="T3" t="n">
-        <v>34.29139369706078</v>
+        <v>34.49805473853071</v>
       </c>
       <c r="U3" t="n">
-        <v>28.58318224083462</v>
+        <v>28.58318745849732</v>
       </c>
       <c r="V3" t="n">
-        <v>48.80603582453966</v>
+        <v>48.86009119597215</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33801,10 +33805,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>1484.06682785009</v>
+        <v>1483.407896247832</v>
       </c>
       <c r="D4" t="n">
-        <v>92.75417674063064</v>
+        <v>92.71299351548953</v>
       </c>
       <c r="E4" t="n">
         <v>42.59120622446582</v>
@@ -33816,7 +33820,7 @@
         <v>65</v>
       </c>
       <c r="H4" t="n">
-        <v>77.56767147640011</v>
+        <v>77.56800852872141</v>
       </c>
       <c r="I4" t="n">
         <v>7</v>
@@ -33825,40 +33829,40 @@
         <v>0.4375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5556273670059386</v>
+        <v>0.556107762320211</v>
       </c>
       <c r="L4" t="n">
         <v>0.3114622517227964</v>
       </c>
       <c r="M4" t="n">
-        <v>1.021453101697254</v>
+        <v>1.022559488973951</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7415748454419371</v>
+        <v>0.7416269630789394</v>
       </c>
       <c r="O4" t="n">
         <v>0.4480023286854959</v>
       </c>
       <c r="P4" t="n">
-        <v>1.199939108112964</v>
+        <v>1.200294494364172</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.77695849714937</v>
+        <v>6.790785631324797</v>
       </c>
       <c r="R4" t="n">
-        <v>4.216765210617172</v>
+        <v>4.216765055313099</v>
       </c>
       <c r="S4" t="n">
-        <v>6.276130190984438</v>
+        <v>6.299518690188031</v>
       </c>
       <c r="T4" t="n">
-        <v>236.1691421713352</v>
+        <v>236.1737692606519</v>
       </c>
       <c r="U4" t="n">
-        <v>42.22467294568736</v>
+        <v>42.22467499512189</v>
       </c>
       <c r="V4" t="n">
-        <v>724.6956140436411</v>
+        <v>724.9981193685427</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33876,10 +33880,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>4127.661860880648</v>
+        <v>4127.678474360554</v>
       </c>
       <c r="D5" t="n">
-        <v>275.1774573920432</v>
+        <v>275.1785649573704</v>
       </c>
       <c r="E5" t="n">
         <v>55.818338304</v>
@@ -33891,7 +33895,7 @@
         <v>60</v>
       </c>
       <c r="H5" t="n">
-        <v>73.80291708452189</v>
+        <v>73.80285112318768</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -33900,40 +33904,40 @@
         <v>0.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4639725567342155</v>
+        <v>0.4697974693056451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4573138526874467</v>
+        <v>0.4616953768730572</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4300048404154178</v>
+        <v>0.4309987007766786</v>
       </c>
       <c r="N5" t="n">
-        <v>1.198046391676924</v>
+        <v>1.205100884744937</v>
       </c>
       <c r="O5" t="n">
         <v>1.091154032760818</v>
       </c>
       <c r="P5" t="n">
-        <v>1.058656936056966</v>
+        <v>1.059859585372926</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.172117975440862</v>
+        <v>3.177278128540773</v>
       </c>
       <c r="R5" t="n">
-        <v>2.517655721301416</v>
+        <v>2.51765531412128</v>
       </c>
       <c r="S5" t="n">
-        <v>3.017975062133066</v>
+        <v>3.018796629217304</v>
       </c>
       <c r="T5" t="n">
-        <v>780.6152541333507</v>
+        <v>781.7089887513425</v>
       </c>
       <c r="U5" t="n">
-        <v>36.2652055095224</v>
+        <v>36.26521484767193</v>
       </c>
       <c r="V5" t="n">
-        <v>995.5007427404512</v>
+        <v>995.6849059561719</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33951,13 +33955,13 @@
         <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>4565.844720764463</v>
+        <v>4566.118885500463</v>
       </c>
       <c r="D6" t="n">
-        <v>380.4870600637052</v>
+        <v>380.5099071250385</v>
       </c>
       <c r="E6" t="n">
-        <v>191.6290776640435</v>
+        <v>191.7800316480435</v>
       </c>
       <c r="F6" t="n">
         <v>66.66666666666667</v>
@@ -33966,7 +33970,7 @@
         <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>68.5464539463795</v>
+        <v>68.54630534263376</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
@@ -33975,40 +33979,40 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="K6" t="n">
-        <v>1.737065038556014</v>
+        <v>1.737065021659513</v>
       </c>
       <c r="L6" t="n">
         <v>1.421026667367343</v>
       </c>
       <c r="M6" t="n">
-        <v>1.777789399750811</v>
+        <v>1.777813144726125</v>
       </c>
       <c r="N6" t="n">
-        <v>7.466224169611077</v>
+        <v>7.466224135271477</v>
       </c>
       <c r="O6" t="n">
-        <v>4.838661043965619</v>
+        <v>4.838660837928023</v>
       </c>
       <c r="P6" t="n">
-        <v>6.363508382648143</v>
+        <v>6.36336013448911</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.710660373049905</v>
+        <v>6.710660376604894</v>
       </c>
       <c r="R6" t="n">
-        <v>5.255230101671208</v>
+        <v>5.255230480823259</v>
       </c>
       <c r="S6" t="n">
-        <v>8.62126462971197</v>
+        <v>8.62143240441584</v>
       </c>
       <c r="T6" t="n">
-        <v>297.567772457978</v>
+        <v>297.5677870703902</v>
       </c>
       <c r="U6" t="n">
         <v>53.08844953062705</v>
       </c>
       <c r="V6" t="n">
-        <v>378.6877440840155</v>
+        <v>378.6755590732969</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34026,10 +34030,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>13653.85316289731</v>
+        <v>13649.78787060931</v>
       </c>
       <c r="D7" t="n">
-        <v>1137.821096908109</v>
+        <v>1137.482322550776</v>
       </c>
       <c r="E7" t="n">
         <v>369.4166016</v>
@@ -34041,7 +34045,7 @@
         <v>42.5</v>
       </c>
       <c r="H7" t="n">
-        <v>67.97425190305977</v>
+        <v>67.96918115448169</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -34056,34 +34060,34 @@
         <v>0.06966964182151569</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05708997165574407</v>
+        <v>0.05665521605033589</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4495382625113518</v>
+        <v>0.4495382741698297</v>
       </c>
       <c r="O7" t="n">
         <v>0.0104156946851679</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1379948892917234</v>
+        <v>0.1373039802949974</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6843166321794307</v>
+        <v>0.6843167846044751</v>
       </c>
       <c r="R7" t="n">
         <v>0.5727770698567408</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8285840537236938</v>
+        <v>0.8285842481451368</v>
       </c>
       <c r="T7" t="n">
-        <v>1255.555493414559</v>
+        <v>1255.555579335152</v>
       </c>
       <c r="U7" t="n">
-        <v>12.79715848060875</v>
+        <v>12.79715929971285</v>
       </c>
       <c r="V7" t="n">
-        <v>3011.841044185163</v>
+        <v>3012.735013679009</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34101,64 +34105,64 @@
         <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1608.985537017608</v>
+        <v>1609.326592096064</v>
       </c>
       <c r="D8" t="n">
-        <v>73.13570622807309</v>
+        <v>73.15120873163929</v>
       </c>
       <c r="E8" t="n">
-        <v>46.07069697551172</v>
+        <v>46.2583234638125</v>
       </c>
       <c r="F8" t="n">
-        <v>50.90909090909091</v>
+        <v>52.95454545454545</v>
       </c>
       <c r="G8" t="n">
-        <v>52.5</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>63.51802314745224</v>
+        <v>64.71231323112367</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3404915854521147</v>
+        <v>0.3436415888742648</v>
       </c>
       <c r="L8" t="n">
         <v>0.3234938915342116</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3874654522803821</v>
+        <v>0.3905408396284579</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6163883349533382</v>
+        <v>0.6163133244008471</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4316258087447705</v>
+        <v>0.4316257582271296</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5790617594528848</v>
+        <v>0.5765150766822168</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.647117250917235</v>
+        <v>2.6465416435579</v>
       </c>
       <c r="R8" t="n">
-        <v>1.372197876923961</v>
+        <v>1.372197525492757</v>
       </c>
       <c r="S8" t="n">
-        <v>2.435783708722165</v>
+        <v>2.434009923749161</v>
       </c>
       <c r="T8" t="n">
-        <v>169.2674018368369</v>
+        <v>169.284651378245</v>
       </c>
       <c r="U8" t="n">
-        <v>27.63412797025721</v>
+        <v>27.6341283287007</v>
       </c>
       <c r="V8" t="n">
-        <v>318.3127790028595</v>
+        <v>318.2306536733915</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34176,13 +34180,13 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>421.3960727262481</v>
+        <v>421.519886614248</v>
       </c>
       <c r="D9" t="n">
-        <v>105.349018181562</v>
+        <v>105.379971653562</v>
       </c>
       <c r="E9" t="n">
-        <v>78.040854528</v>
+        <v>78.102761472</v>
       </c>
       <c r="F9" t="n">
         <v>40</v>
@@ -34191,7 +34195,7 @@
         <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>62.17332338383583</v>
+        <v>62.16093572834471</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -34200,40 +34204,40 @@
         <v>0.25</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0501928403451431</v>
+        <v>0.06122200544655493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04459680458296655</v>
+        <v>0.04893850873448602</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05512212576728226</v>
+        <v>0.06170254020628146</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1108274420804659</v>
+        <v>0.1152285115536688</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02833985647125031</v>
+        <v>0.02055220982384959</v>
       </c>
       <c r="P9" t="n">
-        <v>0.06901750822753842</v>
+        <v>0.06123702806381508</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.122293177117951</v>
+        <v>1.131222034639694</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9334574619261685</v>
+        <v>0.9461804493360363</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9213440595217196</v>
+        <v>0.9366693622451303</v>
       </c>
       <c r="T9" t="n">
-        <v>77.92894731987316</v>
+        <v>78.6061183406794</v>
       </c>
       <c r="U9" t="n">
-        <v>69.45013879801563</v>
+        <v>70.69666047665791</v>
       </c>
       <c r="V9" t="n">
-        <v>56.5535756214238</v>
+        <v>56.81310899214825</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34251,13 +34255,13 @@
         <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>3268.305459763</v>
+        <v>3276.881058490284</v>
       </c>
       <c r="D10" t="n">
-        <v>163.41527298815</v>
+        <v>156.041955166204</v>
       </c>
       <c r="E10" t="n">
-        <v>55.930095616</v>
+        <v>55.70578432</v>
       </c>
       <c r="F10" t="n">
         <v>60</v>
@@ -34266,7 +34270,7 @@
         <v>60</v>
       </c>
       <c r="H10" t="n">
-        <v>56.28367839123557</v>
+        <v>56.29313183774931</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -34275,40 +34279,40 @@
         <v>0.09523809523809523</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5011774485397275</v>
+        <v>0.5015269838599108</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3428229165472994</v>
+        <v>0.3702846190828928</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2976891677051434</v>
+        <v>0.2975753572713347</v>
       </c>
       <c r="N10" t="n">
-        <v>1.129433981517607</v>
+        <v>1.126975379660942</v>
       </c>
       <c r="O10" t="n">
         <v>0.9488386143528591</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6610266823834662</v>
+        <v>0.6610812648928003</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.860300635255786</v>
+        <v>5.853598569792299</v>
       </c>
       <c r="R10" t="n">
-        <v>3.365044009992087</v>
+        <v>3.365043538937378</v>
       </c>
       <c r="S10" t="n">
-        <v>7.023719169121544</v>
+        <v>7.016871923299492</v>
       </c>
       <c r="T10" t="n">
-        <v>176.3138741260614</v>
+        <v>176.3141733744474</v>
       </c>
       <c r="U10" t="n">
-        <v>26.78660991178884</v>
+        <v>26.6829868959511</v>
       </c>
       <c r="V10" t="n">
-        <v>292.0739871479983</v>
+        <v>291.4120508119377</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34326,13 +34330,13 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>50.575105024</v>
+        <v>50.581838848</v>
       </c>
       <c r="D11" t="n">
-        <v>25.287552512</v>
+        <v>25.290919424</v>
       </c>
       <c r="E11" t="n">
-        <v>25.287552512</v>
+        <v>25.290919424</v>
       </c>
       <c r="F11" t="n">
         <v>30</v>
@@ -34341,7 +34345,7 @@
         <v>30</v>
       </c>
       <c r="H11" t="n">
-        <v>55.27738578799476</v>
+        <v>55.27801449690784</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -34356,7 +34360,7 @@
         <v>0.2554928735899912</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8122405279110654</v>
+        <v>0.8122543755539958</v>
       </c>
       <c r="N11" t="n">
         <v>0.1232126474483262</v>
@@ -34365,25 +34369,25 @@
         <v>0.1232126474483262</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8329152732703864</v>
+        <v>0.8329329252685096</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2150964413380076</v>
+        <v>0.2150963335232143</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2150964413380076</v>
+        <v>0.2150963335232143</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2150964413380077</v>
+        <v>0.2150963335232143</v>
       </c>
       <c r="T11" t="n">
-        <v>11.41082847699657</v>
+        <v>11.4108362700242</v>
       </c>
       <c r="U11" t="n">
-        <v>11.41082847699657</v>
+        <v>11.4108362700242</v>
       </c>
       <c r="V11" t="n">
-        <v>21.05551093055328</v>
+        <v>21.05576517626095</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34401,10 +34405,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>2689.191236608</v>
+        <v>2689.173445632</v>
       </c>
       <c r="D12" t="n">
-        <v>268.9191236608</v>
+        <v>268.9173445632</v>
       </c>
       <c r="E12" t="n">
         <v>96.662212608</v>
@@ -34416,7 +34420,7 @@
         <v>87.5</v>
       </c>
       <c r="H12" t="n">
-        <v>53.26903961738645</v>
+        <v>53.26867823468865</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
@@ -34431,34 +34435,34 @@
         <v>0.2453997723713699</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2044659784336932</v>
+        <v>0.2044606727429696</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2712071289597857</v>
+        <v>0.2712071388418666</v>
       </c>
       <c r="O12" t="n">
-        <v>0.106016289460465</v>
+        <v>0.1060163388708696</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2380826821444036</v>
+        <v>0.2380857316461126</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.292688165615006</v>
+        <v>1.292688069659016</v>
       </c>
       <c r="R12" t="n">
         <v>0.3452443419615151</v>
       </c>
       <c r="S12" t="n">
-        <v>4.963700944316557</v>
+        <v>4.963737784913453</v>
       </c>
       <c r="T12" t="n">
-        <v>54.83767794449068</v>
+        <v>54.83766743226399</v>
       </c>
       <c r="U12" t="n">
         <v>7.584272739316891</v>
       </c>
       <c r="V12" t="n">
-        <v>217.438075157238</v>
+        <v>217.4395833757301</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34476,22 +34480,22 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>1208.156560018516</v>
+        <v>1208.029065362516</v>
       </c>
       <c r="D13" t="n">
-        <v>63.58718736939556</v>
+        <v>63.58047712434292</v>
       </c>
       <c r="E13" t="n">
         <v>44.960280576</v>
       </c>
       <c r="F13" t="n">
-        <v>31.05263157894737</v>
+        <v>32.36842105263158</v>
       </c>
       <c r="G13" t="n">
         <v>25</v>
       </c>
       <c r="H13" t="n">
-        <v>42.25648931735746</v>
+        <v>45.25630676067757</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
@@ -34500,40 +34504,40 @@
         <v>0.1578947368421053</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.03585224003874834</v>
+        <v>-0.03537016277199762</v>
       </c>
       <c r="L13" t="n">
         <v>0.02211851013774391</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1000007152583203</v>
+        <v>0.1011047075696061</v>
       </c>
       <c r="N13" t="n">
-        <v>0.09316541451062546</v>
+        <v>0.09194438326588641</v>
       </c>
       <c r="O13" t="n">
         <v>0.03312442999390219</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2601166298051127</v>
+        <v>0.2573270020385816</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.39647361337348</v>
+        <v>2.386814643624268</v>
       </c>
       <c r="R13" t="n">
-        <v>1.634399123046201</v>
+        <v>1.634399432823354</v>
       </c>
       <c r="S13" t="n">
-        <v>2.064869343820049</v>
+        <v>2.038251096717599</v>
       </c>
       <c r="T13" t="n">
-        <v>73.75153691705032</v>
+        <v>73.75426578583011</v>
       </c>
       <c r="U13" t="n">
-        <v>12.16853694035522</v>
+        <v>12.16853472499045</v>
       </c>
       <c r="V13" t="n">
-        <v>102.7942464007091</v>
+        <v>102.8030479706224</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34551,10 +34555,10 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>2343.513728762299</v>
+        <v>2342.583865239486</v>
       </c>
       <c r="D14" t="n">
-        <v>234.3513728762299</v>
+        <v>234.2583865239486</v>
       </c>
       <c r="E14" t="n">
         <v>52.65784923075</v>
@@ -34566,7 +34570,7 @@
         <v>55</v>
       </c>
       <c r="H14" t="n">
-        <v>13.54178795463398</v>
+        <v>13.55500722470792</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
@@ -34575,40 +34579,40 @@
         <v>0.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09677325989759915</v>
+        <v>0.09677326168541048</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06345038683401272</v>
+        <v>0.06345032948541074</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.03096274685674486</v>
+        <v>-0.03092800949398284</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1947821348701242</v>
+        <v>0.1947821101587378</v>
       </c>
       <c r="O14" t="n">
         <v>0.1762156630172396</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2269380639685906</v>
+        <v>0.2268836431647259</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5188927809549047</v>
+        <v>0.5188925488940632</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3690922267756775</v>
+        <v>0.3690921174195643</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7006586849348484</v>
+        <v>0.7006874276302203</v>
       </c>
       <c r="T14" t="n">
-        <v>15.99219802371976</v>
+        <v>15.9921957876534</v>
       </c>
       <c r="U14" t="n">
-        <v>3.289274420537067</v>
+        <v>3.289273995590651</v>
       </c>
       <c r="V14" t="n">
-        <v>2.806235840204174</v>
+        <v>2.807460326689859</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -1024,16 +1024,16 @@
         <v>453.1150103759766</v>
       </c>
       <c r="AG3" t="n">
-        <v>429.6539505004883</v>
+        <v>429.6539512634278</v>
       </c>
       <c r="AH3" t="n">
         <v>0.09382826331786864</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1535562615110861</v>
+        <v>0.1535562594627082</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.05460454826066274</v>
+        <v>0.05460454638799406</v>
       </c>
       <c r="AK3" t="n">
         <v>537.6464233398438</v>
@@ -1072,13 +1072,13 @@
         <v>-0.002599009870587476</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.7149102799980402</v>
+        <v>0.7149095556703464</v>
       </c>
       <c r="AX3" t="n">
         <v>0.05462505519623884</v>
       </c>
       <c r="AY3" t="n">
-        <v>8397.480698943207</v>
+        <v>8397.481229099616</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1268,13 +1268,13 @@
         <v>1.957717803516736</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.206413767596303</v>
+        <v>4.206412941685683</v>
       </c>
       <c r="AX4" t="n">
         <v>2.321982329146867</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.251978127284558</v>
+        <v>4.251977707069563</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
@@ -1416,16 +1416,16 @@
         <v>600.902197265625</v>
       </c>
       <c r="AG5" t="n">
-        <v>622.5782839965821</v>
+        <v>622.5782849121093</v>
       </c>
       <c r="AH5" t="n">
         <v>0.07842845681993316</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.04088119671779733</v>
+        <v>0.04088119518713818</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.03481664440945398</v>
+        <v>-0.03481664582879629</v>
       </c>
       <c r="AK5" t="n">
         <v>777.7011108398438</v>
@@ -1461,16 +1461,16 @@
         <v>0.05780582477842255</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.1341670638786125</v>
+        <v>-0.1341671344864807</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.7374177085686509</v>
+        <v>0.737417566413243</v>
       </c>
       <c r="AX5" t="n">
         <v>-0.001881861088982584</v>
       </c>
       <c r="AY5" t="n">
-        <v>16.09968370898972</v>
+        <v>16.09967854527519</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -1612,16 +1612,16 @@
         <v>346.9777496337891</v>
       </c>
       <c r="AG6" t="n">
-        <v>336.3809658813477</v>
+        <v>336.3809657287597</v>
       </c>
       <c r="AH6" t="n">
         <v>-0.02443312184350943</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.006299506611797456</v>
+        <v>0.006299507068271204</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.03150232869055736</v>
+        <v>0.03150232915846374</v>
       </c>
       <c r="AK6" t="n">
         <v>402.1211853027344</v>
@@ -1657,10 +1657,10 @@
         <v>0.1212118179624675</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.4119079606978782</v>
+        <v>0.4119080505594885</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.377363626445911</v>
+        <v>1.377363881218482</v>
       </c>
       <c r="AX6" t="n">
         <v>0.07618107138345542</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="X7" t="n">
-        <v>61045092352</v>
+        <v>57012838400</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>61045092352</v>
+        <v>57012838400</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -2384,16 +2384,16 @@
         <v>140.6299467468262</v>
       </c>
       <c r="AG10" t="n">
-        <v>166.8175089645386</v>
+        <v>166.8175086593628</v>
       </c>
       <c r="AH10" t="n">
         <v>0.06862017838806089</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.09913533829807508</v>
+        <v>-0.09913533665003416</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1569832949806201</v>
+        <v>-0.1569832934384063</v>
       </c>
       <c r="AK10" t="n">
         <v>324.4519958496094</v>
@@ -2429,16 +2429,16 @@
         <v>-0.02437296863035288</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.5062923382987412</v>
+        <v>-0.5062922888006263</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.7862063968632773</v>
+        <v>0.7862065588398521</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.2247226929797956</v>
+        <v>-0.2247226319512438</v>
       </c>
       <c r="AY10" t="n">
-        <v>2990.385372388566</v>
+        <v>2990.384485102764</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2624,13 +2624,13 @@
         <v>-0.275870939666826</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.08255307053061633</v>
+        <v>0.0825529870474393</v>
       </c>
       <c r="AX11" t="n">
         <v>-0.3043479187343738</v>
       </c>
       <c r="AY11" t="n">
-        <v>608.1361819570965</v>
+        <v>608.1362852069659</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
@@ -2816,13 +2816,13 @@
         <v>-0.2903769299056658</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.3179885595200022</v>
+        <v>-0.3179884945843425</v>
       </c>
       <c r="AX12" t="n">
         <v>-0.291743876346652</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.2370492813136365</v>
+        <v>0.2370493881315128</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>14821988352</v>
+        <v>14759337984</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>14821988352</v>
+        <v>14759337984</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="X18" t="n">
-        <v>29133248512</v>
+        <v>29178312704</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>29133248512</v>
+        <v>29178312704</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -4755,16 +4755,16 @@
         <v>0.1277732642630893</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.01393743323475483</v>
+        <v>0.01393734656336121</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.989548382805551</v>
+        <v>6.989549055484776</v>
       </c>
       <c r="AX22" t="n">
         <v>0.0451742685812544</v>
       </c>
       <c r="AY22" t="n">
-        <v>317.767752326703</v>
+        <v>317.7679865664864</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
@@ -4906,16 +4906,16 @@
         <v>237.1030813598633</v>
       </c>
       <c r="AG23" t="n">
-        <v>258.0273531341552</v>
+        <v>258.0273535919189</v>
       </c>
       <c r="AH23" t="n">
         <v>0.02609376432725208</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.05711549441953967</v>
+        <v>-0.05711549609230138</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.08109323108629063</v>
+        <v>-0.08109323271651381</v>
       </c>
       <c r="AK23" t="n">
         <v>326.8851013183594</v>
@@ -4951,16 +4951,16 @@
         <v>0.002268520599327362</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.02877417944781357</v>
+        <v>-0.02877412028670689</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.207604887086692</v>
+        <v>1.20760503991667</v>
       </c>
       <c r="AX23" t="n">
-        <v>-0.1483840812308197</v>
+        <v>-0.1483841722039867</v>
       </c>
       <c r="AY23" t="n">
-        <v>168.6051232295094</v>
+        <v>168.6051514194302</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5093,7 +5093,7 @@
         <v>29567</v>
       </c>
       <c r="AD24" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="AE24" t="n">
         <v>332.2699890136719</v>
@@ -5102,16 +5102,16 @@
         <v>317.8303741455078</v>
       </c>
       <c r="AG24" t="n">
-        <v>284.5368991851807</v>
+        <v>284.5368969726562</v>
       </c>
       <c r="AH24" t="n">
         <v>0.0454318279270356</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1677571167928762</v>
+        <v>0.1677571258732142</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1170093406362007</v>
+        <v>0.1170093493219302</v>
       </c>
       <c r="AK24" t="n">
         <v>339.7869262695312</v>
@@ -5150,13 +5150,13 @@
         <v>0.4497995740678464</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.207777594829726</v>
+        <v>1.207776699466175</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.2293803880831269</v>
+        <v>0.2293805268965801</v>
       </c>
       <c r="AY24" t="n">
-        <v>3385.280334952015</v>
+        <v>3385.281363453541</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5490,16 +5490,16 @@
         <v>212.3561532592773</v>
       </c>
       <c r="AG26" t="n">
-        <v>197.1051929473877</v>
+        <v>197.1051928710937</v>
       </c>
       <c r="AH26" t="n">
         <v>0.02794286831712633</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1074796661719606</v>
+        <v>0.1074796666006352</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.07737472607309992</v>
+        <v>0.07737472649012189</v>
       </c>
       <c r="AK26" t="n">
         <v>235.202392578125</v>
@@ -5532,19 +5532,19 @@
         <v>0.06503360332428509</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.2138082500949225</v>
+        <v>0.2138083530828809</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.2350453814344682</v>
+        <v>0.2350452748111889</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.598190240151791</v>
+        <v>8.598189435190632</v>
       </c>
       <c r="AX26" t="n">
         <v>0.1585955986034835</v>
       </c>
       <c r="AY26" t="n">
-        <v>5817.413780112818</v>
+        <v>5817.41435785695</v>
       </c>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>0.1490868479013443</v>
+        <v>0.1490846127271652</v>
       </c>
       <c r="AA28" t="n">
-        <v>97504019388.94238</v>
+        <v>97502557566.72559</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
@@ -6316,13 +6316,13 @@
         <v>3.182852494449236</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.088626622413908</v>
+        <v>1.0886264607558</v>
       </c>
       <c r="AX30" t="n">
         <v>1.614017258743895</v>
       </c>
       <c r="AY30" t="n">
-        <v>566.1632843449839</v>
+        <v>566.1632377807866</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6455,7 +6455,7 @@
         <v>33585</v>
       </c>
       <c r="AD31" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="AE31" t="n">
         <v>181.9700012207031</v>
@@ -6464,28 +6464,28 @@
         <v>167.8024603271484</v>
       </c>
       <c r="AG31" t="n">
-        <v>166.4593501281738</v>
+        <v>166.4593502426147</v>
       </c>
       <c r="AH31" t="n">
         <v>0.0844298758548212</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.09317981285272392</v>
+        <v>0.09317981210116222</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.008068697840886596</v>
+        <v>0.008068697147838755</v>
       </c>
       <c r="AK31" t="n">
-        <v>248.7424926757812</v>
+        <v>248.7425079345703</v>
       </c>
       <c r="AL31" t="n">
-        <v>122.9443130493164</v>
+        <v>122.9443054199219</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0.2684402280317721</v>
+        <v>-0.2684402729083649</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.4801010043279501</v>
+        <v>0.4801010961766492</v>
       </c>
       <c r="AO31" t="n">
         <v>80.41228104081972</v>
@@ -6509,16 +6509,16 @@
         <v>0.4145441441817588</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.1501423840060041</v>
+        <v>0.1501424949294952</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.4026838698810877</v>
+        <v>0.402683539914648</v>
       </c>
       <c r="AX31" t="n">
         <v>0.06841928392637908</v>
       </c>
       <c r="AY31" t="n">
-        <v>541.2931196477541</v>
+        <v>541.2933123020266</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
@@ -6704,7 +6704,7 @@
         <v>6.804807488360287</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.242268784622484</v>
+        <v>4.242268274485537</v>
       </c>
       <c r="AX32" t="n">
         <v>4.278251218089809</v>
@@ -6900,7 +6900,7 @@
         <v>2.588393791907249</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.441159917053373</v>
+        <v>4.44116027472621</v>
       </c>
       <c r="AX33" t="n">
         <v>1.364593793492743</v>
@@ -7098,7 +7098,7 @@
         <v>1.737572926819951</v>
       </c>
       <c r="AY34" t="n">
-        <v>27.26115241316053</v>
+        <v>27.26115988990115</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7284,13 +7284,13 @@
         <v>6.278814266453553</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.661409185290411</v>
+        <v>6.66141010202343</v>
       </c>
       <c r="AX35" t="n">
         <v>3.470322288087283</v>
       </c>
       <c r="AY35" t="n">
-        <v>133.2129188640086</v>
+        <v>133.2129100724851</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA36" t="n">
-        <v>7500452575.149536</v>
+        <v>7499582516.784668</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
@@ -7476,13 +7476,13 @@
         <v>7.822905011209466</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.293791511379664</v>
+        <v>4.2937918326055</v>
       </c>
       <c r="AX36" t="n">
         <v>4.073170663628245</v>
       </c>
       <c r="AY36" t="n">
-        <v>13.50121847008162</v>
+        <v>13.50121967527242</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="X38" t="n">
-        <v>12852446208</v>
+        <v>12822445056</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>12852446208</v>
+        <v>12822445056</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
@@ -7816,16 +7816,16 @@
         <v>56.28073356628418</v>
       </c>
       <c r="AG38" t="n">
-        <v>56.32725648880005</v>
+        <v>56.32725671768188</v>
       </c>
       <c r="AH38" t="n">
         <v>-0.08085775958638242</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.08161691573737173</v>
+        <v>-0.08161691946915661</v>
       </c>
       <c r="AJ38" t="n">
-        <v>-0.0008259397921345224</v>
+        <v>-0.000825943852207911</v>
       </c>
       <c r="AK38" t="n">
         <v>93.37815856933594</v>
@@ -7867,7 +7867,7 @@
         <v>0.9479422416482752</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.2111586717106346</v>
+        <v>0.2111587798838475</v>
       </c>
       <c r="AY38" t="n">
         <v>3.190138934003741</v>
@@ -8056,13 +8056,13 @@
         <v>0.2107603892268155</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.044324296820654</v>
+        <v>1.044324465136008</v>
       </c>
       <c r="AX39" t="n">
         <v>0.1253661186097392</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.632144345582888</v>
+        <v>3.632143049360775</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="X40" t="n">
-        <v>14236608626688</v>
+        <v>14267368603648</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>0.00651236716657877</v>
       </c>
       <c r="AA40" t="n">
-        <v>92714022583.875</v>
+        <v>92914342847.87402</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         <v>187.0133999633789</v>
       </c>
       <c r="AG41" t="n">
-        <v>178.1654887390137</v>
+        <v>178.1654884338379</v>
       </c>
       <c r="AH41" t="n">
         <v>0.008376949822753721</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.05845415498675366</v>
+        <v>0.05845415679975674</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.04966119581849049</v>
+        <v>0.04966119761643228</v>
       </c>
       <c r="AK41" t="n">
         <v>202.5594635009766</v>
@@ -8441,16 +8441,16 @@
         <v>0.05694186929571288</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.1108041317727211</v>
+        <v>0.1108042316115425</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.3345997084972185</v>
+        <v>0.3346002849804299</v>
       </c>
       <c r="AX41" t="n">
         <v>0.2328575223559801</v>
       </c>
       <c r="AY41" t="n">
-        <v>35.99377267965599</v>
+        <v>35.99376921921329</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8637,10 +8637,10 @@
         <v>0.08035399408722066</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.3290945945840307</v>
+        <v>0.3290944906849667</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.2985354628332308</v>
+        <v>0.2985351653046637</v>
       </c>
       <c r="AX42" t="n">
         <v>0.3787888605369425</v>
@@ -8788,28 +8788,28 @@
         <v>121.4274002075195</v>
       </c>
       <c r="AG43" t="n">
-        <v>109.3037474060059</v>
+        <v>109.3037472915649</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.05144967191644501</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.05376076336470637</v>
+        <v>0.05376076446799294</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.1109170828012025</v>
+        <v>0.1109170839643314</v>
       </c>
       <c r="AK43" t="n">
         <v>133.0599975585938</v>
       </c>
       <c r="AL43" t="n">
-        <v>77.69111633300781</v>
+        <v>77.69110870361328</v>
       </c>
       <c r="AM43" t="n">
         <v>-0.1343754515367731</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.4825375891302577</v>
+        <v>0.4825377347178847</v>
       </c>
       <c r="AO43" t="n">
         <v>36.33094490431546</v>
@@ -8839,10 +8839,10 @@
         <v>1.834340358383641</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.4045281691811533</v>
+        <v>0.4045280385117627</v>
       </c>
       <c r="AY43" t="n">
-        <v>98.96806774073896</v>
+        <v>98.96802636788964</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -8980,28 +8980,28 @@
         <v>2.18869544506073</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.173684566020965</v>
+        <v>2.173684567213058</v>
       </c>
       <c r="AH44" t="n">
         <v>-0.02224856832705846</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.01549648078812627</v>
+        <v>-0.01549648132804815</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.006905730147977573</v>
+        <v>0.00690572959576996</v>
       </c>
       <c r="AK44" t="n">
         <v>2.30321192741394</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.061682462692261</v>
+        <v>2.061682224273682</v>
       </c>
       <c r="AM44" t="n">
         <v>-0.07086270289205254</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.03798724761408812</v>
+        <v>0.03798736764977639</v>
       </c>
       <c r="AO44" t="n">
         <v>25.67112826337086</v>
@@ -9028,13 +9028,13 @@
         <v>-0.03678298057557294</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.06435019376538054</v>
+        <v>0.06435006755492445</v>
       </c>
       <c r="AX44" t="n">
         <v>0.01481794284745197</v>
       </c>
       <c r="AY44" t="n">
-        <v>2.977313856374117</v>
+        <v>2.977314737577442</v>
       </c>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
@@ -9163,7 +9163,7 @@
         <v>40525</v>
       </c>
       <c r="AD45" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="AE45" t="n">
         <v>12.0600004196167</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="X48" t="n">
-        <v>1993217015808</v>
+        <v>1992068956160</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>1993217015808</v>
+        <v>1992068956160</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="X49" t="n">
-        <v>10551757824</v>
+        <v>10547602432</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>10551757824</v>
+        <v>10547602432</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
@@ -9937,13 +9937,13 @@
         <v>16.86722755432129</v>
       </c>
       <c r="AL49" t="n">
-        <v>11.91677379608154</v>
+        <v>11.91677284240723</v>
       </c>
       <c r="AM49" t="n">
         <v>-0.1231516908026825</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.24110772050706</v>
+        <v>0.2411078198303056</v>
       </c>
       <c r="AO49" t="n">
         <v>53.8460127717481</v>
@@ -9970,13 +9970,13 @@
         <v>0.208269148124244</v>
       </c>
       <c r="AW49" t="n">
-        <v>-0.2654902434403713</v>
+        <v>-0.2654899651378101</v>
       </c>
       <c r="AX49" t="n">
         <v>0.03450408380073022</v>
       </c>
       <c r="AY49" t="n">
-        <v>6.500327325998982</v>
+        <v>6.500329139686472</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10118,16 +10118,16 @@
         <v>1002.329603271484</v>
       </c>
       <c r="AG50" t="n">
-        <v>893.2902505493164</v>
+        <v>893.2902514648438</v>
       </c>
       <c r="AH50" t="n">
         <v>-0.04495485675885991</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.07162259852560804</v>
+        <v>0.07162259742730903</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.122064863749622</v>
+        <v>0.122064862599625</v>
       </c>
       <c r="AK50" t="n">
         <v>1174.859985351562</v>
@@ -10167,10 +10167,10 @@
       </c>
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="n">
-        <v>0.4112927267356079</v>
+        <v>0.4112925997426113</v>
       </c>
       <c r="AY50" t="n">
-        <v>6.324306944541086</v>
+        <v>6.324307799644687</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10312,28 +10312,28 @@
         <v>67.84656311035157</v>
       </c>
       <c r="AG51" t="n">
-        <v>62.96072395324707</v>
+        <v>62.96072414398193</v>
       </c>
       <c r="AH51" t="n">
         <v>-0.05138893320696514</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.02222459605362159</v>
+        <v>0.02222459295686763</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.07760138146970141</v>
+        <v>0.07760137820518764</v>
       </c>
       <c r="AK51" t="n">
         <v>70.97299957275391</v>
       </c>
       <c r="AL51" t="n">
-        <v>55.35892868041992</v>
+        <v>55.35893249511719</v>
       </c>
       <c r="AM51" t="n">
         <v>-0.0931762642443118</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.1625947637443219</v>
+        <v>0.1625946836317389</v>
       </c>
       <c r="AO51" t="n">
         <v>37.09052042422923</v>
@@ -10357,16 +10357,16 @@
         <v>0.03877805391089284</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.1183147131905433</v>
+        <v>0.1183147873168129</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.0283558119979237</v>
+        <v>0.02835556127690841</v>
       </c>
       <c r="AX51" t="n">
         <v>0.120204340034672</v>
       </c>
       <c r="AY51" t="n">
-        <v>174.9186635232768</v>
+        <v>174.9187495056376</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10508,16 +10508,16 @@
         <v>109.265920715332</v>
       </c>
       <c r="AG52" t="n">
-        <v>104.7508229446411</v>
+        <v>104.7508230209351</v>
       </c>
       <c r="AH52" t="n">
         <v>-0.03602146816235141</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.005529110608702981</v>
+        <v>0.005529109876338367</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.04310322003939837</v>
+        <v>0.0431032192796672</v>
       </c>
       <c r="AK52" t="n">
         <v>116.6635665893555</v>
@@ -10556,13 +10556,13 @@
         <v>0.2013501666171391</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.229217906321854</v>
+        <v>1.229218086297221</v>
       </c>
       <c r="AX52" t="n">
         <v>0.1425278409052821</v>
       </c>
       <c r="AY52" t="n">
-        <v>196.1452079662031</v>
+        <v>196.1451859723959</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10756,7 +10756,7 @@
         <v>-0.2190755155207131</v>
       </c>
       <c r="AY53" t="n">
-        <v>6.043039953472564</v>
+        <v>6.043040618005776</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10898,16 +10898,16 @@
         <v>123.5100679016113</v>
       </c>
       <c r="AG54" t="n">
-        <v>122.3461171340942</v>
+        <v>122.3461167907715</v>
       </c>
       <c r="AH54" t="n">
         <v>-0.03311527393802571</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.02391672930610322</v>
+        <v>-0.02391672656705757</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.009513589763060271</v>
+        <v>0.009513592595916665</v>
       </c>
       <c r="AK54" t="n">
         <v>131.1634063720703</v>
@@ -10940,19 +10940,19 @@
         <v>-0.03600892906742037</v>
       </c>
       <c r="AU54" t="n">
-        <v>-0.08741285813200106</v>
+        <v>-0.08741275171972063</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.01229280570979929</v>
+        <v>0.01229274024237026</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.370088932347046</v>
+        <v>0.3700892921228054</v>
       </c>
       <c r="AX54" t="n">
         <v>0.04347649280678301</v>
       </c>
       <c r="AY54" t="n">
-        <v>161.7225399053083</v>
+        <v>161.7225795531758</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11092,16 +11092,16 @@
         <v>148.8540002441406</v>
       </c>
       <c r="AG55" t="n">
-        <v>157.0050724029541</v>
+        <v>157.0050727081299</v>
       </c>
       <c r="AH55" t="n">
         <v>-0.00318429710018342</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.05493496094193273</v>
+        <v>-0.05493496277888588</v>
       </c>
       <c r="AJ55" t="n">
-        <v>-0.0519159797455061</v>
+        <v>-0.05191598158832733</v>
       </c>
       <c r="AK55" t="n">
         <v>217.0162200927734</v>
@@ -11137,16 +11137,16 @@
         <v>-0.06391631742452597</v>
       </c>
       <c r="AV55" t="n">
-        <v>-0.2690107178633612</v>
+        <v>-0.2690107728132318</v>
       </c>
       <c r="AW55" t="n">
-        <v>7.517854636257788</v>
+        <v>7.517857434185869</v>
       </c>
       <c r="AX55" t="n">
-        <v>-0.09949466780026628</v>
+        <v>-0.09949475119089068</v>
       </c>
       <c r="AY55" t="n">
-        <v>12.08738809441496</v>
+        <v>12.08738919527145</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA56" t="n">
-        <v>142410275204.6982</v>
+        <v>142393755501.3945</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
@@ -11525,16 +11525,16 @@
         <v>-0.1172077287486526</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.02861186966113949</v>
+        <v>0.02861196317624026</v>
       </c>
       <c r="AW57" t="n">
-        <v>0.450988677832161</v>
+        <v>0.4509889569567094</v>
       </c>
       <c r="AX57" t="n">
         <v>0.009956801965402162</v>
       </c>
       <c r="AY57" t="n">
-        <v>176.6978896332866</v>
+        <v>176.6978242217564</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11724,13 +11724,13 @@
         <v>-0.0225949006443551</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.5791290714273325</v>
+        <v>0.5791289623013243</v>
       </c>
       <c r="AX58" t="n">
         <v>0.02447311198179936</v>
       </c>
       <c r="AY58" t="n">
-        <v>323.0878071113752</v>
+        <v>323.0879148396873</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -11922,7 +11922,7 @@
         <v>-0.4410642291427752</v>
       </c>
       <c r="AY59" t="n">
-        <v>-0.9299773823965434</v>
+        <v>-0.9299773902559232</v>
       </c>
       <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
@@ -12444,16 +12444,16 @@
         <v>167.8812966918945</v>
       </c>
       <c r="AG62" t="n">
-        <v>191.8257102203369</v>
+        <v>191.8257099914551</v>
       </c>
       <c r="AH62" t="n">
         <v>-0.105796785733098</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.2174146263044976</v>
+        <v>-0.2174146253707356</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.1248237970861105</v>
+        <v>-0.1248237960418713</v>
       </c>
       <c r="AK62" t="n">
         <v>237.7264404296875</v>
@@ -12492,13 +12492,13 @@
         <v>-0.112402644785095</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.759188523620641</v>
+        <v>1.759188717077582</v>
       </c>
       <c r="AX62" t="n">
         <v>-0.1709335309286669</v>
       </c>
       <c r="AY62" t="n">
-        <v>9.611075241780931</v>
+        <v>9.611075957067982</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -12690,7 +12690,7 @@
         <v>-0.01907464793006219</v>
       </c>
       <c r="AY63" t="n">
-        <v>15.1577955620556</v>
+        <v>15.15779813735503</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12801,7 +12801,7 @@
         </is>
       </c>
       <c r="X64" t="n">
-        <v>171696865280</v>
+        <v>171666178048</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>1</v>
       </c>
       <c r="AA64" t="n">
-        <v>171696865280</v>
+        <v>171666178048</v>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
@@ -12832,28 +12832,28 @@
         <v>85.63172836303711</v>
       </c>
       <c r="AG64" t="n">
-        <v>86.55546867370606</v>
+        <v>86.55546863555908</v>
       </c>
       <c r="AH64" t="n">
         <v>-0.03879088823666887</v>
       </c>
       <c r="AI64" t="n">
-        <v>-0.04904913785536469</v>
+        <v>-0.04904913743625883</v>
       </c>
       <c r="AJ64" t="n">
-        <v>-0.0106722350976024</v>
+        <v>-0.01067223466158296</v>
       </c>
       <c r="AK64" t="n">
         <v>96.44304656982422</v>
       </c>
       <c r="AL64" t="n">
-        <v>67.87922668457031</v>
+        <v>67.87921905517578</v>
       </c>
       <c r="AM64" t="n">
         <v>-0.1465429547686283</v>
       </c>
       <c r="AN64" t="n">
-        <v>0.212594803725183</v>
+        <v>0.212594940016736</v>
       </c>
       <c r="AO64" t="n">
         <v>44.95100260838581</v>
@@ -12880,10 +12880,10 @@
         <v>0.1872616281865767</v>
       </c>
       <c r="AW64" t="n">
-        <v>0.09870477819140677</v>
+        <v>0.09870500197569698</v>
       </c>
       <c r="AX64" t="n">
-        <v>0.03924345910238802</v>
+        <v>0.03924355921115819</v>
       </c>
       <c r="AY64" t="n">
         <v>237.6419604019922</v>
@@ -13028,25 +13028,25 @@
         <v>124.7768704223633</v>
       </c>
       <c r="AG65" t="n">
-        <v>144.878759727478</v>
+        <v>144.8787600326538</v>
       </c>
       <c r="AH65" t="n">
         <v>-0.09069686793380538</v>
       </c>
       <c r="AI65" t="n">
-        <v>-0.2168624351982662</v>
+        <v>-0.2168624368478842</v>
       </c>
       <c r="AJ65" t="n">
-        <v>-0.1387497335215121</v>
+        <v>-0.1387497353356684</v>
       </c>
       <c r="AK65" t="n">
-        <v>182.8191833496094</v>
+        <v>182.8191986083984</v>
       </c>
       <c r="AL65" t="n">
         <v>109.5100021362305</v>
       </c>
       <c r="AM65" t="n">
-        <v>-0.3793867962559462</v>
+        <v>-0.3793868480546961</v>
       </c>
       <c r="AN65" t="n">
         <v>0.0360697367472278</v>
@@ -13070,10 +13070,10 @@
         <v>-0.09251021239810941</v>
       </c>
       <c r="AU65" t="n">
-        <v>-0.2528851336116935</v>
+        <v>-0.2528852086792028</v>
       </c>
       <c r="AV65" t="n">
-        <v>-0.2726567418387896</v>
+        <v>-0.2726565995449136</v>
       </c>
       <c r="AW65" t="n">
         <v>1.848101789458746</v>
@@ -13082,7 +13082,7 @@
         <v>-0.3104960057120867</v>
       </c>
       <c r="AY65" t="n">
-        <v>14.89347478983514</v>
+        <v>14.89346948178655</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="X66" t="n">
-        <v>6604485632</v>
+        <v>6519808000</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>6604485632</v>
+        <v>6519808000</v>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
@@ -13606,16 +13606,16 @@
         <v>181.4109027099609</v>
       </c>
       <c r="AG68" t="n">
-        <v>131.7051400756836</v>
+        <v>131.7051403045654</v>
       </c>
       <c r="AH68" t="n">
         <v>0.09850067334654633</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.5130768523140536</v>
+        <v>0.5130768496845757</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.3774018432820025</v>
+        <v>0.3774018408883053</v>
       </c>
       <c r="AK68" t="n">
         <v>207.0800018310547</v>
@@ -13651,16 +13651,16 @@
         <v>1.036378315962156</v>
       </c>
       <c r="AV68" t="n">
-        <v>0.6209733872697376</v>
+        <v>0.6209734878651461</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.444390914961116</v>
+        <v>1.444391143714604</v>
       </c>
       <c r="AX68" t="n">
         <v>0.8870019371368951</v>
       </c>
       <c r="AY68" t="n">
-        <v>211.5167853794182</v>
+        <v>211.5167988877866</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13846,7 +13846,7 @@
         <v>9.579347526230009</v>
       </c>
       <c r="AW69" t="n">
-        <v>6.058741742898738</v>
+        <v>6.058743285053041</v>
       </c>
       <c r="AX69" t="n">
         <v>1.389297060726459</v>
@@ -13967,10 +13967,10 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>0.0007456843159161508</v>
+        <v>0.0007449344266206026</v>
       </c>
       <c r="AA70" t="n">
-        <v>959141726498.1094</v>
+        <v>958177176086.8125</v>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
@@ -13990,16 +13990,16 @@
         <v>1756381.4375</v>
       </c>
       <c r="AG70" t="n">
-        <v>1336251.39546875</v>
+        <v>1336251.3965625</v>
       </c>
       <c r="AH70" t="n">
         <v>0.03166656246331456</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.3560322602053185</v>
+        <v>0.3560322590953775</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.3144094318299069</v>
+        <v>0.314409430754035</v>
       </c>
       <c r="AK70" t="n">
         <v>2918367.25</v>
@@ -14035,16 +14035,16 @@
         <v>0.9491354442737323</v>
       </c>
       <c r="AV70" t="n">
-        <v>5.755916757653973</v>
+        <v>5.755915970498794</v>
       </c>
       <c r="AW70" t="n">
-        <v>14.47712080550214</v>
+        <v>14.47711873992167</v>
       </c>
       <c r="AX70" t="n">
         <v>1.682482754741024</v>
       </c>
       <c r="AY70" t="n">
-        <v>-8.918744914984863</v>
+        <v>-8.918742211372678</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14163,10 +14163,10 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>0.0007456843159161508</v>
+        <v>0.0007449344266206026</v>
       </c>
       <c r="AA71" t="n">
-        <v>1270663355118.422</v>
+        <v>1269385526380.562</v>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
@@ -14186,28 +14186,28 @@
         <v>259460</v>
       </c>
       <c r="AG71" t="n">
-        <v>215571.015390625</v>
+        <v>215571.0155859375</v>
       </c>
       <c r="AH71" t="n">
         <v>0.0001541663454867059</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.2037796432408763</v>
+        <v>0.2037796421502229</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.2035940895386426</v>
+        <v>0.2035940884481575</v>
       </c>
       <c r="AK71" t="n">
         <v>362100.65625</v>
       </c>
       <c r="AL71" t="n">
-        <v>66762.203125</v>
+        <v>66762.1953125</v>
       </c>
       <c r="AM71" t="n">
         <v>-0.2833484404931951</v>
       </c>
       <c r="AN71" t="n">
-        <v>2.886929847328941</v>
+        <v>2.886930302176768</v>
       </c>
       <c r="AO71" t="n">
         <v>51.96850393700787</v>
@@ -14228,19 +14228,19 @@
         <v>-0.2291211015101948</v>
       </c>
       <c r="AU71" t="n">
-        <v>0.3854384314514545</v>
+        <v>0.3854385470246606</v>
       </c>
       <c r="AV71" t="n">
-        <v>2.769819899623551</v>
+        <v>2.769820327475903</v>
       </c>
       <c r="AW71" t="n">
-        <v>2.558768809131345</v>
+        <v>2.55876804655712</v>
       </c>
       <c r="AX71" t="n">
         <v>1.0258668851272</v>
       </c>
       <c r="AY71" t="n">
-        <v>59.78044434583563</v>
+        <v>59.7804512970467</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14426,13 +14426,13 @@
         <v>7.492507565916174</v>
       </c>
       <c r="AW72" t="n">
-        <v>4.333660455963548</v>
+        <v>4.333661088734792</v>
       </c>
       <c r="AX72" t="n">
         <v>0.8986552642408132</v>
       </c>
       <c r="AY72" t="n">
-        <v>3.505365126646732</v>
+        <v>3.50536557814489</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14779,13 +14779,13 @@
         <v>433.3299865722656</v>
       </c>
       <c r="AL74" t="n">
-        <v>114.9438400268555</v>
+        <v>114.94384765625</v>
       </c>
       <c r="AM74" t="n">
         <v>-0.3117946819704582</v>
       </c>
       <c r="AN74" t="n">
-        <v>1.594484412135762</v>
+        <v>1.594484239926934</v>
       </c>
       <c r="AO74" t="n">
         <v>42.17106145701388</v>
@@ -14809,7 +14809,7 @@
         <v>0.4063622593446763</v>
       </c>
       <c r="AV74" t="n">
-        <v>1.594484412135762</v>
+        <v>1.594484239926934</v>
       </c>
       <c r="AW74" t="n">
         <v>4.144068438445124</v>
@@ -14818,7 +14818,7 @@
         <v>0.6145445719687945</v>
       </c>
       <c r="AY74" t="n">
-        <v>1580.800987088059</v>
+        <v>1580.801237132436</v>
       </c>
       <c r="AZ74" t="inlineStr"/>
       <c r="BA74" t="n">
@@ -14960,16 +14960,16 @@
         <v>928.6070019531249</v>
       </c>
       <c r="AG75" t="n">
-        <v>621.9325052642822</v>
+        <v>621.9325054168701</v>
       </c>
       <c r="AH75" t="n">
         <v>0.05023977604559904</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.5681122975735138</v>
+        <v>0.5681122971887858</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.4930993220213267</v>
+        <v>0.4930993216550026</v>
       </c>
       <c r="AK75" t="n">
         <v>1213.373413085938</v>
@@ -15002,7 +15002,7 @@
         <v>-0.006316142964417515</v>
       </c>
       <c r="AU75" t="n">
-        <v>1.289957921719005</v>
+        <v>1.289957757628058</v>
       </c>
       <c r="AV75" t="n">
         <v>5.4875162188819</v>
@@ -15011,7 +15011,7 @@
         <v>12.55000890936919</v>
       </c>
       <c r="AX75" t="n">
-        <v>2.093715194600453</v>
+        <v>2.093715494095987</v>
       </c>
       <c r="AY75" t="n">
         <v>721.0154401002217</v>
@@ -15350,28 +15350,28 @@
         <v>848.2073986816406</v>
       </c>
       <c r="AG77" t="n">
-        <v>605.2932033538818</v>
+        <v>605.293203125</v>
       </c>
       <c r="AH77" t="n">
         <v>-0.02126533651972351</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.3715171066026348</v>
+        <v>0.3715171071212517</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.4013165751437326</v>
+        <v>0.4013165756736179</v>
       </c>
       <c r="AK77" t="n">
         <v>1093.260498046875</v>
       </c>
       <c r="AL77" t="n">
-        <v>194.3849945068359</v>
+        <v>194.3850250244141</v>
       </c>
       <c r="AM77" t="n">
         <v>-0.2406476000978116</v>
       </c>
       <c r="AN77" t="n">
-        <v>3.270751376752806</v>
+        <v>3.270750706263972</v>
       </c>
       <c r="AO77" t="n">
         <v>47.05322685241872</v>
@@ -15398,13 +15398,13 @@
         <v>3.252957295731137</v>
       </c>
       <c r="AW77" t="n">
-        <v>9.669445383582952</v>
+        <v>9.669444337402275</v>
       </c>
       <c r="AX77" t="n">
         <v>1.894244516598677</v>
       </c>
       <c r="AY77" t="n">
-        <v>156.4856891850746</v>
+        <v>156.4857461680869</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15544,28 +15544,28 @@
         <v>494.6775927734375</v>
       </c>
       <c r="AG78" t="n">
-        <v>379.0106123352051</v>
+        <v>379.0106120300293</v>
       </c>
       <c r="AH78" t="n">
         <v>-0.09601728639326135</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.1798614026149901</v>
+        <v>0.1798614035650032</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.3051813766521505</v>
+        <v>0.3051813777030703</v>
       </c>
       <c r="AK78" t="n">
         <v>745.990478515625</v>
       </c>
       <c r="AL78" t="n">
-        <v>95.97096252441406</v>
+        <v>95.97095489501953</v>
       </c>
       <c r="AM78" t="n">
         <v>-0.4005553615569171</v>
       </c>
       <c r="AN78" t="n">
-        <v>3.659534310307903</v>
+        <v>3.65953468072649</v>
       </c>
       <c r="AO78" t="n">
         <v>46.23351960205819</v>
@@ -15586,19 +15586,19 @@
         <v>-0.2053655687556025</v>
       </c>
       <c r="AU78" t="n">
-        <v>0.6432487291428597</v>
+        <v>0.6432485448645322</v>
       </c>
       <c r="AV78" t="n">
-        <v>3.659534310307903</v>
+        <v>3.65953468072649</v>
       </c>
       <c r="AW78" t="n">
-        <v>8.68113573619271</v>
+        <v>8.681136535714616</v>
       </c>
       <c r="AX78" t="n">
-        <v>1.38494598664461</v>
+        <v>1.384945792558361</v>
       </c>
       <c r="AY78" t="n">
-        <v>657.2740277355766</v>
+        <v>657.2739699777102</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="X79" t="n">
-        <v>9432905728</v>
+        <v>9404672000</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>9432905728</v>
+        <v>9404672000</v>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
@@ -16246,28 +16246,28 @@
         <v>80.27049957275391</v>
       </c>
       <c r="AG82" t="n">
-        <v>73.0320651435852</v>
+        <v>73.03206558227539</v>
       </c>
       <c r="AH82" t="n">
         <v>0.04546500414992005</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.1490842824169605</v>
+        <v>0.1490842755146224</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.09911310073099444</v>
+        <v>0.09911309412882408</v>
       </c>
       <c r="AK82" t="n">
         <v>88.16000366210938</v>
       </c>
       <c r="AL82" t="n">
-        <v>58.88565826416016</v>
+        <v>58.88565444946289</v>
       </c>
       <c r="AM82" t="n">
         <v>-0.04809443417691683</v>
       </c>
       <c r="AN82" t="n">
-        <v>0.4251347550957398</v>
+        <v>0.4251348474180161</v>
       </c>
       <c r="AO82" t="n">
         <v>64.498009818745</v>
@@ -16294,13 +16294,13 @@
         <v>0.4144474977009491</v>
       </c>
       <c r="AW82" t="n">
-        <v>3.558486571925111</v>
+        <v>3.558487044212144</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.2055359538563837</v>
+        <v>0.2055360859813806</v>
       </c>
       <c r="AY82" t="n">
-        <v>1340.28236987739</v>
+        <v>1340.282849043941</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -17195,10 +17195,10 @@
         </is>
       </c>
       <c r="Z87" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA87" t="n">
-        <v>7203788995.908875</v>
+        <v>7202953350.751221</v>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>37055</v>
       </c>
       <c r="AD87" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="AE87" t="n">
         <v>142.1999969482422</v>
@@ -17266,13 +17266,13 @@
         <v>0.08141723482576002</v>
       </c>
       <c r="AW87" t="n">
-        <v>1.041217429777988</v>
+        <v>1.041217206230922</v>
       </c>
       <c r="AX87" t="n">
         <v>0.1286185580544279</v>
       </c>
       <c r="AY87" t="n">
-        <v>7.80497333721339</v>
+        <v>7.804974377101559</v>
       </c>
       <c r="AZ87" t="inlineStr"/>
       <c r="BA87" t="n">
@@ -17458,7 +17458,7 @@
         <v>1.409090993536689</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.051402790332227</v>
+        <v>1.051402970624388</v>
       </c>
       <c r="AX88" t="n">
         <v>0.7096773768243965</v>
@@ -17571,7 +17571,7 @@
         </is>
       </c>
       <c r="X89" t="n">
-        <v>37188722688</v>
+        <v>37188132864</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
@@ -17579,10 +17579,10 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA89" t="n">
-        <v>43147375701.00293</v>
+        <v>43141686321.08203</v>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
@@ -17771,10 +17771,10 @@
         </is>
       </c>
       <c r="Z90" t="n">
-        <v>0.1490868479013443</v>
+        <v>0.1490846127271652</v>
       </c>
       <c r="AA90" t="n">
-        <v>21890013975.73853</v>
+        <v>21889685791.22925</v>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
@@ -17842,13 +17842,13 @@
         <v>1.581283699222637</v>
       </c>
       <c r="AW90" t="n">
-        <v>6.915992228703978</v>
+        <v>6.915991554820075</v>
       </c>
       <c r="AX90" t="n">
         <v>1.504023662647851</v>
       </c>
       <c r="AY90" t="n">
-        <v>19.36990945146228</v>
+        <v>19.36990722034421</v>
       </c>
       <c r="AZ90" t="inlineStr"/>
       <c r="BA90" t="n">
@@ -17955,7 +17955,7 @@
         </is>
       </c>
       <c r="X91" t="n">
-        <v>1083174289408</v>
+        <v>1090744287232</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -17963,10 +17963,10 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>0.1490868479013443</v>
+        <v>0.1490846127271652</v>
       </c>
       <c r="AA91" t="n">
-        <v>161487040535.6172</v>
+        <v>162613189646.3506</v>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
@@ -18155,10 +18155,10 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>0.1490868479013443</v>
+        <v>0.1490846127271652</v>
       </c>
       <c r="AA92" t="n">
-        <v>87927037973.69629</v>
+        <v>87925719733.70605</v>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>0.3906082408166636</v>
       </c>
       <c r="AY92" t="n">
-        <v>228.3949700793907</v>
+        <v>228.3949552495158</v>
       </c>
       <c r="AZ92" t="inlineStr"/>
       <c r="BA92" t="n">
@@ -18537,7 +18537,7 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>143335014400</v>
+        <v>143043723264</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>1</v>
       </c>
       <c r="AA94" t="n">
-        <v>143335014400</v>
+        <v>143043723264</v>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
@@ -18616,13 +18616,13 @@
         <v>1.224077457323134</v>
       </c>
       <c r="AW94" t="n">
-        <v>3.775291003593885</v>
+        <v>3.775290480828999</v>
       </c>
       <c r="AX94" t="n">
         <v>0.8449372876054011</v>
       </c>
       <c r="AY94" t="n">
-        <v>216.4702649445689</v>
+        <v>216.4702988256008</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18764,28 +18764,28 @@
         <v>216.8398794555664</v>
       </c>
       <c r="AG95" t="n">
-        <v>154.7597800064087</v>
+        <v>154.7597797775269</v>
       </c>
       <c r="AH95" t="n">
         <v>0.08882188413084724</v>
       </c>
       <c r="AI95" t="n">
-        <v>0.5255902153242824</v>
+        <v>0.5255902175805527</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.4011384575927086</v>
+        <v>0.4011384596649212</v>
       </c>
       <c r="AK95" t="n">
         <v>316.3519592285156</v>
       </c>
       <c r="AL95" t="n">
-        <v>66.44841766357422</v>
+        <v>66.44842529296875</v>
       </c>
       <c r="AM95" t="n">
         <v>-0.2536793302014302</v>
       </c>
       <c r="AN95" t="n">
-        <v>2.553132104648163</v>
+        <v>2.553131696688959</v>
       </c>
       <c r="AO95" t="n">
         <v>49.56449814743989</v>
@@ -18809,16 +18809,16 @@
         <v>1.689238258735586</v>
       </c>
       <c r="AV95" t="n">
-        <v>2.553132104648163</v>
+        <v>2.553131696688959</v>
       </c>
       <c r="AW95" t="n">
-        <v>2.910343169222694</v>
+        <v>2.910344157443346</v>
       </c>
       <c r="AX95" t="n">
         <v>1.645110953951491</v>
       </c>
       <c r="AY95" t="n">
-        <v>18.46524987496561</v>
+        <v>18.46525905777374</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -18924,7 +18924,9 @@
           <t>DKK</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr"/>
+      <c r="X96" t="n">
+        <v>49414942720</v>
+      </c>
       <c r="Y96" t="inlineStr">
         <is>
           <t>DKK</t>
@@ -18933,10 +18935,12 @@
       <c r="Z96" t="n">
         <v>0.1551782935857773</v>
       </c>
-      <c r="AA96" t="inlineStr"/>
+      <c r="AA96" t="n">
+        <v>7668126488.928528</v>
+      </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC96" s="2" t="n">
@@ -19006,7 +19010,7 @@
         <v>0.1219660194174756</v>
       </c>
       <c r="AY96" t="n">
-        <v>26.37210534198059</v>
+        <v>26.37210225047868</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19117,7 +19121,7 @@
         </is>
       </c>
       <c r="X97" t="n">
-        <v>61365223424</v>
+        <v>61455826944</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
@@ -19128,7 +19132,7 @@
         <v>1</v>
       </c>
       <c r="AA97" t="n">
-        <v>61365223424</v>
+        <v>61455826944</v>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
@@ -19148,16 +19152,16 @@
         <v>205.5617034912109</v>
       </c>
       <c r="AG97" t="n">
-        <v>214.3561728668213</v>
+        <v>214.3561724090576</v>
       </c>
       <c r="AH97" t="n">
         <v>0.03112594960047987</v>
       </c>
       <c r="AI97" t="n">
-        <v>-0.01117843316993172</v>
+        <v>-0.01117843105827532</v>
       </c>
       <c r="AJ97" t="n">
-        <v>-0.04102736701253906</v>
+        <v>-0.04102736496462589</v>
       </c>
       <c r="AK97" t="n">
         <v>246.3216247558594</v>
@@ -19196,13 +19200,13 @@
         <v>0.008779446100566801</v>
       </c>
       <c r="AW97" t="n">
-        <v>0.5305453799018649</v>
+        <v>0.5305457171803649</v>
       </c>
       <c r="AX97" t="n">
         <v>-0.08127626505466301</v>
       </c>
       <c r="AY97" t="n">
-        <v>6.962670461796258</v>
+        <v>6.962673885097205</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19344,16 +19348,16 @@
         <v>383.0855993652344</v>
       </c>
       <c r="AG98" t="n">
-        <v>369.4377291870117</v>
+        <v>369.437728729248</v>
       </c>
       <c r="AH98" t="n">
         <v>-0.05506761195360621</v>
       </c>
       <c r="AI98" t="n">
-        <v>-0.02015965984044532</v>
+        <v>-0.02015965862634261</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.03694227497623559</v>
+        <v>0.03694227626109226</v>
       </c>
       <c r="AK98" t="n">
         <v>480.8090515136719</v>
@@ -19389,16 +19393,16 @@
         <v>0.1277732642630893</v>
       </c>
       <c r="AV98" t="n">
-        <v>0.01393743323475483</v>
+        <v>0.01393734656336121</v>
       </c>
       <c r="AW98" t="n">
-        <v>6.989550400843566</v>
+        <v>6.989549055484776</v>
       </c>
       <c r="AX98" t="n">
         <v>0.0451742685812544</v>
       </c>
       <c r="AY98" t="n">
-        <v>317.7678861779656</v>
+        <v>317.7679865664864</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19930,16 +19934,16 @@
         <v>78.22238220214844</v>
       </c>
       <c r="AG101" t="n">
-        <v>77.04982259750366</v>
+        <v>77.04982248306274</v>
       </c>
       <c r="AH101" t="n">
         <v>-0.05142243358827003</v>
       </c>
       <c r="AI101" t="n">
-        <v>-0.03698679053615117</v>
+        <v>-0.03698678910580244</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0.01521819992720874</v>
+        <v>0.01521820143509678</v>
       </c>
       <c r="AK101" t="n">
         <v>102.0957336425781</v>
@@ -19975,16 +19979,16 @@
         <v>0.2111894718443408</v>
       </c>
       <c r="AV101" t="n">
-        <v>0.1710775498521604</v>
+        <v>0.1710776203583959</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.05534037577789719</v>
+        <v>0.05534049029526078</v>
       </c>
       <c r="AX101" t="n">
-        <v>0.1604306491015695</v>
+        <v>0.1604307875616626</v>
       </c>
       <c r="AY101" t="n">
-        <v>423.9102286367834</v>
+        <v>423.9101561196683</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20091,7 +20095,7 @@
         </is>
       </c>
       <c r="X102" t="n">
-        <v>45943218176</v>
+        <v>45949857792</v>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
@@ -20102,7 +20106,7 @@
         <v>1</v>
       </c>
       <c r="AA102" t="n">
-        <v>45943218176</v>
+        <v>45949857792</v>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
@@ -20122,16 +20126,16 @@
         <v>56.26079986572265</v>
       </c>
       <c r="AG102" t="n">
-        <v>45.81929414749145</v>
+        <v>45.81929413795471</v>
       </c>
       <c r="AH102" t="n">
         <v>-0.08444248136407873</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.1241988616350893</v>
+        <v>0.1241988618690779</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.2278844733971717</v>
+        <v>0.2278844736527412</v>
       </c>
       <c r="AK102" t="n">
         <v>79.81999969482422</v>
@@ -20167,16 +20171,16 @@
         <v>0.5733219256251763</v>
       </c>
       <c r="AV102" t="n">
-        <v>0.9906641160446528</v>
+        <v>0.9906639693093913</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.19678205393756</v>
+        <v>0.1967819478660771</v>
       </c>
       <c r="AX102" t="n">
         <v>0.8894807230605781</v>
       </c>
       <c r="AY102" t="n">
-        <v>22.52406792963226</v>
+        <v>22.5240628068805</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20477,7 +20481,7 @@
         </is>
       </c>
       <c r="X104" t="n">
-        <v>165213700096</v>
+        <v>165171167232</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -20488,7 +20492,7 @@
         <v>1</v>
       </c>
       <c r="AA104" t="n">
-        <v>165213700096</v>
+        <v>165171167232</v>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
@@ -20508,28 +20512,28 @@
         <v>415.2714404296875</v>
       </c>
       <c r="AG104" t="n">
-        <v>380.9242803955078</v>
+        <v>380.9242797851563</v>
       </c>
       <c r="AH104" t="n">
         <v>0.02431796098727834</v>
       </c>
       <c r="AI104" t="n">
-        <v>0.1166786078207784</v>
+        <v>0.1166786096100225</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.09016794623466251</v>
+        <v>0.09016794798142902</v>
       </c>
       <c r="AK104" t="n">
         <v>459.9599914550781</v>
       </c>
       <c r="AL104" t="n">
-        <v>313.2000122070312</v>
+        <v>313.2000427246094</v>
       </c>
       <c r="AM104" t="n">
         <v>-0.07520218493018394</v>
       </c>
       <c r="AN104" t="n">
-        <v>0.358141693928191</v>
+        <v>0.3581415615936137</v>
       </c>
       <c r="AO104" t="n">
         <v>52.78806215490184</v>
@@ -20556,13 +20560,13 @@
         <v>0.1944917302253835</v>
       </c>
       <c r="AW104" t="n">
-        <v>1.762786948235172</v>
+        <v>1.762787495853646</v>
       </c>
       <c r="AX104" t="n">
         <v>0.3104650208403865</v>
       </c>
       <c r="AY104" t="n">
-        <v>1233.591858710512</v>
+        <v>1233.592392660112</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20677,10 +20681,10 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA105" t="n">
-        <v>190268901620.1797</v>
+        <v>190246830278.7812</v>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
@@ -20748,13 +20752,13 @@
         <v>0.291634890681584</v>
       </c>
       <c r="AW105" t="n">
-        <v>1.298819148076014</v>
+        <v>1.298819563583454</v>
       </c>
       <c r="AX105" t="n">
         <v>0.2472272894666976</v>
       </c>
       <c r="AY105" t="n">
-        <v>14.64281869989337</v>
+        <v>14.64282350982918</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20861,7 +20865,7 @@
         </is>
       </c>
       <c r="X106" t="n">
-        <v>628541685760</v>
+        <v>628726824960</v>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
@@ -20872,7 +20876,7 @@
         <v>0.03161855414509773</v>
       </c>
       <c r="AA106" t="n">
-        <v>19873579323.65356</v>
+        <v>19879433157.47314</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
@@ -20940,7 +20944,7 @@
         <v>1.25855018110979</v>
       </c>
       <c r="AW106" t="n">
-        <v>5.20030992204815</v>
+        <v>5.200309392619952</v>
       </c>
       <c r="AX106" t="n">
         <v>0.7040558252684641</v>
@@ -21061,10 +21065,10 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA107" t="n">
-        <v>43138203778.40039</v>
+        <v>43133199713.02344</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
@@ -21132,13 +21136,13 @@
         <v>0.04725705494249</v>
       </c>
       <c r="AW107" t="n">
-        <v>0.7460674058115271</v>
+        <v>0.7460672418346221</v>
       </c>
       <c r="AX107" t="n">
         <v>0.1279728663777335</v>
       </c>
       <c r="AY107" t="n">
-        <v>9.475951386231095</v>
+        <v>9.475949910566657</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21330,7 +21334,7 @@
         <v>0.6366542354821523</v>
       </c>
       <c r="AY108" t="n">
-        <v>64.58186176027263</v>
+        <v>64.58188707963257</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21520,13 +21524,13 @@
         <v>0.5449460152910517</v>
       </c>
       <c r="AW109" t="n">
-        <v>1.534946891541186</v>
+        <v>1.534946114951027</v>
       </c>
       <c r="AX109" t="n">
         <v>0.3960970939331083</v>
       </c>
       <c r="AY109" t="n">
-        <v>855.4515404573906</v>
+        <v>855.4514250327325</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21641,10 +21645,10 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA110" t="n">
-        <v>88291797356.10938</v>
+        <v>88281555438.5625</v>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
@@ -21712,13 +21716,13 @@
         <v>0.8583092931365022</v>
       </c>
       <c r="AW110" t="n">
-        <v>0.7546123980858217</v>
+        <v>0.7546121975364353</v>
       </c>
       <c r="AX110" t="n">
         <v>0.5421563231244895</v>
       </c>
       <c r="AY110" t="n">
-        <v>0.1590857455921619</v>
+        <v>0.1590856580756304</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21871,13 +21875,13 @@
         <v>184.09619140625</v>
       </c>
       <c r="AL111" t="n">
-        <v>94.14984893798828</v>
+        <v>94.14984130859375</v>
       </c>
       <c r="AM111" t="n">
         <v>-0.1179610852215612</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.724697455327453</v>
+        <v>0.7246975950876178</v>
       </c>
       <c r="AO111" t="n">
         <v>60.40415900751429</v>
@@ -21901,16 +21905,16 @@
         <v>0.4812569783626304</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.707938894972072</v>
+        <v>0.70793875791478</v>
       </c>
       <c r="AW111" t="n">
-        <v>4.135520330887824</v>
+        <v>4.13551940152004</v>
       </c>
       <c r="AX111" t="n">
         <v>0.5272574571895901</v>
       </c>
       <c r="AY111" t="n">
-        <v>7.502514084485943</v>
+        <v>7.502513235320702</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22067,13 +22071,13 @@
         <v>785.1200561523438</v>
       </c>
       <c r="AL112" t="n">
-        <v>375.6900634765625</v>
+        <v>375.6901245117188</v>
       </c>
       <c r="AM112" t="n">
         <v>-0.1713623770125597</v>
       </c>
       <c r="AN112" t="n">
-        <v>0.7316934365245205</v>
+        <v>0.7316931551911221</v>
       </c>
       <c r="AO112" t="n">
         <v>53.45888465826619</v>
@@ -22097,10 +22101,10 @@
         <v>0.1641931124209326</v>
       </c>
       <c r="AV112" t="n">
-        <v>0.6711170303664067</v>
+        <v>0.6711168993688965</v>
       </c>
       <c r="AW112" t="n">
-        <v>4.652982663346365</v>
+        <v>4.652983412851675</v>
       </c>
       <c r="AX112" t="n">
         <v>0.4801838637494129</v>
@@ -22248,16 +22252,16 @@
         <v>277.0487933349609</v>
       </c>
       <c r="AG113" t="n">
-        <v>239.6324000549317</v>
+        <v>239.6324010467529</v>
       </c>
       <c r="AH113" t="n">
         <v>-0.03013469586866502</v>
       </c>
       <c r="AI113" t="n">
-        <v>0.1213008430639444</v>
+        <v>0.1213008384229608</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.1561407942809578</v>
+        <v>0.1561407894957743</v>
       </c>
       <c r="AK113" t="n">
         <v>330.5873718261719</v>
@@ -22293,16 +22297,16 @@
         <v>0.4228328260364922</v>
       </c>
       <c r="AV113" t="n">
-        <v>0.4952999524564978</v>
+        <v>0.495299825484198</v>
       </c>
       <c r="AW113" t="n">
-        <v>0.6304384136859051</v>
+        <v>0.6304387156054703</v>
       </c>
       <c r="AX113" t="n">
         <v>0.5390933280379866</v>
       </c>
       <c r="AY113" t="n">
-        <v>391.7937545275893</v>
+        <v>391.7936518530633</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22413,7 +22417,7 @@
         </is>
       </c>
       <c r="X114" t="n">
-        <v>47365718016</v>
+        <v>47725150208</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -22424,7 +22428,7 @@
         <v>1</v>
       </c>
       <c r="AA114" t="n">
-        <v>47365718016</v>
+        <v>47725150208</v>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
@@ -22444,28 +22448,28 @@
         <v>63.44828910827637</v>
       </c>
       <c r="AG114" t="n">
-        <v>61.17890142440796</v>
+        <v>61.17890167236328</v>
       </c>
       <c r="AH114" t="n">
         <v>-0.0943806382798521</v>
       </c>
       <c r="AI114" t="n">
-        <v>-0.06078733441348805</v>
+        <v>-0.06078733822007443</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.03709428628221523</v>
+        <v>0.03709428207891885</v>
       </c>
       <c r="AK114" t="n">
         <v>75.72768402099609</v>
       </c>
       <c r="AL114" t="n">
-        <v>49.78788757324219</v>
+        <v>49.78789138793945</v>
       </c>
       <c r="AM114" t="n">
         <v>-0.2412286229624899</v>
       </c>
       <c r="AN114" t="n">
-        <v>0.1540959435152605</v>
+        <v>0.1540958550896108</v>
       </c>
       <c r="AO114" t="n">
         <v>35.60830479855863</v>
@@ -22486,19 +22490,19 @@
         <v>-0.1751305609353182</v>
       </c>
       <c r="AU114" t="n">
-        <v>0.03992854130266998</v>
+        <v>0.03992861309887497</v>
       </c>
       <c r="AV114" t="n">
-        <v>-0.06350310460147512</v>
+        <v>-0.06350316282615642</v>
       </c>
       <c r="AW114" t="n">
         <v>0.07433489180473041</v>
       </c>
       <c r="AX114" t="n">
-        <v>0.08595428014442108</v>
+        <v>0.08595420185239799</v>
       </c>
       <c r="AY114" t="n">
-        <v>4.215002885290093</v>
+        <v>4.21500378805288</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22836,16 +22840,16 @@
         <v>61.02492607116699</v>
       </c>
       <c r="AG116" t="n">
-        <v>56.37644330978394</v>
+        <v>56.37644315719604</v>
       </c>
       <c r="AH116" t="n">
         <v>-0.1433009075942481</v>
       </c>
       <c r="AI116" t="n">
-        <v>-0.07266234423440721</v>
+        <v>-0.07266234172448471</v>
       </c>
       <c r="AJ116" t="n">
-        <v>0.08245434597283885</v>
+        <v>0.0824543489025984</v>
       </c>
       <c r="AK116" t="n">
         <v>86.98540496826172</v>
@@ -22884,13 +22888,13 @@
         <v>0.1660412987041053</v>
       </c>
       <c r="AW116" t="n">
-        <v>-0.4940093615494184</v>
+        <v>-0.4940092868237982</v>
       </c>
       <c r="AX116" t="n">
         <v>0.4172553934738501</v>
       </c>
       <c r="AY116" t="n">
-        <v>29.09113703929774</v>
+        <v>29.09113497462275</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -23082,7 +23086,7 @@
         <v>0.03549680509580733</v>
       </c>
       <c r="AY117" t="n">
-        <v>18.37840791748473</v>
+        <v>18.37841674139106</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -23224,16 +23228,16 @@
         <v>1318.587006835937</v>
       </c>
       <c r="AG118" t="n">
-        <v>1254.920339355469</v>
+        <v>1254.920336303711</v>
       </c>
       <c r="AH118" t="n">
         <v>-0.06380090616872336</v>
       </c>
       <c r="AI118" t="n">
-        <v>-0.01630412527099312</v>
+        <v>-0.01630412287880811</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0.05073363263294328</v>
+        <v>0.05073363518815288</v>
       </c>
       <c r="AK118" t="n">
         <v>1687.3154296875</v>
@@ -23269,16 +23273,16 @@
         <v>0.1769211315774069</v>
       </c>
       <c r="AV118" t="n">
-        <v>0.4792092304377549</v>
+        <v>0.4792093386215719</v>
       </c>
       <c r="AW118" t="n">
-        <v>1.549541387677451</v>
+        <v>1.549541226984376</v>
       </c>
       <c r="AX118" t="n">
         <v>0.3230825046483616</v>
       </c>
       <c r="AY118" t="n">
-        <v>146.0532033949273</v>
+        <v>146.0531532769928</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23612,16 +23616,16 @@
         <v>464.2001568603516</v>
       </c>
       <c r="AG120" t="n">
-        <v>443.1174645996094</v>
+        <v>443.1174650573731</v>
       </c>
       <c r="AH120" t="n">
         <v>-0.0467043526941372</v>
       </c>
       <c r="AI120" t="n">
-        <v>-0.001348345830777364</v>
+        <v>-0.001348346862437122</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0.04757811177628035</v>
+        <v>0.04757811069407691</v>
       </c>
       <c r="AK120" t="n">
         <v>502.2725524902344</v>
@@ -23660,13 +23664,13 @@
         <v>0.07415410473978401</v>
       </c>
       <c r="AW120" t="n">
-        <v>1.351476109007468</v>
+        <v>1.35147553701611</v>
       </c>
       <c r="AX120" t="n">
         <v>0.1197111861506492</v>
       </c>
       <c r="AY120" t="n">
-        <v>496.5462932123036</v>
+        <v>496.5466266498429</v>
       </c>
       <c r="AZ120" t="inlineStr"/>
       <c r="BA120" t="n">
@@ -24050,7 +24054,7 @@
         <v>0.3443647918038379</v>
       </c>
       <c r="AY122" t="n">
-        <v>213.4564700086271</v>
+        <v>213.4564410460151</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
@@ -24190,28 +24194,28 @@
         <v>278.7325991821289</v>
       </c>
       <c r="AG123" t="n">
-        <v>259.3688683319092</v>
+        <v>259.3688678741455</v>
       </c>
       <c r="AH123" t="n">
         <v>-0.07775409724993776</v>
       </c>
       <c r="AI123" t="n">
-        <v>-0.008901880893279923</v>
+        <v>-0.008901879144077141</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0.0746571127628175</v>
+        <v>0.07465711465949476</v>
       </c>
       <c r="AK123" t="n">
         <v>376.1517333984375</v>
       </c>
       <c r="AL123" t="n">
-        <v>134.6916351318359</v>
+        <v>134.6916198730469</v>
       </c>
       <c r="AM123" t="n">
         <v>-0.3166055749999594</v>
       </c>
       <c r="AN123" t="n">
-        <v>0.908507512786402</v>
+        <v>0.9085077289952024</v>
       </c>
       <c r="AO123" t="n">
         <v>48.03408585654849</v>
@@ -24232,19 +24236,19 @@
         <v>-0.1510764554471811</v>
       </c>
       <c r="AU123" t="n">
-        <v>-0.006587415460754698</v>
+        <v>-0.00658729830195004</v>
       </c>
       <c r="AV123" t="n">
         <v>0.8962725001561778</v>
       </c>
       <c r="AW123" t="n">
-        <v>8.162433724991168</v>
+        <v>8.162434347889697</v>
       </c>
       <c r="AX123" t="n">
-        <v>0.4644647444818799</v>
+        <v>0.4644648717862903</v>
       </c>
       <c r="AY123" t="n">
-        <v>24.86858131847862</v>
+        <v>24.86858380110207</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
@@ -24359,10 +24363,10 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>0.1032577827572823</v>
+        <v>0.1031555235385895</v>
       </c>
       <c r="AA124" t="n">
-        <v>2776431794.555283</v>
+        <v>2773682212.504578</v>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
@@ -24436,7 +24440,7 @@
         <v>-0.2349132495901315</v>
       </c>
       <c r="AY124" t="n">
-        <v>1.361050054211353</v>
+        <v>1.361050342945241</v>
       </c>
       <c r="AZ124" t="inlineStr"/>
       <c r="BA124" t="n">
@@ -24857,10 +24861,10 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA127" t="n">
-        <v>239583373528.7168</v>
+        <v>239555581670.0078</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -24934,7 +24938,7 @@
         <v>0.1210134822666133</v>
       </c>
       <c r="AY127" t="n">
-        <v>26.83960539389182</v>
+        <v>26.83959701521436</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -25045,7 +25049,7 @@
         </is>
       </c>
       <c r="X128" t="n">
-        <v>79690465280</v>
+        <v>79812878336</v>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
@@ -25056,7 +25060,7 @@
         <v>1</v>
       </c>
       <c r="AA128" t="n">
-        <v>79690465280</v>
+        <v>79812878336</v>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
@@ -25245,10 +25249,10 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA129" t="n">
-        <v>17378225906.32654</v>
+        <v>17376210018.52979</v>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
@@ -25259,7 +25263,7 @@
         <v>35996</v>
       </c>
       <c r="AD129" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="AE129" t="n">
         <v>189.25</v>
@@ -25316,7 +25320,7 @@
         <v>0.6333027791932562</v>
       </c>
       <c r="AW129" t="n">
-        <v>2.432210443544038</v>
+        <v>2.432210206094146</v>
       </c>
       <c r="AX129" t="n">
         <v>0.2772843734130734</v>
@@ -25660,16 +25664,16 @@
         <v>418.9347991943359</v>
       </c>
       <c r="AG131" t="n">
-        <v>374.9871116638184</v>
+        <v>374.9871136474609</v>
       </c>
       <c r="AH131" t="n">
         <v>0.03414658096570089</v>
       </c>
       <c r="AI131" t="n">
-        <v>0.1553463486040587</v>
+        <v>0.1553463424923975</v>
       </c>
       <c r="AJ131" t="n">
-        <v>0.1171978613758793</v>
+        <v>0.1171978554660196</v>
       </c>
       <c r="AK131" t="n">
         <v>477.5700073242188</v>
@@ -25714,7 +25718,7 @@
         <v>0.3625300792233379</v>
       </c>
       <c r="AY131" t="n">
-        <v>137.7298218081567</v>
+        <v>137.7298535822063</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25906,7 +25910,7 @@
         <v>0.5000319113671245</v>
       </c>
       <c r="AY132" t="n">
-        <v>12.37537405716182</v>
+        <v>12.37537818801857</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26098,7 +26102,7 @@
         <v>1.938560260497212</v>
       </c>
       <c r="AY133" t="n">
-        <v>2.744905618827064</v>
+        <v>2.744906504955742</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26288,13 +26292,13 @@
         <v>1.586293904262781</v>
       </c>
       <c r="AW134" t="n">
-        <v>2.918339764377794</v>
+        <v>2.918339473014786</v>
       </c>
       <c r="AX134" t="n">
         <v>0.4064773229425358</v>
       </c>
       <c r="AY134" t="n">
-        <v>17.99113522447463</v>
+        <v>17.99114206882559</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26436,28 +26440,28 @@
         <v>516.4606408691407</v>
       </c>
       <c r="AG135" t="n">
-        <v>411.0397342681885</v>
+        <v>411.039734954834</v>
       </c>
       <c r="AH135" t="n">
         <v>-0.1161185304147133</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.110573874438455</v>
+        <v>0.1105738725832315</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.2564737610796743</v>
+        <v>0.2564737589807238</v>
       </c>
       <c r="AK135" t="n">
         <v>722.2277221679688</v>
       </c>
       <c r="AL135" t="n">
-        <v>166.8769989013672</v>
+        <v>166.8770141601562</v>
       </c>
       <c r="AM135" t="n">
         <v>-0.3679417499177511</v>
       </c>
       <c r="AN135" t="n">
-        <v>1.735487773867409</v>
+        <v>1.735487523741703</v>
       </c>
       <c r="AO135" t="n">
         <v>35.03965121002578</v>
@@ -26481,16 +26485,16 @@
         <v>0.3396954758803989</v>
       </c>
       <c r="AV135" t="n">
-        <v>1.697707124676037</v>
+        <v>1.697707367940375</v>
       </c>
       <c r="AW135" t="n">
-        <v>2.502677306737371</v>
+        <v>2.502676486538888</v>
       </c>
       <c r="AX135" t="n">
-        <v>0.7038600440025082</v>
+        <v>0.7038602380851491</v>
       </c>
       <c r="AY135" t="n">
-        <v>6622.183376384152</v>
+        <v>6622.1826604182</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26605,10 +26609,10 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>1.160227417945862</v>
+        <v>1.160092830657959</v>
       </c>
       <c r="AA136" t="n">
-        <v>47050237869.20947</v>
+        <v>47044780004.81836</v>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
@@ -26676,13 +26680,13 @@
         <v>0.8281034068089408</v>
       </c>
       <c r="AW136" t="n">
-        <v>1.676350418993946</v>
+        <v>1.676350155692504</v>
       </c>
       <c r="AX136" t="n">
         <v>0.5049338540377588</v>
       </c>
       <c r="AY136" t="n">
-        <v>281.4536760350092</v>
+        <v>281.4536302121961</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26824,16 +26828,16 @@
         <v>1738.094543457031</v>
       </c>
       <c r="AG137" t="n">
-        <v>1491.523651428223</v>
+        <v>1491.523657836914</v>
       </c>
       <c r="AH137" t="n">
         <v>-0.02289547181349294</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.138634340261317</v>
+        <v>0.1386343353688999</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.1653147717722763</v>
+        <v>0.1653147667652199</v>
       </c>
       <c r="AK137" t="n">
         <v>1986.870361328125</v>
@@ -26872,13 +26876,13 @@
         <v>1.125803490281717</v>
       </c>
       <c r="AW137" t="n">
-        <v>1.074369858190369</v>
+        <v>1.074369394253185</v>
       </c>
       <c r="AX137" t="n">
         <v>0.4663067634362432</v>
       </c>
       <c r="AY137" t="n">
-        <v>964.0757791566708</v>
+        <v>964.0759099087381</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27020,28 +27024,28 @@
         <v>198.311156616211</v>
       </c>
       <c r="AG138" t="n">
-        <v>172.5825635528564</v>
+        <v>172.5825632095337</v>
       </c>
       <c r="AH138" t="n">
         <v>-0.0891082354018099</v>
       </c>
       <c r="AI138" t="n">
-        <v>0.04668742699678496</v>
+        <v>0.04668742907898604</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0.1490799101235663</v>
+        <v>0.1490799124094593</v>
       </c>
       <c r="AK138" t="n">
         <v>301.3693542480469</v>
       </c>
       <c r="AL138" t="n">
-        <v>95.41329193115234</v>
+        <v>95.41328430175781</v>
       </c>
       <c r="AM138" t="n">
         <v>-0.4006026265000727</v>
       </c>
       <c r="AN138" t="n">
-        <v>0.8932372600663794</v>
+        <v>0.8932374114525736</v>
       </c>
       <c r="AO138" t="n">
         <v>46.71374727949298</v>
@@ -27065,7 +27069,7 @@
         <v>0.2763984165807265</v>
       </c>
       <c r="AV138" t="n">
-        <v>0.8932372600663794</v>
+        <v>0.8932374114525736</v>
       </c>
       <c r="AW138" t="n">
         <v>4.549091924116841</v>
@@ -27074,7 +27078,7 @@
         <v>0.4226327764177782</v>
       </c>
       <c r="AY138" t="n">
-        <v>2979.627872424193</v>
+        <v>2979.628422070165</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27412,28 +27416,28 @@
         <v>365.6934375</v>
       </c>
       <c r="AG140" t="n">
-        <v>320.3741926574707</v>
+        <v>320.3741924285889</v>
       </c>
       <c r="AH140" t="n">
         <v>0.03835607173208611</v>
       </c>
       <c r="AI140" t="n">
-        <v>0.1852390421056238</v>
+        <v>0.1852390429523827</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0.1414572268340681</v>
+        <v>0.1414572276495485</v>
       </c>
       <c r="AK140" t="n">
         <v>483.6542053222656</v>
       </c>
       <c r="AL140" t="n">
-        <v>112.0230102539062</v>
+        <v>112.0230178833008</v>
       </c>
       <c r="AM140" t="n">
         <v>-0.2148936222570621</v>
       </c>
       <c r="AN140" t="n">
-        <v>2.389660752376205</v>
+        <v>2.389660521521335</v>
       </c>
       <c r="AO140" t="n">
         <v>51.48695142225591</v>
@@ -27457,7 +27461,7 @@
         <v>0.3267553938009435</v>
       </c>
       <c r="AV140" t="n">
-        <v>2.292277102995972</v>
+        <v>2.292276667434656</v>
       </c>
       <c r="AW140" t="n">
         <v>2.17550712852658</v>
@@ -27466,7 +27470,7 @@
         <v>0.8316063272566419</v>
       </c>
       <c r="AY140" t="n">
-        <v>340.0657929127381</v>
+        <v>340.0658659514395</v>
       </c>
       <c r="AZ140" t="inlineStr"/>
       <c r="BA140" t="n">
@@ -27577,7 +27581,7 @@
         </is>
       </c>
       <c r="X141" t="n">
-        <v>25761505280</v>
+        <v>25763864576</v>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
@@ -27588,7 +27592,7 @@
         <v>1</v>
       </c>
       <c r="AA141" t="n">
-        <v>25761505280</v>
+        <v>25763864576</v>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
@@ -28038,13 +28042,13 @@
         <v>1.277695401812586</v>
       </c>
       <c r="AW143" t="n">
-        <v>0.7043972594970211</v>
+        <v>0.7043974236211203</v>
       </c>
       <c r="AX143" t="n">
         <v>0.09450472038799984</v>
       </c>
       <c r="AY143" t="n">
-        <v>265.4230140951702</v>
+        <v>265.4229827649019</v>
       </c>
       <c r="AZ143" t="inlineStr"/>
       <c r="BA143" t="n">
@@ -28428,7 +28432,7 @@
         <v>0.2811255516943993</v>
       </c>
       <c r="AY145" t="n">
-        <v>25.61084050445034</v>
+        <v>25.61083822246127</v>
       </c>
       <c r="AZ145" t="inlineStr"/>
       <c r="BA145" t="n">
@@ -28570,16 +28574,16 @@
         <v>448.7317785644531</v>
       </c>
       <c r="AG146" t="n">
-        <v>261.1508752822876</v>
+        <v>261.1508754348755</v>
       </c>
       <c r="AH146" t="n">
         <v>0.2642072728661486</v>
       </c>
       <c r="AI146" t="n">
-        <v>1.172269104647416</v>
+        <v>1.17226910337818</v>
       </c>
       <c r="AJ146" t="n">
-        <v>0.7182855622421425</v>
+        <v>0.7182855612381649</v>
       </c>
       <c r="AK146" t="n">
         <v>567.2899780273438</v>
@@ -28618,13 +28622,13 @@
         <v>3.582586931511815</v>
       </c>
       <c r="AW146" t="n">
-        <v>11.683863339917</v>
+        <v>11.68386009443489</v>
       </c>
       <c r="AX146" t="n">
-        <v>3.479492581674595</v>
+        <v>3.479492851537152</v>
       </c>
       <c r="AY146" t="n">
-        <v>50.74863757254941</v>
+        <v>50.74862856881375</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28814,7 +28818,7 @@
         <v>1.549610310271502</v>
       </c>
       <c r="AW147" t="n">
-        <v>3.619799361917025</v>
+        <v>3.619799689728903</v>
       </c>
       <c r="AX147" t="n">
         <v>1.593015808988345</v>
@@ -29010,13 +29014,13 @@
         <v>0.3621345839635881</v>
       </c>
       <c r="AW148" t="n">
-        <v>1.135952676902177</v>
+        <v>1.135952438510717</v>
       </c>
       <c r="AX148" t="n">
         <v>0.2007632302274407</v>
       </c>
       <c r="AY148" t="n">
-        <v>46.28117395542905</v>
+        <v>46.28113745199876</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29202,13 +29206,13 @@
         <v>0.7561868864342607</v>
       </c>
       <c r="AW149" t="n">
-        <v>6.500129480875004</v>
+        <v>6.500128902481166</v>
       </c>
       <c r="AX149" t="n">
         <v>0.2406611047327465</v>
       </c>
       <c r="AY149" t="n">
-        <v>37.65078489504264</v>
+        <v>37.65078105494056</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29515,10 +29519,10 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>1.352887034416199</v>
+        <v>1.353033423423767</v>
       </c>
       <c r="AA151" t="n">
-        <v>162181692014.5586</v>
+        <v>162199240868.4805</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
@@ -29586,13 +29590,13 @@
         <v>0.2873624475878274</v>
       </c>
       <c r="AW151" t="n">
-        <v>12.328143118832</v>
+        <v>12.32814405055286</v>
       </c>
       <c r="AX151" t="n">
         <v>0.2153045512002121</v>
       </c>
       <c r="AY151" t="n">
-        <v>10.68251806707193</v>
+        <v>10.68251591953522</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29778,13 +29782,13 @@
         <v>1.50081439757112</v>
       </c>
       <c r="AW152" t="n">
-        <v>6.914598463214</v>
+        <v>6.914599290767164</v>
       </c>
       <c r="AX152" t="n">
         <v>0.5825466534444343</v>
       </c>
       <c r="AY152" t="n">
-        <v>81.15411477648358</v>
+        <v>81.1541092036418</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29895,7 +29899,7 @@
         </is>
       </c>
       <c r="X153" t="n">
-        <v>26344310784</v>
+        <v>25939607552</v>
       </c>
       <c r="Y153" t="inlineStr">
         <is>
@@ -29906,7 +29910,7 @@
         <v>1</v>
       </c>
       <c r="AA153" t="n">
-        <v>26344310784</v>
+        <v>25939607552</v>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
@@ -30170,13 +30174,13 @@
         <v>0.2865761534076094</v>
       </c>
       <c r="AW154" t="n">
-        <v>1.721691532166064</v>
+        <v>1.721691304280843</v>
       </c>
       <c r="AX154" t="n">
         <v>0.100798968347741</v>
       </c>
       <c r="AY154" t="n">
-        <v>676.0470361218443</v>
+        <v>676.0470912071983</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30362,13 +30366,13 @@
         <v>0.565029914610981</v>
       </c>
       <c r="AW155" t="n">
-        <v>1.926646775056136</v>
+        <v>1.926647038555185</v>
       </c>
       <c r="AX155" t="n">
         <v>0.4368063630303214</v>
       </c>
       <c r="AY155" t="n">
-        <v>7.158155374320971</v>
+        <v>7.158153838701823</v>
       </c>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="n">
@@ -30554,13 +30558,13 @@
         <v>0.3705709815400917</v>
       </c>
       <c r="AW156" t="n">
-        <v>4.178462086134936</v>
+        <v>4.178462694139246</v>
       </c>
       <c r="AX156" t="n">
         <v>0.2666649052450922</v>
       </c>
       <c r="AY156" t="n">
-        <v>16.68945482445296</v>
+        <v>16.68945127710476</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30747,16 +30751,16 @@
         <v>0.4446488211799347</v>
       </c>
       <c r="AV157" t="n">
-        <v>0.6908229350234771</v>
+        <v>0.6908227405033824</v>
       </c>
       <c r="AW157" t="n">
-        <v>1.170217098450263</v>
+        <v>1.170216617759489</v>
       </c>
       <c r="AX157" t="n">
         <v>0.4881553908068952</v>
       </c>
       <c r="AY157" t="n">
-        <v>2262.673411334917</v>
+        <v>2262.673751818292</v>
       </c>
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="n">
@@ -31094,28 +31098,28 @@
         <v>322.106947631836</v>
       </c>
       <c r="AG159" t="n">
-        <v>294.9937574768066</v>
+        <v>294.9937591552734</v>
       </c>
       <c r="AH159" t="n">
         <v>-0.01250193790968179</v>
       </c>
       <c r="AI159" t="n">
-        <v>0.07826005978202466</v>
+        <v>0.07826005364689936</v>
       </c>
       <c r="AJ159" t="n">
-        <v>0.09191106410840244</v>
+        <v>0.09191105789560505</v>
       </c>
       <c r="AK159" t="n">
         <v>385.5466918945312</v>
       </c>
       <c r="AL159" t="n">
-        <v>192.3445281982422</v>
+        <v>192.3445129394531</v>
       </c>
       <c r="AM159" t="n">
         <v>-0.1749897139325516</v>
       </c>
       <c r="AN159" t="n">
-        <v>0.6536991696713756</v>
+        <v>0.6536993008601808</v>
       </c>
       <c r="AO159" t="n">
         <v>53.2750509174165</v>
@@ -31139,16 +31143,16 @@
         <v>0.2695813267060276</v>
       </c>
       <c r="AV159" t="n">
-        <v>0.4861247100031811</v>
+        <v>0.4861246040548293</v>
       </c>
       <c r="AW159" t="n">
-        <v>4.206783256118798</v>
+        <v>4.206784231521757</v>
       </c>
       <c r="AX159" t="n">
         <v>0.324183924424728</v>
       </c>
       <c r="AY159" t="n">
-        <v>429.5292887569382</v>
+        <v>429.5292540233918</v>
       </c>
       <c r="AZ159" t="inlineStr"/>
       <c r="BA159" t="n">
@@ -32572,16 +32576,16 @@
         <v>383.0855993652344</v>
       </c>
       <c r="AG5" t="n">
-        <v>369.4377291870117</v>
+        <v>369.437728729248</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.05506761195360621</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.02015965984044532</v>
+        <v>-0.02015965862634261</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.03694227497623559</v>
+        <v>0.03694227626109226</v>
       </c>
       <c r="AK5" t="n">
         <v>480.8090515136719</v>
@@ -32617,16 +32621,16 @@
         <v>0.1277732642630893</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.01393743323475483</v>
+        <v>0.01393734656336121</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.989550400843566</v>
+        <v>6.989549055484776</v>
       </c>
       <c r="AX5" t="n">
         <v>0.0451742685812544</v>
       </c>
       <c r="AY5" t="n">
-        <v>317.7678861779656</v>
+        <v>317.7679865664864</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32989,13 +32993,13 @@
         <v>433.3299865722656</v>
       </c>
       <c r="AL7" t="n">
-        <v>114.9438400268555</v>
+        <v>114.94384765625</v>
       </c>
       <c r="AM7" t="n">
         <v>-0.3117946819704582</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.594484412135762</v>
+        <v>1.594484239926934</v>
       </c>
       <c r="AO7" t="n">
         <v>42.17106145701388</v>
@@ -33019,7 +33023,7 @@
         <v>0.4063622593446763</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.594484412135762</v>
+        <v>1.594484239926934</v>
       </c>
       <c r="AW7" t="n">
         <v>4.144068438445124</v>
@@ -33028,7 +33032,7 @@
         <v>0.6145445719687945</v>
       </c>
       <c r="AY7" t="n">
-        <v>1580.800987088059</v>
+        <v>1580.801237132436</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33176,28 +33180,28 @@
         <v>216.8398794555664</v>
       </c>
       <c r="AG8" t="n">
-        <v>154.7597800064087</v>
+        <v>154.7597797775269</v>
       </c>
       <c r="AH8" t="n">
         <v>0.08882188413084724</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.5255902153242824</v>
+        <v>0.5255902175805527</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.4011384575927086</v>
+        <v>0.4011384596649212</v>
       </c>
       <c r="AK8" t="n">
         <v>316.3519592285156</v>
       </c>
       <c r="AL8" t="n">
-        <v>66.44841766357422</v>
+        <v>66.44842529296875</v>
       </c>
       <c r="AM8" t="n">
         <v>-0.2536793302014302</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.553132104648163</v>
+        <v>2.553131696688959</v>
       </c>
       <c r="AO8" t="n">
         <v>49.56449814743989</v>
@@ -33221,16 +33225,16 @@
         <v>1.689238258735586</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.553132104648163</v>
+        <v>2.553131696688959</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.910343169222694</v>
+        <v>2.910344157443346</v>
       </c>
       <c r="AX8" t="n">
         <v>1.645110953951491</v>
       </c>
       <c r="AY8" t="n">
-        <v>18.46524987496561</v>
+        <v>18.46525905777374</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33343,7 +33347,7 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>61045092352</v>
+        <v>57012838400</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -33354,7 +33358,7 @@
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>61045092352</v>
+        <v>57012838400</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -33507,7 +33511,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.871026180220513</v>
+        <v>0.871026096865585</v>
       </c>
     </row>
   </sheetData>
@@ -33651,10 +33655,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>12190.78075282894</v>
+        <v>12190.77929100673</v>
       </c>
       <c r="D2" t="n">
-        <v>1523.847594103618</v>
+        <v>1523.847411375841</v>
       </c>
       <c r="E2" t="n">
         <v>413.47350528</v>
@@ -33666,7 +33670,7 @@
         <v>72.5</v>
       </c>
       <c r="H2" t="n">
-        <v>93.08561365693356</v>
+        <v>93.0856176242997</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -33675,40 +33679,40 @@
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6709867421147913</v>
+        <v>0.6709867594664729</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3965746754673237</v>
+        <v>0.3965747448740503</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3597824340552492</v>
+        <v>0.359782518485823</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9311327650985878</v>
+        <v>0.9311327656361142</v>
       </c>
       <c r="O2" t="n">
         <v>0.4071691950025514</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6051403772433395</v>
+        <v>0.6051404007361075</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.91688886322037</v>
+        <v>3.916888550084762</v>
       </c>
       <c r="R2" t="n">
         <v>1.349969281217933</v>
       </c>
       <c r="S2" t="n">
-        <v>4.718670041067009</v>
+        <v>4.718668527007228</v>
       </c>
       <c r="T2" t="n">
-        <v>1312.339527894158</v>
+        <v>1312.339746936125</v>
       </c>
       <c r="U2" t="n">
-        <v>352.1804761743786</v>
+        <v>352.1805725015148</v>
       </c>
       <c r="V2" t="n">
-        <v>3907.357163111829</v>
+        <v>3907.358290807244</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33726,10 +33730,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>4137.936979341727</v>
+        <v>4137.933880773337</v>
       </c>
       <c r="D3" t="n">
-        <v>275.8624652894485</v>
+        <v>275.8622587182224</v>
       </c>
       <c r="E3" t="n">
         <v>59.365711872</v>
@@ -33741,7 +33745,7 @@
         <v>60</v>
       </c>
       <c r="H3" t="n">
-        <v>78.79478914374249</v>
+        <v>78.79478326196158</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -33750,40 +33754,40 @@
         <v>0.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4898229874662344</v>
+        <v>0.4898230004050771</v>
       </c>
       <c r="L3" t="n">
         <v>0.4226327764177782</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4364430473798321</v>
+        <v>0.4364428821145317</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2001211395717</v>
+        <v>1.200121136844314</v>
       </c>
       <c r="O3" t="n">
         <v>1.125803490281717</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9782694451279339</v>
+        <v>0.9782693722562313</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.165919080318758</v>
+        <v>3.165918960699043</v>
       </c>
       <c r="R3" t="n">
-        <v>2.538017659458036</v>
+        <v>2.538017249358794</v>
       </c>
       <c r="S3" t="n">
-        <v>2.926358901994654</v>
+        <v>2.926360402218545</v>
       </c>
       <c r="T3" t="n">
-        <v>779.4917053236533</v>
+        <v>779.4917054350602</v>
       </c>
       <c r="U3" t="n">
         <v>34.5682251961798</v>
       </c>
       <c r="V3" t="n">
-        <v>987.4028473682696</v>
+        <v>987.4032228482602</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33801,10 +33805,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>1524.292433415551</v>
+        <v>1523.905279037473</v>
       </c>
       <c r="D4" t="n">
-        <v>95.26827708847195</v>
+        <v>95.24407993984207</v>
       </c>
       <c r="E4" t="n">
         <v>43.19344640535009</v>
@@ -33816,7 +33820,7 @@
         <v>72.5</v>
       </c>
       <c r="H4" t="n">
-        <v>78.36094208126632</v>
+        <v>78.35937055852584</v>
       </c>
       <c r="I4" t="n">
         <v>8</v>
@@ -33825,40 +33829,40 @@
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.589544509868914</v>
+        <v>0.5895445267353239</v>
       </c>
       <c r="L4" t="n">
         <v>0.3097017758417258</v>
       </c>
       <c r="M4" t="n">
-        <v>1.16092354104413</v>
+        <v>1.161142620263629</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7680581462464452</v>
+        <v>0.7680581274671674</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4481774767691958</v>
+        <v>0.4481774237950199</v>
       </c>
       <c r="P4" t="n">
-        <v>1.318976850299747</v>
+        <v>1.319338456014733</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.982273910829386</v>
+        <v>6.982273858526188</v>
       </c>
       <c r="R4" t="n">
-        <v>4.192622671126867</v>
+        <v>4.192623462830502</v>
       </c>
       <c r="S4" t="n">
-        <v>6.713950257038555</v>
+        <v>6.713260274420884</v>
       </c>
       <c r="T4" t="n">
-        <v>239.2660758722272</v>
+        <v>239.2660945400126</v>
       </c>
       <c r="U4" t="n">
-        <v>41.21351976685477</v>
+        <v>41.21351784680373</v>
       </c>
       <c r="V4" t="n">
-        <v>738.2490050212693</v>
+        <v>738.4248892035364</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33876,10 +33880,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>13629.14429489245</v>
+        <v>13625.11204094045</v>
       </c>
       <c r="D5" t="n">
-        <v>1135.762024574371</v>
+        <v>1135.426003411704</v>
       </c>
       <c r="E5" t="n">
         <v>352.277921792</v>
@@ -33891,7 +33895,7 @@
         <v>60</v>
       </c>
       <c r="H5" t="n">
-        <v>72.49281397139784</v>
+        <v>72.49651112987671</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -33900,40 +33904,40 @@
         <v>0.25</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4413457406718749</v>
+        <v>0.4413457457575875</v>
       </c>
       <c r="L5" t="n">
         <v>0.06540306328984713</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05570401844894451</v>
+        <v>0.05527766061705892</v>
       </c>
       <c r="N5" t="n">
-        <v>0.296900278856094</v>
+        <v>0.2969002845854155</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.06838303687460001</v>
+        <v>-0.06838307217853407</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1128468061360255</v>
+        <v>0.1124310824188258</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6848646102631869</v>
+        <v>0.6848644808439774</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5957424107014953</v>
+        <v>0.5957420485376483</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8402232093297275</v>
+        <v>0.8402230732291365</v>
       </c>
       <c r="T5" t="n">
-        <v>1232.51772180392</v>
+        <v>1232.517700190867</v>
       </c>
       <c r="U5" t="n">
-        <v>13.16359193078881</v>
+        <v>13.16358934893154</v>
       </c>
       <c r="V5" t="n">
-        <v>2960.333170186414</v>
+        <v>2961.206350867455</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33951,10 +33955,10 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>231.9362371389691</v>
+        <v>231.9053659286043</v>
       </c>
       <c r="D6" t="n">
-        <v>33.13374816270987</v>
+        <v>33.12933798980061</v>
       </c>
       <c r="E6" t="n">
         <v>13.69463807880896</v>
@@ -33966,7 +33970,7 @@
         <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>70.82669960738517</v>
+        <v>70.83266873895568</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -33975,13 +33979,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="K6" t="n">
-        <v>2.165106193336312</v>
+        <v>2.165106208789628</v>
       </c>
       <c r="L6" t="n">
         <v>1.737572926819951</v>
       </c>
       <c r="M6" t="n">
-        <v>2.02787597961992</v>
+        <v>2.028103337331895</v>
       </c>
       <c r="N6" t="n">
         <v>4.202511672332323</v>
@@ -33990,25 +33994,25 @@
         <v>4.609529296781873</v>
       </c>
       <c r="P6" t="n">
-        <v>3.953099797902925</v>
+        <v>3.953460533818736</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.071652642093385</v>
+        <v>4.071652797164063</v>
       </c>
       <c r="R6" t="n">
-        <v>4.293791511379664</v>
+        <v>4.2937918326055</v>
       </c>
       <c r="S6" t="n">
-        <v>4.878164929091728</v>
+        <v>4.878675905976077</v>
       </c>
       <c r="T6" t="n">
-        <v>36.08832703933998</v>
+        <v>36.08832702368397</v>
       </c>
       <c r="U6" t="n">
-        <v>27.26115241316053</v>
+        <v>27.26115988990115</v>
       </c>
       <c r="V6" t="n">
-        <v>52.69022037473084</v>
+        <v>52.69677040618198</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34026,13 +34030,13 @@
         <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>1613.251089258423</v>
+        <v>1613.533775513869</v>
       </c>
       <c r="D7" t="n">
-        <v>73.32959496629195</v>
+        <v>73.34244434153952</v>
       </c>
       <c r="E7" t="n">
-        <v>45.25196089720019</v>
+        <v>45.42917496051172</v>
       </c>
       <c r="F7" t="n">
         <v>50</v>
@@ -34041,7 +34045,7 @@
         <v>45</v>
       </c>
       <c r="H7" t="n">
-        <v>61.83746837221284</v>
+        <v>61.83252607370451</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -34050,40 +34054,40 @@
         <v>0.1739130434782609</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3383509634097989</v>
+        <v>0.3383509656376347</v>
       </c>
       <c r="L7" t="n">
         <v>0.3436109529136453</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3854070263661142</v>
+        <v>0.3853462076566503</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5905843036214745</v>
+        <v>0.5905842879365669</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4872545914471264</v>
+        <v>0.487254582052885</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5334192553471209</v>
+        <v>0.5333010865767651</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.552016965807692</v>
+        <v>2.552016937606695</v>
       </c>
       <c r="R7" t="n">
-        <v>1.443211500274327</v>
+        <v>1.443210825983568</v>
       </c>
       <c r="S7" t="n">
-        <v>2.274902911679122</v>
+        <v>2.274467134668301</v>
       </c>
       <c r="T7" t="n">
-        <v>172.6897857206239</v>
+        <v>172.6898133732471</v>
       </c>
       <c r="U7" t="n">
-        <v>26.97985917888818</v>
+        <v>26.97985938786241</v>
       </c>
       <c r="V7" t="n">
-        <v>336.6213533057638</v>
+        <v>336.5308756919588</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34101,10 +34105,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>4602.22810839565</v>
+        <v>4599.957495518493</v>
       </c>
       <c r="D8" t="n">
-        <v>383.5190090329708</v>
+        <v>383.3297912932077</v>
       </c>
       <c r="E8" t="n">
         <v>188.0718788466943</v>
@@ -34116,7 +34120,7 @@
         <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>60.58455697682687</v>
+        <v>60.58521379295658</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -34125,40 +34129,40 @@
         <v>0.1538461538461539</v>
       </c>
       <c r="K8" t="n">
-        <v>1.703449127764178</v>
+        <v>1.703449136548285</v>
       </c>
       <c r="L8" t="n">
-        <v>1.387121523685535</v>
+        <v>1.38712142664241</v>
       </c>
       <c r="M8" t="n">
-        <v>1.747155495872239</v>
+        <v>1.747380974371368</v>
       </c>
       <c r="N8" t="n">
-        <v>6.48007570960763</v>
+        <v>6.480075704566159</v>
       </c>
       <c r="O8" t="n">
-        <v>4.573525264594901</v>
+        <v>4.573525449804195</v>
       </c>
       <c r="P8" t="n">
-        <v>5.550249939627902</v>
+        <v>5.551013325612136</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.647876629633302</v>
+        <v>6.647876562519857</v>
       </c>
       <c r="R8" t="n">
-        <v>5.196201099431143</v>
+        <v>5.196202186893917</v>
       </c>
       <c r="S8" t="n">
-        <v>8.671752177781782</v>
+        <v>8.672322781009521</v>
       </c>
       <c r="T8" t="n">
-        <v>289.0544938547952</v>
+        <v>289.0545165951464</v>
       </c>
       <c r="U8" t="n">
-        <v>52.07563850050028</v>
+        <v>52.07564197610581</v>
       </c>
       <c r="V8" t="n">
-        <v>350.3037036328843</v>
+        <v>350.4618415633592</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34176,13 +34180,13 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>49.476672</v>
+        <v>49.483311616</v>
       </c>
       <c r="D9" t="n">
-        <v>24.738336</v>
+        <v>24.741655808</v>
       </c>
       <c r="E9" t="n">
-        <v>24.738336</v>
+        <v>24.741655808</v>
       </c>
       <c r="F9" t="n">
         <v>32.5</v>
@@ -34191,7 +34195,7 @@
         <v>32.5</v>
       </c>
       <c r="H9" t="n">
-        <v>56.07208907826298</v>
+        <v>56.07261612100428</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -34206,34 +34210,34 @@
         <v>0.2086888575022282</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7922410938185285</v>
+        <v>0.792254141324386</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1177027172319359</v>
+        <v>0.1177026438643051</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1177027172319359</v>
+        <v>0.1177026438643051</v>
       </c>
       <c r="P9" t="n">
-        <v>0.865976311948242</v>
+        <v>0.8659929061624907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.19678205393756</v>
+        <v>0.1967819478660771</v>
       </c>
       <c r="R9" t="n">
-        <v>0.19678205393756</v>
+        <v>0.1967819478660771</v>
       </c>
       <c r="S9" t="n">
-        <v>0.19678205393756</v>
+        <v>0.1967819478660771</v>
       </c>
       <c r="T9" t="n">
-        <v>11.18996633546931</v>
+        <v>11.18996377409344</v>
       </c>
       <c r="U9" t="n">
-        <v>11.18996633546931</v>
+        <v>11.18996377409344</v>
       </c>
       <c r="V9" t="n">
-        <v>20.90518278636718</v>
+        <v>20.90539524963291</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34251,13 +34255,13 @@
         <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>3374.754110557964</v>
+        <v>3383.339527092048</v>
       </c>
       <c r="D10" t="n">
-        <v>168.7377055278982</v>
+        <v>161.1114060520023</v>
       </c>
       <c r="E10" t="n">
-        <v>60.583256064</v>
+        <v>59.801288704</v>
       </c>
       <c r="F10" t="n">
         <v>63.33333333333334</v>
@@ -34266,7 +34270,7 @@
         <v>60</v>
       </c>
       <c r="H10" t="n">
-        <v>54.82451140604501</v>
+        <v>54.83736706675327</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -34275,40 +34279,40 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5759919721231389</v>
+        <v>0.5759919850081432</v>
       </c>
       <c r="L10" t="n">
         <v>0.4868980908830125</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3523511453505843</v>
+        <v>0.3518195682224436</v>
       </c>
       <c r="N10" t="n">
-        <v>1.063146081442765</v>
+        <v>1.063146061246367</v>
       </c>
       <c r="O10" t="n">
         <v>0.6655675527290204</v>
       </c>
       <c r="P10" t="n">
-        <v>0.609590065819857</v>
+        <v>0.6096063392269743</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.625520550500855</v>
+        <v>6.625520515081964</v>
       </c>
       <c r="R10" t="n">
-        <v>3.558486571925111</v>
+        <v>3.558487044212144</v>
       </c>
       <c r="S10" t="n">
-        <v>7.657745754732154</v>
+        <v>7.651945742866662</v>
       </c>
       <c r="T10" t="n">
-        <v>184.1877557032243</v>
+        <v>184.1877811514381</v>
       </c>
       <c r="U10" t="n">
-        <v>26.37210534198059</v>
+        <v>26.37210225047868</v>
       </c>
       <c r="V10" t="n">
-        <v>296.4551300416551</v>
+        <v>295.8104122665402</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34326,13 +34330,13 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>412.8046345710433</v>
+        <v>412.8972398805376</v>
       </c>
       <c r="D11" t="n">
-        <v>103.2011586427608</v>
+        <v>103.2243099701344</v>
       </c>
       <c r="E11" t="n">
-        <v>77.921517568</v>
+        <v>77.982724096</v>
       </c>
       <c r="F11" t="n">
         <v>38.75</v>
@@ -34341,7 +34345,7 @@
         <v>42.5</v>
       </c>
       <c r="H11" t="n">
-        <v>50.99757695971361</v>
+        <v>50.99457348965004</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -34356,7 +34360,7 @@
         <v>0.02663109810363867</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03694125008453546</v>
+        <v>0.03690337925337711</v>
       </c>
       <c r="N11" t="n">
         <v>0.134685515564421</v>
@@ -34365,25 +34369,25 @@
         <v>0.04481157110862455</v>
       </c>
       <c r="P11" t="n">
-        <v>0.07991811713046142</v>
+        <v>0.07983020669320683</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.136432677134309</v>
+        <v>1.136432617771836</v>
       </c>
       <c r="R11" t="n">
         <v>0.9665450843868131</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9685573540113112</v>
+        <v>0.9684695948998382</v>
       </c>
       <c r="T11" t="n">
-        <v>77.21336555814975</v>
+        <v>77.21336346348038</v>
       </c>
       <c r="U11" t="n">
         <v>69.16442964005671</v>
       </c>
       <c r="V11" t="n">
-        <v>56.18055322329502</v>
+        <v>56.20830643552128</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34401,10 +34405,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>2714.416308224</v>
+        <v>2714.398722048</v>
       </c>
       <c r="D12" t="n">
-        <v>271.4416308224</v>
+        <v>271.4398722048001</v>
       </c>
       <c r="E12" t="n">
         <v>97.74932787200001</v>
@@ -34416,7 +34420,7 @@
         <v>85</v>
       </c>
       <c r="H12" t="n">
-        <v>50.69100698709964</v>
+        <v>50.6905538968224</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
@@ -34425,40 +34429,40 @@
         <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2742595356832438</v>
+        <v>0.2742595265859271</v>
       </c>
       <c r="L12" t="n">
         <v>0.1775795212671972</v>
       </c>
       <c r="M12" t="n">
-        <v>0.20383550068074</v>
+        <v>0.2038305059168966</v>
       </c>
       <c r="N12" t="n">
-        <v>0.225699630520207</v>
+        <v>0.2256996277691782</v>
       </c>
       <c r="O12" t="n">
         <v>0.06560570933348919</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1776750410311326</v>
+        <v>0.177676711367178</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.256263967273778</v>
+        <v>1.256264049824698</v>
       </c>
       <c r="R12" t="n">
         <v>0.3317662417195366</v>
       </c>
       <c r="S12" t="n">
-        <v>5.037664567095729</v>
+        <v>5.037699358189217</v>
       </c>
       <c r="T12" t="n">
-        <v>55.6770967733568</v>
+        <v>55.67712301632721</v>
       </c>
       <c r="U12" t="n">
         <v>7.59271739874022</v>
       </c>
       <c r="V12" t="n">
-        <v>221.4969213297414</v>
+        <v>221.4986524376581</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34476,10 +34480,10 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>1191.413651844698</v>
+        <v>1191.277611885394</v>
       </c>
       <c r="D13" t="n">
-        <v>62.70598167603675</v>
+        <v>62.69882167817867</v>
       </c>
       <c r="E13" t="n">
         <v>44.465762304</v>
@@ -34491,7 +34495,7 @@
         <v>15</v>
       </c>
       <c r="H13" t="n">
-        <v>34.46762295007122</v>
+        <v>34.47105453487822</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
@@ -34500,40 +34504,40 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.06540896904097501</v>
+        <v>-0.06540897484491454</v>
       </c>
       <c r="L13" t="n">
         <v>-0.01907464793006219</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09351373372913574</v>
+        <v>0.09352354624405375</v>
       </c>
       <c r="N13" t="n">
-        <v>0.01532909985003196</v>
+        <v>0.01532910982466073</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01229280570979929</v>
+        <v>0.01229274024237026</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1944066269645373</v>
+        <v>0.1943976984366987</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.017432855145617</v>
+        <v>2.0174331021769</v>
       </c>
       <c r="R13" t="n">
-        <v>1.494203214971247</v>
+        <v>1.494203401687402</v>
       </c>
       <c r="S13" t="n">
-        <v>1.949875247575221</v>
+        <v>1.950012039372698</v>
       </c>
       <c r="T13" t="n">
-        <v>72.54939216523481</v>
+        <v>72.54939997376441</v>
       </c>
       <c r="U13" t="n">
-        <v>12.08738809441496</v>
+        <v>12.08738919527145</v>
       </c>
       <c r="V13" t="n">
-        <v>101.534047028156</v>
+        <v>101.5377223440939</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34551,10 +34555,10 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>2391.690062282029</v>
+        <v>2390.742322898027</v>
       </c>
       <c r="D14" t="n">
-        <v>239.1690062282028</v>
+        <v>239.0742322898028</v>
       </c>
       <c r="E14" t="n">
         <v>52.75461632</v>
@@ -34566,7 +34570,7 @@
         <v>42.5</v>
       </c>
       <c r="H14" t="n">
-        <v>13.69527572470557</v>
+        <v>13.70866486202596</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
@@ -34575,40 +34579,40 @@
         <v>0.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09215426797619192</v>
+        <v>0.09215425490925286</v>
       </c>
       <c r="L14" t="n">
         <v>0.06752794862490252</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.01376948154002711</v>
+        <v>-0.01373580694084171</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1105527726016025</v>
+        <v>0.1105527721504644</v>
       </c>
       <c r="O14" t="n">
         <v>0.1500282396580679</v>
       </c>
       <c r="P14" t="n">
-        <v>0.196978711072755</v>
+        <v>0.1969551111543572</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4710584900344388</v>
+        <v>0.4710585301668816</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3165675856652247</v>
+        <v>0.3165677251425468</v>
       </c>
       <c r="S14" t="n">
-        <v>0.676724970224086</v>
+        <v>0.6767906014861454</v>
       </c>
       <c r="T14" t="n">
-        <v>15.80304839580905</v>
+        <v>15.80304387097797</v>
       </c>
       <c r="U14" t="n">
-        <v>3.304729100978502</v>
+        <v>3.304728893469109</v>
       </c>
       <c r="V14" t="n">
-        <v>2.731639254959604</v>
+        <v>2.732826727705612</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -828,16 +828,16 @@
         <v>28.31139766693115</v>
       </c>
       <c r="AG2" t="n">
-        <v>16.57006565093994</v>
+        <v>16.57006566047669</v>
       </c>
       <c r="AH2" t="n">
         <v>0.3273806638995302</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.267945258800043</v>
+        <v>1.267945257494748</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.7085869340128523</v>
+        <v>0.7085869330294914</v>
       </c>
       <c r="AK2" t="n">
         <v>37.58000183105469</v>
@@ -873,16 +873,16 @@
         <v>2.963599907984868</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.397299247361619</v>
+        <v>2.397299540255927</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.150336364059194</v>
+        <v>5.150335884092616</v>
       </c>
       <c r="AX2" t="n">
         <v>2.988501758947474</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.305728596673119</v>
+        <v>5.305727083094468</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1024,16 +1024,16 @@
         <v>464.1994812011719</v>
       </c>
       <c r="AG3" t="n">
-        <v>430.0756800842285</v>
+        <v>430.075680847168</v>
       </c>
       <c r="AH3" t="n">
         <v>0.06372371959912981</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1481235085940971</v>
+        <v>0.1481235065573654</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.07934371250720429</v>
+        <v>0.07934371059248568</v>
       </c>
       <c r="AK3" t="n">
         <v>537.6464233398438</v>
@@ -1066,10 +1066,10 @@
         <v>0.3467347461958088</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.2982979009536684</v>
+        <v>0.2982980051291018</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.02086211812844208</v>
+        <v>-0.0208621773806108</v>
       </c>
       <c r="AW3" t="n">
         <v>0.7323827606095734</v>
@@ -1078,7 +1078,7 @@
         <v>0.05068852437725657</v>
       </c>
       <c r="AY3" t="n">
-        <v>8366.131176191575</v>
+        <v>8366.130648014247</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1416,28 +1416,28 @@
         <v>345.3990576171875</v>
       </c>
       <c r="AG5" t="n">
-        <v>337.0870283508301</v>
+        <v>337.0870294189453</v>
       </c>
       <c r="AH5" t="n">
         <v>0.01198888889941285</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.03694292318223269</v>
+        <v>0.03694291989650988</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.02465840737634828</v>
+        <v>0.024658404129551</v>
       </c>
       <c r="AK5" t="n">
         <v>402.1211853027344</v>
       </c>
       <c r="AL5" t="n">
-        <v>235.9563751220703</v>
+        <v>235.9563446044922</v>
       </c>
       <c r="AM5" t="n">
         <v>-0.1307595289172021</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.4813755651403353</v>
+        <v>0.4813757567350756</v>
       </c>
       <c r="AO5" t="n">
         <v>52.53576155289754</v>
@@ -1464,13 +1464,13 @@
         <v>0.3905052113320255</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.479167322782876</v>
+        <v>1.479167054474144</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.111280179873726</v>
+        <v>0.1112802876939802</v>
       </c>
       <c r="AY5" t="n">
-        <v>139.5275291037729</v>
+        <v>139.5275425737254</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -1612,25 +1612,25 @@
         <v>607.3789965820313</v>
       </c>
       <c r="AG6" t="n">
-        <v>623.5469723510743</v>
+        <v>623.54697265625</v>
       </c>
       <c r="AH6" t="n">
         <v>0.09610309830673458</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0676821947988937</v>
+        <v>0.06768219427634969</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.02592904221486614</v>
+        <v>-0.02592904269159491</v>
       </c>
       <c r="AK6" t="n">
-        <v>777.7011108398438</v>
+        <v>777.7010498046875</v>
       </c>
       <c r="AL6" t="n">
         <v>525.233154296875</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.1439513320470214</v>
+        <v>-0.1439512648630255</v>
       </c>
       <c r="AN6" t="n">
         <v>0.267532322652468</v>
@@ -1657,16 +1657,16 @@
         <v>0.1224725158757085</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.1439513320470214</v>
+        <v>-0.1439512648630255</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.7837409253462835</v>
+        <v>0.7837410711949553</v>
       </c>
       <c r="AX6" t="n">
         <v>0.0254109508361251</v>
       </c>
       <c r="AY6" t="n">
-        <v>16.56726196114298</v>
+        <v>16.56725842453464</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
@@ -2240,7 +2240,7 @@
         <v>-0.3196119836529967</v>
       </c>
       <c r="AY9" t="n">
-        <v>594.7705077198035</v>
+        <v>594.7704572276324</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
@@ -2768,16 +2768,16 @@
         <v>141.0024000549316</v>
       </c>
       <c r="AG12" t="n">
-        <v>165.4722225570679</v>
+        <v>165.47222240448</v>
       </c>
       <c r="AH12" t="n">
         <v>0.04686161762385432</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.1079469512809379</v>
+        <v>-0.1079469504583437</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.1478787322971813</v>
+        <v>-0.1478787315114096</v>
       </c>
       <c r="AK12" t="n">
         <v>324.4519958496094</v>
@@ -2819,10 +2819,10 @@
         <v>0.77637961003919</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.2384969078253042</v>
+        <v>-0.2384968478810358</v>
       </c>
       <c r="AY12" t="n">
-        <v>2937.236214308951</v>
+        <v>2937.237085829986</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
@@ -4710,16 +4710,16 @@
         <v>379.7551989746094</v>
       </c>
       <c r="AG22" t="n">
-        <v>368.386103515625</v>
+        <v>368.3861039733887</v>
       </c>
       <c r="AH22" t="n">
         <v>-0.05831444489197768</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.02925223851068914</v>
+        <v>-0.02925223971695912</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.03086190100681185</v>
+        <v>0.03086189972584297</v>
       </c>
       <c r="AK22" t="n">
         <v>480.8090515136719</v>
@@ -4764,7 +4764,7 @@
         <v>0.03252787358891807</v>
       </c>
       <c r="AY22" t="n">
-        <v>313.91089297659</v>
+        <v>313.9108599186503</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
@@ -4948,19 +4948,19 @@
         <v>-0.08335309558511705</v>
       </c>
       <c r="AU23" t="n">
-        <v>-0.03669485908391112</v>
+        <v>-0.03669492076762226</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.1112544390639518</v>
+        <v>-0.1112543340546666</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.104489421239106</v>
+        <v>1.10448927403964</v>
       </c>
       <c r="AX23" t="n">
         <v>-0.196479747843647</v>
       </c>
       <c r="AY23" t="n">
-        <v>159.0266626200259</v>
+        <v>159.0266360221218</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5102,16 +5102,16 @@
         <v>320.0252856445313</v>
       </c>
       <c r="AG24" t="n">
-        <v>285.9436472320556</v>
+        <v>285.9436474609375</v>
       </c>
       <c r="AH24" t="n">
         <v>0.05032327119354441</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1755113573480738</v>
+        <v>0.1755113564071429</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1191900528037153</v>
+        <v>0.1191900519078664</v>
       </c>
       <c r="AK24" t="n">
         <v>339.7869262695312</v>
@@ -5150,13 +5150,13 @@
         <v>0.4182430347852557</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.304363271644069</v>
+        <v>1.304363030589909</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2436623714806181</v>
       </c>
       <c r="AY24" t="n">
-        <v>3424.621195346096</v>
+        <v>3424.620415008259</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5686,16 +5686,16 @@
         <v>214.0669781494141</v>
       </c>
       <c r="AG27" t="n">
-        <v>198.0213689422608</v>
+        <v>198.0213688659668</v>
       </c>
       <c r="AH27" t="n">
         <v>0.03831990433069654</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.1224546394145505</v>
+        <v>0.1224546398470112</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.08102968529538801</v>
+        <v>0.08102968571188862</v>
       </c>
       <c r="AK27" t="n">
         <v>235.202392578125</v>
@@ -5728,19 +5728,19 @@
         <v>0.06646886015332831</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.2899713750733246</v>
+        <v>0.28997148930838</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.2641993983923572</v>
+        <v>0.2641995081084689</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.078051401103753</v>
+        <v>9.078053144244413</v>
       </c>
       <c r="AX27" t="n">
         <v>0.1797198981727677</v>
       </c>
       <c r="AY27" t="n">
-        <v>5923.497863899439</v>
+        <v>5923.501393567516</v>
       </c>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
@@ -6124,13 +6124,13 @@
         <v>2.552502438935519</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.144161951313712</v>
+        <v>1.144162112803648</v>
       </c>
       <c r="AX29" t="n">
         <v>1.757744934701161</v>
       </c>
       <c r="AY29" t="n">
-        <v>597.3479742313801</v>
+        <v>597.3479251069067</v>
       </c>
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
@@ -6272,16 +6272,16 @@
         <v>167.8194256591797</v>
       </c>
       <c r="AG30" t="n">
-        <v>166.991922416687</v>
+        <v>166.9919225692749</v>
       </c>
       <c r="AH30" t="n">
         <v>0.0589954084435389</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.06424310019766621</v>
+        <v>0.06424309922522031</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.004955348920577585</v>
+        <v>0.00495534800230546</v>
       </c>
       <c r="AK30" t="n">
         <v>248.7425079345703</v>
@@ -6326,7 +6326,7 @@
         <v>0.04346581947495132</v>
       </c>
       <c r="AY30" t="n">
-        <v>528.6277348911657</v>
+        <v>528.6274996978084</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6653,19 +6653,19 @@
         <v>832</v>
       </c>
       <c r="AF32" t="n">
-        <v>797.34</v>
+        <v>797.6</v>
       </c>
       <c r="AG32" t="n">
-        <v>496.7676652526856</v>
+        <v>500.2413401794433</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.04346953620789118</v>
+        <v>0.04312938816449341</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.6748272043366497</v>
+        <v>0.663197207375045</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.6050561575790676</v>
+        <v>0.594430399762423</v>
       </c>
       <c r="AK32" t="n">
         <v>914</v>
@@ -6680,41 +6680,41 @@
         <v>7.130968869483265</v>
       </c>
       <c r="AO32" t="n">
-        <v>51.89504373177842</v>
+        <v>42.70833333333334</v>
       </c>
       <c r="AP32" t="n">
-        <v>16244373</v>
+        <v>1787063</v>
       </c>
       <c r="AQ32" t="n">
-        <v>14736743.7</v>
+        <v>14706765.14</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.102304099921342</v>
+        <v>0.1215129896335585</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.02589395807644879</v>
+        <v>0.04785894206549113</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.1277730840622933</v>
+        <v>0.026384617145363</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.408740777809349</v>
+        <v>1.600387859975148</v>
       </c>
       <c r="AV32" t="n">
-        <v>7.052408783787776</v>
+        <v>7.013695280019565</v>
       </c>
       <c r="AW32" t="n">
-        <v>3.83867135288575</v>
+        <v>4.007311971256832</v>
       </c>
       <c r="AX32" t="n">
         <v>4.342463520013043</v>
       </c>
       <c r="AY32" t="n">
-        <v>35.40840266556269</v>
+        <v>35.4083965878533</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
@@ -6725,12 +6725,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unimicron</t>
+          <t>ASE Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6740,16 +6740,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IC substrates / PCBs</t>
+          <t>OSAT / advanced packaging</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IC substrates/PCBs</t>
+          <t>OSAT, advanced packaging</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6758,9 +6758,13 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>SOXX</t>
+        </is>
+      </c>
       <c r="K33" s="1" t="n">
         <v>46195</v>
       </c>
@@ -6798,7 +6802,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Unimicron Technology Corp.</t>
+          <t>ASE Technology Holding Co., Ltd.</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -6808,27 +6812,27 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X33" t="n">
-        <v>1609222193152</v>
+        <v>108390596608</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>0.03148317337036133</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>50663421298.4375</v>
+        <v>108390596608</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -6836,93 +6840,93 @@
         </is>
       </c>
       <c r="AC33" s="2" t="n">
-        <v>36529</v>
+        <v>36801</v>
       </c>
       <c r="AD33" t="n">
-        <v>26.7</v>
+        <v>26</v>
       </c>
       <c r="AE33" t="n">
-        <v>981</v>
+        <v>41.63000106811523</v>
       </c>
       <c r="AF33" t="n">
-        <v>955.54</v>
+        <v>38.03420017242431</v>
       </c>
       <c r="AG33" t="n">
-        <v>670.0693196105957</v>
+        <v>29.0356227016449</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.0266446197961363</v>
+        <v>0.09454125180468398</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.4640276330963768</v>
+        <v>0.4337560966363174</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.4260315642496553</v>
+        <v>0.3099150847648133</v>
       </c>
       <c r="AK33" t="n">
-        <v>1180</v>
+        <v>44.67063140869141</v>
       </c>
       <c r="AL33" t="n">
-        <v>133.2271881103516</v>
+        <v>10.96964931488037</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.1686440677966101</v>
+        <v>-0.06806777170345901</v>
       </c>
       <c r="AN33" t="n">
-        <v>6.363361892674951</v>
+        <v>2.795016583770274</v>
       </c>
       <c r="AO33" t="n">
-        <v>47.07792207792208</v>
+        <v>63.32181355810051</v>
       </c>
       <c r="AP33" t="n">
-        <v>13722988</v>
+        <v>19273900</v>
       </c>
       <c r="AQ33" t="n">
-        <v>23115218.22</v>
+        <v>7810192</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.5936776313072593</v>
+        <v>2.467788243874158</v>
       </c>
       <c r="AS33" t="n">
-        <v>-0.09585253456221199</v>
+        <v>0.1402356335788246</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.05586331241976428</v>
+        <v>-0.03602056667536446</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.969957502896527</v>
+        <v>0.9731948445504395</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.363361892674951</v>
+        <v>2.665979026123622</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.639169609394931</v>
+        <v>4.701337591160438</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.48862452877546</v>
+        <v>1.493996430309914</v>
       </c>
       <c r="AY33" t="n">
-        <v>133.762426463219</v>
+        <v>39.53451770439582</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>Strong momentum</t>
+          <t>Positive momentum</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>4062.T</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ASE Technology</t>
+          <t>Ibiden</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6932,16 +6936,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OSAT / advanced packaging</t>
+          <t>IC substrates / PCBs</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OSAT, advanced packaging</t>
+          <t>IC substrates</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -6950,13 +6954,9 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>SOXX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" s="1" t="n">
         <v>46195</v>
       </c>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>ASE Technology Holding Co., Ltd.</t>
+          <t>Ibiden Co.,Ltd.</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -7004,27 +7004,27 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="X34" t="n">
-        <v>108390596608</v>
+        <v>5496825184256</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>1</v>
+        <v>0.006375315133482218</v>
       </c>
       <c r="AA34" t="n">
-        <v>108390596608</v>
+        <v>35043992783.29346</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -7032,77 +7032,77 @@
         </is>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>36801</v>
+        <v>36892</v>
       </c>
       <c r="AD34" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="AE34" t="n">
-        <v>41.63000106811523</v>
+        <v>19555</v>
       </c>
       <c r="AF34" t="n">
-        <v>38.03420017242431</v>
+        <v>18995.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>29.0356227016449</v>
+        <v>13600.07851806641</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.09454125180468398</v>
+        <v>0.02946518349275884</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.4337560966363174</v>
+        <v>0.4378593457400299</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.3099150847648133</v>
+        <v>0.396705171574308</v>
       </c>
       <c r="AK34" t="n">
-        <v>44.67063140869141</v>
+        <v>26425</v>
       </c>
       <c r="AL34" t="n">
-        <v>10.96964931488037</v>
+        <v>3580.43896484375</v>
       </c>
       <c r="AM34" t="n">
-        <v>-0.06806777170345901</v>
+        <v>-0.2599810785241249</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.795016583770274</v>
+        <v>4.461620821360204</v>
       </c>
       <c r="AO34" t="n">
-        <v>63.32181355810051</v>
+        <v>45.22292993630574</v>
       </c>
       <c r="AP34" t="n">
-        <v>19273900</v>
+        <v>9800900</v>
       </c>
       <c r="AQ34" t="n">
-        <v>7810192</v>
+        <v>8263504</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.467788243874158</v>
+        <v>1.186046500370787</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.1402356335788246</v>
+        <v>0.01902032308494017</v>
       </c>
       <c r="AT34" t="n">
-        <v>-0.03602056667536446</v>
+        <v>-0.2599810785241249</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.9731948445504395</v>
+        <v>1.309932528069085</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.665979026123622</v>
+        <v>4.409763299621911</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.701337963481163</v>
+        <v>6.019235900868899</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.493996430309914</v>
+        <v>1.736873138239476</v>
       </c>
       <c r="AY34" t="n">
-        <v>39.53451299946061</v>
+        <v>27.25392570058711</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
@@ -7113,12 +7113,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4062.T</t>
+          <t>ATS.VI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ibiden</t>
+          <t>AT&amp;S</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7133,11 +7133,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IC substrates</t>
+          <t>Advanced substrates/PCBs</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Ibiden Co.,Ltd.</t>
+          <t>AT &amp; S Austria Technologie &amp; Systemtechnik Aktiengesellschaft</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -7201,96 +7201,96 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X35" t="n">
-        <v>5496825184256</v>
+        <v>6829830144</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>0.006375315133482218</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA35" t="n">
-        <v>35043992783.29346</v>
+        <v>7847673827.365723</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC35" s="2" t="n">
-        <v>36892</v>
+        <v>39388</v>
       </c>
       <c r="AD35" t="n">
-        <v>25.7</v>
+        <v>18.9</v>
       </c>
       <c r="AE35" t="n">
-        <v>19555</v>
+        <v>175.8000030517578</v>
       </c>
       <c r="AF35" t="n">
-        <v>18995.3</v>
+        <v>156.0280001831055</v>
       </c>
       <c r="AG35" t="n">
-        <v>13600.07851806641</v>
+        <v>101.9550001621246</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.02946518349275884</v>
+        <v>0.1267208632133274</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.4378593457400299</v>
+        <v>0.7242901551881507</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.396705171574308</v>
+        <v>0.5303614333283917</v>
       </c>
       <c r="AK35" t="n">
-        <v>26425</v>
+        <v>239</v>
       </c>
       <c r="AL35" t="n">
-        <v>3580.438720703125</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="AM35" t="n">
-        <v>-0.2599810785241249</v>
+        <v>-0.2644351336746535</v>
       </c>
       <c r="AN35" t="n">
-        <v>4.46162119377365</v>
+        <v>7.253521565666434</v>
       </c>
       <c r="AO35" t="n">
-        <v>45.22292993630574</v>
+        <v>61.48936494867852</v>
       </c>
       <c r="AP35" t="n">
-        <v>9800900</v>
+        <v>370066</v>
       </c>
       <c r="AQ35" t="n">
-        <v>8263504</v>
+        <v>131079.88</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.186046500370787</v>
+        <v>2.823209786276887</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.01902032308494017</v>
+        <v>0.2293706507115931</v>
       </c>
       <c r="AT35" t="n">
-        <v>-0.2599810785241249</v>
+        <v>-0.2116591791400995</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.309932528069085</v>
+        <v>2.413592292267142</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.409762934246995</v>
+        <v>7.253521565666434</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.019234670623278</v>
+        <v>4.826624695337522</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.736873138239476</v>
+        <v>4.359756315272175</v>
       </c>
       <c r="AY35" t="n">
-        <v>27.25392819219602</v>
+        <v>14.32039870674789</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7305,12 +7305,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ATS.VI</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AT&amp;S</t>
+          <t>Unimicron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Advanced substrates/PCBs</t>
+          <t>IC substrates/PCBs</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>AT &amp; S Austria Technologie &amp; Systemtechnik Aktiengesellschaft</t>
+          <t>Unimicron Technology Corp.</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -7393,100 +7393,100 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X36" t="n">
-        <v>6829830144</v>
+        <v>1609222193152</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>1.148897051811218</v>
+        <v>0.03148317337036133</v>
       </c>
       <c r="AA36" t="n">
-        <v>7846771716.812988</v>
+        <v>50663421298.4375</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Mid cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>39388</v>
+        <v>36529</v>
       </c>
       <c r="AD36" t="n">
-        <v>18.9</v>
+        <v>26.7</v>
       </c>
       <c r="AE36" t="n">
-        <v>175.8000030517578</v>
+        <v>981</v>
       </c>
       <c r="AF36" t="n">
-        <v>156.0280001831055</v>
+        <v>957.1</v>
       </c>
       <c r="AG36" t="n">
-        <v>101.9550001621246</v>
+        <v>674.0961178588867</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.1267208632133274</v>
+        <v>0.02497126737018074</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.7242901551881507</v>
+        <v>0.4552820792321484</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.5303614333283917</v>
+        <v>0.4198271947330166</v>
       </c>
       <c r="AK36" t="n">
-        <v>239</v>
+        <v>1180</v>
       </c>
       <c r="AL36" t="n">
-        <v>21.29999923706055</v>
+        <v>134.7241363525391</v>
       </c>
       <c r="AM36" t="n">
-        <v>-0.2644351336746535</v>
+        <v>-0.1686440677966101</v>
       </c>
       <c r="AN36" t="n">
-        <v>7.253521565666434</v>
+        <v>6.281546028493147</v>
       </c>
       <c r="AO36" t="n">
-        <v>61.48936494867852</v>
+        <v>51.78571428571429</v>
       </c>
       <c r="AP36" t="n">
-        <v>370066</v>
+        <v>2148719</v>
       </c>
       <c r="AQ36" t="n">
-        <v>131079.88</v>
+        <v>22506930.18</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.823209786276887</v>
+        <v>0.09546921693965107</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.2293706507115931</v>
+        <v>-0.08744186046511626</v>
       </c>
       <c r="AT36" t="n">
-        <v>-0.2116591791400995</v>
+        <v>-0.03626592187212374</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.413592292267142</v>
+        <v>1.136975570115509</v>
       </c>
       <c r="AV36" t="n">
-        <v>7.253521565666434</v>
+        <v>6.281546028493147</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.826624695337522</v>
+        <v>6.719864572071088</v>
       </c>
       <c r="AX36" t="n">
-        <v>4.359756315272175</v>
+        <v>3.48862452877546</v>
       </c>
       <c r="AY36" t="n">
-        <v>14.32039870674789</v>
+        <v>133.7623999806631</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
@@ -7624,28 +7624,28 @@
         <v>54.17536872863769</v>
       </c>
       <c r="AG37" t="n">
-        <v>56.64354764938354</v>
+        <v>56.64354753494263</v>
       </c>
       <c r="AH37" t="n">
         <v>-0.07153379077101851</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.1119906622302114</v>
+        <v>-0.1119906604361041</v>
       </c>
       <c r="AJ37" t="n">
-        <v>-0.04357387598713924</v>
+        <v>-0.04357387405480473</v>
       </c>
       <c r="AK37" t="n">
         <v>93.37815856933594</v>
       </c>
       <c r="AL37" t="n">
-        <v>28.06438255310059</v>
+        <v>28.06438446044922</v>
       </c>
       <c r="AM37" t="n">
         <v>-0.4613301439253445</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.7923073540594729</v>
+        <v>0.7923072322483216</v>
       </c>
       <c r="AO37" t="n">
         <v>55.75216562328513</v>
@@ -7669,7 +7669,7 @@
         <v>0.101271864716169</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.7369891070674996</v>
+        <v>0.736989221475481</v>
       </c>
       <c r="AW37" t="n">
         <v>0.8581346746559235</v>
@@ -7678,7 +7678,7 @@
         <v>0.1776779586719965</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.074309290754759</v>
+        <v>3.074309605486201</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7864,13 +7864,13 @@
         <v>0.2001433888315194</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.699994864095913</v>
+        <v>1.699994673091592</v>
       </c>
       <c r="AX38" t="n">
         <v>0.006416760786752462</v>
       </c>
       <c r="AY38" t="n">
-        <v>2.994117428525532</v>
+        <v>2.994118682476039</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8056,13 +8056,13 @@
         <v>0.1546546127274884</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.840197013518944</v>
+        <v>0.8401968678020388</v>
       </c>
       <c r="AX39" t="n">
         <v>0.1304393635973777</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.9276338496486365</v>
+        <v>0.9276343293288245</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8396,16 +8396,16 @@
         <v>186.4015063476562</v>
       </c>
       <c r="AG41" t="n">
-        <v>177.6265552520752</v>
+        <v>177.626555557251</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.02296929522920976</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.02529711764513776</v>
+        <v>0.02529711588360017</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.04940112182622824</v>
+        <v>0.04940112002327823</v>
       </c>
       <c r="AK41" t="n">
         <v>201.1799774169922</v>
@@ -8441,16 +8441,16 @@
         <v>0.06515505296942559</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.09322988664512577</v>
+        <v>0.09322998678002636</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.4058423523192587</v>
+        <v>0.4058418555476284</v>
       </c>
       <c r="AX41" t="n">
         <v>0.198788818537621</v>
       </c>
       <c r="AY41" t="n">
-        <v>34.97148074860115</v>
+        <v>34.9714773607131</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8592,28 +8592,28 @@
         <v>1041.055670166016</v>
       </c>
       <c r="AG42" t="n">
-        <v>965.2767684936523</v>
+        <v>965.2767672729492</v>
       </c>
       <c r="AH42" t="n">
         <v>-0.01893812586161026</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.05807998305947537</v>
+        <v>0.05807998439753881</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.07850484352857579</v>
+        <v>0.07850484489246878</v>
       </c>
       <c r="AK42" t="n">
         <v>1110.633178710938</v>
       </c>
       <c r="AL42" t="n">
-        <v>715.1827392578125</v>
+        <v>715.1826782226562</v>
       </c>
       <c r="AM42" t="n">
         <v>-0.08039841917842516</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.4280826015395363</v>
+        <v>0.4280827234150337</v>
       </c>
       <c r="AO42" t="n">
         <v>43.10477996641221</v>
@@ -8646,7 +8646,7 @@
         <v>0.3570252973879491</v>
       </c>
       <c r="AY42" t="n">
-        <v>2.322199862852532</v>
+        <v>2.322199203282168</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8788,16 +8788,16 @@
         <v>120.1711859130859</v>
       </c>
       <c r="AG43" t="n">
-        <v>109.2199789047241</v>
+        <v>109.2199789810181</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.04852402454788729</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.04687802986697931</v>
+        <v>0.0468780291356985</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.1002674338356619</v>
+        <v>0.1002674330670867</v>
       </c>
       <c r="AK43" t="n">
         <v>132.0340881347656</v>
@@ -8842,7 +8842,7 @@
         <v>0.4051186399647249</v>
       </c>
       <c r="AY43" t="n">
-        <v>99.01007323028209</v>
+        <v>99.01008365824461</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -8980,28 +8980,28 @@
         <v>2.18717146396637</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.172941920757294</v>
+        <v>2.172941918373108</v>
       </c>
       <c r="AH44" t="n">
         <v>-0.01699517811535856</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.01055795609201859</v>
+        <v>-0.01055795500638734</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.006548515205651029</v>
+        <v>0.006548516310051822</v>
       </c>
       <c r="AK44" t="n">
         <v>2.30321192741394</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.061682462692261</v>
+        <v>2.061682224273682</v>
       </c>
       <c r="AM44" t="n">
         <v>-0.06652094417491838</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.04283765044974031</v>
+        <v>0.04283777104634234</v>
       </c>
       <c r="AO44" t="n">
         <v>44.00447737027243</v>
@@ -9028,13 +9028,13 @@
         <v>-0.03228197097925689</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.08205391386505489</v>
+        <v>0.08205378402778818</v>
       </c>
       <c r="AX44" t="n">
         <v>0.01956007801238013</v>
       </c>
       <c r="AY44" t="n">
-        <v>2.995902072471015</v>
+        <v>2.995900744488344</v>
       </c>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
@@ -9924,16 +9924,16 @@
         <v>14.72013038635254</v>
       </c>
       <c r="AG49" t="n">
-        <v>14.37083113193512</v>
+        <v>14.37083113670349</v>
       </c>
       <c r="AH49" t="n">
         <v>0.007463897021957155</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.0319514429997414</v>
+        <v>0.03195144265733063</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.02430612754478756</v>
+        <v>0.02430612720491343</v>
       </c>
       <c r="AK49" t="n">
         <v>16.86722755432129</v>
@@ -9966,7 +9966,7 @@
         <v>0.02442809001095814</v>
       </c>
       <c r="AU49" t="n">
-        <v>0.0775120241844578</v>
+        <v>0.07751194952184925</v>
       </c>
       <c r="AV49" t="n">
         <v>0.2021814689709123</v>
@@ -9975,10 +9975,10 @@
         <v>-0.2397455933461431</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.03730185936626884</v>
+        <v>0.03730192856040304</v>
       </c>
       <c r="AY49" t="n">
-        <v>6.520613531572804</v>
+        <v>6.52061535016612</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10120,28 +10120,28 @@
         <v>67.34740325927734</v>
       </c>
       <c r="AG50" t="n">
-        <v>63.07638687133789</v>
+        <v>63.07638675689697</v>
       </c>
       <c r="AH50" t="n">
         <v>-0.05593981721490771</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.007984207477578886</v>
+        <v>0.007984209306387546</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.06771181102448676</v>
+        <v>0.06771181296166051</v>
       </c>
       <c r="AK50" t="n">
         <v>70.97299957275391</v>
       </c>
       <c r="AL50" t="n">
-        <v>55.35893249511719</v>
+        <v>55.35892868041992</v>
       </c>
       <c r="AM50" t="n">
         <v>-0.1041663419357204</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.1485048386123164</v>
+        <v>0.1485049177539901</v>
       </c>
       <c r="AO50" t="n">
         <v>40.53429930562957</v>
@@ -10174,7 +10174,7 @@
         <v>0.1066282367173335</v>
       </c>
       <c r="AY50" t="n">
-        <v>172.7868489532951</v>
+        <v>172.7867215426892</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10368,7 +10368,7 @@
         <v>0.3863182662922036</v>
       </c>
       <c r="AY51" t="n">
-        <v>6.194694004545028</v>
+        <v>6.194695684487933</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10510,16 +10510,16 @@
         <v>108.1698550415039</v>
       </c>
       <c r="AG52" t="n">
-        <v>104.9674143600464</v>
+        <v>104.9674142456055</v>
       </c>
       <c r="AH52" t="n">
         <v>-0.05694611408058148</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.02817457438431104</v>
+        <v>-0.02817457332477646</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.03050890317706489</v>
+        <v>0.03050890430057929</v>
       </c>
       <c r="AK52" t="n">
         <v>116.6635665893555</v>
@@ -10564,7 +10564,7 @@
         <v>0.1065153846516704</v>
       </c>
       <c r="AY52" t="n">
-        <v>189.9311520839121</v>
+        <v>189.9309816796186</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10706,28 +10706,28 @@
         <v>122.7165016174316</v>
       </c>
       <c r="AG53" t="n">
-        <v>122.3165890884399</v>
+        <v>122.3165891647339</v>
       </c>
       <c r="AH53" t="n">
         <v>-0.0422641027879338</v>
       </c>
       <c r="AI53" t="n">
-        <v>-0.03913279747918874</v>
+        <v>-0.03913279807852155</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.003269487254116799</v>
+        <v>0.003269486628336038</v>
       </c>
       <c r="AK53" t="n">
         <v>131.1634063720703</v>
       </c>
       <c r="AL53" t="n">
-        <v>111.0921020507812</v>
+        <v>111.0920944213867</v>
       </c>
       <c r="AM53" t="n">
         <v>-0.1039421586391226</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.05795098490055395</v>
+        <v>0.05795105755671814</v>
       </c>
       <c r="AO53" t="n">
         <v>35.53187552046387</v>
@@ -10754,13 +10754,13 @@
         <v>0.01050532770612511</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.3871264220846842</v>
+        <v>0.3871261722784065</v>
       </c>
       <c r="AX53" t="n">
         <v>0.02696192267819142</v>
       </c>
       <c r="AY53" t="n">
-        <v>159.1471742577596</v>
+        <v>159.1472783121003</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10950,13 +10950,13 @@
         <v>-0.03396549905406976</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.5478366931104672</v>
+        <v>0.5478365862437058</v>
       </c>
       <c r="AX54" t="n">
         <v>0.005081323138168559</v>
       </c>
       <c r="AY54" t="n">
-        <v>316.9534363005037</v>
+        <v>316.9535772195395</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11094,16 +11094,16 @@
         <v>163.7036489868164</v>
       </c>
       <c r="AG55" t="n">
-        <v>191.1090460968018</v>
+        <v>191.1090460205078</v>
       </c>
       <c r="AH55" t="n">
         <v>-0.09885940120772008</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.2280846601173543</v>
+        <v>-0.2280846598091927</v>
       </c>
       <c r="AJ55" t="n">
-        <v>-0.1434018832164743</v>
+        <v>-0.1434018828745058</v>
       </c>
       <c r="AK55" t="n">
         <v>237.7264404296875</v>
@@ -11139,16 +11139,16 @@
         <v>-0.2593222600993386</v>
       </c>
       <c r="AV55" t="n">
-        <v>-0.1474722497103678</v>
+        <v>-0.1474721745331514</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.736633963246867</v>
+        <v>1.736633769585694</v>
       </c>
       <c r="AX55" t="n">
         <v>-0.1852924790992457</v>
       </c>
       <c r="AY55" t="n">
-        <v>9.427299710065052</v>
+        <v>9.427296195571575</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11334,13 +11334,13 @@
         <v>0.1112261928027645</v>
       </c>
       <c r="AW56" t="n">
-        <v>2.792156410125644</v>
+        <v>2.792156110752919</v>
       </c>
       <c r="AX56" t="n">
         <v>-0.07041391014529907</v>
       </c>
       <c r="AY56" t="n">
-        <v>14.312136812948</v>
+        <v>14.31214169397851</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11482,16 +11482,16 @@
         <v>270.9358029174805</v>
       </c>
       <c r="AG57" t="n">
-        <v>292.0293510437012</v>
+        <v>292.029352645874</v>
       </c>
       <c r="AH57" t="n">
         <v>-0.05988797356750675</v>
       </c>
       <c r="AI57" t="n">
-        <v>-0.1277931283155482</v>
+        <v>-0.1277931331007733</v>
       </c>
       <c r="AJ57" t="n">
-        <v>-0.07223091805954851</v>
+        <v>-0.07223092314960677</v>
       </c>
       <c r="AK57" t="n">
         <v>401.7044372558594</v>
@@ -11527,14 +11527,14 @@
         <v>-0.09394688502828941</v>
       </c>
       <c r="AV57" t="n">
-        <v>-0.206303375746426</v>
+        <v>-0.2063033002696805</v>
       </c>
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="n">
-        <v>-0.3014599449174981</v>
+        <v>-0.3014598864537408</v>
       </c>
       <c r="AY57" t="n">
-        <v>5.300025447042835</v>
+        <v>5.300027824752556</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11649,10 +11649,10 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>1.148897051811218</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA58" t="n">
-        <v>137050747398.8027</v>
+        <v>137066503550.498</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
@@ -11883,13 +11883,13 @@
         <v>49.3515510559082</v>
       </c>
       <c r="AL59" t="n">
-        <v>41.58327102661133</v>
+        <v>41.58327484130859</v>
       </c>
       <c r="AM59" t="n">
         <v>-0.1475445291037567</v>
       </c>
       <c r="AN59" t="n">
-        <v>0.01170491537092899</v>
+        <v>0.01170482256082717</v>
       </c>
       <c r="AO59" t="n">
         <v>34.11495948795117</v>
@@ -11913,16 +11913,16 @@
         <v>-0.07687369128047095</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.01170491537092899</v>
+        <v>0.01170482256082717</v>
       </c>
       <c r="AW59" t="n">
-        <v>0.3936435190301359</v>
+        <v>0.3936436951429769</v>
       </c>
       <c r="AX59" t="n">
         <v>-0.01554952500729068</v>
       </c>
       <c r="AY59" t="n">
-        <v>172.2100782800356</v>
+        <v>172.2101420395983</v>
       </c>
       <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
@@ -12114,7 +12114,7 @@
         <v>-0.4670458872383888</v>
       </c>
       <c r="AY60" t="n">
-        <v>-0.9332323472251607</v>
+        <v>-0.9332323322370795</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12256,28 +12256,28 @@
         <v>85.01782882690429</v>
       </c>
       <c r="AG61" t="n">
-        <v>86.49730278015137</v>
+        <v>86.49730297088622</v>
       </c>
       <c r="AH61" t="n">
         <v>-0.05349263406220961</v>
       </c>
       <c r="AI61" t="n">
-        <v>-0.06968195961864532</v>
+        <v>-0.06968196167008589</v>
       </c>
       <c r="AJ61" t="n">
-        <v>-0.01710427846527696</v>
+        <v>-0.01710428063265623</v>
       </c>
       <c r="AK61" t="n">
         <v>96.44304656982422</v>
       </c>
       <c r="AL61" t="n">
-        <v>68.81240844726562</v>
+        <v>68.81240081787109</v>
       </c>
       <c r="AM61" t="n">
         <v>-0.1656215343379546</v>
       </c>
       <c r="AN61" t="n">
-        <v>0.1694112012133873</v>
+        <v>0.1694113308687881</v>
       </c>
       <c r="AO61" t="n">
         <v>41.87428050131411</v>
@@ -12298,19 +12298,19 @@
         <v>-0.05814215463598726</v>
       </c>
       <c r="AU61" t="n">
-        <v>-0.08749762625203039</v>
+        <v>-0.08749770519692224</v>
       </c>
       <c r="AV61" t="n">
-        <v>0.1694112012133873</v>
+        <v>0.1694113308687881</v>
       </c>
       <c r="AW61" t="n">
-        <v>0.08824071999078842</v>
+        <v>0.08824083227173252</v>
       </c>
       <c r="AX61" t="n">
         <v>0.01601172279278651</v>
       </c>
       <c r="AY61" t="n">
-        <v>232.3071249988659</v>
+        <v>232.3072661129649</v>
       </c>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
@@ -12452,16 +12452,16 @@
         <v>121.5869432067871</v>
       </c>
       <c r="AG62" t="n">
-        <v>143.4060050201416</v>
+        <v>143.4060049438476</v>
       </c>
       <c r="AH62" t="n">
         <v>-0.1474413211802584</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.2771571619504346</v>
+        <v>-0.2771571615658723</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.152148871382966</v>
+        <v>-0.1521488709318976</v>
       </c>
       <c r="AK62" t="n">
         <v>182.8191986083984</v>
@@ -12497,16 +12497,16 @@
         <v>-0.2843172257542734</v>
       </c>
       <c r="AV62" t="n">
-        <v>-0.3608565614295216</v>
+        <v>-0.360856621561498</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.681183990003767</v>
+        <v>1.681183725457249</v>
       </c>
       <c r="AX62" t="n">
-        <v>-0.3700512325959858</v>
+        <v>-0.3700512910102983</v>
       </c>
       <c r="AY62" t="n">
-        <v>13.5206925635339</v>
+        <v>13.52068868387622</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -13412,16 +13412,16 @@
         <v>147.4555999755859</v>
       </c>
       <c r="AG67" t="n">
-        <v>156.1812226867676</v>
+        <v>156.1812227630615</v>
       </c>
       <c r="AH67" t="n">
         <v>-0.04601793223020423</v>
       </c>
       <c r="AI67" t="n">
-        <v>-0.09931555311825868</v>
+        <v>-0.09931555355823973</v>
       </c>
       <c r="AJ67" t="n">
-        <v>-0.05586857729166006</v>
+        <v>-0.0558685777528648</v>
       </c>
       <c r="AK67" t="n">
         <v>217.0162200927734</v>
@@ -13460,13 +13460,13 @@
         <v>-0.3271417232463639</v>
       </c>
       <c r="AW67" t="n">
-        <v>7.296677845659699</v>
+        <v>7.296676912325873</v>
       </c>
       <c r="AX67" t="n">
         <v>-0.146286027341038</v>
       </c>
       <c r="AY67" t="n">
-        <v>11.40735242992542</v>
+        <v>11.40735138627078</v>
       </c>
       <c r="AZ67" t="inlineStr"/>
       <c r="BA67" t="n">
@@ -13608,16 +13608,16 @@
         <v>184.3362005615234</v>
       </c>
       <c r="AG68" t="n">
-        <v>133.7953612518311</v>
+        <v>133.7953616333008</v>
       </c>
       <c r="AH68" t="n">
         <v>0.07298508205998888</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.4783023225584808</v>
+        <v>0.4783023183436292</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.3777473212584992</v>
+        <v>0.3777473173303443</v>
       </c>
       <c r="AK68" t="n">
         <v>207.0800018310547</v>
@@ -13653,16 +13653,16 @@
         <v>0.9721778905487306</v>
       </c>
       <c r="AV68" t="n">
-        <v>0.5926835685993619</v>
+        <v>0.5926834707529893</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.415537082677265</v>
+        <v>1.415537307744987</v>
       </c>
       <c r="AX68" t="n">
         <v>0.8728929283594558</v>
       </c>
       <c r="AY68" t="n">
-        <v>209.9278359820676</v>
+        <v>209.9277957599664</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13797,64 +13797,64 @@
         <v>525</v>
       </c>
       <c r="AF69" t="n">
-        <v>471.16</v>
+        <v>473.2</v>
       </c>
       <c r="AG69" t="n">
-        <v>319.9545816040039</v>
+        <v>321.8643802642822</v>
       </c>
       <c r="AH69" t="n">
-        <v>0.114271160539944</v>
+        <v>0.1094674556213018</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.6408578910420895</v>
+        <v>0.631121777342754</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.4725840075112209</v>
+        <v>0.4701844286449355</v>
       </c>
       <c r="AK69" t="n">
         <v>543</v>
       </c>
       <c r="AL69" t="n">
-        <v>53.3286018371582</v>
+        <v>53.72732162475586</v>
       </c>
       <c r="AM69" t="n">
         <v>-0.03314917127071826</v>
       </c>
       <c r="AN69" t="n">
-        <v>8.844623371209247</v>
+        <v>8.771564710906723</v>
       </c>
       <c r="AO69" t="n">
-        <v>46.44268774703557</v>
+        <v>51.53508771929824</v>
       </c>
       <c r="AP69" t="n">
-        <v>76407003</v>
+        <v>8761606</v>
       </c>
       <c r="AQ69" t="n">
-        <v>78883638.84</v>
+        <v>76488305.59999999</v>
       </c>
       <c r="AR69" t="n">
-        <v>0.9686039351579182</v>
+        <v>0.114548308153397</v>
       </c>
       <c r="AS69" t="n">
-        <v>-0.005681818181818232</v>
+        <v>0.0479041916167664</v>
       </c>
       <c r="AT69" t="n">
-        <v>0.187570110554637</v>
+        <v>0.1041663551079151</v>
       </c>
       <c r="AU69" t="n">
-        <v>1.361826582465821</v>
+        <v>1.432736047460074</v>
       </c>
       <c r="AV69" t="n">
-        <v>8.844623371209247</v>
+        <v>8.771564710906723</v>
       </c>
       <c r="AW69" t="n">
-        <v>6.633457209729383</v>
+        <v>6.815206562462095</v>
       </c>
       <c r="AX69" t="n">
         <v>1.544383279678278</v>
       </c>
       <c r="AY69" t="n">
-        <v>-0.3873831526093692</v>
+        <v>-0.3873831962407139</v>
       </c>
       <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
@@ -13869,12 +13869,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Winbond</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -13889,22 +13889,26 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Specialty memory</t>
+          <t>Etch/deposition, memory equipment</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+        </is>
+      </c>
       <c r="K70" s="1" t="n">
         <v>46195</v>
       </c>
@@ -13938,11 +13942,11 @@
         </is>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>Winbond Electronics Corporation</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -13952,101 +13956,101 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X70" t="n">
-        <v>807750074368</v>
+        <v>360518057984</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>0.03148317337036133</v>
+        <v>1</v>
       </c>
       <c r="AA70" t="n">
-        <v>25430535631.25</v>
+        <v>360518057984</v>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC70" s="2" t="n">
-        <v>36529</v>
+        <v>30806</v>
       </c>
       <c r="AD70" t="n">
-        <v>26.7</v>
+        <v>42.4</v>
       </c>
       <c r="AE70" t="n">
-        <v>179.5</v>
+        <v>288.1099853515625</v>
       </c>
       <c r="AF70" t="n">
-        <v>168.44</v>
+        <v>307.3807989501953</v>
       </c>
       <c r="AG70" t="n">
-        <v>128.9797222137451</v>
+        <v>267.0084088897705</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.0656613630966516</v>
+        <v>-0.06269361542571572</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.3916916312048859</v>
+        <v>0.07902963262293117</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.3059417178838495</v>
+        <v>0.1512026914369269</v>
       </c>
       <c r="AK70" t="n">
-        <v>222</v>
+        <v>433.3299865722656</v>
       </c>
       <c r="AL70" t="n">
-        <v>24.42213439941406</v>
+        <v>125.6247329711914</v>
       </c>
       <c r="AM70" t="n">
-        <v>-0.1914414414414415</v>
+        <v>-0.3351256680144038</v>
       </c>
       <c r="AN70" t="n">
-        <v>6.349889942637716</v>
+        <v>1.293417693613189</v>
       </c>
       <c r="AO70" t="n">
-        <v>48.27586206896552</v>
+        <v>44.06472660920067</v>
       </c>
       <c r="AP70" t="n">
-        <v>136049588</v>
+        <v>19608300</v>
       </c>
       <c r="AQ70" t="n">
-        <v>133911703.42</v>
+        <v>9599400</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.015964882272424</v>
+        <v>2.042658916182261</v>
       </c>
       <c r="AS70" t="n">
-        <v>-0.008287292817679592</v>
+        <v>-0.07219918692515426</v>
       </c>
       <c r="AT70" t="n">
-        <v>-0.124390243902439</v>
+        <v>-0.2965034444981213</v>
       </c>
       <c r="AU70" t="n">
-        <v>0.6785095999430399</v>
+        <v>0.2625369552102919</v>
       </c>
       <c r="AV70" t="n">
-        <v>6.334950493405811</v>
+        <v>1.293417693613189</v>
       </c>
       <c r="AW70" t="n">
-        <v>4.598465857159955</v>
+        <v>3.985515619164275</v>
       </c>
       <c r="AX70" t="n">
-        <v>0.9872222736514633</v>
+        <v>0.5598095737217816</v>
       </c>
       <c r="AY70" t="n">
-        <v>3.715527458829068</v>
+        <v>1527.176156440602</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14061,12 +14065,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -14076,16 +14080,16 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Enterprise storage / data storage</t>
+          <t>HBM + DRAM + NAND</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Etch/deposition, memory equipment</t>
+          <t>HBM, DRAM, NAND</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -14098,7 +14102,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
         </is>
       </c>
       <c r="K71" s="1" t="n">
@@ -14120,10 +14124,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q71" s="1" t="n">
         <v>46192</v>
@@ -14134,11 +14138,11 @@
         </is>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -14148,7 +14152,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -14157,7 +14161,7 @@
         </is>
       </c>
       <c r="X71" t="n">
-        <v>360518057984</v>
+        <v>1147237564416</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -14168,7 +14172,7 @@
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>360518057984</v>
+        <v>1147237564416</v>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
@@ -14176,73 +14180,73 @@
         </is>
       </c>
       <c r="AC71" s="2" t="n">
-        <v>30806</v>
+        <v>30834</v>
       </c>
       <c r="AD71" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="AE71" t="n">
-        <v>288.1099853515625</v>
+        <v>1015.799987792969</v>
       </c>
       <c r="AF71" t="n">
-        <v>307.3807989501953</v>
+        <v>927.257001953125</v>
       </c>
       <c r="AG71" t="n">
-        <v>267.0084088897705</v>
+        <v>640.0172517395019</v>
       </c>
       <c r="AH71" t="n">
-        <v>-0.06269361542571572</v>
+        <v>0.09548915311865147</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.07902963262293117</v>
+        <v>0.5871446981032582</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.1512026914369269</v>
+        <v>0.4488000119261388</v>
       </c>
       <c r="AK71" t="n">
-        <v>433.3299865722656</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="AL71" t="n">
-        <v>125.6247253417969</v>
+        <v>156.5786743164062</v>
       </c>
       <c r="AM71" t="n">
-        <v>-0.3351256680144038</v>
+        <v>-0.1628298619058135</v>
       </c>
       <c r="AN71" t="n">
-        <v>1.293417832896187</v>
+        <v>5.487473420168903</v>
       </c>
       <c r="AO71" t="n">
-        <v>44.06472660920067</v>
+        <v>61.03630159648797</v>
       </c>
       <c r="AP71" t="n">
-        <v>19608300</v>
+        <v>35656400</v>
       </c>
       <c r="AQ71" t="n">
-        <v>9599400</v>
+        <v>34439294</v>
       </c>
       <c r="AR71" t="n">
-        <v>2.042658916182261</v>
+        <v>1.035340619932569</v>
       </c>
       <c r="AS71" t="n">
-        <v>-0.07219918692515426</v>
+        <v>0.04256255065094749</v>
       </c>
       <c r="AT71" t="n">
-        <v>-0.2965034444981213</v>
+        <v>-0.1613232744402168</v>
       </c>
       <c r="AU71" t="n">
-        <v>0.2625369552102919</v>
+        <v>1.403364911053993</v>
       </c>
       <c r="AV71" t="n">
-        <v>1.293417832896187</v>
+        <v>5.024218870963027</v>
       </c>
       <c r="AW71" t="n">
-        <v>3.985514960973383</v>
+        <v>13.01075565387399</v>
       </c>
       <c r="AX71" t="n">
-        <v>0.5598095737217816</v>
+        <v>2.222315921335985</v>
       </c>
       <c r="AY71" t="n">
-        <v>1527.176035656825</v>
+        <v>751.0282526841673</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14257,12 +14261,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -14272,29 +14276,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>HBM + DRAM + NAND</t>
+          <t>NAND / SSD storage</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HBM, DRAM, NAND</t>
+          <t>NAND/storage, si cotiza separada en tu fuente</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="K72" s="1" t="n">
@@ -14316,10 +14320,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="1" t="n">
         <v>46192</v>
@@ -14334,7 +14338,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Sandisk Corporation</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -14344,7 +14348,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -14353,7 +14357,7 @@
         </is>
       </c>
       <c r="X72" t="n">
-        <v>1147237564416</v>
+        <v>262356500480</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
@@ -14364,7 +14368,7 @@
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>1147237564416</v>
+        <v>262356500480</v>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
@@ -14372,73 +14376,71 @@
         </is>
       </c>
       <c r="AC72" s="2" t="n">
-        <v>30834</v>
+        <v>45701</v>
       </c>
       <c r="AD72" t="n">
-        <v>42.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE72" t="n">
-        <v>1015.799987792969</v>
+        <v>1791.819946289062</v>
       </c>
       <c r="AF72" t="n">
-        <v>927.257001953125</v>
+        <v>1504.201291503906</v>
       </c>
       <c r="AG72" t="n">
-        <v>640.0172520446778</v>
+        <v>1068.238122787476</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.09548915311865147</v>
+        <v>0.1912102166177467</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.5871446973464689</v>
+        <v>0.6773600455425262</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.4488000112353157</v>
+        <v>0.4081142204313233</v>
       </c>
       <c r="AK72" t="n">
-        <v>1213.373413085938</v>
+        <v>2335</v>
       </c>
       <c r="AL72" t="n">
-        <v>156.5786895751953</v>
+        <v>94.29000091552734</v>
       </c>
       <c r="AM72" t="n">
-        <v>-0.1628298619058135</v>
+        <v>-0.2326252906684957</v>
       </c>
       <c r="AN72" t="n">
-        <v>5.487472787956507</v>
+        <v>18.00328697519391</v>
       </c>
       <c r="AO72" t="n">
-        <v>61.03630159648797</v>
+        <v>67.86196328652967</v>
       </c>
       <c r="AP72" t="n">
-        <v>35656400</v>
+        <v>17693500</v>
       </c>
       <c r="AQ72" t="n">
-        <v>34439294</v>
+        <v>14134788</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.035340619932569</v>
+        <v>1.251769747094898</v>
       </c>
       <c r="AS72" t="n">
-        <v>0.04256255065094749</v>
+        <v>0.1194536815453668</v>
       </c>
       <c r="AT72" t="n">
-        <v>-0.1613232744402168</v>
+        <v>-0.2119469058856045</v>
       </c>
       <c r="AU72" t="n">
-        <v>1.403364911053993</v>
+        <v>1.524721211218993</v>
       </c>
       <c r="AV72" t="n">
-        <v>5.024218870963027</v>
-      </c>
-      <c r="AW72" t="n">
-        <v>13.01075565387399</v>
-      </c>
+        <v>17.12298873786576</v>
+      </c>
+      <c r="AW72" t="inlineStr"/>
       <c r="AX72" t="n">
-        <v>2.222316233281064</v>
+        <v>5.510027648101843</v>
       </c>
       <c r="AY72" t="n">
-        <v>751.0285181632784</v>
+        <v>48.77277628580729</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14453,12 +14455,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Seagate</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -14468,12 +14470,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NAND / SSD storage</t>
+          <t>HDD / enterprise storage</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>NAND/storage, si cotiza separada en tu fuente</t>
+          <t>HDD/enterprise storage</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -14483,14 +14485,14 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>S&amp;P 500, Nasdaq-100</t>
         </is>
       </c>
       <c r="K73" s="1" t="n">
@@ -14530,7 +14532,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>Sandisk Corporation</t>
+          <t>Seagate Technology Holdings plc</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -14549,7 +14551,7 @@
         </is>
       </c>
       <c r="X73" t="n">
-        <v>262356500480</v>
+        <v>195282829312</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -14560,79 +14562,81 @@
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>262356500480</v>
+        <v>195282829312</v>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC73" s="2" t="n">
-        <v>45701</v>
+        <v>37601</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.6</v>
+        <v>23.8</v>
       </c>
       <c r="AE73" t="n">
-        <v>1791.819946289062</v>
+        <v>858.7899780273438</v>
       </c>
       <c r="AF73" t="n">
-        <v>1504.201291503906</v>
+        <v>843.3331970214844</v>
       </c>
       <c r="AG73" t="n">
-        <v>1068.238122787476</v>
+        <v>618.7675816345214</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.1912102166177467</v>
+        <v>0.0183282017836488</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.6773600455425262</v>
+        <v>0.3879039618701177</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.4081142204313233</v>
+        <v>0.3629240154982842</v>
       </c>
       <c r="AK73" t="n">
-        <v>2335</v>
+        <v>1093.260498046875</v>
       </c>
       <c r="AL73" t="n">
-        <v>94.29000091552734</v>
+        <v>210.5585479736328</v>
       </c>
       <c r="AM73" t="n">
-        <v>-0.2326252906684957</v>
+        <v>-0.2144690313410355</v>
       </c>
       <c r="AN73" t="n">
-        <v>18.00328697519391</v>
+        <v>3.078627945966296</v>
       </c>
       <c r="AO73" t="n">
-        <v>67.86196328652967</v>
+        <v>54.07186659144357</v>
       </c>
       <c r="AP73" t="n">
-        <v>17693500</v>
+        <v>6966500</v>
       </c>
       <c r="AQ73" t="n">
-        <v>14134788</v>
+        <v>4610218</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.251769747094898</v>
+        <v>1.511099908941399</v>
       </c>
       <c r="AS73" t="n">
-        <v>0.1194536815453668</v>
+        <v>0.01005596995103919</v>
       </c>
       <c r="AT73" t="n">
-        <v>-0.2119469058856045</v>
+        <v>-0.2144690313410355</v>
       </c>
       <c r="AU73" t="n">
-        <v>1.524721211218993</v>
+        <v>1.09347904231887</v>
       </c>
       <c r="AV73" t="n">
-        <v>17.12298873786576</v>
-      </c>
-      <c r="AW73" t="inlineStr"/>
+        <v>2.99686509579162</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>10.87617949847411</v>
+      </c>
       <c r="AX73" t="n">
-        <v>5.510027648101843</v>
+        <v>1.9940231952286</v>
       </c>
       <c r="AY73" t="n">
-        <v>48.77277628580729</v>
+        <v>161.9149275481618</v>
       </c>
       <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
@@ -14647,12 +14651,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Seagate</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -14662,16 +14666,16 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HDD / enterprise storage</t>
+          <t>NAND / SSD storage</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HDD/enterprise storage</t>
+          <t>HDD/NAND/storage</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -14719,12 +14723,10 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
+      <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings plc</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -14743,7 +14745,7 @@
         </is>
       </c>
       <c r="X74" t="n">
-        <v>195282829312</v>
+        <v>159128338432</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
@@ -14754,7 +14756,7 @@
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>195282829312</v>
+        <v>159128338432</v>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
@@ -14762,73 +14764,73 @@
         </is>
       </c>
       <c r="AC74" s="2" t="n">
-        <v>37601</v>
+        <v>28794</v>
       </c>
       <c r="AD74" t="n">
-        <v>23.8</v>
+        <v>47.9</v>
       </c>
       <c r="AE74" t="n">
-        <v>858.7899780273438</v>
+        <v>441.3599853515625</v>
       </c>
       <c r="AF74" t="n">
-        <v>843.3331970214844</v>
+        <v>481.5792150878906</v>
       </c>
       <c r="AG74" t="n">
-        <v>618.7675805664062</v>
+        <v>385.6687264251709</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.0183282017836488</v>
+        <v>-0.08351529400825142</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.3879039642659143</v>
+        <v>0.1444018016254607</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.3629240178509607</v>
+        <v>0.2486861964456657</v>
       </c>
       <c r="AK74" t="n">
-        <v>1093.260498046875</v>
+        <v>745.990478515625</v>
       </c>
       <c r="AL74" t="n">
-        <v>210.5585479736328</v>
+        <v>104.9542007446289</v>
       </c>
       <c r="AM74" t="n">
-        <v>-0.2144690313410355</v>
+        <v>-0.4083570795303145</v>
       </c>
       <c r="AN74" t="n">
-        <v>3.078627945966296</v>
+        <v>3.205262697635753</v>
       </c>
       <c r="AO74" t="n">
-        <v>54.07186659144357</v>
+        <v>44.33794424722701</v>
       </c>
       <c r="AP74" t="n">
-        <v>6966500</v>
+        <v>13506300</v>
       </c>
       <c r="AQ74" t="n">
-        <v>4610218</v>
+        <v>7289618</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.511099908941399</v>
+        <v>1.85281313780777</v>
       </c>
       <c r="AS74" t="n">
-        <v>0.01005596995103919</v>
+        <v>-0.05873218292760551</v>
       </c>
       <c r="AT74" t="n">
-        <v>-0.2144690313410355</v>
+        <v>-0.3973660669863828</v>
       </c>
       <c r="AU74" t="n">
-        <v>1.093479198058939</v>
+        <v>0.5067101155289817</v>
       </c>
       <c r="AV74" t="n">
-        <v>2.99686509579162</v>
+        <v>3.205262697635753</v>
       </c>
       <c r="AW74" t="n">
-        <v>10.87617824545826</v>
+        <v>9.028728133968007</v>
       </c>
       <c r="AX74" t="n">
-        <v>1.9940231952286</v>
+        <v>1.35390593789604</v>
       </c>
       <c r="AY74" t="n">
-        <v>161.9150012324824</v>
+        <v>648.7067645720251</v>
       </c>
       <c r="AZ74" t="inlineStr"/>
       <c r="BA74" t="n">
@@ -14843,12 +14845,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>000660.KS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -14858,31 +14860,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NAND / SSD storage</t>
+          <t>HBM + DRAM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HDD/NAND/storage</t>
+          <t>HBM/DRAM, memoria crítica para IA</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" s="1" t="n">
         <v>46195</v>
       </c>
@@ -14915,10 +14913,12 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>SK hynix Inc.</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -14928,105 +14928,105 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="X75" t="n">
-        <v>159128338432</v>
+        <v>1318200625070080</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>1</v>
+        <v>0.0007220216793939471</v>
       </c>
       <c r="AA75" t="n">
-        <v>159128338432</v>
+        <v>951769429091.25</v>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC75" s="2" t="n">
-        <v>28794</v>
+        <v>36529</v>
       </c>
       <c r="AD75" t="n">
-        <v>47.9</v>
+        <v>26.7</v>
       </c>
       <c r="AE75" t="n">
-        <v>441.3599853515625</v>
+        <v>1857000</v>
       </c>
       <c r="AF75" t="n">
-        <v>481.5792150878906</v>
+        <v>1706750.1375</v>
       </c>
       <c r="AG75" t="n">
-        <v>385.6687265014648</v>
+        <v>1366565.9725</v>
       </c>
       <c r="AH75" t="n">
-        <v>-0.08351529400825142</v>
+        <v>0.08803272324329892</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.1444018013990722</v>
+        <v>0.3588806083052094</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.2486861961986475</v>
+        <v>0.2489335837754441</v>
       </c>
       <c r="AK75" t="n">
-        <v>745.990478515625</v>
+        <v>2918367.25</v>
       </c>
       <c r="AL75" t="n">
-        <v>104.9541931152344</v>
+        <v>272696.15625</v>
       </c>
       <c r="AM75" t="n">
-        <v>-0.4083570795303145</v>
+        <v>-0.363685293548987</v>
       </c>
       <c r="AN75" t="n">
-        <v>3.205263003327286</v>
+        <v>5.80977695298923</v>
       </c>
       <c r="AO75" t="n">
-        <v>44.33794424722701</v>
+        <v>62.41519674355494</v>
       </c>
       <c r="AP75" t="n">
-        <v>13506300</v>
+        <v>4764077</v>
       </c>
       <c r="AQ75" t="n">
-        <v>7289618</v>
+        <v>4867785.22</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.85281313780777</v>
+        <v>0.9786949885188239</v>
       </c>
       <c r="AS75" t="n">
-        <v>-0.05873218292760551</v>
+        <v>0.07364313073643136</v>
       </c>
       <c r="AT75" t="n">
-        <v>-0.3973660669863828</v>
+        <v>-0.363685293548987</v>
       </c>
       <c r="AU75" t="n">
-        <v>0.5067101155289817</v>
+        <v>0.8338729140636858</v>
       </c>
       <c r="AV75" t="n">
-        <v>3.205263003327286</v>
+        <v>5.80977695298923</v>
       </c>
       <c r="AW75" t="n">
-        <v>9.028728133968007</v>
+        <v>15.39241494955472</v>
       </c>
       <c r="AX75" t="n">
-        <v>1.353906129456273</v>
+        <v>1.749100703948168</v>
       </c>
       <c r="AY75" t="n">
-        <v>648.7068215782082</v>
+        <v>-9.115401933225746</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
@@ -15037,12 +15037,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>000660.KS</t>
+          <t>005930.KS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -15052,16 +15052,16 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HBM + DRAM</t>
+          <t>HBM/DRAM/NAND + foundry + packaging</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HBM/DRAM, memoria crítica para IA</t>
+          <t>HBM/DRAM/NAND, foundry, packaging</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -15072,7 +15072,11 @@
       <c r="I76" t="n">
         <v>0</v>
       </c>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>STOXX Global AI Infrastructure</t>
+        </is>
+      </c>
       <c r="K76" s="1" t="n">
         <v>46195</v>
       </c>
@@ -15092,10 +15096,10 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="Q76" s="1" t="n">
         <v>46192</v>
@@ -15110,7 +15114,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>SK hynix Inc.</t>
+          <t>Samsung Electronics Co., Ltd.</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -15120,7 +15124,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -15129,7 +15133,7 @@
         </is>
       </c>
       <c r="X76" t="n">
-        <v>1318200625070080</v>
+        <v>1713873010819072</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
@@ -15140,7 +15144,7 @@
         <v>0.0007220216793939471</v>
       </c>
       <c r="AA76" t="n">
-        <v>951769429091.25</v>
+        <v>1237453469539.547</v>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
@@ -15154,67 +15158,67 @@
         <v>26.7</v>
       </c>
       <c r="AE76" t="n">
-        <v>1857000</v>
+        <v>261000</v>
       </c>
       <c r="AF76" t="n">
-        <v>1706750.1375</v>
+        <v>255010</v>
       </c>
       <c r="AG76" t="n">
-        <v>1366565.97234375</v>
+        <v>219473.5001953125</v>
       </c>
       <c r="AH76" t="n">
-        <v>0.08803272324329892</v>
+        <v>0.02348927493039499</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.3588806084605807</v>
+        <v>0.1892096301728112</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.2489335839182443</v>
+        <v>0.1619170413424085</v>
       </c>
       <c r="AK76" t="n">
-        <v>2918367.25</v>
+        <v>362100.65625</v>
       </c>
       <c r="AL76" t="n">
-        <v>272696.125</v>
+        <v>68638.65625</v>
       </c>
       <c r="AM76" t="n">
-        <v>-0.363685293548987</v>
+        <v>-0.2792059459295719</v>
       </c>
       <c r="AN76" t="n">
-        <v>5.809777733365298</v>
+        <v>2.802521993574139</v>
       </c>
       <c r="AO76" t="n">
-        <v>62.41519674355494</v>
+        <v>50.73529411764706</v>
       </c>
       <c r="AP76" t="n">
-        <v>4764077</v>
+        <v>17489615</v>
       </c>
       <c r="AQ76" t="n">
-        <v>4867785.22</v>
+        <v>24374586.6</v>
       </c>
       <c r="AR76" t="n">
-        <v>0.9786949885188239</v>
+        <v>0.7175348360574861</v>
       </c>
       <c r="AS76" t="n">
-        <v>0.07364313073643136</v>
+        <v>-0.0728241563055062</v>
       </c>
       <c r="AT76" t="n">
-        <v>-0.363685293548987</v>
+        <v>-0.2608548012445463</v>
       </c>
       <c r="AU76" t="n">
-        <v>0.8338729140636858</v>
+        <v>0.3058786114532683</v>
       </c>
       <c r="AV76" t="n">
-        <v>5.809777733365298</v>
+        <v>2.802521993574139</v>
       </c>
       <c r="AW76" t="n">
-        <v>15.39241494955472</v>
+        <v>2.619757714169811</v>
       </c>
       <c r="AX76" t="n">
-        <v>1.749100703948168</v>
+        <v>1.037577098336028</v>
       </c>
       <c r="AY76" t="n">
-        <v>-9.115401379074695</v>
+        <v>60.13179037686204</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
@@ -15229,12 +15233,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>005930.KS</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Winbond</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -15244,16 +15248,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HBM/DRAM/NAND + foundry + packaging</t>
+          <t>Enterprise storage / data storage</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HBM/DRAM/NAND, foundry, packaging</t>
+          <t>Specialty memory</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -15264,11 +15268,7 @@
       <c r="I77" t="n">
         <v>0</v>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>STOXX Global AI Infrastructure</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" s="1" t="n">
         <v>46195</v>
       </c>
@@ -15288,10 +15288,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="1" t="n">
         <v>46192</v>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Samsung Electronics Co., Ltd.</t>
+          <t>Winbond Electronics Corporation</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -15316,31 +15316,31 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X77" t="n">
-        <v>1713873010819072</v>
+        <v>807750074368</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>0.0007220216793939471</v>
+        <v>0.03148317337036133</v>
       </c>
       <c r="AA77" t="n">
-        <v>1237453469539.547</v>
+        <v>25430535631.25</v>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC77" s="2" t="n">
@@ -15350,67 +15350,67 @@
         <v>26.7</v>
       </c>
       <c r="AE77" t="n">
-        <v>261000</v>
+        <v>179.5</v>
       </c>
       <c r="AF77" t="n">
-        <v>255010</v>
+        <v>168.69</v>
       </c>
       <c r="AG77" t="n">
-        <v>219473.5003125</v>
+        <v>129.5912195968628</v>
       </c>
       <c r="AH77" t="n">
-        <v>0.02348927493039499</v>
+        <v>0.06408204398600992</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.1892096295378349</v>
+        <v>0.385124706429921</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.1619170407220047</v>
+        <v>0.3017085611568988</v>
       </c>
       <c r="AK77" t="n">
-        <v>362100.65625</v>
+        <v>222</v>
       </c>
       <c r="AL77" t="n">
-        <v>68638.6484375</v>
+        <v>24.42213439941406</v>
       </c>
       <c r="AM77" t="n">
-        <v>-0.2792059459295719</v>
+        <v>-0.1914414414414415</v>
       </c>
       <c r="AN77" t="n">
-        <v>2.802522426379908</v>
+        <v>6.349889942637716</v>
       </c>
       <c r="AO77" t="n">
-        <v>50.73529411764706</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="AP77" t="n">
-        <v>17489615</v>
+        <v>20039216</v>
       </c>
       <c r="AQ77" t="n">
-        <v>24374586.6</v>
+        <v>131365249.98</v>
       </c>
       <c r="AR77" t="n">
-        <v>0.7175348360574861</v>
+        <v>0.1525457912427443</v>
       </c>
       <c r="AS77" t="n">
-        <v>-0.0728241563055062</v>
+        <v>0.01412429378531077</v>
       </c>
       <c r="AT77" t="n">
-        <v>-0.2608548012445463</v>
+        <v>-0.1822323462414579</v>
       </c>
       <c r="AU77" t="n">
-        <v>0.3058786114532683</v>
+        <v>0.8134651853255257</v>
       </c>
       <c r="AV77" t="n">
-        <v>2.802522426379908</v>
+        <v>6.349889942637716</v>
       </c>
       <c r="AW77" t="n">
-        <v>2.619758498571676</v>
+        <v>4.763125528640334</v>
       </c>
       <c r="AX77" t="n">
-        <v>1.037577098336028</v>
+        <v>0.9872222736514633</v>
       </c>
       <c r="AY77" t="n">
-        <v>60.13179037686204</v>
+        <v>3.71552793138827</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15733,7 +15733,7 @@
         <v>35564</v>
       </c>
       <c r="AD79" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="AE79" t="n">
         <v>87.59999847412109</v>
@@ -16680,13 +16680,13 @@
         <v>2.160277989808225</v>
       </c>
       <c r="AW84" t="n">
-        <v>7.008292375657749</v>
+        <v>7.008293001673719</v>
       </c>
       <c r="AX84" t="n">
         <v>1.758717899832289</v>
       </c>
       <c r="AY84" t="n">
-        <v>21.44181912895508</v>
+        <v>21.44181667090001</v>
       </c>
       <c r="AZ84" t="inlineStr"/>
       <c r="BA84" t="n">
@@ -17022,16 +17022,16 @@
         <v>79.95339981079101</v>
       </c>
       <c r="AG86" t="n">
-        <v>73.25200618743897</v>
+        <v>73.25200571060181</v>
       </c>
       <c r="AH86" t="n">
         <v>-0.0300599694912389</v>
       </c>
       <c r="AI86" t="n">
-        <v>0.05867411813023971</v>
+        <v>0.05867412502172553</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.09148409677960712</v>
+        <v>0.09148410388467099</v>
       </c>
       <c r="AK86" t="n">
         <v>88.16000366210938</v>
@@ -17070,10 +17070,10 @@
         <v>0.277473053491099</v>
       </c>
       <c r="AW86" t="n">
-        <v>3.274616913352624</v>
+        <v>3.274616463942743</v>
       </c>
       <c r="AX86" t="n">
-        <v>0.1140291847796544</v>
+        <v>0.1140290626836804</v>
       </c>
       <c r="AY86" t="n">
         <v>1238.471865106173</v>
@@ -17608,16 +17608,16 @@
         <v>154.7744488525391</v>
       </c>
       <c r="AG89" t="n">
-        <v>146.6304936218262</v>
+        <v>146.6304941558838</v>
       </c>
       <c r="AH89" t="n">
         <v>-0.03000782108519429</v>
       </c>
       <c r="AI89" t="n">
-        <v>0.02386619027561832</v>
+        <v>0.02386618654649264</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.05554066572071226</v>
+        <v>0.05554066187622198</v>
       </c>
       <c r="AK89" t="n">
         <v>255.2094421386719</v>
@@ -17653,16 +17653,16 @@
         <v>0.2092087668164067</v>
       </c>
       <c r="AV89" t="n">
-        <v>0.9020249123020005</v>
+        <v>0.9020250961483534</v>
       </c>
       <c r="AW89" t="n">
-        <v>3.368110535982487</v>
+        <v>3.36811150562112</v>
       </c>
       <c r="AX89" t="n">
         <v>0.6645459985352418</v>
       </c>
       <c r="AY89" t="n">
-        <v>195.206763856427</v>
+        <v>195.20679442468</v>
       </c>
       <c r="AZ89" t="inlineStr"/>
       <c r="BA89" t="n">
@@ -18000,28 +18000,28 @@
         <v>215.9457998657226</v>
       </c>
       <c r="AG91" t="n">
-        <v>158.3619704055786</v>
+        <v>158.3619702529907</v>
       </c>
       <c r="AH91" t="n">
         <v>0.1310708527411841</v>
       </c>
       <c r="AI91" t="n">
-        <v>0.5423526202310742</v>
+        <v>0.5423526217171908</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0.3636215772806244</v>
+        <v>0.3636215785945265</v>
       </c>
       <c r="AK91" t="n">
         <v>316.3519592285156</v>
       </c>
       <c r="AL91" t="n">
-        <v>73.67493438720703</v>
+        <v>73.67494201660156</v>
       </c>
       <c r="AM91" t="n">
         <v>-0.2279169043376559</v>
       </c>
       <c r="AN91" t="n">
-        <v>2.315238785504935</v>
+        <v>2.315238442196017</v>
       </c>
       <c r="AO91" t="n">
         <v>64.01542628797245</v>
@@ -18048,13 +18048,13 @@
         <v>2.297458900645704</v>
       </c>
       <c r="AW91" t="n">
-        <v>2.988906833700439</v>
+        <v>2.988906336692607</v>
       </c>
       <c r="AX91" t="n">
         <v>1.73641818636544</v>
       </c>
       <c r="AY91" t="n">
-        <v>19.13718193273938</v>
+        <v>19.13718034944063</v>
       </c>
       <c r="AZ91" t="inlineStr"/>
       <c r="BA91" t="n">
@@ -18169,10 +18169,10 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>1.148897051811218</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA92" t="n">
-        <v>6860191722.834595</v>
+        <v>6860980410.408325</v>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
@@ -18240,13 +18240,13 @@
         <v>0.03494023191517615</v>
       </c>
       <c r="AW92" t="n">
-        <v>0.8594671290173481</v>
+        <v>0.8594673218501994</v>
       </c>
       <c r="AX92" t="n">
         <v>0.08575967299290999</v>
       </c>
       <c r="AY92" t="n">
-        <v>7.470609632666173</v>
+        <v>7.470608632267149</v>
       </c>
       <c r="AZ92" t="inlineStr"/>
       <c r="BA92" t="n">
@@ -18434,7 +18434,7 @@
         <v>0.1195388349514563</v>
       </c>
       <c r="AY93" t="n">
-        <v>26.31289040343655</v>
+        <v>26.31288731862259</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18620,13 +18620,13 @@
         <v>1.243697435217268</v>
       </c>
       <c r="AW94" t="n">
-        <v>1.064150963219221</v>
+        <v>1.064151343681684</v>
       </c>
       <c r="AX94" t="n">
         <v>0.6405529845903228</v>
       </c>
       <c r="AY94" t="n">
-        <v>16.87311631247413</v>
+        <v>16.8731127468192</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18741,10 +18741,10 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>1.148897051811218</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA95" t="n">
-        <v>42102606801.84961</v>
+        <v>42107447162.60742</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>0.5158842905345578</v>
       </c>
       <c r="AW95" t="n">
-        <v>3.482454599997584</v>
+        <v>3.482454287027323</v>
       </c>
       <c r="AX95" t="n">
         <v>0.3725263593040771</v>
@@ -19004,7 +19004,7 @@
         <v>1.281274202214599</v>
       </c>
       <c r="AW96" t="n">
-        <v>23.65446460930291</v>
+        <v>23.65446711217507</v>
       </c>
       <c r="AX96" t="n">
         <v>0.4875885393589443</v>
@@ -19196,7 +19196,7 @@
         <v>0.7870612041157252</v>
       </c>
       <c r="AW97" t="n">
-        <v>32.03813314029429</v>
+        <v>32.03813080107443</v>
       </c>
       <c r="AX97" t="n">
         <v>0.4629330192988541</v>
@@ -19344,16 +19344,16 @@
         <v>379.7551989746094</v>
       </c>
       <c r="AG98" t="n">
-        <v>368.386103515625</v>
+        <v>368.3861039733887</v>
       </c>
       <c r="AH98" t="n">
         <v>-0.05831444489197768</v>
       </c>
       <c r="AI98" t="n">
-        <v>-0.02925223851068914</v>
+        <v>-0.02925223971695912</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.03086190100681185</v>
+        <v>0.03086189972584297</v>
       </c>
       <c r="AK98" t="n">
         <v>480.8090515136719</v>
@@ -19398,7 +19398,7 @@
         <v>0.03252787358891807</v>
       </c>
       <c r="AY98" t="n">
-        <v>313.91089297659</v>
+        <v>313.9108599186503</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19540,28 +19540,28 @@
         <v>76.80423034667969</v>
       </c>
       <c r="AG99" t="n">
-        <v>77.54174966812134</v>
+        <v>77.54174955368042</v>
       </c>
       <c r="AH99" t="n">
         <v>-0.04601613332573506</v>
       </c>
       <c r="AI99" t="n">
-        <v>-0.05508971674405128</v>
+        <v>-0.05508971534949403</v>
       </c>
       <c r="AJ99" t="n">
-        <v>-0.009511254577027617</v>
+        <v>-0.009511253115202956</v>
       </c>
       <c r="AK99" t="n">
         <v>102.0957336425781</v>
       </c>
       <c r="AL99" t="n">
-        <v>47.76882934570312</v>
+        <v>47.76882553100586</v>
       </c>
       <c r="AM99" t="n">
         <v>-0.2823402699707934</v>
       </c>
       <c r="AN99" t="n">
-        <v>0.5338453474086895</v>
+        <v>0.5338454698976891</v>
       </c>
       <c r="AO99" t="n">
         <v>50.90232737451163</v>
@@ -19588,13 +19588,13 @@
         <v>0.1347583639828276</v>
       </c>
       <c r="AW99" t="n">
-        <v>0.0170165958590518</v>
+        <v>0.0170167035601243</v>
       </c>
       <c r="AX99" t="n">
-        <v>0.1458862992738732</v>
+        <v>0.145886162549197</v>
       </c>
       <c r="AY99" t="n">
-        <v>418.5846756463006</v>
+        <v>418.5847472545814</v>
       </c>
       <c r="AZ99" t="inlineStr"/>
       <c r="BA99" t="n">
@@ -19784,13 +19784,13 @@
         <v>-0.04443587319161102</v>
       </c>
       <c r="AW100" t="n">
-        <v>0.5170736077476383</v>
+        <v>0.5170741206232596</v>
       </c>
       <c r="AX100" t="n">
         <v>-0.1096234102077395</v>
       </c>
       <c r="AY100" t="n">
-        <v>6.71698679132017</v>
+        <v>6.716987344266406</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -20124,16 +20124,16 @@
         <v>54.17279991149903</v>
       </c>
       <c r="AG102" t="n">
-        <v>46.46951143264771</v>
+        <v>46.46951146125794</v>
       </c>
       <c r="AH102" t="n">
         <v>-0.07370487796174829</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.0798478132894942</v>
+        <v>0.07984781262465623</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.1657708084582805</v>
+        <v>0.1657708077405418</v>
       </c>
       <c r="AK102" t="n">
         <v>79.81999969482422</v>
@@ -20169,16 +20169,16 @@
         <v>0.6325274211942977</v>
       </c>
       <c r="AV102" t="n">
-        <v>0.7862547022073938</v>
+        <v>0.7862548234865656</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.1525270565179038</v>
+        <v>0.1525272584762238</v>
       </c>
       <c r="AX102" t="n">
         <v>0.8406939691195356</v>
       </c>
       <c r="AY102" t="n">
-        <v>21.91667448811267</v>
+        <v>21.91667698335469</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20483,10 +20483,10 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>1.148897051811218</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA104" t="n">
-        <v>184930276518.334</v>
+        <v>184951537179.4043</v>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>0.2243050171506149</v>
       </c>
       <c r="AY104" t="n">
-        <v>14.35532425842279</v>
+        <v>14.35532583226747</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20695,64 +20695,64 @@
         <v>282</v>
       </c>
       <c r="AF105" t="n">
-        <v>256.574896850586</v>
+        <v>257.8154818725586</v>
       </c>
       <c r="AG105" t="n">
-        <v>197.0923736572266</v>
+        <v>197.7504431152344</v>
       </c>
       <c r="AH105" t="n">
-        <v>0.09909427407553473</v>
+        <v>0.09380553080747922</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.4308011759523513</v>
+        <v>0.4260397881165365</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.3018002274243674</v>
+        <v>0.3037416139812279</v>
       </c>
       <c r="AK105" t="n">
         <v>317.5</v>
       </c>
       <c r="AL105" t="n">
-        <v>130.4320373535156</v>
+        <v>136.7589569091797</v>
       </c>
       <c r="AM105" t="n">
         <v>-0.1118110236220472</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.162045504477425</v>
+        <v>1.062022162009275</v>
       </c>
       <c r="AO105" t="n">
-        <v>37.22222222222222</v>
+        <v>39.1812865497076</v>
       </c>
       <c r="AP105" t="n">
-        <v>23894520</v>
+        <v>1708502</v>
       </c>
       <c r="AQ105" t="n">
-        <v>28702747.28</v>
+        <v>28080118</v>
       </c>
       <c r="AR105" t="n">
-        <v>0.8324819839336299</v>
+        <v>0.06084383263631585</v>
       </c>
       <c r="AS105" t="n">
-        <v>0.08045977011494254</v>
+        <v>-0.01742160278745641</v>
       </c>
       <c r="AT105" t="n">
-        <v>0.3145564537639991</v>
+        <v>0.3237278321640655</v>
       </c>
       <c r="AU105" t="n">
-        <v>0.8480616062134199</v>
+        <v>0.860140449966901</v>
       </c>
       <c r="AV105" t="n">
-        <v>1.162045504477425</v>
+        <v>1.062022162009275</v>
       </c>
       <c r="AW105" t="n">
-        <v>5.247042980221635</v>
+        <v>5.225612334432994</v>
       </c>
       <c r="AX105" t="n">
-        <v>0.7348149556884727</v>
+        <v>0.73481479284242</v>
       </c>
       <c r="AY105" t="n">
-        <v>73.57504219615458</v>
+        <v>73.57507510981881</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20894,16 +20894,16 @@
         <v>415.4618524169922</v>
       </c>
       <c r="AG106" t="n">
-        <v>382.610661315918</v>
+        <v>382.6106610107422</v>
       </c>
       <c r="AH106" t="n">
         <v>0.02240431111190744</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.1101885858401195</v>
+        <v>0.1101885867256218</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.08586062653896964</v>
+        <v>0.08586062740506772</v>
       </c>
       <c r="AK106" t="n">
         <v>459.9599914550781</v>
@@ -20942,13 +20942,13 @@
         <v>0.1568557781687472</v>
       </c>
       <c r="AW106" t="n">
-        <v>1.900260096651978</v>
+        <v>1.900259794489807</v>
       </c>
       <c r="AX106" t="n">
         <v>0.3086165429976291</v>
       </c>
       <c r="AY106" t="n">
-        <v>1231.850190559649</v>
+        <v>1231.850083920453</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -20963,12 +20963,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Delta Electronics</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -20978,27 +20978,31 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Power supplies, thermal, data center power</t>
+          <t>Analog/power semiconductors</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+        </is>
+      </c>
       <c r="K107" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21036,7 +21040,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>Delta Electronics, Inc.</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -21046,27 +21050,27 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X107" t="n">
-        <v>4506737704960</v>
+        <v>182060941312</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>0.03148317337036133</v>
+        <v>1</v>
       </c>
       <c r="AA107" t="n">
-        <v>141886404500</v>
+        <v>182060941312</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
@@ -21074,73 +21078,73 @@
         </is>
       </c>
       <c r="AC107" s="2" t="n">
-        <v>36529</v>
+        <v>29297</v>
       </c>
       <c r="AD107" t="n">
-        <v>26.7</v>
+        <v>46.5</v>
       </c>
       <c r="AE107" t="n">
-        <v>1735</v>
+        <v>375.7200012207031</v>
       </c>
       <c r="AF107" t="n">
-        <v>1753.4</v>
+        <v>372.5613116455078</v>
       </c>
       <c r="AG107" t="n">
-        <v>1614.432506713867</v>
+        <v>351.8728149414063</v>
       </c>
       <c r="AH107" t="n">
-        <v>-0.01049389757043462</v>
+        <v>0.008478308070272167</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.07468103670158666</v>
+        <v>0.06777217581661676</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.08607823040493479</v>
+        <v>0.05879538238140558</v>
       </c>
       <c r="AK107" t="n">
-        <v>2506.891357421875</v>
+        <v>444.1268615722656</v>
       </c>
       <c r="AL107" t="n">
-        <v>722.2235107421875</v>
+        <v>222.4181976318359</v>
       </c>
       <c r="AM107" t="n">
-        <v>-0.307907781937427</v>
+        <v>-0.1540254964750241</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.402303406347213</v>
+        <v>0.6892502736787049</v>
       </c>
       <c r="AO107" t="n">
-        <v>42.22222222222222</v>
+        <v>60.55525306947217</v>
       </c>
       <c r="AP107" t="n">
-        <v>12081302</v>
+        <v>7701300</v>
       </c>
       <c r="AQ107" t="n">
-        <v>11168976.4</v>
+        <v>3718664</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.081683904354924</v>
+        <v>2.070985708845972</v>
       </c>
       <c r="AS107" t="n">
-        <v>-0.008571428571428563</v>
+        <v>0.01789308842461379</v>
       </c>
       <c r="AT107" t="n">
-        <v>-0.1325</v>
+        <v>-0.1540254964750241</v>
       </c>
       <c r="AU107" t="n">
-        <v>0.2369307701445569</v>
+        <v>0.2212682484557569</v>
       </c>
       <c r="AV107" t="n">
-        <v>1.402303406347213</v>
+        <v>0.5274808939160343</v>
       </c>
       <c r="AW107" t="n">
-        <v>5.070537746099649</v>
+        <v>1.363578909275559</v>
       </c>
       <c r="AX107" t="n">
-        <v>0.7528364805935397</v>
+        <v>0.3848186375395215</v>
       </c>
       <c r="AY107" t="n">
-        <v>69.23738598601352</v>
+        <v>848.5327584099359</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21155,12 +21159,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -21175,26 +21179,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Analog/power semiconductors</t>
+          <t>Power semiconductors</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Infineon Technologies AG</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -21247,22 +21247,22 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X108" t="n">
-        <v>182060941312</v>
+        <v>72590049280</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>1</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA108" t="n">
-        <v>182060941312</v>
+        <v>83408081584.91211</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -21270,73 +21270,73 @@
         </is>
       </c>
       <c r="AC108" s="2" t="n">
-        <v>29297</v>
+        <v>36598</v>
       </c>
       <c r="AD108" t="n">
-        <v>46.5</v>
+        <v>26.5</v>
       </c>
       <c r="AE108" t="n">
-        <v>375.7200012207031</v>
+        <v>55.86000061035156</v>
       </c>
       <c r="AF108" t="n">
-        <v>372.5613116455078</v>
+        <v>60.21260040283203</v>
       </c>
       <c r="AG108" t="n">
-        <v>351.8728132629395</v>
+        <v>54.32363271713257</v>
       </c>
       <c r="AH108" t="n">
-        <v>0.008478308070272167</v>
+        <v>-0.072287191773165</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.0677721809099916</v>
+        <v>0.02828175908667574</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.05879538743196022</v>
+        <v>0.1084052628874026</v>
       </c>
       <c r="AK108" t="n">
-        <v>444.1268615722656</v>
+        <v>88</v>
       </c>
       <c r="AL108" t="n">
-        <v>222.418212890625</v>
+        <v>31.45297431945801</v>
       </c>
       <c r="AM108" t="n">
-        <v>-0.1540254964750241</v>
+        <v>-0.3652272657914595</v>
       </c>
       <c r="AN108" t="n">
-        <v>0.6892501577893033</v>
+        <v>0.7759846824977197</v>
       </c>
       <c r="AO108" t="n">
-        <v>60.55525306947217</v>
+        <v>47.14419300074758</v>
       </c>
       <c r="AP108" t="n">
-        <v>7701300</v>
+        <v>9826247</v>
       </c>
       <c r="AQ108" t="n">
-        <v>3718664</v>
+        <v>4263936.5</v>
       </c>
       <c r="AR108" t="n">
-        <v>2.070985708845972</v>
+        <v>2.304501251367134</v>
       </c>
       <c r="AS108" t="n">
-        <v>0.01789308842461379</v>
+        <v>0.008121291539048281</v>
       </c>
       <c r="AT108" t="n">
-        <v>-0.1540254964750241</v>
+        <v>-0.306603744994867</v>
       </c>
       <c r="AU108" t="n">
-        <v>0.2212682484557569</v>
+        <v>0.4512860008941595</v>
       </c>
       <c r="AV108" t="n">
-        <v>0.5274808939160343</v>
+        <v>0.7062695545247528</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.363579363035388</v>
+        <v>0.6362072044067328</v>
       </c>
       <c r="AX108" t="n">
-        <v>0.3848186375395215</v>
+        <v>0.4710527857036872</v>
       </c>
       <c r="AY108" t="n">
-        <v>848.5329873944761</v>
+        <v>0.1056442783103928</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21351,12 +21351,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>nVent Electric</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21366,12 +21366,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Power semiconductors</t>
+          <t>Enclosures, electrical/thermal infra</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -21424,37 +21424,37 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>Infineon Technologies AG</t>
+          <t>nVent Electric plc</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X109" t="n">
-        <v>72590049280</v>
+        <v>25554130944</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>1.148897051811218</v>
+        <v>1</v>
       </c>
       <c r="AA109" t="n">
-        <v>83398493608.62305</v>
+        <v>25554130944</v>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
@@ -21462,73 +21462,73 @@
         </is>
       </c>
       <c r="AC109" s="2" t="n">
-        <v>36598</v>
+        <v>43214</v>
       </c>
       <c r="AD109" t="n">
-        <v>26.5</v>
+        <v>8.4</v>
       </c>
       <c r="AE109" t="n">
-        <v>55.86000061035156</v>
+        <v>157.8800048828125</v>
       </c>
       <c r="AF109" t="n">
-        <v>60.21260040283203</v>
+        <v>156.4071734619141</v>
       </c>
       <c r="AG109" t="n">
-        <v>54.32363271713257</v>
+        <v>137.4104351425171</v>
       </c>
       <c r="AH109" t="n">
-        <v>-0.072287191773165</v>
+        <v>0.009416648791093163</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.02828175908667574</v>
+        <v>0.1489666321125112</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.1084052628874026</v>
+        <v>0.1382481490557412</v>
       </c>
       <c r="AK109" t="n">
-        <v>88</v>
+        <v>184.09619140625</v>
       </c>
       <c r="AL109" t="n">
-        <v>31.45297431945801</v>
+        <v>94.54652404785156</v>
       </c>
       <c r="AM109" t="n">
-        <v>-0.3652272657914595</v>
+        <v>-0.142404828275809</v>
       </c>
       <c r="AN109" t="n">
-        <v>0.7759846824977197</v>
+        <v>0.6698657774336243</v>
       </c>
       <c r="AO109" t="n">
-        <v>47.14419300074758</v>
+        <v>57.51039013762895</v>
       </c>
       <c r="AP109" t="n">
-        <v>9826247</v>
+        <v>3566200</v>
       </c>
       <c r="AQ109" t="n">
-        <v>4263936.5</v>
+        <v>2295006</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.304501251367134</v>
+        <v>1.553895719662607</v>
       </c>
       <c r="AS109" t="n">
-        <v>0.008121291539048281</v>
+        <v>0.02320156681950181</v>
       </c>
       <c r="AT109" t="n">
-        <v>-0.306603744994867</v>
+        <v>-0.142404828275809</v>
       </c>
       <c r="AU109" t="n">
-        <v>0.4512860008941595</v>
+        <v>0.3613239024492931</v>
       </c>
       <c r="AV109" t="n">
-        <v>0.7062695545247528</v>
+        <v>0.6111171622242888</v>
       </c>
       <c r="AW109" t="n">
-        <v>0.6362072044067328</v>
+        <v>4.058980393000525</v>
       </c>
       <c r="AX109" t="n">
-        <v>0.4710527857036872</v>
+        <v>0.4849329199886392</v>
       </c>
       <c r="AY109" t="n">
-        <v>0.1056441948289484</v>
+        <v>7.266885852994021</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21543,12 +21543,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nVent Electric</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -21558,19 +21558,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power distribution / UPS / electrical</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Enclosures, electrical/thermal infra</t>
+          <t>Grid/electrical infrastructure construction</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -21578,7 +21578,11 @@
       <c r="I110" t="n">
         <v>0</v>
       </c>
-      <c r="J110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
       <c r="K110" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21616,7 +21620,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>nVent Electric plc</t>
+          <t>Quanta Services, Inc.</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -21626,7 +21630,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
@@ -21635,7 +21639,7 @@
         </is>
       </c>
       <c r="X110" t="n">
-        <v>25554130944</v>
+        <v>95725142016</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -21646,7 +21650,7 @@
         <v>1</v>
       </c>
       <c r="AA110" t="n">
-        <v>25554130944</v>
+        <v>95725142016</v>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
@@ -21654,73 +21658,73 @@
         </is>
       </c>
       <c r="AC110" s="2" t="n">
-        <v>43214</v>
+        <v>35838</v>
       </c>
       <c r="AD110" t="n">
-        <v>8.4</v>
+        <v>28.6</v>
       </c>
       <c r="AE110" t="n">
-        <v>157.8800048828125</v>
+        <v>636.7100219726562</v>
       </c>
       <c r="AF110" t="n">
-        <v>156.4071734619141</v>
+        <v>642.0926062011719</v>
       </c>
       <c r="AG110" t="n">
-        <v>137.4104351425171</v>
+        <v>595.8852598571777</v>
       </c>
       <c r="AH110" t="n">
-        <v>0.009416648791093163</v>
+        <v>-0.008382878383167647</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.1489666321125112</v>
+        <v>0.06851111256765008</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.1382481490557412</v>
+        <v>0.07754403315005498</v>
       </c>
       <c r="AK110" t="n">
-        <v>184.09619140625</v>
+        <v>785.1200561523438</v>
       </c>
       <c r="AL110" t="n">
-        <v>94.54652404785156</v>
+        <v>388.2493591308594</v>
       </c>
       <c r="AM110" t="n">
-        <v>-0.142404828275809</v>
+        <v>-0.1890284587901168</v>
       </c>
       <c r="AN110" t="n">
-        <v>0.6698657774336243</v>
+        <v>0.6399512503974365</v>
       </c>
       <c r="AO110" t="n">
-        <v>57.51039013762895</v>
+        <v>60.91392411608614</v>
       </c>
       <c r="AP110" t="n">
-        <v>3566200</v>
+        <v>1313500</v>
       </c>
       <c r="AQ110" t="n">
-        <v>2295006</v>
+        <v>1053024</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.553895719662607</v>
+        <v>1.247359984197891</v>
       </c>
       <c r="AS110" t="n">
-        <v>0.02320156681950181</v>
+        <v>-0.03888470401628608</v>
       </c>
       <c r="AT110" t="n">
-        <v>-0.142404828275809</v>
+        <v>-0.1396123468310421</v>
       </c>
       <c r="AU110" t="n">
-        <v>0.3613239024492931</v>
+        <v>0.1468200427578894</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.6111170367897445</v>
+        <v>0.6312613824926443</v>
       </c>
       <c r="AW110" t="n">
-        <v>4.05897946542321</v>
+        <v>4.572819525008383</v>
       </c>
       <c r="AX110" t="n">
-        <v>0.4849329199886392</v>
+        <v>0.4486271875167507</v>
       </c>
       <c r="AY110" t="n">
-        <v>7.266885027361502</v>
+        <v>85.57862917409429</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21735,12 +21739,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -21750,29 +21754,29 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Power distribution / UPS / electrical</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Grid/electrical infrastructure construction</t>
+          <t>Analog/power semiconductors</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
         </is>
       </c>
       <c r="K111" s="1" t="n">
@@ -21812,17 +21816,17 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>Quanta Services, Inc.</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -21831,7 +21835,7 @@
         </is>
       </c>
       <c r="X111" t="n">
-        <v>95725142016</v>
+        <v>243508379648</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -21842,81 +21846,81 @@
         <v>1</v>
       </c>
       <c r="AA111" t="n">
-        <v>95725142016</v>
+        <v>243508379648</v>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC111" s="2" t="n">
-        <v>35838</v>
+        <v>26451</v>
       </c>
       <c r="AD111" t="n">
-        <v>28.6</v>
+        <v>54.3</v>
       </c>
       <c r="AE111" t="n">
-        <v>636.7100219726562</v>
+        <v>266.6400146484375</v>
       </c>
       <c r="AF111" t="n">
-        <v>642.0926062011719</v>
+        <v>273.4529870605469</v>
       </c>
       <c r="AG111" t="n">
-        <v>595.8852603149414</v>
+        <v>242.1380748748779</v>
       </c>
       <c r="AH111" t="n">
-        <v>-0.008382878383167647</v>
+        <v>-0.024914602269826</v>
       </c>
       <c r="AI111" t="n">
-        <v>0.06851111174681157</v>
+        <v>0.1011899503463909</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.07754403232227736</v>
+        <v>0.129326675294047</v>
       </c>
       <c r="AK111" t="n">
-        <v>785.1200561523438</v>
+        <v>330.5873718261719</v>
       </c>
       <c r="AL111" t="n">
-        <v>388.2493591308594</v>
+        <v>150.7934722900391</v>
       </c>
       <c r="AM111" t="n">
-        <v>-0.1890284587901168</v>
+        <v>-0.1934355714330156</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.6399512503974365</v>
+        <v>0.7682464008493481</v>
       </c>
       <c r="AO111" t="n">
-        <v>60.91392411608614</v>
+        <v>57.72798292523304</v>
       </c>
       <c r="AP111" t="n">
-        <v>1313500</v>
+        <v>19052200</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1053024</v>
+        <v>6745596</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.247359984197891</v>
+        <v>2.824390906303905</v>
       </c>
       <c r="AS111" t="n">
-        <v>-0.03888470401628608</v>
+        <v>0.003915694732764985</v>
       </c>
       <c r="AT111" t="n">
-        <v>-0.1396123468310421</v>
+        <v>-0.1934355714330156</v>
       </c>
       <c r="AU111" t="n">
-        <v>0.1468200427578894</v>
+        <v>0.4390030016903705</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.6312612549499887</v>
+        <v>0.5061404382019421</v>
       </c>
       <c r="AW111" t="n">
-        <v>4.572819152875271</v>
+        <v>0.5837417263648716</v>
       </c>
       <c r="AX111" t="n">
-        <v>0.4486271875167507</v>
+        <v>0.5272938179740894</v>
       </c>
       <c r="AY111" t="n">
-        <v>85.5786235603867</v>
+        <v>388.7821504391661</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -21931,12 +21935,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>VICR</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Vicor</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -21951,26 +21955,22 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Analog/power semiconductors</t>
+          <t>High-density power modules</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" s="1" t="n">
         <v>46195</v>
       </c>
@@ -22008,7 +22008,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>Vicor Corporation</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -22018,7 +22018,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -22027,7 +22027,7 @@
         </is>
       </c>
       <c r="X112" t="n">
-        <v>243508379648</v>
+        <v>10268891136</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -22038,81 +22038,81 @@
         <v>1</v>
       </c>
       <c r="AA112" t="n">
-        <v>243508379648</v>
+        <v>10268891136</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC112" s="2" t="n">
-        <v>26451</v>
+        <v>32966</v>
       </c>
       <c r="AD112" t="n">
-        <v>54.3</v>
+        <v>36.5</v>
       </c>
       <c r="AE112" t="n">
-        <v>266.6400146484375</v>
+        <v>222.7200012207031</v>
       </c>
       <c r="AF112" t="n">
-        <v>273.4529870605469</v>
+        <v>211.5211999511719</v>
       </c>
       <c r="AG112" t="n">
-        <v>242.1380748748779</v>
+        <v>207.1982501983643</v>
       </c>
       <c r="AH112" t="n">
-        <v>-0.024914602269826</v>
+        <v>0.05294410807104177</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.1011899503463909</v>
+        <v>0.07491255841918987</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.129326675294047</v>
+        <v>0.02086383330297892</v>
       </c>
       <c r="AK112" t="n">
-        <v>330.5873718261719</v>
+        <v>379.7799987792969</v>
       </c>
       <c r="AL112" t="n">
-        <v>150.7934722900391</v>
+        <v>48.45999908447266</v>
       </c>
       <c r="AM112" t="n">
-        <v>-0.1934355714330156</v>
+        <v>-0.4135552110785767</v>
       </c>
       <c r="AN112" t="n">
-        <v>0.7682464008493481</v>
+        <v>3.595955539175115</v>
       </c>
       <c r="AO112" t="n">
-        <v>57.72798292523304</v>
+        <v>64.25136544332695</v>
       </c>
       <c r="AP112" t="n">
-        <v>19052200</v>
+        <v>1724000</v>
       </c>
       <c r="AQ112" t="n">
-        <v>6745596</v>
+        <v>836050</v>
       </c>
       <c r="AR112" t="n">
-        <v>2.824390906303905</v>
+        <v>2.062077626936188</v>
       </c>
       <c r="AS112" t="n">
-        <v>0.003915694732764985</v>
+        <v>0.07262570735591356</v>
       </c>
       <c r="AT112" t="n">
-        <v>-0.1934355714330156</v>
+        <v>-0.3906929610032388</v>
       </c>
       <c r="AU112" t="n">
-        <v>0.4390030016903705</v>
+        <v>0.3535918944240872</v>
       </c>
       <c r="AV112" t="n">
-        <v>0.5061403083867126</v>
+        <v>3.136701348244662</v>
       </c>
       <c r="AW112" t="n">
-        <v>0.5837418699017518</v>
+        <v>0.7597977679921333</v>
       </c>
       <c r="AX112" t="n">
-        <v>0.5272938179740894</v>
+        <v>0.9058702726121191</v>
       </c>
       <c r="AY112" t="n">
-        <v>388.7822862889078</v>
+        <v>104.5980003472624</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22127,12 +22127,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vicor</t>
+          <t>Delta Electronics</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -22142,16 +22142,16 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>High-density power modules</t>
+          <t>Power supplies, thermal, data center power</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -22200,7 +22200,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>Vicor Corporation</t>
+          <t>Delta Electronics, Inc.</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -22215,22 +22215,22 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X113" t="n">
-        <v>10268891136</v>
+        <v>4506737704960</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>1</v>
+        <v>0.03148317337036133</v>
       </c>
       <c r="AA113" t="n">
-        <v>10268891136</v>
+        <v>141886404500</v>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
@@ -22238,77 +22238,77 @@
         </is>
       </c>
       <c r="AC113" s="2" t="n">
-        <v>32966</v>
+        <v>36529</v>
       </c>
       <c r="AD113" t="n">
-        <v>36.5</v>
+        <v>26.7</v>
       </c>
       <c r="AE113" t="n">
-        <v>222.7200012207031</v>
+        <v>1735</v>
       </c>
       <c r="AF113" t="n">
-        <v>211.5211999511719</v>
+        <v>1750.3</v>
       </c>
       <c r="AG113" t="n">
-        <v>207.1982501983643</v>
+        <v>1618.581174926758</v>
       </c>
       <c r="AH113" t="n">
-        <v>0.05294410807104177</v>
+        <v>-0.008741358624235862</v>
       </c>
       <c r="AI113" t="n">
-        <v>0.07491255841918987</v>
+        <v>0.07192646675784453</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.02086383330297892</v>
+        <v>0.08137919006700578</v>
       </c>
       <c r="AK113" t="n">
-        <v>379.7799987792969</v>
+        <v>2506.891357421875</v>
       </c>
       <c r="AL113" t="n">
-        <v>48.45999908447266</v>
+        <v>779.9217529296875</v>
       </c>
       <c r="AM113" t="n">
-        <v>-0.4135552110785767</v>
+        <v>-0.307907781937427</v>
       </c>
       <c r="AN113" t="n">
-        <v>3.595955539175115</v>
+        <v>1.22458213722424</v>
       </c>
       <c r="AO113" t="n">
-        <v>64.25136544332695</v>
+        <v>40</v>
       </c>
       <c r="AP113" t="n">
-        <v>1724000</v>
+        <v>1635825</v>
       </c>
       <c r="AQ113" t="n">
-        <v>836050</v>
+        <v>11025559.54</v>
       </c>
       <c r="AR113" t="n">
-        <v>2.062077626936188</v>
+        <v>0.1483666197679433</v>
       </c>
       <c r="AS113" t="n">
-        <v>0.07262570735591356</v>
+        <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>-0.3906929610032388</v>
+        <v>-0.1237373737373737</v>
       </c>
       <c r="AU113" t="n">
-        <v>0.3535918944240872</v>
+        <v>0.2325599828364024</v>
       </c>
       <c r="AV113" t="n">
-        <v>3.136701348244662</v>
+        <v>1.22458213722424</v>
       </c>
       <c r="AW113" t="n">
-        <v>0.7597977679921333</v>
+        <v>5.297198406152797</v>
       </c>
       <c r="AX113" t="n">
-        <v>0.9058702726121191</v>
+        <v>0.7528364805935397</v>
       </c>
       <c r="AY113" t="n">
-        <v>104.5979764734289</v>
+        <v>69.23738598601352</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
@@ -22457,13 +22457,13 @@
         <v>26150</v>
       </c>
       <c r="AL114" t="n">
-        <v>16864.4609375</v>
+        <v>16864.458984375</v>
       </c>
       <c r="AM114" t="n">
         <v>-0.2068833652007648</v>
       </c>
       <c r="AN114" t="n">
-        <v>0.2298050958677433</v>
+        <v>0.2298052382952638</v>
       </c>
       <c r="AO114" t="n">
         <v>40.83885209713024</v>
@@ -22490,13 +22490,13 @@
         <v>0.1319610287178528</v>
       </c>
       <c r="AW114" t="n">
-        <v>-0.02426527787757704</v>
+        <v>-0.0242651882204441</v>
       </c>
       <c r="AX114" t="n">
         <v>0.03350354849312032</v>
       </c>
       <c r="AY114" t="n">
-        <v>18.34111688972238</v>
+        <v>18.34110808279942</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22638,28 +22638,28 @@
         <v>1303.066003417969</v>
       </c>
       <c r="AG115" t="n">
-        <v>1261.227660217285</v>
+        <v>1261.227658081055</v>
       </c>
       <c r="AH115" t="n">
         <v>-0.06543487004203108</v>
       </c>
       <c r="AI115" t="n">
-        <v>-0.03443280920565794</v>
+        <v>-0.0344328075702085</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0.03317271300050262</v>
+        <v>0.03317271475046035</v>
       </c>
       <c r="AK115" t="n">
         <v>1687.3154296875</v>
       </c>
       <c r="AL115" t="n">
-        <v>852.5052490234375</v>
+        <v>852.5053100585938</v>
       </c>
       <c r="AM115" t="n">
         <v>-0.2782617716868337</v>
       </c>
       <c r="AN115" t="n">
-        <v>0.4284956605524017</v>
+        <v>0.4284955582791903</v>
       </c>
       <c r="AO115" t="n">
         <v>44.16105686012438</v>
@@ -22683,7 +22683,7 @@
         <v>0.1433752787174214</v>
       </c>
       <c r="AV115" t="n">
-        <v>0.336182257384787</v>
+        <v>0.3361823468667504</v>
       </c>
       <c r="AW115" t="n">
         <v>1.580661166153464</v>
@@ -22692,7 +22692,7 @@
         <v>0.3052265684994455</v>
       </c>
       <c r="AY115" t="n">
-        <v>144.0685667480457</v>
+        <v>144.0685502675341</v>
       </c>
       <c r="AZ115" t="inlineStr"/>
       <c r="BA115" t="n">
@@ -23222,28 +23222,28 @@
         <v>58.92995872497558</v>
       </c>
       <c r="AG118" t="n">
-        <v>56.76989591598511</v>
+        <v>56.76989568710327</v>
       </c>
       <c r="AH118" t="n">
         <v>-0.1449171104154831</v>
       </c>
       <c r="AI118" t="n">
-        <v>-0.1123816844015075</v>
+        <v>-0.1123816808228554</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0.03804944106621577</v>
+        <v>0.038049445251368</v>
       </c>
       <c r="AK118" t="n">
         <v>86.98540496826172</v>
       </c>
       <c r="AL118" t="n">
-        <v>30.38825798034668</v>
+        <v>30.38825988769531</v>
       </c>
       <c r="AM118" t="n">
         <v>-0.4207074231816914</v>
       </c>
       <c r="AN118" t="n">
-        <v>0.6582062526334249</v>
+        <v>0.6582061485544997</v>
       </c>
       <c r="AO118" t="n">
         <v>46.59134208936764</v>
@@ -23264,19 +23264,19 @@
         <v>-0.4207074231816914</v>
       </c>
       <c r="AU118" t="n">
-        <v>0.09206591399361574</v>
+        <v>0.09206600427817135</v>
       </c>
       <c r="AV118" t="n">
         <v>0.1251204381700757</v>
       </c>
       <c r="AW118" t="n">
-        <v>-0.509936798810561</v>
+        <v>-0.509936907897075</v>
       </c>
       <c r="AX118" t="n">
         <v>0.3660195118520955</v>
       </c>
       <c r="AY118" t="n">
-        <v>28.00329786626735</v>
+        <v>28.00329587623342</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23418,28 +23418,28 @@
         <v>459.0618786621094</v>
       </c>
       <c r="AG119" t="n">
-        <v>443.4044960021973</v>
+        <v>443.4044963073731</v>
       </c>
       <c r="AH119" t="n">
         <v>-0.06524587360169987</v>
       </c>
       <c r="AI119" t="n">
-        <v>-0.03223808233681946</v>
+        <v>-0.03223808300288733</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0.03531173635152896</v>
+        <v>0.03531173563896939</v>
       </c>
       <c r="AK119" t="n">
         <v>502.2725524902344</v>
       </c>
       <c r="AL119" t="n">
-        <v>373.7903137207031</v>
+        <v>373.790283203125</v>
       </c>
       <c r="AM119" t="n">
         <v>-0.145663080285667</v>
       </c>
       <c r="AN119" t="n">
-        <v>0.1479965360263304</v>
+        <v>0.1479966297528812</v>
       </c>
       <c r="AO119" t="n">
         <v>34.03800619144323</v>
@@ -23460,19 +23460,19 @@
         <v>-0.12503413101381</v>
       </c>
       <c r="AU119" t="n">
-        <v>0.05054231030495671</v>
+        <v>0.0505422318160087</v>
       </c>
       <c r="AV119" t="n">
         <v>0.07366733795010583</v>
       </c>
       <c r="AW119" t="n">
-        <v>1.415143404912981</v>
+        <v>1.415143819740315</v>
       </c>
       <c r="AX119" t="n">
         <v>0.08577976727790504</v>
       </c>
       <c r="AY119" t="n">
-        <v>481.4688846086289</v>
+        <v>481.4689169419364</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23587,10 +23587,10 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>1.148897051811218</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA120" t="n">
-        <v>40895020926.86719</v>
+        <v>40899722456.52344</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>0.07986402612216614</v>
       </c>
       <c r="AY120" t="n">
-        <v>9.029143946489867</v>
+        <v>9.02914465285307</v>
       </c>
       <c r="AZ120" t="inlineStr"/>
       <c r="BA120" t="n">
@@ -23806,16 +23806,16 @@
         <v>62.11169738769532</v>
       </c>
       <c r="AG121" t="n">
-        <v>61.22489225387573</v>
+        <v>61.22489198684693</v>
       </c>
       <c r="AH121" t="n">
         <v>-0.1325305323439901</v>
       </c>
       <c r="AI121" t="n">
-        <v>-0.1199657674415187</v>
+        <v>-0.1199657636033006</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0.01448438863954804</v>
+        <v>0.01448439306416249</v>
       </c>
       <c r="AK121" t="n">
         <v>75.72768402099609</v>
@@ -23854,13 +23854,13 @@
         <v>-0.1046040279356727</v>
       </c>
       <c r="AW121" t="n">
-        <v>0.03758150825271511</v>
+        <v>0.03758158447412208</v>
       </c>
       <c r="AX121" t="n">
         <v>0.01829471785604064</v>
       </c>
       <c r="AY121" t="n">
-        <v>3.890086840012014</v>
+        <v>3.890087263270497</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -24000,28 +24000,28 @@
         <v>271.3915585327148</v>
       </c>
       <c r="AG122" t="n">
-        <v>260.9728151702881</v>
+        <v>260.9728160095215</v>
       </c>
       <c r="AH122" t="n">
         <v>-0.08106943068538452</v>
       </c>
       <c r="AI122" t="n">
-        <v>-0.04438322732228528</v>
+        <v>-0.04438323039534675</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0.03992271515187662</v>
+        <v>0.03992271180770501</v>
       </c>
       <c r="AK122" t="n">
         <v>376.0595397949219</v>
       </c>
       <c r="AL122" t="n">
-        <v>138.4725494384766</v>
+        <v>138.4725341796875</v>
       </c>
       <c r="AM122" t="n">
         <v>-0.3368337377489498</v>
       </c>
       <c r="AN122" t="n">
-        <v>0.801006772829387</v>
+        <v>0.8010069712888332</v>
       </c>
       <c r="AO122" t="n">
         <v>47.02128965552175</v>
@@ -24045,16 +24045,16 @@
         <v>-0.02492173403083386</v>
       </c>
       <c r="AV122" t="n">
-        <v>0.7586330155338166</v>
+        <v>0.7586328263031876</v>
       </c>
       <c r="AW122" t="n">
-        <v>9.456562605013724</v>
+        <v>9.456561768777652</v>
       </c>
       <c r="AX122" t="n">
-        <v>0.4211173180082892</v>
+        <v>0.4211171944417562</v>
       </c>
       <c r="AY122" t="n">
-        <v>24.10288102345088</v>
+        <v>24.10288584290963</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
@@ -24240,13 +24240,13 @@
         <v>0.04667960978023689</v>
       </c>
       <c r="AW123" t="n">
-        <v>0.6646915622955083</v>
+        <v>0.664691724930623</v>
       </c>
       <c r="AX123" t="n">
         <v>-0.3247707026975789</v>
       </c>
       <c r="AY123" t="n">
-        <v>1.083750853281554</v>
+        <v>1.083751108104396</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
@@ -24630,7 +24630,7 @@
         <v>0.3402457530913108</v>
       </c>
       <c r="AY125" t="n">
-        <v>212.7993327929484</v>
+        <v>212.7992894821658</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24859,10 +24859,10 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>1.148897051811218</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA127" t="n">
-        <v>236661005614.3594</v>
+        <v>236688213541.1719</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -24930,13 +24930,13 @@
         <v>0.1804402632139313</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.182109593674803</v>
+        <v>1.182109731281412</v>
       </c>
       <c r="AX127" t="n">
         <v>0.1182602159218009</v>
       </c>
       <c r="AY127" t="n">
-        <v>26.77121875758676</v>
+        <v>26.77122154361865</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -25051,10 +25051,10 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>1.148897051811218</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA128" t="n">
-        <v>16970203425.83386</v>
+        <v>16972154419.20349</v>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>0.2597364359398946</v>
       </c>
       <c r="AY128" t="n">
-        <v>87.63326846795277</v>
+        <v>87.63324839849948</v>
       </c>
       <c r="AZ128" t="inlineStr"/>
       <c r="BA128" t="n">
@@ -25662,28 +25662,28 @@
         <v>416.3257373046875</v>
       </c>
       <c r="AG131" t="n">
-        <v>377.4277185058594</v>
+        <v>377.4277194213867</v>
       </c>
       <c r="AH131" t="n">
         <v>0.04406231582464382</v>
       </c>
       <c r="AI131" t="n">
-        <v>0.1516642581220127</v>
+        <v>0.151664255328418</v>
       </c>
       <c r="AJ131" t="n">
-        <v>0.1030608428888464</v>
+        <v>0.103060840213149</v>
       </c>
       <c r="AK131" t="n">
         <v>476.2922668457031</v>
       </c>
       <c r="AL131" t="n">
-        <v>262.0960388183594</v>
+        <v>262.0960693359375</v>
       </c>
       <c r="AM131" t="n">
         <v>-0.087388052074867</v>
       </c>
       <c r="AN131" t="n">
-        <v>0.6584379351454985</v>
+        <v>0.6584377420426055</v>
       </c>
       <c r="AO131" t="n">
         <v>60.61484028006096</v>
@@ -25707,16 +25707,16 @@
         <v>0.32686427316999</v>
       </c>
       <c r="AV131" t="n">
-        <v>0.6351637302846667</v>
+        <v>0.6351639180056954</v>
       </c>
       <c r="AW131" t="n">
-        <v>2.824706177417068</v>
+        <v>2.824706434176601</v>
       </c>
       <c r="AX131" t="n">
         <v>0.3706948377364665</v>
       </c>
       <c r="AY131" t="n">
-        <v>138.561176977259</v>
+        <v>138.561112876863</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25902,13 +25902,13 @@
         <v>1.693306044001586</v>
       </c>
       <c r="AW132" t="n">
-        <v>13.63827862671134</v>
+        <v>13.63827699444138</v>
       </c>
       <c r="AX132" t="n">
         <v>0.5156375397010196</v>
       </c>
       <c r="AY132" t="n">
-        <v>12.51452378312531</v>
+        <v>12.51452100057249</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26046,16 +26046,16 @@
         <v>38501</v>
       </c>
       <c r="AG133" t="n">
-        <v>37526.30203125</v>
+        <v>37526.30201171875</v>
       </c>
       <c r="AH133" t="n">
         <v>0.0152983039401573</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.04166938611344739</v>
+        <v>0.04166938665560327</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.02597372818505583</v>
+        <v>0.02597372871904269</v>
       </c>
       <c r="AK133" t="n">
         <v>57263.48828125</v>
@@ -26094,13 +26094,13 @@
         <v>1.463629027746243</v>
       </c>
       <c r="AW133" t="n">
-        <v>0.9236254360434102</v>
+        <v>0.9236250662703198</v>
       </c>
       <c r="AX133" t="n">
         <v>0.2376103419139981</v>
       </c>
       <c r="AY133" t="n">
-        <v>300.2575049719557</v>
+        <v>300.2575403986149</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26290,13 +26290,13 @@
         <v>1.628404334148304</v>
       </c>
       <c r="AW134" t="n">
-        <v>3.059467089249153</v>
+        <v>3.059466483222502</v>
       </c>
       <c r="AX134" t="n">
         <v>0.4515742444904405</v>
       </c>
       <c r="AY134" t="n">
-        <v>18.60006379027775</v>
+        <v>18.60005849242531</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26438,16 +26438,16 @@
         <v>500.7875982666015</v>
       </c>
       <c r="AG135" t="n">
-        <v>415.5235311889649</v>
+        <v>415.5235307312012</v>
       </c>
       <c r="AH135" t="n">
         <v>-0.1122583529164285</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.06990332425251888</v>
+        <v>0.0699033254311836</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.2051967233568337</v>
+        <v>0.205196724684545</v>
       </c>
       <c r="AK135" t="n">
         <v>722.2277221679688</v>
@@ -26480,13 +26480,13 @@
         <v>-0.3048120711944303</v>
       </c>
       <c r="AU135" t="n">
-        <v>0.247965841558204</v>
+        <v>0.2479657346489583</v>
       </c>
       <c r="AV135" t="n">
         <v>1.355759617487642</v>
       </c>
       <c r="AW135" t="n">
-        <v>2.322900372888141</v>
+        <v>2.322900751866665</v>
       </c>
       <c r="AX135" t="n">
         <v>0.6593686055110328</v>
@@ -26607,10 +26607,10 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>1.148897051811218</v>
+        <v>1.149029135704041</v>
       </c>
       <c r="AA136" t="n">
-        <v>45642578544.94922</v>
+        <v>45647825881.46484</v>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>0.4752049313867512</v>
       </c>
       <c r="AY136" t="n">
-        <v>275.8739774563435</v>
+        <v>275.8739549975377</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26826,28 +26826,28 @@
         <v>1721.602231445313</v>
       </c>
       <c r="AG137" t="n">
-        <v>1506.139687194824</v>
+        <v>1506.139679870606</v>
       </c>
       <c r="AH137" t="n">
         <v>-0.02421127641372023</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.1153813011023919</v>
+        <v>0.1153813065263884</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.1430561494941986</v>
+        <v>0.1430561550527756</v>
       </c>
       <c r="AK137" t="n">
         <v>1986.870361328125</v>
       </c>
       <c r="AL137" t="n">
-        <v>921.7288818359375</v>
+        <v>921.7289428710938</v>
       </c>
       <c r="AM137" t="n">
         <v>-0.1544893533857092</v>
       </c>
       <c r="AN137" t="n">
-        <v>0.8225750294372665</v>
+        <v>0.8225749087497773</v>
       </c>
       <c r="AO137" t="n">
         <v>48.43593638313081</v>
@@ -26871,16 +26871,16 @@
         <v>0.2797622092036016</v>
       </c>
       <c r="AV137" t="n">
-        <v>0.8225750294372665</v>
+        <v>0.8225749087497773</v>
       </c>
       <c r="AW137" t="n">
-        <v>1.020996361608705</v>
+        <v>1.020996213212607</v>
       </c>
       <c r="AX137" t="n">
         <v>0.4504375267308354</v>
       </c>
       <c r="AY137" t="n">
-        <v>953.6314831603511</v>
+        <v>953.6312891547983</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27022,28 +27022,28 @@
         <v>192.6250076293945</v>
       </c>
       <c r="AG138" t="n">
-        <v>173.9582666397095</v>
+        <v>173.9582667160034</v>
       </c>
       <c r="AH138" t="n">
         <v>-0.08116808055531299</v>
       </c>
       <c r="AI138" t="n">
-        <v>0.01742796655782808</v>
+        <v>0.01742796611160857</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0.1073058576074819</v>
+        <v>0.1073058571218442</v>
       </c>
       <c r="AK138" t="n">
         <v>301.3693542480469</v>
       </c>
       <c r="AL138" t="n">
-        <v>97.74768829345703</v>
+        <v>97.74769592285156</v>
       </c>
       <c r="AM138" t="n">
         <v>-0.4127139903299869</v>
       </c>
       <c r="AN138" t="n">
-        <v>0.8106822635212265</v>
+        <v>0.8106821221940144</v>
       </c>
       <c r="AO138" t="n">
         <v>51.19029069106202</v>
@@ -27067,16 +27067,16 @@
         <v>0.1838242963679655</v>
       </c>
       <c r="AV138" t="n">
-        <v>0.7000715910365882</v>
+        <v>0.7000717156244645</v>
       </c>
       <c r="AW138" t="n">
-        <v>4.225207335920511</v>
+        <v>4.225206158996864</v>
       </c>
       <c r="AX138" t="n">
-        <v>0.3938871997547555</v>
+        <v>0.3938871160024897</v>
       </c>
       <c r="AY138" t="n">
-        <v>2919.401062965564</v>
+        <v>2919.402319558463</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27414,28 +27414,28 @@
         <v>364.1425073242187</v>
       </c>
       <c r="AG140" t="n">
-        <v>324.6456483459473</v>
+        <v>324.6456481170654</v>
       </c>
       <c r="AH140" t="n">
         <v>0.02012259966661967</v>
       </c>
       <c r="AI140" t="n">
-        <v>0.1442321901227492</v>
+        <v>0.1442321909294564</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0.1216614458857093</v>
+        <v>0.1216614466765036</v>
       </c>
       <c r="AK140" t="n">
         <v>483.6542053222656</v>
       </c>
       <c r="AL140" t="n">
-        <v>118.5902862548828</v>
+        <v>118.5903015136719</v>
       </c>
       <c r="AM140" t="n">
         <v>-0.2319512636653548</v>
       </c>
       <c r="AN140" t="n">
-        <v>2.13238135223245</v>
+        <v>2.132380949194885</v>
       </c>
       <c r="AO140" t="n">
         <v>54.38399335538768</v>
@@ -27459,16 +27459,16 @@
         <v>0.2782486954014218</v>
       </c>
       <c r="AV140" t="n">
-        <v>2.13238135223245</v>
+        <v>2.132380949194885</v>
       </c>
       <c r="AW140" t="n">
-        <v>2.095339709564181</v>
+        <v>2.095340299907024</v>
       </c>
       <c r="AX140" t="n">
         <v>0.7918118677831085</v>
       </c>
       <c r="AY140" t="n">
-        <v>332.6556506588597</v>
+        <v>332.6556149329517</v>
       </c>
       <c r="AZ140" t="inlineStr"/>
       <c r="BA140" t="n">
@@ -27654,7 +27654,7 @@
         <v>2.582685653385002</v>
       </c>
       <c r="AW141" t="n">
-        <v>1.653678593732534</v>
+        <v>1.653678866620981</v>
       </c>
       <c r="AX141" t="n">
         <v>2.194256702915672</v>
@@ -28232,13 +28232,13 @@
         <v>0.4011122848949473</v>
       </c>
       <c r="AW144" t="n">
-        <v>4.524386231395053</v>
+        <v>4.524385662841929</v>
       </c>
       <c r="AX144" t="n">
         <v>0.03166224722217703</v>
       </c>
       <c r="AY144" t="n">
-        <v>34.86929391245137</v>
+        <v>34.86928792021939</v>
       </c>
       <c r="AZ144" t="inlineStr"/>
       <c r="BA144" t="n">
@@ -28620,13 +28620,13 @@
         <v>3.354695116551942</v>
       </c>
       <c r="AW146" t="n">
-        <v>11.47631537563328</v>
+        <v>11.47631223975133</v>
       </c>
       <c r="AX146" t="n">
         <v>3.485572887887606</v>
       </c>
       <c r="AY146" t="n">
-        <v>50.81887485129307</v>
+        <v>50.81887935927197</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28768,16 +28768,16 @@
         <v>52.34456520080566</v>
       </c>
       <c r="AG147" t="n">
-        <v>34.71637151718139</v>
+        <v>34.71637149810791</v>
       </c>
       <c r="AH147" t="n">
         <v>0.1607699498208464</v>
       </c>
       <c r="AI147" t="n">
-        <v>0.7501828580058438</v>
+        <v>0.7501828589674098</v>
       </c>
       <c r="AJ147" t="n">
-        <v>0.5077775387586212</v>
+        <v>0.5077775395870074</v>
       </c>
       <c r="AK147" t="n">
         <v>61.933349609375</v>
@@ -28813,16 +28813,16 @@
         <v>1.834754504200866</v>
       </c>
       <c r="AV147" t="n">
-        <v>1.450697953839629</v>
+        <v>1.450697765304678</v>
       </c>
       <c r="AW147" t="n">
-        <v>3.866106205443909</v>
+        <v>3.866106948763472</v>
       </c>
       <c r="AX147" t="n">
         <v>1.543890213177134</v>
       </c>
       <c r="AY147" t="n">
-        <v>7.454317125354608</v>
+        <v>7.45431656442369</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -28960,16 +28960,16 @@
         <v>1469.131345214844</v>
       </c>
       <c r="AG148" t="n">
-        <v>1304.952167358398</v>
+        <v>1304.952168579101</v>
       </c>
       <c r="AH148" t="n">
         <v>-0.01302221566312445</v>
       </c>
       <c r="AI148" t="n">
-        <v>0.1111518385652561</v>
+        <v>0.1111518375258413</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0.1258124105719458</v>
+        <v>0.1258124095188171</v>
       </c>
       <c r="AK148" t="n">
         <v>1570.339965820312</v>
@@ -29008,13 +29008,13 @@
         <v>0.2609731650422196</v>
       </c>
       <c r="AW148" t="n">
-        <v>11.12827583495869</v>
+        <v>11.12827660892175</v>
       </c>
       <c r="AX148" t="n">
         <v>0.2114613150123743</v>
       </c>
       <c r="AY148" t="n">
-        <v>10.64557154382083</v>
+        <v>10.64557225740255</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29149,64 +29149,64 @@
         <v>186.5</v>
       </c>
       <c r="AF149" t="n">
-        <v>177.75</v>
+        <v>178.61</v>
       </c>
       <c r="AG149" t="n">
-        <v>147.7825833129883</v>
+        <v>148.0422565460205</v>
       </c>
       <c r="AH149" t="n">
-        <v>0.04922644163150491</v>
+        <v>0.0441744583170034</v>
       </c>
       <c r="AI149" t="n">
-        <v>0.2619890369964111</v>
+        <v>0.259775447573136</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0.2027804360649441</v>
+        <v>0.2064798535712484</v>
       </c>
       <c r="AK149" t="n">
         <v>198</v>
       </c>
       <c r="AL149" t="n">
-        <v>110.4496994018555</v>
+        <v>111.8966369628906</v>
       </c>
       <c r="AM149" t="n">
         <v>-0.05808080808080807</v>
       </c>
       <c r="AN149" t="n">
-        <v>0.6885514493022418</v>
+        <v>0.666716758090333</v>
       </c>
       <c r="AO149" t="n">
-        <v>58.76288659793814</v>
+        <v>55.05617977528089</v>
       </c>
       <c r="AP149" t="n">
-        <v>39701494</v>
+        <v>8195926</v>
       </c>
       <c r="AQ149" t="n">
-        <v>69306072.31999999</v>
+        <v>68939826.09999999</v>
       </c>
       <c r="AR149" t="n">
-        <v>0.5728429367154189</v>
+        <v>0.1188852143043047</v>
       </c>
       <c r="AS149" t="n">
         <v>0.06267806267806275</v>
       </c>
       <c r="AT149" t="n">
-        <v>0.2275501531918809</v>
+        <v>0.2083696043011658</v>
       </c>
       <c r="AU149" t="n">
-        <v>0.5405509560865744</v>
+        <v>0.4987530791358059</v>
       </c>
       <c r="AV149" t="n">
-        <v>0.6885514493022418</v>
+        <v>0.666716758090333</v>
       </c>
       <c r="AW149" t="n">
-        <v>6.766183959343772</v>
+        <v>6.790722320325838</v>
       </c>
       <c r="AX149" t="n">
         <v>0.24734930475826</v>
       </c>
       <c r="AY149" t="n">
-        <v>37.85914878223522</v>
+        <v>37.85914492143101</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29341,19 +29341,19 @@
         <v>90.30000305175781</v>
       </c>
       <c r="AF150" t="n">
-        <v>88.25400009155274</v>
+        <v>88.40800018310547</v>
       </c>
       <c r="AG150" t="n">
-        <v>77.74979339599609</v>
+        <v>77.86588802337647</v>
       </c>
       <c r="AH150" t="n">
-        <v>0.02318311870377077</v>
+        <v>0.02140081061367449</v>
       </c>
       <c r="AI150" t="n">
-        <v>0.1614179164675185</v>
+        <v>0.1596862932411229</v>
       </c>
       <c r="AJ150" t="n">
-        <v>0.1351026959268755</v>
+        <v>0.1353880682201185</v>
       </c>
       <c r="AK150" t="n">
         <v>95.40000152587891</v>
@@ -29368,37 +29368,37 @@
         <v>0.3816084942094857</v>
       </c>
       <c r="AO150" t="n">
-        <v>47.56098752360346</v>
+        <v>47.85276848936002</v>
       </c>
       <c r="AP150" t="n">
-        <v>9004119</v>
+        <v>456950</v>
       </c>
       <c r="AQ150" t="n">
-        <v>11896565.82</v>
+        <v>11749066.74</v>
       </c>
       <c r="AR150" t="n">
-        <v>0.7568670771242788</v>
+        <v>0.03889245078881899</v>
       </c>
       <c r="AS150" t="n">
-        <v>0.01918741091325482</v>
+        <v>0.01119820790398407</v>
       </c>
       <c r="AT150" t="n">
-        <v>0.07500003633045016</v>
+        <v>0.05000003548555587</v>
       </c>
       <c r="AU150" t="n">
-        <v>0.2465504435881201</v>
+        <v>0.2351291809576961</v>
       </c>
       <c r="AV150" t="n">
-        <v>0.3328229123253386</v>
+        <v>0.3347082847910965</v>
       </c>
       <c r="AW150" t="n">
-        <v>0.7348653151953131</v>
+        <v>0.7374202635385925</v>
       </c>
       <c r="AX150" t="n">
         <v>0.3695771284661926</v>
       </c>
       <c r="AY150" t="n">
-        <v>-0.05635186832460026</v>
+        <v>-0.05635209403087271</v>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="n">
@@ -29413,12 +29413,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Hon Hai / Foxconn</t>
+          <t>Super Micro Computer</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -29428,19 +29428,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Server ODM</t>
+          <t>AI servers / rack integration</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ODM, AI server manufacturing</t>
+          <t>AI servers/racks</t>
         </is>
       </c>
       <c r="F151" t="n">
         <v>8</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -29450,7 +29450,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>STOXX Global AI Infrastructure</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="K151" s="1" t="n">
@@ -29472,10 +29472,10 @@
         </is>
       </c>
       <c r="O151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q151" s="1" t="n">
         <v>46192</v>
@@ -29490,7 +29490,7 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>Hon Hai Precision Industry Co., Ltd.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -29500,27 +29500,27 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X151" t="n">
-        <v>3509923872768</v>
+        <v>25680777216</v>
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>0.03148317337036133</v>
+        <v>1</v>
       </c>
       <c r="AA151" t="n">
-        <v>110503541803.125</v>
+        <v>25680777216</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
@@ -29528,73 +29528,73 @@
         </is>
       </c>
       <c r="AC151" s="2" t="n">
-        <v>33974</v>
+        <v>39170</v>
       </c>
       <c r="AD151" t="n">
-        <v>33.7</v>
+        <v>19.5</v>
       </c>
       <c r="AE151" t="n">
-        <v>250.5</v>
+        <v>39.09000015258789</v>
       </c>
       <c r="AF151" t="n">
-        <v>249.69</v>
+        <v>33.5567998123169</v>
       </c>
       <c r="AG151" t="n">
-        <v>231.6492882537842</v>
+        <v>31.60359992027283</v>
       </c>
       <c r="AH151" t="n">
-        <v>0.003244022588009043</v>
+        <v>0.1648905846570046</v>
       </c>
       <c r="AI151" t="n">
-        <v>0.08137608316570288</v>
+        <v>0.2368844135225476</v>
       </c>
       <c r="AJ151" t="n">
-        <v>0.07787941798660403</v>
+        <v>0.06180308246438559</v>
       </c>
       <c r="AK151" t="n">
-        <v>300.0641784667969</v>
+        <v>58.68000030517578</v>
       </c>
       <c r="AL151" t="n">
-        <v>182.0777740478516</v>
+        <v>20.53000068664551</v>
       </c>
       <c r="AM151" t="n">
-        <v>-0.1651785918600788</v>
+        <v>-0.3338445816412169</v>
       </c>
       <c r="AN151" t="n">
-        <v>0.375785711957169</v>
+        <v>0.9040428078512153</v>
       </c>
       <c r="AO151" t="n">
-        <v>50.64935064935064</v>
+        <v>54.93857396215331</v>
       </c>
       <c r="AP151" t="n">
-        <v>43948586</v>
+        <v>47970800</v>
       </c>
       <c r="AQ151" t="n">
-        <v>42496976.74</v>
+        <v>47077462</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.034157941843277</v>
+        <v>1.01897591675609</v>
       </c>
       <c r="AS151" t="n">
-        <v>0.02036659877800417</v>
+        <v>0.07095890829007923</v>
       </c>
       <c r="AT151" t="n">
-        <v>0.007655515784268596</v>
+        <v>0.1023688990929712</v>
       </c>
       <c r="AU151" t="n">
-        <v>0.3161215097875545</v>
+        <v>0.9040428078512153</v>
       </c>
       <c r="AV151" t="n">
-        <v>0.2676158000423445</v>
+        <v>-0.1491075028055961</v>
       </c>
       <c r="AW151" t="n">
-        <v>1.622598759403955</v>
+        <v>9.527874907109542</v>
       </c>
       <c r="AX151" t="n">
-        <v>0.111895732141569</v>
+        <v>0.2625969414899842</v>
       </c>
       <c r="AY151" t="n">
-        <v>682.8718288473777</v>
+        <v>43.62328850125003</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29609,12 +29609,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Super Micro Computer</t>
+          <t>Hon Hai / Foxconn</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -29624,19 +29624,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>AI servers / rack integration</t>
+          <t>Server ODM</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AI servers/racks</t>
+          <t>ODM, AI server manufacturing</t>
         </is>
       </c>
       <c r="F152" t="n">
         <v>8</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>STOXX Global AI Infrastructure</t>
         </is>
       </c>
       <c r="K152" s="1" t="n">
@@ -29668,10 +29668,10 @@
         </is>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q152" s="1" t="n">
         <v>46192</v>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Hon Hai Precision Industry Co., Ltd.</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -29696,27 +29696,27 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X152" t="n">
-        <v>25680777216</v>
+        <v>3509923872768</v>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>1</v>
+        <v>0.03148317337036133</v>
       </c>
       <c r="AA152" t="n">
-        <v>25680777216</v>
+        <v>110503541803.125</v>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
@@ -29724,77 +29724,77 @@
         </is>
       </c>
       <c r="AC152" s="2" t="n">
-        <v>39170</v>
+        <v>33974</v>
       </c>
       <c r="AD152" t="n">
-        <v>19.5</v>
+        <v>33.7</v>
       </c>
       <c r="AE152" t="n">
-        <v>39.09000015258789</v>
+        <v>250.5</v>
       </c>
       <c r="AF152" t="n">
-        <v>33.5567998123169</v>
+        <v>249.97</v>
       </c>
       <c r="AG152" t="n">
-        <v>31.60359992027283</v>
+        <v>231.8384539794922</v>
       </c>
       <c r="AH152" t="n">
-        <v>0.1648905846570046</v>
+        <v>0.002120254430531654</v>
       </c>
       <c r="AI152" t="n">
-        <v>0.2368844135225476</v>
+        <v>0.08049374769449846</v>
       </c>
       <c r="AJ152" t="n">
-        <v>0.06180308246438559</v>
+        <v>0.0782076730985779</v>
       </c>
       <c r="AK152" t="n">
-        <v>58.68000030517578</v>
+        <v>300.0641784667969</v>
       </c>
       <c r="AL152" t="n">
-        <v>20.53000068664551</v>
+        <v>182.0777740478516</v>
       </c>
       <c r="AM152" t="n">
-        <v>-0.3338445816412169</v>
+        <v>-0.1651785918600788</v>
       </c>
       <c r="AN152" t="n">
-        <v>0.9040428078512153</v>
+        <v>0.375785711957169</v>
       </c>
       <c r="AO152" t="n">
-        <v>54.93857396215331</v>
+        <v>41.53846153846154</v>
       </c>
       <c r="AP152" t="n">
-        <v>47970800</v>
+        <v>7418117</v>
       </c>
       <c r="AQ152" t="n">
-        <v>47077462</v>
+        <v>41910168.98</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.01897591675609</v>
+        <v>0.1770004077898137</v>
       </c>
       <c r="AS152" t="n">
-        <v>0.07095890829007923</v>
+        <v>0.02874743326488716</v>
       </c>
       <c r="AT152" t="n">
-        <v>0.1023688990929712</v>
+        <v>0.001785689767905385</v>
       </c>
       <c r="AU152" t="n">
-        <v>0.9040428078512153</v>
+        <v>0.322870872617991</v>
       </c>
       <c r="AV152" t="n">
-        <v>-0.1491075028055961</v>
+        <v>0.2431798501605207</v>
       </c>
       <c r="AW152" t="n">
-        <v>9.527874907109542</v>
+        <v>1.69013366385996</v>
       </c>
       <c r="AX152" t="n">
-        <v>0.2625969414899842</v>
+        <v>0.111895732141569</v>
       </c>
       <c r="AY152" t="n">
-        <v>43.62328850125003</v>
+        <v>682.871995769219</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
@@ -29919,25 +29919,25 @@
         <v>43052</v>
       </c>
       <c r="AD153" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AE153" t="n">
         <v>2140</v>
       </c>
       <c r="AF153" t="n">
-        <v>2078.892687988281</v>
+        <v>2088.435285644531</v>
       </c>
       <c r="AG153" t="n">
-        <v>1596.028107910156</v>
+        <v>1599.934765625</v>
       </c>
       <c r="AH153" t="n">
-        <v>0.02939416371263093</v>
+        <v>0.02469059717096034</v>
       </c>
       <c r="AI153" t="n">
-        <v>0.3408285163612326</v>
+        <v>0.3375545340837871</v>
       </c>
       <c r="AJ153" t="n">
-        <v>0.302541401172683</v>
+        <v>0.3053252735768279</v>
       </c>
       <c r="AK153" t="n">
         <v>2614.997314453125</v>
@@ -29952,37 +29952,37 @@
         <v>1.182075677132989</v>
       </c>
       <c r="AO153" t="n">
-        <v>38.43063937046047</v>
+        <v>20.12585414959084</v>
       </c>
       <c r="AP153" t="n">
-        <v>3936746</v>
+        <v>621853</v>
       </c>
       <c r="AQ153" t="n">
-        <v>4661899.14</v>
+        <v>4612306.2</v>
       </c>
       <c r="AR153" t="n">
-        <v>0.8444511307037844</v>
+        <v>0.1348247434222819</v>
       </c>
       <c r="AS153" t="n">
-        <v>0.02049253378079841</v>
+        <v>0.01320323062099016</v>
       </c>
       <c r="AT153" t="n">
-        <v>0.3861412129463044</v>
+        <v>0.4044400991502564</v>
       </c>
       <c r="AU153" t="n">
-        <v>0.8019335534124163</v>
+        <v>0.7632343557768826</v>
       </c>
       <c r="AV153" t="n">
-        <v>1.101775497525113</v>
+        <v>1.182075677132989</v>
       </c>
       <c r="AW153" t="n">
-        <v>6.475205512527429</v>
+        <v>6.548853551195602</v>
       </c>
       <c r="AX153" t="n">
         <v>0.4660821811130258</v>
       </c>
       <c r="AY153" t="n">
-        <v>75.10813579904477</v>
+        <v>75.10814612448394</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30172,13 +30172,13 @@
         <v>0.3285339151152953</v>
       </c>
       <c r="AW154" t="n">
-        <v>1.103868385192169</v>
+        <v>1.103868149501933</v>
       </c>
       <c r="AX154" t="n">
         <v>0.1783121747405956</v>
       </c>
       <c r="AY154" t="n">
-        <v>45.39710326862783</v>
+        <v>45.39712834325791</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30193,12 +30193,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2382.TW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Quanta Computer</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -30208,27 +30208,31 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Server ODM</t>
+          <t>AI servers / rack integration</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AI server ODM/QCT</t>
+          <t>Networking, UCS servers, data center networking</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
-      <c r="J155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100, STOXX Global AI Infrastructure</t>
+        </is>
+      </c>
       <c r="K155" s="1" t="n">
         <v>46195</v>
       </c>
@@ -30248,10 +30252,10 @@
         </is>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q155" s="1" t="n">
         <v>46192</v>
@@ -30266,7 +30270,7 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>Quanta Computer Inc.</t>
+          <t>Cisco Systems, Inc.</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
@@ -30276,101 +30280,101 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X155" t="n">
-        <v>1406134779904</v>
+        <v>431752708096</v>
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>0.03148317337036133</v>
+        <v>1</v>
       </c>
       <c r="AA155" t="n">
-        <v>44269585057.8125</v>
+        <v>431752708096</v>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC155" s="2" t="n">
-        <v>36529</v>
+        <v>32920</v>
       </c>
       <c r="AD155" t="n">
-        <v>26.7</v>
+        <v>36.6</v>
       </c>
       <c r="AE155" t="n">
-        <v>343</v>
+        <v>109.5100021362305</v>
       </c>
       <c r="AF155" t="n">
-        <v>327.977275390625</v>
+        <v>113.2683996582031</v>
       </c>
       <c r="AG155" t="n">
-        <v>305.1640489959717</v>
+        <v>95.77699035644531</v>
       </c>
       <c r="AH155" t="n">
-        <v>0.04580416308258783</v>
+        <v>-0.03318134213349822</v>
       </c>
       <c r="AI155" t="n">
-        <v>0.1239856107838175</v>
+        <v>0.1433852925287811</v>
       </c>
       <c r="AJ155" t="n">
-        <v>0.07475725423657131</v>
+        <v>0.1826264245374749</v>
       </c>
       <c r="AK155" t="n">
-        <v>399.9259948730469</v>
+        <v>129.5154876708984</v>
       </c>
       <c r="AL155" t="n">
-        <v>249.3543395996094</v>
+        <v>65.85634613037109</v>
       </c>
       <c r="AM155" t="n">
-        <v>-0.1423413221516585</v>
+        <v>-0.1544640405130723</v>
       </c>
       <c r="AN155" t="n">
-        <v>0.3755525592646927</v>
+        <v>0.6628617980026004</v>
       </c>
       <c r="AO155" t="n">
-        <v>52.83018867924528</v>
+        <v>48.80952792862617</v>
       </c>
       <c r="AP155" t="n">
-        <v>21255470</v>
+        <v>41260700</v>
       </c>
       <c r="AQ155" t="n">
-        <v>19886809.58</v>
+        <v>19425620</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.068822523517118</v>
+        <v>2.124035165930354</v>
       </c>
       <c r="AS155" t="n">
-        <v>0.06687402799377917</v>
+        <v>-0.0007299407275598302</v>
       </c>
       <c r="AT155" t="n">
-        <v>-0.03859223529351385</v>
+        <v>-0.09553465409672146</v>
       </c>
       <c r="AU155" t="n">
-        <v>0.2772988608615004</v>
+        <v>0.4232489694512562</v>
       </c>
       <c r="AV155" t="n">
-        <v>0.3755525592646927</v>
+        <v>0.6275124846829272</v>
       </c>
       <c r="AW155" t="n">
-        <v>4.226515368963115</v>
+        <v>1.167662616093946</v>
       </c>
       <c r="AX155" t="n">
-        <v>0.2911324294177315</v>
+        <v>0.4533836084735867</v>
       </c>
       <c r="AY155" t="n">
-        <v>17.03115306028934</v>
+        <v>2209.781279107047</v>
       </c>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="n">
@@ -30385,12 +30389,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -30400,29 +30404,29 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>AI servers / rack integration</t>
+          <t>EMS / contract manufacturing</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Networking, UCS servers, data center networking</t>
+          <t>EMS/manufacturing</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, STOXX Global AI Infrastructure</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="K156" s="1" t="n">
@@ -30444,10 +30448,10 @@
         </is>
       </c>
       <c r="O156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Q156" s="1" t="n">
         <v>46192</v>
@@ -30462,7 +30466,7 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc.</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -30472,7 +30476,7 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
@@ -30481,7 +30485,7 @@
         </is>
       </c>
       <c r="X156" t="n">
-        <v>431752708096</v>
+        <v>40083918848</v>
       </c>
       <c r="Y156" t="inlineStr">
         <is>
@@ -30492,81 +30496,81 @@
         <v>1</v>
       </c>
       <c r="AA156" t="n">
-        <v>431752708096</v>
+        <v>40083918848</v>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC156" s="2" t="n">
-        <v>32920</v>
+        <v>34411</v>
       </c>
       <c r="AD156" t="n">
-        <v>36.6</v>
+        <v>32.5</v>
       </c>
       <c r="AE156" t="n">
-        <v>109.5100021362305</v>
+        <v>108.5100021362305</v>
       </c>
       <c r="AF156" t="n">
-        <v>113.2683996582031</v>
+        <v>116.8420002746582</v>
       </c>
       <c r="AG156" t="n">
-        <v>95.77699031829835</v>
+        <v>97.2312000656128</v>
       </c>
       <c r="AH156" t="n">
-        <v>-0.03318134213349822</v>
+        <v>-0.07130995805311335</v>
       </c>
       <c r="AI156" t="n">
-        <v>0.1433852929841795</v>
+        <v>0.1159998237500577</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.1826264250085023</v>
+        <v>0.2016924628700643</v>
       </c>
       <c r="AK156" t="n">
-        <v>129.5154876708984</v>
+        <v>162.0700073242188</v>
       </c>
       <c r="AL156" t="n">
-        <v>65.85634613037109</v>
+        <v>54.5099983215332</v>
       </c>
       <c r="AM156" t="n">
-        <v>-0.1544640405130723</v>
+        <v>-0.3304745034091486</v>
       </c>
       <c r="AN156" t="n">
-        <v>0.6628617980026004</v>
+        <v>0.9906440190324777</v>
       </c>
       <c r="AO156" t="n">
-        <v>48.80952792862617</v>
+        <v>47.27322716851896</v>
       </c>
       <c r="AP156" t="n">
-        <v>41260700</v>
+        <v>9526600</v>
       </c>
       <c r="AQ156" t="n">
-        <v>19425620</v>
+        <v>3848206</v>
       </c>
       <c r="AR156" t="n">
-        <v>2.124035165930354</v>
+        <v>2.47559512146699</v>
       </c>
       <c r="AS156" t="n">
-        <v>-0.0007299407275598302</v>
+        <v>-0.01640679444888238</v>
       </c>
       <c r="AT156" t="n">
-        <v>-0.09553465409672146</v>
+        <v>-0.3035748422021231</v>
       </c>
       <c r="AU156" t="n">
-        <v>0.4232489694512562</v>
+        <v>0.7603829203550119</v>
       </c>
       <c r="AV156" t="n">
-        <v>0.6275124846829272</v>
+        <v>0.8666781376639103</v>
       </c>
       <c r="AW156" t="n">
-        <v>1.16766228873848</v>
+        <v>6.779187837388075</v>
       </c>
       <c r="AX156" t="n">
-        <v>0.4533836084735867</v>
+        <v>0.7039887188475877</v>
       </c>
       <c r="AY156" t="n">
-        <v>2209.780780315543</v>
+        <v>78.44428165225989</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30581,12 +30585,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -30658,7 +30662,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>Flex Ltd.</t>
+          <t>Jabil Inc.</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -30677,7 +30681,7 @@
         </is>
       </c>
       <c r="X157" t="n">
-        <v>40083918848</v>
+        <v>31391068160</v>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
@@ -30688,7 +30692,7 @@
         <v>1</v>
       </c>
       <c r="AA157" t="n">
-        <v>40083918848</v>
+        <v>31391068160</v>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
@@ -30696,73 +30700,73 @@
         </is>
       </c>
       <c r="AC157" s="2" t="n">
-        <v>34411</v>
+        <v>34092</v>
       </c>
       <c r="AD157" t="n">
-        <v>32.5</v>
+        <v>33.4</v>
       </c>
       <c r="AE157" t="n">
-        <v>108.5100021362305</v>
+        <v>299.5700073242188</v>
       </c>
       <c r="AF157" t="n">
-        <v>116.8420002746582</v>
+        <v>318.6981127929687</v>
       </c>
       <c r="AG157" t="n">
-        <v>97.2312000656128</v>
+        <v>297.2899478912353</v>
       </c>
       <c r="AH157" t="n">
-        <v>-0.07130995805311335</v>
+        <v>-0.0600195128270995</v>
       </c>
       <c r="AI157" t="n">
-        <v>0.1159998237500577</v>
+        <v>0.007669480415185781</v>
       </c>
       <c r="AJ157" t="n">
-        <v>0.2016924628700643</v>
+        <v>0.0720110621081802</v>
       </c>
       <c r="AK157" t="n">
-        <v>162.0700073242188</v>
+        <v>385.5466918945312</v>
       </c>
       <c r="AL157" t="n">
-        <v>54.5099983215332</v>
+        <v>192.3445129394531</v>
       </c>
       <c r="AM157" t="n">
-        <v>-0.3304745034091486</v>
+        <v>-0.2229994093525564</v>
       </c>
       <c r="AN157" t="n">
-        <v>0.9906440190324777</v>
+        <v>0.5574658343309145</v>
       </c>
       <c r="AO157" t="n">
-        <v>47.27322716851896</v>
+        <v>48.76445454209968</v>
       </c>
       <c r="AP157" t="n">
-        <v>9526600</v>
+        <v>3806700</v>
       </c>
       <c r="AQ157" t="n">
-        <v>3848206</v>
+        <v>1041710</v>
       </c>
       <c r="AR157" t="n">
-        <v>2.47559512146699</v>
+        <v>3.654279981952751</v>
       </c>
       <c r="AS157" t="n">
-        <v>-0.01640679444888238</v>
+        <v>-0.05393963966994175</v>
       </c>
       <c r="AT157" t="n">
-        <v>-0.3035748422021231</v>
+        <v>-0.2057185487505593</v>
       </c>
       <c r="AU157" t="n">
-        <v>0.7603829203550119</v>
+        <v>0.1816519420262499</v>
       </c>
       <c r="AV157" t="n">
-        <v>0.8666781376639103</v>
+        <v>0.3431656632238871</v>
       </c>
       <c r="AW157" t="n">
-        <v>6.779187837388075</v>
+        <v>3.838246272438362</v>
       </c>
       <c r="AX157" t="n">
-        <v>0.7039887188475877</v>
+        <v>0.2471258950094433</v>
       </c>
       <c r="AY157" t="n">
-        <v>78.44428165225989</v>
+        <v>404.4756301593569</v>
       </c>
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="n">
@@ -30777,12 +30781,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>2356.TW</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -30792,19 +30796,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>EMS / contract manufacturing</t>
+          <t>Server ODM</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>EMS/manufacturing</t>
+          <t>Server ODM</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -30812,11 +30816,7 @@
       <c r="I158" t="n">
         <v>0</v>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" s="1" t="n">
         <v>46195</v>
       </c>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>Jabil Inc.</t>
+          <t>Inventec Corporation</t>
         </is>
       </c>
       <c r="U158" t="inlineStr">
@@ -30864,105 +30864,105 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X158" t="n">
-        <v>31391068160</v>
+        <v>221347201024</v>
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>1</v>
+        <v>0.03148317337036133</v>
       </c>
       <c r="AA158" t="n">
-        <v>31391068160</v>
+        <v>6968712304.882812</v>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC158" s="2" t="n">
-        <v>34092</v>
+        <v>36529</v>
       </c>
       <c r="AD158" t="n">
-        <v>33.4</v>
+        <v>26.7</v>
       </c>
       <c r="AE158" t="n">
-        <v>299.5700073242188</v>
+        <v>61.70000076293945</v>
       </c>
       <c r="AF158" t="n">
-        <v>318.6981127929687</v>
+        <v>63.81199981689453</v>
       </c>
       <c r="AG158" t="n">
-        <v>297.2899478912353</v>
+        <v>52.62502964019775</v>
       </c>
       <c r="AH158" t="n">
-        <v>-0.0600195128270995</v>
+        <v>-0.03309720836230423</v>
       </c>
       <c r="AI158" t="n">
-        <v>0.007669480415185781</v>
+        <v>0.1724459099555502</v>
       </c>
       <c r="AJ158" t="n">
-        <v>0.0720110621081802</v>
+        <v>0.212578886001265</v>
       </c>
       <c r="AK158" t="n">
-        <v>385.5466918945312</v>
+        <v>82.71868133544922</v>
       </c>
       <c r="AL158" t="n">
-        <v>192.3445129394531</v>
+        <v>38.79254150390625</v>
       </c>
       <c r="AM158" t="n">
-        <v>-0.2229994093525564</v>
+        <v>-0.2540983515836365</v>
       </c>
       <c r="AN158" t="n">
-        <v>0.5574658343309145</v>
+        <v>0.5905119481982513</v>
       </c>
       <c r="AO158" t="n">
-        <v>48.76445454209968</v>
+        <v>31.57896548331759</v>
       </c>
       <c r="AP158" t="n">
-        <v>3806700</v>
+        <v>1422084</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1041710</v>
+        <v>26091718.54</v>
       </c>
       <c r="AR158" t="n">
-        <v>3.654279981952751</v>
+        <v>0.05450327075312687</v>
       </c>
       <c r="AS158" t="n">
-        <v>-0.05393963966994175</v>
+        <v>-0.06656577628975724</v>
       </c>
       <c r="AT158" t="n">
-        <v>-0.2057185487505593</v>
+        <v>-0.04497743980523405</v>
       </c>
       <c r="AU158" t="n">
-        <v>0.1816519420262499</v>
+        <v>0.5076923205990542</v>
       </c>
       <c r="AV158" t="n">
-        <v>0.3431656632238871</v>
+        <v>0.5094785913809676</v>
       </c>
       <c r="AW158" t="n">
-        <v>3.838245676271775</v>
+        <v>2.169248485551507</v>
       </c>
       <c r="AX158" t="n">
-        <v>0.2471259742308156</v>
+        <v>0.4298540918575338</v>
       </c>
       <c r="AY158" t="n">
-        <v>404.4757937210014</v>
+        <v>7.118679001162578</v>
       </c>
       <c r="AZ158" t="inlineStr"/>
       <c r="BA158" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
@@ -30973,12 +30973,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2356.TW</t>
+          <t>2382.TW</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Quanta Computer</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -30993,11 +30993,11 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Server ODM</t>
+          <t>AI server ODM/QCT</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>Inventec Corporation</t>
+          <t>Quanta Computer Inc.</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -31065,7 +31065,7 @@
         </is>
       </c>
       <c r="X159" t="n">
-        <v>221347201024</v>
+        <v>1406134779904</v>
       </c>
       <c r="Y159" t="inlineStr">
         <is>
@@ -31076,11 +31076,11 @@
         <v>0.03148317337036133</v>
       </c>
       <c r="AA159" t="n">
-        <v>6968712304.882812</v>
+        <v>44269585057.8125</v>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>Mid cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC159" s="2" t="n">
@@ -31090,67 +31090,67 @@
         <v>26.7</v>
       </c>
       <c r="AE159" t="n">
-        <v>61.70000076293945</v>
+        <v>343</v>
       </c>
       <c r="AF159" t="n">
-        <v>63.83137184143067</v>
+        <v>327.5868188476563</v>
       </c>
       <c r="AG159" t="n">
-        <v>52.5153353691101</v>
+        <v>305.5603481292725</v>
       </c>
       <c r="AH159" t="n">
-        <v>-0.03339065128955632</v>
+        <v>0.04705067562413623</v>
       </c>
       <c r="AI159" t="n">
-        <v>0.1748949202984968</v>
+        <v>0.1225278479355838</v>
       </c>
       <c r="AJ159" t="n">
-        <v>0.2154806094788215</v>
+        <v>0.0720855007962784</v>
       </c>
       <c r="AK159" t="n">
-        <v>82.71868133544922</v>
+        <v>399.9259948730469</v>
       </c>
       <c r="AL159" t="n">
-        <v>38.79254150390625</v>
+        <v>249.3543395996094</v>
       </c>
       <c r="AM159" t="n">
-        <v>-0.2540983515836365</v>
+        <v>-0.1423413221516585</v>
       </c>
       <c r="AN159" t="n">
-        <v>0.5905119481982513</v>
+        <v>0.3755525592646927</v>
       </c>
       <c r="AO159" t="n">
-        <v>31.34330525166885</v>
+        <v>50.65789473684211</v>
       </c>
       <c r="AP159" t="n">
-        <v>22018211</v>
+        <v>1114814</v>
       </c>
       <c r="AQ159" t="n">
-        <v>27331234.42</v>
+        <v>19610267.48</v>
       </c>
       <c r="AR159" t="n">
-        <v>0.8056061669826327</v>
+        <v>0.05684848516915793</v>
       </c>
       <c r="AS159" t="n">
-        <v>-0.06088274537446159</v>
+        <v>0.05538461538461537</v>
       </c>
       <c r="AT159" t="n">
-        <v>-0.04066269383622112</v>
+        <v>-0.02416462387692875</v>
       </c>
       <c r="AU159" t="n">
-        <v>0.5184743835425587</v>
+        <v>0.2704925750937459</v>
       </c>
       <c r="AV159" t="n">
-        <v>0.5221028514599093</v>
+        <v>0.3624521079299201</v>
       </c>
       <c r="AW159" t="n">
-        <v>2.129383325579665</v>
+        <v>4.266852624833499</v>
       </c>
       <c r="AX159" t="n">
-        <v>0.4298540918575338</v>
+        <v>0.2911324294177315</v>
       </c>
       <c r="AY159" t="n">
-        <v>7.118679510558765</v>
+        <v>17.03115306028934</v>
       </c>
       <c r="AZ159" t="inlineStr"/>
       <c r="BA159" t="n">
@@ -32574,16 +32574,16 @@
         <v>379.7551989746094</v>
       </c>
       <c r="AG5" t="n">
-        <v>368.386103515625</v>
+        <v>368.3861039733887</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.05831444489197768</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.02925223851068914</v>
+        <v>-0.02925223971695912</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.03086190100681185</v>
+        <v>0.03086189972584297</v>
       </c>
       <c r="AK5" t="n">
         <v>480.8090515136719</v>
@@ -32628,7 +32628,7 @@
         <v>0.03252787358891807</v>
       </c>
       <c r="AY5" t="n">
-        <v>313.91089297659</v>
+        <v>313.9108599186503</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32991,13 +32991,13 @@
         <v>433.3299865722656</v>
       </c>
       <c r="AL7" t="n">
-        <v>125.6247253417969</v>
+        <v>125.6247329711914</v>
       </c>
       <c r="AM7" t="n">
         <v>-0.3351256680144038</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.293417832896187</v>
+        <v>1.293417693613189</v>
       </c>
       <c r="AO7" t="n">
         <v>44.06472660920067</v>
@@ -33021,16 +33021,16 @@
         <v>0.2625369552102919</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.293417832896187</v>
+        <v>1.293417693613189</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.985514960973383</v>
+        <v>3.985515619164275</v>
       </c>
       <c r="AX7" t="n">
         <v>0.5598095737217816</v>
       </c>
       <c r="AY7" t="n">
-        <v>1527.176035656825</v>
+        <v>1527.176156440602</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33178,28 +33178,28 @@
         <v>215.9457998657226</v>
       </c>
       <c r="AG8" t="n">
-        <v>158.3619704055786</v>
+        <v>158.3619702529907</v>
       </c>
       <c r="AH8" t="n">
         <v>0.1310708527411841</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.5423526202310742</v>
+        <v>0.5423526217171908</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3636215772806244</v>
+        <v>0.3636215785945265</v>
       </c>
       <c r="AK8" t="n">
         <v>316.3519592285156</v>
       </c>
       <c r="AL8" t="n">
-        <v>73.67493438720703</v>
+        <v>73.67494201660156</v>
       </c>
       <c r="AM8" t="n">
         <v>-0.2279169043376559</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.315238785504935</v>
+        <v>2.315238442196017</v>
       </c>
       <c r="AO8" t="n">
         <v>64.01542628797245</v>
@@ -33226,13 +33226,13 @@
         <v>2.297458900645704</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.988906833700439</v>
+        <v>2.988906336692607</v>
       </c>
       <c r="AX8" t="n">
         <v>1.73641818636544</v>
       </c>
       <c r="AY8" t="n">
-        <v>19.13718193273938</v>
+        <v>19.13718034944063</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8092577851904883</v>
+        <v>0.8092577677801136</v>
       </c>
     </row>
   </sheetData>
@@ -33686,31 +33686,31 @@
         <v>0.4060160492687241</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9353749590517075</v>
+        <v>0.9353749727662215</v>
       </c>
       <c r="O2" t="n">
         <v>0.4328322019708022</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6111388976239606</v>
+        <v>0.6111389448669197</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.280081579611553</v>
+        <v>4.280081817265331</v>
       </c>
       <c r="R2" t="n">
         <v>1.595028179814861</v>
       </c>
       <c r="S2" t="n">
-        <v>5.034353593709446</v>
+        <v>5.034354272900875</v>
       </c>
       <c r="T2" t="n">
-        <v>1334.7726086348</v>
+        <v>1334.772916761351</v>
       </c>
       <c r="U2" t="n">
-        <v>352.7918908461003</v>
+        <v>352.7917732494217</v>
       </c>
       <c r="V2" t="n">
-        <v>3947.233739074247</v>
+        <v>3947.234945970698</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33752,40 +33752,40 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5401952602534307</v>
+        <v>0.5401952742338076</v>
       </c>
       <c r="L3" t="n">
         <v>0.03820357209392355</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06950305089939993</v>
+        <v>0.06950308628982607</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3228129064166746</v>
+        <v>0.3228129314855193</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.08240672508773172</v>
+        <v>-0.08240672112181813</v>
       </c>
       <c r="P3" t="n">
-        <v>0.09817532345957848</v>
+        <v>0.09817531722555473</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.79620644879074</v>
+        <v>0.7962063885480761</v>
       </c>
       <c r="R3" t="n">
         <v>0.6000575165078259</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8919616173871162</v>
+        <v>0.8919615495110802</v>
       </c>
       <c r="T3" t="n">
-        <v>1222.222824104272</v>
+        <v>1222.222849210214</v>
       </c>
       <c r="U3" t="n">
-        <v>13.37213081272481</v>
+        <v>13.37212904442064</v>
       </c>
       <c r="V3" t="n">
-        <v>2901.805481811231</v>
+        <v>2901.805371473803</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33812,13 +33812,13 @@
         <v>41.016131584</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>74.375</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>81.78808980027883</v>
+        <v>81.27176157969804</v>
       </c>
       <c r="I4" t="n">
         <v>8</v>
@@ -33827,40 +33827,40 @@
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5570405058543419</v>
+        <v>0.5570405009030062</v>
       </c>
       <c r="L4" t="n">
         <v>0.2768646854538579</v>
       </c>
       <c r="M4" t="n">
-        <v>1.151525148638116</v>
+        <v>1.151525146978877</v>
       </c>
       <c r="N4" t="n">
-        <v>0.669950230772377</v>
+        <v>0.6705871064618294</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3593591112442899</v>
+        <v>0.3528088855769036</v>
       </c>
       <c r="P4" t="n">
-        <v>1.222188891344224</v>
+        <v>1.221685426181254</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.907216549687747</v>
+        <v>6.922746408283011</v>
       </c>
       <c r="R4" t="n">
-        <v>4.046310787203512</v>
+        <v>4.066479786798485</v>
       </c>
       <c r="S4" t="n">
-        <v>6.55103886330565</v>
+        <v>6.559553116470287</v>
       </c>
       <c r="T4" t="n">
-        <v>233.762332742217</v>
+        <v>233.7623663432478</v>
       </c>
       <c r="U4" t="n">
-        <v>40.74121864174263</v>
+        <v>40.74121671134052</v>
       </c>
       <c r="V4" t="n">
-        <v>718.8195578657923</v>
+        <v>718.819713223677</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33871,146 +33871,146 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Advanced Packaging / Substrates</t>
+          <t>Semiconductor Manufacturing</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>236.6006544465096</v>
+        <v>4129.912686400663</v>
       </c>
       <c r="D5" t="n">
-        <v>33.80009349235851</v>
+        <v>275.3275124267109</v>
       </c>
       <c r="E5" t="n">
-        <v>13.801890759375</v>
+        <v>61.71963392</v>
       </c>
       <c r="F5" t="n">
-        <v>62.85714285714285</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
       </c>
       <c r="H5" t="n">
-        <v>72.46736312633374</v>
+        <v>68.86402674931114</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.229401236009831</v>
+        <v>0.5078512174061179</v>
       </c>
       <c r="L5" t="n">
-        <v>1.736873138239476</v>
+        <v>0.4504375267308354</v>
       </c>
       <c r="M5" t="n">
-        <v>2.096216101694194</v>
+        <v>0.4395224871124955</v>
       </c>
       <c r="N5" t="n">
-        <v>4.097452385485544</v>
+        <v>1.078567548594382</v>
       </c>
       <c r="O5" t="n">
-        <v>4.409762934246995</v>
+        <v>0.8225749087497773</v>
       </c>
       <c r="P5" t="n">
-        <v>3.93502114614768</v>
+        <v>0.8478543276151781</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.083309690067782</v>
+        <v>3.161330013952877</v>
       </c>
       <c r="R5" t="n">
-        <v>4.701337963481163</v>
+        <v>2.360998715777082</v>
       </c>
       <c r="S5" t="n">
-        <v>4.956313573691096</v>
+        <v>2.910046653149571</v>
       </c>
       <c r="T5" t="n">
-        <v>36.6211565352095</v>
+        <v>764.8407020951022</v>
       </c>
       <c r="U5" t="n">
-        <v>27.25392819219602</v>
+        <v>34.86928792021939</v>
       </c>
       <c r="V5" t="n">
-        <v>53.59930788589018</v>
+        <v>949.9819461025003</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Narrow momentum</t>
+          <t>Weak breadth</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturing</t>
+          <t>Advanced Packaging / Substrates</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4129.907439064147</v>
+        <v>236.6015565570623</v>
       </c>
       <c r="D6" t="n">
-        <v>275.3271626042765</v>
+        <v>33.80022236529462</v>
       </c>
       <c r="E6" t="n">
-        <v>61.71963392</v>
+        <v>13.801890759375</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>58.57142857142857</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
       </c>
       <c r="H6" t="n">
-        <v>68.86403165882763</v>
+        <v>66.82242256854506</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5078512229896023</v>
+        <v>2.229401236009831</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4504375267308354</v>
+        <v>1.736873138239476</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4395224464649891</v>
+        <v>2.096224732083372</v>
       </c>
       <c r="N6" t="n">
-        <v>1.078567562688792</v>
+        <v>4.08023397289024</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8225750294372665</v>
+        <v>4.409763299621911</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8478545140729863</v>
+        <v>3.915256342713203</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.161330228450965</v>
+        <v>4.118929154063184</v>
       </c>
       <c r="R6" t="n">
-        <v>2.360998526287821</v>
+        <v>4.701337591160438</v>
       </c>
       <c r="S6" t="n">
-        <v>2.91004846736906</v>
+        <v>4.983429737013064</v>
       </c>
       <c r="T6" t="n">
-        <v>764.8406379846853</v>
+        <v>36.62115242402992</v>
       </c>
       <c r="U6" t="n">
-        <v>34.86929391245137</v>
+        <v>27.25392570058711</v>
       </c>
       <c r="V6" t="n">
-        <v>949.9827984539662</v>
+        <v>53.59915394593872</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34037,13 +34037,13 @@
         <v>190.2709075748916</v>
       </c>
       <c r="F7" t="n">
-        <v>64.16666666666667</v>
+        <v>63.75</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
       </c>
       <c r="H7" t="n">
-        <v>62.93549912573997</v>
+        <v>62.9080007261317</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -34052,40 +34052,40 @@
         <v>0.1538461538461539</v>
       </c>
       <c r="K7" t="n">
-        <v>1.793461792986458</v>
+        <v>1.793461751027682</v>
       </c>
       <c r="L7" t="n">
-        <v>1.449144704567275</v>
+        <v>1.449144608787159</v>
       </c>
       <c r="M7" t="n">
-        <v>1.858330386026936</v>
+        <v>1.85833030203958</v>
       </c>
       <c r="N7" t="n">
-        <v>5.847242919948822</v>
+        <v>5.842399506026041</v>
       </c>
       <c r="O7" t="n">
-        <v>4.114740937145157</v>
+        <v>4.11474078429939</v>
       </c>
       <c r="P7" t="n">
-        <v>5.293020480707152</v>
+        <v>5.292293134968901</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.025545428056505</v>
+        <v>7.060186465665073</v>
       </c>
       <c r="R7" t="n">
-        <v>5.615961533444669</v>
+        <v>5.789166045551214</v>
       </c>
       <c r="S7" t="n">
-        <v>9.183312871599046</v>
+        <v>9.186544231939854</v>
       </c>
       <c r="T7" t="n">
-        <v>287.1283283319557</v>
+        <v>287.1283020208589</v>
       </c>
       <c r="U7" t="n">
         <v>54.45228333133466</v>
       </c>
       <c r="V7" t="n">
-        <v>354.6753947503285</v>
+        <v>354.6753327772446</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34103,22 +34103,22 @@
         <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1588.905816268522</v>
+        <v>1588.941366435538</v>
       </c>
       <c r="D8" t="n">
-        <v>72.22299164856919</v>
+        <v>72.22460756525172</v>
       </c>
       <c r="E8" t="n">
-        <v>42.65482847943359</v>
+        <v>42.65717924426171</v>
       </c>
       <c r="F8" t="n">
-        <v>48.40909090909091</v>
+        <v>48.18181818181818</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
       </c>
       <c r="H8" t="n">
-        <v>61.49821122266164</v>
+        <v>61.05217338973989</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -34127,40 +34127,40 @@
         <v>0.08695652173913043</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3171000427167981</v>
+        <v>0.3171000296980442</v>
       </c>
       <c r="L8" t="n">
         <v>0.3244311480444699</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3767084985052087</v>
+        <v>0.3767061407117226</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5260103585472572</v>
+        <v>0.513385616340559</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3431827829917773</v>
+        <v>0.343182827732759</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5016267329648848</v>
+        <v>0.4844851815174461</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.615576081809857</v>
+        <v>2.624904727834151</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36438018420086</v>
+        <v>1.364379957320946</v>
       </c>
       <c r="S8" t="n">
-        <v>2.336746920779837</v>
+        <v>2.356684423010836</v>
       </c>
       <c r="T8" t="n">
-        <v>171.7829206561221</v>
+        <v>171.7829007179242</v>
       </c>
       <c r="U8" t="n">
-        <v>26.05308944485912</v>
+        <v>26.05309085957152</v>
       </c>
       <c r="V8" t="n">
-        <v>337.3456747804545</v>
+        <v>337.3382907367857</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34211,31 +34211,31 @@
         <v>0.746691946059853</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001600602539787332</v>
+        <v>0.001600663179373241</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001600602539787332</v>
+        <v>0.001600663179373241</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6756417858398229</v>
+        <v>0.6756418985706146</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1525270565179038</v>
+        <v>0.1525272584762238</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1525270565179038</v>
+        <v>0.1525272584762238</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1525270565179038</v>
+        <v>0.1525272584762238</v>
       </c>
       <c r="T9" t="n">
-        <v>10.86937104687991</v>
+        <v>10.86937229450092</v>
       </c>
       <c r="U9" t="n">
-        <v>10.86937104687991</v>
+        <v>10.86937229450092</v>
       </c>
       <c r="V9" t="n">
-        <v>20.35933291282503</v>
+        <v>20.35933523218955</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34286,31 +34286,31 @@
         <v>0.2576535131560101</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2763153807764226</v>
+        <v>0.2763153912773512</v>
       </c>
       <c r="O10" t="n">
         <v>0.1736070926600137</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2206321792723551</v>
+        <v>0.2206321875242279</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.391854008518499</v>
+        <v>1.391853993798553</v>
       </c>
       <c r="R10" t="n">
         <v>0.3720572839636201</v>
       </c>
       <c r="S10" t="n">
-        <v>4.99409715240135</v>
+        <v>4.994097140834076</v>
       </c>
       <c r="T10" t="n">
-        <v>55.1312089348687</v>
+        <v>55.13120296928431</v>
       </c>
       <c r="U10" t="n">
         <v>8.041561687201929</v>
       </c>
       <c r="V10" t="n">
-        <v>213.2578228851159</v>
+        <v>213.2578002895631</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34328,10 +34328,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>3340.362540316455</v>
+        <v>3340.368169364786</v>
       </c>
       <c r="D11" t="n">
-        <v>167.0181270158227</v>
+        <v>167.0184084682393</v>
       </c>
       <c r="E11" t="n">
         <v>59.632664576</v>
@@ -34343,7 +34343,7 @@
         <v>65</v>
       </c>
       <c r="H11" t="n">
-        <v>56.13248830350629</v>
+        <v>56.13250324666507</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
@@ -34352,40 +34352,40 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5934358335829651</v>
+        <v>0.5934358212581723</v>
       </c>
       <c r="L11" t="n">
         <v>0.4875885393589443</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3498506577266356</v>
+        <v>0.3498506196124008</v>
       </c>
       <c r="N11" t="n">
-        <v>1.023714223126673</v>
+        <v>1.023714231881262</v>
       </c>
       <c r="O11" t="n">
         <v>0.7870612041157252</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5784712373888663</v>
+        <v>0.5784710254827345</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.149108439570523</v>
+        <v>6.149108528717415</v>
       </c>
       <c r="R11" t="n">
-        <v>3.368110535982487</v>
+        <v>3.36811150562112</v>
       </c>
       <c r="S11" t="n">
-        <v>7.390856530487243</v>
+        <v>7.390849190349079</v>
       </c>
       <c r="T11" t="n">
-        <v>180.7055687023244</v>
+        <v>180.7055714632443</v>
       </c>
       <c r="U11" t="n">
-        <v>26.31289040343655</v>
+        <v>26.31288731862259</v>
       </c>
       <c r="V11" t="n">
-        <v>283.5541453610679</v>
+        <v>283.5536697535063</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34403,10 +34403,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>405.3142400801933</v>
+        <v>405.3433990003754</v>
       </c>
       <c r="D12" t="n">
-        <v>101.3285600200483</v>
+        <v>101.3358497500938</v>
       </c>
       <c r="E12" t="n">
         <v>75.84151552</v>
@@ -34418,7 +34418,7 @@
         <v>25</v>
       </c>
       <c r="H12" t="n">
-        <v>47.54742820441368</v>
+        <v>47.54925864633162</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -34433,7 +34433,7 @@
         <v>0.01483242667748685</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02673357827637868</v>
+        <v>0.0267408433190465</v>
       </c>
       <c r="N12" t="n">
         <v>0.05942915098568174</v>
@@ -34442,25 +34442,25 @@
         <v>-0.008861315388135671</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04620424752061746</v>
+        <v>0.04621534636272496</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.058199014145146</v>
+        <v>1.058199048546798</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9502541696912724</v>
+        <v>0.9502542384945768</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9485296605955356</v>
+        <v>0.9485513050177236</v>
       </c>
       <c r="T12" t="n">
-        <v>75.68489092346775</v>
+        <v>75.68488660261239</v>
       </c>
       <c r="U12" t="n">
-        <v>67.75917399402103</v>
+        <v>67.75916395929438</v>
       </c>
       <c r="V12" t="n">
-        <v>55.01366490913689</v>
+        <v>55.01192697784129</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34478,10 +34478,10 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>1151.787553286803</v>
+        <v>1151.803309438498</v>
       </c>
       <c r="D13" t="n">
-        <v>60.62039754141065</v>
+        <v>60.62122681255251</v>
       </c>
       <c r="E13" t="n">
         <v>43.342782464</v>
@@ -34493,7 +34493,7 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>25.90733979856068</v>
+        <v>25.90705379554722</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -34502,40 +34502,40 @@
         <v>0.05263157894736842</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.09679126259769516</v>
+        <v>-0.09679125895329627</v>
       </c>
       <c r="L13" t="n">
         <v>-0.07041391014529907</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06547846814874429</v>
+        <v>0.0654795814518726</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.03762940720243609</v>
+        <v>-0.0376294004988948</v>
       </c>
       <c r="O13" t="n">
         <v>0.01050532770612511</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1700241167773124</v>
+        <v>0.1700283555719341</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.852943141700174</v>
+        <v>1.852943031750581</v>
       </c>
       <c r="R13" t="n">
-        <v>1.412545235437154</v>
+        <v>1.412545103163895</v>
       </c>
       <c r="S13" t="n">
-        <v>1.85586973606614</v>
+        <v>1.855940294809057</v>
       </c>
       <c r="T13" t="n">
-        <v>70.83214533297334</v>
+        <v>70.83215345753112</v>
       </c>
       <c r="U13" t="n">
-        <v>11.40735242992542</v>
+        <v>11.40735138627078</v>
       </c>
       <c r="V13" t="n">
-        <v>100.4999131791482</v>
+        <v>100.4986431685812</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34586,31 +34586,31 @@
         <v>-0.008018079126882275</v>
       </c>
       <c r="N14" t="n">
-        <v>0.09985338275387619</v>
+        <v>0.09985339387997623</v>
       </c>
       <c r="O14" t="n">
         <v>0.1546546127274884</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2005003568255149</v>
+        <v>0.2005003743668157</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5148879663815237</v>
+        <v>0.5148878698407985</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3748906438095811</v>
+        <v>0.374890395423766</v>
       </c>
       <c r="S14" t="n">
-        <v>0.728898136316126</v>
+        <v>0.7288980112249338</v>
       </c>
       <c r="T14" t="n">
-        <v>15.71720529322538</v>
+        <v>15.71720584644554</v>
       </c>
       <c r="U14" t="n">
-        <v>3.336182268674302</v>
+        <v>3.336181604682966</v>
       </c>
       <c r="V14" t="n">
-        <v>2.644694618588668</v>
+        <v>2.644694657356748</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -828,16 +828,16 @@
         <v>475.4040515136719</v>
       </c>
       <c r="AG2" t="n">
-        <v>430.609797668457</v>
+        <v>430.6097988891602</v>
       </c>
       <c r="AH2" t="n">
         <v>0.085750071474332</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.198695398258391</v>
+        <v>0.1986953948603001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1040251617305366</v>
+        <v>0.1040251586008192</v>
       </c>
       <c r="AK2" t="n">
         <v>537.6464233398438</v>
@@ -882,7 +882,7 @@
         <v>0.09833099561027558</v>
       </c>
       <c r="AY2" t="n">
-        <v>8745.532985167958</v>
+        <v>8745.528016024722</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1072,13 +1072,13 @@
         <v>2.179416713537089</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.649363953163083</v>
+        <v>4.649364362700444</v>
       </c>
       <c r="AX3" t="n">
         <v>2.943925426619157</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.235254950008053</v>
+        <v>5.235255448895819</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1416,16 +1416,16 @@
         <v>615.3199987792968</v>
       </c>
       <c r="AG5" t="n">
-        <v>625.4245977783203</v>
+        <v>625.424596862793</v>
       </c>
       <c r="AH5" t="n">
         <v>0.2215757242340775</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.2018394796345293</v>
+        <v>0.2018394813938411</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01615638245588313</v>
+        <v>-0.01615638101568451</v>
       </c>
       <c r="AK5" t="n">
         <v>777.5900268554688</v>
@@ -1461,16 +1461,16 @@
         <v>0.4322271421251329</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.007076490222437171</v>
+        <v>0.007076572576226736</v>
       </c>
       <c r="AW5" t="n">
         <v>1.133424651340498</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1586460757430999</v>
+        <v>0.1586461847515757</v>
       </c>
       <c r="AY5" t="n">
-        <v>18.84983233587104</v>
+        <v>18.84983433551365</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -1612,28 +1612,28 @@
         <v>344.1353118896484</v>
       </c>
       <c r="AG6" t="n">
-        <v>337.8175523376465</v>
+        <v>337.8175514221192</v>
       </c>
       <c r="AH6" t="n">
         <v>-0.0006256215345408211</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.01806436950318235</v>
+        <v>0.01806437226226265</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01870169121848186</v>
+        <v>0.01870169397928922</v>
       </c>
       <c r="AK6" t="n">
         <v>402.1211853027344</v>
       </c>
       <c r="AL6" t="n">
-        <v>235.9563598632812</v>
+        <v>235.9563751220703</v>
       </c>
       <c r="AM6" t="n">
         <v>-0.1447354031625656</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.4575577179907753</v>
+        <v>0.4575576237336663</v>
       </c>
       <c r="AO6" t="n">
         <v>53.99123914597289</v>
@@ -1657,16 +1657,16 @@
         <v>0.2551819715594119</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.4028823919669415</v>
+        <v>0.4028823046486716</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.502839342800882</v>
+        <v>1.502839898652224</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0934128343610543</v>
+        <v>0.0934127282743622</v>
       </c>
       <c r="AY6" t="n">
-        <v>137.2680909619668</v>
+        <v>137.2680644552161</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
@@ -2240,7 +2240,7 @@
         <v>-0.2910324293798078</v>
       </c>
       <c r="AY9" t="n">
-        <v>619.79561626969</v>
+        <v>619.7957214958492</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
@@ -3008,13 +3008,13 @@
         <v>-0.5240358811288224</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.7019797550281883</v>
+        <v>0.701979432630965</v>
       </c>
       <c r="AX13" t="n">
         <v>-0.2927167104419421</v>
       </c>
       <c r="AY13" t="n">
-        <v>2728.031169052281</v>
+        <v>2728.030966685321</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
@@ -4710,25 +4710,25 @@
         <v>376.0055322265625</v>
       </c>
       <c r="AG22" t="n">
-        <v>367.0419474792481</v>
+        <v>367.0419497680664</v>
       </c>
       <c r="AH22" t="n">
         <v>-0.06168934411845894</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.03877472321187203</v>
+        <v>-0.03877472920592806</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.02442114534557716</v>
+        <v>0.02442113895744114</v>
       </c>
       <c r="AK22" t="n">
-        <v>479.9350891113281</v>
+        <v>479.9351196289062</v>
       </c>
       <c r="AL22" t="n">
         <v>292.4138793945312</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.2648797606945672</v>
+        <v>-0.2648798074385715</v>
       </c>
       <c r="AN22" t="n">
         <v>0.2065432676763428</v>
@@ -4752,19 +4752,19 @@
         <v>-0.0510070422899398</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.1773708982535498</v>
+        <v>0.1773707783489811</v>
       </c>
       <c r="AV22" t="n">
         <v>0.05752237848357877</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.846206352959322</v>
+        <v>6.846205687320551</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.02052367955942147</v>
+        <v>0.02052376964502511</v>
       </c>
       <c r="AY22" t="n">
-        <v>310.2497735497959</v>
+        <v>310.249675350489</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
@@ -4906,16 +4906,16 @@
         <v>230.1554028320313</v>
       </c>
       <c r="AG23" t="n">
-        <v>254.8089638519287</v>
+        <v>254.8089641571045</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.02018379003071058</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.1149840606161666</v>
+        <v>-0.1149840616761192</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.09675311514638796</v>
+        <v>-0.09675311622817517</v>
       </c>
       <c r="AK23" t="n">
         <v>326.8851013183594</v>
@@ -4954,13 +4954,13 @@
         <v>-0.177897452225898</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.126560591090547</v>
+        <v>1.126560438094654</v>
       </c>
       <c r="AX23" t="n">
         <v>-0.2106214539711677</v>
       </c>
       <c r="AY23" t="n">
-        <v>156.2102562738796</v>
+        <v>156.210204014301</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5102,16 +5102,16 @@
         <v>321.7428021240235</v>
       </c>
       <c r="AG24" t="n">
-        <v>287.3879038238525</v>
+        <v>287.3879029083252</v>
       </c>
       <c r="AH24" t="n">
         <v>0.06007035766644808</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1867931906183127</v>
+        <v>0.1867931943990619</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1195419077945186</v>
+        <v>0.1195419113610263</v>
       </c>
       <c r="AK24" t="n">
         <v>341.0700073242188</v>
@@ -5147,16 +5147,16 @@
         <v>0.3733065189034541</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.3326972041658034</v>
+        <v>0.3326970452491333</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.446357009959505</v>
+        <v>1.446356742217715</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.2619401064705107</v>
+        <v>0.2619399639806466</v>
       </c>
       <c r="AY24" t="n">
-        <v>3474.964680921438</v>
+        <v>3474.965472727186</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5686,16 +5686,16 @@
         <v>215.7947650146484</v>
       </c>
       <c r="AG27" t="n">
-        <v>199.1272191619873</v>
+        <v>199.1272193145752</v>
       </c>
       <c r="AH27" t="n">
         <v>0.04298177626755995</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.1302824810762175</v>
+        <v>0.1302824802101008</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.0837030011407045</v>
+        <v>0.08370300031028077</v>
       </c>
       <c r="AK27" t="n">
         <v>235.202392578125</v>
@@ -5728,19 +5728,19 @@
         <v>0.1556745010213683</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.3466121905832746</v>
+        <v>0.3466120676448941</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.2696787366384157</v>
+        <v>0.269678955223341</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.707210788085131</v>
+        <v>9.707211759635234</v>
       </c>
       <c r="AX27" t="n">
         <v>0.1945811896273448</v>
       </c>
       <c r="AY27" t="n">
-        <v>5998.134740699801</v>
+        <v>5998.132953632723</v>
       </c>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
@@ -5882,16 +5882,16 @@
         <v>169.6396423339844</v>
       </c>
       <c r="AG28" t="n">
-        <v>167.646210975647</v>
+        <v>167.6462112808227</v>
       </c>
       <c r="AH28" t="n">
         <v>0.1905825692739151</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.2047394333895336</v>
+        <v>0.204739431196479</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01189070332539144</v>
+        <v>0.01189070148339022</v>
       </c>
       <c r="AK28" t="n">
         <v>248.7425079345703</v>
@@ -5927,16 +5927,16 @@
         <v>0.6034872254594352</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.215087334448637</v>
+        <v>0.2150872229041401</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.6960476378988689</v>
+        <v>0.6960474205740941</v>
       </c>
       <c r="AX28" t="n">
         <v>0.1858473519330988</v>
       </c>
       <c r="AY28" t="n">
-        <v>600.89548742825</v>
+        <v>600.8955943424739</v>
       </c>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
@@ -6512,13 +6512,13 @@
         <v>2.618711207005395</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.520604547119286</v>
+        <v>1.520604153030275</v>
       </c>
       <c r="AX31" t="n">
         <v>2.123412815231975</v>
       </c>
       <c r="AY31" t="n">
-        <v>676.6866634713289</v>
+        <v>676.6868860241036</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
@@ -6704,13 +6704,13 @@
         <v>8.134093435282963</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.154080233783367</v>
+        <v>4.154079812429183</v>
       </c>
       <c r="AX32" t="n">
         <v>5.177223445015081</v>
       </c>
       <c r="AY32" t="n">
-        <v>41.0972226094107</v>
+        <v>41.09721206838083</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6896,13 +6896,13 @@
         <v>7.217484604152117</v>
       </c>
       <c r="AW33" t="n">
-        <v>8.038777041786393</v>
+        <v>8.038778093799419</v>
       </c>
       <c r="AX33" t="n">
         <v>4.422038803872498</v>
       </c>
       <c r="AY33" t="n">
-        <v>161.786427950588</v>
+        <v>161.7863426449202</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7092,13 +7092,13 @@
         <v>2.905387592605263</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.601695664220405</v>
+        <v>5.601695195213436</v>
       </c>
       <c r="AX34" t="n">
         <v>1.654551583392943</v>
       </c>
       <c r="AY34" t="n">
-        <v>42.14399946049576</v>
+        <v>42.14398944484818</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA35" t="n">
-        <v>9012739513.275696</v>
+        <v>9013766800.820251</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>5.204268436996377</v>
       </c>
       <c r="AY35" t="n">
-        <v>16.73436485673023</v>
+        <v>16.73436338283398</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7482,7 +7482,7 @@
         <v>2.267312882239865</v>
       </c>
       <c r="AY36" t="n">
-        <v>32.72988470878067</v>
+        <v>32.72988173426776</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7674,7 +7674,7 @@
         <v>0.0623648056555588</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.216155723006776</v>
+        <v>3.216154840567716</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7831,13 +7831,13 @@
         <v>93.37815856933594</v>
       </c>
       <c r="AL38" t="n">
-        <v>28.06438446044922</v>
+        <v>28.06438255310059</v>
       </c>
       <c r="AM38" t="n">
         <v>-0.4258828677742171</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.9102503632639247</v>
+        <v>0.9102504930908828</v>
       </c>
       <c r="AO38" t="n">
         <v>62.07609420502148</v>
@@ -7864,13 +7864,13 @@
         <v>0.8512921398786966</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.215153031670285</v>
+        <v>1.215153206249194</v>
       </c>
       <c r="AX38" t="n">
         <v>0.2551754011865341</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.342420017437918</v>
+        <v>3.342419681995564</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8053,7 +8053,7 @@
         <v>0.1406672250299625</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.1290646371941562</v>
+        <v>0.1290647476524553</v>
       </c>
       <c r="AW39" t="n">
         <v>0.8450250513977304</v>
@@ -8062,7 +8062,7 @@
         <v>0.1227883553450333</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.9145879270983133</v>
+        <v>0.9145882447209177</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8254,7 +8254,7 @@
         <v>0.1283364019976896</v>
       </c>
       <c r="AY40" t="n">
-        <v>3.644370394663938</v>
+        <v>3.644369528234956</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8441,16 +8441,16 @@
         <v>0.05701604046723685</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.3152105880756582</v>
+        <v>0.3152104833445706</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.3098128928564432</v>
+        <v>0.3098127889832358</v>
       </c>
       <c r="AX41" t="n">
         <v>0.3394071014664934</v>
       </c>
       <c r="AY41" t="n">
-        <v>2.279067246518951</v>
+        <v>2.279067897526144</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8592,16 +8592,16 @@
         <v>187.1601187133789</v>
       </c>
       <c r="AG42" t="n">
-        <v>178.2753211975098</v>
+        <v>178.2753216552734</v>
       </c>
       <c r="AH42" t="n">
         <v>-0.04568344026390136</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.001877317682524415</v>
+        <v>0.00187731510996958</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.04983750670697562</v>
+        <v>0.04983750401127174</v>
       </c>
       <c r="AK42" t="n">
         <v>201.1799774169922</v>
@@ -8640,13 +8640,13 @@
         <v>0.07216019021080777</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.3457927453062064</v>
+        <v>0.3457929000348481</v>
       </c>
       <c r="AX42" t="n">
         <v>0.1756845890145757</v>
       </c>
       <c r="AY42" t="n">
-        <v>34.27821651199049</v>
+        <v>34.27821983458698</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8788,16 +8788,16 @@
         <v>119.5427145385742</v>
       </c>
       <c r="AG43" t="n">
-        <v>110.0622708511353</v>
+        <v>110.0622709274292</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.06828285033231607</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.01197255328363167</v>
+        <v>0.01197255258214347</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.08613708961413069</v>
+        <v>0.0861370888612325</v>
       </c>
       <c r="AK43" t="n">
         <v>132.0340881347656</v>
@@ -8833,16 +8833,16 @@
         <v>0.149672686459569</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.1421388214958508</v>
+        <v>0.1421387321404877</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.033011856104574</v>
+        <v>2.033012801301893</v>
       </c>
       <c r="AX43" t="n">
         <v>0.3687433555403647</v>
       </c>
       <c r="AY43" t="n">
-        <v>96.4210428412582</v>
+        <v>96.4210529992648</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -8977,34 +8977,34 @@
         <v>2.119999885559082</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.18315085887909</v>
+        <v>2.180658111572265</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.176386179924011</v>
+        <v>2.173196541070938</v>
       </c>
       <c r="AH44" t="n">
-        <v>-0.02892652748350688</v>
+        <v>-0.02781647691184774</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.02590822110756918</v>
+        <v>-0.02447852944107909</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.003108216279573472</v>
+        <v>0.003433454066538388</v>
       </c>
       <c r="AK44" t="n">
-        <v>2.306842803955078</v>
+        <v>2.30321192741394</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.064932584762573</v>
+        <v>2.061682462692261</v>
       </c>
       <c r="AM44" t="n">
-        <v>-0.08099508040845016</v>
+        <v>-0.07954632384201399</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.02666784436589276</v>
+        <v>0.02828632630005834</v>
       </c>
       <c r="AO44" t="n">
-        <v>27.60018074099422</v>
+        <v>28.05053262339173</v>
       </c>
       <c r="AP44" t="n">
         <v>12537600</v>
@@ -9016,25 +9016,25 @@
         <v>0.8424713231835679</v>
       </c>
       <c r="AS44" t="n">
-        <v>-0.02653780042299769</v>
+        <v>-0.02500320177123738</v>
       </c>
       <c r="AT44" t="n">
-        <v>-0.01945448915480052</v>
+        <v>-0.01790873961558281</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.007532993814927336</v>
+        <v>0.009121208159470706</v>
       </c>
       <c r="AV44" t="n">
-        <v>-0.04743629943622363</v>
+        <v>-0.04593468888589181</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.06951993095451314</v>
+        <v>0.0712061200942915</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.003751230570920638</v>
+        <v>0.00533355945617453</v>
       </c>
       <c r="AY44" t="n">
-        <v>2.933942645439771</v>
+        <v>2.940143602446216</v>
       </c>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
@@ -9924,28 +9924,28 @@
         <v>14.74225925445557</v>
       </c>
       <c r="AG49" t="n">
-        <v>14.40708016872406</v>
+        <v>14.4070801448822</v>
       </c>
       <c r="AH49" t="n">
         <v>0.008664929092527585</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.03213140424108718</v>
+        <v>0.03213140594913133</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.0232648865562044</v>
+        <v>0.02326488824957562</v>
       </c>
       <c r="AK49" t="n">
         <v>16.86722755432129</v>
       </c>
       <c r="AL49" t="n">
-        <v>12.41211414337158</v>
+        <v>12.4121150970459</v>
       </c>
       <c r="AM49" t="n">
         <v>-0.1184087700441635</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.1980231339960792</v>
+        <v>0.1980230419469897</v>
       </c>
       <c r="AO49" t="n">
         <v>66.66666666666666</v>
@@ -9969,16 +9969,16 @@
         <v>0.08813561214552323</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.1980231339960792</v>
+        <v>0.1980230419469897</v>
       </c>
       <c r="AW49" t="n">
-        <v>-0.239288570100156</v>
+        <v>-0.2392884958736456</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.04009970393930895</v>
+        <v>0.04009977332007586</v>
       </c>
       <c r="AY49" t="n">
-        <v>6.540897009257804</v>
+        <v>6.540896553383485</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10120,16 +10120,16 @@
         <v>972.9046057128907</v>
       </c>
       <c r="AG50" t="n">
-        <v>909.8637399291993</v>
+        <v>909.8637384033203</v>
       </c>
       <c r="AH50" t="n">
         <v>-0.01569999847917847</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.05249826194560758</v>
+        <v>0.05249826371069055</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.06928605132522025</v>
+        <v>0.06928605311845693</v>
       </c>
       <c r="AK50" t="n">
         <v>1174.859985351562</v>
@@ -10165,14 +10165,14 @@
         <v>0.123024251461989</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.5798729601619486</v>
+        <v>0.5798731192460178</v>
       </c>
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="n">
         <v>0.4118234492047397</v>
       </c>
       <c r="AY50" t="n">
-        <v>6.327062135897167</v>
+        <v>6.327061280472001</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10329,13 +10329,13 @@
         <v>70.97299957275391</v>
       </c>
       <c r="AL51" t="n">
-        <v>55.35893249511719</v>
+        <v>55.35892868041992</v>
       </c>
       <c r="AM51" t="n">
         <v>-0.1450269726450951</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.09611940783951933</v>
+        <v>0.09611948337139498</v>
       </c>
       <c r="AO51" t="n">
         <v>18.68936533479501</v>
@@ -10368,7 +10368,7 @@
         <v>0.0561528752414322</v>
       </c>
       <c r="AY51" t="n">
-        <v>164.8600686808666</v>
+        <v>164.8599741037633</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10510,16 +10510,16 @@
         <v>271.7564495849609</v>
       </c>
       <c r="AG52" t="n">
-        <v>289.5858560180664</v>
+        <v>289.5858558654785</v>
       </c>
       <c r="AH52" t="n">
         <v>-0.03122818459046683</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.09087414477436617</v>
+        <v>-0.09087414429533169</v>
       </c>
       <c r="AJ52" t="n">
-        <v>-0.06156863694334969</v>
+        <v>-0.06156863644887356</v>
       </c>
       <c r="AK52" t="n">
         <v>401.7044372558594</v>
@@ -10555,14 +10555,14 @@
         <v>-0.1240692355250037</v>
       </c>
       <c r="AV52" t="n">
-        <v>-0.1887301530280321</v>
+        <v>-0.1887300767359584</v>
       </c>
       <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="n">
-        <v>-0.2779842653226717</v>
+        <v>-0.2779843257511972</v>
       </c>
       <c r="AY52" t="n">
-        <v>5.511750838186389</v>
+        <v>5.51175022378211</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10677,10 +10677,10 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA53" t="n">
-        <v>138316256891.9482</v>
+        <v>138332022416.7041</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>0.1661898030828035</v>
       </c>
       <c r="AY53" t="n">
-        <v>5.543038962180086</v>
+        <v>5.543039534804142</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10944,13 +10944,13 @@
         <v>0.1183986562353625</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.144250231212266</v>
+        <v>1.144250765023386</v>
       </c>
       <c r="AX54" t="n">
         <v>0.06920124344057621</v>
       </c>
       <c r="AY54" t="n">
-        <v>183.4924292770543</v>
+        <v>183.4924498592876</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11146,7 +11146,7 @@
         <v>-0.03941617989464163</v>
       </c>
       <c r="AY55" t="n">
-        <v>219.5792895501604</v>
+        <v>219.5791370751232</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11286,25 +11286,25 @@
         <v>145.3874822998047</v>
       </c>
       <c r="AG56" t="n">
-        <v>155.1605130767822</v>
+        <v>155.160513381958</v>
       </c>
       <c r="AH56" t="n">
         <v>-0.04764836336908485</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.1076337402587131</v>
+        <v>-0.107633742013854</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-0.06298658455802664</v>
+        <v>-0.06298658640098143</v>
       </c>
       <c r="AK56" t="n">
-        <v>209.6322174072266</v>
+        <v>209.6322326660156</v>
       </c>
       <c r="AL56" t="n">
         <v>134.3016815185547</v>
       </c>
       <c r="AM56" t="n">
-        <v>-0.3395098881919564</v>
+        <v>-0.3395099362679567</v>
       </c>
       <c r="AN56" t="n">
         <v>0.03096256985239609</v>
@@ -11331,16 +11331,16 @@
         <v>-0.106759844392725</v>
       </c>
       <c r="AV56" t="n">
-        <v>-0.3092731680385243</v>
+        <v>-0.3092732206170424</v>
       </c>
       <c r="AW56" t="n">
-        <v>7.695947796224727</v>
+        <v>7.695947275378456</v>
       </c>
       <c r="AX56" t="n">
-        <v>-0.158322112185874</v>
+        <v>-0.1583221902564738</v>
       </c>
       <c r="AY56" t="n">
-        <v>11.23242664125129</v>
+        <v>11.2324276718771</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11478,16 +11478,16 @@
         <v>160.0781793212891</v>
       </c>
       <c r="AG57" t="n">
-        <v>190.2534168243408</v>
+        <v>190.2534169769287</v>
       </c>
       <c r="AH57" t="n">
         <v>-0.134985156579128</v>
       </c>
       <c r="AI57" t="n">
-        <v>-0.2721812646941781</v>
+        <v>-0.2721812652779065</v>
       </c>
       <c r="AJ57" t="n">
-        <v>-0.1586054957999112</v>
+        <v>-0.1586054964747302</v>
       </c>
       <c r="AK57" t="n">
         <v>237.7264404296875</v>
@@ -11523,7 +11523,7 @@
         <v>-0.3145072228219964</v>
       </c>
       <c r="AV57" t="n">
-        <v>-0.2096729426176661</v>
+        <v>-0.2096728737876118</v>
       </c>
       <c r="AW57" t="n">
         <v>1.67001670310633</v>
@@ -11532,7 +11532,7 @@
         <v>-0.2352728569253212</v>
       </c>
       <c r="AY57" t="n">
-        <v>8.787606917317095</v>
+        <v>8.787610216205161</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11724,7 +11724,7 @@
         <v>-0.1064326108321304</v>
       </c>
       <c r="AY58" t="n">
-        <v>13.71883815198651</v>
+        <v>13.71883697901052</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -11920,7 +11920,7 @@
         <v>-0.009562379157800005</v>
       </c>
       <c r="AY59" t="n">
-        <v>153.4515652729513</v>
+        <v>153.4514900077457</v>
       </c>
       <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
@@ -12062,16 +12062,16 @@
         <v>44.17409942626953</v>
       </c>
       <c r="AG60" t="n">
-        <v>44.95726451873779</v>
+        <v>44.95726448059082</v>
       </c>
       <c r="AH60" t="n">
         <v>-0.08679518820935073</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.1027034099066563</v>
+        <v>-0.1027034091452855</v>
       </c>
       <c r="AJ60" t="n">
-        <v>-0.01742021230277147</v>
+        <v>-0.0174202114690365</v>
       </c>
       <c r="AK60" t="n">
         <v>49.3515510559082</v>
@@ -12107,16 +12107,16 @@
         <v>-0.1492738745016563</v>
       </c>
       <c r="AV60" t="n">
-        <v>-0.04474463113747851</v>
+        <v>-0.04474445855637921</v>
       </c>
       <c r="AW60" t="n">
-        <v>0.35918476334674</v>
+        <v>0.35918458865148</v>
       </c>
       <c r="AX60" t="n">
         <v>-0.05603202758504211</v>
       </c>
       <c r="AY60" t="n">
-        <v>165.0873559212954</v>
+        <v>165.0873661109013</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12308,7 +12308,7 @@
         <v>-0.4602935511037844</v>
       </c>
       <c r="AY61" t="n">
-        <v>-0.9323864175883676</v>
+        <v>-0.9323864024103894</v>
       </c>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
@@ -12450,25 +12450,25 @@
         <v>117.9568788146973</v>
       </c>
       <c r="AG62" t="n">
-        <v>141.8342597198486</v>
+        <v>141.8342600250244</v>
       </c>
       <c r="AH62" t="n">
         <v>-0.1490958072546417</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.2923430280890308</v>
+        <v>-0.2923430296116514</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.1683470619321032</v>
+        <v>-0.1683470637215181</v>
       </c>
       <c r="AK62" t="n">
-        <v>182.8191833496094</v>
+        <v>182.8191986083984</v>
       </c>
       <c r="AL62" t="n">
         <v>97.84999847412109</v>
       </c>
       <c r="AM62" t="n">
-        <v>-0.4509875774106148</v>
+        <v>-0.45098762323329</v>
       </c>
       <c r="AN62" t="n">
         <v>0.02575374871495195</v>
@@ -12492,19 +12492,19 @@
         <v>-0.3244833791150672</v>
       </c>
       <c r="AU62" t="n">
-        <v>-0.3161314459318657</v>
+        <v>-0.3161313748332005</v>
       </c>
       <c r="AV62" t="n">
-        <v>-0.3764708441744087</v>
+        <v>-0.3764709623858677</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.780891814665653</v>
+        <v>1.780892402499267</v>
       </c>
       <c r="AX62" t="n">
         <v>-0.3900447879526898</v>
       </c>
       <c r="AY62" t="n">
-        <v>13.05982362428862</v>
+        <v>13.05982550254968</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -13030,28 +13030,28 @@
         <v>90.20786560058593</v>
       </c>
       <c r="AG65" t="n">
-        <v>90.9946240234375</v>
+        <v>90.99462379455566</v>
       </c>
       <c r="AH65" t="n">
         <v>-0.08123314190376285</v>
       </c>
       <c r="AI65" t="n">
-        <v>-0.08917699102673848</v>
+        <v>-0.08917698873571478</v>
       </c>
       <c r="AJ65" t="n">
-        <v>-0.008646207743535639</v>
+        <v>-0.00864620524995019</v>
       </c>
       <c r="AK65" t="n">
-        <v>97.49111938476562</v>
+        <v>97.49111175537109</v>
       </c>
       <c r="AL65" t="n">
-        <v>82.06203460693359</v>
+        <v>82.06204223632812</v>
       </c>
       <c r="AM65" t="n">
-        <v>-0.1498713136494241</v>
+        <v>-0.1498712471206192</v>
       </c>
       <c r="AN65" t="n">
-        <v>0.009967613530450503</v>
+        <v>0.009967519632697375</v>
       </c>
       <c r="AO65" t="n">
         <v>19.62834871173233</v>
@@ -13075,16 +13075,16 @@
         <v>-0.1181972019490296</v>
       </c>
       <c r="AV65" t="n">
-        <v>-0.08617056634349263</v>
+        <v>-0.08617064321591972</v>
       </c>
       <c r="AW65" t="n">
         <v>0.5556388513938282</v>
       </c>
       <c r="AX65" t="n">
-        <v>-0.02594550314558741</v>
+        <v>-0.02594541580685272</v>
       </c>
       <c r="AY65" t="n">
-        <v>307.1380879600175</v>
+        <v>307.1380538178492</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
@@ -13652,13 +13652,13 @@
         <v>7.791230266833614</v>
       </c>
       <c r="AW68" t="n">
-        <v>6.680746494023148</v>
+        <v>6.680747388829383</v>
       </c>
       <c r="AX68" t="n">
         <v>1.437761504148903</v>
       </c>
       <c r="AY68" t="n">
-        <v>-0.4130547993440807</v>
+        <v>-0.4130548411470525</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13791,7 +13791,7 @@
         <v>35024</v>
       </c>
       <c r="AD69" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="AE69" t="n">
         <v>201.1499938964844</v>
@@ -13800,16 +13800,16 @@
         <v>187.4690005493164</v>
       </c>
       <c r="AG69" t="n">
-        <v>135.855426826477</v>
+        <v>135.855426864624</v>
       </c>
       <c r="AH69" t="n">
         <v>0.07297736322848203</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.4806180260535753</v>
+        <v>0.480618025637831</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.3799154360522043</v>
+        <v>0.3799154356647363</v>
       </c>
       <c r="AK69" t="n">
         <v>207.0800018310547</v>
@@ -13845,16 +13845,16 @@
         <v>0.9815750891441268</v>
       </c>
       <c r="AV69" t="n">
-        <v>0.6945709983450941</v>
+        <v>0.6945711072605758</v>
       </c>
       <c r="AW69" t="n">
-        <v>1.533330642914108</v>
+        <v>1.53333137317019</v>
       </c>
       <c r="AX69" t="n">
         <v>0.9047091050924578</v>
       </c>
       <c r="AY69" t="n">
-        <v>213.5110321931475</v>
+        <v>213.511004922887</v>
       </c>
       <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
@@ -14007,13 +14007,13 @@
         <v>2918367.25</v>
       </c>
       <c r="AL70" t="n">
-        <v>303106.5</v>
+        <v>303106.46875</v>
       </c>
       <c r="AM70" t="n">
         <v>-0.3619720067787905</v>
       </c>
       <c r="AN70" t="n">
-        <v>5.143055328737589</v>
+        <v>5.143055962080981</v>
       </c>
       <c r="AO70" t="n">
         <v>69.50146627565982</v>
@@ -14037,16 +14037,16 @@
         <v>0.8891634548076679</v>
       </c>
       <c r="AV70" t="n">
-        <v>5.143055328737589</v>
+        <v>5.143055962080981</v>
       </c>
       <c r="AW70" t="n">
-        <v>15.93248355477577</v>
+        <v>15.93248114885339</v>
       </c>
       <c r="AX70" t="n">
         <v>1.756502698304518</v>
       </c>
       <c r="AY70" t="n">
-        <v>-9.137250550538589</v>
+        <v>-9.137252773110575</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14188,28 +14188,28 @@
         <v>255380</v>
       </c>
       <c r="AG71" t="n">
-        <v>222131.7525390625</v>
+        <v>222131.752578125</v>
       </c>
       <c r="AH71" t="n">
         <v>0.1179418905160936</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.2852732521875458</v>
+        <v>0.2852732519615269</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.149678049539949</v>
+        <v>0.149678049337775</v>
       </c>
       <c r="AK71" t="n">
         <v>362100.65625</v>
       </c>
       <c r="AL71" t="n">
-        <v>71700.2265625</v>
+        <v>71700.234375</v>
       </c>
       <c r="AM71" t="n">
         <v>-0.2115452013903938</v>
       </c>
       <c r="AN71" t="n">
-        <v>2.981856316048513</v>
+        <v>2.981855882183091</v>
       </c>
       <c r="AO71" t="n">
         <v>72.04968944099379</v>
@@ -14233,16 +14233,16 @@
         <v>0.509786177524149</v>
       </c>
       <c r="AV71" t="n">
-        <v>2.981856316048513</v>
+        <v>2.981855882183091</v>
       </c>
       <c r="AW71" t="n">
-        <v>3.02007264160377</v>
+        <v>3.020072199370236</v>
       </c>
       <c r="AX71" t="n">
         <v>1.228843914080214</v>
       </c>
       <c r="AY71" t="n">
-        <v>65.87021514403874</v>
+        <v>65.87020749636545</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14428,13 +14428,13 @@
         <v>5.773984066911588</v>
       </c>
       <c r="AW72" t="n">
-        <v>4.63895493371129</v>
+        <v>4.638955287352797</v>
       </c>
       <c r="AX72" t="n">
         <v>0.8986552642408132</v>
       </c>
       <c r="AY72" t="n">
-        <v>3.505364223650687</v>
+        <v>3.505364675148664</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14766,16 +14766,16 @@
         <v>304.2803045654297</v>
       </c>
       <c r="AG74" t="n">
-        <v>270.4669855499267</v>
+        <v>270.4669844818116</v>
       </c>
       <c r="AH74" t="n">
         <v>0.0359197973896408</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.1654287151320066</v>
+        <v>0.1654287197344615</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.1250182862309499</v>
+        <v>0.125018290673818</v>
       </c>
       <c r="AK74" t="n">
         <v>432.8701477050781</v>
@@ -14962,28 +14962,28 @@
         <v>941.6152026367188</v>
       </c>
       <c r="AG75" t="n">
-        <v>660.9748895263672</v>
+        <v>660.9748892974853</v>
       </c>
       <c r="AH75" t="n">
         <v>0.14938674127846</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.6373996144882315</v>
+        <v>0.6373996150552288</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.4245854382024243</v>
+        <v>0.4245854386957286</v>
       </c>
       <c r="AK75" t="n">
         <v>1213.373413085938</v>
       </c>
       <c r="AL75" t="n">
-        <v>156.5786895751953</v>
+        <v>156.5786743164062</v>
       </c>
       <c r="AM75" t="n">
         <v>-0.1080404287544562</v>
       </c>
       <c r="AN75" t="n">
-        <v>5.912051903315496</v>
+        <v>5.912052576903662</v>
       </c>
       <c r="AO75" t="n">
         <v>59.2134411896589</v>
@@ -15004,19 +15004,19 @@
         <v>-0.05486301595479481</v>
       </c>
       <c r="AU75" t="n">
-        <v>2.031468446287617</v>
+        <v>2.031468705416941</v>
       </c>
       <c r="AV75" t="n">
-        <v>5.912051903315496</v>
+        <v>5.912052576903662</v>
       </c>
       <c r="AW75" t="n">
-        <v>14.33611478685037</v>
+        <v>14.33611644483758</v>
       </c>
       <c r="AX75" t="n">
-        <v>2.433203927218402</v>
+        <v>2.433203594857768</v>
       </c>
       <c r="AY75" t="n">
-        <v>800.2455610933196</v>
+        <v>800.2457025201473</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15397,16 +15397,16 @@
         <v>1.415921234499359</v>
       </c>
       <c r="AV77" t="n">
-        <v>3.208056040020021</v>
+        <v>3.208055745310447</v>
       </c>
       <c r="AW77" t="n">
-        <v>11.8404214863361</v>
+        <v>11.84042011431825</v>
       </c>
       <c r="AX77" t="n">
         <v>2.198931924850136</v>
       </c>
       <c r="AY77" t="n">
-        <v>173.06469989886</v>
+        <v>173.0648574795769</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15594,13 +15594,13 @@
         <v>3.268839269984638</v>
       </c>
       <c r="AW78" t="n">
-        <v>9.7262711146311</v>
+        <v>9.72627015385547</v>
       </c>
       <c r="AX78" t="n">
         <v>1.436305513484498</v>
       </c>
       <c r="AY78" t="n">
-        <v>671.4500529914156</v>
+        <v>671.4501119931267</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -16296,13 +16296,13 @@
         <v>0.3844053237430947</v>
       </c>
       <c r="AW82" t="n">
-        <v>3.740811026950464</v>
+        <v>3.740810007371328</v>
       </c>
       <c r="AX82" t="n">
         <v>0.2098516379495721</v>
       </c>
       <c r="AY82" t="n">
-        <v>1345.084692990355</v>
+        <v>1345.084371905037</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -17028,16 +17028,16 @@
         <v>207.6196176147461</v>
       </c>
       <c r="AG86" t="n">
-        <v>213.5185118865967</v>
+        <v>213.5185122680664</v>
       </c>
       <c r="AH86" t="n">
         <v>0.05283883502521869</v>
       </c>
       <c r="AI86" t="n">
-        <v>0.02375196607771168</v>
+        <v>0.02375196424868831</v>
       </c>
       <c r="AJ86" t="n">
-        <v>-0.02762708591273622</v>
+        <v>-0.02762708764996658</v>
       </c>
       <c r="AK86" t="n">
         <v>246.3216247558594</v>
@@ -17070,19 +17070,19 @@
         <v>0.1066238854399169</v>
       </c>
       <c r="AU86" t="n">
-        <v>0.08979795528527346</v>
+        <v>0.08979803819047838</v>
       </c>
       <c r="AV86" t="n">
-        <v>0.03029253432585</v>
+        <v>0.03029246022710352</v>
       </c>
       <c r="AW86" t="n">
-        <v>0.6930063795391477</v>
+        <v>0.6930067797022803</v>
       </c>
       <c r="AX86" t="n">
-        <v>-0.05253904143142751</v>
+        <v>-0.05253910409460383</v>
       </c>
       <c r="AY86" t="n">
-        <v>7.211743604456366</v>
+        <v>7.211740662471664</v>
       </c>
       <c r="AZ86" t="inlineStr"/>
       <c r="BA86" t="n">
@@ -17468,7 +17468,7 @@
         <v>1.56939151190834</v>
       </c>
       <c r="AY88" t="n">
-        <v>19.90166847208789</v>
+        <v>19.90167534017597</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
@@ -17660,7 +17660,7 @@
         <v>0.4385016219413842</v>
       </c>
       <c r="AY89" t="n">
-        <v>192.567960657401</v>
+        <v>192.5679207708204</v>
       </c>
       <c r="AZ89" t="inlineStr"/>
       <c r="BA89" t="n">
@@ -17846,13 +17846,13 @@
         <v>0.6059637773489173</v>
       </c>
       <c r="AW90" t="n">
-        <v>30.92096392192995</v>
+        <v>30.92096615582546</v>
       </c>
       <c r="AX90" t="n">
         <v>0.4300581199887674</v>
       </c>
       <c r="AY90" t="n">
-        <v>234.9025983038881</v>
+        <v>234.9025830533115</v>
       </c>
       <c r="AZ90" t="inlineStr"/>
       <c r="BA90" t="n">
@@ -18384,16 +18384,16 @@
         <v>152.6000695800781</v>
       </c>
       <c r="AG93" t="n">
-        <v>148.4271802902222</v>
+        <v>148.4271798324585</v>
       </c>
       <c r="AH93" t="n">
         <v>0.02712931864630286</v>
       </c>
       <c r="AI93" t="n">
-        <v>0.05600608451017997</v>
+        <v>0.05600608776700389</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0.02811405082072316</v>
+        <v>0.02811405399152567</v>
       </c>
       <c r="AK93" t="n">
         <v>255.2094421386719</v>
@@ -18429,7 +18429,7 @@
         <v>0.1495930695699839</v>
       </c>
       <c r="AV93" t="n">
-        <v>0.9980649793849696</v>
+        <v>0.9980651737103265</v>
       </c>
       <c r="AW93" t="n">
         <v>3.675674402398077</v>
@@ -18580,28 +18580,28 @@
         <v>220.5695999145508</v>
       </c>
       <c r="AG94" t="n">
-        <v>162.4622030258179</v>
+        <v>162.4622031021118</v>
       </c>
       <c r="AH94" t="n">
         <v>0.1875616700709548</v>
       </c>
       <c r="AI94" t="n">
-        <v>0.6123134954644174</v>
+        <v>0.6123134947072579</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.3576671730808594</v>
+        <v>0.3576671724432847</v>
       </c>
       <c r="AK94" t="n">
         <v>316.3519592285156</v>
       </c>
       <c r="AL94" t="n">
-        <v>73.67494201660156</v>
+        <v>73.67493438720703</v>
       </c>
       <c r="AM94" t="n">
         <v>-0.1719981659661703</v>
       </c>
       <c r="AN94" t="n">
-        <v>2.555347249304681</v>
+        <v>2.555347617478024</v>
       </c>
       <c r="AO94" t="n">
         <v>70.02192129756001</v>
@@ -18625,16 +18625,16 @@
         <v>1.762813954942466</v>
       </c>
       <c r="AV94" t="n">
-        <v>2.132061746490468</v>
+        <v>2.132061460765076</v>
       </c>
       <c r="AW94" t="n">
-        <v>3.397652399348287</v>
+        <v>3.39765183606095</v>
       </c>
       <c r="AX94" t="n">
         <v>1.934605471513907</v>
       </c>
       <c r="AY94" t="n">
-        <v>20.59563350921103</v>
+        <v>20.59564030109542</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18749,10 +18749,10 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA95" t="n">
-        <v>6744983325.662903</v>
+        <v>6745752130.458435</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>0.0762354897688573</v>
       </c>
       <c r="AY95" t="n">
-        <v>7.396303255148405</v>
+        <v>7.396305238394937</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -19014,7 +19014,7 @@
         <v>0.1140776699029127</v>
       </c>
       <c r="AY96" t="n">
-        <v>26.17965372194638</v>
+        <v>26.17965986147926</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19200,13 +19200,13 @@
         <v>1.220085624877288</v>
       </c>
       <c r="AW97" t="n">
-        <v>1.16199442291542</v>
+        <v>1.161994637433406</v>
       </c>
       <c r="AX97" t="n">
         <v>0.5960061410178092</v>
       </c>
       <c r="AY97" t="n">
-        <v>16.3877959543951</v>
+        <v>16.38779768881264</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19321,10 +19321,10 @@
         </is>
       </c>
       <c r="Z98" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA98" t="n">
-        <v>41759174606.68311</v>
+        <v>41763934389.19775</v>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
@@ -19392,13 +19392,13 @@
         <v>0.4806952410073393</v>
       </c>
       <c r="AW98" t="n">
-        <v>3.30491360200337</v>
+        <v>3.304913313216455</v>
       </c>
       <c r="AX98" t="n">
         <v>0.3719659670072348</v>
       </c>
       <c r="AY98" t="n">
-        <v>10.6904537487034</v>
+        <v>10.69044948937395</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19540,28 +19540,28 @@
         <v>75.88820831298828</v>
       </c>
       <c r="AG99" t="n">
-        <v>77.87492372512817</v>
+        <v>77.87492368698121</v>
       </c>
       <c r="AH99" t="n">
         <v>0.03692001946946011</v>
       </c>
       <c r="AI99" t="n">
-        <v>0.01046651062099313</v>
+        <v>0.01046651111596919</v>
       </c>
       <c r="AJ99" t="n">
-        <v>-0.02551161936482038</v>
+        <v>-0.025511618887468</v>
       </c>
       <c r="AK99" t="n">
         <v>102.0957336425781</v>
       </c>
       <c r="AL99" t="n">
-        <v>47.76882934570312</v>
+        <v>47.76882553100586</v>
       </c>
       <c r="AM99" t="n">
         <v>-0.2292527842849128</v>
       </c>
       <c r="AN99" t="n">
-        <v>0.6473085800769058</v>
+        <v>0.6473087116267915</v>
       </c>
       <c r="AO99" t="n">
         <v>60.6603966424877</v>
@@ -19582,13 +19582,13 @@
         <v>-0.111122295515501</v>
       </c>
       <c r="AU99" t="n">
-        <v>0.2832382117748349</v>
+        <v>0.2832381319468698</v>
       </c>
       <c r="AV99" t="n">
-        <v>0.245389779588095</v>
+        <v>0.2453897043996527</v>
       </c>
       <c r="AW99" t="n">
-        <v>0.1214895875683</v>
+        <v>0.1214894656241532</v>
       </c>
       <c r="AX99" t="n">
         <v>0.2306508674734979</v>
@@ -19736,25 +19736,25 @@
         <v>376.0055322265625</v>
       </c>
       <c r="AG100" t="n">
-        <v>367.0419474792481</v>
+        <v>367.0419497680664</v>
       </c>
       <c r="AH100" t="n">
         <v>-0.06168934411845894</v>
       </c>
       <c r="AI100" t="n">
-        <v>-0.03877472321187203</v>
+        <v>-0.03877472920592806</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0.02442114534557716</v>
+        <v>0.02442113895744114</v>
       </c>
       <c r="AK100" t="n">
-        <v>479.9350891113281</v>
+        <v>479.9351196289062</v>
       </c>
       <c r="AL100" t="n">
         <v>292.4138793945312</v>
       </c>
       <c r="AM100" t="n">
-        <v>-0.2648797606945672</v>
+        <v>-0.2648798074385715</v>
       </c>
       <c r="AN100" t="n">
         <v>0.2065432676763428</v>
@@ -19778,19 +19778,19 @@
         <v>-0.0510070422899398</v>
       </c>
       <c r="AU100" t="n">
-        <v>0.1773708982535498</v>
+        <v>0.1773707783489811</v>
       </c>
       <c r="AV100" t="n">
         <v>0.05752237848357877</v>
       </c>
       <c r="AW100" t="n">
-        <v>6.846206352959322</v>
+        <v>6.846205687320551</v>
       </c>
       <c r="AX100" t="n">
-        <v>0.02052367955942147</v>
+        <v>0.02052376964502511</v>
       </c>
       <c r="AY100" t="n">
-        <v>310.2497735497959</v>
+        <v>310.249675350489</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -20124,25 +20124,25 @@
         <v>52.49704002380371</v>
       </c>
       <c r="AG102" t="n">
-        <v>47.06169429779052</v>
+        <v>47.06169447898865</v>
       </c>
       <c r="AH102" t="n">
         <v>-0.01080136553167221</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.1034451921042252</v>
+        <v>0.1034451878557126</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.1154940510985465</v>
+        <v>0.1154940468036429</v>
       </c>
       <c r="AK102" t="n">
-        <v>79.68086242675781</v>
+        <v>79.68085479736328</v>
       </c>
       <c r="AL102" t="n">
         <v>21.00741767883301</v>
       </c>
       <c r="AM102" t="n">
-        <v>-0.3482751224874161</v>
+        <v>-0.3482750600851461</v>
       </c>
       <c r="AN102" t="n">
         <v>1.471983996276717</v>
@@ -20166,19 +20166,19 @@
         <v>-0.304443372822237</v>
       </c>
       <c r="AU102" t="n">
-        <v>0.6004714482808891</v>
+        <v>0.6004712601164441</v>
       </c>
       <c r="AV102" t="n">
-        <v>0.8518041202053954</v>
+        <v>0.8518042461564705</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.2105726840906859</v>
+        <v>0.2105724687860349</v>
       </c>
       <c r="AX102" t="n">
         <v>0.9082135192606642</v>
       </c>
       <c r="AY102" t="n">
-        <v>22.75729774603112</v>
+        <v>22.75728219830729</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20506,16 +20506,16 @@
         <v>262.2336721801758</v>
       </c>
       <c r="AG104" t="n">
-        <v>199.7437473297119</v>
+        <v>199.7437478637695</v>
       </c>
       <c r="AH104" t="n">
         <v>0.09444373643521931</v>
       </c>
       <c r="AI104" t="n">
-        <v>0.4368409716788602</v>
+        <v>0.4368409678371588</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.3128504680915662</v>
+        <v>0.3128504645813797</v>
       </c>
       <c r="AK104" t="n">
         <v>317.5</v>
@@ -20557,10 +20557,10 @@
         <v>5.292819634281168</v>
       </c>
       <c r="AX104" t="n">
-        <v>0.765574086108481</v>
+        <v>0.7655739203750871</v>
       </c>
       <c r="AY104" t="n">
-        <v>74.89731385863928</v>
+        <v>74.89729950268116</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20702,28 +20702,28 @@
         <v>418.7993347167969</v>
       </c>
       <c r="AG105" t="n">
-        <v>385.2207057189942</v>
+        <v>385.2207051086426</v>
       </c>
       <c r="AH105" t="n">
         <v>0.05057476102213543</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.1421504723250235</v>
+        <v>0.1421504741346704</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.08716724853906799</v>
+        <v>0.08716725026159811</v>
       </c>
       <c r="AK105" t="n">
         <v>459.9599914550781</v>
       </c>
       <c r="AL105" t="n">
-        <v>313.2000427246094</v>
+        <v>313.2000122070312</v>
       </c>
       <c r="AM105" t="n">
         <v>-0.04343851821882061</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.4047891154765706</v>
+        <v>0.4047892523563914</v>
       </c>
       <c r="AO105" t="n">
         <v>61.33198944836609</v>
@@ -20747,16 +20747,16 @@
         <v>0.2376354618062948</v>
       </c>
       <c r="AV105" t="n">
-        <v>0.219733120496622</v>
+        <v>0.2197332236888023</v>
       </c>
       <c r="AW105" t="n">
-        <v>2.038087395087606</v>
+        <v>2.03808675488483</v>
       </c>
       <c r="AX105" t="n">
         <v>0.3554750473354551</v>
       </c>
       <c r="AY105" t="n">
-        <v>1275.997004135046</v>
+        <v>1275.995678641205</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20871,10 +20871,10 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA106" t="n">
-        <v>186868044484.207</v>
+        <v>186889344025.1836</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>0.2467988101166367</v>
       </c>
       <c r="AY106" t="n">
-        <v>14.63744467957947</v>
+        <v>14.63744628234027</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21090,16 +21090,16 @@
         <v>372.4577258300781</v>
       </c>
       <c r="AG107" t="n">
-        <v>354.6833262634277</v>
+        <v>354.6833261108399</v>
       </c>
       <c r="AH107" t="n">
         <v>0.05676424143523606</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.1097223268149459</v>
+        <v>0.1097223272923582</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.0501134342961731</v>
+        <v>0.05011343474794105</v>
       </c>
       <c r="AK107" t="n">
         <v>444.1268615722656</v>
@@ -21135,16 +21135,16 @@
         <v>0.2876677576703803</v>
       </c>
       <c r="AV107" t="n">
-        <v>0.6099978391862757</v>
+        <v>0.609997738697968</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.524709046396856</v>
+        <v>1.524709787722506</v>
       </c>
       <c r="AX107" t="n">
         <v>0.450720276846905</v>
       </c>
       <c r="AY107" t="n">
-        <v>888.9608692880582</v>
+        <v>888.960929258447</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21286,16 +21286,16 @@
         <v>1303.824204101563</v>
       </c>
       <c r="AG108" t="n">
-        <v>1270.887424926758</v>
+        <v>1270.887425231934</v>
       </c>
       <c r="AH108" t="n">
         <v>0.0487840687489034</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.07596473683713056</v>
+        <v>0.07596473657876124</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.02591636247931484</v>
+        <v>0.02591636223296345</v>
       </c>
       <c r="AK108" t="n">
         <v>1687.3154296875</v>
@@ -21334,13 +21334,13 @@
         <v>0.5447766128658031</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.902251501551587</v>
+        <v>1.902252065496096</v>
       </c>
       <c r="AX108" t="n">
         <v>0.4655985918095813</v>
       </c>
       <c r="AY108" t="n">
-        <v>161.8929935378079</v>
+        <v>161.893030548727</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21526,13 +21526,13 @@
         <v>0.7133582892581551</v>
       </c>
       <c r="AW109" t="n">
-        <v>4.481576239323262</v>
+        <v>4.481576587911547</v>
       </c>
       <c r="AX109" t="n">
         <v>0.5463506256751971</v>
       </c>
       <c r="AY109" t="n">
-        <v>7.60881025344789</v>
+        <v>7.608808533885162</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21674,16 +21674,16 @@
         <v>455.2322113037109</v>
       </c>
       <c r="AG110" t="n">
-        <v>444.3598246765137</v>
+        <v>444.3598249816894</v>
       </c>
       <c r="AH110" t="n">
         <v>-0.001740230244331564</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.02268471901624047</v>
+        <v>0.02268471831388497</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.02446752839348654</v>
+        <v>0.02446752768990645</v>
       </c>
       <c r="AK110" t="n">
         <v>502.2725524902344</v>
@@ -21719,16 +21719,16 @@
         <v>0.1129074435950812</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.1261055104045592</v>
+        <v>0.1261054252453448</v>
       </c>
       <c r="AW110" t="n">
-        <v>1.637343933888806</v>
+        <v>1.637342766146897</v>
       </c>
       <c r="AX110" t="n">
         <v>0.1498724731104746</v>
       </c>
       <c r="AY110" t="n">
-        <v>509.9489769980286</v>
+        <v>509.9487373044194</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21920,7 +21920,7 @@
         <v>0.9296355492413031</v>
       </c>
       <c r="AY111" t="n">
-        <v>76.32184854944427</v>
+        <v>76.32184257907576</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22035,10 +22035,10 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA112" t="n">
-        <v>84011204682.28711</v>
+        <v>84020780423.83008</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
@@ -22106,13 +22106,13 @@
         <v>0.7296117555351305</v>
       </c>
       <c r="AW112" t="n">
-        <v>0.5796862917864885</v>
+        <v>0.5796864596445421</v>
       </c>
       <c r="AX112" t="n">
         <v>0.4934371861608546</v>
       </c>
       <c r="AY112" t="n">
-        <v>0.1224682394767276</v>
+        <v>0.1224684937319684</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22308,7 +22308,7 @@
         <v>0.4768849337155752</v>
       </c>
       <c r="AY113" t="n">
-        <v>87.26746932674254</v>
+        <v>87.26749221959248</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22450,16 +22450,16 @@
         <v>270.7192205810547</v>
       </c>
       <c r="AG114" t="n">
-        <v>244.5234378051758</v>
+        <v>244.5234376525879</v>
       </c>
       <c r="AH114" t="n">
         <v>0.02715280698351163</v>
       </c>
       <c r="AI114" t="n">
-        <v>0.1371916320993787</v>
+        <v>0.1371916328090108</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.1071299463601949</v>
+        <v>0.1071299470510678</v>
       </c>
       <c r="AK114" t="n">
         <v>330.5873718261719</v>
@@ -22498,13 +22498,13 @@
         <v>0.5670797941975487</v>
       </c>
       <c r="AW114" t="n">
-        <v>0.6635519410514092</v>
+        <v>0.6635522447681472</v>
       </c>
       <c r="AX114" t="n">
         <v>0.5927639507155185</v>
       </c>
       <c r="AY114" t="n">
-        <v>405.4908825267948</v>
+        <v>405.4909887816887</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22882,13 +22882,13 @@
         <v>0.1717838514152377</v>
       </c>
       <c r="AW116" t="n">
-        <v>-0.01602187166748437</v>
+        <v>-0.01602169035959555</v>
       </c>
       <c r="AX116" t="n">
         <v>0.0394833183011809</v>
       </c>
       <c r="AY116" t="n">
-        <v>18.45301199031431</v>
+        <v>18.45302084819141</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -23028,16 +23028,16 @@
         <v>265.8928448486328</v>
       </c>
       <c r="AG117" t="n">
-        <v>262.6495832061768</v>
+        <v>262.649584197998</v>
       </c>
       <c r="AH117" t="n">
         <v>-0.04743582354205944</v>
       </c>
       <c r="AI117" t="n">
-        <v>-0.03567332684295521</v>
+        <v>-0.03567333048445986</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0.01234824591330153</v>
+        <v>0.01234824209045726</v>
       </c>
       <c r="AK117" t="n">
         <v>376.0595397949219</v>
@@ -23073,16 +23073,16 @@
         <v>0.009259564961147992</v>
       </c>
       <c r="AV117" t="n">
-        <v>0.8140491627255066</v>
+        <v>0.8140493609773924</v>
       </c>
       <c r="AW117" t="n">
-        <v>9.668620989354972</v>
+        <v>9.668622703611556</v>
       </c>
       <c r="AX117" t="n">
-        <v>0.4432839867327789</v>
+        <v>0.4432841122267315</v>
       </c>
       <c r="AY117" t="n">
-        <v>24.49444453083917</v>
+        <v>24.49443718888907</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -23224,28 +23224,28 @@
         <v>60.74507766723633</v>
       </c>
       <c r="AG118" t="n">
-        <v>61.27004327774048</v>
+        <v>61.27004329681397</v>
       </c>
       <c r="AH118" t="n">
         <v>-0.07202359274801495</v>
       </c>
       <c r="AI118" t="n">
-        <v>-0.07997455336604775</v>
+        <v>-0.07997455365245354</v>
       </c>
       <c r="AJ118" t="n">
-        <v>-0.008568063321327313</v>
+        <v>-0.008568063629962097</v>
       </c>
       <c r="AK118" t="n">
         <v>75.72768402099609</v>
       </c>
       <c r="AL118" t="n">
-        <v>49.78788757324219</v>
+        <v>49.78789138793945</v>
       </c>
       <c r="AM118" t="n">
         <v>-0.2556223043047805</v>
       </c>
       <c r="AN118" t="n">
-        <v>0.1322030654335302</v>
+        <v>0.1322029786852903</v>
       </c>
       <c r="AO118" t="n">
         <v>34.81817585968568</v>
@@ -23278,7 +23278,7 @@
         <v>0.06535395360000229</v>
       </c>
       <c r="AY118" t="n">
-        <v>4.116076178243171</v>
+        <v>4.116075735424395</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23664,7 +23664,7 @@
         <v>0.3410842111491788</v>
       </c>
       <c r="AW120" t="n">
-        <v>-0.4745439498602024</v>
+        <v>-0.4745438288429344</v>
       </c>
       <c r="AX120" t="n">
         <v>0.4156289232080181</v>
@@ -23785,10 +23785,10 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA121" t="n">
-        <v>40294144798.73047</v>
+        <v>40298737594.62891</v>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>-0.01832959864784878</v>
       </c>
       <c r="AW121" t="n">
-        <v>0.5836177339855577</v>
+        <v>0.5836175920994819</v>
       </c>
       <c r="AX121" t="n">
         <v>0.07230977349861067</v>
@@ -24240,13 +24240,13 @@
         <v>0.08429593175282291</v>
       </c>
       <c r="AW123" t="n">
-        <v>0.8457305070302514</v>
+        <v>0.845730703635567</v>
       </c>
       <c r="AX123" t="n">
         <v>-0.3133437612096632</v>
       </c>
       <c r="AY123" t="n">
-        <v>1.119014021208828</v>
+        <v>1.119014409911592</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
@@ -24438,7 +24438,7 @@
         <v>0.406647331570317</v>
       </c>
       <c r="AY124" t="n">
-        <v>223.3919078918137</v>
+        <v>223.3918321308263</v>
       </c>
       <c r="AZ124" t="inlineStr"/>
       <c r="BA124" t="n">
@@ -24859,10 +24859,10 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA127" t="n">
-        <v>247546205859.6113</v>
+        <v>247574421601.7402</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>0.2564834700765968</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.264123595417745</v>
+        <v>1.264123454885132</v>
       </c>
       <c r="AX127" t="n">
         <v>0.178832592577272</v>
@@ -25443,10 +25443,10 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA130" t="n">
-        <v>16922678143.29358</v>
+        <v>16924607019.24207</v>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
@@ -25514,13 +25514,13 @@
         <v>0.4771729452598961</v>
       </c>
       <c r="AW130" t="n">
-        <v>2.03946522260255</v>
+        <v>2.039465034748069</v>
       </c>
       <c r="AX130" t="n">
         <v>0.2661482496603313</v>
       </c>
       <c r="AY130" t="n">
-        <v>88.08438449919859</v>
+        <v>88.08437441339828</v>
       </c>
       <c r="AZ130" t="inlineStr"/>
       <c r="BA130" t="n">
@@ -25712,7 +25712,7 @@
         <v>0.6078526162194904</v>
       </c>
       <c r="AY131" t="n">
-        <v>13.33677734850123</v>
+        <v>13.33678325220268</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25902,13 +25902,13 @@
         <v>0.6459882737620408</v>
       </c>
       <c r="AW132" t="n">
-        <v>3.255831738060457</v>
+        <v>3.255832351381999</v>
       </c>
       <c r="AX132" t="n">
         <v>0.4209601805360748</v>
       </c>
       <c r="AY132" t="n">
-        <v>143.6790741404032</v>
+        <v>143.6790962907631</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26094,7 +26094,7 @@
         <v>1.553595568581633</v>
       </c>
       <c r="AW133" t="n">
-        <v>1.093832985542741</v>
+        <v>1.093832776235337</v>
       </c>
       <c r="AX133" t="n">
         <v>0.2952325169532275</v>
@@ -26296,7 +26296,7 @@
         <v>0.5447745490227773</v>
       </c>
       <c r="AY134" t="n">
-        <v>19.83498546493184</v>
+        <v>19.83499296533227</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26438,28 +26438,28 @@
         <v>489.9774499511719</v>
       </c>
       <c r="AG135" t="n">
-        <v>420.7011661529541</v>
+        <v>420.7011660766602</v>
       </c>
       <c r="AH135" t="n">
         <v>-0.0101585286254865</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.1528373083322256</v>
+        <v>0.152837308541292</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.1646686279282408</v>
+        <v>0.1646686281394527</v>
       </c>
       <c r="AK135" t="n">
         <v>722.2277221679688</v>
       </c>
       <c r="AL135" t="n">
-        <v>198.5020751953125</v>
+        <v>198.5020904541016</v>
       </c>
       <c r="AM135" t="n">
         <v>-0.3284666523958168</v>
       </c>
       <c r="AN135" t="n">
-        <v>1.443299393836528</v>
+        <v>1.443299206020924</v>
       </c>
       <c r="AO135" t="n">
         <v>60.0745065025204</v>
@@ -26483,16 +26483,16 @@
         <v>0.4417717616862813</v>
       </c>
       <c r="AV135" t="n">
-        <v>1.443299393836528</v>
+        <v>1.443299206020924</v>
       </c>
       <c r="AW135" t="n">
-        <v>2.729672613302809</v>
+        <v>2.729672175660095</v>
       </c>
       <c r="AX135" t="n">
         <v>0.8102743521647287</v>
       </c>
       <c r="AY135" t="n">
-        <v>7035.836283905711</v>
+        <v>7035.834001859753</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26607,10 +26607,10 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>1.139990925788879</v>
+        <v>1.14012086391449</v>
       </c>
       <c r="AA136" t="n">
-        <v>47002811260.19189</v>
+        <v>47008168721.42725</v>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
@@ -26678,13 +26678,13 @@
         <v>0.6349564007325796</v>
       </c>
       <c r="AW136" t="n">
-        <v>1.4645250225073</v>
+        <v>1.464525241972418</v>
       </c>
       <c r="AX136" t="n">
         <v>0.5310371930731426</v>
       </c>
       <c r="AY136" t="n">
-        <v>286.3528141684976</v>
+        <v>286.3528374773008</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26826,16 +26826,16 @@
         <v>1717.254716796875</v>
       </c>
       <c r="AG137" t="n">
-        <v>1521.72969543457</v>
+        <v>1521.729696960449</v>
       </c>
       <c r="AH137" t="n">
         <v>0.01553946793586314</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.1460247812987718</v>
+        <v>0.1460247801496222</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.1284886678290571</v>
+        <v>0.1284886666974914</v>
       </c>
       <c r="AK137" t="n">
         <v>1986.870361328125</v>
@@ -26868,19 +26868,19 @@
         <v>-0.07270665806770538</v>
       </c>
       <c r="AU137" t="n">
-        <v>0.3436083043946541</v>
+        <v>0.3436081780305129</v>
       </c>
       <c r="AV137" t="n">
-        <v>0.848693165278898</v>
+        <v>0.8486932848918576</v>
       </c>
       <c r="AW137" t="n">
-        <v>1.174124695407942</v>
+        <v>1.17412486083916</v>
       </c>
       <c r="AX137" t="n">
         <v>0.5057120989162642</v>
       </c>
       <c r="AY137" t="n">
-        <v>990.0116360249762</v>
+        <v>990.0110318283058</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27022,16 +27022,16 @@
         <v>188.7938778686523</v>
       </c>
       <c r="AG138" t="n">
-        <v>175.6209778976441</v>
+        <v>175.6209772491455</v>
       </c>
       <c r="AH138" t="n">
         <v>-0.004628750198748532</v>
       </c>
       <c r="AI138" t="n">
-        <v>0.07003161250172174</v>
+        <v>0.07003161645292377</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0.07500755393063452</v>
+        <v>0.07500755790021052</v>
       </c>
       <c r="AK138" t="n">
         <v>301.3693542480469</v>
@@ -27064,19 +27064,19 @@
         <v>-0.3242128361712624</v>
       </c>
       <c r="AU138" t="n">
-        <v>0.3052327587056585</v>
+        <v>0.3052328970377829</v>
       </c>
       <c r="AV138" t="n">
-        <v>0.7839085704353117</v>
+        <v>0.7839084412353969</v>
       </c>
       <c r="AW138" t="n">
-        <v>4.554449323391826</v>
+        <v>4.554448070830514</v>
       </c>
       <c r="AX138" t="n">
         <v>0.4799665059942999</v>
       </c>
       <c r="AY138" t="n">
-        <v>3099.751350421347</v>
+        <v>3099.751541020528</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27414,16 +27414,16 @@
         <v>368.8975042724609</v>
       </c>
       <c r="AG140" t="n">
-        <v>329.4916696929932</v>
+        <v>329.4916688537598</v>
       </c>
       <c r="AH140" t="n">
         <v>0.07992057487213655</v>
       </c>
       <c r="AI140" t="n">
-        <v>0.2090745883014482</v>
+        <v>0.2090745913810277</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0.1195958447634944</v>
+        <v>0.1195958476151664</v>
       </c>
       <c r="AK140" t="n">
         <v>483.6542053222656</v>
@@ -27465,10 +27465,10 @@
         <v>2.486006594486356</v>
       </c>
       <c r="AX140" t="n">
-        <v>0.9216143183283194</v>
+        <v>0.9216141768939503</v>
       </c>
       <c r="AY140" t="n">
-        <v>356.8262331732931</v>
+        <v>356.8263098012082</v>
       </c>
       <c r="AZ140" t="inlineStr"/>
       <c r="BA140" t="n">
@@ -27660,7 +27660,7 @@
         <v>2.155318033974383</v>
       </c>
       <c r="AY141" t="n">
-        <v>3.021142368754234</v>
+        <v>3.021142051590146</v>
       </c>
       <c r="AZ141" t="inlineStr"/>
       <c r="BA141" t="n">
@@ -27802,16 +27802,16 @@
         <v>48.94534973144531</v>
       </c>
       <c r="AG142" t="n">
-        <v>53.83385149002075</v>
+        <v>53.83385187149048</v>
       </c>
       <c r="AH142" t="n">
         <v>0.001116556912036382</v>
       </c>
       <c r="AI142" t="n">
-        <v>-0.08979204266885499</v>
+        <v>-0.08979204911864036</v>
       </c>
       <c r="AJ142" t="n">
-        <v>-0.09080720816495225</v>
+        <v>-0.09080721460754393</v>
       </c>
       <c r="AK142" t="n">
         <v>89.60572814941406</v>
@@ -27844,14 +27844,14 @@
         <v>-0.3935439935291497</v>
       </c>
       <c r="AU142" t="n">
-        <v>0.1456388230822072</v>
+        <v>0.1456387209037351</v>
       </c>
       <c r="AV142" t="n">
         <v>0.4979819606206808</v>
       </c>
       <c r="AW142" t="inlineStr"/>
       <c r="AX142" t="n">
-        <v>0.3342481038334459</v>
+        <v>0.3342482424251489</v>
       </c>
       <c r="AY142" t="n">
         <v>0.0602096589507346</v>
@@ -28232,13 +28232,13 @@
         <v>0.4020311407371464</v>
       </c>
       <c r="AW144" t="n">
-        <v>4.62236426105842</v>
+        <v>4.622363691709574</v>
       </c>
       <c r="AX144" t="n">
         <v>0.06708750561591814</v>
       </c>
       <c r="AY144" t="n">
-        <v>36.10098751871566</v>
+        <v>36.10098132071804</v>
       </c>
       <c r="AZ144" t="inlineStr"/>
       <c r="BA144" t="n">
@@ -28430,7 +28430,7 @@
         <v>0.2731601995823187</v>
       </c>
       <c r="AY145" t="n">
-        <v>25.44539082701797</v>
+        <v>25.4453885592167</v>
       </c>
       <c r="AZ145" t="inlineStr"/>
       <c r="BA145" t="n">
@@ -28623,10 +28623,10 @@
         <v>11.12009484933358</v>
       </c>
       <c r="AX146" t="n">
-        <v>3.444749145197915</v>
+        <v>3.444749412967389</v>
       </c>
       <c r="AY146" t="n">
-        <v>50.34726498867979</v>
+        <v>50.34727838953583</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28818,7 +28818,7 @@
         <v>0.233972904707233</v>
       </c>
       <c r="AY147" t="n">
-        <v>37.44242868805576</v>
+        <v>37.44242486865427</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -29004,13 +29004,13 @@
         <v>0.3571674266861595</v>
       </c>
       <c r="AW148" t="n">
-        <v>0.7776045757422825</v>
+        <v>0.7776047077683348</v>
       </c>
       <c r="AX148" t="n">
         <v>0.3847440950462622</v>
       </c>
       <c r="AY148" t="n">
-        <v>-0.04590187539221324</v>
+        <v>-0.04590179932361727</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29152,16 +29152,16 @@
         <v>53.83076728820801</v>
       </c>
       <c r="AG149" t="n">
-        <v>35.71299161911011</v>
+        <v>35.71299164772034</v>
       </c>
       <c r="AH149" t="n">
         <v>0.169219793760889</v>
       </c>
       <c r="AI149" t="n">
-        <v>0.7623838209350584</v>
+        <v>0.7623838195231853</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0.507316101163674</v>
+        <v>0.5073160999561397</v>
       </c>
       <c r="AK149" t="n">
         <v>63.52000045776367</v>
@@ -29197,16 +29197,16 @@
         <v>1.643433697559597</v>
       </c>
       <c r="AV149" t="n">
-        <v>1.646630448626536</v>
+        <v>1.646630236355898</v>
       </c>
       <c r="AW149" t="n">
-        <v>4.42785959870894</v>
+        <v>4.427858705895967</v>
       </c>
       <c r="AX149" t="n">
         <v>1.635161918381633</v>
       </c>
       <c r="AY149" t="n">
-        <v>7.757651987969957</v>
+        <v>7.757654312198525</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29396,13 +29396,13 @@
         <v>0.4323802691522609</v>
       </c>
       <c r="AW150" t="n">
-        <v>1.272775329501393</v>
+        <v>1.272775591882894</v>
       </c>
       <c r="AX150" t="n">
         <v>0.2386792305030851</v>
       </c>
       <c r="AY150" t="n">
-        <v>47.7741097537466</v>
+        <v>47.77414751524423</v>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="n">
@@ -29517,10 +29517,10 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>1.324643611907959</v>
+        <v>1.325345873832703</v>
       </c>
       <c r="AA151" t="n">
-        <v>161550026489.0156</v>
+        <v>161635672493.3633</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>0.2376957390593266</v>
       </c>
       <c r="AY151" t="n">
-        <v>10.8985715284564</v>
+        <v>10.89857371585894</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29980,13 +29980,13 @@
         <v>0.1860221517709344</v>
       </c>
       <c r="AW153" t="n">
-        <v>1.735361642846396</v>
+        <v>1.735361187080555</v>
       </c>
       <c r="AX153" t="n">
         <v>0.111895732141569</v>
       </c>
       <c r="AY153" t="n">
-        <v>682.871995769219</v>
+        <v>682.8720514098509</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30178,7 +30178,7 @@
         <v>0.4489550528289952</v>
       </c>
       <c r="AY154" t="n">
-        <v>74.21902206307463</v>
+        <v>74.21901696066823</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30512,16 +30512,16 @@
         <v>112.4467997741699</v>
       </c>
       <c r="AG156" t="n">
-        <v>96.54890575408936</v>
+        <v>96.54890602111817</v>
       </c>
       <c r="AH156" t="n">
         <v>-0.05110685975473905</v>
       </c>
       <c r="AI156" t="n">
-        <v>0.105139370714441</v>
+        <v>0.1051393676579169</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.1646615660313395</v>
+        <v>0.1646615628101928</v>
       </c>
       <c r="AK156" t="n">
         <v>129.5154876708984</v>
@@ -30554,7 +30554,7 @@
         <v>-0.09006662924666542</v>
       </c>
       <c r="AU156" t="n">
-        <v>0.347341123581477</v>
+        <v>0.3473409937796648</v>
       </c>
       <c r="AV156" t="n">
         <v>0.6051493299014568</v>
@@ -30566,7 +30566,7 @@
         <v>0.4160900699813914</v>
       </c>
       <c r="AY156" t="n">
-        <v>2153.053226853755</v>
+        <v>2153.053550849</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30708,16 +30708,16 @@
         <v>317.5754479980469</v>
       </c>
       <c r="AG157" t="n">
-        <v>299.5867183685303</v>
+        <v>299.5867188262939</v>
       </c>
       <c r="AH157" t="n">
         <v>-0.002630737889022794</v>
       </c>
       <c r="AI157" t="n">
-        <v>0.05725644968260579</v>
+        <v>0.05725644806713492</v>
       </c>
       <c r="AJ157" t="n">
-        <v>0.06004515062442817</v>
+        <v>0.06004514900469649</v>
       </c>
       <c r="AK157" t="n">
         <v>385.5466918945312</v>
@@ -30753,16 +30753,16 @@
         <v>0.2136344172425784</v>
       </c>
       <c r="AV157" t="n">
-        <v>0.5085883158613</v>
+        <v>0.5085880965865712</v>
       </c>
       <c r="AW157" t="n">
         <v>4.441984587983346</v>
       </c>
       <c r="AX157" t="n">
-        <v>0.3186055320664571</v>
+        <v>0.3186054483044782</v>
       </c>
       <c r="AY157" t="n">
-        <v>427.7155353108029</v>
+        <v>427.7154661363755</v>
       </c>
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="n">
@@ -30948,13 +30948,13 @@
         <v>0.4249228414597195</v>
       </c>
       <c r="AW158" t="n">
-        <v>2.044471400980149</v>
+        <v>2.044471105840875</v>
       </c>
       <c r="AX158" t="n">
         <v>0.3881403764178835</v>
       </c>
       <c r="AY158" t="n">
-        <v>6.881831946654767</v>
+        <v>6.881827990371601</v>
       </c>
       <c r="AZ158" t="inlineStr"/>
       <c r="BA158" t="n">
@@ -31140,7 +31140,7 @@
         <v>0.2881444035875367</v>
       </c>
       <c r="AW159" t="n">
-        <v>4.238181266293361</v>
+        <v>4.238180647860732</v>
       </c>
       <c r="AX159" t="n">
         <v>0.274193374221289</v>
@@ -32574,25 +32574,25 @@
         <v>376.0055322265625</v>
       </c>
       <c r="AG5" t="n">
-        <v>367.0419474792481</v>
+        <v>367.0419497680664</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.06168934411845894</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.03877472321187203</v>
+        <v>-0.03877472920592806</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.02442114534557716</v>
+        <v>0.02442113895744114</v>
       </c>
       <c r="AK5" t="n">
-        <v>479.9350891113281</v>
+        <v>479.9351196289062</v>
       </c>
       <c r="AL5" t="n">
         <v>292.4138793945312</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.2648797606945672</v>
+        <v>-0.2648798074385715</v>
       </c>
       <c r="AN5" t="n">
         <v>0.2065432676763428</v>
@@ -32616,19 +32616,19 @@
         <v>-0.0510070422899398</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1773708982535498</v>
+        <v>0.1773707783489811</v>
       </c>
       <c r="AV5" t="n">
         <v>0.05752237848357877</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.846206352959322</v>
+        <v>6.846205687320551</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.02052367955942147</v>
+        <v>0.02052376964502511</v>
       </c>
       <c r="AY5" t="n">
-        <v>310.2497735497959</v>
+        <v>310.249675350489</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32643,7 +32643,7 @@
         <v>0.125</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.002565459944927684</v>
+        <v>0.002565471205628139</v>
       </c>
     </row>
     <row r="6">
@@ -32976,16 +32976,16 @@
         <v>304.2803045654297</v>
       </c>
       <c r="AG7" t="n">
-        <v>270.4669855499267</v>
+        <v>270.4669844818116</v>
       </c>
       <c r="AH7" t="n">
         <v>0.0359197973896408</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1654287151320066</v>
+        <v>0.1654287197344615</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1250182862309499</v>
+        <v>0.125018290673818</v>
       </c>
       <c r="AK7" t="n">
         <v>432.8701477050781</v>
@@ -33178,28 +33178,28 @@
         <v>220.5695999145508</v>
       </c>
       <c r="AG8" t="n">
-        <v>162.4622030258179</v>
+        <v>162.4622031021118</v>
       </c>
       <c r="AH8" t="n">
         <v>0.1875616700709548</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.6123134954644174</v>
+        <v>0.6123134947072579</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3576671730808594</v>
+        <v>0.3576671724432847</v>
       </c>
       <c r="AK8" t="n">
         <v>316.3519592285156</v>
       </c>
       <c r="AL8" t="n">
-        <v>73.67494201660156</v>
+        <v>73.67493438720703</v>
       </c>
       <c r="AM8" t="n">
         <v>-0.1719981659661703</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.555347249304681</v>
+        <v>2.555347617478024</v>
       </c>
       <c r="AO8" t="n">
         <v>70.02192129756001</v>
@@ -33223,16 +33223,16 @@
         <v>1.762813954942466</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.132061746490468</v>
+        <v>2.132061460765076</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.397652399348287</v>
+        <v>3.39765183606095</v>
       </c>
       <c r="AX8" t="n">
         <v>1.934605471513907</v>
       </c>
       <c r="AY8" t="n">
-        <v>20.59563350921103</v>
+        <v>20.59564030109542</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33499,7 +33499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.007054026128393</v>
+        <v>1.007054037389093</v>
       </c>
     </row>
     <row r="5">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9728410122234974</v>
+        <v>0.9728409765078234</v>
       </c>
     </row>
   </sheetData>
@@ -33677,40 +33677,40 @@
         <v>0.625</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9055617320817689</v>
+        <v>0.905561714270536</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5212363051646919</v>
+        <v>0.5212362339197598</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4925719653776622</v>
+        <v>0.4925719102496884</v>
       </c>
       <c r="N2" t="n">
-        <v>1.040797696994961</v>
+        <v>1.040797690510431</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4661194405226031</v>
+        <v>0.4661193610642681</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6497145093707747</v>
+        <v>0.6497145383520829</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.752124680229962</v>
+        <v>4.75212469342918</v>
       </c>
       <c r="R2" t="n">
         <v>1.744083515325491</v>
       </c>
       <c r="S2" t="n">
-        <v>5.42496772535404</v>
+        <v>5.424968016100467</v>
       </c>
       <c r="T2" t="n">
-        <v>1372.385343423687</v>
+        <v>1372.385260199396</v>
       </c>
       <c r="U2" t="n">
-        <v>400.1803374003204</v>
+        <v>400.1803908574324</v>
       </c>
       <c r="V2" t="n">
-        <v>3938.733396349411</v>
+        <v>3938.732960836293</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33728,10 +33728,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>265.5745848358625</v>
+        <v>265.575612123407</v>
       </c>
       <c r="D3" t="n">
-        <v>37.93922640512322</v>
+        <v>37.93937316048673</v>
       </c>
       <c r="E3" t="n">
         <v>15.99267225801965</v>
@@ -33743,7 +33743,7 @@
         <v>85</v>
       </c>
       <c r="H3" t="n">
-        <v>85.57486775271047</v>
+        <v>85.5748655290331</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
@@ -33758,7 +33758,7 @@
         <v>2.267312882239865</v>
       </c>
       <c r="M3" t="n">
-        <v>2.599623247834129</v>
+        <v>2.599633323004584</v>
       </c>
       <c r="N3" t="n">
         <v>4.678350345170606</v>
@@ -33767,25 +33767,25 @@
         <v>5.001539971344583</v>
       </c>
       <c r="P3" t="n">
-        <v>4.540618106698685</v>
+        <v>4.540632949820639</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.888431238301459</v>
+        <v>4.888431286334429</v>
       </c>
       <c r="R3" t="n">
-        <v>5.601695664220405</v>
+        <v>5.601695195213436</v>
       </c>
       <c r="S3" t="n">
-        <v>6.027055756669901</v>
+        <v>6.027055420151694</v>
       </c>
       <c r="T3" t="n">
-        <v>43.00721076092144</v>
+        <v>43.00719482825918</v>
       </c>
       <c r="U3" t="n">
-        <v>32.72988470878067</v>
+        <v>32.72988173426776</v>
       </c>
       <c r="V3" t="n">
-        <v>64.13190608328796</v>
+        <v>64.13169749301183</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33803,10 +33803,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>1504.277199705826</v>
+        <v>1504.362845710174</v>
       </c>
       <c r="D4" t="n">
-        <v>94.01732498161412</v>
+        <v>94.02267785688585</v>
       </c>
       <c r="E4" t="n">
         <v>43.07282742404004</v>
@@ -33818,7 +33818,7 @@
         <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>82.18831167606113</v>
+        <v>82.18904106785449</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -33827,40 +33827,40 @@
         <v>0.5625</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5881330945076824</v>
+        <v>0.5881331060081508</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3516748135563597</v>
+        <v>0.3516747716753702</v>
       </c>
       <c r="M4" t="n">
-        <v>1.142784004156342</v>
+        <v>1.142732537755757</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7042279577952439</v>
+        <v>0.7042279308236584</v>
       </c>
       <c r="O4" t="n">
         <v>0.4630835358047549</v>
       </c>
       <c r="P4" t="n">
-        <v>1.225282265191111</v>
+        <v>1.225226887579246</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.481933922533894</v>
+        <v>7.481933805799946</v>
       </c>
       <c r="R4" t="n">
-        <v>4.434922093346144</v>
+        <v>4.434921646939657</v>
       </c>
       <c r="S4" t="n">
-        <v>6.715815156270618</v>
+        <v>6.715967104240008</v>
       </c>
       <c r="T4" t="n">
-        <v>232.6789188032539</v>
+        <v>232.6789408865921</v>
       </c>
       <c r="U4" t="n">
-        <v>42.87718834041497</v>
+        <v>42.87720722116379</v>
       </c>
       <c r="V4" t="n">
-        <v>685.8833360474944</v>
+        <v>685.8450068021061</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33902,40 +33902,40 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5769758133431759</v>
+        <v>0.5769758135866579</v>
       </c>
       <c r="L5" t="n">
         <v>0.1003133966328317</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09099419141569888</v>
+        <v>0.09099417449895303</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3221745944643722</v>
+        <v>0.3221745940506656</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01673949784981688</v>
+        <v>0.01673953902671166</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1350410528695067</v>
+        <v>0.1350410379403836</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.794110235478205</v>
+        <v>0.794110299777353</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5950008665450703</v>
+        <v>0.5950007053464587</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9676608789458957</v>
+        <v>0.9676610389721066</v>
       </c>
       <c r="T5" t="n">
-        <v>1235.099394353219</v>
+        <v>1235.098970162197</v>
       </c>
       <c r="U5" t="n">
-        <v>14.85816621371189</v>
+        <v>14.85816721353319</v>
       </c>
       <c r="V5" t="n">
-        <v>3023.271395229188</v>
+        <v>3023.270028603182</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33953,10 +33953,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>435.8740157789049</v>
+        <v>435.9041603969823</v>
       </c>
       <c r="D6" t="n">
-        <v>108.9685039447262</v>
+        <v>108.9760400992456</v>
       </c>
       <c r="E6" t="n">
         <v>85.70256588800001</v>
@@ -33968,7 +33968,7 @@
         <v>40</v>
       </c>
       <c r="H6" t="n">
-        <v>70.84246295862779</v>
+        <v>70.84382380457811</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -33983,7 +33983,7 @@
         <v>0.1147545876797981</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1010421695515214</v>
+        <v>0.1010479354603872</v>
       </c>
       <c r="N6" t="n">
         <v>0.1341336393761722</v>
@@ -33992,25 +33992,25 @@
         <v>0.09273499424020976</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1259520355721986</v>
+        <v>0.1259620389244424</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.16380975250516</v>
+        <v>1.163809670408386</v>
       </c>
       <c r="R6" t="n">
-        <v>1.145328496663655</v>
+        <v>1.145328426397349</v>
       </c>
       <c r="S6" t="n">
-        <v>1.069496819067063</v>
+        <v>1.069513622109289</v>
       </c>
       <c r="T6" t="n">
-        <v>82.87241047707388</v>
+        <v>82.87240795562381</v>
       </c>
       <c r="U6" t="n">
-        <v>70.57457382201993</v>
+        <v>70.57456877911977</v>
       </c>
       <c r="V6" t="n">
-        <v>62.80582153882442</v>
+        <v>62.80369788310124</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34028,13 +34028,13 @@
         <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>1656.69401358876</v>
+        <v>1656.729481667177</v>
       </c>
       <c r="D7" t="n">
-        <v>75.30427334494361</v>
+        <v>75.30588553032624</v>
       </c>
       <c r="E7" t="n">
-        <v>43.38067393536524</v>
+        <v>43.38297033331445</v>
       </c>
       <c r="F7" t="n">
         <v>51.81818181818182</v>
@@ -34043,7 +34043,7 @@
         <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>68.10123727000833</v>
+        <v>68.10141678076263</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
@@ -34052,40 +34052,40 @@
         <v>0.2608695652173913</v>
       </c>
       <c r="K7" t="n">
-        <v>0.391013952203104</v>
+        <v>0.3910139503740384</v>
       </c>
       <c r="L7" t="n">
         <v>0.4111381273891676</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4455993564882747</v>
+        <v>0.4455960476264313</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6265722827689394</v>
+        <v>0.6265722880324186</v>
       </c>
       <c r="O7" t="n">
         <v>0.5308391026935807</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5509355712545128</v>
+        <v>0.5509306107392195</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.839446791606827</v>
+        <v>2.83944690018817</v>
       </c>
       <c r="R7" t="n">
-        <v>1.481845839177678</v>
+        <v>1.481846209840504</v>
       </c>
       <c r="S7" t="n">
-        <v>2.533949586641576</v>
+        <v>2.533916277207341</v>
       </c>
       <c r="T7" t="n">
-        <v>180.862068901245</v>
+        <v>180.8620037400428</v>
       </c>
       <c r="U7" t="n">
-        <v>26.77552213133401</v>
+        <v>26.77551846035895</v>
       </c>
       <c r="V7" t="n">
-        <v>353.4566914974177</v>
+        <v>353.4492118004828</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34103,10 +34103,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>4308.502486581609</v>
+        <v>4308.507844042843</v>
       </c>
       <c r="D8" t="n">
-        <v>287.2334991054407</v>
+        <v>287.233856269523</v>
       </c>
       <c r="E8" t="n">
         <v>62.283030528</v>
@@ -34118,7 +34118,7 @@
         <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>64.96188418509711</v>
+        <v>64.96187801518791</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -34127,40 +34127,40 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5683272927831714</v>
+        <v>0.5683272925936602</v>
       </c>
       <c r="L8" t="n">
         <v>0.5057120989162642</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5041928970998252</v>
+        <v>0.5041929293137017</v>
       </c>
       <c r="N8" t="n">
-        <v>1.071034966717461</v>
+        <v>1.071034953557291</v>
       </c>
       <c r="O8" t="n">
-        <v>0.848693165278898</v>
+        <v>0.8486932848918576</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8677891783415167</v>
+        <v>0.8677888832871677</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.372289483486304</v>
+        <v>3.372289378440418</v>
       </c>
       <c r="R8" t="n">
-        <v>2.68317591428381</v>
+        <v>2.683175695462453</v>
       </c>
       <c r="S8" t="n">
-        <v>3.258481260750737</v>
+        <v>3.258479261693907</v>
       </c>
       <c r="T8" t="n">
-        <v>822.2161240593815</v>
+        <v>822.2159527970329</v>
       </c>
       <c r="U8" t="n">
-        <v>36.10098751871566</v>
+        <v>36.10098132071804</v>
       </c>
       <c r="V8" t="n">
-        <v>1048.499845380946</v>
+        <v>1048.498624544705</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34202,40 +34202,40 @@
         <v>0.1538461538461539</v>
       </c>
       <c r="K9" t="n">
-        <v>1.869675721946847</v>
+        <v>1.869675694250128</v>
       </c>
       <c r="L9" t="n">
         <v>1.437033508816701</v>
       </c>
       <c r="M9" t="n">
-        <v>1.960580439109166</v>
+        <v>1.960580356600908</v>
       </c>
       <c r="N9" t="n">
-        <v>5.762424276418952</v>
+        <v>5.762424333691623</v>
       </c>
       <c r="O9" t="n">
-        <v>4.205947299361114</v>
+        <v>4.205947616032809</v>
       </c>
       <c r="P9" t="n">
-        <v>5.320219439346271</v>
+        <v>5.320219598517901</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.58838068239765</v>
+        <v>7.588380527971815</v>
       </c>
       <c r="R9" t="n">
-        <v>5.659850713867218</v>
+        <v>5.65985133809109</v>
       </c>
       <c r="S9" t="n">
-        <v>9.764960238182228</v>
+        <v>9.764959948476745</v>
       </c>
       <c r="T9" t="n">
-        <v>307.1600739151501</v>
+        <v>307.1601006883538</v>
       </c>
       <c r="U9" t="n">
-        <v>57.12677491685444</v>
+        <v>57.12677109301779</v>
       </c>
       <c r="V9" t="n">
-        <v>384.7738326723382</v>
+        <v>384.7738736197971</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34286,31 +34286,31 @@
         <v>0.8115771873588377</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03757314638780895</v>
+        <v>0.03757320936334652</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03757314638780895</v>
+        <v>0.03757320936334652</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7387491948518414</v>
+        <v>0.7387493120588439</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2105726840906859</v>
+        <v>0.2105724687860349</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2105726840906859</v>
+        <v>0.2105724687860349</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2105726840906858</v>
+        <v>0.2105724687860349</v>
       </c>
       <c r="T10" t="n">
-        <v>11.2971379249581</v>
+        <v>11.29713015109619</v>
       </c>
       <c r="U10" t="n">
-        <v>11.2971379249581</v>
+        <v>11.29713015109619</v>
       </c>
       <c r="V10" t="n">
-        <v>21.16606926815026</v>
+        <v>21.16605479981718</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34328,10 +34328,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>3378.689924181914</v>
+        <v>3378.695452769225</v>
       </c>
       <c r="D11" t="n">
-        <v>168.9344962090957</v>
+        <v>168.9347726384612</v>
       </c>
       <c r="E11" t="n">
         <v>62.455136256</v>
@@ -34343,7 +34343,7 @@
         <v>60</v>
       </c>
       <c r="H11" t="n">
-        <v>55.53785091673058</v>
+        <v>55.53785821818201</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -34352,40 +34352,40 @@
         <v>0.2380952380952381</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6339882384115006</v>
+        <v>0.6339882397173306</v>
       </c>
       <c r="L11" t="n">
         <v>0.4730484528875036</v>
       </c>
       <c r="M11" t="n">
-        <v>0.38604246673975</v>
+        <v>0.3860424201457247</v>
       </c>
       <c r="N11" t="n">
-        <v>1.077608751265596</v>
+        <v>1.0776087398043</v>
       </c>
       <c r="O11" t="n">
         <v>0.8172846701872509</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6102462503610803</v>
+        <v>0.6102459303447335</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.354911009833363</v>
+        <v>6.354911019798642</v>
       </c>
       <c r="R11" t="n">
         <v>3.675674402398077</v>
       </c>
       <c r="S11" t="n">
-        <v>7.495481735817148</v>
+        <v>7.495473690232401</v>
       </c>
       <c r="T11" t="n">
-        <v>184.6447269822984</v>
+        <v>184.6447051677305</v>
       </c>
       <c r="U11" t="n">
-        <v>26.17965372194638</v>
+        <v>26.17965986147926</v>
       </c>
       <c r="V11" t="n">
-        <v>288.0565263034575</v>
+        <v>288.0560012356455</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34427,13 +34427,13 @@
         <v>0.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4162196097308432</v>
+        <v>0.4162196187394034</v>
       </c>
       <c r="L12" t="n">
         <v>0.2914011396250181</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2915407464717227</v>
+        <v>0.2915408013097682</v>
       </c>
       <c r="N12" t="n">
         <v>0.3546216641588759</v>
@@ -34445,22 +34445,22 @@
         <v>0.2782766052826565</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.452434560179699</v>
+        <v>1.452434478316232</v>
       </c>
       <c r="R12" t="n">
         <v>0.4841768518680486</v>
       </c>
       <c r="S12" t="n">
-        <v>4.967048800771058</v>
+        <v>4.967048383826176</v>
       </c>
       <c r="T12" t="n">
-        <v>54.89683570956693</v>
+        <v>54.89682066367838</v>
       </c>
       <c r="U12" t="n">
         <v>8.969433404723024</v>
       </c>
       <c r="V12" t="n">
-        <v>207.3950970238594</v>
+        <v>207.3950332336242</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34478,10 +34478,10 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>1135.803847035948</v>
+        <v>1135.819612560704</v>
       </c>
       <c r="D13" t="n">
-        <v>59.77914984399727</v>
+        <v>59.7799796084581</v>
       </c>
       <c r="E13" t="n">
         <v>41.560444928</v>
@@ -34493,7 +34493,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>23.21171186892827</v>
+        <v>23.21173669091627</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -34502,40 +34502,40 @@
         <v>0.05263157894736842</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1129059099734679</v>
+        <v>-0.1129059090145007</v>
       </c>
       <c r="L13" t="n">
         <v>-0.103414675084556</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0562330470847603</v>
+        <v>0.05623457314071326</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0798406946750333</v>
+        <v>-0.07984068746051737</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.04474463113747851</v>
+        <v>-0.04474445855637921</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1422130929025873</v>
+        <v>0.1422173342957318</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95662668925143</v>
+        <v>1.956626720522037</v>
       </c>
       <c r="R13" t="n">
-        <v>1.407133467159298</v>
+        <v>1.407133734064858</v>
       </c>
       <c r="S13" t="n">
-        <v>1.87926268552135</v>
+        <v>1.8793279584431</v>
       </c>
       <c r="T13" t="n">
-        <v>68.13107574747409</v>
+        <v>68.13105880059102</v>
       </c>
       <c r="U13" t="n">
-        <v>11.23242664125129</v>
+        <v>11.2324276718771</v>
       </c>
       <c r="V13" t="n">
-        <v>93.88105243976528</v>
+        <v>93.87979293377052</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34577,40 +34577,40 @@
         <v>0.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.07449678331970484</v>
+        <v>0.07465501620823023</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06326979295797697</v>
+        <v>0.06406095740060391</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.03124350264527794</v>
+        <v>-0.03124043020838893</v>
       </c>
       <c r="N14" t="n">
-        <v>0.05379103225671952</v>
+        <v>0.05395786858140621</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1290646371941562</v>
+        <v>0.1290647476524553</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1794498408581686</v>
+        <v>0.1794675178427019</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.532799708544486</v>
+        <v>0.5330106066935525</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3278028190813248</v>
+        <v>0.327802844509042</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7284733700295097</v>
+        <v>0.7284937031011458</v>
       </c>
       <c r="T14" t="n">
-        <v>15.32296635139432</v>
+        <v>15.32358780537536</v>
       </c>
       <c r="U14" t="n">
-        <v>3.289156520051854</v>
+        <v>3.292256565340586</v>
       </c>
       <c r="V14" t="n">
-        <v>2.568679670392144</v>
+        <v>2.568691963430578</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -828,16 +828,16 @@
         <v>30.6677518081665</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.74903693199158</v>
+        <v>17.74903693675995</v>
       </c>
       <c r="AH2" t="n">
         <v>0.1190908257476233</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9336260229964632</v>
+        <v>0.9336260224769843</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.7278544140549801</v>
+        <v>0.7278544135907825</v>
       </c>
       <c r="AK2" t="n">
         <v>37.58000183105469</v>
@@ -1024,25 +1024,25 @@
         <v>487.3905255126953</v>
       </c>
       <c r="AG3" t="n">
-        <v>431.4557308959961</v>
+        <v>431.4557313537597</v>
       </c>
       <c r="AH3" t="n">
         <v>0.061838509791456</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1994974043388646</v>
+        <v>0.1994974030662282</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1296420249200085</v>
+        <v>0.1296420237214868</v>
       </c>
       <c r="AK3" t="n">
-        <v>537.6463623046875</v>
+        <v>537.6464233398438</v>
       </c>
       <c r="AL3" t="n">
         <v>352.1670227050781</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.03741554750148657</v>
+        <v>-0.03741565677682057</v>
       </c>
       <c r="AN3" t="n">
         <v>0.4695584649624618</v>
@@ -1066,10 +1066,10 @@
         <v>0.3334643856435444</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.3935510718192528</v>
+        <v>0.3935509573048126</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.01172698157924978</v>
+        <v>0.01172710229702489</v>
       </c>
       <c r="AW3" t="n">
         <v>0.8331132528245107</v>
@@ -1078,7 +1078,7 @@
         <v>0.1012249668822567</v>
       </c>
       <c r="AY3" t="n">
-        <v>8768.57684282529</v>
+        <v>8768.581271482328</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1403,7 +1403,7 @@
         <v>45586</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>242.8099975585938</v>
@@ -1606,16 +1606,16 @@
         <v>624.6631774902344</v>
       </c>
       <c r="AG6" t="n">
-        <v>627.3872259521485</v>
+        <v>627.3872256469726</v>
       </c>
       <c r="AH6" t="n">
         <v>0.1655561642277628</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.1604954435992536</v>
+        <v>0.1604954441637458</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.004341893410054642</v>
+        <v>-0.004341892925743274</v>
       </c>
       <c r="AK6" t="n">
         <v>777.5900268554688</v>
@@ -1651,16 +1651,16 @@
         <v>0.2727825518489595</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.004813625526956189</v>
+        <v>0.004813540887679491</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.078888349221005</v>
+        <v>1.078888892664822</v>
       </c>
       <c r="AX6" t="n">
         <v>0.1222988640274481</v>
       </c>
       <c r="AY6" t="n">
-        <v>18.22713492614356</v>
+        <v>18.22713105231833</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
@@ -1802,28 +1802,28 @@
         <v>344.2332257080078</v>
       </c>
       <c r="AG7" t="n">
-        <v>338.5440653991699</v>
+        <v>338.5440660095215</v>
       </c>
       <c r="AH7" t="n">
         <v>-0.002130025962774895</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01463896463518455</v>
+        <v>0.0146389628059207</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01680478522679141</v>
+        <v>0.01680478339362268</v>
       </c>
       <c r="AK7" t="n">
         <v>402.1211853027344</v>
       </c>
       <c r="AL7" t="n">
-        <v>235.9563751220703</v>
+        <v>235.9563446044922</v>
       </c>
       <c r="AM7" t="n">
         <v>-0.145779897815137</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.455777576775761</v>
+        <v>0.4557777650597676</v>
       </c>
       <c r="AO7" t="n">
         <v>45.0177550107955</v>
@@ -1847,13 +1847,13 @@
         <v>0.1464586138797805</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.4017393645601341</v>
+        <v>0.4017392772775008</v>
       </c>
       <c r="AW7" t="n">
         <v>1.458096718015835</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.09207739444672658</v>
+        <v>0.09207750040386009</v>
       </c>
       <c r="AY7" t="n">
         <v>137.0992173718921</v>
@@ -2384,16 +2384,16 @@
         <v>143.5920001220703</v>
       </c>
       <c r="AG10" t="n">
-        <v>162.2088568496704</v>
+        <v>162.2088567733765</v>
       </c>
       <c r="AH10" t="n">
         <v>-0.008997695339671763</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.1227359232077163</v>
+        <v>-0.1227359227951005</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1147709014733613</v>
+        <v>-0.1147709010569992</v>
       </c>
       <c r="AK10" t="n">
         <v>310.009765625</v>
@@ -2432,13 +2432,13 @@
         <v>-0.5016210269528798</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.6720361022286887</v>
+        <v>0.6720358024461157</v>
       </c>
       <c r="AX10" t="n">
         <v>-0.2658905194608296</v>
       </c>
       <c r="AY10" t="n">
-        <v>2831.539425184948</v>
+        <v>2831.539005100049</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2624,7 +2624,7 @@
         <v>-0.4358185077128415</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.2510291218236016</v>
+        <v>-0.2510290409588749</v>
       </c>
       <c r="AX11" t="n">
         <v>-0.3140996567722592</v>
@@ -3014,7 +3014,7 @@
         <v>-0.3160395207854998</v>
       </c>
       <c r="AY13" t="n">
-        <v>597.898624956724</v>
+        <v>597.8986757140107</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
@@ -4710,16 +4710,16 @@
         <v>372.6729040527344</v>
       </c>
       <c r="AG22" t="n">
-        <v>366.2593502807617</v>
+        <v>366.2593504333496</v>
       </c>
       <c r="AH22" t="n">
         <v>-0.04704632189147817</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.03035918570761553</v>
+        <v>-0.03035918611157906</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.01751096256534135</v>
+        <v>0.01751096214143466</v>
       </c>
       <c r="AK22" t="n">
         <v>479.9351196289062</v>
@@ -4758,13 +4758,13 @@
         <v>0.05795905632301102</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.684791697655564</v>
+        <v>6.684792331999373</v>
       </c>
       <c r="AX22" t="n">
         <v>0.02726348178560789</v>
       </c>
       <c r="AY22" t="n">
-        <v>312.3053857667985</v>
+        <v>312.3053528175004</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
@@ -4906,16 +4906,16 @@
         <v>231.5099725341797</v>
       </c>
       <c r="AG23" t="n">
-        <v>252.7491662597656</v>
+        <v>252.7491654968262</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.03831356829875532</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.1191266713781052</v>
+        <v>-0.119126668719133</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.08403269549762671</v>
+        <v>-0.08403269273272118</v>
       </c>
       <c r="AK23" t="n">
         <v>326.8851013183594</v>
@@ -4951,16 +4951,16 @@
         <v>-0.08451206616087792</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.2033064866462193</v>
+        <v>-0.2033065736482497</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03509923715867</v>
+        <v>1.035099379083406</v>
       </c>
       <c r="AX23" t="n">
         <v>-0.220667627657038</v>
       </c>
       <c r="AY23" t="n">
-        <v>154.2093873589477</v>
+        <v>154.209477649263</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5147,16 +5147,16 @@
         <v>0.3199997589379149</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.2415187518791233</v>
+        <v>0.2415188524109624</v>
       </c>
       <c r="AW24" t="n">
-        <v>9.848590137267101</v>
+        <v>9.848589177748046</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2417126075139737</v>
       </c>
       <c r="AY24" t="n">
-        <v>6234.825431569482</v>
+        <v>6234.826669952698</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5346,13 +5346,13 @@
         <v>0.3025421263555994</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.353414659895348</v>
+        <v>1.353414913159563</v>
       </c>
       <c r="AX25" t="n">
         <v>0.2346344978049082</v>
       </c>
       <c r="AY25" t="n">
-        <v>3399.752965960514</v>
+        <v>3399.752191287819</v>
       </c>
       <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
@@ -6124,13 +6124,13 @@
         <v>2.199195824982504</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.370235947315637</v>
+        <v>1.370235588126229</v>
       </c>
       <c r="AX29" t="n">
         <v>2.030218349274564</v>
       </c>
       <c r="AY29" t="n">
-        <v>656.4665364995651</v>
+        <v>656.4664825214475</v>
       </c>
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
@@ -6272,28 +6272,28 @@
         <v>170.9377996826172</v>
       </c>
       <c r="AG30" t="n">
-        <v>167.8430082702637</v>
+        <v>167.8430081558228</v>
       </c>
       <c r="AH30" t="n">
         <v>0.08150447391061788</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.1014459108091454</v>
+        <v>0.1014459115601476</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.01843860786485796</v>
+        <v>0.01843860855926316</v>
       </c>
       <c r="AK30" t="n">
-        <v>248.7424926757812</v>
+        <v>248.7425079345703</v>
       </c>
       <c r="AL30" t="n">
-        <v>122.9443130493164</v>
+        <v>122.9443054199219</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.2567816092518103</v>
+        <v>-0.2567816548435861</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.5036888696350759</v>
+        <v>0.5036889629475363</v>
       </c>
       <c r="AO30" t="n">
         <v>52.93532213673005</v>
@@ -6320,7 +6320,7 @@
         <v>0.1176777295080484</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.544075580896684</v>
+        <v>0.5440752857200843</v>
       </c>
       <c r="AX30" t="n">
         <v>0.0854463179511511</v>
@@ -6704,13 +6704,13 @@
         <v>8.561795504568799</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.565759787125756</v>
+        <v>5.565759160655137</v>
       </c>
       <c r="AX32" t="n">
         <v>5.742291701939537</v>
       </c>
       <c r="AY32" t="n">
-        <v>44.94810049043645</v>
+        <v>44.94810432552984</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6900,13 +6900,13 @@
         <v>3.298415402611449</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.103264808018142</v>
+        <v>6.103264300969239</v>
       </c>
       <c r="AX33" t="n">
         <v>1.84266465252655</v>
       </c>
       <c r="AY33" t="n">
-        <v>45.20136552127269</v>
+        <v>45.20137624667511</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7092,13 +7092,13 @@
         <v>7.643411108310053</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.830906468128515</v>
+        <v>5.830905669928297</v>
       </c>
       <c r="AX34" t="n">
         <v>5.79878064594689</v>
       </c>
       <c r="AY34" t="n">
-        <v>18.43372659975843</v>
+        <v>18.43372498462888</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7290,7 +7290,7 @@
         <v>4.971106024517814</v>
       </c>
       <c r="AY35" t="n">
-        <v>178.2710590570329</v>
+        <v>178.2711177721721</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7476,13 +7476,13 @@
         <v>5.118615583225608</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.463950218004577</v>
+        <v>7.463952386169193</v>
       </c>
       <c r="AX36" t="n">
         <v>2.391537101609046</v>
       </c>
       <c r="AY36" t="n">
-        <v>34.01231546342356</v>
+        <v>34.01230000460952</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7668,13 +7668,13 @@
         <v>0.2613151656855131</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.815318068303137</v>
+        <v>1.815318474061732</v>
       </c>
       <c r="AX37" t="n">
         <v>0.04266554986824844</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.137975417865881</v>
+        <v>3.137976732727171</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7870,7 +7870,7 @@
         <v>0.3116008108265493</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.537631154226718</v>
+        <v>3.537631504748809</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8053,16 +8053,16 @@
         <v>0.1040757103196976</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.1161003067967095</v>
+        <v>0.1161001949216915</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.8038259935868124</v>
+        <v>0.8038255552508111</v>
       </c>
       <c r="AX39" t="n">
         <v>0.1002625812049645</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.8761770900496477</v>
+        <v>0.8761767739134032</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8245,16 +8245,16 @@
         <v>0.08449083183307127</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.214470505897326</v>
+        <v>0.2144703815774927</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.058121852507846</v>
+        <v>1.058122031024496</v>
       </c>
       <c r="AX40" t="n">
         <v>0.09079404762857002</v>
       </c>
       <c r="AY40" t="n">
-        <v>3.489840721072705</v>
+        <v>3.489840296288503</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8411,13 +8411,13 @@
         <v>1110.633178710938</v>
       </c>
       <c r="AL41" t="n">
-        <v>715.1827392578125</v>
+        <v>715.1826782226562</v>
       </c>
       <c r="AM41" t="n">
         <v>-0.07645477339905105</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.4342068319036549</v>
+        <v>0.4342069543018068</v>
       </c>
       <c r="AO41" t="n">
         <v>59.25038831857431</v>
@@ -8438,19 +8438,19 @@
         <v>0.007518591442462919</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.01932758475641072</v>
+        <v>0.01932752292932483</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.3560310612151496</v>
+        <v>0.3560308423783018</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.4032038049348023</v>
+        <v>0.4032039220984256</v>
       </c>
       <c r="AX41" t="n">
         <v>0.3628448035721019</v>
       </c>
       <c r="AY41" t="n">
-        <v>2.336445555177017</v>
+        <v>2.336445886376295</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8640,13 +8640,13 @@
         <v>0.1346100773975289</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.111584686960502</v>
+        <v>2.111585989853497</v>
       </c>
       <c r="AX42" t="n">
         <v>0.3934441737880774</v>
       </c>
       <c r="AY42" t="n">
-        <v>98.17918854190312</v>
+        <v>98.17914717659551</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8788,16 +8788,16 @@
         <v>187.223359375</v>
       </c>
       <c r="AG43" t="n">
-        <v>178.8625176239014</v>
+        <v>178.8625173950195</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.04632625091332676</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.001747233441053764</v>
+        <v>-0.001747232163637258</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.04674451563227566</v>
+        <v>0.04674451697174464</v>
       </c>
       <c r="AK43" t="n">
         <v>201.1799774169922</v>
@@ -8836,13 +8836,13 @@
         <v>0.05705700741320485</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.4320987971619081</v>
+        <v>0.4320985342578156</v>
       </c>
       <c r="AX43" t="n">
         <v>0.1752896603724161</v>
       </c>
       <c r="AY43" t="n">
-        <v>34.26634282295188</v>
+        <v>34.26636275181733</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -9344,25 +9344,25 @@
         <v>2.171823034286499</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.176922837495804</v>
+        <v>2.176922795772553</v>
       </c>
       <c r="AH46" t="n">
         <v>-0.01925705694493696</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.02155461013439619</v>
+        <v>-0.02155459138135518</v>
       </c>
       <c r="AJ46" t="n">
-        <v>-0.002342666042849384</v>
+        <v>-0.002342646921589142</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.306842803955078</v>
+        <v>2.306842565536499</v>
       </c>
       <c r="AL46" t="n">
         <v>2.064932584762573</v>
       </c>
       <c r="AM46" t="n">
-        <v>-0.07666005208979287</v>
+        <v>-0.07665995666004766</v>
       </c>
       <c r="AN46" t="n">
         <v>0.03151072832037571</v>
@@ -9386,19 +9386,19 @@
         <v>-0.00595379497266002</v>
       </c>
       <c r="AU46" t="n">
-        <v>-0.01041143633026698</v>
+        <v>-0.01041132671530132</v>
       </c>
       <c r="AV46" t="n">
-        <v>-0.05874650659572012</v>
+        <v>-0.05874640742722637</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.09196687235972711</v>
+        <v>0.09196680562538662</v>
       </c>
       <c r="AX46" t="n">
         <v>0.008486014810537013</v>
       </c>
       <c r="AY46" t="n">
-        <v>2.952498530068234</v>
+        <v>2.9524989672318</v>
       </c>
       <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
@@ -9924,16 +9924,16 @@
         <v>14.76741893768311</v>
       </c>
       <c r="AG49" t="n">
-        <v>14.4443915605545</v>
+        <v>14.44439154624939</v>
       </c>
       <c r="AH49" t="n">
         <v>0.009655100212886181</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.03223453787621722</v>
+        <v>0.03223453889849859</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.02236351567834416</v>
+        <v>0.02236351669084957</v>
       </c>
       <c r="AK49" t="n">
         <v>16.86722755432129</v>
@@ -9969,16 +9969,16 @@
         <v>0.06593696393848569</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.09532767454094793</v>
+        <v>0.09532775127896964</v>
       </c>
       <c r="AW49" t="n">
-        <v>-0.2219545397134289</v>
+        <v>-0.221954384834452</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.04289754851234884</v>
+        <v>0.04289761807974846</v>
       </c>
       <c r="AY49" t="n">
-        <v>6.5611827650886</v>
+        <v>6.561181393786604</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10120,16 +10120,16 @@
         <v>965.0416052246094</v>
       </c>
       <c r="AG50" t="n">
-        <v>917.0619338989258</v>
+        <v>917.0619351196289</v>
       </c>
       <c r="AH50" t="n">
         <v>0.02451542695603837</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.07811694680590797</v>
+        <v>0.07811694537082414</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.05231889968619252</v>
+        <v>0.05231889828544856</v>
       </c>
       <c r="AK50" t="n">
         <v>1174.859985351562</v>
@@ -10165,7 +10165,7 @@
         <v>0.102350430811146</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.6346025905832804</v>
+        <v>0.6346027555285749</v>
       </c>
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="n">
@@ -10314,28 +10314,28 @@
         <v>65.53655204772949</v>
       </c>
       <c r="AG51" t="n">
-        <v>63.27524311065674</v>
+        <v>63.27524297714233</v>
       </c>
       <c r="AH51" t="n">
         <v>-0.06449150195390696</v>
       </c>
       <c r="AI51" t="n">
-        <v>-0.03105862009773519</v>
+        <v>-0.03105861805321308</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.03573765703464993</v>
+        <v>0.03573765922011596</v>
       </c>
       <c r="AK51" t="n">
         <v>70.97299957275391</v>
       </c>
       <c r="AL51" t="n">
-        <v>55.35893249511719</v>
+        <v>55.35892868041992</v>
       </c>
       <c r="AM51" t="n">
         <v>-0.1361503424912656</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.1074997043828243</v>
+        <v>0.1074997806988982</v>
       </c>
       <c r="AO51" t="n">
         <v>29.1942123460075</v>
@@ -10359,16 +10359,16 @@
         <v>0.005295675309001435</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.04648448828483986</v>
+        <v>0.04648455642362248</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.04027634553949877</v>
+        <v>0.04027607620866358</v>
       </c>
       <c r="AX51" t="n">
         <v>0.06711822521092325</v>
       </c>
       <c r="AY51" t="n">
-        <v>166.5820315427481</v>
+        <v>166.5821544044458</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10510,16 +10510,16 @@
         <v>271.3335272216797</v>
       </c>
       <c r="AG52" t="n">
-        <v>287.0583164978027</v>
+        <v>287.0583145904541</v>
       </c>
       <c r="AH52" t="n">
         <v>-0.05102037012917504</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.1030045971988205</v>
+        <v>-0.1030045912387669</v>
       </c>
       <c r="AJ52" t="n">
-        <v>-0.05477907579188146</v>
+        <v>-0.05477906951139511</v>
       </c>
       <c r="AK52" t="n">
         <v>401.7044372558594</v>
@@ -10552,17 +10552,17 @@
         <v>0.07582412138887551</v>
       </c>
       <c r="AU52" t="n">
-        <v>-0.06132263182446196</v>
+        <v>-0.06132252739514044</v>
       </c>
       <c r="AV52" t="n">
-        <v>-0.2756410124332339</v>
+        <v>-0.2756409502465416</v>
       </c>
       <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="n">
-        <v>-0.2938358043490524</v>
+        <v>-0.2938358634509011</v>
       </c>
       <c r="AY52" t="n">
-        <v>5.368788270239205</v>
+        <v>5.368787068408589</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10704,28 +10704,28 @@
         <v>105.398846282959</v>
       </c>
       <c r="AG53" t="n">
-        <v>105.3623581314087</v>
+        <v>105.3623580551147</v>
       </c>
       <c r="AH53" t="n">
         <v>-0.04258910585034903</v>
       </c>
       <c r="AI53" t="n">
-        <v>-0.04225754385400438</v>
+        <v>-0.04225754316049335</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.0003463110753916254</v>
+        <v>0.000346311799752641</v>
       </c>
       <c r="AK53" t="n">
         <v>116.6635665893555</v>
       </c>
       <c r="AL53" t="n">
-        <v>89.56781005859375</v>
+        <v>89.56781768798828</v>
       </c>
       <c r="AM53" t="n">
         <v>-0.1350341275155518</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.1266324765124407</v>
+        <v>0.1266323805457881</v>
       </c>
       <c r="AO53" t="n">
         <v>38.76544403726411</v>
@@ -10752,13 +10752,13 @@
         <v>0.1053034858091946</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.403432499975923</v>
+        <v>1.403432718344304</v>
       </c>
       <c r="AX53" t="n">
         <v>0.09458356219093877</v>
       </c>
       <c r="AY53" t="n">
-        <v>187.8721689628229</v>
+        <v>187.8721900336637</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10941,7 +10941,7 @@
         <v>-0.3737686695470248</v>
       </c>
       <c r="AV54" t="n">
-        <v>-0.2696130774041049</v>
+        <v>-0.2696130170449812</v>
       </c>
       <c r="AW54" t="n">
         <v>1.553796963377056</v>
@@ -11092,16 +11092,16 @@
         <v>43.62748031616211</v>
       </c>
       <c r="AG55" t="n">
-        <v>44.91162815093994</v>
+        <v>44.91162809371949</v>
       </c>
       <c r="AH55" t="n">
         <v>-0.06641412139615099</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.09310792729780148</v>
+        <v>-0.09310792614235963</v>
       </c>
       <c r="AJ55" t="n">
-        <v>-0.02859276957099044</v>
+        <v>-0.02859276833335189</v>
       </c>
       <c r="AK55" t="n">
         <v>49.35155487060547</v>
@@ -11146,7 +11146,7 @@
         <v>-0.04690592615477507</v>
       </c>
       <c r="AY55" t="n">
-        <v>166.6931080855575</v>
+        <v>166.6931286618055</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11288,16 +11288,16 @@
         <v>82.74342376708984</v>
       </c>
       <c r="AG56" t="n">
-        <v>86.31451889038085</v>
+        <v>86.31451900482178</v>
       </c>
       <c r="AH56" t="n">
         <v>-0.07146697183670492</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.1098832175774677</v>
+        <v>-0.1098832187576375</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-0.04137305252000878</v>
+        <v>-0.04137305379101341</v>
       </c>
       <c r="AK56" t="n">
         <v>96.44304656982422</v>
@@ -11339,10 +11339,10 @@
         <v>0.115793282899755</v>
       </c>
       <c r="AX56" t="n">
-        <v>-0.02994679584446569</v>
+        <v>-0.02994670240068942</v>
       </c>
       <c r="AY56" t="n">
-        <v>221.7537698758837</v>
+        <v>221.7536928867857</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11496,13 +11496,13 @@
         <v>-0.1854470918764226</v>
       </c>
       <c r="AK57" t="n">
-        <v>182.8191833496094</v>
+        <v>182.8191986083984</v>
       </c>
       <c r="AL57" t="n">
         <v>95.23000335693359</v>
       </c>
       <c r="AM57" t="n">
-        <v>-0.4791027855385228</v>
+        <v>-0.4791028290145952</v>
       </c>
       <c r="AN57" t="n">
         <v>0</v>
@@ -11529,16 +11529,16 @@
         <v>-0.3600753780926945</v>
       </c>
       <c r="AV57" t="n">
-        <v>-0.4237490165358628</v>
+        <v>-0.4237490697429628</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.567372410282253</v>
+        <v>1.56737320239209</v>
       </c>
       <c r="AX57" t="n">
         <v>-0.4212809076283249</v>
       </c>
       <c r="AY57" t="n">
-        <v>12.33981016239809</v>
+        <v>12.33981194447172</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11680,28 +11680,28 @@
         <v>89.08323287963867</v>
       </c>
       <c r="AG58" t="n">
-        <v>91.00129364013672</v>
+        <v>91.00129390716553</v>
       </c>
       <c r="AH58" t="n">
         <v>-0.06020472636171459</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.08001306495957472</v>
+        <v>-0.08001306765912997</v>
       </c>
       <c r="AJ58" t="n">
-        <v>-0.02107729114360724</v>
+        <v>-0.02107729401610003</v>
       </c>
       <c r="AK58" t="n">
-        <v>97.49111175537109</v>
+        <v>97.49111938476562</v>
       </c>
       <c r="AL58" t="n">
-        <v>82.06204223632812</v>
+        <v>82.06203460693359</v>
       </c>
       <c r="AM58" t="n">
-        <v>-0.1412550363485754</v>
+        <v>-0.1412551035516619</v>
       </c>
       <c r="AN58" t="n">
-        <v>0.02020372561043859</v>
+        <v>0.02020382045986269</v>
       </c>
       <c r="AO58" t="n">
         <v>31.27856665087371</v>
@@ -11722,13 +11722,13 @@
         <v>-0.1323743077716176</v>
       </c>
       <c r="AU58" t="n">
-        <v>-0.1220320716561688</v>
+        <v>-0.1220321419016054</v>
       </c>
       <c r="AV58" t="n">
-        <v>-0.07887510318571678</v>
+        <v>-0.07887518050678644</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.60965887916991</v>
+        <v>0.6096586430522433</v>
       </c>
       <c r="AX58" t="n">
         <v>-0.01607328223795568</v>
@@ -12256,25 +12256,25 @@
         <v>143.123818359375</v>
       </c>
       <c r="AG61" t="n">
-        <v>154.4550553131104</v>
+        <v>154.4550552368164</v>
       </c>
       <c r="AH61" t="n">
         <v>-0.02168621632997936</v>
       </c>
       <c r="AI61" t="n">
-        <v>-0.09345793837169514</v>
+        <v>-0.09345793792390344</v>
       </c>
       <c r="AJ61" t="n">
-        <v>-0.0733626810127046</v>
+        <v>-0.07336268055498674</v>
       </c>
       <c r="AK61" t="n">
-        <v>209.6322174072266</v>
+        <v>209.6322326660156</v>
       </c>
       <c r="AL61" t="n">
         <v>134.3016815185547</v>
       </c>
       <c r="AM61" t="n">
-        <v>-0.3320682955880707</v>
+        <v>-0.3320683442057325</v>
       </c>
       <c r="AN61" t="n">
         <v>0.04257819179364652</v>
@@ -12301,16 +12301,16 @@
         <v>-0.0735158647271823</v>
       </c>
       <c r="AV61" t="n">
-        <v>-0.305041121876402</v>
+        <v>-0.3050411745081949</v>
       </c>
       <c r="AW61" t="n">
-        <v>7.917273550237764</v>
+        <v>7.917274633426731</v>
       </c>
       <c r="AX61" t="n">
         <v>-0.1488391179171695</v>
       </c>
       <c r="AY61" t="n">
-        <v>11.37024662370633</v>
+        <v>11.37024766594397</v>
       </c>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
@@ -12502,7 +12502,7 @@
         <v>-0.1357548456255144</v>
       </c>
       <c r="AY62" t="n">
-        <v>13.23584356235482</v>
+        <v>13.23584242786963</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -12698,7 +12698,7 @@
         <v>-0.002746850744687612</v>
       </c>
       <c r="AY63" t="n">
-        <v>154.5144101398732</v>
+        <v>154.5142333126553</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12890,7 +12890,7 @@
         <v>0.1892518356965414</v>
       </c>
       <c r="AY64" t="n">
-        <v>5.672431088178671</v>
+        <v>5.672431672126677</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13082,7 +13082,7 @@
         <v>-0.4889174155139048</v>
       </c>
       <c r="AY65" t="n">
-        <v>-0.9359723635050625</v>
+        <v>-0.9359723563185621</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
@@ -13656,13 +13656,13 @@
         <v>0.9174641806458304</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.701232108505189</v>
+        <v>1.701231862475875</v>
       </c>
       <c r="AX68" t="n">
         <v>1.142572957615179</v>
       </c>
       <c r="AY68" t="n">
-        <v>240.2995341920289</v>
+        <v>240.2995648678458</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13848,13 +13848,13 @@
         <v>5.596131883464931</v>
       </c>
       <c r="AW69" t="n">
-        <v>7.198823260232256</v>
+        <v>7.198824235238575</v>
       </c>
       <c r="AX69" t="n">
         <v>1.549229724020523</v>
       </c>
       <c r="AY69" t="n">
-        <v>-0.3862163508051421</v>
+        <v>-0.3862162196617859</v>
       </c>
       <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
@@ -13996,25 +13996,25 @@
         <v>854.133515625</v>
       </c>
       <c r="AG70" t="n">
-        <v>649.7307438659668</v>
+        <v>649.7307449340821</v>
       </c>
       <c r="AH70" t="n">
         <v>-0.006021921978862088</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.3066797257934795</v>
+        <v>0.3066797236453827</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.3145961210682675</v>
+        <v>0.3145961189071567</v>
       </c>
       <c r="AK70" t="n">
-        <v>1092.384765625</v>
+        <v>1092.384887695312</v>
       </c>
       <c r="AL70" t="n">
         <v>210.389892578125</v>
       </c>
       <c r="AM70" t="n">
-        <v>-0.2228104812971906</v>
+        <v>-0.2228105681454878</v>
       </c>
       <c r="AN70" t="n">
         <v>3.035317380653711</v>
@@ -14041,7 +14041,7 @@
         <v>0.8757475931582897</v>
       </c>
       <c r="AV70" t="n">
-        <v>2.352415189590917</v>
+        <v>2.352414987599427</v>
       </c>
       <c r="AW70" t="n">
         <v>10.2568650106652</v>
@@ -14050,7 +14050,7 @@
         <v>1.962229784163807</v>
       </c>
       <c r="AY70" t="n">
-        <v>160.1850384059705</v>
+        <v>160.1850529980442</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14192,28 +14192,28 @@
         <v>305.7798626708984</v>
       </c>
       <c r="AG71" t="n">
-        <v>274.6133799743652</v>
+        <v>274.6133786010742</v>
       </c>
       <c r="AH71" t="n">
         <v>0.1364057371180389</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.2653789493680632</v>
+        <v>0.2653789556959907</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.1134922220448347</v>
+        <v>0.1134922276132044</v>
       </c>
       <c r="AK71" t="n">
         <v>432.8701477050781</v>
       </c>
       <c r="AL71" t="n">
-        <v>130.7660064697266</v>
+        <v>130.7659912109375</v>
       </c>
       <c r="AM71" t="n">
         <v>-0.1972419625685856</v>
       </c>
       <c r="AN71" t="n">
-        <v>1.657341916416342</v>
+        <v>1.657342226495587</v>
       </c>
       <c r="AO71" t="n">
         <v>90.71985397777416</v>
@@ -14237,7 +14237,7 @@
         <v>0.5776305985090133</v>
       </c>
       <c r="AV71" t="n">
-        <v>1.374957737354422</v>
+        <v>1.374957489675245</v>
       </c>
       <c r="AW71" t="n">
         <v>4.927760033146161</v>
@@ -14246,7 +14246,7 @@
         <v>0.8832877971149351</v>
       </c>
       <c r="AY71" t="n">
-        <v>1844.094054572067</v>
+        <v>1844.094200559296</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14388,16 +14388,16 @@
         <v>956.04580078125</v>
       </c>
       <c r="AG72" t="n">
-        <v>681.4971128082275</v>
+        <v>681.4971128845215</v>
       </c>
       <c r="AH72" t="n">
         <v>0.1243080757951887</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.5772480828556501</v>
+        <v>0.5772480826790762</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.4028611168163234</v>
+        <v>0.4028611166592724</v>
       </c>
       <c r="AK72" t="n">
         <v>1213.373413085938</v>
@@ -14436,13 +14436,13 @@
         <v>4.859130984745664</v>
       </c>
       <c r="AW72" t="n">
-        <v>13.66209359043271</v>
+        <v>13.66209511630458</v>
       </c>
       <c r="AX72" t="n">
         <v>2.409761355401106</v>
       </c>
       <c r="AY72" t="n">
-        <v>794.7745736741151</v>
+        <v>794.7746439046906</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14972,16 +14972,16 @@
         <v>466.0630963134765</v>
       </c>
       <c r="AG75" t="n">
-        <v>399.8304119873047</v>
+        <v>399.8304111480713</v>
       </c>
       <c r="AH75" t="n">
         <v>-0.1089403734605162</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.03866538435827649</v>
+        <v>0.03866538653840768</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.1656519422746534</v>
+        <v>0.1656519447213258</v>
       </c>
       <c r="AK75" t="n">
         <v>745.990478515625</v>
@@ -15017,16 +15017,16 @@
         <v>0.3662062455725523</v>
       </c>
       <c r="AV75" t="n">
-        <v>2.169776139393327</v>
+        <v>2.169775770223906</v>
       </c>
       <c r="AW75" t="n">
         <v>8.348481201543182</v>
       </c>
       <c r="AX75" t="n">
-        <v>1.214866887590918</v>
+        <v>1.214867067836191</v>
       </c>
       <c r="AY75" t="n">
-        <v>610.330343574276</v>
+        <v>610.3301826573722</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15164,28 +15164,28 @@
         <v>1684917.985</v>
       </c>
       <c r="AG76" t="n">
-        <v>1417721.0365625</v>
+        <v>1417721.0384375</v>
       </c>
       <c r="AH76" t="n">
         <v>0.09263478483197507</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.2985629418773457</v>
+        <v>0.2985629401599377</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.1884693402627102</v>
+        <v>0.188469338690906</v>
       </c>
       <c r="AK76" t="n">
         <v>2918367.25</v>
       </c>
       <c r="AL76" t="n">
-        <v>332519.8125</v>
+        <v>332519.78125</v>
       </c>
       <c r="AM76" t="n">
         <v>-0.3691678112136161</v>
       </c>
       <c r="AN76" t="n">
-        <v>4.536512204066036</v>
+        <v>4.536512724383972</v>
       </c>
       <c r="AO76" t="n">
         <v>48.98648648648648</v>
@@ -15209,7 +15209,7 @@
         <v>1.282165038279104</v>
       </c>
       <c r="AV76" t="n">
-        <v>4.536512204066036</v>
+        <v>4.536512724383972</v>
       </c>
       <c r="AW76" t="n">
         <v>15.18346275749454</v>
@@ -15218,7 +15218,7 @@
         <v>1.72541432200785</v>
       </c>
       <c r="AY76" t="n">
-        <v>-9.045475949336664</v>
+        <v>-9.045477597465139</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
@@ -15360,16 +15360,16 @@
         <v>256630</v>
       </c>
       <c r="AG77" t="n">
-        <v>226356.6070703125</v>
+        <v>226356.6071484375</v>
       </c>
       <c r="AH77" t="n">
         <v>0.07547831508397307</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.2193149719471936</v>
+        <v>0.2193149715263576</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.1337420335174213</v>
+        <v>0.1337420331261201</v>
       </c>
       <c r="AK77" t="n">
         <v>362100.65625</v>
@@ -15408,7 +15408,7 @@
         <v>2.573702815575671</v>
       </c>
       <c r="AW77" t="n">
-        <v>2.747848949211491</v>
+        <v>2.747850142008384</v>
       </c>
       <c r="AX77" t="n">
         <v>1.154679230424305</v>
@@ -15600,7 +15600,7 @@
         <v>4.570810258536265</v>
       </c>
       <c r="AW78" t="n">
-        <v>5.106264924465127</v>
+        <v>5.106264527156213</v>
       </c>
       <c r="AX78" t="n">
         <v>0.9816868355632977</v>
@@ -16636,16 +16636,16 @@
         <v>81.0468132019043</v>
       </c>
       <c r="AG84" t="n">
-        <v>73.91954601287841</v>
+        <v>73.91954597473145</v>
       </c>
       <c r="AH84" t="n">
         <v>0.0729601282142629</v>
       </c>
       <c r="AI84" t="n">
-        <v>0.1764141390874114</v>
+        <v>0.1764141396945125</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.09641925002872931</v>
+        <v>0.09641925059454803</v>
       </c>
       <c r="AK84" t="n">
         <v>88.02348327636719</v>
@@ -16684,13 +16684,13 @@
         <v>0.4171742855082448</v>
       </c>
       <c r="AW84" t="n">
-        <v>3.707831339919315</v>
+        <v>3.707829881530021</v>
       </c>
       <c r="AX84" t="n">
         <v>0.2511440350846574</v>
       </c>
       <c r="AY84" t="n">
-        <v>1391.026576370869</v>
+        <v>1391.02616131599</v>
       </c>
       <c r="AZ84" t="inlineStr"/>
       <c r="BA84" t="n">
@@ -17239,13 +17239,13 @@
         <v>316.3519592285156</v>
       </c>
       <c r="AL87" t="n">
-        <v>73.67493438720703</v>
+        <v>73.67494201660156</v>
       </c>
       <c r="AM87" t="n">
         <v>-0.1392814218411897</v>
       </c>
       <c r="AN87" t="n">
-        <v>2.695829671376029</v>
+        <v>2.695829288655094</v>
       </c>
       <c r="AO87" t="n">
         <v>83.26491524979657</v>
@@ -17266,19 +17266,19 @@
         <v>0.1805686455677795</v>
       </c>
       <c r="AU87" t="n">
-        <v>1.488297999543331</v>
+        <v>1.488297826057856</v>
       </c>
       <c r="AV87" t="n">
-        <v>2.165547034272823</v>
+        <v>2.165546753499481</v>
       </c>
       <c r="AW87" t="n">
-        <v>3.398185053420253</v>
+        <v>3.398185324424063</v>
       </c>
       <c r="AX87" t="n">
         <v>2.05056021022692</v>
       </c>
       <c r="AY87" t="n">
-        <v>21.4489393675998</v>
+        <v>21.44894466278791</v>
       </c>
       <c r="AZ87" t="inlineStr"/>
       <c r="BA87" t="n">
@@ -17470,7 +17470,7 @@
         <v>0.08258486451385227</v>
       </c>
       <c r="AY88" t="n">
-        <v>7.445838209483547</v>
+        <v>7.44583920695689</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
@@ -17612,25 +17612,25 @@
         <v>208.9379382324219</v>
       </c>
       <c r="AG89" t="n">
-        <v>213.0373706817627</v>
+        <v>213.0373707580567</v>
       </c>
       <c r="AH89" t="n">
         <v>0.05466724939739676</v>
       </c>
       <c r="AI89" t="n">
-        <v>0.03437251363530702</v>
+        <v>0.03437251326487267</v>
       </c>
       <c r="AJ89" t="n">
-        <v>-0.01924278560245929</v>
+        <v>-0.01924278595369278</v>
       </c>
       <c r="AK89" t="n">
-        <v>246.3216247558594</v>
+        <v>246.3216094970703</v>
       </c>
       <c r="AL89" t="n">
         <v>194.3271179199219</v>
       </c>
       <c r="AM89" t="n">
-        <v>-0.1053972592590665</v>
+        <v>-0.105397203841458</v>
       </c>
       <c r="AN89" t="n">
         <v>0.1339642298464865</v>
@@ -17657,16 +17657,16 @@
         <v>0.05886403271283114</v>
       </c>
       <c r="AV89" t="n">
-        <v>0.007444612396297901</v>
+        <v>0.007444682675964431</v>
       </c>
       <c r="AW89" t="n">
-        <v>0.643582256087901</v>
+        <v>0.6435826301987366</v>
       </c>
       <c r="AX89" t="n">
         <v>-0.04486716181985329</v>
       </c>
       <c r="AY89" t="n">
-        <v>7.278231206435823</v>
+        <v>7.278232985918519</v>
       </c>
       <c r="AZ89" t="inlineStr"/>
       <c r="BA89" t="n">
@@ -18244,7 +18244,7 @@
         <v>1.327827200627327</v>
       </c>
       <c r="AY92" t="n">
-        <v>17.93657603816204</v>
+        <v>17.93657811228766</v>
       </c>
       <c r="AZ92" t="inlineStr"/>
       <c r="BA92" t="n">
@@ -18580,16 +18580,16 @@
         <v>152.797998046875</v>
       </c>
       <c r="AG94" t="n">
-        <v>150.0940255737305</v>
+        <v>150.0940254592896</v>
       </c>
       <c r="AH94" t="n">
         <v>0.07455597939860725</v>
       </c>
       <c r="AI94" t="n">
-        <v>0.09391431013855667</v>
+        <v>0.09391431097262415</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.01801519056343959</v>
+        <v>0.01801519133963692</v>
       </c>
       <c r="AK94" t="n">
         <v>255.2094421386719</v>
@@ -18628,13 +18628,13 @@
         <v>1.007051119262362</v>
       </c>
       <c r="AW94" t="n">
-        <v>3.835542940818351</v>
+        <v>3.835544027328908</v>
       </c>
       <c r="AX94" t="n">
         <v>0.8204343080962828</v>
       </c>
       <c r="AY94" t="n">
-        <v>213.5820324808505</v>
+        <v>213.5819823342777</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18820,13 +18820,13 @@
         <v>1.172131174772344</v>
       </c>
       <c r="AW95" t="n">
-        <v>1.095995125709385</v>
+        <v>1.095994730456852</v>
       </c>
       <c r="AX95" t="n">
         <v>0.628264210259543</v>
       </c>
       <c r="AY95" t="n">
-        <v>16.73923188396545</v>
+        <v>16.73922834502093</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -18968,25 +18968,25 @@
         <v>372.6729040527344</v>
       </c>
       <c r="AG96" t="n">
-        <v>366.2593502807617</v>
+        <v>366.259348449707</v>
       </c>
       <c r="AH96" t="n">
         <v>-0.04704632189147817</v>
       </c>
       <c r="AI96" t="n">
-        <v>-0.03035918570761553</v>
+        <v>-0.03035918086005218</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0.01751096256534135</v>
+        <v>0.01751096765222382</v>
       </c>
       <c r="AK96" t="n">
-        <v>479.9351196289062</v>
+        <v>479.9350891113281</v>
       </c>
       <c r="AL96" t="n">
         <v>292.4138793945312</v>
       </c>
       <c r="AM96" t="n">
-        <v>-0.2600249489492713</v>
+        <v>-0.2600249018965616</v>
       </c>
       <c r="AN96" t="n">
         <v>0.214511484146328</v>
@@ -19016,13 +19016,13 @@
         <v>0.05795905632301102</v>
       </c>
       <c r="AW96" t="n">
-        <v>6.684791697655564</v>
+        <v>6.684791063311859</v>
       </c>
       <c r="AX96" t="n">
-        <v>0.02726348178560789</v>
+        <v>0.02726339110506371</v>
       </c>
       <c r="AY96" t="n">
-        <v>312.3053857667985</v>
+        <v>312.3052210203775</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19164,16 +19164,16 @@
         <v>75.59979476928712</v>
       </c>
       <c r="AG97" t="n">
-        <v>78.18392126083374</v>
+        <v>78.18392122268676</v>
       </c>
       <c r="AH97" t="n">
         <v>0.0756642917218735</v>
       </c>
       <c r="AI97" t="n">
-        <v>0.04011155213778594</v>
+        <v>0.04011155264527022</v>
       </c>
       <c r="AJ97" t="n">
-        <v>-0.03305189161497257</v>
+        <v>-0.03305189114318574</v>
       </c>
       <c r="AK97" t="n">
         <v>102.0957336425781</v>
@@ -19206,19 +19206,19 @@
         <v>-0.02781622520407034</v>
       </c>
       <c r="AU97" t="n">
-        <v>0.2231457945055622</v>
+        <v>0.2231459348674525</v>
       </c>
       <c r="AV97" t="n">
         <v>0.2619076624949077</v>
       </c>
       <c r="AW97" t="n">
-        <v>0.09218909995016955</v>
+        <v>0.09218887612017301</v>
       </c>
       <c r="AX97" t="n">
-        <v>0.2717821451691393</v>
+        <v>0.2717819934228427</v>
       </c>
       <c r="AY97" t="n">
-        <v>464.6831043328477</v>
+        <v>464.6832235462473</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19401,7 +19401,7 @@
         <v>0.4214656157325041</v>
       </c>
       <c r="AV98" t="n">
-        <v>0.9693443176480891</v>
+        <v>0.9693444640496176</v>
       </c>
       <c r="AW98" t="n">
         <v>22.65290862621235</v>
@@ -19410,7 +19410,7 @@
         <v>0.2981294775632668</v>
       </c>
       <c r="AY98" t="n">
-        <v>173.679192360618</v>
+        <v>173.6791383690715</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19596,13 +19596,13 @@
         <v>0.5779863465067696</v>
       </c>
       <c r="AW99" t="n">
-        <v>27.91138232046595</v>
+        <v>27.91138027124792</v>
       </c>
       <c r="AX99" t="n">
         <v>0.2788335831623692</v>
       </c>
       <c r="AY99" t="n">
-        <v>209.9565900521552</v>
+        <v>209.9566036900307</v>
       </c>
       <c r="AZ99" t="inlineStr"/>
       <c r="BA99" t="n">
@@ -19794,7 +19794,7 @@
         <v>0.08373786407766981</v>
       </c>
       <c r="AY100" t="n">
-        <v>25.43947005991203</v>
+        <v>25.43946707374523</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -20128,16 +20128,16 @@
         <v>51.73919662475586</v>
       </c>
       <c r="AG102" t="n">
-        <v>47.76324349403382</v>
+        <v>47.7632434463501</v>
       </c>
       <c r="AH102" t="n">
         <v>0.1067044341027859</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.1988297722847412</v>
+        <v>0.1988297734815749</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.08324294666501642</v>
+        <v>0.0832429477464558</v>
       </c>
       <c r="AK102" t="n">
         <v>79.68086242675781</v>
@@ -20176,13 +20176,13 @@
         <v>1.000170296834178</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.2876342933024056</v>
+        <v>0.2876341828452695</v>
       </c>
       <c r="AX102" t="n">
         <v>1.104068982628186</v>
       </c>
       <c r="AY102" t="n">
-        <v>25.19569945485126</v>
+        <v>25.1956851685919</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20514,16 +20514,16 @@
         <v>374.8640026855469</v>
       </c>
       <c r="AG104" t="n">
-        <v>357.8011695861816</v>
+        <v>357.8011688232422</v>
       </c>
       <c r="AH104" t="n">
         <v>0.1128035525097055</v>
       </c>
       <c r="AI104" t="n">
-        <v>0.1658709622971417</v>
+        <v>0.1658709647831285</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.04768803053131276</v>
+        <v>0.04768803276529821</v>
       </c>
       <c r="AK104" t="n">
         <v>444.1268615722656</v>
@@ -20562,13 +20562,13 @@
         <v>0.7477027247148846</v>
       </c>
       <c r="AW104" t="n">
-        <v>1.563388836786617</v>
+        <v>1.56338955785787</v>
       </c>
       <c r="AX104" t="n">
         <v>0.5375201860973424</v>
       </c>
       <c r="AY104" t="n">
-        <v>942.2094524509193</v>
+        <v>942.2095160094992</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20710,28 +20710,28 @@
         <v>421.7266027832031</v>
       </c>
       <c r="AG105" t="n">
-        <v>387.5767649841309</v>
+        <v>387.5767652893066</v>
       </c>
       <c r="AH105" t="n">
         <v>0.03410594084754348</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.1252222133837635</v>
+        <v>0.12522221249777</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.08811115857389051</v>
+        <v>0.08811115771711786</v>
       </c>
       <c r="AK105" t="n">
         <v>459.9599914550781</v>
       </c>
       <c r="AL105" t="n">
-        <v>313.2000427246094</v>
+        <v>313.2000122070312</v>
       </c>
       <c r="AM105" t="n">
         <v>-0.05185234921860571</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.3924327134751555</v>
+        <v>0.3924328491509936</v>
       </c>
       <c r="AO105" t="n">
         <v>77.33231154894719</v>
@@ -20758,13 +20758,13 @@
         <v>0.1704328048260602</v>
       </c>
       <c r="AW105" t="n">
-        <v>2.037568151818338</v>
+        <v>2.037566860492304</v>
       </c>
       <c r="AX105" t="n">
         <v>0.3435524075575394</v>
       </c>
       <c r="AY105" t="n">
-        <v>1264.763227029479</v>
+        <v>1264.763336515599</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20902,28 +20902,28 @@
         <v>157.4260003662109</v>
       </c>
       <c r="AG106" t="n">
-        <v>140.2698530960083</v>
+        <v>140.2698531341553</v>
       </c>
       <c r="AH106" t="n">
         <v>0.07707746601041898</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.2088128262495412</v>
+        <v>0.2088128259207993</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.1223081573947329</v>
+        <v>0.1223081570895164</v>
       </c>
       <c r="AK106" t="n">
         <v>184.09619140625</v>
       </c>
       <c r="AL106" t="n">
-        <v>94.54652404785156</v>
+        <v>94.54653167724609</v>
       </c>
       <c r="AM106" t="n">
         <v>-0.0789597749775216</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.7934027640484871</v>
+        <v>0.793402619330569</v>
       </c>
       <c r="AO106" t="n">
         <v>84.35251461271447</v>
@@ -20950,13 +20950,13 @@
         <v>0.7167340679733307</v>
       </c>
       <c r="AW106" t="n">
-        <v>4.434870673546405</v>
+        <v>4.434871005811818</v>
       </c>
       <c r="AX106" t="n">
-        <v>0.5947885387692915</v>
+        <v>0.5947886532079913</v>
       </c>
       <c r="AY106" t="n">
-        <v>7.878471634779117</v>
+        <v>7.878469861353357</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21085,7 +21085,7 @@
         <v>36528</v>
       </c>
       <c r="AD107" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="AE107" t="n">
         <v>303</v>
@@ -21142,13 +21142,13 @@
         <v>0.2369028618604663</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.209909119257409</v>
+        <v>1.209908873319079</v>
       </c>
       <c r="AX107" t="n">
         <v>0.2982131940389723</v>
       </c>
       <c r="AY107" t="n">
-        <v>15.28228775914976</v>
+        <v>15.28229109685815</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21532,7 +21532,7 @@
         <v>0.7317390426464718</v>
       </c>
       <c r="AY109" t="n">
-        <v>73.4428310248759</v>
+        <v>73.44283571849114</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21674,16 +21674,16 @@
         <v>1302.731481933594</v>
       </c>
       <c r="AG110" t="n">
-        <v>1279.332379455566</v>
+        <v>1279.332376708984</v>
       </c>
       <c r="AH110" t="n">
         <v>0.1051624992832865</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.1253760192339091</v>
+        <v>0.125376021649964</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.01829008852881953</v>
+        <v>0.01829009071497301</v>
       </c>
       <c r="AK110" t="n">
         <v>1684.826782226562</v>
@@ -21722,13 +21722,13 @@
         <v>0.5576307645820193</v>
       </c>
       <c r="AW110" t="n">
-        <v>1.93687932162966</v>
+        <v>1.936879138802298</v>
       </c>
       <c r="AX110" t="n">
-        <v>0.5453682164918121</v>
+        <v>0.5453683177343429</v>
       </c>
       <c r="AY110" t="n">
-        <v>170.7589632203255</v>
+        <v>170.7589436788294</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21870,16 +21870,16 @@
         <v>642.9331103515625</v>
       </c>
       <c r="AG111" t="n">
-        <v>605.4477471923828</v>
+        <v>605.4477484130859</v>
       </c>
       <c r="AH111" t="n">
         <v>0.05230231056018209</v>
       </c>
       <c r="AI111" t="n">
-        <v>0.1174539845857494</v>
+        <v>0.1174539823327401</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.06191345716126451</v>
+        <v>0.0619134550202356</v>
       </c>
       <c r="AK111" t="n">
         <v>784.9856567382812</v>
@@ -21915,7 +21915,7 @@
         <v>0.2207857471679577</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.6088214680230892</v>
+        <v>0.6088217015245023</v>
       </c>
       <c r="AW111" t="n">
         <v>4.827984238600812</v>
@@ -21924,7 +21924,7 @@
         <v>0.5395564897571086</v>
       </c>
       <c r="AY111" t="n">
-        <v>91.01310421471955</v>
+        <v>91.01312211601578</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22066,16 +22066,16 @@
         <v>270.3983825683594</v>
       </c>
       <c r="AG112" t="n">
-        <v>247.1726522064209</v>
+        <v>247.1726516723633</v>
       </c>
       <c r="AH112" t="n">
         <v>0.08654491569931366</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.1886427773069652</v>
+        <v>0.1886427798752257</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.09396561534866721</v>
+        <v>0.09396561771236178</v>
       </c>
       <c r="AK112" t="n">
         <v>330.5873718261719</v>
@@ -22108,19 +22108,19 @@
         <v>0.006833581959059254</v>
       </c>
       <c r="AU112" t="n">
-        <v>0.4883397715152693</v>
+        <v>0.4883398865615289</v>
       </c>
       <c r="AV112" t="n">
         <v>0.6531841984087958</v>
       </c>
       <c r="AW112" t="n">
-        <v>0.689747285733906</v>
+        <v>0.6897478788940403</v>
       </c>
       <c r="AX112" t="n">
-        <v>0.6828640880053056</v>
+        <v>0.6828642350896399</v>
       </c>
       <c r="AY112" t="n">
-        <v>428.4854661940288</v>
+        <v>428.4855410377454</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22316,7 +22316,7 @@
         <v>0.1738344783598105</v>
       </c>
       <c r="AY113" t="n">
-        <v>520.5963847613875</v>
+        <v>520.5962099839489</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22502,13 +22502,13 @@
         <v>0.9113084570919125</v>
       </c>
       <c r="AW114" t="n">
-        <v>0.7320641537800117</v>
+        <v>0.7320639767338004</v>
       </c>
       <c r="AX114" t="n">
         <v>0.7022708580566293</v>
       </c>
       <c r="AY114" t="n">
-        <v>0.2794279393886723</v>
+        <v>0.2794278427857282</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22700,7 +22700,7 @@
         <v>0.9043785394344797</v>
       </c>
       <c r="AY115" t="n">
-        <v>75.30977068451043</v>
+        <v>75.30977657673184</v>
       </c>
       <c r="AZ115" t="inlineStr"/>
       <c r="BA115" t="n">
@@ -22892,7 +22892,7 @@
         <v>0.1494428922210698</v>
       </c>
       <c r="AY116" t="n">
-        <v>9.675351660478947</v>
+        <v>9.675350908602757</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -23226,16 +23226,16 @@
         <v>21452.8544921875</v>
       </c>
       <c r="AG118" t="n">
-        <v>21173.93918945313</v>
+        <v>21173.93923828125</v>
       </c>
       <c r="AH118" t="n">
         <v>-0.04045403340164111</v>
       </c>
       <c r="AI118" t="n">
-        <v>-0.02781434215823575</v>
+        <v>-0.02781434440014274</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0.01317257503380875</v>
+        <v>0.01317257269738392</v>
       </c>
       <c r="AK118" t="n">
         <v>25925</v>
@@ -23271,16 +23271,16 @@
         <v>0.09368741363730515</v>
       </c>
       <c r="AV118" t="n">
-        <v>0.1984221496692762</v>
+        <v>0.1984222859388418</v>
       </c>
       <c r="AW118" t="n">
         <v>-0.1081211971251085</v>
       </c>
       <c r="AX118" t="n">
-        <v>0.03468238565429016</v>
+        <v>0.03468228407779206</v>
       </c>
       <c r="AY118" t="n">
-        <v>18.36316802469927</v>
+        <v>18.36317469481574</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23422,28 +23422,28 @@
         <v>55.0538355255127</v>
       </c>
       <c r="AG119" t="n">
-        <v>57.54275300979614</v>
+        <v>57.54275295257568</v>
       </c>
       <c r="AH119" t="n">
         <v>-0.01078646810656536</v>
       </c>
       <c r="AI119" t="n">
-        <v>-0.05357327837266801</v>
+        <v>-0.05357327743154217</v>
       </c>
       <c r="AJ119" t="n">
-        <v>-0.04325336126792079</v>
+        <v>-0.04325336031653282</v>
       </c>
       <c r="AK119" t="n">
         <v>86.98540496826172</v>
       </c>
       <c r="AL119" t="n">
-        <v>30.38825798034668</v>
+        <v>30.38825988769531</v>
       </c>
       <c r="AM119" t="n">
         <v>-0.3739179681425473</v>
       </c>
       <c r="AN119" t="n">
-        <v>0.7921395533661111</v>
+        <v>0.7921394408807321</v>
       </c>
       <c r="AO119" t="n">
         <v>71.76299641663879</v>
@@ -23470,13 +23470,13 @@
         <v>0.4233997353676253</v>
       </c>
       <c r="AW119" t="n">
-        <v>-0.4547912082003189</v>
+        <v>-0.4547912498429452</v>
       </c>
       <c r="AX119" t="n">
         <v>0.4763528927551339</v>
       </c>
       <c r="AY119" t="n">
-        <v>30.34587455806568</v>
+        <v>30.34590036728429</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23851,16 +23851,16 @@
         <v>-0.187708807491569</v>
       </c>
       <c r="AV121" t="n">
-        <v>0.167571290147783</v>
+        <v>0.1675713687019003</v>
       </c>
       <c r="AW121" t="n">
-        <v>0.9461560631735006</v>
+        <v>0.946156281425125</v>
       </c>
       <c r="AX121" t="n">
         <v>-0.3123049627571693</v>
       </c>
       <c r="AY121" t="n">
-        <v>1.122219612680563</v>
+        <v>1.122220261498574</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -24002,28 +24002,28 @@
         <v>59.49159996032715</v>
       </c>
       <c r="AG122" t="n">
-        <v>61.33784780502319</v>
+        <v>61.33784769058227</v>
       </c>
       <c r="AH122" t="n">
         <v>-0.07348266026393058</v>
       </c>
       <c r="AI122" t="n">
-        <v>-0.1013705093289763</v>
+        <v>-0.1013705076523608</v>
       </c>
       <c r="AJ122" t="n">
-        <v>-0.03009965153268468</v>
+        <v>-0.03009964972309576</v>
       </c>
       <c r="AK122" t="n">
         <v>75.72768402099609</v>
       </c>
       <c r="AL122" t="n">
-        <v>49.78789138793945</v>
+        <v>49.78788757324219</v>
       </c>
       <c r="AM122" t="n">
         <v>-0.2721288172948441</v>
       </c>
       <c r="AN122" t="n">
-        <v>0.1070964725619401</v>
+        <v>0.107096557386545</v>
       </c>
       <c r="AO122" t="n">
         <v>37.95045016019156</v>
@@ -24050,13 +24050,13 @@
         <v>-0.04978330837235523</v>
       </c>
       <c r="AW122" t="n">
-        <v>0.1297656272479004</v>
+        <v>0.1297653622461485</v>
       </c>
       <c r="AX122" t="n">
         <v>0.04172981900299488</v>
       </c>
       <c r="AY122" t="n">
-        <v>4.002627617945493</v>
+        <v>4.002627184946186</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
@@ -24248,7 +24248,7 @@
         <v>0.2655351185137955</v>
       </c>
       <c r="AY123" t="n">
-        <v>200.8813203553603</v>
+        <v>200.8812385624315</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
@@ -24625,16 +24625,16 @@
         <v>-0.02487425397298915</v>
       </c>
       <c r="AV125" t="n">
-        <v>0.5617948678937033</v>
+        <v>0.5617947203035503</v>
       </c>
       <c r="AW125" t="n">
-        <v>9.49473211294929</v>
+        <v>9.494734612048672</v>
       </c>
       <c r="AX125" t="n">
         <v>0.4370157413041462</v>
       </c>
       <c r="AY125" t="n">
-        <v>24.38371129733541</v>
+        <v>24.38371860739771</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24934,13 +24934,13 @@
         <v>0.1591770104536434</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.259797487963538</v>
+        <v>1.259797770186764</v>
       </c>
       <c r="AX127" t="n">
         <v>0.16951383500503</v>
       </c>
       <c r="AY127" t="n">
-        <v>28.04406401230495</v>
+        <v>28.04406983975452</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -25710,13 +25710,13 @@
         <v>1.667602328643806</v>
       </c>
       <c r="AW131" t="n">
-        <v>14.82554308998822</v>
+        <v>14.82554625563659</v>
       </c>
       <c r="AX131" t="n">
         <v>0.8268043107223209</v>
       </c>
       <c r="AY131" t="n">
-        <v>15.28911244125213</v>
+        <v>15.28911411816397</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25858,16 +25858,16 @@
         <v>374.8449230957031</v>
       </c>
       <c r="AG132" t="n">
-        <v>334.8677409362793</v>
+        <v>334.8677413177491</v>
       </c>
       <c r="AH132" t="n">
         <v>0.1979354150950465</v>
       </c>
       <c r="AI132" t="n">
-        <v>0.3409473462251713</v>
+        <v>0.3409473446976103</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.1193820045121363</v>
+        <v>0.119382003236975</v>
       </c>
       <c r="AK132" t="n">
         <v>483.6542053222656</v>
@@ -25903,16 +25903,16 @@
         <v>0.4246653318022413</v>
       </c>
       <c r="AV132" t="n">
-        <v>2.112916159937683</v>
+        <v>2.11291648922115</v>
       </c>
       <c r="AW132" t="n">
-        <v>2.893869920365524</v>
+        <v>2.893869662752458</v>
       </c>
       <c r="AX132" t="n">
-        <v>1.165976293580115</v>
+        <v>1.16597645299999</v>
       </c>
       <c r="AY132" t="n">
-        <v>402.3293017755686</v>
+        <v>402.3290858448734</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26054,16 +26054,16 @@
         <v>1721.490451660156</v>
       </c>
       <c r="AG133" t="n">
-        <v>1539.716709899902</v>
+        <v>1539.716707458496</v>
       </c>
       <c r="AH133" t="n">
         <v>0.08470544044724138</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.2127620922651055</v>
+        <v>0.2127620941880859</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.118056614305414</v>
+        <v>0.1180566160782275</v>
       </c>
       <c r="AK133" t="n">
         <v>1986.870361328125</v>
@@ -26102,13 +26102,13 @@
         <v>0.8245622489020961</v>
       </c>
       <c r="AW133" t="n">
-        <v>1.343060444801504</v>
+        <v>1.34305990646756</v>
       </c>
       <c r="AX133" t="n">
         <v>0.6122294586506516</v>
       </c>
       <c r="AY133" t="n">
-        <v>1060.117530510936</v>
+        <v>1060.117602393022</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26250,28 +26250,28 @@
         <v>424.0705377197266</v>
       </c>
       <c r="AG134" t="n">
-        <v>385.4128001403809</v>
+        <v>385.4127996826172</v>
       </c>
       <c r="AH134" t="n">
         <v>0.114861695701584</v>
       </c>
       <c r="AI134" t="n">
-        <v>0.2266847354501298</v>
+        <v>0.2266847369070917</v>
       </c>
       <c r="AJ134" t="n">
-        <v>0.1003021632007688</v>
+        <v>0.100302164507623</v>
       </c>
       <c r="AK134" t="n">
         <v>476.2922668457031</v>
       </c>
       <c r="AL134" t="n">
-        <v>272.1793518066406</v>
+        <v>272.1793212890625</v>
       </c>
       <c r="AM134" t="n">
         <v>-0.007374186630546453</v>
       </c>
       <c r="AN134" t="n">
-        <v>0.7370164034895832</v>
+        <v>0.7370165982491761</v>
       </c>
       <c r="AO134" t="n">
         <v>85.90618185554091</v>
@@ -26298,13 +26298,13 @@
         <v>0.6583380754012347</v>
       </c>
       <c r="AW134" t="n">
-        <v>3.409475186223314</v>
+        <v>3.409474872458128</v>
       </c>
       <c r="AX134" t="n">
         <v>0.4908714281933642</v>
       </c>
       <c r="AY134" t="n">
-        <v>150.7972504176948</v>
+        <v>150.7972736578419</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26682,13 +26682,13 @@
         <v>0.7314320126500682</v>
       </c>
       <c r="AW136" t="n">
-        <v>1.363445206705608</v>
+        <v>1.363445387132511</v>
       </c>
       <c r="AX136" t="n">
         <v>0.7126734112472199</v>
       </c>
       <c r="AY136" t="n">
-        <v>320.4432976946368</v>
+        <v>320.4433237687172</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -27262,13 +27262,13 @@
         <v>1.727478597168307</v>
       </c>
       <c r="AW139" t="n">
-        <v>1.233349093178508</v>
+        <v>1.233349304361944</v>
       </c>
       <c r="AX139" t="n">
         <v>0.4605005134943139</v>
       </c>
       <c r="AY139" t="n">
-        <v>359.8805403224459</v>
+        <v>359.880346467974</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
@@ -27410,28 +27410,28 @@
         <v>10897.46568359375</v>
       </c>
       <c r="AG140" t="n">
-        <v>9650.59197265625</v>
+        <v>9650.591982421874</v>
       </c>
       <c r="AH140" t="n">
         <v>0.1103499062370692</v>
       </c>
       <c r="AI140" t="n">
-        <v>0.2538090963003972</v>
+        <v>0.253809095031643</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0.1292017851827496</v>
+        <v>0.1292017840400879</v>
       </c>
       <c r="AK140" t="n">
         <v>15222.7265625</v>
       </c>
       <c r="AL140" t="n">
-        <v>4823.43310546875</v>
+        <v>4823.4326171875</v>
       </c>
       <c r="AM140" t="n">
         <v>-0.2051358243662206</v>
       </c>
       <c r="AN140" t="n">
-        <v>1.508586671655333</v>
+        <v>1.508586925602249</v>
       </c>
       <c r="AO140" t="n">
         <v>70.45185685722748</v>
@@ -27455,13 +27455,13 @@
         <v>0.6126492172981826</v>
       </c>
       <c r="AV140" t="n">
-        <v>1.508586671655333</v>
+        <v>1.508586925602249</v>
       </c>
       <c r="AW140" t="n">
         <v>3.482504101367889</v>
       </c>
       <c r="AX140" t="n">
-        <v>0.7119145335953763</v>
+        <v>0.7119146518583692</v>
       </c>
       <c r="AY140" t="n">
         <v>22.08927401345573</v>
@@ -27606,16 +27606,16 @@
         <v>486.893115234375</v>
       </c>
       <c r="AG141" t="n">
-        <v>426.9578826141358</v>
+        <v>426.9578833007812</v>
       </c>
       <c r="AH141" t="n">
         <v>0.1091550920110784</v>
       </c>
       <c r="AI141" t="n">
-        <v>0.2648553874233215</v>
+        <v>0.2648553853891462</v>
       </c>
       <c r="AJ141" t="n">
-        <v>0.1403773886390707</v>
+        <v>0.1403773868050842</v>
       </c>
       <c r="AK141" t="n">
         <v>722.2277221679688</v>
@@ -27648,19 +27648,19 @@
         <v>-0.02503618643462679</v>
       </c>
       <c r="AU141" t="n">
-        <v>0.5350506394096173</v>
+        <v>0.5350505062509223</v>
       </c>
       <c r="AV141" t="n">
-        <v>1.428672949877414</v>
+        <v>1.428672783217098</v>
       </c>
       <c r="AW141" t="n">
-        <v>2.943163371603969</v>
+        <v>2.94316249295865</v>
       </c>
       <c r="AX141" t="n">
         <v>1.015712415188668</v>
       </c>
       <c r="AY141" t="n">
-        <v>7834.40383123605</v>
+        <v>7834.406372257732</v>
       </c>
       <c r="AZ141" t="inlineStr"/>
       <c r="BA141" t="n">
@@ -27802,28 +27802,28 @@
         <v>187.1484677124024</v>
       </c>
       <c r="AG142" t="n">
-        <v>177.5066925048828</v>
+        <v>177.5066931915283</v>
       </c>
       <c r="AH142" t="n">
         <v>0.1054859380819704</v>
       </c>
       <c r="AI142" t="n">
-        <v>0.1655335157797353</v>
+        <v>0.1655335112711258</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0.05431781231152355</v>
+        <v>0.05431780823312748</v>
       </c>
       <c r="AK142" t="n">
         <v>301.3693542480469</v>
       </c>
       <c r="AL142" t="n">
-        <v>97.74768829345703</v>
+        <v>97.7476806640625</v>
       </c>
       <c r="AM142" t="n">
         <v>-0.313500206728504</v>
       </c>
       <c r="AN142" t="n">
-        <v>1.116571788056262</v>
+        <v>1.116571953258762</v>
       </c>
       <c r="AO142" t="n">
         <v>90.31568559226567</v>
@@ -27847,16 +27847,16 @@
         <v>0.3466242036824847</v>
       </c>
       <c r="AV142" t="n">
-        <v>0.8257998529125319</v>
+        <v>0.8257999758422654</v>
       </c>
       <c r="AW142" t="n">
-        <v>4.937943395774012</v>
+        <v>4.937944045892826</v>
       </c>
       <c r="AX142" t="n">
         <v>0.6293650090746981</v>
       </c>
       <c r="AY142" t="n">
-        <v>3412.762317202128</v>
+        <v>3412.762527041612</v>
       </c>
       <c r="AZ142" t="inlineStr"/>
       <c r="BA142" t="n">
@@ -28190,16 +28190,16 @@
         <v>48.02641883850097</v>
       </c>
       <c r="AG144" t="n">
-        <v>54.06811729431152</v>
+        <v>54.06811763763428</v>
       </c>
       <c r="AH144" t="n">
         <v>0.04463333686512372</v>
       </c>
       <c r="AI144" t="n">
-        <v>-0.07209644649077374</v>
+        <v>-0.07209645238279327</v>
       </c>
       <c r="AJ144" t="n">
-        <v>-0.1117423494316158</v>
+        <v>-0.1117423550718911</v>
       </c>
       <c r="AK144" t="n">
         <v>89.60572814941406</v>
@@ -28235,11 +28235,11 @@
         <v>0.1549724775798536</v>
       </c>
       <c r="AV144" t="n">
-        <v>0.4092991193544111</v>
+        <v>0.409298968338639</v>
       </c>
       <c r="AW144" t="inlineStr"/>
       <c r="AX144" t="n">
-        <v>0.3661066311478109</v>
+        <v>0.3661067730487393</v>
       </c>
       <c r="AY144" t="n">
         <v>0.08552482955625496</v>
@@ -28380,16 +28380,16 @@
         <v>58253.920625</v>
       </c>
       <c r="AG145" t="n">
-        <v>64829.62427734375</v>
+        <v>64829.624296875</v>
       </c>
       <c r="AH145" t="n">
         <v>0.0349517998643718</v>
       </c>
       <c r="AI145" t="n">
-        <v>-0.07002391773740735</v>
+        <v>-0.07002391801758179</v>
       </c>
       <c r="AJ145" t="n">
-        <v>-0.1014305377463337</v>
+        <v>-0.1014305380170462</v>
       </c>
       <c r="AK145" t="n">
         <v>88201.875</v>
@@ -28428,10 +28428,10 @@
         <v>0.2810826199948373</v>
       </c>
       <c r="AW145" t="n">
-        <v>4.946955820727539</v>
+        <v>4.946955247873285</v>
       </c>
       <c r="AX145" t="n">
-        <v>0.1902907899809521</v>
+        <v>0.1902908817763547</v>
       </c>
       <c r="AY145" t="n">
         <v>40.38457110369737</v>
@@ -28624,13 +28624,13 @@
         <v>1.883176156426967</v>
       </c>
       <c r="AW146" t="n">
-        <v>4.671436826413384</v>
+        <v>4.671437268864308</v>
       </c>
       <c r="AX146" t="n">
         <v>1.902697562961117</v>
       </c>
       <c r="AY146" t="n">
-        <v>8.646776647265701</v>
+        <v>8.646774727118629</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -29014,7 +29014,7 @@
         <v>0.3528933726562986</v>
       </c>
       <c r="AY148" t="n">
-        <v>-0.06784709168377434</v>
+        <v>-0.06784716600271623</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29156,16 +29156,16 @@
         <v>488.9562023925781</v>
       </c>
       <c r="AG149" t="n">
-        <v>292.6326711654663</v>
+        <v>292.6326713180542</v>
       </c>
       <c r="AH149" t="n">
         <v>0.1504507290810644</v>
       </c>
       <c r="AI149" t="n">
-        <v>0.9222734675896065</v>
+        <v>0.9222734665872727</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0.6708872609651386</v>
+        <v>0.6708872600938856</v>
       </c>
       <c r="AK149" t="n">
         <v>588.4000244140625</v>
@@ -29204,7 +29204,7 @@
         <v>2.865700220080373</v>
       </c>
       <c r="AW149" t="n">
-        <v>10.6501416081452</v>
+        <v>10.65013792647945</v>
       </c>
       <c r="AX149" t="n">
         <v>3.441827819872604</v>
@@ -29352,16 +29352,16 @@
         <v>145.6631213378906</v>
       </c>
       <c r="AG150" t="n">
-        <v>136.9273958206177</v>
+        <v>136.9273957824707</v>
       </c>
       <c r="AH150" t="n">
         <v>0.0726119559853351</v>
       </c>
       <c r="AI150" t="n">
-        <v>0.1410427004530703</v>
+        <v>0.1410427007709565</v>
       </c>
       <c r="AJ150" t="n">
-        <v>0.0637982301855593</v>
+        <v>0.06379823048192557</v>
       </c>
       <c r="AK150" t="n">
         <v>156.2400054931641</v>
@@ -29400,13 +29400,13 @@
         <v>0.4503520799081799</v>
       </c>
       <c r="AW150" t="n">
-        <v>1.382083123036299</v>
+        <v>1.382083677204688</v>
       </c>
       <c r="AX150" t="n">
         <v>0.2884903709069961</v>
       </c>
       <c r="AY150" t="n">
-        <v>49.73544860690403</v>
+        <v>49.73547217488134</v>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="n">
@@ -29598,7 +29598,7 @@
         <v>0.2341866175054446</v>
       </c>
       <c r="AY151" t="n">
-        <v>10.86483954333069</v>
+        <v>10.86483808919656</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29788,13 +29788,13 @@
         <v>0.2022079445749696</v>
       </c>
       <c r="AW152" t="n">
-        <v>1.740821446524732</v>
+        <v>1.740821218186936</v>
       </c>
       <c r="AX152" t="n">
         <v>0.1141150849003347</v>
       </c>
       <c r="AY152" t="n">
-        <v>684.2370654845213</v>
+        <v>684.2370097328303</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29980,7 +29980,7 @@
         <v>0.9997634984434216</v>
       </c>
       <c r="AW153" t="n">
-        <v>7.013764837708468</v>
+        <v>7.013765777685505</v>
       </c>
       <c r="AX153" t="n">
         <v>0.4284024988881583</v>
@@ -30128,28 +30128,28 @@
         <v>111.672180480957</v>
       </c>
       <c r="AG154" t="n">
-        <v>96.93961303710938</v>
+        <v>96.93961311340333</v>
       </c>
       <c r="AH154" t="n">
         <v>0.004726481250853398</v>
       </c>
       <c r="AI154" t="n">
-        <v>0.1574215476318332</v>
+        <v>0.157421546720913</v>
       </c>
       <c r="AJ154" t="n">
-        <v>0.1519767511162633</v>
+        <v>0.1519767502096283</v>
       </c>
       <c r="AK154" t="n">
         <v>129.0153350830078</v>
       </c>
       <c r="AL154" t="n">
-        <v>66.23379516601562</v>
+        <v>66.23380279541016</v>
       </c>
       <c r="AM154" t="n">
         <v>-0.1303359645110926</v>
       </c>
       <c r="AN154" t="n">
-        <v>0.6939992139513047</v>
+        <v>0.6939990188215099</v>
       </c>
       <c r="AO154" t="n">
         <v>56.67262343287564</v>
@@ -30176,13 +30176,13 @@
         <v>0.6830217829668506</v>
       </c>
       <c r="AW154" t="n">
-        <v>1.304073154898205</v>
+        <v>1.30407387686943</v>
       </c>
       <c r="AX154" t="n">
         <v>0.4948570408610928</v>
       </c>
       <c r="AY154" t="n">
-        <v>2272.868010904556</v>
+        <v>2272.867839233235</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30712,28 +30712,28 @@
         <v>316.8352130126953</v>
       </c>
       <c r="AG157" t="n">
-        <v>301.5557110595703</v>
+        <v>301.5557098388672</v>
       </c>
       <c r="AH157" t="n">
         <v>-0.03921663009751397</v>
       </c>
       <c r="AI157" t="n">
-        <v>0.009465224825323304</v>
+        <v>0.009465228911657242</v>
       </c>
       <c r="AJ157" t="n">
-        <v>0.05066891918391381</v>
+        <v>0.05066892343704099</v>
       </c>
       <c r="AK157" t="n">
         <v>385.5466918945312</v>
       </c>
       <c r="AL157" t="n">
-        <v>192.3445129394531</v>
+        <v>192.3445281982422</v>
       </c>
       <c r="AM157" t="n">
         <v>-0.2104458161311816</v>
       </c>
       <c r="AN157" t="n">
-        <v>0.5826289973654337</v>
+        <v>0.5826288718146719</v>
       </c>
       <c r="AO157" t="n">
         <v>53.63671188971703</v>
@@ -30754,19 +30754,19 @@
         <v>-0.0517136051418422</v>
       </c>
       <c r="AU157" t="n">
-        <v>0.1386118462851686</v>
+        <v>0.1386119762550104</v>
       </c>
       <c r="AV157" t="n">
         <v>0.4129586014143316</v>
       </c>
       <c r="AW157" t="n">
-        <v>3.955045643350372</v>
+        <v>3.955045951028414</v>
       </c>
       <c r="AX157" t="n">
-        <v>0.2672750575329184</v>
+        <v>0.2672751380342289</v>
       </c>
       <c r="AY157" t="n">
-        <v>411.0267548814879</v>
+        <v>411.026555436531</v>
       </c>
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="n">
@@ -30958,7 +30958,7 @@
         <v>0.3672834744965963</v>
       </c>
       <c r="AY158" t="n">
-        <v>6.763403972304922</v>
+        <v>6.763404459409799</v>
       </c>
       <c r="AZ158" t="inlineStr"/>
       <c r="BA158" t="n">
@@ -32578,25 +32578,25 @@
         <v>372.6729040527344</v>
       </c>
       <c r="AG5" t="n">
-        <v>366.2593502807617</v>
+        <v>366.259348449707</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.04704632189147817</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.03035918570761553</v>
+        <v>-0.03035918086005218</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.01751096256534135</v>
+        <v>0.01751096765222382</v>
       </c>
       <c r="AK5" t="n">
-        <v>479.9351196289062</v>
+        <v>479.9350891113281</v>
       </c>
       <c r="AL5" t="n">
         <v>292.4138793945312</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.2600249489492713</v>
+        <v>-0.2600249018965616</v>
       </c>
       <c r="AN5" t="n">
         <v>0.214511484146328</v>
@@ -32626,13 +32626,13 @@
         <v>0.05795905632301102</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.684791697655564</v>
+        <v>6.684791063311859</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.02726348178560789</v>
+        <v>0.02726339110506371</v>
       </c>
       <c r="AY5" t="n">
-        <v>312.3053857667985</v>
+        <v>312.3052210203775</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32647,7 +32647,7 @@
         <v>0.125</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.003407935223200986</v>
+        <v>0.003407923888132963</v>
       </c>
     </row>
     <row r="6">
@@ -32980,28 +32980,28 @@
         <v>305.7798626708984</v>
       </c>
       <c r="AG7" t="n">
-        <v>274.6133799743652</v>
+        <v>274.6133786010742</v>
       </c>
       <c r="AH7" t="n">
         <v>0.1364057371180389</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2653789493680632</v>
+        <v>0.2653789556959907</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1134922220448347</v>
+        <v>0.1134922276132044</v>
       </c>
       <c r="AK7" t="n">
         <v>432.8701477050781</v>
       </c>
       <c r="AL7" t="n">
-        <v>130.7660064697266</v>
+        <v>130.7659912109375</v>
       </c>
       <c r="AM7" t="n">
         <v>-0.1972419625685856</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.657341916416342</v>
+        <v>1.657342226495587</v>
       </c>
       <c r="AO7" t="n">
         <v>90.71985397777416</v>
@@ -33025,7 +33025,7 @@
         <v>0.5776305985090133</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.374957737354422</v>
+        <v>1.374957489675245</v>
       </c>
       <c r="AW7" t="n">
         <v>4.927760033146161</v>
@@ -33034,7 +33034,7 @@
         <v>0.8832877971149351</v>
       </c>
       <c r="AY7" t="n">
-        <v>1844.094054572067</v>
+        <v>1844.094200559296</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33197,13 +33197,13 @@
         <v>316.3519592285156</v>
       </c>
       <c r="AL8" t="n">
-        <v>73.67493438720703</v>
+        <v>73.67494201660156</v>
       </c>
       <c r="AM8" t="n">
         <v>-0.1392814218411897</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.695829671376029</v>
+        <v>2.695829288655094</v>
       </c>
       <c r="AO8" t="n">
         <v>83.26491524979657</v>
@@ -33224,19 +33224,19 @@
         <v>0.1805686455677795</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.488297999543331</v>
+        <v>1.488297826057856</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.165547034272823</v>
+        <v>2.165546753499481</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.398185053420253</v>
+        <v>3.398185324424063</v>
       </c>
       <c r="AX8" t="n">
         <v>2.05056021022692</v>
       </c>
       <c r="AY8" t="n">
-        <v>21.4489393675998</v>
+        <v>21.44894466278791</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33371,7 +33371,7 @@
         <v>45586</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>242.8099975585938</v>
@@ -33503,7 +33503,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.046286097419683</v>
+        <v>1.046286086084615</v>
       </c>
     </row>
     <row r="5">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8895651617309592</v>
+        <v>0.8895650956743943</v>
       </c>
     </row>
   </sheetData>
@@ -33690,31 +33690,31 @@
         <v>0.4921252633013883</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9020582706790035</v>
+        <v>0.9020582832454833</v>
       </c>
       <c r="O2" t="n">
         <v>0.4285021175046884</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5790475081957351</v>
+        <v>0.5790475521202296</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.627128763046903</v>
+        <v>4.627128568672496</v>
       </c>
       <c r="R2" t="n">
         <v>1.842358230303476</v>
       </c>
       <c r="S2" t="n">
-        <v>5.527133877434532</v>
+        <v>5.527133522547373</v>
       </c>
       <c r="T2" t="n">
-        <v>1383.725407203806</v>
+        <v>1383.725458420356</v>
       </c>
       <c r="U2" t="n">
         <v>375.2216433423201</v>
       </c>
       <c r="V2" t="n">
-        <v>4061.441973638215</v>
+        <v>4061.442220299005</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33774,22 +33774,22 @@
         <v>4.909659380353385</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.366222170112414</v>
+        <v>5.366222261855768</v>
       </c>
       <c r="R3" t="n">
-        <v>5.830906468128515</v>
+        <v>5.830905669928297</v>
       </c>
       <c r="S3" t="n">
-        <v>6.722492699850088</v>
+        <v>6.72249275483605</v>
       </c>
       <c r="T3" t="n">
-        <v>46.79173910057381</v>
+        <v>46.79174736729876</v>
       </c>
       <c r="U3" t="n">
-        <v>34.01231546342356</v>
+        <v>34.01230000460952</v>
       </c>
       <c r="V3" t="n">
-        <v>70.86143860069333</v>
+        <v>70.86145510301041</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33831,13 +33831,13 @@
         <v>0.625</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6174672877912901</v>
+        <v>0.617467292822622</v>
       </c>
       <c r="L4" t="n">
         <v>0.3206918717816474</v>
       </c>
       <c r="M4" t="n">
-        <v>1.174611520325245</v>
+        <v>1.174611521993729</v>
       </c>
       <c r="N4" t="n">
         <v>0.6861301515064695</v>
@@ -33849,22 +33849,22 @@
         <v>1.139489319426226</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.223312991230361</v>
+        <v>7.223312932245491</v>
       </c>
       <c r="R4" t="n">
-        <v>4.591976807617396</v>
+        <v>4.591977028842858</v>
       </c>
       <c r="S4" t="n">
-        <v>6.485810766642497</v>
+        <v>6.485810191332365</v>
       </c>
       <c r="T4" t="n">
-        <v>239.8468249963234</v>
+        <v>239.8467996049806</v>
       </c>
       <c r="U4" t="n">
         <v>45.50419105227319</v>
       </c>
       <c r="V4" t="n">
-        <v>735.0518975128167</v>
+        <v>735.0518412135352</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33906,40 +33906,40 @@
         <v>0.4666666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>0.720047134165126</v>
+        <v>0.7200471682570726</v>
       </c>
       <c r="L5" t="n">
         <v>0.6293650090746981</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6170270625045208</v>
+        <v>0.6170270711119483</v>
       </c>
       <c r="N5" t="n">
-        <v>1.094829273771619</v>
+        <v>1.094829299670554</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8257998529125319</v>
+        <v>0.8257999758422654</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8807112871800566</v>
+        <v>0.8807112925937379</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.635411883564411</v>
+        <v>3.635412001147678</v>
       </c>
       <c r="R5" t="n">
-        <v>2.918516645984746</v>
+        <v>2.918516077855554</v>
       </c>
       <c r="S5" t="n">
-        <v>3.496363261137137</v>
+        <v>3.496363080734063</v>
       </c>
       <c r="T5" t="n">
-        <v>910.68982015813</v>
+        <v>910.6899844214119</v>
       </c>
       <c r="U5" t="n">
         <v>40.38457110369737</v>
       </c>
       <c r="V5" t="n">
-        <v>1190.733863381512</v>
+        <v>1190.734132239081</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33999,22 +33999,22 @@
         <v>0.1127969291157173</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.278666296357076</v>
+        <v>1.278666366912882</v>
       </c>
       <c r="R6" t="n">
-        <v>1.240641023850877</v>
+        <v>1.24064116496249</v>
       </c>
       <c r="S6" t="n">
-        <v>1.139482397308836</v>
+        <v>1.139482548885001</v>
       </c>
       <c r="T6" t="n">
-        <v>90.04515333240164</v>
+        <v>90.04515478926405</v>
       </c>
       <c r="U6" t="n">
         <v>78.73077313277192</v>
       </c>
       <c r="V6" t="n">
-        <v>69.16359424019033</v>
+        <v>69.16359736999105</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34056,40 +34056,40 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5660645165328463</v>
+        <v>0.5660645253626075</v>
       </c>
       <c r="L7" t="n">
         <v>0.1058442809520797</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08562609836634368</v>
+        <v>0.0856261301950661</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2818540799447526</v>
+        <v>0.2818540756777413</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008270303553102987</v>
+        <v>0.008270321592352192</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1246354996407328</v>
+        <v>0.1246354953683461</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7313402799018427</v>
+        <v>0.7313403123544397</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5745229961754436</v>
+        <v>0.5745228462841571</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9443080979375722</v>
+        <v>0.944308162803687</v>
       </c>
       <c r="T7" t="n">
-        <v>1245.293133562099</v>
+        <v>1245.293471516733</v>
       </c>
       <c r="U7" t="n">
-        <v>14.68381740203662</v>
+        <v>14.68381546512401</v>
       </c>
       <c r="V7" t="n">
-        <v>3059.339265597196</v>
+        <v>3059.340470834064</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34131,40 +34131,40 @@
         <v>0.391304347826087</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4354466588845674</v>
+        <v>0.4354466707567978</v>
       </c>
       <c r="L8" t="n">
         <v>0.4566843170296401</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4980602283607888</v>
+        <v>0.4980602553295257</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6662614277784431</v>
+        <v>0.6662614414482133</v>
       </c>
       <c r="O8" t="n">
         <v>0.5284832688650697</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5692483385887835</v>
+        <v>0.569248347108707</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.750212901765855</v>
+        <v>2.75021299995065</v>
       </c>
       <c r="R8" t="n">
-        <v>1.490708893737891</v>
+        <v>1.490709254273518</v>
       </c>
       <c r="S8" t="n">
-        <v>2.503646665529283</v>
+        <v>2.503646811438692</v>
       </c>
       <c r="T8" t="n">
-        <v>184.5035479518609</v>
+        <v>184.503549814802</v>
       </c>
       <c r="U8" t="n">
-        <v>27.36479292770055</v>
+        <v>27.364809487341</v>
       </c>
       <c r="V8" t="n">
-        <v>361.9466604968511</v>
+        <v>361.9466814833027</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34206,40 +34206,40 @@
         <v>0.4615384615384616</v>
       </c>
       <c r="K9" t="n">
-        <v>1.875160539833369</v>
+        <v>1.875160554853808</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38204830580572</v>
+        <v>1.382048395928357</v>
       </c>
       <c r="M9" t="n">
-        <v>1.917793567713074</v>
+        <v>1.917793573226031</v>
       </c>
       <c r="N9" t="n">
-        <v>4.47462712558487</v>
+        <v>4.474627100708024</v>
       </c>
       <c r="O9" t="n">
-        <v>3.555107509820854</v>
+        <v>3.555107769979822</v>
       </c>
       <c r="P9" t="n">
-        <v>4.321456007079821</v>
+        <v>4.321456069285253</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.299264072334408</v>
+        <v>7.299264377368095</v>
       </c>
       <c r="R9" t="n">
-        <v>6.152544092348691</v>
+        <v>6.152544381197394</v>
       </c>
       <c r="S9" t="n">
-        <v>9.232717975618938</v>
+        <v>9.232718760571069</v>
       </c>
       <c r="T9" t="n">
-        <v>316.9456406345806</v>
+        <v>316.9456488888979</v>
       </c>
       <c r="U9" t="n">
         <v>55.21129830261416</v>
       </c>
       <c r="V9" t="n">
-        <v>407.6807419927982</v>
+        <v>407.6807679827791</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34299,22 +34299,22 @@
         <v>0.8944249432839972</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2876342933024056</v>
+        <v>0.2876341828452695</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2876342933024056</v>
+        <v>0.2876341828452695</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2876342933024056</v>
+        <v>0.2876341828452695</v>
       </c>
       <c r="T10" t="n">
-        <v>12.48303857815807</v>
+        <v>12.48303143502839</v>
       </c>
       <c r="U10" t="n">
-        <v>12.48303857815807</v>
+        <v>12.48303143502839</v>
       </c>
       <c r="V10" t="n">
-        <v>23.70535373292226</v>
+        <v>23.70534028407474</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34356,40 +34356,40 @@
         <v>0.3809523809523809</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6736911468999733</v>
+        <v>0.6736911353558381</v>
       </c>
       <c r="L11" t="n">
         <v>0.5520209328647576</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4209515417222377</v>
+        <v>0.4209514949467315</v>
       </c>
       <c r="N11" t="n">
-        <v>1.069063474883517</v>
+        <v>1.06906347183151</v>
       </c>
       <c r="O11" t="n">
         <v>0.6714216429900646</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6429662321158848</v>
+        <v>0.642966219455148</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.094881591213306</v>
+        <v>6.094881431770761</v>
       </c>
       <c r="R11" t="n">
-        <v>3.707831339919315</v>
+        <v>3.707829881530021</v>
       </c>
       <c r="S11" t="n">
-        <v>7.04269203295468</v>
+        <v>7.042691629183519</v>
       </c>
       <c r="T11" t="n">
-        <v>191.8248137747821</v>
+        <v>191.8247877049256</v>
       </c>
       <c r="U11" t="n">
-        <v>25.43947005991203</v>
+        <v>25.43946707374523</v>
       </c>
       <c r="V11" t="n">
-        <v>294.240226223546</v>
+        <v>294.2401167569695</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34440,31 +34440,31 @@
         <v>0.3450083244175666</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3200417762757083</v>
+        <v>0.3200417675755052</v>
       </c>
       <c r="O12" t="n">
         <v>0.1431575101749655</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2887083622482514</v>
+        <v>0.2887083557749935</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.486183036052896</v>
+        <v>1.48618311367975</v>
       </c>
       <c r="R12" t="n">
         <v>0.5240702018272422</v>
       </c>
       <c r="S12" t="n">
-        <v>4.911704357477323</v>
+        <v>4.911704749498369</v>
       </c>
       <c r="T12" t="n">
-        <v>55.23506955943306</v>
+        <v>55.23507529353478</v>
       </c>
       <c r="U12" t="n">
         <v>8.272261629262729</v>
       </c>
       <c r="V12" t="n">
-        <v>206.6280446375979</v>
+        <v>206.628031541523</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34515,31 +34515,31 @@
         <v>0.019297739125896</v>
       </c>
       <c r="N13" t="n">
-        <v>0.00912240983319728</v>
+        <v>0.009122370292841143</v>
       </c>
       <c r="O13" t="n">
         <v>0.05705700741320485</v>
       </c>
       <c r="P13" t="n">
-        <v>0.169684088325367</v>
+        <v>0.1696839835919514</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5386281251525803</v>
+        <v>0.5386282289774346</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4176513010483552</v>
+        <v>0.4176512281781206</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7508612228967978</v>
+        <v>0.7508612543220141</v>
       </c>
       <c r="T13" t="n">
-        <v>15.39389072884369</v>
+        <v>15.39388858794372</v>
       </c>
       <c r="U13" t="n">
-        <v>3.221169625570469</v>
+        <v>3.221169631760151</v>
       </c>
       <c r="V13" t="n">
-        <v>2.520161984107835</v>
+        <v>2.520161954472506</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34581,40 +34581,40 @@
         <v>0.05263157894736842</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1121584364044906</v>
+        <v>-0.1121584309355786</v>
       </c>
       <c r="L14" t="n">
         <v>-0.1219512195121951</v>
       </c>
       <c r="M14" t="n">
-        <v>0.07554080189128137</v>
+        <v>0.07554081089865829</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1079570183072304</v>
+        <v>-0.1079570051910223</v>
       </c>
       <c r="O14" t="n">
         <v>-0.06103178005694243</v>
       </c>
       <c r="P14" t="n">
-        <v>0.133897274420799</v>
+        <v>0.133897312260588</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.886247061573873</v>
+        <v>1.886247170517476</v>
       </c>
       <c r="R14" t="n">
-        <v>1.478614731676489</v>
+        <v>1.47861484086068</v>
       </c>
       <c r="S14" t="n">
-        <v>1.932127307868862</v>
+        <v>1.932127361564118</v>
       </c>
       <c r="T14" t="n">
-        <v>68.79545360663413</v>
+        <v>68.79544889086036</v>
       </c>
       <c r="U14" t="n">
-        <v>11.37024662370633</v>
+        <v>11.37024766594397</v>
       </c>
       <c r="V14" t="n">
-        <v>95.03223555842642</v>
+        <v>95.03221848117539</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -1072,13 +1072,13 @@
         <v>-0.01690812402664033</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.224054001268547</v>
+        <v>1.224054421357531</v>
       </c>
       <c r="AX3" t="n">
         <v>0.107793767853356</v>
       </c>
       <c r="AY3" t="n">
-        <v>17.97863285963067</v>
+        <v>17.97863094775178</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1220,16 +1220,16 @@
         <v>500.1885009765625</v>
       </c>
       <c r="AG4" t="n">
-        <v>432.7045623779297</v>
+        <v>432.7045631408691</v>
       </c>
       <c r="AH4" t="n">
         <v>0.06973672181498358</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.2365712170533616</v>
+        <v>0.2365712148730543</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1559584632705848</v>
+        <v>0.1559584612324127</v>
       </c>
       <c r="AK4" t="n">
         <v>537.6464233398438</v>
@@ -1265,16 +1265,16 @@
         <v>0.3977115003179557</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0326807556229094</v>
+        <v>0.03268063397586296</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.9692807383836559</v>
+        <v>0.9692805171991634</v>
       </c>
       <c r="AX4" t="n">
         <v>0.13854736486662</v>
       </c>
       <c r="AY4" t="n">
-        <v>9065.796238136865</v>
+        <v>9065.789942355921</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
@@ -1802,28 +1802,28 @@
         <v>346.1388287353516</v>
       </c>
       <c r="AG7" t="n">
-        <v>339.6683973693848</v>
+        <v>339.6683972167968</v>
       </c>
       <c r="AH7" t="n">
         <v>0.01595075290145842</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.03530386219499815</v>
+        <v>0.03530386266008367</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0190492592660314</v>
+        <v>0.01904925972381499</v>
       </c>
       <c r="AK7" t="n">
         <v>402.1211853027344</v>
       </c>
       <c r="AL7" t="n">
-        <v>235.9563446044922</v>
+        <v>235.9563598632812</v>
       </c>
       <c r="AM7" t="n">
         <v>-0.1254874985077835</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.4903604488854012</v>
+        <v>0.4903603525070042</v>
       </c>
       <c r="AO7" t="n">
         <v>46.88148002470388</v>
@@ -1850,13 +1850,13 @@
         <v>0.4597547189924709</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.656049792657367</v>
+        <v>1.656050404866232</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1180203138029947</v>
+        <v>0.1180202053288</v>
       </c>
       <c r="AY7" t="n">
-        <v>140.379842625108</v>
+        <v>140.3798290734615</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -2384,25 +2384,25 @@
         <v>145.220361328125</v>
       </c>
       <c r="AG10" t="n">
-        <v>160.5146378326416</v>
+        <v>160.5146385192871</v>
       </c>
       <c r="AH10" t="n">
         <v>-0.0263073813940492</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.1190834941551364</v>
+        <v>-0.119083497923499</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.09528275247060625</v>
+        <v>-0.09528275634078309</v>
       </c>
       <c r="AK10" t="n">
-        <v>308.867431640625</v>
+        <v>308.8674621582031</v>
       </c>
       <c r="AL10" t="n">
         <v>114.566276550293</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.542198433983785</v>
+        <v>-0.5421984792167627</v>
       </c>
       <c r="AN10" t="n">
         <v>0.2342200353732522</v>
@@ -2435,10 +2435,10 @@
         <v>0.7008607005366543</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.2678356226465541</v>
+        <v>-0.2678356804944856</v>
       </c>
       <c r="AY10" t="n">
-        <v>2824.034362514292</v>
+        <v>2824.034152253562</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2624,13 +2624,13 @@
         <v>-0.3528741188375372</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.1524299368649099</v>
+        <v>-0.152429740015937</v>
       </c>
       <c r="AX11" t="n">
         <v>-0.2783304278664579</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.2604774922890409</v>
+        <v>0.2604773834481731</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3825645125632</v>
+        <v>3825543938048</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>0.1274339854717255</v>
       </c>
       <c r="AA12" t="n">
-        <v>487517205359.7656</v>
+        <v>487504310622.6562</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -4710,16 +4710,16 @@
         <v>231.8859478759766</v>
       </c>
       <c r="AG22" t="n">
-        <v>250.9319671630859</v>
+        <v>250.9319679260254</v>
       </c>
       <c r="AH22" t="n">
         <v>-0.02050983699843589</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.09485424495478512</v>
+        <v>-0.0948542477068115</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0.07590112771375579</v>
+        <v>-0.07590113052340774</v>
       </c>
       <c r="AK22" t="n">
         <v>326.8851013183594</v>
@@ -4758,13 +4758,13 @@
         <v>-0.1914975206424832</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.9961848350781677</v>
+        <v>0.9961842996799239</v>
       </c>
       <c r="AX22" t="n">
         <v>-0.2049507455046247</v>
       </c>
       <c r="AY22" t="n">
-        <v>157.3395517172316</v>
+        <v>157.339617510975</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
@@ -4906,25 +4906,25 @@
         <v>371.3881274414063</v>
       </c>
       <c r="AG23" t="n">
-        <v>367.1055648803711</v>
+        <v>367.1055668640137</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.02651705363962698</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.01516064279020912</v>
+        <v>-0.01516064811175533</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.01166575222696697</v>
+        <v>0.01166574676046506</v>
       </c>
       <c r="AK23" t="n">
-        <v>479.9350891113281</v>
+        <v>479.9351196289062</v>
       </c>
       <c r="AL23" t="n">
         <v>292.4138793945312</v>
       </c>
       <c r="AM23" t="n">
-        <v>-0.2466897779564993</v>
+        <v>-0.246689825857148</v>
       </c>
       <c r="AN23" t="n">
         <v>0.236398249267519</v>
@@ -4951,7 +4951,7 @@
         <v>-0.04470945747025556</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.05567263030562253</v>
+        <v>0.0556725362353967</v>
       </c>
       <c r="AW23" t="n">
         <v>7.298314166986252</v>
@@ -5102,16 +5102,16 @@
         <v>322.3565734863281</v>
       </c>
       <c r="AG24" t="n">
-        <v>290.4023234558106</v>
+        <v>290.4023246002197</v>
       </c>
       <c r="AH24" t="n">
         <v>0.04430944592701214</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1592194258034672</v>
+        <v>0.1592194212352485</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1100344158760833</v>
+        <v>0.1100344115016916</v>
       </c>
       <c r="AK24" t="n">
         <v>341.0700073242188</v>
@@ -5147,16 +5147,16 @@
         <v>0.3010831370684059</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.3300408922627835</v>
+        <v>0.3300408120794158</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.480525570943161</v>
+        <v>1.480526128734598</v>
       </c>
       <c r="AX24" t="n">
         <v>0.245549379320982</v>
       </c>
       <c r="AY24" t="n">
-        <v>3429.817324378985</v>
+        <v>3429.817063871902</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5686,16 +5686,16 @@
         <v>221.9403125</v>
       </c>
       <c r="AG27" t="n">
-        <v>201.8288954925537</v>
+        <v>201.8288955688477</v>
       </c>
       <c r="AH27" t="n">
         <v>0.03307054133888765</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.1360117599600894</v>
+        <v>0.136011759530662</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.09964587557378923</v>
+        <v>0.09964587515810863</v>
       </c>
       <c r="AK27" t="n">
         <v>239.2400054931641</v>
@@ -5740,7 +5740,7 @@
         <v>0.2169261331430019</v>
       </c>
       <c r="AY27" t="n">
-        <v>6110.350074481819</v>
+        <v>6110.3476471559</v>
       </c>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
@@ -6124,13 +6124,13 @@
         <v>1.769841245012258</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.125925147912127</v>
+        <v>1.125925477248282</v>
       </c>
       <c r="AX29" t="n">
         <v>1.658709855470637</v>
       </c>
       <c r="AY29" t="n">
-        <v>575.8603784490289</v>
+        <v>575.8600942870941</v>
       </c>
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
@@ -6272,16 +6272,16 @@
         <v>172.6907846069336</v>
       </c>
       <c r="AG30" t="n">
-        <v>168.0017881393433</v>
+        <v>168.0017880630493</v>
       </c>
       <c r="AH30" t="n">
         <v>0.01626731501313494</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.04463173841005563</v>
+        <v>0.04463173888444993</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.02791039618995717</v>
+        <v>0.02791039665675799</v>
       </c>
       <c r="AK30" t="n">
         <v>248.7425079345703</v>
@@ -6317,16 +6317,16 @@
         <v>0.3494885373057486</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.08146048346164592</v>
+        <v>0.08146058514838006</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.5444983505327827</v>
+        <v>0.5444980394263308</v>
       </c>
       <c r="AX30" t="n">
         <v>0.03043129675896483</v>
       </c>
       <c r="AY30" t="n">
-        <v>522.0116225440212</v>
+        <v>522.0118083483437</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>0.1496333926916122</v>
+        <v>0.1494276821613312</v>
       </c>
       <c r="AA31" t="n">
-        <v>92779251981.50293</v>
+        <v>92651702450.07227</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
@@ -6704,13 +6704,13 @@
         <v>7.003777311704185</v>
       </c>
       <c r="AW32" t="n">
-        <v>8.753705538141956</v>
+        <v>8.753706681166825</v>
       </c>
       <c r="AX32" t="n">
         <v>4.810961418496263</v>
       </c>
       <c r="AY32" t="n">
-        <v>173.4630572746069</v>
+        <v>173.463034418447</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6896,7 +6896,7 @@
         <v>8.657760567288152</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.418162443520905</v>
+        <v>5.418161858821064</v>
       </c>
       <c r="AX33" t="n">
         <v>5.902822456747622</v>
@@ -7092,13 +7092,13 @@
         <v>3.004873428160245</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.978874382025197</v>
+        <v>6.978873728210583</v>
       </c>
       <c r="AX34" t="n">
         <v>1.781557820066594</v>
       </c>
       <c r="AY34" t="n">
-        <v>44.20821662258238</v>
+        <v>44.20820612773667</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>6532031840256</v>
+        <v>6475019190272</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>0.006319275125861168</v>
       </c>
       <c r="AA35" t="n">
-        <v>41277706329.46289</v>
+        <v>40917427708.55957</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
@@ -7284,13 +7284,13 @@
         <v>4.175965264894685</v>
       </c>
       <c r="AW35" t="n">
-        <v>7.320901348179854</v>
+        <v>7.32089988021121</v>
       </c>
       <c r="AX35" t="n">
         <v>2.227566313842295</v>
       </c>
       <c r="AY35" t="n">
-        <v>32.31956245920308</v>
+        <v>32.31956834377364</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7665,16 +7665,16 @@
         <v>0.09143090203170146</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.2437241379398816</v>
+        <v>0.2437240581661519</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.773744667392486</v>
+        <v>1.77374486578021</v>
       </c>
       <c r="AX37" t="n">
         <v>0.0350133598398592</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.107607853371865</v>
+        <v>3.107606548160429</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7864,7 +7864,7 @@
         <v>0.6148345412339522</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.117942979667176</v>
+        <v>1.117943153847982</v>
       </c>
       <c r="AX38" t="n">
         <v>0.1500505158944654</v>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="X39" t="n">
-        <v>10692419649536</v>
+        <v>10690172551168</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>0.006319275125861168</v>
       </c>
       <c r="AA39" t="n">
-        <v>67568341526.58203</v>
+        <v>67554141493.75977</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -8008,16 +8008,16 @@
         <v>2909.39716796875</v>
       </c>
       <c r="AG39" t="n">
-        <v>2702.765686035156</v>
+        <v>2702.765672607422</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.005635933158001261</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.07038505592540267</v>
+        <v>0.07038506124323174</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.07645186669389514</v>
+        <v>0.07645187204186521</v>
       </c>
       <c r="AK39" t="n">
         <v>3065.2041015625</v>
@@ -8053,16 +8053,16 @@
         <v>0.06181852199892068</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.2393185285928852</v>
+        <v>0.2393186582085671</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.056867887641056</v>
+        <v>1.056867709126193</v>
       </c>
       <c r="AX39" t="n">
         <v>0.08947598128411993</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.484416672800556</v>
+        <v>3.484415824258332</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8248,13 +8248,13 @@
         <v>0.1415187496939978</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.7854625775563662</v>
+        <v>0.7854627182247942</v>
       </c>
       <c r="AX40" t="n">
         <v>0.1196904085280541</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.9093055860611206</v>
+        <v>0.9093057469203629</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8396,28 +8396,28 @@
         <v>1040.886158447266</v>
       </c>
       <c r="AG41" t="n">
-        <v>987.3042825317383</v>
+        <v>987.3042834472657</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.01424372851266686</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.03925413547546919</v>
+        <v>0.03925413451176873</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.05427088372201494</v>
+        <v>0.0542708827443894</v>
       </c>
       <c r="AK41" t="n">
         <v>1110.633178710938</v>
       </c>
       <c r="AL41" t="n">
-        <v>715.1826171875</v>
+        <v>715.1826782226562</v>
       </c>
       <c r="AM41" t="n">
         <v>-0.07614856258422587</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.4346826026460133</v>
+        <v>0.4346824802072582</v>
       </c>
       <c r="AO41" t="n">
         <v>39.96786135952572</v>
@@ -8438,13 +8438,13 @@
         <v>0.00725197638600461</v>
       </c>
       <c r="AU41" t="n">
-        <v>-0.01966070667138164</v>
+        <v>-0.01966059233349915</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.2965209428133764</v>
+        <v>0.2965210428056364</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.4428341019994932</v>
+        <v>0.442834349667635</v>
       </c>
       <c r="AX41" t="n">
         <v>0.3632966686305334</v>
@@ -8592,28 +8592,28 @@
         <v>117.3557234191895</v>
       </c>
       <c r="AG42" t="n">
-        <v>111.6985484695435</v>
+        <v>111.6985485839844</v>
       </c>
       <c r="AH42" t="n">
         <v>-0.02424867914446915</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.02517001075849801</v>
+        <v>0.02517000970815841</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.05064680810233213</v>
+        <v>0.05064680702589031</v>
       </c>
       <c r="AK42" t="n">
         <v>132.0340881347656</v>
       </c>
       <c r="AL42" t="n">
-        <v>77.09210205078125</v>
+        <v>77.09209442138672</v>
       </c>
       <c r="AM42" t="n">
         <v>-0.1327239521709616</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.4853661930349455</v>
+        <v>0.4853663400337371</v>
       </c>
       <c r="AO42" t="n">
         <v>44.60562479616607</v>
@@ -8634,19 +8634,19 @@
         <v>-0.05919007274592258</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.03851191315971536</v>
+        <v>0.03851198501680897</v>
       </c>
       <c r="AV42" t="n">
         <v>0.1278029188716001</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.1323618921784</v>
+        <v>2.132362219037488</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.4072078329313178</v>
+        <v>0.4072077009953832</v>
       </c>
       <c r="AY42" t="n">
-        <v>99.15878310427318</v>
+        <v>99.15876221734081</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8788,28 +8788,28 @@
         <v>185.9639965820313</v>
       </c>
       <c r="AG43" t="n">
-        <v>179.6863548278808</v>
+        <v>179.6863551330567</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.03873869247597905</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.005155429425524605</v>
+        <v>-0.005155431115149267</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.03493666372253856</v>
+        <v>0.03493666196482237</v>
       </c>
       <c r="AK43" t="n">
         <v>201.1799774169922</v>
       </c>
       <c r="AL43" t="n">
-        <v>144.9624176025391</v>
+        <v>144.9624328613281</v>
       </c>
       <c r="AM43" t="n">
         <v>-0.1114424168747451</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.2331471664398133</v>
+        <v>0.2331470366383734</v>
       </c>
       <c r="AO43" t="n">
         <v>37.86467755933517</v>
@@ -8830,19 +8830,19 @@
         <v>0.03971902275482941</v>
       </c>
       <c r="AU43" t="n">
-        <v>-0.05558621585863732</v>
+        <v>-0.05558629199188148</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.04948158890119458</v>
+        <v>0.04948149488571918</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.4567514715064829</v>
+        <v>0.4567511997925893</v>
       </c>
       <c r="AX43" t="n">
         <v>0.1766719106199748</v>
       </c>
       <c r="AY43" t="n">
-        <v>34.30783928333786</v>
+        <v>34.30782265641658</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -9154,25 +9154,25 @@
         <v>2.166963968276978</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.177976551055908</v>
+        <v>2.17797651052475</v>
       </c>
       <c r="AH45" t="n">
         <v>-0.01705789961309367</v>
       </c>
       <c r="AI45" t="n">
-        <v>-0.02202798583471</v>
+        <v>-0.02202796763509285</v>
       </c>
       <c r="AJ45" t="n">
-        <v>-0.005056336705549724</v>
+        <v>-0.005056318190097775</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.306842803955078</v>
+        <v>2.306842565536499</v>
       </c>
       <c r="AL45" t="n">
         <v>2.064932584762573</v>
       </c>
       <c r="AM45" t="n">
-        <v>-0.07666005208979287</v>
+        <v>-0.07665995666004766</v>
       </c>
       <c r="AN45" t="n">
         <v>0.03151072832037571</v>
@@ -9193,22 +9193,22 @@
         <v>-0.004672892510771409</v>
       </c>
       <c r="AT45" t="n">
-        <v>-0.03211289712911169</v>
+        <v>-0.03211279226909525</v>
       </c>
       <c r="AU45" t="n">
         <v>-0.04468275331759508</v>
       </c>
       <c r="AV45" t="n">
-        <v>-0.05480818162678236</v>
+        <v>-0.05480808162668516</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.1332596843189628</v>
+        <v>0.1332598999497103</v>
       </c>
       <c r="AX45" t="n">
         <v>0.008486014810537013</v>
       </c>
       <c r="AY45" t="n">
-        <v>2.952499841559221</v>
+        <v>2.952499404395462</v>
       </c>
       <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
@@ -9969,7 +9969,7 @@
         <v>0.06288969404984357</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.07643961724636883</v>
+        <v>0.07643969121181438</v>
       </c>
       <c r="AW49" t="n">
         <v>-0.1995675258854984</v>
@@ -9978,7 +9978,7 @@
         <v>0.04499598497303281</v>
       </c>
       <c r="AY49" t="n">
-        <v>6.576397651304516</v>
+        <v>6.576397193283918</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10120,16 +10120,16 @@
         <v>273.8756225585938</v>
       </c>
       <c r="AG50" t="n">
-        <v>285.4471280670166</v>
+        <v>285.4471286010742</v>
       </c>
       <c r="AH50" t="n">
         <v>0.08834077505546789</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.04422142672333562</v>
+        <v>0.04422142476964841</v>
       </c>
       <c r="AJ50" t="n">
-        <v>-0.04053817457118047</v>
+        <v>-0.04053817636628665</v>
       </c>
       <c r="AK50" t="n">
         <v>401.7044372558594</v>
@@ -10165,14 +10165,14 @@
         <v>0.02492811085624447</v>
       </c>
       <c r="AV50" t="n">
-        <v>-0.217868504738037</v>
+        <v>-0.217868567369319</v>
       </c>
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="n">
-        <v>-0.1825455072575846</v>
+        <v>-0.1825454388413775</v>
       </c>
       <c r="AY50" t="n">
-        <v>6.372497883894472</v>
+        <v>6.372499275131701</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10357,16 +10357,16 @@
         <v>0.02383670937412452</v>
       </c>
       <c r="AV51" t="n">
-        <v>-0.2265806811086954</v>
+        <v>-0.226580737632494</v>
       </c>
       <c r="AW51" t="n">
-        <v>9.338349885674578</v>
+        <v>9.338348623225841</v>
       </c>
       <c r="AX51" t="n">
         <v>-0.0183870060828405</v>
       </c>
       <c r="AY51" t="n">
-        <v>13.26615825806048</v>
+        <v>13.2661558541109</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10508,16 +10508,16 @@
         <v>968.7100036621093</v>
       </c>
       <c r="AG52" t="n">
-        <v>925.8943325805664</v>
+        <v>925.8943338012696</v>
       </c>
       <c r="AH52" t="n">
         <v>0.03718344671828588</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.08514540494967737</v>
+        <v>0.08514540351901689</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.04624250259984963</v>
+        <v>0.04624250122047902</v>
       </c>
       <c r="AK52" t="n">
         <v>1174.859985351562</v>
@@ -10907,13 +10907,13 @@
         <v>70.97299957275391</v>
       </c>
       <c r="AL54" t="n">
-        <v>55.35893249511719</v>
+        <v>55.35892868041992</v>
       </c>
       <c r="AM54" t="n">
         <v>-0.1315007149097351</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.113460766157029</v>
+        <v>0.1134608428838704</v>
       </c>
       <c r="AO54" t="n">
         <v>40.8385104205169</v>
@@ -10937,16 +10937,16 @@
         <v>-0.001331327000079208</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.06660866683784983</v>
+        <v>0.06660873724352978</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.05243441497133161</v>
+        <v>0.05243468915882366</v>
       </c>
       <c r="AX54" t="n">
-        <v>0.07286186445927734</v>
+        <v>0.072861935692911</v>
       </c>
       <c r="AY54" t="n">
-        <v>167.4841020708287</v>
+        <v>167.4839510984026</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11330,7 +11330,7 @@
         <v>-0.205671225398652</v>
       </c>
       <c r="AY56" t="n">
-        <v>9.166473628402578</v>
+        <v>9.166472943085983</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11522,7 +11522,7 @@
         <v>-0.1065340935480216</v>
       </c>
       <c r="AY57" t="n">
-        <v>13.71717004766071</v>
+        <v>13.71717591188017</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11664,28 +11664,28 @@
         <v>119.3431271362305</v>
       </c>
       <c r="AG58" t="n">
-        <v>122.4176868438721</v>
+        <v>122.4176867294312</v>
       </c>
       <c r="AH58" t="n">
         <v>-0.02256623967358717</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.04711480396904666</v>
+        <v>-0.04711480307825167</v>
       </c>
       <c r="AJ58" t="n">
-        <v>-0.0251153226866867</v>
+        <v>-0.02511532177532572</v>
       </c>
       <c r="AK58" t="n">
         <v>131.1634063720703</v>
       </c>
       <c r="AL58" t="n">
-        <v>111.0920944213867</v>
+        <v>111.0921020507812</v>
       </c>
       <c r="AM58" t="n">
         <v>-0.1106513260643852</v>
       </c>
       <c r="AN58" t="n">
-        <v>0.05002972653850879</v>
+        <v>0.05002965442635232</v>
       </c>
       <c r="AO58" t="n">
         <v>49.50821640479343</v>
@@ -11712,13 +11712,13 @@
         <v>-0.03180288875732951</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.403657806959135</v>
+        <v>0.4036575492334327</v>
       </c>
       <c r="AX58" t="n">
         <v>0.01927262053654255</v>
       </c>
       <c r="AY58" t="n">
-        <v>157.9481227540764</v>
+        <v>157.9481485728868</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -12052,16 +12052,16 @@
         <v>104.5512539672852</v>
       </c>
       <c r="AG60" t="n">
-        <v>105.6624032592773</v>
+        <v>105.6624035263062</v>
       </c>
       <c r="AH60" t="n">
         <v>-0.01675016653626493</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.02709005397592268</v>
+        <v>-0.02709005643464946</v>
       </c>
       <c r="AJ60" t="n">
-        <v>-0.01051603273934254</v>
+        <v>-0.01051603523995503</v>
       </c>
       <c r="AK60" t="n">
         <v>116.6635665893555</v>
@@ -12106,7 +12106,7 @@
         <v>0.1150846244184975</v>
       </c>
       <c r="AY60" t="n">
-        <v>191.4097463628745</v>
+        <v>191.4097248973719</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12248,25 +12248,25 @@
         <v>43.12933448791504</v>
       </c>
       <c r="AG61" t="n">
-        <v>44.88129806518555</v>
+        <v>44.88129796981811</v>
       </c>
       <c r="AH61" t="n">
         <v>-0.0317495315575882</v>
       </c>
       <c r="AI61" t="n">
-        <v>-0.06954566552685204</v>
+        <v>-0.06954566354974689</v>
       </c>
       <c r="AJ61" t="n">
-        <v>-0.03903549257256234</v>
+        <v>-0.03903549053062683</v>
       </c>
       <c r="AK61" t="n">
-        <v>49.35155487060547</v>
+        <v>49.3515510559082</v>
       </c>
       <c r="AL61" t="n">
         <v>40.20000076293945</v>
       </c>
       <c r="AM61" t="n">
-        <v>-0.1538260865129076</v>
+        <v>-0.1538260211067097</v>
       </c>
       <c r="AN61" t="n">
         <v>0.03880590868127332</v>
@@ -12293,7 +12293,7 @@
         <v>-0.1162183388077561</v>
       </c>
       <c r="AV61" t="n">
-        <v>-0.07215569423091606</v>
+        <v>-0.07215561558976602</v>
       </c>
       <c r="AW61" t="n">
         <v>0.4466062813558871</v>
@@ -12302,7 +12302,7 @@
         <v>-0.02280364911944943</v>
       </c>
       <c r="AY61" t="n">
-        <v>170.9336917491258</v>
+        <v>170.93367065257</v>
       </c>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
@@ -12636,16 +12636,16 @@
         <v>81.64354354858398</v>
       </c>
       <c r="AG63" t="n">
-        <v>86.27709426879883</v>
+        <v>86.27709392547608</v>
       </c>
       <c r="AH63" t="n">
         <v>-0.05222147532865085</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.1031223535143835</v>
+        <v>-0.103122349945435</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.05370545634950208</v>
+        <v>-0.0537054525839088</v>
       </c>
       <c r="AK63" t="n">
         <v>96.44304656982422</v>
@@ -12678,7 +12678,7 @@
         <v>-0.1293066260116782</v>
       </c>
       <c r="AU63" t="n">
-        <v>-0.1491558965599975</v>
+        <v>-0.1491558251824885</v>
       </c>
       <c r="AV63" t="n">
         <v>-0.04905245604035657</v>
@@ -12690,7 +12690,7 @@
         <v>-0.02300247670222821</v>
       </c>
       <c r="AY63" t="n">
-        <v>223.3483173542602</v>
+        <v>223.3482010439921</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12832,16 +12832,16 @@
         <v>111.4061003112793</v>
       </c>
       <c r="AG64" t="n">
-        <v>138.9161910629273</v>
+        <v>138.9161907577515</v>
       </c>
       <c r="AH64" t="n">
         <v>-0.03084300663047523</v>
       </c>
       <c r="AI64" t="n">
-        <v>-0.2227687759463971</v>
+        <v>-0.2227687742389491</v>
       </c>
       <c r="AJ64" t="n">
-        <v>-0.198033724803081</v>
+        <v>-0.1980337230412942</v>
       </c>
       <c r="AK64" t="n">
         <v>182.8191986083984</v>
@@ -12886,7 +12886,7 @@
         <v>-0.343859089497086</v>
       </c>
       <c r="AY64" t="n">
-        <v>14.12442789820823</v>
+        <v>14.12442688796751</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13268,13 +13268,13 @@
         <v>-0.07401107237545135</v>
       </c>
       <c r="AW66" t="n">
-        <v>0.6570298934338581</v>
+        <v>0.6570295287757788</v>
       </c>
       <c r="AX66" t="n">
         <v>0.01272061435685967</v>
       </c>
       <c r="AY66" t="n">
-        <v>319.3701021402325</v>
+        <v>319.369889155268</v>
       </c>
       <c r="AZ66" t="inlineStr"/>
       <c r="BA66" t="n">
@@ -13652,7 +13652,7 @@
         <v>5.589010357259252</v>
       </c>
       <c r="AW68" t="n">
-        <v>7.036341206831217</v>
+        <v>7.036340280651798</v>
       </c>
       <c r="AX68" t="n">
         <v>1.578308390073988</v>
@@ -13800,28 +13800,28 @@
         <v>197.831852722168</v>
       </c>
       <c r="AG69" t="n">
-        <v>141.0051990127563</v>
+        <v>141.0051989746094</v>
       </c>
       <c r="AH69" t="n">
         <v>0.1987452507434897</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.6818528363271916</v>
+        <v>0.681852836782193</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.4030110528355106</v>
+        <v>0.4030110532150755</v>
       </c>
       <c r="AK69" t="n">
         <v>237.1499938964844</v>
       </c>
       <c r="AL69" t="n">
-        <v>93.13681793212891</v>
+        <v>93.13681030273438</v>
       </c>
       <c r="AM69" t="n">
         <v>0</v>
       </c>
       <c r="AN69" t="n">
-        <v>1.546253985929618</v>
+        <v>1.546254194508548</v>
       </c>
       <c r="AO69" t="n">
         <v>80.66867396983351</v>
@@ -13848,7 +13848,7 @@
         <v>1.00147323749477</v>
       </c>
       <c r="AW69" t="n">
-        <v>1.974404905610799</v>
+        <v>1.974404336368655</v>
       </c>
       <c r="AX69" t="n">
         <v>1.250661994037329</v>
@@ -14040,13 +14040,13 @@
         <v>3.881390681469647</v>
       </c>
       <c r="AW70" t="n">
-        <v>4.47357607888737</v>
+        <v>4.47357543318991</v>
       </c>
       <c r="AX70" t="n">
         <v>0.9595450832106351</v>
       </c>
       <c r="AY70" t="n">
-        <v>3.649852520884231</v>
+        <v>3.64985205490654</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="X71" t="n">
-        <v>1162145562624</v>
+        <v>1164234457088</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>1162145562624</v>
+        <v>1164234457088</v>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
@@ -14188,16 +14188,16 @@
         <v>976.1861999511718</v>
       </c>
       <c r="AG71" t="n">
-        <v>701.5695658874512</v>
+        <v>701.5695654296875</v>
       </c>
       <c r="AH71" t="n">
         <v>0.05410217851007304</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.4667112857131499</v>
+        <v>0.4667112866701573</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.3914317943885495</v>
+        <v>0.3914317952964379</v>
       </c>
       <c r="AK71" t="n">
         <v>1213.373413085938</v>
@@ -14233,16 +14233,16 @@
         <v>1.412692788290599</v>
       </c>
       <c r="AV71" t="n">
-        <v>4.355412996642928</v>
+        <v>4.355412571347615</v>
       </c>
       <c r="AW71" t="n">
-        <v>13.92159158081721</v>
+        <v>13.92159323165744</v>
       </c>
       <c r="AX71" t="n">
-        <v>2.264189253684067</v>
+        <v>2.264188937685356</v>
       </c>
       <c r="AY71" t="n">
-        <v>760.8009002651514</v>
+        <v>760.800765800662</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14380,28 +14380,28 @@
         <v>1678321.8675</v>
       </c>
       <c r="AG72" t="n">
-        <v>1434975.285</v>
+        <v>1434975.2834375</v>
       </c>
       <c r="AH72" t="n">
         <v>0.001595720434715675</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.1714487472862642</v>
+        <v>0.1714487485618184</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.1695824207174412</v>
+        <v>0.169582421990963</v>
       </c>
       <c r="AK72" t="n">
         <v>2918367.25</v>
       </c>
       <c r="AL72" t="n">
-        <v>335511</v>
+        <v>335510.96875</v>
       </c>
       <c r="AM72" t="n">
         <v>-0.4239929878599069</v>
       </c>
       <c r="AN72" t="n">
-        <v>4.010267919680726</v>
+        <v>4.010268386344672</v>
       </c>
       <c r="AO72" t="n">
         <v>49.23599320882852</v>
@@ -14434,7 +14434,7 @@
         <v>1.488550502604669</v>
       </c>
       <c r="AY72" t="n">
-        <v>-8.34625086438832</v>
+        <v>-8.346251867649197</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14576,16 +14576,16 @@
         <v>257080</v>
       </c>
       <c r="AG73" t="n">
-        <v>228752.6222265625</v>
+        <v>228752.6223046875</v>
       </c>
       <c r="AH73" t="n">
         <v>0.01913801151392569</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.1453420618737582</v>
+        <v>0.145342061482594</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.1238341117042205</v>
+        <v>0.1238341113204018</v>
       </c>
       <c r="AK73" t="n">
         <v>362100.65625</v>
@@ -14621,16 +14621,16 @@
         <v>0.4086409638975268</v>
       </c>
       <c r="AV73" t="n">
-        <v>2.132087789237838</v>
+        <v>2.132088081758557</v>
       </c>
       <c r="AW73" t="n">
-        <v>2.55337575995048</v>
+        <v>2.553375383445293</v>
       </c>
       <c r="AX73" t="n">
         <v>1.045383907141913</v>
       </c>
       <c r="AY73" t="n">
-        <v>60.365997759572</v>
+        <v>60.36601881411212</v>
       </c>
       <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
@@ -15016,7 +15016,7 @@
         <v>0.7280137304971483</v>
       </c>
       <c r="AY75" t="n">
-        <v>1691.968866986562</v>
+        <v>1691.96926883901</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15352,25 +15352,25 @@
         <v>854.7187097167969</v>
       </c>
       <c r="AG77" t="n">
-        <v>662.8784977722167</v>
+        <v>662.8784968566895</v>
       </c>
       <c r="AH77" t="n">
         <v>-0.08390913747583717</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.1812119455246839</v>
+        <v>0.1812119471561016</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.2894047892476694</v>
+        <v>0.2894047910285165</v>
       </c>
       <c r="AK77" t="n">
-        <v>1092.384887695312</v>
+        <v>1092.384765625</v>
       </c>
       <c r="AL77" t="n">
         <v>210.389892578125</v>
       </c>
       <c r="AM77" t="n">
-        <v>-0.2832196702647959</v>
+        <v>-0.283219590167012</v>
       </c>
       <c r="AN77" t="n">
         <v>2.721661674926922</v>
@@ -15546,28 +15546,28 @@
         <v>457.5265911865234</v>
       </c>
       <c r="AG78" t="n">
-        <v>405.7100405883789</v>
+        <v>405.7100409698486</v>
       </c>
       <c r="AH78" t="n">
         <v>-0.1316788872336064</v>
       </c>
       <c r="AI78" t="n">
-        <v>-0.02077848947700778</v>
+        <v>-0.02077849039772295</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.1277181864244668</v>
+        <v>0.1277181853641272</v>
       </c>
       <c r="AK78" t="n">
         <v>745.990478515625</v>
       </c>
       <c r="AL78" t="n">
-        <v>112.9193267822266</v>
+        <v>112.9193420410156</v>
       </c>
       <c r="AM78" t="n">
         <v>-0.4674462875587818</v>
       </c>
       <c r="AN78" t="n">
-        <v>2.518263968624975</v>
+        <v>2.518263493202016</v>
       </c>
       <c r="AO78" t="n">
         <v>36.89954698918758</v>
@@ -15594,13 +15594,13 @@
         <v>2.325156119672784</v>
       </c>
       <c r="AW78" t="n">
-        <v>8.274402702656491</v>
+        <v>8.27440435448649</v>
       </c>
       <c r="AX78" t="n">
         <v>1.118814072800511</v>
       </c>
       <c r="AY78" t="n">
-        <v>583.8185921926997</v>
+        <v>583.818643505508</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -16444,16 +16444,16 @@
         <v>82.21921936035156</v>
       </c>
       <c r="AG83" t="n">
-        <v>74.46857349395752</v>
+        <v>74.46857334136963</v>
       </c>
       <c r="AH83" t="n">
         <v>0.0610657525391094</v>
       </c>
       <c r="AI83" t="n">
-        <v>0.1715008596323966</v>
+        <v>0.1715008620328298</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.1040794190454439</v>
+        <v>0.104079421307729</v>
       </c>
       <c r="AK83" t="n">
         <v>88.62000274658203</v>
@@ -16492,13 +16492,13 @@
         <v>0.3916697980508237</v>
       </c>
       <c r="AW83" t="n">
-        <v>3.962542307139389</v>
+        <v>3.962541768717344</v>
       </c>
       <c r="AX83" t="n">
         <v>0.2551725402161715</v>
       </c>
       <c r="AY83" t="n">
-        <v>1395.508203497987</v>
+        <v>1395.508619889234</v>
       </c>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="n">
@@ -16997,7 +16997,7 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>61221072896</v>
+        <v>61564620800</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1</v>
       </c>
       <c r="AA86" t="n">
-        <v>61221072896</v>
+        <v>61564620800</v>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
@@ -17224,16 +17224,16 @@
         <v>236.4425393676758</v>
       </c>
       <c r="AG87" t="n">
-        <v>171.7013274002075</v>
+        <v>171.7013272094727</v>
       </c>
       <c r="AH87" t="n">
         <v>0.1642574957767122</v>
       </c>
       <c r="AI87" t="n">
-        <v>0.603249100909188</v>
+        <v>0.6032491026901616</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.3770571430503105</v>
+        <v>0.3770571445800182</v>
       </c>
       <c r="AK87" t="n">
         <v>316.2828369140625</v>
@@ -17266,19 +17266,19 @@
         <v>0.2378176261332783</v>
       </c>
       <c r="AU87" t="n">
-        <v>1.097547970695078</v>
+        <v>1.097548214571192</v>
       </c>
       <c r="AV87" t="n">
         <v>2.04286251969071</v>
       </c>
       <c r="AW87" t="n">
-        <v>3.870651642608925</v>
+        <v>3.870652957590498</v>
       </c>
       <c r="AX87" t="n">
         <v>2.084732048982278</v>
       </c>
       <c r="AY87" t="n">
-        <v>21.70041083802038</v>
+        <v>21.70041619369545</v>
       </c>
       <c r="AZ87" t="inlineStr"/>
       <c r="BA87" t="n">
@@ -17393,10 +17393,10 @@
         </is>
       </c>
       <c r="Z88" t="n">
-        <v>0.1496333926916122</v>
+        <v>0.1494276821613312</v>
       </c>
       <c r="AA88" t="n">
-        <v>18421278506.21436</v>
+        <v>18395953604.4541</v>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>1.099534136234722</v>
       </c>
       <c r="AY88" t="n">
-        <v>16.07943746658648</v>
+        <v>16.07944494943924</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
@@ -18050,7 +18050,7 @@
         <v>0.3809330134088802</v>
       </c>
       <c r="AY91" t="n">
-        <v>10.76686150497565</v>
+        <v>10.76685936139124</v>
       </c>
       <c r="AZ91" t="inlineStr"/>
       <c r="BA91" t="n">
@@ -18388,16 +18388,16 @@
         <v>209.9893106079102</v>
       </c>
       <c r="AG93" t="n">
-        <v>212.8374850463867</v>
+        <v>212.8374839019775</v>
       </c>
       <c r="AH93" t="n">
         <v>0.03952907247608239</v>
       </c>
       <c r="AI93" t="n">
-        <v>0.02561817641548325</v>
+        <v>0.02561818193014553</v>
       </c>
       <c r="AJ93" t="n">
-        <v>-0.01338192113036762</v>
+        <v>-0.0133819158254056</v>
       </c>
       <c r="AK93" t="n">
         <v>246.3216247558594</v>
@@ -18433,16 +18433,16 @@
         <v>-0.06119822026133026</v>
       </c>
       <c r="AV93" t="n">
-        <v>-0.008075262802779926</v>
+        <v>-0.0080753315798473</v>
       </c>
       <c r="AW93" t="n">
         <v>0.6816445773693172</v>
       </c>
       <c r="AX93" t="n">
-        <v>-0.05383944338256208</v>
+        <v>-0.05383938080538764</v>
       </c>
       <c r="AY93" t="n">
-        <v>7.200472251396985</v>
+        <v>7.20046931345084</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18557,10 +18557,10 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>0.1496333926916122</v>
+        <v>0.1494276821613312</v>
       </c>
       <c r="AA94" t="n">
-        <v>136648438817.5635</v>
+        <v>136460579528.2324</v>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
@@ -18628,13 +18628,13 @@
         <v>0.8979101377381202</v>
       </c>
       <c r="AW94" t="n">
-        <v>22.4184325183107</v>
+        <v>22.41842981987854</v>
       </c>
       <c r="AX94" t="n">
         <v>0.2448997712846546</v>
       </c>
       <c r="AY94" t="n">
-        <v>166.5164673260651</v>
+        <v>166.5164500668561</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18749,10 +18749,10 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>0.1496333926916122</v>
+        <v>0.1494276821613312</v>
       </c>
       <c r="AA95" t="n">
-        <v>77260473865.11963</v>
+        <v>77154258983.78418</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -18820,13 +18820,13 @@
         <v>0.5027668235869218</v>
       </c>
       <c r="AW95" t="n">
-        <v>24.80482592838824</v>
+        <v>24.80482764378883</v>
       </c>
       <c r="AX95" t="n">
         <v>0.2170288125898985</v>
       </c>
       <c r="AY95" t="n">
-        <v>199.761252348896</v>
+        <v>199.761239370129</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -18968,28 +18968,28 @@
         <v>155.3395812988281</v>
       </c>
       <c r="AG96" t="n">
-        <v>151.9367193984985</v>
+        <v>151.9367199707031</v>
       </c>
       <c r="AH96" t="n">
         <v>0.00862891071126648</v>
       </c>
       <c r="AI96" t="n">
-        <v>0.03121874222413679</v>
+        <v>0.03121873834049294</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0.0223965734800724</v>
+        <v>0.02239656962965331</v>
       </c>
       <c r="AK96" t="n">
         <v>255.2094421386719</v>
       </c>
       <c r="AL96" t="n">
-        <v>77.61928558349609</v>
+        <v>77.61929321289062</v>
       </c>
       <c r="AM96" t="n">
         <v>-0.3860729001137551</v>
       </c>
       <c r="AN96" t="n">
-        <v>1.018570404223039</v>
+        <v>1.018570205812704</v>
       </c>
       <c r="AO96" t="n">
         <v>48.37799663273938</v>
@@ -19013,16 +19013,16 @@
         <v>-0.1024969342259259</v>
       </c>
       <c r="AV96" t="n">
-        <v>0.8126659845456516</v>
+        <v>0.8126658245485694</v>
       </c>
       <c r="AW96" t="n">
-        <v>3.856696730785717</v>
+        <v>3.856697305072151</v>
       </c>
       <c r="AX96" t="n">
         <v>0.7371680968276597</v>
       </c>
       <c r="AY96" t="n">
-        <v>203.7670878771279</v>
+        <v>203.7670240733014</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19208,13 +19208,13 @@
         <v>1</v>
       </c>
       <c r="AW97" t="n">
-        <v>1.108458846344242</v>
+        <v>1.108459050960741</v>
       </c>
       <c r="AX97" t="n">
         <v>0.5913977407734576</v>
       </c>
       <c r="AY97" t="n">
-        <v>16.33758424060119</v>
+        <v>16.33758769941842</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19356,16 +19356,16 @@
         <v>75.90490921020508</v>
       </c>
       <c r="AG98" t="n">
-        <v>78.54482257843017</v>
+        <v>78.54482252120971</v>
       </c>
       <c r="AH98" t="n">
         <v>-0.00467566804492725</v>
       </c>
       <c r="AI98" t="n">
-        <v>-0.03812879612379172</v>
+        <v>-0.03812879542306169</v>
       </c>
       <c r="AJ98" t="n">
-        <v>-0.03361027858442278</v>
+        <v>-0.03361027788040094</v>
       </c>
       <c r="AK98" t="n">
         <v>102.0957336425781</v>
@@ -19401,16 +19401,16 @@
         <v>0.03855913605217087</v>
       </c>
       <c r="AV98" t="n">
-        <v>0.1771762268768298</v>
+        <v>0.1771763668157778</v>
       </c>
       <c r="AW98" t="n">
         <v>0.1493680935559296</v>
       </c>
       <c r="AX98" t="n">
-        <v>0.1815437019779258</v>
+        <v>0.1815438429571832</v>
       </c>
       <c r="AY98" t="n">
-        <v>431.6411103847437</v>
+        <v>431.6413318944026</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19552,25 +19552,25 @@
         <v>371.3881274414063</v>
       </c>
       <c r="AG99" t="n">
-        <v>367.1055668640137</v>
+        <v>367.1055651855469</v>
       </c>
       <c r="AH99" t="n">
         <v>-0.02651705363962698</v>
       </c>
       <c r="AI99" t="n">
-        <v>-0.01516064811175533</v>
+        <v>-0.01516064360890845</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0.01166574676046506</v>
+        <v>0.01166575138596659</v>
       </c>
       <c r="AK99" t="n">
-        <v>479.9351196289062</v>
+        <v>479.9350891113281</v>
       </c>
       <c r="AL99" t="n">
         <v>292.4138793945312</v>
       </c>
       <c r="AM99" t="n">
-        <v>-0.246689825857148</v>
+        <v>-0.2466897779564993</v>
       </c>
       <c r="AN99" t="n">
         <v>0.236398249267519</v>
@@ -19600,13 +19600,13 @@
         <v>0.05567263030562253</v>
       </c>
       <c r="AW99" t="n">
-        <v>7.298314893566349</v>
+        <v>7.298314166986252</v>
       </c>
       <c r="AX99" t="n">
-        <v>0.04577584238236421</v>
+        <v>0.04577575006766188</v>
       </c>
       <c r="AY99" t="n">
-        <v>317.9512076232351</v>
+        <v>317.9513417953951</v>
       </c>
       <c r="AZ99" t="inlineStr"/>
       <c r="BA99" t="n">
@@ -19792,13 +19792,13 @@
         <v>0.09904619816139637</v>
       </c>
       <c r="AW100" t="n">
-        <v>0.63669325115041</v>
+        <v>0.6366927769660224</v>
       </c>
       <c r="AX100" t="n">
         <v>0.0262333764593794</v>
       </c>
       <c r="AY100" t="n">
-        <v>7.006211239542184</v>
+        <v>7.006210293989819</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -19990,7 +19990,7 @@
         <v>0.04247572815533984</v>
       </c>
       <c r="AY101" t="n">
-        <v>24.43281610466342</v>
+        <v>24.43281323219166</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20128,28 +20128,28 @@
         <v>52.16374168395996</v>
       </c>
       <c r="AG102" t="n">
-        <v>48.50867149353027</v>
+        <v>48.50867136001587</v>
       </c>
       <c r="AH102" t="n">
         <v>-0.001988743662168058</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.07321020696751912</v>
+        <v>0.07321020992140381</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.0753488000782947</v>
+        <v>0.07534880303806579</v>
       </c>
       <c r="AK102" t="n">
-        <v>79.68085479736328</v>
+        <v>79.68086242675781</v>
       </c>
       <c r="AL102" t="n">
-        <v>21.00741767883301</v>
+        <v>21.00741958618164</v>
       </c>
       <c r="AM102" t="n">
-        <v>-0.3466435380784377</v>
+        <v>-0.346643600636925</v>
       </c>
       <c r="AN102" t="n">
-        <v>1.478172337466612</v>
+        <v>1.478172112463317</v>
       </c>
       <c r="AO102" t="n">
         <v>51.48571591747086</v>
@@ -20170,19 +20170,19 @@
         <v>-0.2563679598694646</v>
       </c>
       <c r="AU102" t="n">
-        <v>0.2948837014241312</v>
+        <v>0.2948838242861007</v>
       </c>
       <c r="AV102" t="n">
         <v>0.8305662002666867</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.2980100824114393</v>
+        <v>0.2980098354995813</v>
       </c>
       <c r="AX102" t="n">
         <v>0.9129905228084783</v>
       </c>
       <c r="AY102" t="n">
-        <v>22.81676894113746</v>
+        <v>22.8167663433623</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20510,16 +20510,16 @@
         <v>275.8859579467774</v>
       </c>
       <c r="AG104" t="n">
-        <v>204.8376805114746</v>
+        <v>204.8376811218262</v>
       </c>
       <c r="AH104" t="n">
         <v>0.07834411803369967</v>
       </c>
       <c r="AI104" t="n">
-        <v>0.4523695018277392</v>
+        <v>0.4523694975001371</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.3468516010232929</v>
+        <v>0.3468515970101009</v>
       </c>
       <c r="AK104" t="n">
         <v>317.5</v>
@@ -20555,16 +20555,16 @@
         <v>0.937061131358488</v>
       </c>
       <c r="AV104" t="n">
-        <v>0.6701535487344987</v>
+        <v>0.6701534056653926</v>
       </c>
       <c r="AW104" t="n">
-        <v>4.992218735948746</v>
+        <v>4.992217815121092</v>
       </c>
       <c r="AX104" t="n">
-        <v>0.8301682599904985</v>
+        <v>0.8301680881936879</v>
       </c>
       <c r="AY104" t="n">
-        <v>77.67403989307489</v>
+        <v>77.67404485346755</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20721,13 +20721,13 @@
         <v>444.1268615722656</v>
       </c>
       <c r="AL105" t="n">
-        <v>222.418212890625</v>
+        <v>222.4181976318359</v>
       </c>
       <c r="AM105" t="n">
         <v>-0.08541897014865996</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.8262443401662962</v>
+        <v>0.8262444654540535</v>
       </c>
       <c r="AO105" t="n">
         <v>66.33788366258935</v>
@@ -20760,7 +20760,7 @@
         <v>0.497124145468804</v>
       </c>
       <c r="AY105" t="n">
-        <v>917.4277269931391</v>
+        <v>917.4282839911242</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20947,7 +20947,7 @@
         <v>0.07074915785224256</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.1517811051813567</v>
+        <v>0.15178101095441</v>
       </c>
       <c r="AW106" t="n">
         <v>2.129533774351588</v>
@@ -20956,7 +20956,7 @@
         <v>0.3236506915597397</v>
       </c>
       <c r="AY106" t="n">
-        <v>1246.013567570139</v>
+        <v>1246.01367543443</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21094,28 +21094,28 @@
         <v>159.8096005249024</v>
       </c>
       <c r="AG107" t="n">
-        <v>141.9835748291016</v>
+        <v>141.9835748672485</v>
       </c>
       <c r="AH107" t="n">
         <v>0.04768419497858289</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.1792208561962765</v>
+        <v>0.1792208558794532</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.1255499146098911</v>
+        <v>0.1255499143074876</v>
       </c>
       <c r="AK107" t="n">
         <v>184.09619140625</v>
       </c>
       <c r="AL107" t="n">
-        <v>94.54653167724609</v>
+        <v>94.54652404785156</v>
       </c>
       <c r="AM107" t="n">
         <v>-0.09052983987969099</v>
       </c>
       <c r="AN107" t="n">
-        <v>0.770873978194544</v>
+        <v>0.7708741210945222</v>
       </c>
       <c r="AO107" t="n">
         <v>59.41993579867754</v>
@@ -21142,13 +21142,13 @@
         <v>0.7246557644971696</v>
       </c>
       <c r="AW107" t="n">
-        <v>4.43991395443653</v>
+        <v>4.439912943085178</v>
       </c>
       <c r="AX107" t="n">
-        <v>0.574754991570239</v>
+        <v>0.5747548785691128</v>
       </c>
       <c r="AY107" t="n">
-        <v>7.766938931718546</v>
+        <v>7.76694243401538</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21340,7 +21340,7 @@
         <v>0.9852009708163145</v>
       </c>
       <c r="AY108" t="n">
-        <v>78.54841235339856</v>
+        <v>78.54836935736773</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21482,28 +21482,28 @@
         <v>1315.240004882812</v>
       </c>
       <c r="AG109" t="n">
-        <v>1291.789645385742</v>
+        <v>1291.789650268555</v>
       </c>
       <c r="AH109" t="n">
         <v>0.05402058477229654</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.07315463010120271</v>
+        <v>0.07315462604480483</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.01815338865800209</v>
+        <v>0.01815338480950257</v>
       </c>
       <c r="AK109" t="n">
         <v>1684.826782226562</v>
       </c>
       <c r="AL109" t="n">
-        <v>851.247802734375</v>
+        <v>851.2479248046875</v>
       </c>
       <c r="AM109" t="n">
         <v>-0.1771913565912899</v>
       </c>
       <c r="AN109" t="n">
-        <v>0.6285387575855872</v>
+        <v>0.6285385240505272</v>
       </c>
       <c r="AO109" t="n">
         <v>61.83952818256373</v>
@@ -21530,13 +21530,13 @@
         <v>0.4251645689394989</v>
       </c>
       <c r="AW109" t="n">
-        <v>2.099110442613284</v>
+        <v>2.099110654044983</v>
       </c>
       <c r="AX109" t="n">
         <v>0.4880071918130626</v>
       </c>
       <c r="AY109" t="n">
-        <v>164.3836275915456</v>
+        <v>164.3836464077083</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21678,28 +21678,28 @@
         <v>651.7779638671875</v>
       </c>
       <c r="AG110" t="n">
-        <v>612.2639773559571</v>
+        <v>612.2639785766602</v>
       </c>
       <c r="AH110" t="n">
         <v>0.08309891032961536</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.1529994063834788</v>
+        <v>0.1529994040846829</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.06453750011860948</v>
+        <v>0.0645374979961848</v>
       </c>
       <c r="AK110" t="n">
         <v>784.9856567382812</v>
       </c>
       <c r="AL110" t="n">
-        <v>411.8881530761719</v>
+        <v>411.88818359375</v>
       </c>
       <c r="AM110" t="n">
         <v>-0.1006969409165004</v>
       </c>
       <c r="AN110" t="n">
-        <v>0.7139118888686617</v>
+        <v>0.7139117618816735</v>
       </c>
       <c r="AO110" t="n">
         <v>68.078972717371</v>
@@ -21723,13 +21723,13 @@
         <v>0.1851649760874001</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.6433094023991555</v>
+        <v>0.6433095191395035</v>
       </c>
       <c r="AW110" t="n">
         <v>5.286891172720417</v>
       </c>
       <c r="AX110" t="n">
-        <v>0.606412610943186</v>
+        <v>0.6064124993862821</v>
       </c>
       <c r="AY110" t="n">
         <v>95.00881967004317</v>
@@ -21924,7 +21924,7 @@
         <v>1.27682702322911</v>
       </c>
       <c r="AY111" t="n">
-        <v>125.1514932283829</v>
+        <v>125.1514789680746</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22066,28 +22066,28 @@
         <v>454.6739031982422</v>
       </c>
       <c r="AG112" t="n">
-        <v>448.0629469299316</v>
+        <v>448.0629467773438</v>
       </c>
       <c r="AH112" t="n">
         <v>0.04905957353431001</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.06453794997897599</v>
+        <v>0.06453795034150445</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.01475452570583657</v>
+        <v>0.01475452605141125</v>
       </c>
       <c r="AK112" t="n">
         <v>502.2725524902344</v>
       </c>
       <c r="AL112" t="n">
-        <v>373.7903137207031</v>
+        <v>373.790283203125</v>
       </c>
       <c r="AM112" t="n">
         <v>-0.05035620875261348</v>
       </c>
       <c r="AN112" t="n">
-        <v>0.2760630585594268</v>
+        <v>0.2760631627417875</v>
       </c>
       <c r="AO112" t="n">
         <v>78.97529228437307</v>
@@ -22114,13 +22114,13 @@
         <v>0.1474022005024593</v>
       </c>
       <c r="AW112" t="n">
-        <v>1.896468682289262</v>
+        <v>1.896467877135737</v>
       </c>
       <c r="AX112" t="n">
         <v>0.2069056023029743</v>
       </c>
       <c r="AY112" t="n">
-        <v>535.2914444711541</v>
+        <v>535.2917319936846</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22312,7 +22312,7 @@
         <v>0.141399296925141</v>
       </c>
       <c r="AY113" t="n">
-        <v>13.31552044028606</v>
+        <v>13.31551603847623</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22504,7 +22504,7 @@
         <v>0.5500566938470977</v>
       </c>
       <c r="AY114" t="n">
-        <v>0.1650234936926698</v>
+        <v>0.1650235816575296</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22646,16 +22646,16 @@
         <v>271.8782006835938</v>
       </c>
       <c r="AG115" t="n">
-        <v>250.0942182159424</v>
+        <v>250.094217376709</v>
       </c>
       <c r="AH115" t="n">
         <v>0.04362905713277732</v>
       </c>
       <c r="AI115" t="n">
-        <v>0.1345323864679726</v>
+        <v>0.1345323902750877</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0.08710310307470648</v>
+        <v>0.08710310672266464</v>
       </c>
       <c r="AK115" t="n">
         <v>330.5873718261719</v>
@@ -22688,16 +22688,16 @@
         <v>-0.06662490488151096</v>
       </c>
       <c r="AU115" t="n">
-        <v>0.3226977018719384</v>
+        <v>0.3226977959570163</v>
       </c>
       <c r="AV115" t="n">
-        <v>0.6265534875384668</v>
+        <v>0.6265533452609815</v>
       </c>
       <c r="AW115" t="n">
         <v>0.7169974789611027</v>
       </c>
       <c r="AX115" t="n">
-        <v>0.6252411835799037</v>
+        <v>0.6252413256279274</v>
       </c>
       <c r="AY115" t="n">
         <v>413.7794657825924</v>
@@ -22838,16 +22838,16 @@
         <v>21148.6577734375</v>
       </c>
       <c r="AG116" t="n">
-        <v>21215.55754882812</v>
+        <v>21215.5575</v>
       </c>
       <c r="AH116" t="n">
         <v>0.001009152769463562</v>
       </c>
       <c r="AI116" t="n">
-        <v>-0.002147365145755531</v>
+        <v>-0.002147362849173273</v>
       </c>
       <c r="AJ116" t="n">
-        <v>-0.003153335717746453</v>
+        <v>-0.003153333423479454</v>
       </c>
       <c r="AK116" t="n">
         <v>25925</v>
@@ -22886,13 +22886,13 @@
         <v>0.2455350966340455</v>
       </c>
       <c r="AW116" t="n">
-        <v>-0.1193933024904122</v>
+        <v>-0.1193933740343951</v>
       </c>
       <c r="AX116" t="n">
-        <v>0.06408666280917452</v>
+        <v>0.06408676727234996</v>
       </c>
       <c r="AY116" t="n">
-        <v>18.91345423162786</v>
+        <v>18.91344279883976</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -23274,13 +23274,13 @@
         <v>-0.02381065747673128</v>
       </c>
       <c r="AW118" t="n">
-        <v>0.6218616679628446</v>
+        <v>0.6218618124454303</v>
       </c>
       <c r="AX118" t="n">
         <v>0.1045147515956582</v>
       </c>
       <c r="AY118" t="n">
-        <v>9.258084709391643</v>
+        <v>9.258086876855023</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23614,16 +23614,16 @@
         <v>58.60240005493164</v>
       </c>
       <c r="AG120" t="n">
-        <v>61.4140076828003</v>
+        <v>61.41400766372681</v>
       </c>
       <c r="AH120" t="n">
         <v>-0.05191593994083521</v>
       </c>
       <c r="AI120" t="n">
-        <v>-0.095320376089847</v>
+        <v>-0.09532037580887864</v>
       </c>
       <c r="AJ120" t="n">
-        <v>-0.04578121073600083</v>
+        <v>-0.04578121043964689</v>
       </c>
       <c r="AK120" t="n">
         <v>75.72768402099609</v>
@@ -23662,7 +23662,7 @@
         <v>-0.02900979635548695</v>
       </c>
       <c r="AW120" t="n">
-        <v>0.1396541676069418</v>
+        <v>0.1396542567821291</v>
       </c>
       <c r="AX120" t="n">
         <v>0.05004556052202935</v>
@@ -23860,7 +23860,7 @@
         <v>0.2893970648855606</v>
       </c>
       <c r="AY121" t="n">
-        <v>204.6879070361039</v>
+        <v>204.6878514792905</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -24052,7 +24052,7 @@
         <v>-0.3393141187982179</v>
       </c>
       <c r="AY122" t="n">
-        <v>1.038870016756236</v>
+        <v>1.038870266090581</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
@@ -24386,16 +24386,16 @@
         <v>54.17237213134766</v>
       </c>
       <c r="AG124" t="n">
-        <v>57.93355070114136</v>
+        <v>57.9335506439209</v>
       </c>
       <c r="AH124" t="n">
         <v>-0.09326475841251303</v>
       </c>
       <c r="AI124" t="n">
-        <v>-0.1521320834402604</v>
+        <v>-0.1521320826028286</v>
       </c>
       <c r="AJ124" t="n">
-        <v>-0.06492228638282993</v>
+        <v>-0.06492228545926193</v>
       </c>
       <c r="AK124" t="n">
         <v>86.98540496826172</v>
@@ -24428,19 +24428,19 @@
         <v>-0.3029129239970407</v>
       </c>
       <c r="AU124" t="n">
-        <v>-0.07366088145036653</v>
+        <v>-0.07366081480932607</v>
       </c>
       <c r="AV124" t="n">
-        <v>0.332431663341584</v>
+        <v>0.3324318012185326</v>
       </c>
       <c r="AW124" t="n">
-        <v>-0.4633719254511772</v>
+        <v>-0.4633719701790731</v>
       </c>
       <c r="AX124" t="n">
         <v>0.3315911445891528</v>
       </c>
       <c r="AY124" t="n">
-        <v>27.27232130819048</v>
+        <v>27.27231354867581</v>
       </c>
       <c r="AZ124" t="inlineStr"/>
       <c r="BA124" t="n">
@@ -24580,28 +24580,28 @@
         <v>259.5617163085938</v>
       </c>
       <c r="AG125" t="n">
-        <v>266.7499436950683</v>
+        <v>266.7499436187744</v>
       </c>
       <c r="AH125" t="n">
         <v>-0.06465405518179368</v>
       </c>
       <c r="AI125" t="n">
-        <v>-0.08985923139752328</v>
+        <v>-0.08985923113721128</v>
       </c>
       <c r="AJ125" t="n">
-        <v>-0.0269474373148948</v>
+        <v>-0.02694743703658919</v>
       </c>
       <c r="AK125" t="n">
         <v>376.0595397949219</v>
       </c>
       <c r="AL125" t="n">
-        <v>149.7264709472656</v>
+        <v>149.7264862060547</v>
       </c>
       <c r="AM125" t="n">
         <v>-0.35441074327833</v>
       </c>
       <c r="AN125" t="n">
-        <v>0.6214901563051276</v>
+        <v>0.621489991057302</v>
       </c>
       <c r="AO125" t="n">
         <v>43.53185962013291</v>
@@ -24625,16 +24625,16 @@
         <v>-0.1902585500368665</v>
       </c>
       <c r="AV125" t="n">
-        <v>0.4391194676385959</v>
+        <v>0.4391193374716182</v>
       </c>
       <c r="AW125" t="n">
-        <v>9.269382973625166</v>
+        <v>9.269382145099735</v>
       </c>
       <c r="AX125" t="n">
-        <v>0.3834511871974402</v>
+        <v>0.383451066905977</v>
       </c>
       <c r="AY125" t="n">
-        <v>23.4375420394319</v>
+        <v>23.43753734771133</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24934,7 +24934,7 @@
         <v>0.1291538355500905</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.199841725988581</v>
+        <v>1.199841454610769</v>
       </c>
       <c r="AX127" t="n">
         <v>0.1525704984001544</v>
@@ -25439,7 +25439,7 @@
         </is>
       </c>
       <c r="X130" t="n">
-        <v>14198307840</v>
+        <v>14196950016</v>
       </c>
       <c r="Y130" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>1.120573759078979</v>
       </c>
       <c r="AA130" t="n">
-        <v>15910251188.82935</v>
+        <v>15908729646.8855</v>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>0.2411087503478617</v>
       </c>
       <c r="AW130" t="n">
-        <v>1.611314255161262</v>
+        <v>1.611314545072431</v>
       </c>
       <c r="AX130" t="n">
         <v>0.2111422822246418</v>
@@ -25858,28 +25858,28 @@
         <v>431.7523028564453</v>
       </c>
       <c r="AG132" t="n">
-        <v>390.0729086303711</v>
+        <v>390.0729095458984</v>
       </c>
       <c r="AH132" t="n">
         <v>0.04993069998590416</v>
       </c>
       <c r="AI132" t="n">
-        <v>0.1621160750441797</v>
+        <v>0.1621160723166151</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.1068502664602355</v>
+        <v>0.1068502638623836</v>
       </c>
       <c r="AK132" t="n">
         <v>485.7999877929688</v>
       </c>
       <c r="AL132" t="n">
-        <v>272.1793212890625</v>
+        <v>272.1793518066406</v>
       </c>
       <c r="AM132" t="n">
         <v>-0.06687935580644999</v>
       </c>
       <c r="AN132" t="n">
-        <v>0.6654828714087544</v>
+        <v>0.665482684669741</v>
       </c>
       <c r="AO132" t="n">
         <v>54.71762682474677</v>
@@ -25903,16 +25903,16 @@
         <v>0.2327584053414549</v>
       </c>
       <c r="AV132" t="n">
-        <v>0.5276366457254273</v>
+        <v>0.5276364886186724</v>
       </c>
       <c r="AW132" t="n">
-        <v>3.504391831934789</v>
+        <v>3.504391490453378</v>
       </c>
       <c r="AX132" t="n">
         <v>0.4294744388922438</v>
       </c>
       <c r="AY132" t="n">
-        <v>144.5459439779916</v>
+        <v>144.5459885441435</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26050,16 +26050,16 @@
         <v>38431.6</v>
       </c>
       <c r="AG133" t="n">
-        <v>38383.41818359375</v>
+        <v>38383.41821289062</v>
       </c>
       <c r="AH133" t="n">
         <v>0.2635435422933212</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.265129639255423</v>
+        <v>0.2651296382897885</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.001255276853556531</v>
+        <v>0.001255276089329405</v>
       </c>
       <c r="AK133" t="n">
         <v>57263.48828125</v>
@@ -26104,7 +26104,7 @@
         <v>0.537435615332406</v>
       </c>
       <c r="AY133" t="n">
-        <v>378.8907226979833</v>
+        <v>378.8907453720175</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26246,16 +26246,16 @@
         <v>1738.611003417969</v>
       </c>
       <c r="AG134" t="n">
-        <v>1558.883284301758</v>
+        <v>1558.883286132813</v>
       </c>
       <c r="AH134" t="n">
         <v>0.02400132192900428</v>
       </c>
       <c r="AI134" t="n">
-        <v>0.1420611047335385</v>
+        <v>0.1420611033920807</v>
       </c>
       <c r="AJ134" t="n">
-        <v>0.1152926078084884</v>
+        <v>0.1152926064984725</v>
       </c>
       <c r="AK134" t="n">
         <v>1986.870361328125</v>
@@ -26291,10 +26291,10 @@
         <v>0.1908653815534138</v>
       </c>
       <c r="AV134" t="n">
-        <v>0.8276321794601569</v>
+        <v>0.8276320649471853</v>
       </c>
       <c r="AW134" t="n">
-        <v>1.61736704580939</v>
+        <v>1.617367515526579</v>
       </c>
       <c r="AX134" t="n">
         <v>0.5371397621400942</v>
@@ -26442,16 +26442,16 @@
         <v>382.8137036132812</v>
       </c>
       <c r="AG135" t="n">
-        <v>340.5118019866943</v>
+        <v>340.5118022918701</v>
       </c>
       <c r="AH135" t="n">
         <v>0.05189544907872201</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.182572792855844</v>
+        <v>0.1825727917959905</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.1242303537785745</v>
+        <v>0.1242303527710089</v>
       </c>
       <c r="AK135" t="n">
         <v>483.6542053222656</v>
@@ -26487,16 +26487,16 @@
         <v>0.08877097851291338</v>
       </c>
       <c r="AV135" t="n">
-        <v>1.778840992176505</v>
+        <v>1.778841284785354</v>
       </c>
       <c r="AW135" t="n">
-        <v>2.826166433663259</v>
+        <v>2.826165878925575</v>
       </c>
       <c r="AX135" t="n">
         <v>0.9423554726471604</v>
       </c>
       <c r="AY135" t="n">
-        <v>360.6884576512575</v>
+        <v>360.6883801962948</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26686,13 +26686,13 @@
         <v>1.474167318601404</v>
       </c>
       <c r="AW136" t="n">
-        <v>3.863761452921107</v>
+        <v>3.863761916997765</v>
       </c>
       <c r="AX136" t="n">
         <v>0.7607253198838395</v>
       </c>
       <c r="AY136" t="n">
-        <v>22.74760178768363</v>
+        <v>22.7475962560352</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26834,28 +26834,28 @@
         <v>489.7854382324219</v>
       </c>
       <c r="AG137" t="n">
-        <v>433.6493914794922</v>
+        <v>433.6493907165527</v>
       </c>
       <c r="AH137" t="n">
         <v>0.03520839780192042</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.1692164424570048</v>
+        <v>0.1692164445140616</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.1294503067591286</v>
+        <v>0.1294503087462229</v>
       </c>
       <c r="AK137" t="n">
         <v>722.2277221679688</v>
       </c>
       <c r="AL137" t="n">
-        <v>208.7951507568359</v>
+        <v>208.7951354980469</v>
       </c>
       <c r="AM137" t="n">
         <v>-0.2979638094515337</v>
       </c>
       <c r="AN137" t="n">
-        <v>1.428360988947425</v>
+        <v>1.428361166412518</v>
       </c>
       <c r="AO137" t="n">
         <v>68.63512556959589</v>
@@ -26882,13 +26882,13 @@
         <v>1.314273307208825</v>
       </c>
       <c r="AW137" t="n">
-        <v>3.220790807034779</v>
+        <v>3.220791343169735</v>
       </c>
       <c r="AX137" t="n">
-        <v>0.8925020765358962</v>
+        <v>0.8925018609655151</v>
       </c>
       <c r="AY137" t="n">
-        <v>7355.464255662493</v>
+        <v>7355.461869962475</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27074,13 +27074,13 @@
         <v>0.6216455809494728</v>
       </c>
       <c r="AW138" t="n">
-        <v>1.174462724804837</v>
+        <v>1.174462561500292</v>
       </c>
       <c r="AX138" t="n">
         <v>0.6017339160850379</v>
       </c>
       <c r="AY138" t="n">
-        <v>299.6216063346122</v>
+        <v>299.6216551048473</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27222,28 +27222,28 @@
         <v>187.9346356201172</v>
       </c>
       <c r="AG139" t="n">
-        <v>179.4206168746948</v>
+        <v>179.4206171417236</v>
       </c>
       <c r="AH139" t="n">
         <v>0.04062780486900452</v>
       </c>
       <c r="AI139" t="n">
-        <v>0.09000855492990789</v>
+        <v>0.09000855330766577</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0.04745284512854209</v>
+        <v>0.04745284356963486</v>
       </c>
       <c r="AK139" t="n">
         <v>301.3693542480469</v>
       </c>
       <c r="AL139" t="n">
-        <v>97.74769592285156</v>
+        <v>97.74768829345703</v>
       </c>
       <c r="AM139" t="n">
         <v>-0.3510620619930329</v>
       </c>
       <c r="AN139" t="n">
-        <v>1.000763347696446</v>
+        <v>1.000763503859862</v>
       </c>
       <c r="AO139" t="n">
         <v>64.55093011201768</v>
@@ -27264,19 +27264,19 @@
         <v>-0.1501017573508753</v>
       </c>
       <c r="AU139" t="n">
-        <v>0.1083399126429108</v>
+        <v>0.1083398167991767</v>
       </c>
       <c r="AV139" t="n">
         <v>0.866451122994232</v>
       </c>
       <c r="AW139" t="n">
-        <v>5.239222487121165</v>
+        <v>5.239222866775884</v>
       </c>
       <c r="AX139" t="n">
-        <v>0.5402141647838408</v>
+        <v>0.5402142573282258</v>
       </c>
       <c r="AY139" t="n">
-        <v>3225.978217158651</v>
+        <v>3225.978613874897</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
@@ -27664,7 +27664,7 @@
         <v>1.980094642649697</v>
       </c>
       <c r="AY141" t="n">
-        <v>2.79783769705816</v>
+        <v>2.797837397507009</v>
       </c>
       <c r="AZ141" t="inlineStr"/>
       <c r="BA141" t="n">
@@ -28380,16 +28380,16 @@
         <v>57971.164921875</v>
       </c>
       <c r="AG145" t="n">
-        <v>65200.65607421875</v>
+        <v>65200.65611328125</v>
       </c>
       <c r="AH145" t="n">
         <v>0.06018224893059743</v>
       </c>
       <c r="AI145" t="n">
-        <v>-0.05737144837868979</v>
+        <v>-0.05737144894342994</v>
       </c>
       <c r="AJ145" t="n">
-        <v>-0.1108806504050255</v>
+        <v>-0.1108806509377076</v>
       </c>
       <c r="AK145" t="n">
         <v>88201.875</v>
@@ -28428,13 +28428,13 @@
         <v>0.3313912472256266</v>
       </c>
       <c r="AW145" t="n">
-        <v>5.382969617043365</v>
+        <v>5.382970264414134</v>
       </c>
       <c r="AX145" t="n">
-        <v>0.2133898150975173</v>
+        <v>0.2133899086743201</v>
       </c>
       <c r="AY145" t="n">
-        <v>41.1877026460977</v>
+        <v>41.1876920411044</v>
       </c>
       <c r="AZ145" t="inlineStr"/>
       <c r="BA145" t="n">
@@ -28812,13 +28812,13 @@
         <v>0.3183806730704322</v>
       </c>
       <c r="AW147" t="n">
-        <v>0.7464527002437009</v>
+        <v>0.7464525705313672</v>
       </c>
       <c r="AX147" t="n">
         <v>0.3604768559463334</v>
       </c>
       <c r="AY147" t="n">
-        <v>-0.06262209388450657</v>
+        <v>-0.0626220191489788</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -28960,28 +28960,28 @@
         <v>111.9376318359375</v>
       </c>
       <c r="AG148" t="n">
-        <v>97.9467877960205</v>
+        <v>97.94678764343261</v>
       </c>
       <c r="AH148" t="n">
         <v>0.05764252332198638</v>
       </c>
       <c r="AI148" t="n">
-        <v>0.2087175297285098</v>
+        <v>0.2087175316115286</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0.1428412748874797</v>
+        <v>0.1428412766678722</v>
       </c>
       <c r="AK148" t="n">
         <v>129.0153350830078</v>
       </c>
       <c r="AL148" t="n">
-        <v>66.23379516601562</v>
+        <v>66.23378753662109</v>
       </c>
       <c r="AM148" t="n">
         <v>-0.08235715302001179</v>
       </c>
       <c r="AN148" t="n">
-        <v>0.7874560727330029</v>
+        <v>0.7874562786280315</v>
       </c>
       <c r="AO148" t="n">
         <v>65.32176555751289</v>
@@ -29005,16 +29005,16 @@
         <v>0.4486165685043806</v>
       </c>
       <c r="AV148" t="n">
-        <v>0.7235820164100908</v>
+        <v>0.7235818249673447</v>
       </c>
       <c r="AW148" t="n">
         <v>1.503489452267797</v>
       </c>
       <c r="AX148" t="n">
-        <v>0.5773275129943691</v>
+        <v>0.5773273526629015</v>
       </c>
       <c r="AY148" t="n">
-        <v>2398.315681114923</v>
+        <v>2398.315318830369</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29210,7 +29210,7 @@
         <v>3.627706310992529</v>
       </c>
       <c r="AY149" t="n">
-        <v>52.46084420204184</v>
+        <v>52.46084885286333</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29352,16 +29352,16 @@
         <v>58.08207725524903</v>
       </c>
       <c r="AG150" t="n">
-        <v>37.90038719177246</v>
+        <v>37.9003872013092</v>
       </c>
       <c r="AH150" t="n">
         <v>0.2647619120377429</v>
       </c>
       <c r="AI150" t="n">
-        <v>0.9382387497196756</v>
+        <v>0.9382387492319633</v>
       </c>
       <c r="AJ150" t="n">
-        <v>0.5324929785376356</v>
+        <v>0.5324929781520196</v>
       </c>
       <c r="AK150" t="n">
         <v>73.45999908447266</v>
@@ -29397,10 +29397,10 @@
         <v>1.977076611291809</v>
       </c>
       <c r="AV150" t="n">
-        <v>1.848937896887377</v>
+        <v>1.848937686148289</v>
       </c>
       <c r="AW150" t="n">
-        <v>4.665319087390198</v>
+        <v>4.665318254039409</v>
       </c>
       <c r="AX150" t="n">
         <v>2.075611635453794</v>
@@ -29596,13 +29596,13 @@
         <v>0.4736976513934015</v>
       </c>
       <c r="AW151" t="n">
-        <v>1.516915930385166</v>
+        <v>1.516915776894355</v>
       </c>
       <c r="AX151" t="n">
         <v>0.2983865847995095</v>
       </c>
       <c r="AY151" t="n">
-        <v>50.12513661925629</v>
+        <v>50.12514453558891</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29798,7 +29798,7 @@
         <v>0.1052376738652723</v>
       </c>
       <c r="AY152" t="n">
-        <v>678.7770091858398</v>
+        <v>678.7770644933033</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29990,7 +29990,7 @@
         <v>0.5345906942491485</v>
       </c>
       <c r="AY153" t="n">
-        <v>78.66459074292537</v>
+        <v>78.66457993499198</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30328,16 +30328,16 @@
         <v>316.6887915039063</v>
       </c>
       <c r="AG155" t="n">
-        <v>303.623575592041</v>
+        <v>303.6235753631592</v>
       </c>
       <c r="AH155" t="n">
         <v>-0.03286757537322249</v>
       </c>
       <c r="AI155" t="n">
-        <v>0.00874906759818006</v>
+        <v>0.008749068358609335</v>
       </c>
       <c r="AJ155" t="n">
-        <v>0.04303096650643545</v>
+        <v>0.04303096729270761</v>
       </c>
       <c r="AK155" t="n">
         <v>385.5466918945312</v>
@@ -30376,13 +30376,13 @@
         <v>0.4978905888187701</v>
       </c>
       <c r="AW155" t="n">
-        <v>4.261378634571059</v>
+        <v>4.261378979349884</v>
       </c>
       <c r="AX155" t="n">
         <v>0.2750599467980901</v>
       </c>
       <c r="AY155" t="n">
-        <v>413.5576740546604</v>
+        <v>413.5576071646427</v>
       </c>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="n">
@@ -30497,10 +30497,10 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>1.323311448097229</v>
+        <v>1.323381543159485</v>
       </c>
       <c r="AA156" t="n">
-        <v>150766513425.6855</v>
+        <v>150774499443.0059</v>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
@@ -30520,16 +30520,16 @@
         <v>1487.739360351562</v>
       </c>
       <c r="AG156" t="n">
-        <v>1330.920026855469</v>
+        <v>1330.92002746582</v>
       </c>
       <c r="AH156" t="n">
         <v>-0.06892296588527225</v>
       </c>
       <c r="AI156" t="n">
-        <v>0.04078376102330661</v>
+        <v>0.04078376054600974</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.1178277660053</v>
+        <v>0.1178277654926712</v>
       </c>
       <c r="AK156" t="n">
         <v>1570.339965820312</v>
@@ -30574,7 +30574,7 @@
         <v>0.1573214857943146</v>
       </c>
       <c r="AY156" t="n">
-        <v>10.12589334994733</v>
+        <v>10.12589744065835</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30766,7 +30766,7 @@
         <v>0.3325220302297336</v>
       </c>
       <c r="AY157" t="n">
-        <v>6.566030719205674</v>
+        <v>6.566031193926707</v>
       </c>
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="n">
@@ -30952,7 +30952,7 @@
         <v>0.1846302162236606</v>
       </c>
       <c r="AW158" t="n">
-        <v>4.473881147805213</v>
+        <v>4.473880094338098</v>
       </c>
       <c r="AX158" t="n">
         <v>0.2252583258760106</v>
@@ -32578,25 +32578,25 @@
         <v>371.3881274414063</v>
       </c>
       <c r="AG5" t="n">
-        <v>367.1055668640137</v>
+        <v>367.1055651855469</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.02651705363962698</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.01516064811175533</v>
+        <v>-0.01516064360890845</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.01166574676046506</v>
+        <v>0.01166575138596659</v>
       </c>
       <c r="AK5" t="n">
-        <v>479.9351196289062</v>
+        <v>479.9350891113281</v>
       </c>
       <c r="AL5" t="n">
         <v>292.4138793945312</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.246689825857148</v>
+        <v>-0.2466897779564993</v>
       </c>
       <c r="AN5" t="n">
         <v>0.236398249267519</v>
@@ -32626,13 +32626,13 @@
         <v>0.05567263030562253</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.298314893566349</v>
+        <v>7.298314166986252</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.04577584238236421</v>
+        <v>0.04577575006766188</v>
       </c>
       <c r="AY5" t="n">
-        <v>317.9512076232351</v>
+        <v>317.9513417953951</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32647,7 +32647,7 @@
         <v>0.125</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.005721980297795526</v>
+        <v>0.005721968758457735</v>
       </c>
     </row>
     <row r="6">
@@ -33034,7 +33034,7 @@
         <v>0.7280137304971483</v>
       </c>
       <c r="AY7" t="n">
-        <v>1691.968866986562</v>
+        <v>1691.96926883901</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33182,16 +33182,16 @@
         <v>236.4425393676758</v>
       </c>
       <c r="AG8" t="n">
-        <v>171.7013274002075</v>
+        <v>171.7013272094727</v>
       </c>
       <c r="AH8" t="n">
         <v>0.1642574957767122</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.603249100909188</v>
+        <v>0.6032491026901616</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3770571430503105</v>
+        <v>0.3770571445800182</v>
       </c>
       <c r="AK8" t="n">
         <v>316.2828369140625</v>
@@ -33224,19 +33224,19 @@
         <v>0.2378176261332783</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.097547970695078</v>
+        <v>1.097548214571192</v>
       </c>
       <c r="AV8" t="n">
         <v>2.04286251969071</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.870651642608925</v>
+        <v>3.870652957590498</v>
       </c>
       <c r="AX8" t="n">
         <v>2.084732048982278</v>
       </c>
       <c r="AY8" t="n">
-        <v>21.70041083802038</v>
+        <v>21.70041619369545</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33503,7 +33503,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9596610017616269</v>
+        <v>0.9596609902222891</v>
       </c>
     </row>
     <row r="5">
@@ -33657,10 +33657,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>12688.6637918855</v>
+        <v>12688.53624235407</v>
       </c>
       <c r="D2" t="n">
-        <v>1586.082973985688</v>
+        <v>1586.067030294259</v>
       </c>
       <c r="E2" t="n">
         <v>418.9209231359999</v>
@@ -33672,7 +33672,7 @@
         <v>77.5</v>
       </c>
       <c r="H2" t="n">
-        <v>91.80639097492129</v>
+        <v>91.80686148886574</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -33687,34 +33687,34 @@
         <v>0.5434205033757616</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4357350404536335</v>
+        <v>0.4357388356605283</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6518595066963487</v>
+        <v>0.6518595093842694</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4451680878322147</v>
+        <v>0.4451680477405309</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4358905138919054</v>
+        <v>0.4358945131023244</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.909094393007227</v>
+        <v>4.90909447529596</v>
       </c>
       <c r="R2" t="n">
         <v>2.118724463893807</v>
       </c>
       <c r="S2" t="n">
-        <v>5.934493783731389</v>
+        <v>5.934417631721769</v>
       </c>
       <c r="T2" t="n">
-        <v>1357.313363719507</v>
+        <v>1357.31301544568</v>
       </c>
       <c r="U2" t="n">
-        <v>357.1574727875723</v>
+        <v>357.1575656897336</v>
       </c>
       <c r="V2" t="n">
-        <v>4042.307197315206</v>
+        <v>4042.346602776659</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33732,10 +33732,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>256.7421483035775</v>
+        <v>256.3818696826742</v>
       </c>
       <c r="D3" t="n">
-        <v>36.67744975765392</v>
+        <v>36.62598138323916</v>
       </c>
       <c r="E3" t="n">
         <v>17.74748175251221</v>
@@ -33747,7 +33747,7 @@
         <v>85</v>
       </c>
       <c r="H3" t="n">
-        <v>87.55774727936769</v>
+        <v>87.56134153376473</v>
       </c>
       <c r="I3" t="n">
         <v>5</v>
@@ -33762,34 +33762,34 @@
         <v>2.227566313842295</v>
       </c>
       <c r="M3" t="n">
-        <v>2.908563571114045</v>
+        <v>2.909520537193559</v>
       </c>
       <c r="N3" t="n">
-        <v>4.386911989575352</v>
+        <v>4.386911978179104</v>
       </c>
       <c r="O3" t="n">
         <v>4.175965264894685</v>
       </c>
       <c r="P3" t="n">
-        <v>4.538360733095743</v>
+        <v>4.53886998375516</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.298442124647515</v>
+        <v>5.298441954520415</v>
       </c>
       <c r="R3" t="n">
         <v>5.725763513605029</v>
       </c>
       <c r="S3" t="n">
-        <v>6.874846744613725</v>
+        <v>6.874219700865534</v>
       </c>
       <c r="T3" t="n">
-        <v>45.69369131716802</v>
+        <v>45.6936872069328</v>
       </c>
       <c r="U3" t="n">
-        <v>32.31956245920308</v>
+        <v>32.31956834377364</v>
       </c>
       <c r="V3" t="n">
-        <v>70.95378992357142</v>
+        <v>71.00807126621355</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33807,10 +33807,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>1572.595085450137</v>
+        <v>1572.603071467457</v>
       </c>
       <c r="D4" t="n">
-        <v>98.28719284063354</v>
+        <v>98.28769196671605</v>
       </c>
       <c r="E4" t="n">
         <v>43.04099406395068</v>
@@ -33822,7 +33822,7 @@
         <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>86.54363548269359</v>
+        <v>86.54352607946957</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -33831,40 +33831,40 @@
         <v>0.5625</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6422482841792791</v>
+        <v>0.6422482741585624</v>
       </c>
       <c r="L4" t="n">
         <v>0.3154543075146216</v>
       </c>
       <c r="M4" t="n">
-        <v>1.267995908362882</v>
+        <v>1.26799022053096</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6707340287108657</v>
+        <v>0.6707340035745011</v>
       </c>
       <c r="O4" t="n">
         <v>0.433900187163894</v>
       </c>
       <c r="P4" t="n">
-        <v>1.147546219677434</v>
+        <v>1.147541423199564</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.262233409904959</v>
+        <v>7.26223329582732</v>
       </c>
       <c r="R4" t="n">
-        <v>4.569600117597705</v>
+        <v>4.569599174188753</v>
       </c>
       <c r="S4" t="n">
-        <v>6.46120118766175</v>
+        <v>6.461212109142311</v>
       </c>
       <c r="T4" t="n">
-        <v>247.9701224978213</v>
+        <v>247.9700995310888</v>
       </c>
       <c r="U4" t="n">
         <v>45.51036912528068</v>
       </c>
       <c r="V4" t="n">
-        <v>792.2278887858982</v>
+        <v>792.2238137662447</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33906,40 +33906,40 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6388458739972495</v>
+        <v>0.6388458720339697</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5402141647838408</v>
+        <v>0.5402142573282258</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5505282381965483</v>
+        <v>0.5505282247962778</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9882445834741287</v>
+        <v>0.9882445848734035</v>
       </c>
       <c r="O5" t="n">
         <v>0.866451122994232</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7962552683542921</v>
+        <v>0.7962551711557306</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.965115775266637</v>
+        <v>3.965115877940256</v>
       </c>
       <c r="R5" t="n">
         <v>3.051246902767851</v>
       </c>
       <c r="S5" t="n">
-        <v>3.835343834684181</v>
+        <v>3.835343812093973</v>
       </c>
       <c r="T5" t="n">
-        <v>859.6236721410395</v>
+        <v>859.6235410167393</v>
       </c>
       <c r="U5" t="n">
-        <v>41.1877026460977</v>
+        <v>41.1876920411044</v>
       </c>
       <c r="V5" t="n">
-        <v>1103.011696829991</v>
+        <v>1103.011525350887</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>444.35786681072</v>
+        <v>444.3563452687761</v>
       </c>
       <c r="D6" t="n">
-        <v>111.08946670268</v>
+        <v>111.089086317194</v>
       </c>
       <c r="E6" t="n">
         <v>97.525846016</v>
@@ -33972,7 +33972,7 @@
         <v>65</v>
       </c>
       <c r="H6" t="n">
-        <v>78.44859371180743</v>
+        <v>78.44886233141203</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -33987,7 +33987,7 @@
         <v>0.1446486565388666</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1311785994681222</v>
+        <v>0.1311783256606283</v>
       </c>
       <c r="N6" t="n">
         <v>0.1087571869718022</v>
@@ -33996,16 +33996,16 @@
         <v>0.09098015715788477</v>
       </c>
       <c r="P6" t="n">
-        <v>0.09070370870795162</v>
+        <v>0.09070319369881119</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.239387710834986</v>
+        <v>1.239387715468325</v>
       </c>
       <c r="R6" t="n">
-        <v>1.291545277262417</v>
+        <v>1.291545141573512</v>
       </c>
       <c r="S6" t="n">
-        <v>1.158695007642472</v>
+        <v>1.158693325646628</v>
       </c>
       <c r="T6" t="n">
         <v>87.75453976553968</v>
@@ -34014,7 +34014,7 @@
         <v>73.98743356872656</v>
       </c>
       <c r="V6" t="n">
-        <v>69.96662904968375</v>
+        <v>69.96658026377592</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34032,10 +34032,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>14312.02020489257</v>
+        <v>14312.00731015546</v>
       </c>
       <c r="D7" t="n">
-        <v>1192.668350407714</v>
+        <v>1192.667275846288</v>
       </c>
       <c r="E7" t="n">
         <v>352.857194496</v>
@@ -34047,7 +34047,7 @@
         <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>76.91545861767678</v>
+        <v>76.91552791645485</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
@@ -34056,40 +34056,40 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5180328352027043</v>
+        <v>0.518032821342527</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1129070408281754</v>
+        <v>0.112906986591078</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1092882713192362</v>
+        <v>0.1092886149321137</v>
       </c>
       <c r="N7" t="n">
-        <v>0.239073017477597</v>
+        <v>0.2390730073403431</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007886315798134536</v>
+        <v>0.007886254974611318</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1484575721700497</v>
+        <v>0.1484579891279952</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7890313804264452</v>
+        <v>0.7890314812226782</v>
       </c>
       <c r="R7" t="n">
         <v>0.6731516516965048</v>
       </c>
       <c r="S7" t="n">
-        <v>1.090835518275922</v>
+        <v>1.090836674028125</v>
       </c>
       <c r="T7" t="n">
-        <v>1279.284273866961</v>
+        <v>1279.283730399124</v>
       </c>
       <c r="U7" t="n">
-        <v>14.0160666129208</v>
+        <v>14.01606565698136</v>
       </c>
       <c r="V7" t="n">
-        <v>3196.337274136733</v>
+        <v>3196.337852247207</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34107,10 +34107,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>4608.388475649543</v>
+        <v>4610.477370113543</v>
       </c>
       <c r="D8" t="n">
-        <v>384.0323729707952</v>
+        <v>384.2064475094619</v>
       </c>
       <c r="E8" t="n">
         <v>177.3820510903965</v>
@@ -34122,7 +34122,7 @@
         <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>66.4967975405529</v>
+        <v>66.50518088875766</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
@@ -34131,40 +34131,40 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="K8" t="n">
-        <v>1.718489419346667</v>
+        <v>1.718489393013441</v>
       </c>
       <c r="L8" t="n">
         <v>1.369606248320999</v>
       </c>
       <c r="M8" t="n">
-        <v>1.728344548530806</v>
+        <v>1.728587246857193</v>
       </c>
       <c r="N8" t="n">
-        <v>4.084534790733723</v>
+        <v>4.084534779669172</v>
       </c>
       <c r="O8" t="n">
         <v>3.111426600925725</v>
       </c>
       <c r="P8" t="n">
-        <v>3.762151209787377</v>
+        <v>3.762419976194314</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.093350349102042</v>
+        <v>7.093350427606644</v>
       </c>
       <c r="R8" t="n">
-        <v>6.066562062695934</v>
+        <v>6.066561599606224</v>
       </c>
       <c r="S8" t="n">
-        <v>8.947761710518975</v>
+        <v>8.950232824667138</v>
       </c>
       <c r="T8" t="n">
-        <v>298.3299675584655</v>
+        <v>298.3299957489712</v>
       </c>
       <c r="U8" t="n">
-        <v>51.65272035602298</v>
+        <v>51.65273088329304</v>
       </c>
       <c r="V8" t="n">
-        <v>384.0401916524553</v>
+        <v>384.210900849509</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34206,40 +34206,40 @@
         <v>0.3478260869565217</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3938871463545999</v>
+        <v>0.3938871340757314</v>
       </c>
       <c r="L9" t="n">
         <v>0.3709434641445575</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4636118853880566</v>
+        <v>0.4636118919618354</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5772980298198781</v>
+        <v>0.5772980182233681</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4321420182890474</v>
+        <v>0.4321419532055586</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5287696111297505</v>
+        <v>0.5287695780051276</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.742811639648393</v>
+        <v>2.742811492510195</v>
       </c>
       <c r="R9" t="n">
         <v>1.545952800661642</v>
       </c>
       <c r="S9" t="n">
-        <v>2.608578997877117</v>
+        <v>2.608578885158335</v>
       </c>
       <c r="T9" t="n">
-        <v>181.7212465538389</v>
+        <v>181.7212847842678</v>
       </c>
       <c r="U9" t="n">
-        <v>25.35493167381119</v>
+        <v>25.35492544819357</v>
       </c>
       <c r="V9" t="n">
-        <v>359.6194880538084</v>
+        <v>359.6195784734591</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34299,22 +34299,22 @@
         <v>0.7320464286111926</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2980100824114393</v>
+        <v>0.2980098354995813</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2980100824114393</v>
+        <v>0.2980098354995813</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2980100824114393</v>
+        <v>0.2980098354995813</v>
       </c>
       <c r="T10" t="n">
-        <v>11.2662373288661</v>
+        <v>11.26623602997852</v>
       </c>
       <c r="U10" t="n">
-        <v>11.2662373288661</v>
+        <v>11.26623602997852</v>
       </c>
       <c r="V10" t="n">
-        <v>21.44015682813829</v>
+        <v>21.44015438516677</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34332,10 +34332,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>3453.250305413227</v>
+        <v>3453.2744542448</v>
       </c>
       <c r="D11" t="n">
-        <v>164.4404907339632</v>
+        <v>164.4416406783238</v>
       </c>
       <c r="E11" t="n">
         <v>63.29114624</v>
@@ -34347,7 +34347,7 @@
         <v>60</v>
       </c>
       <c r="H11" t="n">
-        <v>43.09790188932677</v>
+        <v>43.10270778780769</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
@@ -34356,40 +34356,40 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6442294015600026</v>
+        <v>0.6442294068572278</v>
       </c>
       <c r="L11" t="n">
         <v>0.5913977407734576</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4274258297346837</v>
+        <v>0.4274552929451261</v>
       </c>
       <c r="N11" t="n">
-        <v>1.011477977134216</v>
+        <v>1.011477972903968</v>
       </c>
       <c r="O11" t="n">
         <v>0.5180322165349693</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6133774657071943</v>
+        <v>0.6134551360837898</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.103169869215201</v>
+        <v>6.103169836145011</v>
       </c>
       <c r="R11" t="n">
-        <v>3.870651642608925</v>
+        <v>3.870652957590498</v>
       </c>
       <c r="S11" t="n">
-        <v>7.417975312378077</v>
+        <v>7.416314913531425</v>
       </c>
       <c r="T11" t="n">
-        <v>186.250759939141</v>
+        <v>186.2507925786198</v>
       </c>
       <c r="U11" t="n">
-        <v>24.43281610466342</v>
+        <v>24.43281323219166</v>
       </c>
       <c r="V11" t="n">
-        <v>293.9822431184095</v>
+        <v>294.0414157581691</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34440,31 +34440,31 @@
         <v>0.3882136187749722</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3639211254198099</v>
+        <v>0.3639211160127874</v>
       </c>
       <c r="O12" t="n">
         <v>0.2515527782661736</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2945205890343197</v>
+        <v>0.2945205329995539</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.703528093258579</v>
+        <v>1.703528039718755</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6240087060845113</v>
+        <v>0.6240084383853894</v>
       </c>
       <c r="S12" t="n">
-        <v>5.334539425074518</v>
+        <v>5.334539385531978</v>
       </c>
       <c r="T12" t="n">
-        <v>56.59972454321642</v>
+        <v>56.59973112259077</v>
       </c>
       <c r="U12" t="n">
         <v>8.921920992215439</v>
       </c>
       <c r="V12" t="n">
-        <v>208.7125324241939</v>
+        <v>208.7125372834772</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34482,10 +34482,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>2524.011426554323</v>
+        <v>2523.997226521501</v>
       </c>
       <c r="D13" t="n">
-        <v>252.4011426554324</v>
+        <v>252.3997226521502</v>
       </c>
       <c r="E13" t="n">
         <v>50.800557056</v>
@@ -34497,7 +34497,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="n">
-        <v>32.0961762356851</v>
+        <v>32.09579420811547</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
@@ -34506,40 +34506,40 @@
         <v>0.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06520252313805888</v>
+        <v>0.06520250994446543</v>
       </c>
       <c r="L13" t="n">
         <v>0.04977064179674595</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03864518997652221</v>
+        <v>0.03864490222002763</v>
       </c>
       <c r="N13" t="n">
-        <v>0.007126838786246203</v>
+        <v>0.007126864963197736</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04948158890119458</v>
+        <v>0.04948149488571918</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1612606883101321</v>
+        <v>0.1612578227024763</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5566983458613219</v>
+        <v>0.556698405936028</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4497927867529881</v>
+        <v>0.4497927747301121</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7637288270413204</v>
+        <v>0.7637177813304767</v>
       </c>
       <c r="T13" t="n">
-        <v>15.47472346704128</v>
+        <v>15.47471960317124</v>
       </c>
       <c r="U13" t="n">
-        <v>3.218458257179889</v>
+        <v>3.218457614326897</v>
       </c>
       <c r="V13" t="n">
-        <v>2.518076774440006</v>
+        <v>2.518070593097975</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34581,40 +34581,40 @@
         <v>0.05263157894736842</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0784335155602062</v>
+        <v>-0.07843350821021459</v>
       </c>
       <c r="L14" t="n">
         <v>-0.02300247670222821</v>
       </c>
       <c r="M14" t="n">
-        <v>0.101554335428869</v>
+        <v>0.1015543447748061</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1012771512526147</v>
+        <v>-0.1012771457864465</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.07215569423091606</v>
+        <v>-0.07215561558976602</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1150948525301169</v>
+        <v>0.1150948511060086</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.992604711527782</v>
+        <v>1.992604610862468</v>
       </c>
       <c r="R14" t="n">
         <v>1.568167711715526</v>
       </c>
       <c r="S14" t="n">
-        <v>2.031031829997429</v>
+        <v>2.031031687711696</v>
       </c>
       <c r="T14" t="n">
-        <v>70.33374678058192</v>
+        <v>70.33372076410942</v>
       </c>
       <c r="U14" t="n">
-        <v>13.26615825806048</v>
+        <v>13.2661558541109</v>
       </c>
       <c r="V14" t="n">
-        <v>95.40049123426914</v>
+        <v>95.40045121363134</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -828,28 +828,28 @@
         <v>654.9555773925781</v>
       </c>
       <c r="AG2" t="n">
-        <v>631.0666632080079</v>
+        <v>631.066664428711</v>
       </c>
       <c r="AH2" t="n">
         <v>0.08302004223512971</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1240175696874661</v>
+        <v>0.124017567513224</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.03785481879700581</v>
+        <v>0.03785481678943259</v>
       </c>
       <c r="AK2" t="n">
         <v>777.5900268554688</v>
       </c>
       <c r="AL2" t="n">
-        <v>524.8190307617188</v>
+        <v>524.8189697265625</v>
       </c>
       <c r="AM2" t="n">
         <v>-0.08778406024787211</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.351570685347151</v>
+        <v>0.3515708425314998</v>
       </c>
       <c r="AO2" t="n">
         <v>48.18972643623</v>
@@ -876,13 +876,13 @@
         <v>-0.0004689039370471271</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.200410747676646</v>
+        <v>1.200410955986245</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.09339667854428568</v>
+        <v>0.09339657567465465</v>
       </c>
       <c r="AY2" t="n">
-        <v>17.73198686893485</v>
+        <v>17.73198498190233</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1069,7 +1069,7 @@
         <v>0.2705861158575922</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.04259663238817746</v>
+        <v>0.0425965696855175</v>
       </c>
       <c r="AW3" t="n">
         <v>0.8735352797840539</v>
@@ -1078,7 +1078,7 @@
         <v>0.1257376814982207</v>
       </c>
       <c r="AY3" t="n">
-        <v>8963.784350184667</v>
+        <v>8963.784916089149</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1274,7 +1274,7 @@
         <v>1.978109413860968</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.708322155158061</v>
+        <v>3.708323662024998</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
@@ -1612,28 +1612,28 @@
         <v>344.4919067382813</v>
       </c>
       <c r="AG6" t="n">
-        <v>340.55658203125</v>
+        <v>340.5565817260742</v>
       </c>
       <c r="AH6" t="n">
         <v>-0.01132656623876804</v>
       </c>
       <c r="AI6" t="n">
-        <v>9.811675475868142e-05</v>
+        <v>9.81176509555759e-05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01155556789875867</v>
+        <v>0.01155556880522246</v>
       </c>
       <c r="AK6" t="n">
         <v>402.1211853027344</v>
       </c>
       <c r="AL6" t="n">
-        <v>249.8103485107422</v>
+        <v>249.8103332519531</v>
       </c>
       <c r="AM6" t="n">
         <v>-0.1530165313685733</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.3633942643622901</v>
+        <v>0.3633943476404524</v>
       </c>
       <c r="AO6" t="n">
         <v>47.70894443577671</v>
@@ -1660,7 +1660,7 @@
         <v>0.3579724347652142</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.475134995835023</v>
+        <v>1.47513554476387</v>
       </c>
       <c r="AX6" t="n">
         <v>0.08282582784059245</v>
@@ -2190,16 +2190,16 @@
         <v>144.6427416992188</v>
       </c>
       <c r="AG9" t="n">
-        <v>159.031707611084</v>
+        <v>159.0317079925537</v>
       </c>
       <c r="AH9" t="n">
         <v>-0.1134709269118365</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.1936828343620084</v>
+        <v>-0.1936828362961233</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.09047859780927336</v>
+        <v>-0.09047859999094454</v>
       </c>
       <c r="AK9" t="n">
         <v>308.867431640625</v>
@@ -2238,13 +2238,13 @@
         <v>-0.5848380807053238</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.4398275636529798</v>
+        <v>0.4398270702733043</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.3360294793875311</v>
+        <v>-0.3360293744675747</v>
       </c>
       <c r="AY9" t="n">
-        <v>2560.910035267547</v>
+        <v>2560.910607298586</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
@@ -2822,7 +2822,7 @@
         <v>-0.3215606087726487</v>
       </c>
       <c r="AY12" t="n">
-        <v>593.0642767264362</v>
+        <v>593.0642263788657</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
@@ -3008,13 +3008,13 @@
         <v>-0.3330179673717022</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.2928046723374426</v>
+        <v>-0.2928047422788285</v>
       </c>
       <c r="AX13" t="n">
         <v>-0.2929750784406844</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.2348989544872082</v>
+        <v>0.2348988478550196</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
@@ -3531,7 +3531,7 @@
         <v>43628</v>
       </c>
       <c r="AD16" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AE16" t="n">
         <v>227.3899993896484</v>
@@ -4758,13 +4758,13 @@
         <v>-0.1369535703572059</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.064281000609032</v>
+        <v>1.064280860560779</v>
       </c>
       <c r="AX22" t="n">
         <v>-0.1874136860582474</v>
       </c>
       <c r="AY22" t="n">
-        <v>160.8322186096649</v>
+        <v>160.8322051606628</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
@@ -4906,16 +4906,16 @@
         <v>365.3192327880859</v>
       </c>
       <c r="AG23" t="n">
-        <v>367.0558517456055</v>
+        <v>367.0558497619629</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.1001021285109809</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.1043597358915123</v>
+        <v>-0.1043597310512948</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.004731211746824782</v>
+        <v>-0.004731206368194907</v>
       </c>
       <c r="AK23" t="n">
         <v>479.9351196289062</v>
@@ -4951,16 +4951,16 @@
         <v>-0.1745616950860105</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.064818993850148</v>
+        <v>-0.06481891266516648</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.294499853948911</v>
+        <v>6.294499236522334</v>
       </c>
       <c r="AX23" t="n">
-        <v>-0.04907119528243098</v>
+        <v>-0.0490711113402309</v>
       </c>
       <c r="AY23" t="n">
-        <v>289.0239285749967</v>
+        <v>289.023959075854</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5102,16 +5102,16 @@
         <v>325.6940002441406</v>
       </c>
       <c r="AG24" t="n">
-        <v>292.1421198272705</v>
+        <v>292.1421199798584</v>
       </c>
       <c r="AH24" t="n">
         <v>0.05454810711164493</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1756606396165996</v>
+        <v>0.1756606390025437</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1148478022844077</v>
+        <v>0.1148478017021148</v>
       </c>
       <c r="AK24" t="n">
         <v>343.4599914550781</v>
@@ -5150,13 +5150,13 @@
         <v>0.393124847513783</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.465742503194325</v>
+        <v>1.465741962976068</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2707827716835942</v>
       </c>
       <c r="AY24" t="n">
-        <v>3499.320788593878</v>
+        <v>3499.322117516903</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5490,16 +5490,16 @@
         <v>222.9631530761719</v>
       </c>
       <c r="AG26" t="n">
-        <v>202.6568659973144</v>
+        <v>202.6568658447266</v>
       </c>
       <c r="AH26" t="n">
         <v>-0.03961707605714415</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.05661362041220008</v>
+        <v>0.0566136212077637</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.1002003409996803</v>
+        <v>0.1002003418280621</v>
       </c>
       <c r="AK26" t="n">
         <v>239.2400054931641</v>
@@ -5538,13 +5538,13 @@
         <v>0.1805897419805222</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.392519253310189</v>
+        <v>9.392518291267837</v>
       </c>
       <c r="AX26" t="n">
         <v>0.136516051200636</v>
       </c>
       <c r="AY26" t="n">
-        <v>5706.533009311169</v>
+        <v>5706.532442576977</v>
       </c>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
@@ -5936,7 +5936,7 @@
         <v>1.281614932379214</v>
       </c>
       <c r="AY28" t="n">
-        <v>494.0421192884639</v>
+        <v>494.04199735933</v>
       </c>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
@@ -6078,28 +6078,28 @@
         <v>174.6682028198242</v>
       </c>
       <c r="AG29" t="n">
-        <v>168.083913154602</v>
+        <v>168.0839130401611</v>
       </c>
       <c r="AH29" t="n">
         <v>-0.01464606704696858</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.02395284224520866</v>
+        <v>0.02395284294237299</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.03917263432084672</v>
+        <v>0.03917263502837343</v>
       </c>
       <c r="AK29" t="n">
-        <v>248.7425079345703</v>
+        <v>248.7424926757812</v>
       </c>
       <c r="AL29" t="n">
-        <v>122.9443054199219</v>
+        <v>122.9443130493164</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0.3080796602098115</v>
+        <v>-0.3080796177648459</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.3999021753996821</v>
+        <v>0.3999020885277826</v>
       </c>
       <c r="AO29" t="n">
         <v>29.68545047087238</v>
@@ -6120,13 +6120,13 @@
         <v>-0.002612621670258108</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.2629860165018783</v>
+        <v>0.2629861579219639</v>
       </c>
       <c r="AV29" t="n">
         <v>0.07078359890113539</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.535758767411892</v>
+        <v>0.5357585583090618</v>
       </c>
       <c r="AX29" t="n">
         <v>0.01052724281544615</v>
@@ -6704,13 +6704,13 @@
         <v>8.450112358513637</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.377455321758561</v>
+        <v>5.377455942363119</v>
       </c>
       <c r="AX32" t="n">
         <v>5.421230192323369</v>
       </c>
       <c r="AY32" t="n">
-        <v>42.76009205270829</v>
+        <v>42.76009935764747</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6848,16 +6848,16 @@
         <v>10344.65610351562</v>
       </c>
       <c r="AG33" t="n">
-        <v>7454.35189086914</v>
+        <v>7454.351901855469</v>
       </c>
       <c r="AH33" t="n">
         <v>-0.05613102047136098</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.309838889140712</v>
+        <v>0.3098388872102529</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.387733803684104</v>
+        <v>0.3877338016388423</v>
       </c>
       <c r="AK33" t="n">
         <v>13194.7333984375</v>
@@ -6896,10 +6896,10 @@
         <v>3.280059203070169</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.554882177588736</v>
+        <v>6.554882891160601</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.736774236372788</v>
+        <v>1.736774423652294</v>
       </c>
       <c r="AY33" t="n">
         <v>27.25290808338079</v>
@@ -7094,7 +7094,7 @@
         <v>3.987360587528289</v>
       </c>
       <c r="AY34" t="n">
-        <v>148.7359705534641</v>
+        <v>148.7359999785146</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7284,13 +7284,13 @@
         <v>2.173899330544145</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.346641706525026</v>
+        <v>6.346641055465089</v>
       </c>
       <c r="AX35" t="n">
         <v>1.368188165174725</v>
       </c>
       <c r="AY35" t="n">
-        <v>37.48977646559303</v>
+        <v>37.48978986839135</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA36" t="n">
-        <v>7609253371.148987</v>
+        <v>7608397389.129639</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>0.2123754050992641</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.72799107903737</v>
+        <v>1.727991279620156</v>
       </c>
       <c r="AX37" t="n">
         <v>-0.009806610326421161</v>
@@ -7816,16 +7816,16 @@
         <v>50.87844543457031</v>
       </c>
       <c r="AG38" t="n">
-        <v>57.54996694564819</v>
+        <v>57.54996711730957</v>
       </c>
       <c r="AH38" t="n">
         <v>-0.1780409299532403</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.2733271292002617</v>
+        <v>-0.2733271313677984</v>
       </c>
       <c r="AJ38" t="n">
-        <v>-0.1159257227268029</v>
+        <v>-0.1159257253638402</v>
       </c>
       <c r="AK38" t="n">
         <v>93.37815856933594</v>
@@ -7858,19 +7858,19 @@
         <v>-0.3721421167879616</v>
       </c>
       <c r="AU38" t="n">
-        <v>-0.3959662622827617</v>
+        <v>-0.3959663288450729</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.3368729266959312</v>
+        <v>0.3368730082088305</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.7830685885817115</v>
+        <v>0.7830687335864488</v>
       </c>
       <c r="AX38" t="n">
-        <v>-0.0208649578671003</v>
+        <v>-0.02086487041680529</v>
       </c>
       <c r="AY38" t="n">
-        <v>2.387427751101109</v>
+        <v>2.387428274443852</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8056,13 +8056,13 @@
         <v>0.2939881902038965</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.050509231399661</v>
+        <v>1.050509055023256</v>
       </c>
       <c r="AX39" t="n">
         <v>0.0958780178143066</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.510766106016832</v>
+        <v>3.510766532780785</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8248,13 +8248,13 @@
         <v>0.1788312759678969</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.8298637862553548</v>
+        <v>0.8298642254464501</v>
       </c>
       <c r="AX40" t="n">
         <v>0.1300519559597177</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.9269738599717712</v>
+        <v>0.9269740223195404</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8377,7 +8377,7 @@
         <v>46185</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AE41" t="n">
         <v>146.0299987792969</v>
@@ -8624,7 +8624,7 @@
         <v>0.1583070256821131</v>
       </c>
       <c r="AY42" t="n">
-        <v>33.75677283908038</v>
+        <v>33.75676629211176</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8766,28 +8766,28 @@
         <v>1037.758392333984</v>
       </c>
       <c r="AG43" t="n">
-        <v>993.6573684692382</v>
+        <v>993.6573672485351</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.04989447664092739</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.007726393668589737</v>
+        <v>-0.007726392449586506</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.04438252587276148</v>
+        <v>0.04438252715578028</v>
       </c>
       <c r="AK43" t="n">
         <v>1110.633178710938</v>
       </c>
       <c r="AL43" t="n">
-        <v>715.1827392578125</v>
+        <v>715.1826171875</v>
       </c>
       <c r="AM43" t="n">
         <v>-0.1122361555836707</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.3786406275575944</v>
+        <v>0.3786408628696505</v>
       </c>
       <c r="AO43" t="n">
         <v>41.81187806027509</v>
@@ -8811,10 +8811,10 @@
         <v>-0.098172059410358</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.2390702985779485</v>
+        <v>0.2390702035385184</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.4522843346935326</v>
+        <v>0.4522845958166628</v>
       </c>
       <c r="AX43" t="n">
         <v>0.3100434145655118</v>
@@ -9010,13 +9010,13 @@
         <v>0.09930626326572201</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.18358106782189</v>
+        <v>2.183580724184253</v>
       </c>
       <c r="AX44" t="n">
         <v>0.3826298008164757</v>
       </c>
       <c r="AY44" t="n">
-        <v>97.40942726228519</v>
+        <v>97.40940674016247</v>
       </c>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
@@ -9584,13 +9584,13 @@
         <v>-0.07368171394417944</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.1249708625048411</v>
+        <v>0.1249707896225045</v>
       </c>
       <c r="AX47" t="n">
         <v>-0.01992212620981448</v>
       </c>
       <c r="AY47" t="n">
-        <v>2.841160213050517</v>
+        <v>2.841161062748736</v>
       </c>
       <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="n">
@@ -9924,16 +9924,16 @@
         <v>14.8217999458313</v>
       </c>
       <c r="AG49" t="n">
-        <v>14.5226343536377</v>
+        <v>14.52263432502747</v>
       </c>
       <c r="AH49" t="n">
         <v>0.008649412615361562</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.02942754359992494</v>
+        <v>0.02942754562794248</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.02059995348699717</v>
+        <v>0.02059995549762395</v>
       </c>
       <c r="AK49" t="n">
         <v>16.86722755432129</v>
@@ -9972,13 +9972,13 @@
         <v>0.05898942990642908</v>
       </c>
       <c r="AW49" t="n">
-        <v>-0.237745252018178</v>
+        <v>-0.2377451778889949</v>
       </c>
       <c r="AX49" t="n">
         <v>0.04569546283942127</v>
       </c>
       <c r="AY49" t="n">
-        <v>6.581468984151964</v>
+        <v>6.581470359133832</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10120,16 +10120,16 @@
         <v>64.22406845092773</v>
       </c>
       <c r="AG50" t="n">
-        <v>63.51957078933716</v>
+        <v>63.5195707321167</v>
       </c>
       <c r="AH50" t="n">
         <v>-0.01033984756266437</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.0006365059374842108</v>
+        <v>0.0006365068388896056</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01109103309162851</v>
+        <v>0.01109103400245148</v>
       </c>
       <c r="AK50" t="n">
         <v>70.97299957275391</v>
@@ -10165,16 +10165,16 @@
         <v>0.04218876320298781</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.09330061849186877</v>
+        <v>0.09330069023088172</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.1037246054296881</v>
+        <v>0.1037243129757288</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.1062801229917729</v>
+        <v>0.1062800495393088</v>
       </c>
       <c r="AY50" t="n">
-        <v>172.7321097987848</v>
+        <v>172.7320814942303</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10506,25 +10506,25 @@
         <v>87.72344848632812</v>
       </c>
       <c r="AG52" t="n">
-        <v>91.13071182250977</v>
+        <v>91.13071212768554</v>
       </c>
       <c r="AH52" t="n">
         <v>0.03940282647901561</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.0005408547972500788</v>
+        <v>0.000540851446669155</v>
       </c>
       <c r="AJ52" t="n">
-        <v>-0.037388749281557</v>
+        <v>-0.03738875250512053</v>
       </c>
       <c r="AK52" t="n">
-        <v>97.49111175537109</v>
+        <v>97.49111938476562</v>
       </c>
       <c r="AL52" t="n">
         <v>82.06203460693359</v>
       </c>
       <c r="AM52" t="n">
-        <v>-0.06473524956850862</v>
+        <v>-0.06473532275982918</v>
       </c>
       <c r="AN52" t="n">
         <v>0.1111106462557996</v>
@@ -10554,13 +10554,13 @@
         <v>-0.0430687502442143</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.7678122003004104</v>
+        <v>0.767812461795057</v>
       </c>
       <c r="AX52" t="n">
         <v>0.07160101669502028</v>
       </c>
       <c r="AY52" t="n">
-        <v>337.9966739581494</v>
+        <v>337.9965612740848</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10714,13 +10714,13 @@
         <v>-0.02796338890339323</v>
       </c>
       <c r="AK53" t="n">
-        <v>399.1983947753906</v>
+        <v>399.1984252929688</v>
       </c>
       <c r="AL53" t="n">
         <v>236.1370086669922</v>
       </c>
       <c r="AM53" t="n">
-        <v>-0.3202127095980081</v>
+        <v>-0.3202127615658026</v>
       </c>
       <c r="AN53" t="n">
         <v>0.1492056948171219</v>
@@ -10754,7 +10754,7 @@
         <v>-0.2557701288723212</v>
       </c>
       <c r="AY53" t="n">
-        <v>5.712097974076841</v>
+        <v>5.712096074154029</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10896,16 +10896,16 @@
         <v>963.8384033203125</v>
       </c>
       <c r="AG54" t="n">
-        <v>933.2996447753907</v>
+        <v>933.2996432495117</v>
       </c>
       <c r="AH54" t="n">
         <v>-0.04423811187269244</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.01296435998459133</v>
+        <v>-0.01296435837085785</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.03272127951175996</v>
+        <v>0.03272128120018625</v>
       </c>
       <c r="AK54" t="n">
         <v>1174.859985351562</v>
@@ -10941,14 +10941,14 @@
         <v>-0.06918872508267748</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.5337071909534397</v>
+        <v>0.5337073468049722</v>
       </c>
       <c r="AW54" t="inlineStr"/>
       <c r="AX54" t="n">
         <v>0.3581151091863848</v>
       </c>
       <c r="AY54" t="n">
-        <v>6.048326500419595</v>
+        <v>6.048327323302827</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11090,16 +11090,16 @@
         <v>118.9444129943848</v>
       </c>
       <c r="AG55" t="n">
-        <v>122.5386078262329</v>
+        <v>122.538607711792</v>
       </c>
       <c r="AH55" t="n">
         <v>0.02123334894626439</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.008720570802021266</v>
+        <v>-0.008720569876248363</v>
       </c>
       <c r="AJ55" t="n">
-        <v>-0.02933112180403519</v>
+        <v>-0.02933112089751089</v>
       </c>
       <c r="AK55" t="n">
         <v>131.1634063720703</v>
@@ -11132,19 +11132,19 @@
         <v>-0.02678117180165263</v>
       </c>
       <c r="AU55" t="n">
-        <v>-0.03334214303568739</v>
+        <v>-0.03334208434534613</v>
       </c>
       <c r="AV55" t="n">
-        <v>-0.01308472066531441</v>
+        <v>-0.013084659489352</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.4770490924227893</v>
+        <v>0.4770488183658437</v>
       </c>
       <c r="AX55" t="n">
         <v>0.0613891542327627</v>
       </c>
       <c r="AY55" t="n">
-        <v>164.5158886618854</v>
+        <v>164.5158617762457</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11286,28 +11286,28 @@
         <v>104.3082925415039</v>
       </c>
       <c r="AG56" t="n">
-        <v>105.9947054290771</v>
+        <v>105.9947050857544</v>
       </c>
       <c r="AH56" t="n">
         <v>0.007685947582054986</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.00834668878171041</v>
+        <v>-0.008346685569690093</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-0.01591035024576437</v>
+        <v>-0.01591034705824323</v>
       </c>
       <c r="AK56" t="n">
         <v>116.6635665893555</v>
       </c>
       <c r="AL56" t="n">
-        <v>89.56781005859375</v>
+        <v>89.56781768798828</v>
       </c>
       <c r="AM56" t="n">
         <v>-0.09903319705346703</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.1735242889336066</v>
+        <v>0.1735241889727051</v>
       </c>
       <c r="AO56" t="n">
         <v>79.77907836747976</v>
@@ -11331,16 +11331,16 @@
         <v>-0.06462674358415887</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.12193133739934</v>
+        <v>0.1219314287640811</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.438612302240785</v>
+        <v>1.43861187059105</v>
       </c>
       <c r="AX56" t="n">
         <v>0.1401414598617345</v>
       </c>
       <c r="AY56" t="n">
-        <v>195.7332361485136</v>
+        <v>195.733455627033</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11478,16 +11478,16 @@
         <v>150.5145449829102</v>
       </c>
       <c r="AG57" t="n">
-        <v>187.5101401519775</v>
+        <v>187.5101402282715</v>
       </c>
       <c r="AH57" t="n">
         <v>-0.08972256121564581</v>
       </c>
       <c r="AI57" t="n">
-        <v>-0.2693195450881274</v>
+        <v>-0.269319545385426</v>
       </c>
       <c r="AJ57" t="n">
-        <v>-0.1972991708026154</v>
+        <v>-0.1972991711292176</v>
       </c>
       <c r="AK57" t="n">
         <v>237.7264404296875</v>
@@ -11526,13 +11526,13 @@
         <v>-0.3407245043697229</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.490926508739831</v>
+        <v>1.490926335985228</v>
       </c>
       <c r="AX57" t="n">
         <v>-0.2433360240613274</v>
       </c>
       <c r="AY57" t="n">
-        <v>8.684407872859808</v>
+        <v>8.684409831322599</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11647,10 +11647,10 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA58" t="n">
-        <v>129129235884.2529</v>
+        <v>129114709846.1914</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44103</v>
       </c>
       <c r="AD58" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AE58" t="n">
         <v>134.9799957275391</v>
@@ -11724,7 +11724,7 @@
         <v>0.1038729866767911</v>
       </c>
       <c r="AY58" t="n">
-        <v>5.193404001763283</v>
+        <v>5.193403459738112</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -12058,16 +12058,16 @@
         <v>80.96150817871094</v>
       </c>
       <c r="AG60" t="n">
-        <v>86.28200622558593</v>
+        <v>86.2820064163208</v>
       </c>
       <c r="AH60" t="n">
         <v>-0.014346386981691</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.07512578180995</v>
+        <v>-0.07512578385447555</v>
       </c>
       <c r="AJ60" t="n">
-        <v>-0.06166405116919105</v>
+        <v>-0.06166405324347501</v>
       </c>
       <c r="AK60" t="n">
         <v>96.44304656982422</v>
@@ -12100,19 +12100,19 @@
         <v>-0.08563528377133245</v>
       </c>
       <c r="AU60" t="n">
-        <v>-0.1197806660772476</v>
+        <v>-0.119780740151783</v>
       </c>
       <c r="AV60" t="n">
-        <v>-0.03476349571789217</v>
+        <v>-0.03476358479264008</v>
       </c>
       <c r="AW60" t="n">
-        <v>0.1727747035644032</v>
+        <v>0.172774440570159</v>
       </c>
       <c r="AX60" t="n">
-        <v>0.007552443887922644</v>
+        <v>0.007552346831909862</v>
       </c>
       <c r="AY60" t="n">
-        <v>230.3647554875866</v>
+        <v>230.3647155049412</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12490,13 +12490,13 @@
         <v>-0.1037119950636584</v>
       </c>
       <c r="AW62" t="n">
-        <v>2.833297143885746</v>
+        <v>2.833297487689757</v>
       </c>
       <c r="AX62" t="n">
         <v>-0.1728896239612536</v>
       </c>
       <c r="AY62" t="n">
-        <v>12.62415526325185</v>
+        <v>12.62416177768399</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -12638,25 +12638,25 @@
         <v>42.86581344604492</v>
       </c>
       <c r="AG63" t="n">
-        <v>44.88548171997071</v>
+        <v>44.88548175811768</v>
       </c>
       <c r="AH63" t="n">
         <v>0.0147946930892453</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.0308670346597677</v>
+        <v>-0.03086703548340797</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.04499602536352365</v>
+        <v>-0.04499602617515608</v>
       </c>
       <c r="AK63" t="n">
-        <v>49.35155487060547</v>
+        <v>49.3515510559082</v>
       </c>
       <c r="AL63" t="n">
         <v>40.20000076293945</v>
       </c>
       <c r="AM63" t="n">
-        <v>-0.1185688046900979</v>
+        <v>-0.118568736558639</v>
       </c>
       <c r="AN63" t="n">
         <v>0.08208953170226874</v>
@@ -12686,13 +12686,13 @@
         <v>-0.04778079106933752</v>
       </c>
       <c r="AW63" t="n">
-        <v>0.5315901797028235</v>
+        <v>0.5315897682824007</v>
       </c>
       <c r="AX63" t="n">
         <v>0.01791290641372045</v>
       </c>
       <c r="AY63" t="n">
-        <v>178.09769067288</v>
+        <v>178.0976137582985</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12834,25 +12834,25 @@
         <v>109.2442004394531</v>
       </c>
       <c r="AG64" t="n">
-        <v>137.5552702331543</v>
+        <v>137.5552705383301</v>
       </c>
       <c r="AH64" t="n">
         <v>-0.05029283401179907</v>
       </c>
       <c r="AI64" t="n">
-        <v>-0.2457577247011679</v>
+        <v>-0.2457577263745061</v>
       </c>
       <c r="AJ64" t="n">
-        <v>-0.2058159585286284</v>
+        <v>-0.2058159602905802</v>
       </c>
       <c r="AK64" t="n">
-        <v>182.8191833496094</v>
+        <v>182.8191986083984</v>
       </c>
       <c r="AL64" t="n">
         <v>95.23000335693359</v>
       </c>
       <c r="AM64" t="n">
-        <v>-0.4324993794464311</v>
+        <v>-0.432499426812202</v>
       </c>
       <c r="AN64" t="n">
         <v>0.0894675663418012</v>
@@ -12879,16 +12879,16 @@
         <v>-0.3355570813122106</v>
       </c>
       <c r="AV64" t="n">
-        <v>-0.3819097966973605</v>
+        <v>-0.3819097405103761</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.894227420214229</v>
+        <v>1.894227112223791</v>
       </c>
       <c r="AX64" t="n">
         <v>-0.369504318838295</v>
       </c>
       <c r="AY64" t="n">
-        <v>13.53328954233396</v>
+        <v>13.5332934253568</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13412,16 +13412,16 @@
         <v>144.7395361328125</v>
       </c>
       <c r="AG67" t="n">
-        <v>154.1667574310303</v>
+        <v>154.1667576599121</v>
       </c>
       <c r="AH67" t="n">
         <v>0.05030047998059017</v>
       </c>
       <c r="AI67" t="n">
-        <v>-0.01392487715472468</v>
+        <v>-0.01392487861868941</v>
       </c>
       <c r="AJ67" t="n">
-        <v>-0.06114950755473492</v>
+        <v>-0.06114950894858817</v>
       </c>
       <c r="AK67" t="n">
         <v>209.184814453125</v>
@@ -13460,7 +13460,7 @@
         <v>-0.2732741873740256</v>
       </c>
       <c r="AW67" t="n">
-        <v>8.428029860336636</v>
+        <v>8.428034321328566</v>
       </c>
       <c r="AX67" t="n">
         <v>-0.0758928939967719</v>
@@ -13608,16 +13608,16 @@
         <v>201.6523120117187</v>
       </c>
       <c r="AG68" t="n">
-        <v>143.9000179672241</v>
+        <v>143.9000177764892</v>
       </c>
       <c r="AH68" t="n">
         <v>0.01065046573785011</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.4162611369386833</v>
+        <v>0.4162611388158923</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.4013362531869089</v>
+        <v>0.4013362550443356</v>
       </c>
       <c r="AK68" t="n">
         <v>239.1799926757812</v>
@@ -13656,13 +13656,13 @@
         <v>0.7331183885970205</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.48233915611445</v>
+        <v>1.482338925435438</v>
       </c>
       <c r="AX68" t="n">
         <v>0.9341553154477342</v>
       </c>
       <c r="AY68" t="n">
-        <v>216.8272785738517</v>
+        <v>216.8271814338078</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -14046,7 +14046,7 @@
         <v>1.168783843154342</v>
       </c>
       <c r="AY70" t="n">
-        <v>-0.4778171053670847</v>
+        <v>-0.4778171425576067</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14188,28 +14188,28 @@
         <v>982.9716735839844</v>
       </c>
       <c r="AG71" t="n">
-        <v>717.6230918884278</v>
+        <v>717.6230955505371</v>
       </c>
       <c r="AH71" t="n">
         <v>-0.1059355518850754</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.2246540513945809</v>
+        <v>0.2246540451450372</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.3697603723944987</v>
+        <v>0.3697603654044614</v>
       </c>
       <c r="AK71" t="n">
         <v>1213.182495117188</v>
       </c>
       <c r="AL71" t="n">
-        <v>198.2448425292969</v>
+        <v>198.2448577880859</v>
       </c>
       <c r="AM71" t="n">
         <v>-0.2755912400709531</v>
       </c>
       <c r="AN71" t="n">
-        <v>3.433104113291586</v>
+        <v>3.433103772078193</v>
       </c>
       <c r="AO71" t="n">
         <v>27.02951398264811</v>
@@ -14230,19 +14230,19 @@
         <v>-0.09460215204133549</v>
       </c>
       <c r="AU71" t="n">
-        <v>0.9604689304890595</v>
+        <v>0.9604690639518478</v>
       </c>
       <c r="AV71" t="n">
-        <v>3.344236378057902</v>
+        <v>3.344236050387583</v>
       </c>
       <c r="AW71" t="n">
-        <v>12.00391659616703</v>
+        <v>12.00391953218487</v>
       </c>
       <c r="AX71" t="n">
         <v>1.788291083506025</v>
       </c>
       <c r="AY71" t="n">
-        <v>649.7351138686897</v>
+        <v>649.7349989902114</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14622,13 +14622,13 @@
         <v>2.6712218113724</v>
       </c>
       <c r="AW73" t="n">
-        <v>12.21965117515859</v>
+        <v>12.21965224851251</v>
       </c>
       <c r="AX73" t="n">
         <v>0.8830673642552882</v>
       </c>
       <c r="AY73" t="n">
-        <v>-6.558853287120631</v>
+        <v>-6.558854046280765</v>
       </c>
       <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
@@ -14770,16 +14770,16 @@
         <v>308.8933575439453</v>
       </c>
       <c r="AG74" t="n">
-        <v>281.5233889007569</v>
+        <v>281.5233882141113</v>
       </c>
       <c r="AH74" t="n">
         <v>-0.1455303392082288</v>
       </c>
       <c r="AI74" t="n">
-        <v>-0.06245799515275485</v>
+        <v>-0.06245799286605669</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.09722094050536212</v>
+        <v>0.09722094318152297</v>
       </c>
       <c r="AK74" t="n">
         <v>432.8701477050781</v>
@@ -14815,7 +14815,7 @@
         <v>0.00473674990230033</v>
       </c>
       <c r="AV74" t="n">
-        <v>0.8624649016060577</v>
+        <v>0.8624647010706799</v>
       </c>
       <c r="AW74" t="n">
         <v>4.025986471951604</v>
@@ -14957,7 +14957,7 @@
         <v>37601</v>
       </c>
       <c r="AD75" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AE75" t="n">
         <v>639.010009765625</v>
@@ -14966,28 +14966,28 @@
         <v>841.1995629882813</v>
       </c>
       <c r="AG75" t="n">
-        <v>673.5459016418457</v>
+        <v>673.5459022521973</v>
       </c>
       <c r="AH75" t="n">
         <v>-0.2403586046863805</v>
       </c>
       <c r="AI75" t="n">
-        <v>-0.05127474132354681</v>
+        <v>-0.05127474218325945</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.248912005756045</v>
+        <v>0.2489120046243101</v>
       </c>
       <c r="AK75" t="n">
-        <v>1092.384765625</v>
+        <v>1092.384887695312</v>
       </c>
       <c r="AL75" t="n">
-        <v>213.1436462402344</v>
+        <v>213.1436614990234</v>
       </c>
       <c r="AM75" t="n">
-        <v>-0.4150321115106177</v>
+        <v>-0.4150321768787986</v>
       </c>
       <c r="AN75" t="n">
-        <v>1.99802513955962</v>
+        <v>1.998024924933331</v>
       </c>
       <c r="AO75" t="n">
         <v>18.12663843627931</v>
@@ -15014,13 +15014,13 @@
         <v>1.843766594460251</v>
       </c>
       <c r="AW75" t="n">
-        <v>8.020748093696261</v>
+        <v>8.020747122141069</v>
       </c>
       <c r="AX75" t="n">
         <v>1.229583982237506</v>
       </c>
       <c r="AY75" t="n">
-        <v>120.3192783785798</v>
+        <v>120.3193003446385</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15162,16 +15162,16 @@
         <v>256840</v>
       </c>
       <c r="AG76" t="n">
-        <v>231815.3562890625</v>
+        <v>231815.3563671875</v>
       </c>
       <c r="AH76" t="n">
         <v>-0.1609562373462078</v>
       </c>
       <c r="AI76" t="n">
-        <v>-0.07038082614647001</v>
+        <v>-0.07038082645976451</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.1079507592229265</v>
+        <v>0.1079507588495316</v>
       </c>
       <c r="AK76" t="n">
         <v>362100.65625</v>
@@ -15210,13 +15210,13 @@
         <v>1.589214509813934</v>
       </c>
       <c r="AW76" t="n">
-        <v>2.201634616467178</v>
+        <v>2.201633873249237</v>
       </c>
       <c r="AX76" t="n">
         <v>0.6823672976682527</v>
       </c>
       <c r="AY76" t="n">
-        <v>49.47472158183649</v>
+        <v>49.47470426407544</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
@@ -15546,28 +15546,28 @@
         <v>442.1210241699219</v>
       </c>
       <c r="AG78" t="n">
-        <v>410.3403331756592</v>
+        <v>410.3403335571289</v>
       </c>
       <c r="AH78" t="n">
         <v>-0.2490743894766667</v>
       </c>
       <c r="AI78" t="n">
-        <v>-0.1909155080354314</v>
+        <v>-0.1909155087875907</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.07744959104631333</v>
+        <v>0.07744959004467056</v>
       </c>
       <c r="AK78" t="n">
         <v>745.990478515625</v>
       </c>
       <c r="AL78" t="n">
-        <v>120.2456665039062</v>
+        <v>120.2456741333008</v>
       </c>
       <c r="AM78" t="n">
         <v>-0.5549541052311888</v>
       </c>
       <c r="AN78" t="n">
-        <v>1.761014260661234</v>
+        <v>1.761014085479322</v>
       </c>
       <c r="AO78" t="n">
         <v>19.77259967977315</v>
@@ -15591,16 +15591,16 @@
         <v>-0.1120441329486468</v>
       </c>
       <c r="AV78" t="n">
-        <v>1.641513754130713</v>
+        <v>1.641513593784866</v>
       </c>
       <c r="AW78" t="n">
         <v>6.858083947657562</v>
       </c>
       <c r="AX78" t="n">
-        <v>0.7706561476319354</v>
+        <v>0.7706562917274573</v>
       </c>
       <c r="AY78" t="n">
-        <v>487.7225761709174</v>
+        <v>487.7226619333113</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -16248,16 +16248,16 @@
         <v>82.16219985961914</v>
       </c>
       <c r="AG82" t="n">
-        <v>74.84125120162963</v>
+        <v>74.84125133514404</v>
       </c>
       <c r="AH82" t="n">
         <v>-0.03422743536934159</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.06024414611060491</v>
+        <v>0.06024414421916324</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.09781969890196196</v>
+        <v>0.09781969694348658</v>
       </c>
       <c r="AK82" t="n">
         <v>88.62000274658203</v>
@@ -16296,13 +16296,13 @@
         <v>0.2547748081640639</v>
       </c>
       <c r="AW82" t="n">
-        <v>3.421734539806317</v>
+        <v>3.421733599870076</v>
       </c>
       <c r="AX82" t="n">
         <v>0.141654534499646</v>
       </c>
       <c r="AY82" t="n">
-        <v>1269.208004980564</v>
+        <v>1269.208080727124</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -16444,28 +16444,28 @@
         <v>240.9960021972656</v>
       </c>
       <c r="AG83" t="n">
-        <v>175.7845223236084</v>
+        <v>175.7845219039917</v>
       </c>
       <c r="AH83" t="n">
         <v>-0.05463161316441256</v>
       </c>
       <c r="AI83" t="n">
-        <v>0.2960754383803699</v>
+        <v>0.2960754414742424</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.3709739572725688</v>
+        <v>0.3709739605452322</v>
       </c>
       <c r="AK83" t="n">
         <v>316.2828369140625</v>
       </c>
       <c r="AL83" t="n">
-        <v>73.65883636474609</v>
+        <v>73.65884399414062</v>
       </c>
       <c r="AM83" t="n">
         <v>-0.2796637210733044</v>
       </c>
       <c r="AN83" t="n">
-        <v>2.093043728017628</v>
+        <v>2.093043407648076</v>
       </c>
       <c r="AO83" t="n">
         <v>38.38726800471698</v>
@@ -16492,13 +16492,13 @@
         <v>1.586582520681004</v>
       </c>
       <c r="AW83" t="n">
-        <v>2.655933648444295</v>
+        <v>2.655933872236936</v>
       </c>
       <c r="AX83" t="n">
-        <v>1.553016969937595</v>
+        <v>1.553017188203852</v>
       </c>
       <c r="AY83" t="n">
-        <v>17.78754237767324</v>
+        <v>17.7875438551789</v>
       </c>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="n">
@@ -17222,25 +17222,25 @@
         <v>210.2418127441406</v>
       </c>
       <c r="AG87" t="n">
-        <v>212.4489326477051</v>
+        <v>212.4489325714111</v>
       </c>
       <c r="AH87" t="n">
         <v>0.01140680159767449</v>
       </c>
       <c r="AI87" t="n">
-        <v>0.0008993537390944439</v>
+        <v>0.0008993540985342552</v>
       </c>
       <c r="AJ87" t="n">
-        <v>-0.01038894324418393</v>
+        <v>-0.0103889428887981</v>
       </c>
       <c r="AK87" t="n">
-        <v>246.3216094970703</v>
+        <v>246.3216247558594</v>
       </c>
       <c r="AL87" t="n">
         <v>194.3271179199219</v>
       </c>
       <c r="AM87" t="n">
-        <v>-0.1367383486012115</v>
+        <v>-0.1367384020773423</v>
       </c>
       <c r="AN87" t="n">
         <v>0.0942373955099407</v>
@@ -17270,13 +17270,13 @@
         <v>-0.04120547869806102</v>
       </c>
       <c r="AW87" t="n">
-        <v>0.5780512601467851</v>
+        <v>0.5780516175409138</v>
       </c>
       <c r="AX87" t="n">
         <v>-0.07832889106409435</v>
       </c>
       <c r="AY87" t="n">
-        <v>6.988217936363299</v>
+        <v>6.9882167916022</v>
       </c>
       <c r="AZ87" t="inlineStr"/>
       <c r="BA87" t="n">
@@ -17975,10 +17975,10 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA91" t="n">
-        <v>6208139484.627502</v>
+        <v>6207441117.059326</v>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
@@ -18046,13 +18046,13 @@
         <v>0.07515133983925448</v>
       </c>
       <c r="AW91" t="n">
-        <v>0.5577572819859813</v>
+        <v>0.5577574281071342</v>
       </c>
       <c r="AX91" t="n">
         <v>0.005597545218464672</v>
       </c>
       <c r="AY91" t="n">
-        <v>6.84521883893107</v>
+        <v>6.845220692009075</v>
       </c>
       <c r="AZ91" t="inlineStr"/>
       <c r="BA91" t="n">
@@ -18167,10 +18167,10 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA92" t="n">
-        <v>36811992784.97412</v>
+        <v>36807851721.14258</v>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
@@ -18238,13 +18238,13 @@
         <v>0.240047297131351</v>
       </c>
       <c r="AW92" t="n">
-        <v>2.52091486525284</v>
+        <v>2.520915081387207</v>
       </c>
       <c r="AX92" t="n">
         <v>0.2262506291906492</v>
       </c>
       <c r="AY92" t="n">
-        <v>9.448819652859811</v>
+        <v>9.448818701122303</v>
       </c>
       <c r="AZ92" t="inlineStr"/>
       <c r="BA92" t="n">
@@ -18628,7 +18628,7 @@
         <v>0.008963546765015762</v>
       </c>
       <c r="AY94" t="n">
-        <v>165.4387969435822</v>
+        <v>165.4387754237871</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -19012,13 +19012,13 @@
         <v>0.5354142688997281</v>
       </c>
       <c r="AW96" t="n">
-        <v>3.051780058052511</v>
+        <v>3.051780532488825</v>
       </c>
       <c r="AX96" t="n">
         <v>0.4635320366382427</v>
       </c>
       <c r="AY96" t="n">
-        <v>171.51250299226</v>
+        <v>171.5125433074473</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19210,7 +19210,7 @@
         <v>0.03094660194174748</v>
       </c>
       <c r="AY97" t="n">
-        <v>24.15153946517184</v>
+        <v>24.15154514657925</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19396,13 +19396,13 @@
         <v>0.6091550386536133</v>
       </c>
       <c r="AW98" t="n">
-        <v>0.7543286259507052</v>
+        <v>0.7543289470769894</v>
       </c>
       <c r="AX98" t="n">
         <v>0.4039938589821908</v>
       </c>
       <c r="AY98" t="n">
-        <v>14.29590374290584</v>
+        <v>14.29590069140085</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19544,16 +19544,16 @@
         <v>365.3192327880859</v>
       </c>
       <c r="AG99" t="n">
-        <v>367.0558517456055</v>
+        <v>367.0558497619629</v>
       </c>
       <c r="AH99" t="n">
         <v>-0.1001021285109809</v>
       </c>
       <c r="AI99" t="n">
-        <v>-0.1043597358915123</v>
+        <v>-0.1043597310512948</v>
       </c>
       <c r="AJ99" t="n">
-        <v>-0.004731211746824782</v>
+        <v>-0.004731206368194907</v>
       </c>
       <c r="AK99" t="n">
         <v>479.9351196289062</v>
@@ -19589,16 +19589,16 @@
         <v>-0.1745616950860105</v>
       </c>
       <c r="AV99" t="n">
-        <v>-0.064818993850148</v>
+        <v>-0.06481891266516648</v>
       </c>
       <c r="AW99" t="n">
-        <v>6.294499853948911</v>
+        <v>6.294499236522334</v>
       </c>
       <c r="AX99" t="n">
-        <v>-0.04907119528243098</v>
+        <v>-0.0490711113402309</v>
       </c>
       <c r="AY99" t="n">
-        <v>289.0239285749967</v>
+        <v>289.023959075854</v>
       </c>
       <c r="AZ99" t="inlineStr"/>
       <c r="BA99" t="n">
@@ -19936,28 +19936,28 @@
         <v>75.65104034423828</v>
       </c>
       <c r="AG101" t="n">
-        <v>78.78386398315429</v>
+        <v>78.78386392593384</v>
       </c>
       <c r="AH101" t="n">
         <v>-0.02380723202115698</v>
       </c>
       <c r="AI101" t="n">
-        <v>-0.06262533036064544</v>
+        <v>-0.06262532967983347</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-0.0397647878705959</v>
+        <v>-0.03976478717318033</v>
       </c>
       <c r="AK101" t="n">
         <v>102.0957336425781</v>
       </c>
       <c r="AL101" t="n">
-        <v>47.76882934570312</v>
+        <v>47.76882553100586</v>
       </c>
       <c r="AM101" t="n">
         <v>-0.2766593094608745</v>
       </c>
       <c r="AN101" t="n">
-        <v>0.5459871946969537</v>
+        <v>0.5459873181555706</v>
       </c>
       <c r="AO101" t="n">
         <v>39.65863857581723</v>
@@ -19981,16 +19981,16 @@
         <v>-0.07118793009412416</v>
       </c>
       <c r="AV101" t="n">
-        <v>0.1596678563455152</v>
+        <v>0.1596677868787941</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.1446621256231853</v>
+        <v>0.1446622609844055</v>
       </c>
       <c r="AX101" t="n">
-        <v>0.1549570810700973</v>
+        <v>0.154956943263115</v>
       </c>
       <c r="AY101" t="n">
-        <v>421.9060520236985</v>
+        <v>421.9060159361496</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20128,28 +20128,28 @@
         <v>51.654775390625</v>
       </c>
       <c r="AG102" t="n">
-        <v>49.05459197044372</v>
+        <v>49.05459196090698</v>
       </c>
       <c r="AH102" t="n">
         <v>-0.1212816424735355</v>
       </c>
       <c r="AI102" t="n">
-        <v>-0.07470437391474527</v>
+        <v>-0.07470437373485783</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.05300591271349142</v>
+        <v>0.053005912918207</v>
       </c>
       <c r="AK102" t="n">
         <v>79.68086242675781</v>
       </c>
       <c r="AL102" t="n">
-        <v>21.00741767883301</v>
+        <v>21.00741958618164</v>
       </c>
       <c r="AM102" t="n">
         <v>-0.4303525588547606</v>
       </c>
       <c r="AN102" t="n">
-        <v>1.160665346097403</v>
+        <v>1.160665149921853</v>
       </c>
       <c r="AO102" t="n">
         <v>30.96840557716207</v>
@@ -20173,7 +20173,7 @@
         <v>0.02385363129943374</v>
       </c>
       <c r="AV102" t="n">
-        <v>0.561216867632705</v>
+        <v>0.5612169700554481</v>
       </c>
       <c r="AW102" t="n">
         <v>0.1594180924988078</v>
@@ -20562,13 +20562,13 @@
         <v>0.6571573305242087</v>
       </c>
       <c r="AW104" t="n">
-        <v>1.560381167024658</v>
+        <v>1.560381925899404</v>
       </c>
       <c r="AX104" t="n">
         <v>0.4575020856764505</v>
       </c>
       <c r="AY104" t="n">
-        <v>893.1215483745588</v>
+        <v>893.1210663686255</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20706,16 +20706,16 @@
         <v>282.3607482910156</v>
       </c>
       <c r="AG105" t="n">
-        <v>207.9901264190674</v>
+        <v>207.9901268005371</v>
       </c>
       <c r="AH105" t="n">
         <v>-0.06325506784890444</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.2716949816505909</v>
+        <v>0.2716949793182057</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.3575680401390935</v>
+        <v>0.3575680376492105</v>
       </c>
       <c r="AK105" t="n">
         <v>317.5</v>
@@ -20754,13 +20754,13 @@
         <v>0.6031585445650087</v>
       </c>
       <c r="AW105" t="n">
-        <v>4.43817056463036</v>
+        <v>4.438170991151033</v>
       </c>
       <c r="AX105" t="n">
-        <v>0.6271579992184433</v>
+        <v>0.6271578464780856</v>
       </c>
       <c r="AY105" t="n">
-        <v>68.94716719225082</v>
+        <v>68.94717160241449</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20902,16 +20902,16 @@
         <v>272.3044006347656</v>
       </c>
       <c r="AG106" t="n">
-        <v>252.7853876495361</v>
+        <v>252.7853889465332</v>
       </c>
       <c r="AH106" t="n">
         <v>0.01533434767058051</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.09373414957688309</v>
+        <v>0.09373414396512691</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.07721574876903414</v>
+        <v>0.07721574324203084</v>
       </c>
       <c r="AK106" t="n">
         <v>330.5873718261719</v>
@@ -20944,10 +20944,10 @@
         <v>-0.04601569767331659</v>
       </c>
       <c r="AU106" t="n">
-        <v>0.1951545547465052</v>
+        <v>0.1951544759141606</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.6163669225672797</v>
+        <v>0.6163666341866019</v>
       </c>
       <c r="AW106" t="n">
         <v>0.6473681459078762</v>
@@ -20956,7 +20956,7 @@
         <v>0.5836565720624547</v>
       </c>
       <c r="AY106" t="n">
-        <v>403.1669314604856</v>
+        <v>403.1666497340475</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21098,16 +21098,16 @@
         <v>650.3271765136719</v>
       </c>
       <c r="AG107" t="n">
-        <v>618.0573147583008</v>
+        <v>618.0573144531249</v>
       </c>
       <c r="AH107" t="n">
         <v>-0.02839676985530559</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.02233234728183664</v>
+        <v>0.02233234778662974</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.05221176254178084</v>
+        <v>0.05221176306132747</v>
       </c>
       <c r="AK107" t="n">
         <v>784.9856567382812</v>
@@ -21140,19 +21140,19 @@
         <v>-0.01131387488706759</v>
       </c>
       <c r="AU107" t="n">
-        <v>0.04478697683036903</v>
+        <v>0.04478687138811899</v>
       </c>
       <c r="AV107" t="n">
         <v>0.445313906477425</v>
       </c>
       <c r="AW107" t="n">
-        <v>4.740815934816048</v>
+        <v>4.740815536877111</v>
       </c>
       <c r="AX107" t="n">
-        <v>0.4378386906943628</v>
+        <v>0.4378385908440308</v>
       </c>
       <c r="AY107" t="n">
-        <v>84.93384014878784</v>
+        <v>84.93384572164236</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21294,28 +21294,28 @@
         <v>454.6339862060547</v>
       </c>
       <c r="AG108" t="n">
-        <v>450.0203091430664</v>
+        <v>450.0203088378906</v>
       </c>
       <c r="AH108" t="n">
         <v>0.009361439248964931</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.0197095671576708</v>
+        <v>0.01970956784917455</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.01025215300121385</v>
+        <v>0.01025215368630406</v>
       </c>
       <c r="AK108" t="n">
         <v>502.2725524902344</v>
       </c>
       <c r="AL108" t="n">
-        <v>373.790283203125</v>
+        <v>373.7903137207031</v>
       </c>
       <c r="AM108" t="n">
         <v>-0.08637250358736326</v>
       </c>
       <c r="AN108" t="n">
-        <v>0.2276670509357988</v>
+        <v>0.2276669507046698</v>
       </c>
       <c r="AO108" t="n">
         <v>54.64058223438666</v>
@@ -21336,19 +21336,19 @@
         <v>-0.02110091504221068</v>
       </c>
       <c r="AU108" t="n">
-        <v>-0.03398986277394167</v>
+        <v>-0.0339898007149303</v>
       </c>
       <c r="AV108" t="n">
-        <v>0.1111048056740658</v>
+        <v>0.1111047235724929</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.867920094836292</v>
+        <v>1.867919821343733</v>
       </c>
       <c r="AX108" t="n">
         <v>0.1611323677376659</v>
       </c>
       <c r="AY108" t="n">
-        <v>514.9520999176503</v>
+        <v>514.9519270315318</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21486,16 +21486,16 @@
         <v>20988.824921875</v>
       </c>
       <c r="AG109" t="n">
-        <v>21257.23716796875</v>
+        <v>21257.23711914062</v>
       </c>
       <c r="AH109" t="n">
         <v>0.01696974839948218</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.004128609533674332</v>
+        <v>0.004128611840169549</v>
       </c>
       <c r="AJ109" t="n">
-        <v>-0.01262686415797276</v>
+        <v>-0.01262686188996498</v>
       </c>
       <c r="AK109" t="n">
         <v>25925</v>
@@ -21537,10 +21537,10 @@
         <v>-0.09872952055350337</v>
       </c>
       <c r="AX109" t="n">
-        <v>0.0728828444809555</v>
+        <v>0.07288294980766685</v>
       </c>
       <c r="AY109" t="n">
-        <v>19.07805788133135</v>
+        <v>19.07806479770911</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21732,7 +21732,7 @@
         <v>0.3358564371078521</v>
       </c>
       <c r="AY110" t="n">
-        <v>6.436948312024427</v>
+        <v>6.43694905476914</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21922,13 +21922,13 @@
         <v>0.05330856316016241</v>
       </c>
       <c r="AW111" t="n">
-        <v>1.771374887700831</v>
+        <v>1.771375187241862</v>
       </c>
       <c r="AX111" t="n">
         <v>0.2053493318506148</v>
       </c>
       <c r="AY111" t="n">
-        <v>1134.561655400292</v>
+        <v>1134.562342968043</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22043,10 +22043,10 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA112" t="n">
-        <v>76546873566.72168</v>
+        <v>76538262636.81641</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>0.5481857995569759</v>
       </c>
       <c r="AW112" t="n">
-        <v>0.2804494175022139</v>
+        <v>0.2804492981208604</v>
       </c>
       <c r="AX112" t="n">
         <v>0.3796715664710368</v>
@@ -22262,16 +22262,16 @@
         <v>1306.08048828125</v>
       </c>
       <c r="AG113" t="n">
-        <v>1300.170586853027</v>
+        <v>1300.170591125488</v>
       </c>
       <c r="AH113" t="n">
         <v>-0.07290553973055203</v>
       </c>
       <c r="AI113" t="n">
-        <v>-0.06869144895642876</v>
+        <v>-0.06869145201678062</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.004545481560636722</v>
+        <v>0.004545478259622593</v>
       </c>
       <c r="AK113" t="n">
         <v>1684.826782226562</v>
@@ -22304,10 +22304,10 @@
         <v>-0.1233401499767608</v>
       </c>
       <c r="AU113" t="n">
-        <v>-0.1853703348892497</v>
+        <v>-0.1853702679876339</v>
       </c>
       <c r="AV113" t="n">
-        <v>0.1871345393174328</v>
+        <v>0.1871343972429911</v>
       </c>
       <c r="AW113" t="n">
         <v>1.725609080046674</v>
@@ -22316,7 +22316,7 @@
         <v>0.2997051956748231</v>
       </c>
       <c r="AY113" t="n">
-        <v>143.4549037044083</v>
+        <v>143.4549530095419</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22431,10 +22431,10 @@
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA114" t="n">
-        <v>160427475531.7812</v>
+        <v>160409428684.375</v>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>0.0852719670359865</v>
       </c>
       <c r="AY114" t="n">
-        <v>12.61156702060951</v>
+        <v>12.61156562549102</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22886,13 +22886,13 @@
         <v>0.8869683166631821</v>
       </c>
       <c r="AW116" t="n">
-        <v>5.376943455232283</v>
+        <v>5.376944214259749</v>
       </c>
       <c r="AX116" t="n">
         <v>0.6518084413662464</v>
       </c>
       <c r="AY116" t="n">
-        <v>65.18913188557642</v>
+        <v>65.18912166405309</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -23034,16 +23034,16 @@
         <v>57.69419998168945</v>
       </c>
       <c r="AG117" t="n">
-        <v>61.4651003074646</v>
+        <v>61.46510057449341</v>
       </c>
       <c r="AH117" t="n">
         <v>-0.04669793467184769</v>
       </c>
       <c r="AI117" t="n">
-        <v>-0.1051832710778062</v>
+        <v>-0.1051832749652455</v>
       </c>
       <c r="AJ117" t="n">
-        <v>-0.06135026717457737</v>
+        <v>-0.06135027125244452</v>
       </c>
       <c r="AK117" t="n">
         <v>75.72768402099609</v>
@@ -23082,13 +23082,13 @@
         <v>-0.01593097691472378</v>
       </c>
       <c r="AW117" t="n">
-        <v>0.1519414211606853</v>
+        <v>0.1519417893051782</v>
       </c>
       <c r="AX117" t="n">
         <v>0.03946192226832057</v>
       </c>
       <c r="AY117" t="n">
-        <v>3.991737949268213</v>
+        <v>3.991736653097824</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -23203,10 +23203,10 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA118" t="n">
-        <v>39490916862.20947</v>
+        <v>39486474440.18555</v>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>-0.06181624562574539</v>
       </c>
       <c r="AW118" t="n">
-        <v>0.5603557227486193</v>
+        <v>0.5603559999928929</v>
       </c>
       <c r="AX118" t="n">
         <v>0.06555063511463755</v>
@@ -23472,7 +23472,7 @@
         <v>0.05716925780364468</v>
       </c>
       <c r="AY119" t="n">
-        <v>167.642221321881</v>
+        <v>167.6423010355797</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23587,10 +23587,10 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>0.1010396927595139</v>
+        <v>0.1009238585829735</v>
       </c>
       <c r="AA120" t="n">
-        <v>2416155027.431183</v>
+        <v>2413385092.959366</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
@@ -23804,16 +23804,16 @@
         <v>255.4280242919922</v>
       </c>
       <c r="AG121" t="n">
-        <v>268.2027132415772</v>
+        <v>268.2027124023438</v>
       </c>
       <c r="AH121" t="n">
         <v>-0.1918662850675438</v>
       </c>
       <c r="AI121" t="n">
-        <v>-0.2303582776099008</v>
+        <v>-0.230358275201614</v>
       </c>
       <c r="AJ121" t="n">
-        <v>-0.04763072228161414</v>
+        <v>-0.04763071930155449</v>
       </c>
       <c r="AK121" t="n">
         <v>376.0595397949219</v>
@@ -23849,16 +23849,16 @@
         <v>-0.3431711300118014</v>
       </c>
       <c r="AV121" t="n">
-        <v>0.1620727454870055</v>
+        <v>0.1620728453110054</v>
       </c>
       <c r="AW121" t="n">
         <v>8.315569655370451</v>
       </c>
       <c r="AX121" t="n">
-        <v>0.1762582096277259</v>
+        <v>0.1762581073517582</v>
       </c>
       <c r="AY121" t="n">
-        <v>19.77764611650001</v>
+        <v>19.7776441219682</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -24625,7 +24625,7 @@
         <v>-0.2754789730110606</v>
       </c>
       <c r="AV125" t="n">
-        <v>-0.03723838291086512</v>
+        <v>-0.03723846236885364</v>
       </c>
       <c r="AW125" t="n">
         <v>-0.5188391895134783</v>
@@ -24634,7 +24634,7 @@
         <v>0.2063478669123746</v>
       </c>
       <c r="AY125" t="n">
-        <v>24.61314930678537</v>
+        <v>24.61314754936352</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24863,10 +24863,10 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA127" t="n">
-        <v>232935225082.3652</v>
+        <v>232909021675.1953</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -24934,13 +24934,13 @@
         <v>0.1365292746994615</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.106977466305536</v>
+        <v>1.106977716588841</v>
       </c>
       <c r="AX127" t="n">
         <v>0.146428487173927</v>
       </c>
       <c r="AY127" t="n">
-        <v>27.47076399741654</v>
+        <v>27.47076114120569</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -25447,10 +25447,10 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA130" t="n">
-        <v>13836444045.87256</v>
+        <v>13834887553.17383</v>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
@@ -25518,13 +25518,13 @@
         <v>0.1301852321391292</v>
       </c>
       <c r="AW130" t="n">
-        <v>1.13867615387496</v>
+        <v>1.138676378216734</v>
       </c>
       <c r="AX130" t="n">
         <v>0.04983666146560717</v>
       </c>
       <c r="AY130" t="n">
-        <v>72.86500139142777</v>
+        <v>72.86501811686909</v>
       </c>
       <c r="AZ130" t="inlineStr"/>
       <c r="BA130" t="n">
@@ -25710,13 +25710,13 @@
         <v>1.298238579449948</v>
       </c>
       <c r="AW131" t="n">
-        <v>15.30618930137371</v>
+        <v>15.30619306129305</v>
       </c>
       <c r="AX131" t="n">
         <v>0.6329162011193825</v>
       </c>
       <c r="AY131" t="n">
-        <v>13.56026990183198</v>
+        <v>13.56026840289878</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="X132" t="n">
-        <v>630507831296</v>
+        <v>632670912512</v>
       </c>
       <c r="Y132" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>1</v>
       </c>
       <c r="AA132" t="n">
-        <v>630507831296</v>
+        <v>632670912512</v>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
@@ -25858,28 +25858,28 @@
         <v>1739.630202636719</v>
       </c>
       <c r="AG132" t="n">
-        <v>1574.404447631836</v>
+        <v>1574.404442138672</v>
       </c>
       <c r="AH132" t="n">
         <v>-0.05639714863352296</v>
       </c>
       <c r="AI132" t="n">
-        <v>0.04262918083111811</v>
+        <v>0.04262918446889574</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.1049449239383244</v>
+        <v>0.1049449277935244</v>
       </c>
       <c r="AK132" t="n">
         <v>1986.870361328125</v>
       </c>
       <c r="AL132" t="n">
-        <v>961.9489135742188</v>
+        <v>961.9488525390625</v>
       </c>
       <c r="AM132" t="n">
         <v>-0.1738162431322521</v>
       </c>
       <c r="AN132" t="n">
-        <v>0.7064523867821795</v>
+        <v>0.7064524950556992</v>
       </c>
       <c r="AO132" t="n">
         <v>34.13924552905054</v>
@@ -25903,10 +25903,10 @@
         <v>0.1156336006905192</v>
       </c>
       <c r="AV132" t="n">
-        <v>0.620584860384825</v>
+        <v>0.6205847627336651</v>
       </c>
       <c r="AW132" t="n">
-        <v>1.383361087127536</v>
+        <v>1.383361298337112</v>
       </c>
       <c r="AX132" t="n">
         <v>0.4172830699825656</v>
@@ -26054,16 +26054,16 @@
         <v>433.7545190429688</v>
       </c>
       <c r="AG133" t="n">
-        <v>393.4075839233399</v>
+        <v>393.4075860595703</v>
       </c>
       <c r="AH133" t="n">
         <v>-0.04874769659589784</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.04881045056814259</v>
+        <v>0.04881044487302932</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.1025575936215073</v>
+        <v>0.1025575876345433</v>
       </c>
       <c r="AK133" t="n">
         <v>485.7999877929688</v>
@@ -26099,16 +26099,16 @@
         <v>0.13227878785138</v>
       </c>
       <c r="AV133" t="n">
-        <v>0.3906648650277678</v>
+        <v>0.3906647219885089</v>
       </c>
       <c r="AW133" t="n">
-        <v>3.053860767236189</v>
+        <v>3.053860463366092</v>
       </c>
       <c r="AX133" t="n">
         <v>0.301130419510599</v>
       </c>
       <c r="AY133" t="n">
-        <v>131.4782381508717</v>
+        <v>131.4782482920748</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26294,7 +26294,7 @@
         <v>1.71449531041489</v>
       </c>
       <c r="AW134" t="n">
-        <v>1.451407572280619</v>
+        <v>1.451407861433512</v>
       </c>
       <c r="AX134" t="n">
         <v>1.572538208322881</v>
@@ -26490,13 +26490,13 @@
         <v>0.9946287630909241</v>
       </c>
       <c r="AW135" t="n">
-        <v>3.346952469484061</v>
+        <v>3.346953337457935</v>
       </c>
       <c r="AX135" t="n">
         <v>0.5039382437400384</v>
       </c>
       <c r="AY135" t="n">
-        <v>19.28420872658595</v>
+        <v>19.28421108903792</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26638,16 +26638,16 @@
         <v>482.1113134765625</v>
       </c>
       <c r="AG136" t="n">
-        <v>438.3814297485351</v>
+        <v>438.3814295959473</v>
       </c>
       <c r="AH136" t="n">
         <v>-0.1510466626607815</v>
       </c>
       <c r="AI136" t="n">
-        <v>-0.06636097979857569</v>
+        <v>-0.06636097947360298</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.09975304782666483</v>
+        <v>0.09975304820945707</v>
       </c>
       <c r="AK136" t="n">
         <v>722.2277221679688</v>
@@ -26683,16 +26683,16 @@
         <v>0.04753845998834172</v>
       </c>
       <c r="AV136" t="n">
-        <v>0.8072800900324064</v>
+        <v>0.8072799682625413</v>
       </c>
       <c r="AW136" t="n">
-        <v>2.345688563507261</v>
+        <v>2.3456881461962</v>
       </c>
       <c r="AX136" t="n">
-        <v>0.5276851329142445</v>
+        <v>0.527684958899288</v>
       </c>
       <c r="AY136" t="n">
-        <v>5937.361290869358</v>
+        <v>5937.362574743041</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26821,7 +26821,7 @@
         <v>40231</v>
       </c>
       <c r="AD137" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="AE137" t="n">
         <v>41200</v>
@@ -26830,16 +26830,16 @@
         <v>39003.2</v>
       </c>
       <c r="AG137" t="n">
-        <v>38646.99365234375</v>
+        <v>38646.99366210937</v>
       </c>
       <c r="AH137" t="n">
         <v>0.05632358370595236</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.06605963637488332</v>
+        <v>0.06605963610550303</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.009216922559632135</v>
+        <v>0.00921692230461546</v>
       </c>
       <c r="AK137" t="n">
         <v>57263.48828125</v>
@@ -26878,7 +26878,7 @@
         <v>1.040558499189654</v>
       </c>
       <c r="AW137" t="n">
-        <v>1.254025839916979</v>
+        <v>1.254025117360633</v>
       </c>
       <c r="AX137" t="n">
         <v>0.3044140723166211</v>
@@ -26999,10 +26999,10 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>1.124353528022766</v>
+        <v>1.124227046966553</v>
       </c>
       <c r="AA138" t="n">
-        <v>41330363551.57227</v>
+        <v>41325714206.05469</v>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>0.4156024153411455</v>
       </c>
       <c r="AW138" t="n">
-        <v>0.8106966869443508</v>
+        <v>0.8106965540683739</v>
       </c>
       <c r="AX138" t="n">
         <v>0.3649905750758249</v>
@@ -27218,16 +27218,16 @@
         <v>186.8778192138672</v>
       </c>
       <c r="AG139" t="n">
-        <v>180.7332761764526</v>
+        <v>180.7332762145996</v>
       </c>
       <c r="AH139" t="n">
         <v>-0.1131103402727133</v>
       </c>
       <c r="AI139" t="n">
-        <v>-0.08295799755574851</v>
+        <v>-0.08295799774930657</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0.0339978512391681</v>
+        <v>0.03399785102092467</v>
       </c>
       <c r="AK139" t="n">
         <v>301.3693542480469</v>
@@ -27266,13 +27266,13 @@
         <v>0.5165099071449923</v>
       </c>
       <c r="AW139" t="n">
-        <v>4.350486811782592</v>
+        <v>4.350487141232474</v>
       </c>
       <c r="AX139" t="n">
         <v>0.3052876714732182</v>
       </c>
       <c r="AY139" t="n">
-        <v>2733.772878189565</v>
+        <v>2733.772541983732</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
@@ -27625,13 +27625,13 @@
         <v>483.6542053222656</v>
       </c>
       <c r="AL141" t="n">
-        <v>137.8929138183594</v>
+        <v>137.8928985595703</v>
       </c>
       <c r="AM141" t="n">
         <v>-0.3280323081581645</v>
       </c>
       <c r="AN141" t="n">
-        <v>1.356901388189599</v>
+        <v>1.356901648996802</v>
       </c>
       <c r="AO141" t="n">
         <v>29.25728716758287</v>
@@ -27664,7 +27664,7 @@
         <v>0.5676605247149493</v>
       </c>
       <c r="AY141" t="n">
-        <v>290.9161022340066</v>
+        <v>290.9160709773303</v>
       </c>
       <c r="AZ141" t="inlineStr"/>
       <c r="BA141" t="n">
@@ -27856,7 +27856,7 @@
         <v>0.06314743805729428</v>
       </c>
       <c r="AY142" t="n">
-        <v>35.96398397291571</v>
+        <v>35.96399945937308</v>
       </c>
       <c r="AZ142" t="inlineStr"/>
       <c r="BA142" t="n">
@@ -28626,7 +28626,7 @@
         <v>0.5470305911670981</v>
       </c>
       <c r="AY146" t="n">
-        <v>0.06591479709830517</v>
+        <v>0.06591496706543842</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28768,16 +28768,16 @@
         <v>147.2487319946289</v>
       </c>
       <c r="AG147" t="n">
-        <v>138.6825299072266</v>
+        <v>138.6825300598144</v>
       </c>
       <c r="AH147" t="n">
         <v>-0.01207976971910818</v>
       </c>
       <c r="AI147" t="n">
-        <v>0.04894251149021533</v>
+        <v>0.04894251033609787</v>
       </c>
       <c r="AJ147" t="n">
-        <v>0.06176842961498341</v>
+        <v>0.06176842844675412</v>
       </c>
       <c r="AK147" t="n">
         <v>158.7599945068359</v>
@@ -28816,13 +28816,13 @@
         <v>0.3416094928345046</v>
       </c>
       <c r="AW147" t="n">
-        <v>1.31879636905565</v>
+        <v>1.318796228058014</v>
       </c>
       <c r="AX147" t="n">
         <v>0.1996715901095243</v>
       </c>
       <c r="AY147" t="n">
-        <v>46.23817805663855</v>
+        <v>46.2381743994033</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -29008,13 +29008,13 @@
         <v>0.2958388002327248</v>
       </c>
       <c r="AW148" t="n">
-        <v>7.215163525718536</v>
+        <v>7.215164231060424</v>
       </c>
       <c r="AX148" t="n">
         <v>0.2205965046562062</v>
       </c>
       <c r="AY148" t="n">
-        <v>37.02570481587753</v>
+        <v>37.02570103787953</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29210,7 +29210,7 @@
         <v>0.08304414627761614</v>
       </c>
       <c r="AY149" t="n">
-        <v>665.1269768328887</v>
+        <v>665.1268142422732</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29402,7 +29402,7 @@
         <v>0.2639820673614639</v>
       </c>
       <c r="AY150" t="n">
-        <v>64.61659371459702</v>
+        <v>64.61659816563299</v>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="n">
@@ -29544,16 +29544,16 @@
         <v>513.2592016601562</v>
       </c>
       <c r="AG151" t="n">
-        <v>313.540053100586</v>
+        <v>313.540052986145</v>
       </c>
       <c r="AH151" t="n">
         <v>-0.1199183765356663</v>
       </c>
       <c r="AI151" t="n">
-        <v>0.4406771542842287</v>
+        <v>0.4406771548100703</v>
       </c>
       <c r="AJ151" t="n">
-        <v>0.6369812934091037</v>
+        <v>0.6369812940065955</v>
       </c>
       <c r="AK151" t="n">
         <v>588.4000244140625</v>
@@ -29592,13 +29592,13 @@
         <v>2.023370218125372</v>
       </c>
       <c r="AW151" t="n">
-        <v>8.325850374103332</v>
+        <v>8.325851108578814</v>
       </c>
       <c r="AX151" t="n">
-        <v>2.566838400225361</v>
+        <v>2.566838185344756</v>
       </c>
       <c r="AY151" t="n">
-        <v>40.20533320527683</v>
+        <v>40.20533678993121</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29794,7 +29794,7 @@
         <v>1.308174174528613</v>
       </c>
       <c r="AY152" t="n">
-        <v>6.670944484441516</v>
+        <v>6.670945502352551</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29986,7 +29986,7 @@
         <v>0.3672834744965963</v>
       </c>
       <c r="AY153" t="n">
-        <v>6.763405433619735</v>
+        <v>6.763403972304922</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30368,7 +30368,7 @@
         <v>0.1718922569094277</v>
       </c>
       <c r="AW155" t="n">
-        <v>4.449956689787829</v>
+        <v>4.449957393540992</v>
       </c>
       <c r="AX155" t="n">
         <v>0.2120835051676662</v>
@@ -30516,28 +30516,28 @@
         <v>111.2900611877441</v>
       </c>
       <c r="AG156" t="n">
-        <v>98.84162796020507</v>
+        <v>98.84162780761719</v>
       </c>
       <c r="AH156" t="n">
         <v>-0.03504411585789657</v>
       </c>
       <c r="AI156" t="n">
-        <v>0.08648553859194874</v>
+        <v>0.08648554026922328</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.1259432233608189</v>
+        <v>0.1259432250990065</v>
       </c>
       <c r="AK156" t="n">
         <v>129.0153350830078</v>
       </c>
       <c r="AL156" t="n">
-        <v>67.83415985107422</v>
+        <v>67.83416748046875</v>
       </c>
       <c r="AM156" t="n">
         <v>-0.1676183352889464</v>
       </c>
       <c r="AN156" t="n">
-        <v>0.583125664494359</v>
+        <v>0.5831254864382149</v>
       </c>
       <c r="AO156" t="n">
         <v>51.82119686088319</v>
@@ -30558,19 +30558,19 @@
         <v>-0.03898810913671968</v>
       </c>
       <c r="AU156" t="n">
-        <v>0.2337203994513923</v>
+        <v>0.2337205075847688</v>
       </c>
       <c r="AV156" t="n">
-        <v>0.583125664494359</v>
+        <v>0.5831254864382149</v>
       </c>
       <c r="AW156" t="n">
-        <v>1.241942876083068</v>
+        <v>1.241942697539056</v>
       </c>
       <c r="AX156" t="n">
         <v>0.4307727368275964</v>
       </c>
       <c r="AY156" t="n">
-        <v>2175.387126895251</v>
+        <v>2175.387455518768</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30685,10 +30685,10 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>1.332995653152466</v>
+        <v>1.332942366600037</v>
       </c>
       <c r="AA157" t="n">
-        <v>148076393633.666</v>
+        <v>148070474274.1436</v>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
@@ -30708,16 +30708,16 @@
         <v>1471.908000488281</v>
       </c>
       <c r="AG157" t="n">
-        <v>1336.069904785156</v>
+        <v>1336.069904174805</v>
       </c>
       <c r="AH157" t="n">
         <v>-0.08241549394534287</v>
       </c>
       <c r="AI157" t="n">
-        <v>0.01087523246256916</v>
+        <v>0.01087523292436332</v>
       </c>
       <c r="AJ157" t="n">
-        <v>0.1016699015647449</v>
+        <v>0.1016699020680165</v>
       </c>
       <c r="AK157" t="n">
         <v>1570.339965820312</v>
@@ -31100,28 +31100,28 @@
         <v>313.3447497558594</v>
       </c>
       <c r="AG159" t="n">
-        <v>305.2128067779541</v>
+        <v>305.2128056335449</v>
       </c>
       <c r="AH159" t="n">
         <v>-0.1120004397176056</v>
       </c>
       <c r="AI159" t="n">
-        <v>-0.08834100725520944</v>
+        <v>-0.08834100383690302</v>
       </c>
       <c r="AJ159" t="n">
-        <v>0.0266435182184912</v>
+        <v>0.02664352206793752</v>
       </c>
       <c r="AK159" t="n">
         <v>385.5466918945312</v>
       </c>
       <c r="AL159" t="n">
-        <v>192.3445129394531</v>
+        <v>192.3445281982422</v>
       </c>
       <c r="AM159" t="n">
         <v>-0.2782975295865927</v>
       </c>
       <c r="AN159" t="n">
-        <v>0.4466230190179041</v>
+        <v>0.4466229042565657</v>
       </c>
       <c r="AO159" t="n">
         <v>34.31523944580752</v>
@@ -31148,7 +31148,7 @@
         <v>0.3281723517679354</v>
       </c>
       <c r="AW159" t="n">
-        <v>3.459853741464156</v>
+        <v>3.459852923400096</v>
       </c>
       <c r="AX159" t="n">
         <v>0.1583696426396894</v>
@@ -32578,16 +32578,16 @@
         <v>365.3192327880859</v>
       </c>
       <c r="AG5" t="n">
-        <v>367.0558517456055</v>
+        <v>367.0558497619629</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.1001021285109809</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.1043597358915123</v>
+        <v>-0.1043597310512948</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.004731211746824782</v>
+        <v>-0.004731206368194907</v>
       </c>
       <c r="AK5" t="n">
         <v>479.9351196289062</v>
@@ -32623,16 +32623,16 @@
         <v>-0.1745616950860105</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.064818993850148</v>
+        <v>-0.06481891266516648</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.294499853948911</v>
+        <v>6.294499236522334</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.04907119528243098</v>
+        <v>-0.0490711113402309</v>
       </c>
       <c r="AY5" t="n">
-        <v>289.0239285749967</v>
+        <v>289.023959075854</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32647,7 +32647,7 @@
         <v>0.125</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.006133899410303872</v>
+        <v>-0.006133888917528862</v>
       </c>
     </row>
     <row r="6">
@@ -32980,16 +32980,16 @@
         <v>308.8933575439453</v>
       </c>
       <c r="AG7" t="n">
-        <v>281.5233889007569</v>
+        <v>281.5233882141113</v>
       </c>
       <c r="AH7" t="n">
         <v>-0.1455303392082288</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.06245799515275485</v>
+        <v>-0.06245799286605669</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09722094050536212</v>
+        <v>0.09722094318152297</v>
       </c>
       <c r="AK7" t="n">
         <v>432.8701477050781</v>
@@ -33025,7 +33025,7 @@
         <v>0.00473674990230033</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.8624649016060577</v>
+        <v>0.8624647010706799</v>
       </c>
       <c r="AW7" t="n">
         <v>4.025986471951604</v>
@@ -33182,28 +33182,28 @@
         <v>240.9960021972656</v>
       </c>
       <c r="AG8" t="n">
-        <v>175.7845223236084</v>
+        <v>175.7845219039917</v>
       </c>
       <c r="AH8" t="n">
         <v>-0.05463161316441256</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.2960754383803699</v>
+        <v>0.2960754414742424</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3709739572725688</v>
+        <v>0.3709739605452322</v>
       </c>
       <c r="AK8" t="n">
         <v>316.2828369140625</v>
       </c>
       <c r="AL8" t="n">
-        <v>73.65883636474609</v>
+        <v>73.65884399414062</v>
       </c>
       <c r="AM8" t="n">
         <v>-0.2796637210733044</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.093043728017628</v>
+        <v>2.093043407648076</v>
       </c>
       <c r="AO8" t="n">
         <v>38.38726800471698</v>
@@ -33230,13 +33230,13 @@
         <v>1.586582520681004</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.655933648444295</v>
+        <v>2.655933872236936</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.553016969937595</v>
+        <v>1.553017188203852</v>
       </c>
       <c r="AY8" t="n">
-        <v>17.78754237767324</v>
+        <v>17.7875438551789</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33251,7 +33251,7 @@
         <v>0.125</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.1941271212421994</v>
+        <v>0.1941271485254815</v>
       </c>
     </row>
     <row r="9">
@@ -33503,7 +33503,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6076122812888575</v>
+        <v>0.6076123190649145</v>
       </c>
     </row>
     <row r="5">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5328025001890807</v>
+        <v>0.5328024852702812</v>
       </c>
     </row>
   </sheetData>
@@ -33699,22 +33699,22 @@
         <v>0.3957882208439474</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.166283970277992</v>
+        <v>4.1662837257975</v>
       </c>
       <c r="R2" t="n">
-        <v>1.465742503194325</v>
+        <v>1.465741962976068</v>
       </c>
       <c r="S2" t="n">
-        <v>5.129987997302782</v>
+        <v>5.12998734832561</v>
       </c>
       <c r="T2" t="n">
-        <v>1300.294284258717</v>
+        <v>1300.294364291179</v>
       </c>
       <c r="U2" t="n">
-        <v>330.5608032359188</v>
+        <v>330.5607422713518</v>
       </c>
       <c r="V2" t="n">
-        <v>3914.557141352328</v>
+        <v>3914.557443907483</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33756,40 +33756,40 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2900332883747761</v>
+        <v>0.2900332885456365</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08811125319243907</v>
+        <v>0.08811120175762355</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07397678579465548</v>
+        <v>0.07397677534465799</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07670727853837987</v>
+        <v>0.0767072733131582</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02106386422556517</v>
+        <v>0.02106383287423519</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1188931145495951</v>
+        <v>0.1188930968094591</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5868502530312489</v>
+        <v>0.5868502724229876</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4900212772511564</v>
+        <v>0.4900210305613186</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9704873850068333</v>
+        <v>0.9704875625777368</v>
       </c>
       <c r="T3" t="n">
-        <v>1236.672210823231</v>
+        <v>1236.672301414994</v>
       </c>
       <c r="U3" t="n">
-        <v>12.502743464985</v>
+        <v>12.50274252146874</v>
       </c>
       <c r="V3" t="n">
-        <v>3167.027801599513</v>
+        <v>3167.027975741238</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33807,10 +33807,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>219.6727477189552</v>
+        <v>219.6718917369358</v>
       </c>
       <c r="D4" t="n">
-        <v>31.38182110270788</v>
+        <v>31.38169881956226</v>
       </c>
       <c r="E4" t="n">
         <v>16.24862293224463</v>
@@ -33822,7 +33822,7 @@
         <v>65</v>
       </c>
       <c r="H4" t="n">
-        <v>71.05239674572013</v>
+        <v>71.05243981291825</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -33831,40 +33831,40 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="K4" t="n">
-        <v>2.399122464779357</v>
+        <v>2.399122504026472</v>
       </c>
       <c r="L4" t="n">
-        <v>1.736774236372788</v>
+        <v>1.736774423652294</v>
       </c>
       <c r="M4" t="n">
-        <v>2.367421296822311</v>
+        <v>2.367413757410097</v>
       </c>
       <c r="N4" t="n">
-        <v>3.640890174386882</v>
+        <v>3.640890186031581</v>
       </c>
       <c r="O4" t="n">
         <v>3.280059203070169</v>
       </c>
       <c r="P4" t="n">
-        <v>3.721453115680187</v>
+        <v>3.721448191054021</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.588052085807322</v>
+        <v>4.588052232765038</v>
       </c>
       <c r="R4" t="n">
-        <v>5.377455321758561</v>
+        <v>5.377455942363119</v>
       </c>
       <c r="S4" t="n">
-        <v>6.048506067785623</v>
+        <v>6.048514254131621</v>
       </c>
       <c r="T4" t="n">
-        <v>39.39098161022488</v>
+        <v>39.39098884681499</v>
       </c>
       <c r="U4" t="n">
         <v>27.25290808338079</v>
       </c>
       <c r="V4" t="n">
-        <v>60.38130406528144</v>
+        <v>60.38149734530567</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33882,10 +33882,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>1366.828579368077</v>
+        <v>1366.822660008554</v>
       </c>
       <c r="D5" t="n">
-        <v>85.42678621050479</v>
+        <v>85.42641625053463</v>
       </c>
       <c r="E5" t="n">
         <v>35.867606016</v>
@@ -33897,7 +33897,7 @@
         <v>77.5</v>
       </c>
       <c r="H5" t="n">
-        <v>70.98404382824478</v>
+        <v>70.9840913973306</v>
       </c>
       <c r="I5" t="n">
         <v>8</v>
@@ -33906,40 +33906,40 @@
         <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4182082986720934</v>
+        <v>0.4182082852420556</v>
       </c>
       <c r="L5" t="n">
         <v>0.2163400049119362</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8085253772503654</v>
+        <v>0.8085282774892125</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4484376281501962</v>
+        <v>0.4484376170216872</v>
       </c>
       <c r="O5" t="n">
         <v>0.33489092230122</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7868419773181007</v>
+        <v>0.7868443571786727</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.978972026158082</v>
+        <v>5.978972089030883</v>
       </c>
       <c r="R5" t="n">
-        <v>3.954905215625992</v>
+        <v>3.954905158470544</v>
       </c>
       <c r="S5" t="n">
-        <v>5.07668018298479</v>
+        <v>5.076664647186486</v>
       </c>
       <c r="T5" t="n">
-        <v>225.5032178571431</v>
+        <v>225.5032282546382</v>
       </c>
       <c r="U5" t="n">
-        <v>36.06650516229598</v>
+        <v>36.06650327329697</v>
       </c>
       <c r="V5" t="n">
-        <v>752.0940415211342</v>
+        <v>752.0973458135502</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>3802.215082957361</v>
+        <v>3804.373514827844</v>
       </c>
       <c r="D6" t="n">
-        <v>253.4810055304908</v>
+        <v>253.6249009885229</v>
       </c>
       <c r="E6" t="n">
         <v>49.706745856</v>
@@ -33972,7 +33972,7 @@
         <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>58.28970699213692</v>
+        <v>58.29356910787804</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -33981,40 +33981,40 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3987544075735375</v>
+        <v>0.3987543959725403</v>
       </c>
       <c r="L6" t="n">
         <v>0.3305600979388537</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3644827309195925</v>
+        <v>0.3645127365270809</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6576300666770625</v>
+        <v>0.6576300425130435</v>
       </c>
       <c r="O6" t="n">
-        <v>0.620584860384825</v>
+        <v>0.6205847627336651</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5334925058692286</v>
+        <v>0.5335420616005796</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.263491360222614</v>
+        <v>3.263491637443478</v>
       </c>
       <c r="R6" t="n">
-        <v>2.206158806682194</v>
+        <v>2.206158598026663</v>
       </c>
       <c r="S6" t="n">
-        <v>3.216451123296844</v>
+        <v>3.21540466035765</v>
       </c>
       <c r="T6" t="n">
-        <v>713.4389629549161</v>
+        <v>713.4390258150728</v>
       </c>
       <c r="U6" t="n">
-        <v>35.96398397291571</v>
+        <v>35.96399945937308</v>
       </c>
       <c r="V6" t="n">
-        <v>901.0443236188416</v>
+        <v>901.0627016861089</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34032,10 +34032,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>422.0214048082378</v>
+        <v>421.9936449083692</v>
       </c>
       <c r="D7" t="n">
-        <v>105.5053512020594</v>
+        <v>105.4984112270923</v>
       </c>
       <c r="E7" t="n">
         <v>87.62486784000001</v>
@@ -34047,7 +34047,7 @@
         <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>58.14703035491092</v>
+        <v>58.14617991020576</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
         <v>0.03959296998582296</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07750164302424808</v>
+        <v>0.07749746509919718</v>
       </c>
       <c r="N7" t="n">
         <v>0.07121918091592699</v>
@@ -34071,25 +34071,25 @@
         <v>0.08148288444260898</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08334053124746235</v>
+        <v>0.08333705574551073</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9892722940449501</v>
+        <v>0.9892724127012199</v>
       </c>
       <c r="R7" t="n">
-        <v>1.121941116231228</v>
+        <v>1.121941241372881</v>
       </c>
       <c r="S7" t="n">
-        <v>1.004345732124902</v>
+        <v>1.004339009302197</v>
       </c>
       <c r="T7" t="n">
-        <v>78.95539113562253</v>
+        <v>78.95539460293016</v>
       </c>
       <c r="U7" t="n">
-        <v>64.79789783113056</v>
+        <v>64.79790619385122</v>
       </c>
       <c r="V7" t="n">
-        <v>62.41422896336589</v>
+        <v>62.41635917896895</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34131,40 +34131,40 @@
         <v>0.2307692307692308</v>
       </c>
       <c r="K8" t="n">
-        <v>1.234166842145029</v>
+        <v>1.234166854152989</v>
       </c>
       <c r="L8" t="n">
         <v>0.9086113398515112</v>
       </c>
       <c r="M8" t="n">
-        <v>1.203815135181199</v>
+        <v>1.203815140021953</v>
       </c>
       <c r="N8" t="n">
-        <v>2.974336140948177</v>
+        <v>2.974336083568881</v>
       </c>
       <c r="O8" t="n">
         <v>2.257494202916325</v>
       </c>
       <c r="P8" t="n">
-        <v>2.638651875751606</v>
+        <v>2.638651764385378</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.966730103136669</v>
+        <v>5.96673030952863</v>
       </c>
       <c r="R8" t="n">
         <v>4.95438144158981</v>
       </c>
       <c r="S8" t="n">
-        <v>7.668118232640569</v>
+        <v>7.668119021058042</v>
       </c>
       <c r="T8" t="n">
-        <v>249.2032075472979</v>
+        <v>249.2031973469495</v>
       </c>
       <c r="U8" t="n">
-        <v>42.28319480241998</v>
+        <v>42.28318614353945</v>
       </c>
       <c r="V8" t="n">
-        <v>338.1360294247397</v>
+        <v>338.1359961549018</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34215,13 +34215,13 @@
         <v>0.5950358849851035</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1582034889544438</v>
+        <v>-0.1582034377430722</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1582034889544438</v>
+        <v>-0.1582034377430722</v>
       </c>
       <c r="P9" t="n">
-        <v>0.481218693918916</v>
+        <v>0.4812187906470521</v>
       </c>
       <c r="Q9" t="n">
         <v>0.1594180924988078</v>
@@ -34257,13 +34257,13 @@
         <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>1532.570184254937</v>
+        <v>1532.53631412113</v>
       </c>
       <c r="D10" t="n">
-        <v>69.66228110249715</v>
+        <v>69.66074155096045</v>
       </c>
       <c r="E10" t="n">
-        <v>42.58641945510473</v>
+        <v>42.58419824409278</v>
       </c>
       <c r="F10" t="n">
         <v>26.36363636363636</v>
@@ -34272,7 +34272,7 @@
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>39.60016656902627</v>
+        <v>39.60067033889107</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -34281,40 +34281,40 @@
         <v>0.08695652173913043</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2503070939216359</v>
+        <v>0.2503070825789111</v>
       </c>
       <c r="L10" t="n">
         <v>0.2210285606476023</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3409143312779681</v>
+        <v>0.3409191051427964</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3547858501642981</v>
+        <v>0.3547858277919944</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2282701249689947</v>
+        <v>0.2282700539317738</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3847426821236094</v>
+        <v>0.3847473823924816</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.350778661031673</v>
+        <v>2.350778756419848</v>
       </c>
       <c r="R10" t="n">
-        <v>1.394789713107861</v>
+        <v>1.394790092545235</v>
       </c>
       <c r="S10" t="n">
-        <v>2.166426770022835</v>
+        <v>2.166460863442822</v>
       </c>
       <c r="T10" t="n">
-        <v>167.8762186555836</v>
+        <v>167.8762132440139</v>
       </c>
       <c r="U10" t="n">
-        <v>22.19539771164269</v>
+        <v>22.19539583566586</v>
       </c>
       <c r="V10" t="n">
-        <v>346.6180673427367</v>
+        <v>346.6255031797667</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34356,40 +34356,40 @@
         <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3430829058634619</v>
+        <v>0.3430829142576819</v>
       </c>
       <c r="L11" t="n">
         <v>0.3401171766271127</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1910505094152994</v>
+        <v>0.1910505603579166</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2457371557006567</v>
+        <v>0.2457371638191549</v>
       </c>
       <c r="O11" t="n">
         <v>0.2086208745702655</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1334031090205587</v>
+        <v>0.1334031582898824</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.286591869321926</v>
+        <v>1.286591793574443</v>
       </c>
       <c r="R11" t="n">
         <v>0.3655894545535642</v>
       </c>
       <c r="S11" t="n">
-        <v>4.507877509321299</v>
+        <v>4.507877122774336</v>
       </c>
       <c r="T11" t="n">
-        <v>52.46327708976651</v>
+        <v>52.46327879495203</v>
       </c>
       <c r="U11" t="n">
         <v>7.553431419467353</v>
       </c>
       <c r="V11" t="n">
-        <v>194.7781065367695</v>
+        <v>194.7781239095795</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34440,31 +34440,31 @@
         <v>-0.04868310009117446</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05300954353146931</v>
+        <v>-0.05300955409140599</v>
       </c>
       <c r="O12" t="n">
         <v>0.04052513254044099</v>
       </c>
       <c r="P12" t="n">
-        <v>0.156706257014609</v>
+        <v>0.1567062322967272</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5403350023541358</v>
+        <v>0.5403350157813664</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4725011306737067</v>
+        <v>0.4725012612352718</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7930391139332144</v>
+        <v>0.7930392246898001</v>
       </c>
       <c r="T12" t="n">
-        <v>14.94553921869982</v>
+        <v>14.94553665567168</v>
       </c>
       <c r="U12" t="n">
-        <v>2.781404806729866</v>
+        <v>2.781405231578975</v>
       </c>
       <c r="V12" t="n">
-        <v>2.576893684165253</v>
+        <v>2.576893216284561</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34482,10 +34482,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>3026.159113759547</v>
+        <v>3026.154274328148</v>
       </c>
       <c r="D13" t="n">
-        <v>144.1028149409308</v>
+        <v>144.1025844918166</v>
       </c>
       <c r="E13" t="n">
         <v>51.17161472</v>
@@ -34497,7 +34497,7 @@
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>28.09543975593739</v>
+        <v>28.09545270217932</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
@@ -34506,40 +34506,40 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3825644109259245</v>
+        <v>0.3825644187545661</v>
       </c>
       <c r="L13" t="n">
         <v>0.2262506291906492</v>
       </c>
       <c r="M13" t="n">
-        <v>0.211132546450102</v>
+        <v>0.21113262966837</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6802035422716275</v>
+        <v>0.6802035428296398</v>
       </c>
       <c r="O13" t="n">
         <v>0.5354142688997281</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3382339253560182</v>
+        <v>0.338234161611599</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.367918867796583</v>
+        <v>4.367918884480967</v>
       </c>
       <c r="R13" t="n">
-        <v>3.051780058052511</v>
+        <v>3.051780532488825</v>
       </c>
       <c r="S13" t="n">
-        <v>5.785649072893371</v>
+        <v>5.785654564167903</v>
       </c>
       <c r="T13" t="n">
-        <v>160.5683436214312</v>
+        <v>160.5683480413954</v>
       </c>
       <c r="U13" t="n">
-        <v>24.15153946517184</v>
+        <v>24.15154514657925</v>
       </c>
       <c r="V13" t="n">
-        <v>269.4305105277439</v>
+        <v>269.4309482153637</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34557,10 +34557,10 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>1152.942534572253</v>
+        <v>1152.928008534191</v>
       </c>
       <c r="D14" t="n">
-        <v>60.68118603011857</v>
+        <v>60.68042150179954</v>
       </c>
       <c r="E14" t="n">
         <v>44.816048128</v>
@@ -34572,7 +34572,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>16.96596469384175</v>
+        <v>16.96611545612465</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -34581,40 +34581,40 @@
         <v>0.05263157894736842</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1110128876142678</v>
+        <v>-0.1110128965883982</v>
       </c>
       <c r="L14" t="n">
         <v>-0.0758928939967719</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06537530234903149</v>
+        <v>0.06537479973466895</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1414830732221749</v>
+        <v>-0.1414830549462019</v>
       </c>
       <c r="O14" t="n">
         <v>-0.06792869574304405</v>
       </c>
       <c r="P14" t="n">
-        <v>0.08732215644769363</v>
+        <v>0.0873191374236193</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.786010423336084</v>
+        <v>1.786010610029797</v>
       </c>
       <c r="R14" t="n">
-        <v>1.464769405490308</v>
+        <v>1.464769103288139</v>
       </c>
       <c r="S14" t="n">
-        <v>1.854774690403888</v>
+        <v>1.854723089563496</v>
       </c>
       <c r="T14" t="n">
-        <v>72.53506578247735</v>
+        <v>72.53506298347045</v>
       </c>
       <c r="U14" t="n">
         <v>12.4304019940463</v>
       </c>
       <c r="V14" t="n">
-        <v>105.2377996888194</v>
+        <v>105.2390474039542</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -882,7 +882,7 @@
         <v>0.1160773007091094</v>
       </c>
       <c r="AY2" t="n">
-        <v>8886.85414527246</v>
+        <v>8886.856389465855</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1069,7 +1069,7 @@
         <v>0.9714228817909936</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.9920946440810863</v>
+        <v>0.9920944769167706</v>
       </c>
       <c r="AW3" t="n">
         <v>2.321801128444322</v>
@@ -1078,7 +1078,7 @@
         <v>1.402865167333821</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.798873688173166</v>
+        <v>2.798873992124058</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1464,13 +1464,13 @@
         <v>-0.1215261953866109</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.9346774680345606</v>
+        <v>0.9346776457859556</v>
       </c>
       <c r="AX5" t="n">
         <v>-0.009433477649823274</v>
       </c>
       <c r="AY5" t="n">
-        <v>15.97030692003074</v>
+        <v>15.97030521046742</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="X6" t="n">
-        <v>40303800320</v>
+        <v>43154300928</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>40303800320</v>
+        <v>43154300928</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -2039,16 +2039,16 @@
         <v>-0.2653380706521111</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.5435142200352776</v>
+        <v>-0.5435141696291974</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.3986775190761309</v>
+        <v>0.3986771641608369</v>
       </c>
       <c r="AX8" t="n">
         <v>-0.3467477757050076</v>
       </c>
       <c r="AY8" t="n">
-        <v>2519.553053364323</v>
+        <v>2519.554366556784</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -2190,28 +2190,28 @@
         <v>342.8769323730469</v>
       </c>
       <c r="AG9" t="n">
-        <v>340.9851292419434</v>
+        <v>340.9851293945313</v>
       </c>
       <c r="AH9" t="n">
         <v>-0.06610809528973316</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.06092681470611694</v>
+        <v>-0.06092681512634412</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.005548051715068336</v>
+        <v>0.005548051265094056</v>
       </c>
       <c r="AK9" t="n">
         <v>402.1211853027344</v>
       </c>
       <c r="AL9" t="n">
-        <v>252.4235382080078</v>
+        <v>252.4235229492188</v>
       </c>
       <c r="AM9" t="n">
         <v>-0.2036977827616566</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.2685425207502297</v>
+        <v>0.268542597432555</v>
       </c>
       <c r="AO9" t="n">
         <v>26.40184070951783</v>
@@ -2232,16 +2232,16 @@
         <v>-0.03983753638022014</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.08486838765788585</v>
+        <v>-0.08486846747247168</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2685425207502297</v>
+        <v>0.268542597432555</v>
       </c>
       <c r="AW9" t="n">
         <v>1.264053368150845</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.01803239322446326</v>
+        <v>0.01803229445144194</v>
       </c>
       <c r="AY9" t="n">
         <v>127.7358055738182</v>
@@ -2436,7 +2436,7 @@
         <v>-0.3731986293318776</v>
       </c>
       <c r="AY10" t="n">
-        <v>547.8482946773879</v>
+        <v>547.8481086155606</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2822,7 +2822,7 @@
         <v>-0.3543400022128416</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.1277181778304315</v>
+        <v>0.1277180804531868</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>18510585856</v>
+        <v>18589159424</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>18510585856</v>
+        <v>18589159424</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="X20" t="n">
-        <v>29893652480</v>
+        <v>29847484416</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>29893652480</v>
+        <v>29847484416</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
@@ -4710,16 +4710,16 @@
         <v>233.0399990844727</v>
       </c>
       <c r="AG22" t="n">
-        <v>248.1531408691406</v>
+        <v>248.1531405639649</v>
       </c>
       <c r="AH22" t="n">
         <v>0.08805354683632216</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.02178838708434627</v>
+        <v>0.02178838834092933</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0.06090248034635037</v>
+        <v>-0.06090247919145941</v>
       </c>
       <c r="AK22" t="n">
         <v>326.8851013183594</v>
@@ -4758,13 +4758,13 @@
         <v>-0.08718679447389377</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.25649934996316</v>
+        <v>1.256498737133701</v>
       </c>
       <c r="AX22" t="n">
         <v>-0.1124348051996886</v>
       </c>
       <c r="AY22" t="n">
-        <v>175.7649166651292</v>
+        <v>175.7648285252319</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
@@ -4906,16 +4906,16 @@
         <v>356.4269775390625</v>
       </c>
       <c r="AG23" t="n">
-        <v>366.7394583129883</v>
+        <v>366.7394589233398</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.09748696662410505</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.1228650602378097</v>
+        <v>-0.1228650616975946</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.02811936523373704</v>
+        <v>-0.02811936685120375</v>
       </c>
       <c r="AK23" t="n">
         <v>479.9350891113281</v>
@@ -4954,13 +4954,13 @@
         <v>-0.05872438737176666</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.981361809007367</v>
+        <v>5.981362386992085</v>
       </c>
       <c r="AX23" t="n">
         <v>-0.06952160931791018</v>
       </c>
       <c r="AY23" t="n">
-        <v>282.7868132101579</v>
+        <v>282.7867236754153</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5294,16 +5294,16 @@
         <v>329.4667999267578</v>
       </c>
       <c r="AG25" t="n">
-        <v>294.1080097198486</v>
+        <v>294.1080096435547</v>
       </c>
       <c r="AH25" t="n">
         <v>0.05543262952027428</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.1823207784023186</v>
+        <v>0.182320778709022</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.1202238260718913</v>
+        <v>0.1202238263624862</v>
       </c>
       <c r="AK25" t="n">
         <v>348.2200012207031</v>
@@ -5345,10 +5345,10 @@
         <v>1.432688162952117</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.2865816052888606</v>
+        <v>0.2865817505610946</v>
       </c>
       <c r="AY25" t="n">
-        <v>3542.838049715371</v>
+        <v>3542.839126071033</v>
       </c>
       <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
@@ -5734,13 +5734,13 @@
         <v>1.278825980927513</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.7333000806352583</v>
+        <v>0.7332995534686115</v>
       </c>
       <c r="AX27" t="n">
         <v>1.208227443520347</v>
       </c>
       <c r="AY27" t="n">
-        <v>478.1190350538134</v>
+        <v>478.119153061093</v>
       </c>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
@@ -5882,28 +5882,28 @@
         <v>175.8644390869141</v>
       </c>
       <c r="AG28" t="n">
-        <v>168.1166789245605</v>
+        <v>168.1166788864136</v>
       </c>
       <c r="AH28" t="n">
         <v>0.0002590891906963932</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.04635664222849623</v>
+        <v>0.04635664246592253</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.04608561275368883</v>
+        <v>0.04608561299105363</v>
       </c>
       <c r="AK28" t="n">
-        <v>248.7424926757812</v>
+        <v>248.7425079345703</v>
       </c>
       <c r="AL28" t="n">
-        <v>122.9443130493164</v>
+        <v>122.9443054199219</v>
       </c>
       <c r="AM28" t="n">
-        <v>-0.2928027625284113</v>
+        <v>-0.2928028059105159</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.430810415700537</v>
+        <v>0.4308105044904744</v>
       </c>
       <c r="AO28" t="n">
         <v>43.84461914453072</v>
@@ -5927,10 +5927,10 @@
         <v>0.1814232555479847</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.05612715991464468</v>
+        <v>0.05612725666709961</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.5071788300145195</v>
+        <v>0.507178928535593</v>
       </c>
       <c r="AX28" t="n">
         <v>0.03283859365482411</v>
@@ -6078,16 +6078,16 @@
         <v>222.3939306640625</v>
       </c>
       <c r="AG29" t="n">
-        <v>203.3622362518311</v>
+        <v>203.3622360229492</v>
       </c>
       <c r="AH29" t="n">
         <v>-0.05141293162117289</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.03736077357365164</v>
+        <v>0.03736077474118926</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.09358519439500945</v>
+        <v>0.0935851956258269</v>
       </c>
       <c r="AK29" t="n">
         <v>239.2400054931641</v>
@@ -6123,16 +6123,16 @@
         <v>-0.02385758370230717</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.1608773832329724</v>
+        <v>0.1608772857581162</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.535109549989327</v>
+        <v>8.535107905953616</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.1196909742888101</v>
+        <v>0.119691064969816</v>
       </c>
       <c r="AY29" t="n">
-        <v>5622.037663799632</v>
+        <v>5622.036547111539</v>
       </c>
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
@@ -6710,7 +6710,7 @@
         <v>3.237804976621604</v>
       </c>
       <c r="AY32" t="n">
-        <v>11.11339707784952</v>
+        <v>11.11340009806936</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6896,13 +6896,13 @@
         <v>5.752929679616819</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.882312226068093</v>
+        <v>7.882311671298845</v>
       </c>
       <c r="AX33" t="n">
         <v>3.964482786668068</v>
       </c>
       <c r="AY33" t="n">
-        <v>148.0491180665753</v>
+        <v>148.049137593292</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7094,7 +7094,7 @@
         <v>5.331332969630842</v>
       </c>
       <c r="AY34" t="n">
-        <v>42.14745436530509</v>
+        <v>42.14745076397037</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7284,7 +7284,7 @@
         <v>2.048299997400229</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.116724504424774</v>
+        <v>6.116723880213446</v>
       </c>
       <c r="AX35" t="n">
         <v>1.317864904827309</v>
@@ -7428,16 +7428,16 @@
         <v>10348.38056640625</v>
       </c>
       <c r="AG36" t="n">
-        <v>7604.882171630859</v>
+        <v>7604.882159423828</v>
       </c>
       <c r="AH36" t="n">
         <v>-0.1774558400343003</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.119280983964885</v>
+        <v>0.1192809857615069</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.3607548851985762</v>
+        <v>0.3607548873828017</v>
       </c>
       <c r="AK36" t="n">
         <v>13194.7333984375</v>
@@ -7479,10 +7479,10 @@
         <v>5.097864838393732</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.385848411934487</v>
+        <v>1.385848248669108</v>
       </c>
       <c r="AY36" t="n">
-        <v>23.63014682565929</v>
+        <v>23.63014900062538</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="X37" t="n">
-        <v>1253680349184</v>
+        <v>596738375680</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>0.006376981735229492</v>
       </c>
       <c r="AA37" t="n">
-        <v>7994696688.5625</v>
+        <v>3805389722.421875</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
@@ -7620,16 +7620,16 @@
         <v>2414.405009765625</v>
       </c>
       <c r="AG37" t="n">
-        <v>2361.17020324707</v>
+        <v>2361.170200805664</v>
       </c>
       <c r="AH37" t="n">
         <v>-0.1190376132434899</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.09917548634361073</v>
+        <v>-0.0991754854121748</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.0225459420271128</v>
+        <v>0.02254594308440638</v>
       </c>
       <c r="AK37" t="n">
         <v>2857.67724609375</v>
@@ -7668,13 +7668,13 @@
         <v>0.08542987034183058</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.49650623629246</v>
+        <v>1.496506415137917</v>
       </c>
       <c r="AX37" t="n">
         <v>-0.06993096054948023</v>
       </c>
       <c r="AY37" t="n">
-        <v>2.691121537941887</v>
+        <v>2.69112075602757</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="X38" t="n">
-        <v>9741389824</v>
+        <v>9764182016</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>9741389824</v>
+        <v>9764182016</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
@@ -7816,16 +7816,16 @@
         <v>49.486376953125</v>
       </c>
       <c r="AG38" t="n">
-        <v>57.41132287979126</v>
+        <v>57.41132307052612</v>
       </c>
       <c r="AH38" t="n">
         <v>-0.205842058829914</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.3154660567681481</v>
+        <v>-0.3154660590423422</v>
       </c>
       <c r="AJ38" t="n">
-        <v>-0.1380380302899418</v>
+        <v>-0.1380380331535964</v>
       </c>
       <c r="AK38" t="n">
         <v>93.37815856933594</v>
@@ -7861,16 +7861,16 @@
         <v>-0.4787540176470368</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.2374588672683362</v>
+        <v>0.2374587929494729</v>
       </c>
       <c r="AW38" t="n">
         <v>0.8725806519041515</v>
       </c>
       <c r="AX38" t="n">
-        <v>-0.07986593281671839</v>
+        <v>-0.07986585063602603</v>
       </c>
       <c r="AY38" t="n">
-        <v>2.183306999561387</v>
+        <v>2.183307491368331</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8008,16 +8008,16 @@
         <v>169.4599017333984</v>
       </c>
       <c r="AG39" t="n">
-        <v>154.3384281921387</v>
+        <v>154.3384287261963</v>
       </c>
       <c r="AH39" t="n">
         <v>0.03151247736919305</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.1325760220529533</v>
+        <v>0.132576018133898</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.09797607581201206</v>
+        <v>0.09797607201268277</v>
       </c>
       <c r="AK39" t="n">
         <v>178.1000061035156</v>
@@ -8056,13 +8056,13 @@
         <v>0.180086110685896</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.7776913771510723</v>
+        <v>0.7776915150819195</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.1319948703131528</v>
+        <v>0.1319947584550347</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.9302867427147457</v>
+        <v>0.9302869053416258</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8248,13 +8248,13 @@
         <v>0.2311243782931438</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.9907556155908053</v>
+        <v>0.9907554467624049</v>
       </c>
       <c r="AX40" t="n">
         <v>0.07911974572058256</v>
       </c>
       <c r="AY40" t="n">
-        <v>3.441787036698018</v>
+        <v>3.441789137888003</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8570,16 +8570,16 @@
         <v>1030.347784423828</v>
       </c>
       <c r="AG42" t="n">
-        <v>998.942311706543</v>
+        <v>998.9423114013672</v>
       </c>
       <c r="AH42" t="n">
         <v>-0.07309935175827165</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.04395877709359464</v>
+        <v>-0.04395877680152505</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.03143872508877288</v>
+        <v>0.03143872540387616</v>
       </c>
       <c r="AK42" t="n">
         <v>1110.633178710938</v>
@@ -8615,10 +8615,10 @@
         <v>-0.1151632732645514</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.1725348065092747</v>
+        <v>0.1725347186445632</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.3741573224151644</v>
+        <v>0.3741575637755652</v>
       </c>
       <c r="AX42" t="n">
         <v>0.2689210991868942</v>
@@ -8762,25 +8762,25 @@
         <v>2.143829426765442</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.176732683181763</v>
+        <v>2.176732722520828</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.006450752168930318</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.02146913541654316</v>
+        <v>-0.02146915310107089</v>
       </c>
       <c r="AJ43" t="n">
-        <v>-0.01511589212150088</v>
+        <v>-0.01511590992084777</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.306842565536499</v>
+        <v>2.306842803955078</v>
       </c>
       <c r="AL43" t="n">
         <v>2.029999971389771</v>
       </c>
       <c r="AM43" t="n">
-        <v>-0.07665995666004766</v>
+        <v>-0.07666005208979287</v>
       </c>
       <c r="AN43" t="n">
         <v>0.04926115490666039</v>
@@ -8804,19 +8804,19 @@
         <v>-0.0235474561964284</v>
       </c>
       <c r="AU43" t="n">
-        <v>-0.06886799502763574</v>
+        <v>-0.06886809207481848</v>
       </c>
       <c r="AV43" t="n">
         <v>-0.05874650659572012</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.1428636487490869</v>
+        <v>0.1428637218494173</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.008486014810537013</v>
+        <v>0.008485900969149585</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.9524989672318</v>
+        <v>2.952498092904765</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -9003,16 +9003,16 @@
         <v>-0.1101707632060175</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.01092790546330846</v>
+        <v>0.01092799593210403</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.3847797717739894</v>
+        <v>0.3847795171431503</v>
       </c>
       <c r="AX44" t="n">
         <v>0.1346103027561942</v>
       </c>
       <c r="AY44" t="n">
-        <v>33.04572285902785</v>
+        <v>33.0457132394797</v>
       </c>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
@@ -9154,16 +9154,16 @@
         <v>115.3188851928711</v>
       </c>
       <c r="AG45" t="n">
-        <v>113.2601615524292</v>
+        <v>113.2601615142822</v>
       </c>
       <c r="AH45" t="n">
         <v>-0.04647015187005743</v>
       </c>
       <c r="AI45" t="n">
-        <v>-0.02913789299540126</v>
+        <v>-0.02913789266840683</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.01817694423373117</v>
+        <v>0.01817694457666175</v>
       </c>
       <c r="AK45" t="n">
         <v>132.0340881347656</v>
@@ -9199,16 +9199,16 @@
         <v>-0.01044782616337636</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.09361901156569941</v>
+        <v>0.09361892858302712</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.953088523849854</v>
+        <v>1.953088826386736</v>
       </c>
       <c r="AX45" t="n">
         <v>0.3512930672789891</v>
       </c>
       <c r="AY45" t="n">
-        <v>95.17900920988204</v>
+        <v>95.17902926688581</v>
       </c>
       <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="X49" t="n">
-        <v>10697365504</v>
+        <v>10701580288</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>10697365504</v>
+        <v>10701580288</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
@@ -9939,13 +9939,13 @@
         <v>16.86722755432129</v>
       </c>
       <c r="AL49" t="n">
-        <v>12.96543407440186</v>
+        <v>12.96543312072754</v>
       </c>
       <c r="AM49" t="n">
         <v>-0.1107015096765512</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.1569223146655048</v>
+        <v>0.1569223997630935</v>
       </c>
       <c r="AO49" t="n">
         <v>75</v>
@@ -9969,16 +9969,16 @@
         <v>0.06053001148141535</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.1089234672302055</v>
+        <v>0.1089233890472749</v>
       </c>
       <c r="AW49" t="n">
-        <v>-0.2303857642034729</v>
+        <v>-0.2303858395190773</v>
       </c>
       <c r="AX49" t="n">
         <v>0.04919278546548234</v>
       </c>
       <c r="AY49" t="n">
-        <v>6.606823785180294</v>
+        <v>6.606822865460581</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10120,28 +10120,28 @@
         <v>63.86712242126465</v>
       </c>
       <c r="AG50" t="n">
-        <v>63.69194074630737</v>
+        <v>63.69194068908691</v>
       </c>
       <c r="AH50" t="n">
         <v>0.02086949398136273</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.0236773473105738</v>
+        <v>0.02367734823023948</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.002750452771647316</v>
+        <v>0.002750453672512254</v>
       </c>
       <c r="AK50" t="n">
         <v>70.97299957275391</v>
       </c>
       <c r="AL50" t="n">
-        <v>55.35892868041992</v>
+        <v>55.35893249511719</v>
       </c>
       <c r="AM50" t="n">
         <v>-0.08134082903729967</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.1777684016364101</v>
+        <v>0.1777683204782357</v>
       </c>
       <c r="AO50" t="n">
         <v>71.41388665127502</v>
@@ -10162,19 +10162,19 @@
         <v>-0.06742168689424222</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.06429016252295949</v>
+        <v>0.06429022879534818</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.120401377693877</v>
+        <v>0.1204013042492986</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.1347205218132677</v>
+        <v>0.1347205971471501</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.1348246427850797</v>
+        <v>0.1348247181327877</v>
       </c>
       <c r="AY50" t="n">
-        <v>177.2147434398775</v>
+        <v>177.2147724747457</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10316,28 +10316,28 @@
         <v>118.9407997131348</v>
       </c>
       <c r="AG51" t="n">
-        <v>122.7445679855347</v>
+        <v>122.7445682144165</v>
       </c>
       <c r="AH51" t="n">
         <v>0.05077487000561942</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.01821209205496066</v>
+        <v>0.0182120901563001</v>
       </c>
       <c r="AJ51" t="n">
-        <v>-0.03098930025846991</v>
+        <v>-0.03098930206538442</v>
       </c>
       <c r="AK51" t="n">
         <v>131.1634063720703</v>
       </c>
       <c r="AL51" t="n">
-        <v>111.0921020507812</v>
+        <v>111.0920944213867</v>
       </c>
       <c r="AM51" t="n">
         <v>-0.0471427449634565</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.1250124990866053</v>
+        <v>0.1250125763483065</v>
       </c>
       <c r="AO51" t="n">
         <v>77.96183544960718</v>
@@ -10370,7 +10370,7 @@
         <v>0.0920590987564307</v>
       </c>
       <c r="AY51" t="n">
-        <v>169.2986563990142</v>
+        <v>169.2986149052185</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10512,28 +10512,28 @@
         <v>87.71539978027344</v>
       </c>
       <c r="AG52" t="n">
-        <v>91.29311790466309</v>
+        <v>91.29311809539794</v>
       </c>
       <c r="AH52" t="n">
         <v>0.05899305734611415</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.01749180575312326</v>
+        <v>0.01749180362732061</v>
       </c>
       <c r="AJ52" t="n">
-        <v>-0.03918935190849593</v>
+        <v>-0.03918935391587697</v>
       </c>
       <c r="AK52" t="n">
-        <v>97.49111175537109</v>
+        <v>97.49111938476562</v>
       </c>
       <c r="AL52" t="n">
-        <v>82.06204223632812</v>
+        <v>82.06203460693359</v>
       </c>
       <c r="AM52" t="n">
-        <v>-0.04719519844299203</v>
+        <v>-0.04719527300695014</v>
       </c>
       <c r="AN52" t="n">
-        <v>0.1319484241220465</v>
+        <v>0.1319485293604938</v>
       </c>
       <c r="AO52" t="n">
         <v>78.76105767909185</v>
@@ -10554,7 +10554,7 @@
         <v>-0.03226886398748108</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.007065009752385221</v>
+        <v>0.007064926454094067</v>
       </c>
       <c r="AV52" t="n">
         <v>-0.002005206503974177</v>
@@ -10566,7 +10566,7 @@
         <v>0.09169793215164845</v>
       </c>
       <c r="AY52" t="n">
-        <v>344.3543289079172</v>
+        <v>344.3540993131856</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10723,13 +10723,13 @@
         <v>116.6635665893555</v>
       </c>
       <c r="AL53" t="n">
-        <v>89.56781005859375</v>
+        <v>89.56781768798828</v>
       </c>
       <c r="AM53" t="n">
         <v>-0.07991844004120763</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.1984215787755736</v>
+        <v>0.198421476693919</v>
       </c>
       <c r="AO53" t="n">
         <v>72.60746886737398</v>
@@ -10756,13 +10756,13 @@
         <v>0.1499256596090359</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.512617406683196</v>
+        <v>1.51261718232022</v>
       </c>
       <c r="AX53" t="n">
         <v>0.1643305053333166</v>
       </c>
       <c r="AY53" t="n">
-        <v>199.9072740191544</v>
+        <v>199.9071619516729</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -11139,14 +11139,14 @@
         <v>-0.2720990528264806</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.3719401087219301</v>
+        <v>0.3719402496809276</v>
       </c>
       <c r="AW55" t="inlineStr"/>
       <c r="AX55" t="n">
-        <v>0.2015455919665643</v>
+        <v>0.2015454838473398</v>
       </c>
       <c r="AY55" t="n">
-        <v>5.235764244161746</v>
+        <v>5.235764972179359</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11288,16 +11288,16 @@
         <v>42.74780754089355</v>
       </c>
       <c r="AG56" t="n">
-        <v>44.91433706283569</v>
+        <v>44.91433702468872</v>
       </c>
       <c r="AH56" t="n">
         <v>0.0393515565136997</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.01078356688160209</v>
+        <v>-0.0107835660414336</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-0.04823692530318635</v>
+        <v>-0.04823692449482797</v>
       </c>
       <c r="AK56" t="n">
         <v>49.35155487060547</v>
@@ -11333,16 +11333,16 @@
         <v>-0.02822789098051126</v>
       </c>
       <c r="AV56" t="n">
-        <v>-0.03232670720954134</v>
+        <v>-0.03232678760679908</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.4915887402835746</v>
+        <v>0.4915890268156839</v>
       </c>
       <c r="AX56" t="n">
         <v>0.03967518948514859</v>
       </c>
       <c r="AY56" t="n">
-        <v>181.9268117129481</v>
+        <v>181.9265872586174</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11534,7 +11534,7 @@
         <v>-0.2025162294936794</v>
       </c>
       <c r="AY57" t="n">
-        <v>12.13614815601111</v>
+        <v>12.13614710916319</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11726,7 +11726,7 @@
         <v>-0.02942917067415307</v>
       </c>
       <c r="AY58" t="n">
-        <v>4.445496723644005</v>
+        <v>4.445497200214976</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -12060,25 +12060,25 @@
         <v>106.9736001586914</v>
       </c>
       <c r="AG60" t="n">
-        <v>136.0346382141113</v>
+        <v>136.0346380615234</v>
       </c>
       <c r="AH60" t="n">
         <v>-0.1370768355776074</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.3214228466333502</v>
+        <v>-0.3214228458722008</v>
       </c>
       <c r="AJ60" t="n">
-        <v>-0.2136296934144036</v>
+        <v>-0.2136296925323444</v>
       </c>
       <c r="AK60" t="n">
-        <v>182.8191986083984</v>
+        <v>182.8191833496094</v>
       </c>
       <c r="AL60" t="n">
         <v>92.30999755859375</v>
       </c>
       <c r="AM60" t="n">
-        <v>-0.4950749250557476</v>
+        <v>-0.4950748829127675</v>
       </c>
       <c r="AN60" t="n">
         <v>0</v>
@@ -12102,7 +12102,7 @@
         <v>-0.2737717960637812</v>
       </c>
       <c r="AU60" t="n">
-        <v>-0.4197853841185015</v>
+        <v>-0.4197854397663807</v>
       </c>
       <c r="AV60" t="n">
         <v>-0.4295177195148057</v>
@@ -12114,7 +12114,7 @@
         <v>-0.4390259779398469</v>
       </c>
       <c r="AY60" t="n">
-        <v>11.93078379061316</v>
+        <v>11.93077860831819</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12254,25 +12254,25 @@
         <v>145.0769290161133</v>
       </c>
       <c r="AG61" t="n">
-        <v>153.8022636413574</v>
+        <v>153.802264175415</v>
       </c>
       <c r="AH61" t="n">
         <v>-0.03389184887872687</v>
       </c>
       <c r="AI61" t="n">
-        <v>-0.08869999476119317</v>
+        <v>-0.08869999792555949</v>
       </c>
       <c r="AJ61" t="n">
-        <v>-0.0567308596028876</v>
+        <v>-0.05673086287826257</v>
       </c>
       <c r="AK61" t="n">
-        <v>200.306396484375</v>
+        <v>200.3064117431641</v>
       </c>
       <c r="AL61" t="n">
         <v>134.3016815185547</v>
       </c>
       <c r="AM61" t="n">
-        <v>-0.300271952757921</v>
+        <v>-0.3002720060612705</v>
       </c>
       <c r="AN61" t="n">
         <v>0.04362061649053373</v>
@@ -12302,13 +12302,13 @@
         <v>-0.2633421467907817</v>
       </c>
       <c r="AW61" t="n">
-        <v>6.901040935864919</v>
+        <v>6.901039236821379</v>
       </c>
       <c r="AX61" t="n">
         <v>-0.147988082348335</v>
       </c>
       <c r="AY61" t="n">
-        <v>11.38261504910467</v>
+        <v>11.38261713566429</v>
       </c>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
@@ -12446,16 +12446,16 @@
         <v>146.7067468261719</v>
       </c>
       <c r="AG62" t="n">
-        <v>186.1721834564209</v>
+        <v>186.1721838378906</v>
       </c>
       <c r="AH62" t="n">
         <v>-0.1330323574544965</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.3168152186860996</v>
+        <v>-0.316815220085956</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.2119835299642767</v>
+        <v>-0.2119835315789349</v>
       </c>
       <c r="AK62" t="n">
         <v>237.7264404296875</v>
@@ -12491,16 +12491,16 @@
         <v>-0.4255817471209397</v>
       </c>
       <c r="AV62" t="n">
-        <v>-0.3601494830202331</v>
+        <v>-0.3601495321363598</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.376182823159613</v>
+        <v>1.376183161845316</v>
       </c>
       <c r="AX62" t="n">
         <v>-0.2975688139147968</v>
       </c>
       <c r="AY62" t="n">
-        <v>7.990292025237297</v>
+        <v>7.990293237299094</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -12642,16 +12642,16 @@
         <v>274.1804876708985</v>
       </c>
       <c r="AG63" t="n">
-        <v>281.2667649078369</v>
+        <v>281.2667654418945</v>
       </c>
       <c r="AH63" t="n">
         <v>-0.07560892060101398</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.09889816867879664</v>
+        <v>-0.09889817038977133</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.02519415061093477</v>
+        <v>-0.02519415246185552</v>
       </c>
       <c r="AK63" t="n">
         <v>399.1984252929688</v>
@@ -12691,10 +12691,10 @@
       </c>
       <c r="AW63" t="inlineStr"/>
       <c r="AX63" t="n">
-        <v>-0.3049155111217459</v>
+        <v>-0.3049154529471995</v>
       </c>
       <c r="AY63" t="n">
-        <v>5.268862592238489</v>
+        <v>5.268862000751429</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12836,16 +12836,16 @@
         <v>80.47383087158204</v>
       </c>
       <c r="AG64" t="n">
-        <v>86.31172218322754</v>
+        <v>86.31172191619874</v>
       </c>
       <c r="AH64" t="n">
         <v>0.02020740885486183</v>
       </c>
       <c r="AI64" t="n">
-        <v>-0.04879665939425426</v>
+        <v>-0.04879665645144771</v>
       </c>
       <c r="AJ64" t="n">
-        <v>-0.06763729379947359</v>
+        <v>-0.06763729091495574</v>
       </c>
       <c r="AK64" t="n">
         <v>96.44304656982422</v>
@@ -12881,16 +12881,16 @@
         <v>-0.1213408939908385</v>
       </c>
       <c r="AV64" t="n">
-        <v>0.01452807239957554</v>
+        <v>0.01452816804740165</v>
       </c>
       <c r="AW64" t="n">
-        <v>0.1594991175812361</v>
+        <v>0.1594988677091909</v>
       </c>
       <c r="AX64" t="n">
         <v>0.03659211707227228</v>
       </c>
       <c r="AY64" t="n">
-        <v>237.0330674301737</v>
+        <v>237.0330262951771</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -12997,7 +12997,7 @@
         </is>
       </c>
       <c r="X65" t="n">
-        <v>5394561536</v>
+        <v>5464624640</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>5394561536</v>
+        <v>5464624640</v>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
@@ -13653,16 +13653,16 @@
         <v>0.9976206839797979</v>
       </c>
       <c r="AV68" t="n">
-        <v>0.8574918560348472</v>
+        <v>0.8574919781970853</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.663825280097184</v>
+        <v>1.663825782583993</v>
       </c>
       <c r="AX68" t="n">
         <v>1.045003792287627</v>
       </c>
       <c r="AY68" t="n">
-        <v>229.3111011388222</v>
+        <v>229.3111891736068</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13854,7 +13854,7 @@
         <v>1.006427957689156</v>
       </c>
       <c r="AY69" t="n">
-        <v>-0.5169078918926773</v>
+        <v>-0.5169078574862453</v>
       </c>
       <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
@@ -13996,16 +13996,16 @@
         <v>982.5951342773437</v>
       </c>
       <c r="AG70" t="n">
-        <v>731.8925280761719</v>
+        <v>731.8925250244141</v>
       </c>
       <c r="AH70" t="n">
         <v>-0.1069058280668479</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.1990148199759154</v>
+        <v>0.1990148249754236</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.3425401907847869</v>
+        <v>0.3425401963827501</v>
       </c>
       <c r="AK70" t="n">
         <v>1213.182495117188</v>
@@ -14038,19 +14038,19 @@
         <v>0.06965990050626236</v>
       </c>
       <c r="AU70" t="n">
-        <v>0.6734465299543735</v>
+        <v>0.6734463351799955</v>
       </c>
       <c r="AV70" t="n">
         <v>3.25014080027172</v>
       </c>
       <c r="AW70" t="n">
-        <v>12.36321529776144</v>
+        <v>12.36321685029212</v>
       </c>
       <c r="AX70" t="n">
         <v>1.784198183427027</v>
       </c>
       <c r="AY70" t="n">
-        <v>648.7800220670663</v>
+        <v>648.7798500022465</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14436,7 +14436,7 @@
         <v>0.7104503692431816</v>
       </c>
       <c r="AY72" t="n">
-        <v>3.058769573314202</v>
+        <v>3.058769166570963</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14574,28 +14574,28 @@
         <v>1633569.2275</v>
       </c>
       <c r="AG73" t="n">
-        <v>1473402.8340625</v>
+        <v>1473402.831875</v>
       </c>
       <c r="AH73" t="n">
         <v>-0.218276165770881</v>
       </c>
       <c r="AI73" t="n">
-        <v>-0.1332988029627807</v>
+        <v>-0.1332988016760255</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.108705093905572</v>
+        <v>0.1087050955516204</v>
       </c>
       <c r="AK73" t="n">
         <v>2918367.25</v>
       </c>
       <c r="AL73" t="n">
-        <v>410290.5</v>
+        <v>410290.53125</v>
       </c>
       <c r="AM73" t="n">
         <v>-0.5624265588917913</v>
       </c>
       <c r="AN73" t="n">
-        <v>2.112428876613034</v>
+        <v>2.112428639553207</v>
       </c>
       <c r="AO73" t="n">
         <v>17.37089201877934</v>
@@ -14616,19 +14616,19 @@
         <v>-0.3020344711346572</v>
       </c>
       <c r="AU73" t="n">
-        <v>0.1325269363150925</v>
+        <v>0.1325270618649559</v>
       </c>
       <c r="AV73" t="n">
-        <v>2.112428876613034</v>
+        <v>2.112428639553207</v>
       </c>
       <c r="AW73" t="n">
-        <v>12.07833817028723</v>
+        <v>12.07833712387159</v>
       </c>
       <c r="AX73" t="n">
         <v>0.8904693586116375</v>
       </c>
       <c r="AY73" t="n">
-        <v>-6.580703363369355</v>
+        <v>-6.5807041255134</v>
       </c>
       <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
@@ -14735,7 +14735,7 @@
         </is>
       </c>
       <c r="X74" t="n">
-        <v>6793761652736</v>
+        <v>20381284958208</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>0.006376981735229492</v>
       </c>
       <c r="AA74" t="n">
-        <v>43323693973</v>
+        <v>129971081919</v>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45644</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AE74" t="n">
         <v>12755</v>
@@ -14960,28 +14960,28 @@
         <v>822.6995861816406</v>
       </c>
       <c r="AG75" t="n">
-        <v>682.640249633789</v>
+        <v>682.6402485656738</v>
       </c>
       <c r="AH75" t="n">
         <v>-0.2336327854975101</v>
       </c>
       <c r="AI75" t="n">
-        <v>-0.07639493778368722</v>
+        <v>-0.07639493633853855</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.2051729833144005</v>
+        <v>0.2051729852001134</v>
       </c>
       <c r="AK75" t="n">
         <v>1092.384765625</v>
       </c>
       <c r="AL75" t="n">
-        <v>221.6932678222656</v>
+        <v>221.6932373046875</v>
       </c>
       <c r="AM75" t="n">
         <v>-0.4228315790602913</v>
       </c>
       <c r="AN75" t="n">
-        <v>1.843974453657506</v>
+        <v>1.843974845149884</v>
       </c>
       <c r="AO75" t="n">
         <v>17.31875981319119</v>
@@ -15005,16 +15005,16 @@
         <v>0.05972085396490967</v>
       </c>
       <c r="AV75" t="n">
-        <v>1.801141097888782</v>
+        <v>1.801140907994532</v>
       </c>
       <c r="AW75" t="n">
-        <v>7.943200757795065</v>
+        <v>7.943198822141021</v>
       </c>
       <c r="AX75" t="n">
         <v>1.199856593331356</v>
       </c>
       <c r="AY75" t="n">
-        <v>118.7016662844796</v>
+        <v>118.7017421405956</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15156,28 +15156,28 @@
         <v>302.2157531738281</v>
       </c>
       <c r="AG76" t="n">
-        <v>283.0159564971924</v>
+        <v>283.0159562683106</v>
       </c>
       <c r="AH76" t="n">
         <v>-0.2386233884665604</v>
       </c>
       <c r="AI76" t="n">
-        <v>-0.1869716147760797</v>
+        <v>-0.186971614118564</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.06783997946358267</v>
+        <v>0.06783998032717076</v>
       </c>
       <c r="AK76" t="n">
         <v>432.8701477050781</v>
       </c>
       <c r="AL76" t="n">
-        <v>138.9482116699219</v>
+        <v>138.9481964111328</v>
       </c>
       <c r="AM76" t="n">
         <v>-0.4684317980266759</v>
       </c>
       <c r="AN76" t="n">
-        <v>0.6560127211290001</v>
+        <v>0.656012902986336</v>
       </c>
       <c r="AO76" t="n">
         <v>6.247171146094061</v>
@@ -15204,7 +15204,7 @@
         <v>0.566780765164719</v>
       </c>
       <c r="AW76" t="n">
-        <v>3.256323235744476</v>
+        <v>3.256322635065287</v>
       </c>
       <c r="AX76" t="n">
         <v>0.247070551064049</v>
@@ -15350,16 +15350,16 @@
         <v>432.9542779541015</v>
       </c>
       <c r="AG77" t="n">
-        <v>414.4744064331055</v>
+        <v>414.4744065093994</v>
       </c>
       <c r="AH77" t="n">
         <v>-0.2062210008601241</v>
       </c>
       <c r="AI77" t="n">
-        <v>-0.1708293489450925</v>
+        <v>-0.1708293490977212</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.04458627899375167</v>
+        <v>0.04458627880147059</v>
       </c>
       <c r="AK77" t="n">
         <v>745.990478515625</v>
@@ -15395,16 +15395,16 @@
         <v>-0.1418911211465552</v>
       </c>
       <c r="AV77" t="n">
-        <v>1.738714491509626</v>
+        <v>1.738714324999011</v>
       </c>
       <c r="AW77" t="n">
-        <v>7.247359735384448</v>
+        <v>7.247358980382147</v>
       </c>
       <c r="AX77" t="n">
-        <v>0.8328959986562579</v>
+        <v>0.8328958494956857</v>
       </c>
       <c r="AY77" t="n">
-        <v>504.9014889008919</v>
+        <v>504.9015332893866</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15546,16 +15546,16 @@
         <v>254760</v>
       </c>
       <c r="AG78" t="n">
-        <v>234517.20140625</v>
+        <v>234517.20125</v>
       </c>
       <c r="AH78" t="n">
         <v>-0.154105825090281</v>
       </c>
       <c r="AI78" t="n">
-        <v>-0.0810908594005727</v>
+        <v>-0.0810908587883381</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.08631690329053421</v>
+        <v>0.08631690401430614</v>
       </c>
       <c r="AK78" t="n">
         <v>362100.65625</v>
@@ -15600,7 +15600,7 @@
         <v>0.6823672976682527</v>
       </c>
       <c r="AY78" t="n">
-        <v>49.47472158183649</v>
+        <v>49.47471003666114</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -15711,7 +15711,7 @@
         </is>
       </c>
       <c r="X79" t="n">
-        <v>9261931520</v>
+        <v>9289736192</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>9261931520</v>
+        <v>9289736192</v>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
@@ -16097,16 +16097,16 @@
         <v>0.4450179136074908</v>
       </c>
       <c r="AV81" t="n">
-        <v>1.765438552836348</v>
+        <v>1.765438297499872</v>
       </c>
       <c r="AW81" t="n">
-        <v>2.463223045986195</v>
+        <v>2.463222645538545</v>
       </c>
       <c r="AX81" t="n">
         <v>1.560636830477253</v>
       </c>
       <c r="AY81" t="n">
-        <v>17.84361956838448</v>
+        <v>17.84361808646874</v>
       </c>
       <c r="AZ81" t="inlineStr"/>
       <c r="BA81" t="n">
@@ -17076,7 +17076,7 @@
         <v>0.816038423797075</v>
       </c>
       <c r="AY86" t="n">
-        <v>13.77323990852483</v>
+        <v>13.77324314475493</v>
       </c>
       <c r="AZ86" t="inlineStr"/>
       <c r="BA86" t="n">
@@ -17218,16 +17218,16 @@
         <v>81.49620529174804</v>
       </c>
       <c r="AG87" t="n">
-        <v>75.04222261428833</v>
+        <v>75.04222234725952</v>
       </c>
       <c r="AH87" t="n">
         <v>-0.09087796084914568</v>
       </c>
       <c r="AI87" t="n">
-        <v>-0.01268920673221641</v>
+        <v>-0.01268920321898859</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.08600468446454101</v>
+        <v>0.08600468832895913</v>
       </c>
       <c r="AK87" t="n">
         <v>88.62000274658203</v>
@@ -17263,16 +17263,16 @@
         <v>-4.232080716382036e-05</v>
       </c>
       <c r="AV87" t="n">
-        <v>0.1027615016578685</v>
+        <v>0.102761376432118</v>
       </c>
       <c r="AW87" t="n">
-        <v>3.000204312223679</v>
+        <v>3.000203900282876</v>
       </c>
       <c r="AX87" t="n">
-        <v>0.06597594444306631</v>
+        <v>0.06597582743245156</v>
       </c>
       <c r="AY87" t="n">
-        <v>1185.007948271296</v>
+        <v>1185.007523918721</v>
       </c>
       <c r="AZ87" t="inlineStr"/>
       <c r="BA87" t="n">
@@ -17579,7 +17579,7 @@
         </is>
       </c>
       <c r="X89" t="n">
-        <v>60322156544</v>
+        <v>60233224192</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>1</v>
       </c>
       <c r="AA89" t="n">
-        <v>60322156544</v>
+        <v>60233224192</v>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
@@ -17610,25 +17610,25 @@
         <v>209.8918890380859</v>
       </c>
       <c r="AG89" t="n">
-        <v>212.0285458374023</v>
+        <v>212.0285453796387</v>
       </c>
       <c r="AH89" t="n">
         <v>-0.008775403350597788</v>
       </c>
       <c r="AI89" t="n">
-        <v>-0.01876418465226626</v>
+        <v>-0.01876418253380574</v>
       </c>
       <c r="AJ89" t="n">
-        <v>-0.01007721290960006</v>
+        <v>-0.01007721077238466</v>
       </c>
       <c r="AK89" t="n">
-        <v>246.3216094970703</v>
+        <v>246.3216247558594</v>
       </c>
       <c r="AL89" t="n">
         <v>194.3271179199219</v>
       </c>
       <c r="AM89" t="n">
-        <v>-0.1553725088247594</v>
+        <v>-0.1553725611465673</v>
       </c>
       <c r="AN89" t="n">
         <v>0.0706174479338022</v>
@@ -17658,13 +17658,13 @@
         <v>-0.101575271762515</v>
       </c>
       <c r="AW89" t="n">
-        <v>0.5271052126985663</v>
+        <v>0.527105383735661</v>
       </c>
       <c r="AX89" t="n">
-        <v>-0.09822386391444393</v>
+        <v>-0.09822380427276667</v>
       </c>
       <c r="AY89" t="n">
-        <v>6.815783368087466</v>
+        <v>6.815787848289705</v>
       </c>
       <c r="AZ89" t="inlineStr"/>
       <c r="BA89" t="n">
@@ -17856,7 +17856,7 @@
         <v>-0.1419651280067395</v>
       </c>
       <c r="AY90" t="n">
-        <v>140.5415589823329</v>
+        <v>140.54156813268</v>
       </c>
       <c r="AZ90" t="inlineStr"/>
       <c r="BA90" t="n">
@@ -18156,9 +18156,7 @@
           <t>DKK</t>
         </is>
       </c>
-      <c r="X92" t="n">
-        <v>43081064448</v>
-      </c>
+      <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr">
         <is>
           <t>DKK</t>
@@ -18167,12 +18165,10 @@
       <c r="Z92" t="n">
         <v>0.1498935669660568</v>
       </c>
-      <c r="AA92" t="n">
-        <v>6457574418.805298</v>
-      </c>
+      <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>Mid cap</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AC92" s="2" t="n">
@@ -18242,7 +18238,7 @@
         <v>-0.02184466019417475</v>
       </c>
       <c r="AY92" t="n">
-        <v>22.86361753800521</v>
+        <v>22.86362023324646</v>
       </c>
       <c r="AZ92" t="inlineStr"/>
       <c r="BA92" t="n">
@@ -18349,7 +18345,7 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>721622794240</v>
+        <v>716614533120</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -18360,7 +18356,7 @@
         <v>0.1499205380678177</v>
       </c>
       <c r="AA93" t="n">
-        <v>108186077594.4629</v>
+        <v>107435236392.5684</v>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
@@ -18380,28 +18376,28 @@
         <v>837.9643664550781</v>
       </c>
       <c r="AG93" t="n">
-        <v>839.1509463500977</v>
+        <v>839.1509484863282</v>
       </c>
       <c r="AH93" t="n">
         <v>-0.2689068540295089</v>
       </c>
       <c r="AI93" t="n">
-        <v>-0.2699406375605511</v>
+        <v>-0.2699406394190667</v>
       </c>
       <c r="AJ93" t="n">
-        <v>-0.001414024378070033</v>
+        <v>-0.001414026920175004</v>
       </c>
       <c r="AK93" t="n">
         <v>1380.190307617188</v>
       </c>
       <c r="AL93" t="n">
-        <v>345.1558227539062</v>
+        <v>345.1558532714844</v>
       </c>
       <c r="AM93" t="n">
         <v>-0.5561264258256675</v>
       </c>
       <c r="AN93" t="n">
-        <v>0.7749374760500956</v>
+        <v>0.7749373191157931</v>
       </c>
       <c r="AO93" t="n">
         <v>15.71958694070783</v>
@@ -18425,16 +18421,16 @@
         <v>-0.2781365041639015</v>
       </c>
       <c r="AV93" t="n">
-        <v>0.5767602263566984</v>
+        <v>0.5767603502030305</v>
       </c>
       <c r="AW93" t="n">
-        <v>13.83234136907046</v>
+        <v>13.83233862931908</v>
       </c>
       <c r="AX93" t="n">
         <v>-0.01476188980458826</v>
       </c>
       <c r="AY93" t="n">
-        <v>131.5758085295527</v>
+        <v>131.5757948491037</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18545,7 +18541,7 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>106328604672</v>
+        <v>106545127424</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -18556,7 +18552,7 @@
         <v>1</v>
       </c>
       <c r="AA94" t="n">
-        <v>106328604672</v>
+        <v>106545127424</v>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
@@ -18576,28 +18572,28 @@
         <v>151.1478941345215</v>
       </c>
       <c r="AG94" t="n">
-        <v>154.2809073257446</v>
+        <v>154.2809078979492</v>
       </c>
       <c r="AH94" t="n">
         <v>-0.1816624164718944</v>
       </c>
       <c r="AI94" t="n">
-        <v>-0.1982805611827883</v>
+        <v>-0.1982805641562445</v>
       </c>
       <c r="AJ94" t="n">
-        <v>-0.02030719967577177</v>
+        <v>-0.02030720330930447</v>
       </c>
       <c r="AK94" t="n">
         <v>255.2094421386719</v>
       </c>
       <c r="AL94" t="n">
-        <v>77.61928558349609</v>
+        <v>77.61929321289062</v>
       </c>
       <c r="AM94" t="n">
         <v>-0.5153392389996392</v>
       </c>
       <c r="AN94" t="n">
-        <v>0.5935472931962416</v>
+        <v>0.5935471365624911</v>
       </c>
       <c r="AO94" t="n">
         <v>25.1877637659119</v>
@@ -18621,16 +18617,16 @@
         <v>-0.2612770524089119</v>
       </c>
       <c r="AV94" t="n">
-        <v>0.4535026604924712</v>
+        <v>0.4535027908053013</v>
       </c>
       <c r="AW94" t="n">
-        <v>2.706352167440295</v>
+        <v>2.706353014763187</v>
       </c>
       <c r="AX94" t="n">
         <v>0.3713960695822767</v>
       </c>
       <c r="AY94" t="n">
-        <v>160.6520221947156</v>
+        <v>160.6520725642476</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18816,13 +18812,13 @@
         <v>0.3192869112915966</v>
       </c>
       <c r="AW95" t="n">
-        <v>0.5333092554536982</v>
+        <v>0.5333091177311202</v>
       </c>
       <c r="AX95" t="n">
         <v>0.250384033353696</v>
       </c>
       <c r="AY95" t="n">
-        <v>12.62238864360587</v>
+        <v>12.6223900024269</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -19014,7 +19010,7 @@
         <v>0.1105750721292358</v>
       </c>
       <c r="AY96" t="n">
-        <v>8.46315321389333</v>
+        <v>8.463155799766366</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19156,16 +19152,16 @@
         <v>356.4269775390625</v>
       </c>
       <c r="AG97" t="n">
-        <v>366.7394583129883</v>
+        <v>366.7394589233398</v>
       </c>
       <c r="AH97" t="n">
         <v>-0.09748696662410505</v>
       </c>
       <c r="AI97" t="n">
-        <v>-0.1228650602378097</v>
+        <v>-0.1228650616975946</v>
       </c>
       <c r="AJ97" t="n">
-        <v>-0.02811936523373704</v>
+        <v>-0.02811936685120375</v>
       </c>
       <c r="AK97" t="n">
         <v>479.9350891113281</v>
@@ -19204,13 +19200,13 @@
         <v>-0.05872438737176666</v>
       </c>
       <c r="AW97" t="n">
-        <v>5.981361809007367</v>
+        <v>5.981362386992085</v>
       </c>
       <c r="AX97" t="n">
         <v>-0.06952160931791018</v>
       </c>
       <c r="AY97" t="n">
-        <v>282.7868132101579</v>
+        <v>282.7867236754153</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19744,28 +19740,28 @@
         <v>75.13479064941406</v>
       </c>
       <c r="AG100" t="n">
-        <v>78.96959875106812</v>
+        <v>78.96959867477418</v>
       </c>
       <c r="AH100" t="n">
         <v>-0.01443788674035129</v>
       </c>
       <c r="AI100" t="n">
-        <v>-0.06229733691338735</v>
+        <v>-0.06229733600745602</v>
       </c>
       <c r="AJ100" t="n">
-        <v>-0.0485605620682249</v>
+        <v>-0.0485605611490223</v>
       </c>
       <c r="AK100" t="n">
         <v>102.0957336425781</v>
       </c>
       <c r="AL100" t="n">
-        <v>47.76883316040039</v>
+        <v>47.76882934570312</v>
       </c>
       <c r="AM100" t="n">
         <v>-0.2747003189085669</v>
       </c>
       <c r="AN100" t="n">
-        <v>0.5501739974076674</v>
+        <v>0.5501741212006217</v>
       </c>
       <c r="AO100" t="n">
         <v>32.09820246805883</v>
@@ -19789,16 +19785,16 @@
         <v>-0.1378463324313447</v>
       </c>
       <c r="AV100" t="n">
-        <v>0.167453488483285</v>
+        <v>0.167453418270832</v>
       </c>
       <c r="AW100" t="n">
-        <v>0.1189163372186925</v>
+        <v>0.118916595201235</v>
       </c>
       <c r="AX100" t="n">
-        <v>0.1580849985780295</v>
+        <v>0.1580848603978307</v>
       </c>
       <c r="AY100" t="n">
-        <v>423.0513529821209</v>
+        <v>423.0514253526934</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -19984,13 +19980,13 @@
         <v>-0.05025876846138744</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.479141167493816</v>
+        <v>0.4791413144307726</v>
       </c>
       <c r="AX101" t="n">
         <v>-0.09837504061611269</v>
       </c>
       <c r="AY101" t="n">
-        <v>6.034071583251764</v>
+        <v>6.034070752511476</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20128,28 +20124,28 @@
         <v>50.73111396789551</v>
       </c>
       <c r="AG102" t="n">
-        <v>49.4981554031372</v>
+        <v>49.49815519332886</v>
       </c>
       <c r="AH102" t="n">
         <v>-0.1322879192910859</v>
       </c>
       <c r="AI102" t="n">
-        <v>-0.1106739210937611</v>
+        <v>-0.1106739173241653</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.02490918206378567</v>
+        <v>0.02490918640807904</v>
       </c>
       <c r="AK102" t="n">
-        <v>79.68085479736328</v>
+        <v>79.68086242675781</v>
       </c>
       <c r="AL102" t="n">
-        <v>21.00741767883301</v>
+        <v>21.00741958618164</v>
       </c>
       <c r="AM102" t="n">
-        <v>-0.4475460815560887</v>
+        <v>-0.4475461344532183</v>
       </c>
       <c r="AN102" t="n">
-        <v>1.095450337150103</v>
+        <v>1.095450146895688</v>
       </c>
       <c r="AO102" t="n">
         <v>15.53986521533693</v>
@@ -20176,7 +20172,7 @@
         <v>0.7586518847141819</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.07217954924075953</v>
+        <v>0.07217944962110456</v>
       </c>
       <c r="AX102" t="n">
         <v>0.6175536202142706</v>
@@ -20311,7 +20307,7 @@
         <v>44621</v>
       </c>
       <c r="AD103" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AE103" t="n">
         <v>5.380000114440918</v>
@@ -20562,13 +20558,13 @@
         <v>0.6961648876314095</v>
       </c>
       <c r="AW104" t="n">
-        <v>0.6828836129263167</v>
+        <v>0.6828839165153577</v>
       </c>
       <c r="AX104" t="n">
         <v>0.630682924104909</v>
       </c>
       <c r="AY104" t="n">
-        <v>415.1681490546417</v>
+        <v>415.1683303621374</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20675,7 +20671,7 @@
         </is>
       </c>
       <c r="X105" t="n">
-        <v>579926753280</v>
+        <v>579755966464</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -20686,7 +20682,7 @@
         <v>0.0307031013071537</v>
       </c>
       <c r="AA105" t="n">
-        <v>17805549856.68457</v>
+        <v>17800306171.771</v>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
@@ -20760,7 +20756,7 @@
         <v>0.5717914169192848</v>
       </c>
       <c r="AY105" t="n">
-        <v>66.56712939435995</v>
+        <v>66.56710809385031</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20902,16 +20898,16 @@
         <v>384.0251556396485</v>
       </c>
       <c r="AG106" t="n">
-        <v>367.4641844177246</v>
+        <v>367.4641828918457</v>
       </c>
       <c r="AH106" t="n">
         <v>0.0183447661725078</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.06423979235935451</v>
+        <v>0.06423979677856351</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.04506825950443583</v>
+        <v>0.04506826384403584</v>
       </c>
       <c r="AK106" t="n">
         <v>444.1268615722656</v>
@@ -20947,16 +20943,16 @@
         <v>0.001900114923216289</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.6275274093001715</v>
+        <v>0.6275273059473934</v>
       </c>
       <c r="AW106" t="n">
-        <v>1.452762586944083</v>
+        <v>1.452763056412806</v>
       </c>
       <c r="AX106" t="n">
         <v>0.4413952756461716</v>
       </c>
       <c r="AY106" t="n">
-        <v>883.239924048584</v>
+        <v>883.2401623880417</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21094,16 +21090,16 @@
         <v>20868.9797265625</v>
       </c>
       <c r="AG107" t="n">
-        <v>21299.597890625</v>
+        <v>21299.59784179688</v>
       </c>
       <c r="AH107" t="n">
         <v>0.01514306293734458</v>
       </c>
       <c r="AI107" t="n">
-        <v>-0.005380284229470789</v>
+        <v>-0.005380281949361354</v>
       </c>
       <c r="AJ107" t="n">
-        <v>-0.02021719688201418</v>
+        <v>-0.02021719463591765</v>
       </c>
       <c r="AK107" t="n">
         <v>25925</v>
@@ -21139,16 +21135,16 @@
         <v>0.002526947015448311</v>
       </c>
       <c r="AV107" t="n">
-        <v>0.2107256069104335</v>
+        <v>0.210725742053284</v>
       </c>
       <c r="AW107" t="n">
-        <v>-0.1383781231521162</v>
+        <v>-0.1383782600399754</v>
       </c>
       <c r="AX107" t="n">
-        <v>0.06484062123818424</v>
+        <v>0.06484072577537714</v>
       </c>
       <c r="AY107" t="n">
-        <v>18.92756390633142</v>
+        <v>18.92756161815261</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21259,7 +21255,7 @@
         </is>
       </c>
       <c r="X108" t="n">
-        <v>142160510976</v>
+        <v>142197112832</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -21270,7 +21266,7 @@
         <v>1</v>
       </c>
       <c r="AA108" t="n">
-        <v>142160510976</v>
+        <v>142197112832</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -21290,28 +21286,28 @@
         <v>416.4423999023438</v>
       </c>
       <c r="AG108" t="n">
-        <v>394.2208471679688</v>
+        <v>394.2208467102051</v>
       </c>
       <c r="AH108" t="n">
         <v>-0.120862848169601</v>
       </c>
       <c r="AI108" t="n">
-        <v>-0.07130739538091668</v>
+        <v>-0.07130739430253186</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.05636828415851602</v>
+        <v>0.05636828538515593</v>
       </c>
       <c r="AK108" t="n">
         <v>459.9599914550781</v>
       </c>
       <c r="AL108" t="n">
-        <v>313.2000122070312</v>
+        <v>313.2000427246094</v>
       </c>
       <c r="AM108" t="n">
         <v>-0.2040394987542768</v>
       </c>
       <c r="AN108" t="n">
-        <v>0.1689334964315288</v>
+        <v>0.1689333825330153</v>
       </c>
       <c r="AO108" t="n">
         <v>24.310312097262</v>
@@ -21335,16 +21331,16 @@
         <v>-0.1169590105211695</v>
       </c>
       <c r="AV108" t="n">
-        <v>-0.005929442959832665</v>
+        <v>-0.005929525330555352</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.453237248978686</v>
+        <v>1.453238001482982</v>
       </c>
       <c r="AX108" t="n">
         <v>0.1278988529772378</v>
       </c>
       <c r="AY108" t="n">
-        <v>1061.596714314481</v>
+        <v>1061.595335625936</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21482,16 +21478,16 @@
         <v>155.7393432617187</v>
       </c>
       <c r="AG109" t="n">
-        <v>143.7468952560425</v>
+        <v>143.7468949890137</v>
       </c>
       <c r="AH109" t="n">
         <v>-0.1948084607295076</v>
       </c>
       <c r="AI109" t="n">
-        <v>-0.1276333217318122</v>
+        <v>-0.127633320111276</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.08342752714286639</v>
+        <v>0.08342752915547602</v>
       </c>
       <c r="AK109" t="n">
         <v>183.7933807373047</v>
@@ -21530,13 +21526,13 @@
         <v>0.2541817238688375</v>
       </c>
       <c r="AW109" t="n">
-        <v>3.141391988923653</v>
+        <v>3.14139172805302</v>
       </c>
       <c r="AX109" t="n">
-        <v>0.1813869707544637</v>
+        <v>0.1813870556679977</v>
       </c>
       <c r="AY109" t="n">
-        <v>5.576992590972737</v>
+        <v>5.576989959208001</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21678,16 +21674,16 @@
         <v>641.5450598144531</v>
       </c>
       <c r="AG110" t="n">
-        <v>621.7722662353516</v>
+        <v>621.7722671508789</v>
       </c>
       <c r="AH110" t="n">
         <v>-0.1482593711596516</v>
       </c>
       <c r="AI110" t="n">
-        <v>-0.1211734225711701</v>
+        <v>-0.1211734238651965</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.03180070043783068</v>
+        <v>0.03180069891855797</v>
       </c>
       <c r="AK110" t="n">
         <v>784.9856567382812</v>
@@ -21723,7 +21719,7 @@
         <v>-0.1422812286174098</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.2796166085141365</v>
+        <v>0.2796166999623664</v>
       </c>
       <c r="AW110" t="n">
         <v>3.886641835118374</v>
@@ -21924,7 +21920,7 @@
         <v>-0.008559322848337714</v>
       </c>
       <c r="AY111" t="n">
-        <v>11.4347262720586</v>
+        <v>11.43473009555413</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22120,7 +22116,7 @@
         <v>0.1257333278765365</v>
       </c>
       <c r="AY112" t="n">
-        <v>499.2223801127617</v>
+        <v>499.2222124974073</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22504,7 +22500,7 @@
         <v>0.506417870671644</v>
       </c>
       <c r="AY114" t="n">
-        <v>82.46564775906683</v>
+        <v>82.46565719411969</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22825,7 +22821,7 @@
         <v>38814</v>
       </c>
       <c r="AD116" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AE116" t="n">
         <v>124.0999984741211</v>
@@ -22882,13 +22878,13 @@
         <v>-0.1518728781877045</v>
       </c>
       <c r="AW116" t="n">
-        <v>0.4062123398541471</v>
+        <v>0.4062120967177216</v>
       </c>
       <c r="AX116" t="n">
         <v>-0.01317289409085609</v>
       </c>
       <c r="AY116" t="n">
-        <v>8.165072224935383</v>
+        <v>8.165072870441147</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -23074,13 +23070,13 @@
         <v>0.04748630302760581</v>
       </c>
       <c r="AW117" t="n">
-        <v>0.8896096995220979</v>
+        <v>0.8896092850420658</v>
       </c>
       <c r="AX117" t="n">
         <v>-0.3172393148479464</v>
       </c>
       <c r="AY117" t="n">
-        <v>1.106992511973304</v>
+        <v>1.106992898470917</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -23412,28 +23408,28 @@
         <v>247.6740859985352</v>
       </c>
       <c r="AG119" t="n">
-        <v>268.9738765716553</v>
+        <v>268.9738764953613</v>
       </c>
       <c r="AH119" t="n">
         <v>-0.2154205130472632</v>
       </c>
       <c r="AI119" t="n">
-        <v>-0.2775506313065632</v>
+        <v>-0.2775506311016417</v>
       </c>
       <c r="AJ119" t="n">
-        <v>-0.07918906789241975</v>
+        <v>-0.07918906763123323</v>
       </c>
       <c r="AK119" t="n">
         <v>376.0595397949219</v>
       </c>
       <c r="AL119" t="n">
-        <v>149.7264709472656</v>
+        <v>149.7264862060547</v>
       </c>
       <c r="AM119" t="n">
         <v>-0.4832732938241958</v>
       </c>
       <c r="AN119" t="n">
-        <v>0.2978333496730794</v>
+        <v>0.2978332174094711</v>
       </c>
       <c r="AO119" t="n">
         <v>11.231692640665</v>
@@ -23463,10 +23459,10 @@
         <v>7.410720651329514</v>
       </c>
       <c r="AX119" t="n">
-        <v>0.1073079446641485</v>
+        <v>0.1073078483834249</v>
       </c>
       <c r="AY119" t="n">
-        <v>18.55969943081232</v>
+        <v>18.55969755319587</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23577,7 +23573,7 @@
         </is>
       </c>
       <c r="X120" t="n">
-        <v>46711844864</v>
+        <v>46360043520</v>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
@@ -23588,7 +23584,7 @@
         <v>1</v>
       </c>
       <c r="AA120" t="n">
-        <v>46711844864</v>
+        <v>46360043520</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
@@ -23608,28 +23604,28 @@
         <v>56.95559997558594</v>
       </c>
       <c r="AG120" t="n">
-        <v>61.55197240829468</v>
+        <v>61.55197219848633</v>
       </c>
       <c r="AH120" t="n">
         <v>-0.0125641429012403</v>
       </c>
       <c r="AI120" t="n">
-        <v>-0.08630057692695559</v>
+        <v>-0.08630057381248557</v>
       </c>
       <c r="AJ120" t="n">
-        <v>-0.07467465708847598</v>
+        <v>-0.07467465393437744</v>
       </c>
       <c r="AK120" t="n">
         <v>75.72768402099609</v>
       </c>
       <c r="AL120" t="n">
-        <v>49.78789138793945</v>
+        <v>49.78788757324219</v>
       </c>
       <c r="AM120" t="n">
         <v>-0.2573389453865536</v>
       </c>
       <c r="AN120" t="n">
-        <v>0.1295919572141249</v>
+        <v>0.1295920437623108</v>
       </c>
       <c r="AO120" t="n">
         <v>54.00315955387771</v>
@@ -23650,19 +23646,19 @@
         <v>-0.1095629858401409</v>
       </c>
       <c r="AU120" t="n">
-        <v>-0.0850705619311859</v>
+        <v>-0.08507061871047217</v>
       </c>
       <c r="AV120" t="n">
-        <v>-0.0002627679096843805</v>
+        <v>-0.0002627001164248188</v>
       </c>
       <c r="AW120" t="n">
-        <v>0.1183407692265679</v>
+        <v>0.1183406843939177</v>
       </c>
       <c r="AX120" t="n">
-        <v>0.06289709551041223</v>
+        <v>0.06289717214012991</v>
       </c>
       <c r="AY120" t="n">
-        <v>4.104277335451261</v>
+        <v>4.104277777248834</v>
       </c>
       <c r="AZ120" t="inlineStr"/>
       <c r="BA120" t="n">
@@ -23854,7 +23850,7 @@
         <v>-0.05305021909111751</v>
       </c>
       <c r="AY121" t="n">
-        <v>150.0597310415329</v>
+        <v>150.0597820435356</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -23996,28 +23992,28 @@
         <v>1288.715358886719</v>
       </c>
       <c r="AG122" t="n">
-        <v>1306.94734954834</v>
+        <v>1306.947345275879</v>
       </c>
       <c r="AH122" t="n">
         <v>-0.1153050305056489</v>
       </c>
       <c r="AI122" t="n">
-        <v>-0.1276465761905445</v>
+        <v>-0.1276465733387877</v>
       </c>
       <c r="AJ122" t="n">
-        <v>-0.01395005748924905</v>
+        <v>-0.01395005426581397</v>
       </c>
       <c r="AK122" t="n">
         <v>1684.826782226562</v>
       </c>
       <c r="AL122" t="n">
-        <v>851.2478637695312</v>
+        <v>851.2479248046875</v>
       </c>
       <c r="AM122" t="n">
         <v>-0.3233013582497332</v>
       </c>
       <c r="AN122" t="n">
-        <v>0.3393513730166213</v>
+        <v>0.3393512769840579</v>
       </c>
       <c r="AO122" t="n">
         <v>18.55903148032344</v>
@@ -24038,19 +24034,19 @@
         <v>-0.1093641529642779</v>
       </c>
       <c r="AU122" t="n">
-        <v>-0.2796876019461368</v>
+        <v>-0.279687657498334</v>
       </c>
       <c r="AV122" t="n">
         <v>0.07188125034142323</v>
       </c>
       <c r="AW122" t="n">
-        <v>1.412022325737547</v>
+        <v>1.412022014284855</v>
       </c>
       <c r="AX122" t="n">
         <v>0.223774754532275</v>
       </c>
       <c r="AY122" t="n">
-        <v>135.0156478541087</v>
+        <v>135.0156788038746</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
@@ -24634,7 +24630,7 @@
         <v>0.2735780277600253</v>
       </c>
       <c r="AY125" t="n">
-        <v>26.04058219854824</v>
+        <v>26.04058776464192</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24940,7 +24936,7 @@
         <v>0.08776215832606482</v>
       </c>
       <c r="AY127" t="n">
-        <v>26.01382330832234</v>
+        <v>26.01382059827328</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -25322,7 +25318,7 @@
         <v>-0.01107503726431036</v>
       </c>
       <c r="AW129" t="n">
-        <v>1.04931378844144</v>
+        <v>1.049313567620874</v>
       </c>
       <c r="AX129" t="n">
         <v>-0.0206923625988793</v>
@@ -25439,7 +25435,7 @@
         </is>
       </c>
       <c r="X130" t="n">
-        <v>87293001728</v>
+        <v>87159128064</v>
       </c>
       <c r="Y130" t="inlineStr">
         <is>
@@ -25450,7 +25446,7 @@
         <v>1</v>
       </c>
       <c r="AA130" t="n">
-        <v>87293001728</v>
+        <v>87159128064</v>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
@@ -25716,7 +25712,7 @@
         <v>0.5293515767217152</v>
       </c>
       <c r="AY131" t="n">
-        <v>12.63681229728486</v>
+        <v>12.63680808568713</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25873,13 +25869,13 @@
         <v>485.7999877929688</v>
       </c>
       <c r="AL132" t="n">
-        <v>272.1793212890625</v>
+        <v>272.1793518066406</v>
       </c>
       <c r="AM132" t="n">
         <v>-0.1385137499345109</v>
       </c>
       <c r="AN132" t="n">
-        <v>0.5376260319245745</v>
+        <v>0.5376258595212593</v>
       </c>
       <c r="AO132" t="n">
         <v>21.89459290103802</v>
@@ -25906,13 +25902,13 @@
         <v>0.4547496677051874</v>
       </c>
       <c r="AW132" t="n">
-        <v>2.930727688036839</v>
+        <v>2.930726843047361</v>
       </c>
       <c r="AX132" t="n">
         <v>0.3197356436048513</v>
       </c>
       <c r="AY132" t="n">
-        <v>133.3726531591147</v>
+        <v>133.3726223004461</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26098,13 +26094,13 @@
         <v>1.556161880530701</v>
       </c>
       <c r="AW133" t="n">
-        <v>1.388151692652367</v>
+        <v>1.388151404719058</v>
       </c>
       <c r="AX133" t="n">
         <v>1.451828755464444</v>
       </c>
       <c r="AY133" t="n">
-        <v>2.124614995583836</v>
+        <v>2.124614502681247</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26215,7 +26211,7 @@
         </is>
       </c>
       <c r="X134" t="n">
-        <v>4293624070144</v>
+        <v>21483696947200</v>
       </c>
       <c r="Y134" t="inlineStr">
         <is>
@@ -26226,7 +26222,7 @@
         <v>0.006376981735229492</v>
       </c>
       <c r="AA134" t="n">
-        <v>27380362273.25</v>
+        <v>137001143037.5</v>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
@@ -26294,13 +26290,13 @@
         <v>0.6638679817161632</v>
       </c>
       <c r="AW134" t="n">
-        <v>2.604131674277773</v>
+        <v>2.604131338971251</v>
       </c>
       <c r="AX134" t="n">
-        <v>0.3381230394443351</v>
+        <v>0.3381229470037248</v>
       </c>
       <c r="AY134" t="n">
-        <v>17.04779151382731</v>
+        <v>17.04779571779122</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26442,16 +26438,16 @@
         <v>1722.733603515625</v>
       </c>
       <c r="AG135" t="n">
-        <v>1585.318758544922</v>
+        <v>1585.318757324219</v>
       </c>
       <c r="AH135" t="n">
         <v>-0.08761282323598152</v>
       </c>
       <c r="AI135" t="n">
-        <v>-0.008527439446439744</v>
+        <v>-0.008527438683001098</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.08667963097644082</v>
+        <v>0.08667963181318949</v>
       </c>
       <c r="AK135" t="n">
         <v>1986.870361328125</v>
@@ -26490,13 +26486,13 @@
         <v>0.5265701892037622</v>
       </c>
       <c r="AW135" t="n">
-        <v>1.090087542659222</v>
+        <v>1.090088221193588</v>
       </c>
       <c r="AX135" t="n">
         <v>0.3570870730154152</v>
       </c>
       <c r="AY135" t="n">
-        <v>892.1912070769671</v>
+        <v>892.1909045448147</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26638,28 +26634,28 @@
         <v>468.3741442871094</v>
       </c>
       <c r="AG136" t="n">
-        <v>441.3135588073731</v>
+        <v>441.3135583496094</v>
       </c>
       <c r="AH136" t="n">
         <v>-0.1945755442829695</v>
       </c>
       <c r="AI136" t="n">
-        <v>-0.1451883072574374</v>
+        <v>-0.1451883063707623</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.06131827345814211</v>
+        <v>0.06131827455902128</v>
       </c>
       <c r="AK136" t="n">
         <v>722.2277221679688</v>
       </c>
       <c r="AL136" t="n">
-        <v>219.4479217529297</v>
+        <v>219.4479064941406</v>
       </c>
       <c r="AM136" t="n">
         <v>-0.477671683521115</v>
       </c>
       <c r="AN136" t="n">
-        <v>0.7190410700680911</v>
+        <v>0.7190411895975299</v>
       </c>
       <c r="AO136" t="n">
         <v>5.132651588185226</v>
@@ -26683,16 +26679,16 @@
         <v>-0.06606515784771139</v>
       </c>
       <c r="AV136" t="n">
-        <v>0.6602902935929791</v>
+        <v>0.6602901820941329</v>
       </c>
       <c r="AW136" t="n">
-        <v>1.949967851736516</v>
+        <v>1.949967675738858</v>
       </c>
       <c r="AX136" t="n">
-        <v>0.4080574823343541</v>
+        <v>0.4080576427228295</v>
       </c>
       <c r="AY136" t="n">
-        <v>5472.349132503205</v>
+        <v>5472.35090751029</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26878,13 +26874,13 @@
         <v>0.2810439836695291</v>
       </c>
       <c r="AW137" t="n">
-        <v>0.8180868636411422</v>
+        <v>0.8180867194942254</v>
       </c>
       <c r="AX137" t="n">
         <v>0.2685529718135187</v>
       </c>
       <c r="AY137" t="n">
-        <v>237.0885620757043</v>
+        <v>237.088446199498</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27026,28 +27022,28 @@
         <v>182.4220004272461</v>
       </c>
       <c r="AG138" t="n">
-        <v>181.3721750640869</v>
+        <v>181.3721746826172</v>
       </c>
       <c r="AH138" t="n">
         <v>-0.2017958345521815</v>
       </c>
       <c r="AI138" t="n">
-        <v>-0.1971756386617681</v>
+        <v>-0.1971756369732335</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0.005788238260848066</v>
+        <v>0.005788240376265019</v>
       </c>
       <c r="AK138" t="n">
         <v>301.3693542480469</v>
       </c>
       <c r="AL138" t="n">
-        <v>109.3064193725586</v>
+        <v>109.3064117431641</v>
       </c>
       <c r="AM138" t="n">
         <v>-0.5168387277675721</v>
       </c>
       <c r="AN138" t="n">
-        <v>0.3321267080760948</v>
+        <v>0.3321268010561869</v>
       </c>
       <c r="AO138" t="n">
         <v>3.563811237964387</v>
@@ -27068,19 +27064,19 @@
         <v>-0.2359823163080802</v>
       </c>
       <c r="AU138" t="n">
-        <v>-0.2317861607312488</v>
+        <v>-0.2317860988878778</v>
       </c>
       <c r="AV138" t="n">
         <v>0.2631191257238545</v>
       </c>
       <c r="AW138" t="n">
-        <v>3.678057507667713</v>
+        <v>3.678057221005821</v>
       </c>
       <c r="AX138" t="n">
         <v>0.1467535437467982</v>
       </c>
       <c r="AY138" t="n">
-        <v>2401.621353229204</v>
+        <v>2401.618842568355</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27222,16 +27218,16 @@
         <v>374.4120587158203</v>
       </c>
       <c r="AG139" t="n">
-        <v>347.349457321167</v>
+        <v>347.3494566345215</v>
       </c>
       <c r="AH139" t="n">
         <v>-0.175106680156545</v>
       </c>
       <c r="AI139" t="n">
-        <v>-0.110837804424879</v>
+        <v>-0.11083780266717</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0.07791174226488184</v>
+        <v>0.07791174439571358</v>
       </c>
       <c r="AK139" t="n">
         <v>483.6542053222656</v>
@@ -27270,13 +27266,13 @@
         <v>1.133537332539964</v>
       </c>
       <c r="AW139" t="n">
-        <v>1.718918267606555</v>
+        <v>1.718918084992275</v>
       </c>
       <c r="AX139" t="n">
         <v>0.4897598850044695</v>
       </c>
       <c r="AY139" t="n">
-        <v>276.4100635367389</v>
+        <v>276.4101526471205</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
@@ -27802,16 +27798,16 @@
         <v>57234.64046875</v>
       </c>
       <c r="AG142" t="n">
-        <v>65526.63923828125</v>
+        <v>65526.63912109375</v>
       </c>
       <c r="AH142" t="n">
         <v>-0.1388082532480965</v>
       </c>
       <c r="AI142" t="n">
-        <v>-0.2477868455795251</v>
+        <v>-0.2477868442342711</v>
       </c>
       <c r="AJ142" t="n">
-        <v>-0.1265439348930776</v>
+        <v>-0.1265439333309933</v>
       </c>
       <c r="AK142" t="n">
         <v>88177.4765625</v>
@@ -27847,16 +27843,16 @@
         <v>-0.3215486419617141</v>
       </c>
       <c r="AV142" t="n">
-        <v>-0.0742561836133695</v>
+        <v>-0.07425611569568247</v>
       </c>
       <c r="AW142" t="n">
-        <v>4.104103652835327</v>
+        <v>4.104102104370592</v>
       </c>
       <c r="AX142" t="n">
-        <v>-0.02661026287194346</v>
+        <v>-0.02661018778321056</v>
       </c>
       <c r="AY142" t="n">
-        <v>32.84324429523834</v>
+        <v>32.84325564156683</v>
       </c>
       <c r="AZ142" t="inlineStr"/>
       <c r="BA142" t="n">
@@ -28039,16 +28035,16 @@
         <v>-0.04404330854170135</v>
       </c>
       <c r="AV143" t="n">
-        <v>0.900855031851908</v>
+        <v>0.9008548463332979</v>
       </c>
       <c r="AW143" t="n">
-        <v>0.8107183966258769</v>
+        <v>0.8107182282843282</v>
       </c>
       <c r="AX143" t="n">
         <v>0.2043667793913657</v>
       </c>
       <c r="AY143" t="n">
-        <v>296.5914614166201</v>
+        <v>296.5914258927363</v>
       </c>
       <c r="AZ143" t="inlineStr"/>
       <c r="BA143" t="n">
@@ -28240,7 +28236,7 @@
         <v>0.04900436071090364</v>
       </c>
       <c r="AY144" t="n">
-        <v>20.78934585640798</v>
+        <v>20.78934772493437</v>
       </c>
       <c r="AZ144" t="inlineStr"/>
       <c r="BA144" t="n">
@@ -28576,16 +28572,16 @@
         <v>146.7358737182617</v>
       </c>
       <c r="AG146" t="n">
-        <v>139.4288466644287</v>
+        <v>139.4288464355469</v>
       </c>
       <c r="AH146" t="n">
         <v>-0.0189174394376409</v>
       </c>
       <c r="AI146" t="n">
-        <v>0.03249800997310026</v>
+        <v>0.03249801166801514</v>
       </c>
       <c r="AJ146" t="n">
-        <v>0.052406852876143</v>
+        <v>0.05240685460373951</v>
       </c>
       <c r="AK146" t="n">
         <v>158.7599945068359</v>
@@ -28618,16 +28614,16 @@
         <v>0.0291063518055299</v>
       </c>
       <c r="AU146" t="n">
-        <v>0.009642073600163004</v>
+        <v>0.009642181647268711</v>
       </c>
       <c r="AV146" t="n">
         <v>0.3135118669146886</v>
       </c>
       <c r="AW146" t="n">
-        <v>1.189379543796639</v>
+        <v>1.189379289763557</v>
       </c>
       <c r="AX146" t="n">
-        <v>0.1872189426252859</v>
+        <v>0.18721886792714</v>
       </c>
       <c r="AY146" t="n">
         <v>45.74781889150263</v>
@@ -28816,13 +28812,13 @@
         <v>0.3044204729601119</v>
       </c>
       <c r="AW147" t="n">
-        <v>7.744970519494759</v>
+        <v>7.74496898408923</v>
       </c>
       <c r="AX147" t="n">
         <v>0.2707580048475571</v>
       </c>
       <c r="AY147" t="n">
-        <v>38.58840894704929</v>
+        <v>38.58841288030904</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -29014,7 +29010,7 @@
         <v>0.5697810410372024</v>
       </c>
       <c r="AY148" t="n">
-        <v>0.08158975600282048</v>
+        <v>0.08159010093601005</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29156,16 +29152,16 @@
         <v>512.2139154052734</v>
       </c>
       <c r="AG149" t="n">
-        <v>321.5885196304321</v>
+        <v>321.5885192108154</v>
       </c>
       <c r="AH149" t="n">
         <v>-0.1088879299964698</v>
       </c>
       <c r="AI149" t="n">
-        <v>0.4193292813000438</v>
+        <v>0.4193292831520199</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0.5927618187176178</v>
+        <v>0.5927618207958929</v>
       </c>
       <c r="AK149" t="n">
         <v>587.5860595703125</v>
@@ -29204,13 +29200,13 @@
         <v>1.990684595359674</v>
       </c>
       <c r="AW149" t="n">
-        <v>8.136914190763893</v>
+        <v>8.136916283896896</v>
       </c>
       <c r="AX149" t="n">
-        <v>2.609180656050201</v>
+        <v>2.609180438317535</v>
       </c>
       <c r="AY149" t="n">
-        <v>40.6944883118983</v>
+        <v>40.69449557636531</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29352,16 +29348,16 @@
         <v>59.33377693176269</v>
       </c>
       <c r="AG150" t="n">
-        <v>39.70382934570313</v>
+        <v>39.70382941246033</v>
       </c>
       <c r="AH150" t="n">
         <v>-0.04455772819071013</v>
       </c>
       <c r="AI150" t="n">
-        <v>0.427821939619639</v>
+        <v>0.4278219372189287</v>
       </c>
       <c r="AJ150" t="n">
-        <v>0.4944094287515866</v>
+        <v>0.4944094262389174</v>
       </c>
       <c r="AK150" t="n">
         <v>73.45999908447266</v>
@@ -29394,10 +29390,10 @@
         <v>0.2466195559379996</v>
       </c>
       <c r="AU150" t="n">
-        <v>0.9916025640724964</v>
+        <v>0.9916024306193061</v>
       </c>
       <c r="AV150" t="n">
-        <v>1.488668443400662</v>
+        <v>1.488668651781487</v>
       </c>
       <c r="AW150" t="n">
         <v>3.296767827057685</v>
@@ -29517,7 +29513,7 @@
         </is>
       </c>
       <c r="X151" t="n">
-        <v>21307996160</v>
+        <v>21640437760</v>
       </c>
       <c r="Y151" t="inlineStr">
         <is>
@@ -29528,7 +29524,7 @@
         <v>1</v>
       </c>
       <c r="AA151" t="n">
-        <v>21307996160</v>
+        <v>21640437760</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
@@ -29792,13 +29788,13 @@
         <v>0.1390339275094834</v>
       </c>
       <c r="AW152" t="n">
-        <v>1.749963412479697</v>
+        <v>1.749963176986816</v>
       </c>
       <c r="AX152" t="n">
         <v>0.08748285179514736</v>
       </c>
       <c r="AY152" t="n">
-        <v>667.8570598454739</v>
+        <v>667.856896588477</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29990,7 +29986,7 @@
         <v>0.4020449187634587</v>
       </c>
       <c r="AY153" t="n">
-        <v>6.960781646501245</v>
+        <v>6.960783144969259</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30182,7 +30178,7 @@
         <v>0.2120835051676662</v>
       </c>
       <c r="AY154" t="n">
-        <v>15.92720151925032</v>
+        <v>15.9272032164955</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30368,7 +30364,7 @@
         <v>0.6757547593530571</v>
       </c>
       <c r="AW155" t="n">
-        <v>6.417884308400206</v>
+        <v>6.417884764712725</v>
       </c>
       <c r="AX155" t="n">
         <v>0.2605566417046576</v>
@@ -30516,16 +30512,16 @@
         <v>109.9381394958496</v>
       </c>
       <c r="AG156" t="n">
-        <v>99.6344144821167</v>
+        <v>99.63441459655762</v>
       </c>
       <c r="AH156" t="n">
         <v>-0.03127340076534046</v>
       </c>
       <c r="AI156" t="n">
-        <v>0.06890777201401233</v>
+        <v>0.06890777078625598</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.1034153215762845</v>
+        <v>0.1034153203088923</v>
       </c>
       <c r="AK156" t="n">
         <v>129.0153350830078</v>
@@ -30558,19 +30554,19 @@
         <v>-0.07498820473401013</v>
       </c>
       <c r="AU156" t="n">
-        <v>0.2158715182715618</v>
+        <v>0.2158716241764178</v>
       </c>
       <c r="AV156" t="n">
         <v>0.543641262043967</v>
       </c>
       <c r="AW156" t="n">
-        <v>1.212888784614116</v>
+        <v>1.212888609214108</v>
       </c>
       <c r="AX156" t="n">
         <v>0.4189151442236343</v>
       </c>
       <c r="AY156" t="n">
-        <v>2157.350710767369</v>
+        <v>2157.349570117504</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30685,10 +30681,10 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>1.337488532066345</v>
+        <v>1.337399005889893</v>
       </c>
       <c r="AA157" t="n">
-        <v>127833763136.7744</v>
+        <v>127825206451.793</v>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
@@ -30756,13 +30752,13 @@
         <v>0.03862225425424382</v>
       </c>
       <c r="AW157" t="n">
-        <v>7.628039128278303</v>
+        <v>7.628040103979311</v>
       </c>
       <c r="AX157" t="n">
         <v>-0.02732192842481274</v>
       </c>
       <c r="AY157" t="n">
-        <v>8.350831717402126</v>
+        <v>8.350829998369361</v>
       </c>
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="n">
@@ -31292,28 +31288,28 @@
         <v>305.5650006103515</v>
       </c>
       <c r="AG160" t="n">
-        <v>306.4217672729492</v>
+        <v>306.4217663574219</v>
       </c>
       <c r="AH160" t="n">
         <v>-0.1033986200204177</v>
       </c>
       <c r="AI160" t="n">
-        <v>-0.1059055508394717</v>
+        <v>-0.1059055481680952</v>
       </c>
       <c r="AJ160" t="n">
-        <v>-0.002796037207874025</v>
+        <v>-0.002796034228426669</v>
       </c>
       <c r="AK160" t="n">
         <v>385.5466918945312</v>
       </c>
       <c r="AL160" t="n">
-        <v>192.3445129394531</v>
+        <v>192.3445281982422</v>
       </c>
       <c r="AM160" t="n">
         <v>-0.289398646180968</v>
       </c>
       <c r="AN160" t="n">
-        <v>0.424371285844501</v>
+        <v>0.4243711728484039</v>
       </c>
       <c r="AO160" t="n">
         <v>37.65448430912983</v>
@@ -31337,7 +31333,7 @@
         <v>-0.1957421167721891</v>
       </c>
       <c r="AV160" t="n">
-        <v>0.3278109985084505</v>
+        <v>0.3278110967035044</v>
       </c>
       <c r="AW160" t="n">
         <v>3.476066742759818</v>
@@ -31346,7 +31342,7 @@
         <v>0.140551706193736</v>
       </c>
       <c r="AY160" t="n">
-        <v>369.8253403596021</v>
+        <v>369.8252206922307</v>
       </c>
       <c r="AZ160" t="inlineStr"/>
       <c r="BA160" t="n">
@@ -32578,16 +32574,16 @@
         <v>356.4269775390625</v>
       </c>
       <c r="AG5" t="n">
-        <v>366.7394583129883</v>
+        <v>366.7394589233398</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.09748696662410505</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.1228650602378097</v>
+        <v>-0.1228650616975946</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.02811936523373704</v>
+        <v>-0.02811936685120375</v>
       </c>
       <c r="AK5" t="n">
         <v>479.9350891113281</v>
@@ -32626,13 +32622,13 @@
         <v>-0.05872438737176666</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.981361809007367</v>
+        <v>5.981362386992085</v>
       </c>
       <c r="AX5" t="n">
         <v>-0.06952160931791018</v>
       </c>
       <c r="AY5" t="n">
-        <v>282.7868132101579</v>
+        <v>282.7867236754153</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32980,28 +32976,28 @@
         <v>302.2157531738281</v>
       </c>
       <c r="AG7" t="n">
-        <v>283.0159564971924</v>
+        <v>283.0159562683106</v>
       </c>
       <c r="AH7" t="n">
         <v>-0.2386233884665604</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.1869716147760797</v>
+        <v>-0.186971614118564</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.06783997946358267</v>
+        <v>0.06783998032717076</v>
       </c>
       <c r="AK7" t="n">
         <v>432.8701477050781</v>
       </c>
       <c r="AL7" t="n">
-        <v>138.9482116699219</v>
+        <v>138.9481964111328</v>
       </c>
       <c r="AM7" t="n">
         <v>-0.4684317980266759</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.6560127211290001</v>
+        <v>0.656012902986336</v>
       </c>
       <c r="AO7" t="n">
         <v>6.247171146094061</v>
@@ -33028,7 +33024,7 @@
         <v>0.566780765164719</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.256323235744476</v>
+        <v>3.256322635065287</v>
       </c>
       <c r="AX7" t="n">
         <v>0.247070551064049</v>
@@ -33227,16 +33223,16 @@
         <v>0.4450179136074908</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.765438552836348</v>
+        <v>1.765438297499872</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.463223045986195</v>
+        <v>2.463222645538545</v>
       </c>
       <c r="AX8" t="n">
         <v>1.560636830477253</v>
       </c>
       <c r="AY8" t="n">
-        <v>17.84361956838448</v>
+        <v>17.84361808646874</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33349,7 +33345,7 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>40303800320</v>
+        <v>43154300928</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -33360,7 +33356,7 @@
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>40303800320</v>
+        <v>43154300928</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -33513,7 +33509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4633455013600658</v>
+        <v>0.4633454694430064</v>
       </c>
     </row>
   </sheetData>
@@ -33681,40 +33677,40 @@
         <v>0.625</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5569186300553122</v>
+        <v>0.5569186595494671</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4741499085690859</v>
+        <v>0.4741499812052029</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3306389272324083</v>
+        <v>0.3306390264305659</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4896404065359252</v>
+        <v>0.489640406445625</v>
       </c>
       <c r="O2" t="n">
         <v>0.3035102480872084</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3561335118853571</v>
+        <v>0.3561334723131946</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.950039055912777</v>
+        <v>3.950038759815452</v>
       </c>
       <c r="R2" t="n">
         <v>1.432688162952117</v>
       </c>
       <c r="S2" t="n">
-        <v>4.656794037737559</v>
+        <v>4.656793312962733</v>
       </c>
       <c r="T2" t="n">
-        <v>1294.307134460492</v>
+        <v>1294.307144169848</v>
       </c>
       <c r="U2" t="n">
-        <v>320.6983302818409</v>
+        <v>320.6983892854807</v>
       </c>
       <c r="V2" t="n">
-        <v>3894.350988030484</v>
+        <v>3894.350973804354</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33732,10 +33728,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>210.2511297625063</v>
+        <v>206.0846149883657</v>
       </c>
       <c r="D3" t="n">
-        <v>30.03587568035805</v>
+        <v>29.44065928405225</v>
       </c>
       <c r="E3" t="n">
         <v>15.95129353140967</v>
@@ -33747,7 +33743,7 @@
         <v>85</v>
       </c>
       <c r="H3" t="n">
-        <v>76.03637785889077</v>
+        <v>77.16763413132797</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
@@ -33756,40 +33752,40 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="K3" t="n">
-        <v>2.155362450902301</v>
+        <v>2.155362439318775</v>
       </c>
       <c r="L3" t="n">
-        <v>1.385848411934487</v>
+        <v>1.385848248669108</v>
       </c>
       <c r="M3" t="n">
-        <v>2.257915790012305</v>
+        <v>2.304977901920019</v>
       </c>
       <c r="N3" t="n">
-        <v>2.862703222749807</v>
+        <v>2.862703212132826</v>
       </c>
       <c r="O3" t="n">
         <v>2.304867456576942</v>
       </c>
       <c r="P3" t="n">
-        <v>3.243580154229581</v>
+        <v>3.307446853672149</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.187057241928584</v>
+        <v>4.187057099052139</v>
       </c>
       <c r="R3" t="n">
         <v>5.097864838393732</v>
       </c>
       <c r="S3" t="n">
-        <v>5.848387724486041</v>
+        <v>5.93630246352066</v>
       </c>
       <c r="T3" t="n">
-        <v>38.06948999407009</v>
+        <v>38.06949296985017</v>
       </c>
       <c r="U3" t="n">
-        <v>23.63014682565929</v>
+        <v>23.63014900062538</v>
       </c>
       <c r="V3" t="n">
-        <v>60.49946603594824</v>
+        <v>61.6681551392946</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33807,10 +33803,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>1335.734903402955</v>
+        <v>1336.058788317974</v>
       </c>
       <c r="D4" t="n">
-        <v>83.48343146268471</v>
+        <v>83.50367426987337</v>
       </c>
       <c r="E4" t="n">
         <v>32.09474268302453</v>
@@ -33822,7 +33818,7 @@
         <v>60</v>
       </c>
       <c r="H4" t="n">
-        <v>65.27569308131592</v>
+        <v>65.28073078843499</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -33831,40 +33827,40 @@
         <v>0.375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3929710887869203</v>
+        <v>0.3929710705099946</v>
       </c>
       <c r="L4" t="n">
         <v>0.2070939093434491</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8167240374815402</v>
+        <v>0.8165420846222053</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3975389047168726</v>
+        <v>0.3975389238778651</v>
       </c>
       <c r="O4" t="n">
         <v>0.3089661699374002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7539058973876078</v>
+        <v>0.753645120379563</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.676002249393679</v>
+        <v>5.676002332194619</v>
       </c>
       <c r="R4" t="n">
         <v>3.902824988207366</v>
       </c>
       <c r="S4" t="n">
-        <v>4.694155365605574</v>
+        <v>4.695063971545531</v>
       </c>
       <c r="T4" t="n">
-        <v>223.0868782175119</v>
+        <v>223.086790057831</v>
       </c>
       <c r="U4" t="n">
-        <v>37.59557382902084</v>
+        <v>37.59557579565072</v>
       </c>
       <c r="V4" t="n">
-        <v>757.3131006679579</v>
+        <v>757.1381958758127</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33882,13 +33878,13 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>3723.387156441483</v>
+        <v>3833.007937205733</v>
       </c>
       <c r="D5" t="n">
-        <v>248.2258104294322</v>
+        <v>255.5338624803822</v>
       </c>
       <c r="E5" t="n">
-        <v>47.374393344</v>
+        <v>48.285843456</v>
       </c>
       <c r="F5" t="n">
         <v>30.33333333333333</v>
@@ -33897,7 +33893,7 @@
         <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>64.34810980673552</v>
+        <v>63.79477025250726</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -33906,40 +33902,40 @@
         <v>0.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3046111674727274</v>
+        <v>0.3046111770085005</v>
       </c>
       <c r="L5" t="n">
         <v>0.2685529718135187</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3338067497344618</v>
+        <v>0.3339302018555929</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5055294662028935</v>
+        <v>0.5055294509295756</v>
       </c>
       <c r="O5" t="n">
         <v>0.5059501531546244</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4939684733730916</v>
+        <v>0.498827446263175</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.818137090492793</v>
+        <v>2.818136855069795</v>
       </c>
       <c r="R5" t="n">
-        <v>1.837672461651426</v>
+        <v>1.837672373652597</v>
       </c>
       <c r="S5" t="n">
-        <v>2.921807743016147</v>
+        <v>2.912663009837843</v>
       </c>
       <c r="T5" t="n">
-        <v>653.3701112290377</v>
+        <v>653.3700366543726</v>
       </c>
       <c r="U5" t="n">
-        <v>32.84324429523834</v>
+        <v>32.84325564156683</v>
       </c>
       <c r="V5" t="n">
-        <v>794.2482678856082</v>
+        <v>772.0209412144676</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33957,10 +33953,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>13329.6429989598</v>
+        <v>13332.4934995678</v>
       </c>
       <c r="D6" t="n">
-        <v>1110.80358324665</v>
+        <v>1111.041124963983</v>
       </c>
       <c r="E6" t="n">
         <v>315.166539776</v>
@@ -33972,7 +33968,7 @@
         <v>32.5</v>
       </c>
       <c r="H6" t="n">
-        <v>52.7671269391471</v>
+        <v>52.76439731448209</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -33981,40 +33977,40 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2013224090443829</v>
+        <v>0.2013224008132978</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004299457787319994</v>
+        <v>0.004299408400809335</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03267231332167694</v>
+        <v>0.03282880503849876</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005265271483547412</v>
+        <v>0.005265268143888234</v>
       </c>
       <c r="O6" t="n">
         <v>-0.05282404159439369</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05940700714852797</v>
+        <v>0.05950022292185816</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4288737909212581</v>
+        <v>0.4288737732048681</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4188592105133292</v>
+        <v>0.4188590330556822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8112443510699403</v>
+        <v>0.8112443627789032</v>
       </c>
       <c r="T6" t="n">
-        <v>1220.367592552443</v>
+        <v>1220.367873370863</v>
       </c>
       <c r="U6" t="n">
-        <v>11.45365359734447</v>
+        <v>11.45365274256281</v>
       </c>
       <c r="V6" t="n">
-        <v>3234.755717162162</v>
+        <v>3234.066293113896</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34032,13 +34028,13 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>3652.927269567619</v>
+        <v>3739.602462185619</v>
       </c>
       <c r="D7" t="n">
-        <v>304.4106057973016</v>
+        <v>311.6335385154683</v>
       </c>
       <c r="E7" t="n">
-        <v>136.006344704</v>
+        <v>136.6700465595</v>
       </c>
       <c r="F7" t="n">
         <v>50.41666666666666</v>
@@ -34047,7 +34043,7 @@
         <v>45</v>
       </c>
       <c r="H7" t="n">
-        <v>47.33072677414373</v>
+        <v>47.27640859967924</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -34056,40 +34052,40 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="K7" t="n">
-        <v>1.17756828101423</v>
+        <v>1.177568268584182</v>
       </c>
       <c r="L7" t="n">
         <v>0.9484486581503969</v>
       </c>
       <c r="M7" t="n">
-        <v>1.177279843574165</v>
+        <v>1.204937289021222</v>
       </c>
       <c r="N7" t="n">
-        <v>2.407936276745894</v>
+        <v>2.40793623747069</v>
       </c>
       <c r="O7" t="n">
-        <v>1.956784987250908</v>
+        <v>1.956784773773869</v>
       </c>
       <c r="P7" t="n">
-        <v>2.301977944497219</v>
+        <v>2.36799359127139</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.033995563306524</v>
+        <v>6.033995335033155</v>
       </c>
       <c r="R7" t="n">
         <v>5.351182526201095</v>
       </c>
       <c r="S7" t="n">
-        <v>7.755341563771569</v>
+        <v>7.755301773023445</v>
       </c>
       <c r="T7" t="n">
-        <v>236.2104916773996</v>
+        <v>236.2104936386429</v>
       </c>
       <c r="U7" t="n">
-        <v>41.4322223089304</v>
+        <v>41.43221653634272</v>
       </c>
       <c r="V7" t="n">
-        <v>312.689133626342</v>
+        <v>305.9723815927759</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34107,10 +34103,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>2662.649044992</v>
+        <v>2662.681450496</v>
       </c>
       <c r="D8" t="n">
-        <v>266.2649044992</v>
+        <v>266.2681450496</v>
       </c>
       <c r="E8" t="n">
         <v>105.818136576</v>
@@ -34122,7 +34118,7 @@
         <v>92.5</v>
       </c>
       <c r="H8" t="n">
-        <v>38.90529726171676</v>
+        <v>38.90630088368343</v>
       </c>
       <c r="I8" t="n">
         <v>8</v>
@@ -34137,7 +34133,7 @@
         <v>0.4566717831697081</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2722897810546467</v>
+        <v>0.2723028267177913</v>
       </c>
       <c r="N8" t="n">
         <v>0.2988835015612034</v>
@@ -34146,25 +34142,25 @@
         <v>0.2289345085744285</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1842945718900418</v>
+        <v>0.1842985081107432</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.298069061438542</v>
+        <v>1.298069057954067</v>
       </c>
       <c r="R8" t="n">
         <v>0.3380430488314869</v>
       </c>
       <c r="S8" t="n">
-        <v>4.238691104630957</v>
+        <v>4.238639598170171</v>
       </c>
       <c r="T8" t="n">
-        <v>54.32054537400249</v>
+        <v>54.3205276065385</v>
       </c>
       <c r="U8" t="n">
         <v>8.651534191277793</v>
       </c>
       <c r="V8" t="n">
-        <v>185.9479277442566</v>
+        <v>185.9454715878332</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34182,13 +34178,13 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1475.283150889256</v>
+        <v>1474.962707716342</v>
       </c>
       <c r="D9" t="n">
-        <v>67.05832504042073</v>
+        <v>67.04375944165194</v>
       </c>
       <c r="E9" t="n">
-        <v>42.157020629875</v>
+        <v>41.98111995787499</v>
       </c>
       <c r="F9" t="n">
         <v>20.22727272727273</v>
@@ -34197,7 +34193,7 @@
         <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>37.26695078381938</v>
+        <v>37.27524134180594</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -34206,40 +34202,40 @@
         <v>0.1304347826086956</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1897715306207286</v>
+        <v>0.1897715383388977</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1546429118658508</v>
+        <v>0.1546429543226178</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2956884460951453</v>
+        <v>0.2957388264241776</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2239022931514453</v>
+        <v>0.2239022980905744</v>
       </c>
       <c r="O9" t="n">
-        <v>0.152297236739388</v>
+        <v>0.1522973043108132</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3117233710393787</v>
+        <v>0.3117890974324723</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.075678383323448</v>
+        <v>2.07567838668262</v>
       </c>
       <c r="R9" t="n">
-        <v>1.195425775436056</v>
+        <v>1.19542561970971</v>
       </c>
       <c r="S9" t="n">
-        <v>1.890660668050518</v>
+        <v>1.891063674166363</v>
       </c>
       <c r="T9" t="n">
-        <v>161.3928319871202</v>
+        <v>161.3927841459927</v>
       </c>
       <c r="U9" t="n">
-        <v>22.48407305243983</v>
+        <v>22.48407469139726</v>
       </c>
       <c r="V9" t="n">
-        <v>341.7151138876263</v>
+        <v>341.8144016485726</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34281,40 +34277,40 @@
         <v>0.2</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.04323962754133348</v>
+        <v>-0.04323965011128404</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04380288026555978</v>
+        <v>0.04380282334486607</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0464415111255532</v>
+        <v>-0.04644151560248847</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.09201376898131675</v>
+        <v>-0.092013777912271</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01092790546330846</v>
+        <v>0.01092799593210403</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1241052415883019</v>
+        <v>0.1241052276863698</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4349565980780827</v>
+        <v>0.4349566395117353</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3794685470945769</v>
+        <v>0.3794685404593577</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7119544424973929</v>
+        <v>0.71195449072398</v>
       </c>
       <c r="T10" t="n">
-        <v>14.41123843170668</v>
+        <v>14.41123961440122</v>
       </c>
       <c r="U10" t="n">
         <v>2.701656872200184</v>
       </c>
       <c r="V10" t="n">
-        <v>2.386063278481204</v>
+        <v>2.386063355644893</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34332,13 +34328,13 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>402.4740226329652</v>
+        <v>402.3401489689652</v>
       </c>
       <c r="D11" t="n">
-        <v>100.6185056582413</v>
+        <v>100.5850372422413</v>
       </c>
       <c r="E11" t="n">
-        <v>84.861796352</v>
+        <v>84.79485952</v>
       </c>
       <c r="F11" t="n">
         <v>17.5</v>
@@ -34347,7 +34343,7 @@
         <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>27.13370048891402</v>
+        <v>27.14272888916599</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -34362,7 +34358,7 @@
         <v>-0.0005362643251474175</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03010715940539635</v>
+        <v>0.03011064893207685</v>
       </c>
       <c r="N11" t="n">
         <v>-0.01673608685566039</v>
@@ -34371,25 +34367,25 @@
         <v>-0.03398583135312561</v>
       </c>
       <c r="P11" t="n">
-        <v>0.00885258852204427</v>
+        <v>0.008876034853188877</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8513919248373396</v>
+        <v>0.8513918696321978</v>
       </c>
       <c r="R11" t="n">
         <v>0.9780748544525171</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8518055847771716</v>
+        <v>0.8517532898309296</v>
       </c>
       <c r="T11" t="n">
-        <v>76.19561717712371</v>
+        <v>76.19561649961145</v>
       </c>
       <c r="U11" t="n">
         <v>60.7618251414925</v>
       </c>
       <c r="V11" t="n">
-        <v>61.46955898493847</v>
+        <v>61.43768942258599</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34407,10 +34403,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>1105.474682152827</v>
+        <v>1105.548960040827</v>
       </c>
       <c r="D12" t="n">
-        <v>58.18287800804354</v>
+        <v>58.18678737056985</v>
       </c>
       <c r="E12" t="n">
         <v>45.774184448</v>
@@ -34422,7 +34418,7 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>21.93786649204458</v>
+        <v>21.93671661827489</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -34431,40 +34427,40 @@
         <v>0.05263157894736842</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1428725871054494</v>
+        <v>-0.1428725857684479</v>
       </c>
       <c r="L12" t="n">
         <v>-0.147988082348335</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01879944663101604</v>
+        <v>0.01878537455899864</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1398310536796749</v>
+        <v>-0.1398310560235733</v>
       </c>
       <c r="O12" t="n">
         <v>-0.03321478962148972</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04716324201780422</v>
+        <v>0.04715841775120082</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.455449094863042</v>
+        <v>1.455448998110387</v>
       </c>
       <c r="R12" t="n">
         <v>1.078944853452351</v>
       </c>
       <c r="S12" t="n">
-        <v>1.487705606529594</v>
+        <v>1.487590134263205</v>
       </c>
       <c r="T12" t="n">
-        <v>73.75070045692556</v>
+        <v>73.75066767020935</v>
       </c>
       <c r="U12" t="n">
-        <v>11.38261504910467</v>
+        <v>11.38261713566429</v>
       </c>
       <c r="V12" t="n">
-        <v>114.4453066527676</v>
+        <v>114.4388484115061</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34482,13 +34478,13 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>2910.760804767344</v>
+        <v>2903.679979546644</v>
       </c>
       <c r="D13" t="n">
-        <v>138.6076573698735</v>
+        <v>145.1839989773322</v>
       </c>
       <c r="E13" t="n">
-        <v>45.572968448</v>
+        <v>49.58045388799999</v>
       </c>
       <c r="F13" t="n">
         <v>28.09523809523809</v>
@@ -34497,7 +34493,7 @@
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>18.59841674519521</v>
+        <v>18.59760596332955</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
@@ -34506,40 +34502,40 @@
         <v>0.09523809523809523</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2977957642537542</v>
+        <v>0.2977957549418906</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1580849985780295</v>
+        <v>0.1580848603978307</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1672466934967877</v>
+        <v>0.1677376290012675</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5714610404846037</v>
+        <v>0.57146103112196</v>
       </c>
       <c r="O13" t="n">
         <v>0.3192869112915966</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2949718297309641</v>
+        <v>0.2953690477763686</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.088723886558049</v>
+        <v>4.088723797684459</v>
       </c>
       <c r="R13" t="n">
         <v>2.620934187693535</v>
       </c>
       <c r="S13" t="n">
-        <v>5.430330425492961</v>
+        <v>5.435369518259038</v>
       </c>
       <c r="T13" t="n">
-        <v>150.3998809136465</v>
+        <v>150.3998626453796</v>
       </c>
       <c r="U13" t="n">
-        <v>22.86361753800521</v>
+        <v>22.86362023324646</v>
       </c>
       <c r="V13" t="n">
-        <v>257.4580524656704</v>
+        <v>258.0127108836037</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34599,13 +34595,13 @@
         <v>0.6729585466147568</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07217954924075953</v>
+        <v>0.07217944962110456</v>
       </c>
       <c r="R14" t="n">
-        <v>0.07217954924075953</v>
+        <v>0.07217944962110456</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07217954924075953</v>
+        <v>0.07217944962110456</v>
       </c>
       <c r="T14" t="n">
         <v>9.336683619137427</v>
